--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -430,7 +430,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-09-27 18:45:44</t>
+    <t>2026-09-27 20:57:44</t>
   </si>
 </sst>
 </file>
@@ -1024,58 +1024,58 @@
         <v>115</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
         <v>3.65</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1090,10 +1090,10 @@
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>17</v>
@@ -1108,16 +1108,16 @@
         <v>13</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>50</v>
@@ -1132,58 +1132,58 @@
         <v>55</v>
       </c>
       <c r="AP2">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
       </c>
       <c r="AU2">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AV2">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AW2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX2">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AY2">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB2">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC2">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1266,22 +1266,22 @@
         <v>116</v>
       </c>
       <c r="F3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
         <v>2.22</v>
       </c>
       <c r="H3">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
         <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1299,7 +1299,7 @@
         <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
         <v>1.32</v>
@@ -1308,7 +1308,7 @@
         <v>3.45</v>
       </c>
       <c r="T3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
         <v>2.02</v>
@@ -1317,19 +1317,19 @@
         <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X3">
         <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB3">
         <v>11</v>
@@ -1338,10 +1338,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3">
         <v>15.5</v>
@@ -1371,61 +1371,61 @@
         <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP3">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="AR3">
+        <v>4.1</v>
+      </c>
+      <c r="AS3">
+        <v>4.4</v>
+      </c>
+      <c r="AT3">
+        <v>3.25</v>
+      </c>
+      <c r="AU3">
+        <v>3.15</v>
+      </c>
+      <c r="AV3">
+        <v>13</v>
+      </c>
+      <c r="AW3">
+        <v>4.3</v>
+      </c>
+      <c r="AX3">
+        <v>3.6</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
+        <v>15.5</v>
+      </c>
+      <c r="BA3">
+        <v>4.3</v>
+      </c>
+      <c r="BB3">
         <v>4</v>
       </c>
-      <c r="AS3">
+      <c r="BC3">
+        <v>3.95</v>
+      </c>
+      <c r="BD3">
+        <v>4.2</v>
+      </c>
+      <c r="BE3">
+        <v>4.5</v>
+      </c>
+      <c r="BF3">
+        <v>3.75</v>
+      </c>
+      <c r="BG3">
         <v>4.3</v>
-      </c>
-      <c r="AT3">
-        <v>3.2</v>
-      </c>
-      <c r="AU3">
-        <v>3.05</v>
-      </c>
-      <c r="AV3">
-        <v>3.65</v>
-      </c>
-      <c r="AW3">
-        <v>4.2</v>
-      </c>
-      <c r="AX3">
-        <v>3.5</v>
-      </c>
-      <c r="AY3">
-        <v>3.35</v>
-      </c>
-      <c r="AZ3">
-        <v>3.75</v>
-      </c>
-      <c r="BA3">
-        <v>4.2</v>
-      </c>
-      <c r="BB3">
-        <v>3.9</v>
-      </c>
-      <c r="BC3">
-        <v>3.85</v>
-      </c>
-      <c r="BD3">
-        <v>4.1</v>
-      </c>
-      <c r="BE3">
-        <v>4.3</v>
-      </c>
-      <c r="BF3">
-        <v>3.65</v>
-      </c>
-      <c r="BG3">
-        <v>4.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1511,13 +1511,13 @@
         <v>1.1</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>1.1</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4">
         <v>1.1</v>
@@ -1556,10 +1556,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1750,22 +1750,22 @@
         <v>118</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
         <v>6.2</v>
       </c>
       <c r="J5">
+        <v>3.65</v>
+      </c>
+      <c r="K5">
         <v>3.7</v>
-      </c>
-      <c r="K5">
-        <v>3.8</v>
       </c>
       <c r="L5">
         <v>1.54</v>
@@ -1774,25 +1774,25 @@
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
         <v>5.1</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U5">
         <v>1.69</v>
@@ -1804,10 +1804,10 @@
         <v>2.26</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
         <v>46</v>
@@ -1825,22 +1825,22 @@
         <v>26</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI5">
         <v>140</v>
       </c>
       <c r="AJ5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK5">
         <v>25</v>
@@ -1852,13 +1852,13 @@
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
         <v>13.5</v>
@@ -1867,10 +1867,10 @@
         <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
         <v>7.6</v>
@@ -1879,10 +1879,10 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -1891,28 +1891,28 @@
         <v>25</v>
       </c>
       <c r="BA5">
+        <v>10.5</v>
+      </c>
+      <c r="BB5">
+        <v>16</v>
+      </c>
+      <c r="BC5">
+        <v>20</v>
+      </c>
+      <c r="BD5">
         <v>12.5</v>
       </c>
-      <c r="BB5">
-        <v>16.5</v>
-      </c>
-      <c r="BC5">
-        <v>21</v>
-      </c>
-      <c r="BD5">
-        <v>50</v>
-      </c>
       <c r="BE5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>15</v>
       </c>
       <c r="BG5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI5">
         <v>2.64</v>
@@ -1921,10 +1921,10 @@
         <v>15</v>
       </c>
       <c r="BK5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BL5">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="BM5">
         <v>21</v>
@@ -1942,19 +1942,19 @@
         <v>11</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS5">
         <v>26</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU5">
         <v>8.4</v>
       </c>
       <c r="BV5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BW5">
         <v>50</v>
@@ -1966,7 +1966,7 @@
         <v>21</v>
       </c>
       <c r="BZ5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA5">
         <v>24</v>
@@ -2007,10 +2007,10 @@
         <v>2.98</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
         <v>1.14</v>
@@ -2025,13 +2025,13 @@
         <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="R6">
         <v>1.19</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T6">
         <v>2.14</v>
@@ -2046,10 +2046,10 @@
         <v>1.46</v>
       </c>
       <c r="X6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
         <v>17.5</v>
@@ -2085,10 +2085,10 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM6">
         <v>220</v>
@@ -2127,91 +2127,91 @@
         <v>16</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BC6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD6">
         <v>60</v>
       </c>
       <c r="BE6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BF6">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BG6">
         <v>42</v>
       </c>
       <c r="BH6">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BI6">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BK6">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL6">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BQ6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BR6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BS6">
         <v>21</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY6">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BZ6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="CA6">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="s">
         <v>138</v>
@@ -2237,7 +2237,7 @@
         <v>1.51</v>
       </c>
       <c r="G7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H7">
         <v>6.2</v>
@@ -2246,37 +2246,37 @@
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
         <v>2.08</v>
@@ -2285,7 +2285,7 @@
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2294,13 +2294,13 @@
         <v>36</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC7">
         <v>1000</v>
@@ -2312,7 +2312,7 @@
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
         <v>1000</v>
@@ -2327,7 +2327,7 @@
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
         <v>38</v>
@@ -2339,61 +2339,61 @@
         <v>970</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP7">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AQ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR7">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AS7">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AT7">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AU7">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AV7">
         <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AX7">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AY7">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BB7">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BC7">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="BD7">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BE7">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BF7">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="BG7">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2441,7 +2441,7 @@
         <v>70</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX7">
         <v>70</v>
@@ -2450,7 +2450,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2476,16 +2476,16 @@
         <v>121</v>
       </c>
       <c r="F8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I8">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J8">
         <v>3.4</v>
@@ -2494,13 +2494,13 @@
         <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
         <v>1.39</v>
@@ -2515,10 +2515,10 @@
         <v>1.3</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U8">
         <v>2.04</v>
@@ -2548,10 +2548,10 @@
         <v>7.6</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2566,7 +2566,7 @@
         <v>50</v>
       </c>
       <c r="AJ8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK8">
         <v>42</v>
@@ -2611,7 +2611,7 @@
         <v>18.5</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ8">
         <v>16.5</v>
@@ -2620,7 +2620,7 @@
         <v>40</v>
       </c>
       <c r="BB8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC8">
         <v>34</v>
@@ -2632,16 +2632,16 @@
         <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
         <v>22</v>
       </c>
       <c r="BH8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
         <v>12</v>
@@ -2656,7 +2656,7 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO8">
         <v>5.3</v>
@@ -2730,7 +2730,7 @@
         <v>17</v>
       </c>
       <c r="J9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>8.199999999999999</v>
@@ -2742,16 +2742,16 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O9">
         <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R9">
         <v>1.71</v>
@@ -2772,28 +2772,28 @@
         <v>5.3</v>
       </c>
       <c r="X9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y9">
         <v>55</v>
       </c>
       <c r="Z9">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD9">
         <v>70</v>
       </c>
       <c r="AE9">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AF9">
         <v>8</v>
@@ -2802,10 +2802,10 @@
         <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI9">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ9">
         <v>8.800000000000001</v>
@@ -2814,40 +2814,40 @@
         <v>14</v>
       </c>
       <c r="AL9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM9">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN9">
         <v>3.75</v>
       </c>
       <c r="AO9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AP9">
         <v>10.5</v>
       </c>
       <c r="AQ9">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AR9">
+        <v>12.5</v>
+      </c>
+      <c r="AS9">
         <v>13.5</v>
       </c>
-      <c r="AS9">
-        <v>14.5</v>
-      </c>
       <c r="AT9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU9">
         <v>15.5</v>
       </c>
       <c r="AV9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AW9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX9">
         <v>7.2</v>
@@ -2856,10 +2856,10 @@
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB9">
         <v>8</v>
@@ -2871,13 +2871,13 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH9">
         <v>4.5</v>
@@ -2886,10 +2886,10 @@
         <v>4.1</v>
       </c>
       <c r="BJ9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BL9">
         <v>220</v>
@@ -2904,7 +2904,7 @@
         <v>3.4</v>
       </c>
       <c r="BP9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ9">
         <v>6</v>
@@ -2913,22 +2913,22 @@
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BT9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BU9">
         <v>14</v>
       </c>
       <c r="BV9">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BW9">
         <v>21</v>
       </c>
       <c r="BX9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BY9">
         <v>21</v>
@@ -2972,16 +2972,16 @@
         <v>1.07</v>
       </c>
       <c r="J10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
         <v>7.8</v>
@@ -2990,13 +2990,13 @@
         <v>1.12</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
         <v>1.96</v>
@@ -3005,7 +3005,7 @@
         <v>3.95</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
         <v>15</v>
@@ -3032,16 +3032,16 @@
         <v>65</v>
       </c>
       <c r="AD10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF10">
         <v>1000</v>
       </c>
       <c r="AG10">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="AH10">
         <v>170</v>
@@ -3065,10 +3065,10 @@
         <v>1000</v>
       </c>
       <c r="AO10">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AP10">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -3077,64 +3077,64 @@
         <v>6.6</v>
       </c>
       <c r="AS10">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT10">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU10">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV10">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW10">
         <v>19</v>
       </c>
       <c r="AX10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA10">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BB10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BE10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BF10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BH10">
         <v>6.6</v>
       </c>
       <c r="BI10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ10">
         <v>29</v>
       </c>
       <c r="BK10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BL10">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="BM10">
         <v>21</v>
@@ -3143,7 +3143,7 @@
         <v>46</v>
       </c>
       <c r="BO10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BP10">
         <v>690</v>
@@ -3161,10 +3161,10 @@
         <v>3.9</v>
       </c>
       <c r="BU10">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BV10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BW10">
         <v>4</v>
@@ -3173,10 +3173,10 @@
         <v>38</v>
       </c>
       <c r="BY10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BZ10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CA10">
         <v>4.3</v>
@@ -3208,19 +3208,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="J11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K11">
         <v>5.4</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
         <v>1.05</v>
@@ -3229,46 +3229,46 @@
         <v>4.6</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
         <v>2.26</v>
       </c>
       <c r="Q11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S11">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T11">
         <v>2.06</v>
       </c>
       <c r="U11">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="W11">
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AB11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC11">
         <v>12</v>
@@ -3280,10 +3280,10 @@
         <v>15</v>
       </c>
       <c r="AF11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH11">
         <v>26</v>
@@ -3292,28 +3292,28 @@
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AK11">
         <v>150</v>
       </c>
       <c r="AL11">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM11">
         <v>180</v>
       </c>
       <c r="AN11">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AO11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP11">
         <v>17.5</v>
       </c>
       <c r="AQ11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11">
         <v>7.6</v>
@@ -3322,22 +3322,22 @@
         <v>10.5</v>
       </c>
       <c r="AT11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU11">
         <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
         <v>13.5</v>
       </c>
       <c r="AX11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AY11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AZ11">
         <v>24</v>
@@ -3346,13 +3346,13 @@
         <v>32</v>
       </c>
       <c r="BB11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE11">
         <v>100</v>
@@ -3361,19 +3361,19 @@
         <v>140</v>
       </c>
       <c r="BG11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11">
         <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL11">
         <v>180</v>
@@ -3382,13 +3382,13 @@
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BO11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BP11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BQ11">
         <v>21</v>
@@ -3400,16 +3400,16 @@
         <v>21</v>
       </c>
       <c r="BT11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BU11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX11">
         <v>28</v>
@@ -3418,10 +3418,10 @@
         <v>18.5</v>
       </c>
       <c r="BZ11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
         <v>138</v>
@@ -3462,7 +3462,7 @@
         <v>6.2</v>
       </c>
       <c r="L12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M12">
         <v>1.06</v>
@@ -3474,7 +3474,7 @@
         <v>1.33</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
         <v>1.95</v>
@@ -3483,13 +3483,13 @@
         <v>1.37</v>
       </c>
       <c r="S12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V12">
         <v>1.06</v>
@@ -3528,16 +3528,16 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AI12">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AJ12">
         <v>9</v>
       </c>
       <c r="AK12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL12">
         <v>65</v>
@@ -3549,7 +3549,7 @@
         <v>6.2</v>
       </c>
       <c r="AO12">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="AP12">
         <v>14</v>
@@ -3558,7 +3558,7 @@
         <v>32</v>
       </c>
       <c r="AR12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS12">
         <v>15</v>
@@ -3591,7 +3591,7 @@
         <v>8.4</v>
       </c>
       <c r="BC12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD12">
         <v>50</v>
@@ -3606,10 +3606,10 @@
         <v>14.5</v>
       </c>
       <c r="BH12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI12">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3624,16 +3624,16 @@
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BO12">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BP12">
         <v>11</v>
       </c>
       <c r="BQ12">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR12">
         <v>1000</v>
@@ -3645,7 +3645,7 @@
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BV12">
         <v>1000</v>
@@ -3710,7 +3710,7 @@
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O13">
         <v>1.48</v>
@@ -3719,19 +3719,19 @@
         <v>1.64</v>
       </c>
       <c r="Q13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R13">
         <v>1.23</v>
       </c>
       <c r="S13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>2.3</v>
       </c>
       <c r="U13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V13">
         <v>1.17</v>
@@ -3743,7 +3743,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z13">
         <v>55</v>
@@ -3752,7 +3752,7 @@
         <v>280</v>
       </c>
       <c r="AB13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC13">
         <v>8.6</v>
@@ -3764,7 +3764,7 @@
         <v>160</v>
       </c>
       <c r="AF13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3776,7 +3776,7 @@
         <v>160</v>
       </c>
       <c r="AJ13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK13">
         <v>24</v>
@@ -3794,13 +3794,13 @@
         <v>280</v>
       </c>
       <c r="AP13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
         <v>14</v>
       </c>
       <c r="AR13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS13">
         <v>13.5</v>
@@ -3821,7 +3821,7 @@
         <v>7.8</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
         <v>21</v>
@@ -3848,16 +3848,16 @@
         <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3875,7 +3875,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR13">
         <v>1000</v>
@@ -3937,16 +3937,16 @@
         <v>2</v>
       </c>
       <c r="I14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
         <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -3961,7 +3961,7 @@
         <v>1.77</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R14">
         <v>1.29</v>
@@ -3973,10 +3973,10 @@
         <v>2.02</v>
       </c>
       <c r="U14">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W14">
         <v>1.28</v>
@@ -3994,7 +3994,7 @@
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
         <v>8.199999999999999</v>
@@ -4012,7 +4012,7 @@
         <v>18</v>
       </c>
       <c r="AH14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI14">
         <v>46</v>
@@ -4054,7 +4054,7 @@
         <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW14">
         <v>21</v>
@@ -4066,13 +4066,13 @@
         <v>16.5</v>
       </c>
       <c r="AZ14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA14">
         <v>40</v>
       </c>
       <c r="BB14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC14">
         <v>50</v>
@@ -4081,7 +4081,7 @@
         <v>60</v>
       </c>
       <c r="BE14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF14">
         <v>65</v>
@@ -4093,7 +4093,7 @@
         <v>3</v>
       </c>
       <c r="BI14">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ14">
         <v>13</v>
@@ -4108,7 +4108,7 @@
         <v>21</v>
       </c>
       <c r="BN14">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14">
         <v>6.8</v>
@@ -4129,7 +4129,7 @@
         <v>4.5</v>
       </c>
       <c r="BU14">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV14">
         <v>18</v>
@@ -4176,10 +4176,10 @@
         <v>2.34</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J15">
         <v>3.95</v>
@@ -4197,16 +4197,16 @@
         <v>5.6</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q15">
         <v>1.55</v>
       </c>
       <c r="R15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S15">
         <v>2.38</v>
@@ -4218,7 +4218,7 @@
         <v>2.62</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
         <v>1.74</v>
@@ -4248,7 +4248,7 @@
         <v>36</v>
       </c>
       <c r="AF15">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG15">
         <v>14.5</v>
@@ -4275,19 +4275,19 @@
         <v>13</v>
       </c>
       <c r="AO15">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AP15">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AQ15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR15">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT15">
         <v>13</v>
@@ -4311,22 +4311,22 @@
         <v>13</v>
       </c>
       <c r="BA15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB15">
         <v>21</v>
       </c>
       <c r="BC15">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BD15">
         <v>20</v>
       </c>
       <c r="BE15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG15">
         <v>16</v>
@@ -4338,31 +4338,31 @@
         <v>3.5</v>
       </c>
       <c r="BJ15">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BO15">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
@@ -4374,19 +4374,19 @@
         <v>6</v>
       </c>
       <c r="BV15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4415,10 +4415,10 @@
         <v>4</v>
       </c>
       <c r="G16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H16">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I16">
         <v>1.93</v>
@@ -4430,31 +4430,31 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
         <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U16">
         <v>2.18</v>
@@ -4493,7 +4493,7 @@
         <v>34</v>
       </c>
       <c r="AG16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH16">
         <v>18.5</v>
@@ -4514,13 +4514,13 @@
         <v>90</v>
       </c>
       <c r="AN16">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO16">
         <v>11.5</v>
       </c>
       <c r="AP16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
         <v>9.4</v>
@@ -4529,7 +4529,7 @@
         <v>11</v>
       </c>
       <c r="AS16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT16">
         <v>14.5</v>
@@ -4544,7 +4544,7 @@
         <v>16.5</v>
       </c>
       <c r="AX16">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AY16">
         <v>15</v>
@@ -4556,7 +4556,7 @@
         <v>26</v>
       </c>
       <c r="BB16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC16">
         <v>38</v>
@@ -4565,7 +4565,7 @@
         <v>42</v>
       </c>
       <c r="BE16">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16">
         <v>9.800000000000001</v>
@@ -4580,28 +4580,28 @@
         <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL16">
         <v>120</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN16">
         <v>8.6</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR16">
         <v>46</v>
@@ -4613,22 +4613,22 @@
         <v>5</v>
       </c>
       <c r="BU16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX16">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4672,7 +4672,7 @@
         <v>3.95</v>
       </c>
       <c r="L17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M17">
         <v>1.1</v>
@@ -4738,7 +4738,7 @@
         <v>11</v>
       </c>
       <c r="AH17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI17">
         <v>150</v>
@@ -4771,13 +4771,13 @@
         <v>46</v>
       </c>
       <c r="AS17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT17">
         <v>6</v>
       </c>
       <c r="AU17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV17">
         <v>24</v>
@@ -4795,7 +4795,7 @@
         <v>25</v>
       </c>
       <c r="BA17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB17">
         <v>14.5</v>
@@ -4807,7 +4807,7 @@
         <v>44</v>
       </c>
       <c r="BE17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF17">
         <v>12</v>
@@ -4822,19 +4822,19 @@
         <v>2.56</v>
       </c>
       <c r="BJ17">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BK17">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BO17">
         <v>3.45</v>
@@ -4843,37 +4843,37 @@
         <v>30</v>
       </c>
       <c r="BQ17">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BU17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>138</v>
@@ -4899,7 +4899,7 @@
         <v>2.02</v>
       </c>
       <c r="G18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H18">
         <v>3.65</v>
@@ -4920,13 +4920,13 @@
         <v>1.02</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18">
         <v>1.21</v>
       </c>
       <c r="P18">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
         <v>1.62</v>
@@ -4947,7 +4947,7 @@
         <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="X18">
         <v>26</v>
@@ -4962,7 +4962,7 @@
         <v>75</v>
       </c>
       <c r="AB18">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
@@ -5004,16 +5004,16 @@
         <v>32</v>
       </c>
       <c r="AP18">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
         <v>16</v>
       </c>
       <c r="AR18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5025,7 +5025,7 @@
         <v>14</v>
       </c>
       <c r="AW18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5037,7 +5037,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB18">
         <v>19</v>
@@ -5052,13 +5052,13 @@
         <v>6.4</v>
       </c>
       <c r="BF18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18">
         <v>21</v>
       </c>
       <c r="BH18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI18">
         <v>3.4</v>
@@ -5073,7 +5073,7 @@
         <v>95</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN18">
         <v>5.9</v>
@@ -5109,7 +5109,7 @@
         <v>36</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ18">
         <v>19</v>
@@ -5138,10 +5138,10 @@
         <v>132</v>
       </c>
       <c r="F19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H19">
         <v>3.2</v>
@@ -5150,7 +5150,7 @@
         <v>3.5</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -5162,28 +5162,28 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
         <v>1.61</v>
       </c>
       <c r="U19">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V19">
         <v>1.4</v>
@@ -5195,7 +5195,7 @@
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z19">
         <v>30</v>
@@ -5207,7 +5207,7 @@
         <v>16</v>
       </c>
       <c r="AC19">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD19">
         <v>20</v>
@@ -5225,7 +5225,7 @@
         <v>19.5</v>
       </c>
       <c r="AI19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ19">
         <v>32</v>
@@ -5240,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="AN19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO19">
         <v>36</v>
@@ -5258,7 +5258,7 @@
         <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19">
         <v>6.8</v>
@@ -5279,16 +5279,16 @@
         <v>12.5</v>
       </c>
       <c r="BA19">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC19">
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE19">
         <v>1.01</v>
@@ -5333,7 +5333,7 @@
         <v>38</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT19">
         <v>9.800000000000001</v>
@@ -5342,13 +5342,13 @@
         <v>4.4</v>
       </c>
       <c r="BV19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
@@ -5383,7 +5383,7 @@
         <v>1.76</v>
       </c>
       <c r="G20">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
         <v>4.2</v>
@@ -5392,7 +5392,7 @@
         <v>4.9</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>4.8</v>
@@ -5401,10 +5401,10 @@
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="O20">
         <v>1.16</v>
@@ -5416,130 +5416,130 @@
         <v>1.48</v>
       </c>
       <c r="R20">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S20">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U20">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V20">
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y20">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB20">
+        <v>15.5</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>20</v>
+      </c>
+      <c r="AE20">
+        <v>46</v>
+      </c>
+      <c r="AF20">
+        <v>16</v>
+      </c>
+      <c r="AG20">
+        <v>11.5</v>
+      </c>
+      <c r="AH20">
+        <v>16</v>
+      </c>
+      <c r="AI20">
+        <v>44</v>
+      </c>
+      <c r="AJ20">
+        <v>22</v>
+      </c>
+      <c r="AK20">
         <v>18</v>
       </c>
-      <c r="AC20">
+      <c r="AL20">
+        <v>25</v>
+      </c>
+      <c r="AM20">
+        <v>55</v>
+      </c>
+      <c r="AN20">
+        <v>7.4</v>
+      </c>
+      <c r="AO20">
+        <v>32</v>
+      </c>
+      <c r="AP20">
+        <v>21</v>
+      </c>
+      <c r="AQ20">
+        <v>21</v>
+      </c>
+      <c r="AR20">
+        <v>7.4</v>
+      </c>
+      <c r="AS20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV20">
+        <v>16</v>
+      </c>
+      <c r="AW20">
+        <v>7.6</v>
+      </c>
+      <c r="AX20">
         <v>13</v>
       </c>
-      <c r="AD20">
-        <v>26</v>
-      </c>
-      <c r="AE20">
-        <v>55</v>
-      </c>
-      <c r="AF20">
-        <v>19</v>
-      </c>
-      <c r="AG20">
+      <c r="AY20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20">
         <v>13</v>
       </c>
-      <c r="AH20">
-        <v>19</v>
-      </c>
-      <c r="AI20">
-        <v>55</v>
-      </c>
-      <c r="AJ20">
-        <v>29</v>
-      </c>
-      <c r="AK20">
-        <v>21</v>
-      </c>
-      <c r="AL20">
-        <v>34</v>
-      </c>
-      <c r="AM20">
-        <v>75</v>
-      </c>
-      <c r="AN20">
-        <v>8.4</v>
-      </c>
-      <c r="AO20">
-        <v>40</v>
-      </c>
-      <c r="AP20">
-        <v>3.5</v>
-      </c>
-      <c r="AQ20">
-        <v>3.2</v>
-      </c>
-      <c r="AR20">
-        <v>3.3</v>
-      </c>
-      <c r="AS20">
-        <v>3.4</v>
-      </c>
-      <c r="AT20">
-        <v>10.5</v>
-      </c>
-      <c r="AU20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>12.5</v>
-      </c>
-      <c r="AW20">
-        <v>3.35</v>
-      </c>
-      <c r="AX20">
-        <v>11.5</v>
-      </c>
-      <c r="AY20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ20">
-        <v>11</v>
-      </c>
       <c r="BA20">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BB20">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC20">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD20">
-        <v>3.2</v>
+        <v>20</v>
       </c>
       <c r="BE20">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="BF20">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG20">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5569,7 +5569,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR20">
         <v>28</v>
@@ -5631,10 +5631,10 @@
         <v>3.05</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
         <v>3.9</v>
@@ -5649,7 +5649,7 @@
         <v>4.1</v>
       </c>
       <c r="O21">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P21">
         <v>2.08</v>
@@ -5661,7 +5661,7 @@
         <v>1.43</v>
       </c>
       <c r="S21">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T21">
         <v>1.65</v>
@@ -5670,16 +5670,16 @@
         <v>2.26</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
         <v>1.67</v>
       </c>
       <c r="X21">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z21">
         <v>26</v>
@@ -5694,13 +5694,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21">
         <v>12</v>
@@ -5724,7 +5724,7 @@
         <v>85</v>
       </c>
       <c r="AN21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO21">
         <v>30</v>
@@ -5739,7 +5739,7 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5751,7 +5751,7 @@
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX21">
         <v>13.5</v>
@@ -5763,25 +5763,25 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB21">
-        <v>5.8</v>
+        <v>25</v>
       </c>
       <c r="BC21">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD21">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF21">
         <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -5799,7 +5799,7 @@
         <v>110</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN21">
         <v>6.2</v>
@@ -5817,7 +5817,7 @@
         <v>32</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT21">
         <v>7.4</v>
@@ -5835,7 +5835,7 @@
         <v>38</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ21">
         <v>25</v>
@@ -5888,10 +5888,10 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P22">
         <v>2.84</v>
@@ -5900,28 +5900,28 @@
         <v>1.48</v>
       </c>
       <c r="R22">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S22">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="U22">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
         <v>1.62</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y22">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z22">
         <v>24</v>
@@ -5930,28 +5930,28 @@
         <v>38</v>
       </c>
       <c r="AB22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE22">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF22">
         <v>24</v>
       </c>
       <c r="AG22">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH22">
         <v>17</v>
       </c>
       <c r="AI22">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
         <v>40</v>
@@ -5963,40 +5963,40 @@
         <v>29</v>
       </c>
       <c r="AM22">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP22">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AR22">
-        <v>4.8</v>
+        <v>19</v>
       </c>
       <c r="AS22">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT22">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AU22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV22">
         <v>11</v>
       </c>
       <c r="AW22">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AX22">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="AY22">
         <v>11</v>
@@ -6005,25 +6005,25 @@
         <v>12.5</v>
       </c>
       <c r="BA22">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BB22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BC22">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD22">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BE22">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF22">
         <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6041,13 +6041,13 @@
         <v>85</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN22">
         <v>8.800000000000001</v>
       </c>
       <c r="BO22">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
         <v>24</v>
@@ -6065,7 +6065,7 @@
         <v>8.6</v>
       </c>
       <c r="BU22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV22">
         <v>23</v>
@@ -6106,13 +6106,13 @@
         <v>136</v>
       </c>
       <c r="F23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G23">
         <v>4.9</v>
       </c>
       <c r="H23">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I23">
         <v>1.82</v>
@@ -6133,22 +6133,22 @@
         <v>4.8</v>
       </c>
       <c r="O23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23">
         <v>2.32</v>
       </c>
       <c r="Q23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R23">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S23">
         <v>2.68</v>
       </c>
       <c r="T23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U23">
         <v>2.26</v>
@@ -6175,7 +6175,7 @@
         <v>21</v>
       </c>
       <c r="AC23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>10.5</v>
@@ -6190,7 +6190,7 @@
         <v>18.5</v>
       </c>
       <c r="AH23">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI23">
         <v>29</v>
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="AK23">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL23">
         <v>60</v>
@@ -6208,10 +6208,10 @@
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP23">
         <v>19</v>
@@ -6250,7 +6250,7 @@
         <v>24</v>
       </c>
       <c r="BB23">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="BC23">
         <v>44</v>
@@ -6259,10 +6259,10 @@
         <v>44</v>
       </c>
       <c r="BE23">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="BF23">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BG23">
         <v>7.8</v>
@@ -6295,19 +6295,19 @@
         <v>50</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR23">
         <v>55</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT23">
         <v>6.4</v>
       </c>
       <c r="BU23">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV23">
         <v>17</v>
@@ -6319,7 +6319,7 @@
         <v>32</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ23">
         <v>23</v>
@@ -6348,10 +6348,10 @@
         <v>137</v>
       </c>
       <c r="F24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G24">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>1.91</v>
@@ -6369,7 +6369,7 @@
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24">
         <v>3.25</v>
@@ -6384,7 +6384,7 @@
         <v>2.12</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S24">
         <v>4</v>
@@ -6393,121 +6393,121 @@
         <v>1.94</v>
       </c>
       <c r="U24">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V24">
         <v>1.98</v>
       </c>
       <c r="W24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y24">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC24">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK24">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL24">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24">
-        <v>1.16</v>
+        <v>7</v>
       </c>
       <c r="AR24">
-        <v>1.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS24">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="AT24">
-        <v>1.29</v>
+        <v>12.5</v>
       </c>
       <c r="AU24">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="AV24">
-        <v>1.29</v>
+        <v>9.4</v>
       </c>
       <c r="AW24">
-        <v>1.29</v>
+        <v>4.7</v>
       </c>
       <c r="AX24">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="AY24">
-        <v>1.29</v>
+        <v>16.5</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="BA24">
-        <v>1.29</v>
+        <v>5.1</v>
       </c>
       <c r="BB24">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="BC24">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="BD24">
-        <v>1.27</v>
+        <v>5.4</v>
       </c>
       <c r="BE24">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="BF24">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="BG24">
-        <v>1.29</v>
+        <v>4.7</v>
       </c>
       <c r="BH24">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -430,7 +430,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-09-27 20:57:44</t>
+    <t>2026-09-27 23:08:39</t>
   </si>
 </sst>
 </file>
@@ -1024,22 +1024,22 @@
         <v>115</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1051,40 +1051,40 @@
         <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>75</v>
@@ -1093,19 +1093,19 @@
         <v>9</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
         <v>20</v>
@@ -1114,13 +1114,13 @@
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>30</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM2">
         <v>140</v>
@@ -1132,7 +1132,7 @@
         <v>55</v>
       </c>
       <c r="AP2">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1141,49 +1141,49 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
       </c>
       <c r="AU2">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>6.6</v>
+      </c>
+      <c r="BC2">
         <v>6.2</v>
       </c>
-      <c r="BB2">
+      <c r="BD2">
+        <v>6.6</v>
+      </c>
+      <c r="BE2">
+        <v>7</v>
+      </c>
+      <c r="BF2">
         <v>5.7</v>
       </c>
-      <c r="BC2">
-        <v>5.6</v>
-      </c>
-      <c r="BD2">
-        <v>6</v>
-      </c>
-      <c r="BE2">
-        <v>6.6</v>
-      </c>
-      <c r="BF2">
-        <v>5.4</v>
-      </c>
       <c r="BG2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1266,46 +1266,46 @@
         <v>116</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P3">
         <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
         <v>1.32</v>
       </c>
       <c r="S3">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
         <v>1.79</v>
@@ -1314,31 +1314,31 @@
         <v>2.02</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="X3">
         <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB3">
         <v>11</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE3">
         <v>60</v>
@@ -1347,7 +1347,7 @@
         <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>23</v>
@@ -1359,7 +1359,7 @@
         <v>30</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3">
         <v>48</v>
@@ -1377,28 +1377,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS3">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AU3">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AV3">
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AX3">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1407,25 +1407,25 @@
         <v>15.5</v>
       </c>
       <c r="BA3">
+        <v>5.1</v>
+      </c>
+      <c r="BB3">
+        <v>4.7</v>
+      </c>
+      <c r="BC3">
+        <v>4.5</v>
+      </c>
+      <c r="BD3">
+        <v>4.9</v>
+      </c>
+      <c r="BE3">
+        <v>5.3</v>
+      </c>
+      <c r="BF3">
         <v>4.3</v>
       </c>
-      <c r="BB3">
-        <v>4</v>
-      </c>
-      <c r="BC3">
-        <v>3.95</v>
-      </c>
-      <c r="BD3">
-        <v>4.2</v>
-      </c>
-      <c r="BE3">
-        <v>4.5</v>
-      </c>
-      <c r="BF3">
-        <v>3.75</v>
-      </c>
       <c r="BG3">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1520,7 +1520,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K4">
         <v>920</v>
@@ -1535,13 +1535,13 @@
         <v>1.09</v>
       </c>
       <c r="O4">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R4">
         <v>1.08</v>
@@ -1556,10 +1556,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1834,7 +1834,7 @@
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI5">
         <v>140</v>
@@ -1903,7 +1903,7 @@
         <v>12.5</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF5">
         <v>15</v>
@@ -1912,7 +1912,7 @@
         <v>10.5</v>
       </c>
       <c r="BH5">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BI5">
         <v>2.64</v>
@@ -2025,7 +2025,7 @@
         <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="R6">
         <v>1.19</v>
@@ -2046,7 +2046,7 @@
         <v>1.46</v>
       </c>
       <c r="X6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y6">
         <v>8.6</v>
@@ -2076,7 +2076,7 @@
         <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI6">
         <v>75</v>
@@ -2112,7 +2112,7 @@
         <v>42</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2121,13 +2121,13 @@
         <v>12.5</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
         <v>16</v>
       </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
         <v>21</v>
@@ -2136,19 +2136,19 @@
         <v>60</v>
       </c>
       <c r="BB6">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BD6">
         <v>60</v>
       </c>
       <c r="BE6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF6">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BG6">
         <v>42</v>
@@ -2160,10 +2160,10 @@
         <v>2.28</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK6">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2172,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO6">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>40</v>
       </c>
       <c r="BQ6">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BR6">
         <v>70</v>
@@ -2237,7 +2237,7 @@
         <v>1.51</v>
       </c>
       <c r="G7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H7">
         <v>6.2</v>
@@ -2258,7 +2258,7 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="O7">
         <v>1.19</v>
@@ -2285,7 +2285,7 @@
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2294,7 +2294,7 @@
         <v>36</v>
       </c>
       <c r="Z7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2312,7 +2312,7 @@
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
         <v>1000</v>
@@ -2342,58 +2342,58 @@
         <v>100</v>
       </c>
       <c r="AP7">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7">
         <v>19</v>
       </c>
       <c r="AR7">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AS7">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AT7">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AU7">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AV7">
         <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AX7">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AY7">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="BB7">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="BC7">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="BD7">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="BE7">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="BF7">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="BG7">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="BO7">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
@@ -2447,7 +2447,7 @@
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ7">
         <v>19</v>
@@ -2494,7 +2494,7 @@
         <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
         <v>1.09</v>
@@ -2506,7 +2506,7 @@
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q8">
         <v>2.16</v>
@@ -2518,7 +2518,7 @@
         <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U8">
         <v>2.04</v>
@@ -2563,10 +2563,10 @@
         <v>19</v>
       </c>
       <c r="AI8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK8">
         <v>42</v>
@@ -2581,7 +2581,7 @@
         <v>44</v>
       </c>
       <c r="AO8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP8">
         <v>10.5</v>
@@ -2620,7 +2620,7 @@
         <v>40</v>
       </c>
       <c r="BB8">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BC8">
         <v>34</v>
@@ -2632,7 +2632,7 @@
         <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BG8">
         <v>22</v>
@@ -2647,7 +2647,7 @@
         <v>12</v>
       </c>
       <c r="BK8">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2656,7 +2656,7 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO8">
         <v>5.3</v>
@@ -2674,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
         <v>4.5</v>
@@ -2724,16 +2724,16 @@
         <v>1.23</v>
       </c>
       <c r="H9">
+        <v>16</v>
+      </c>
+      <c r="I9">
         <v>16.5</v>
       </c>
-      <c r="I9">
-        <v>17</v>
-      </c>
       <c r="J9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L9">
         <v>1.29</v>
@@ -2745,7 +2745,7 @@
         <v>6.2</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
         <v>2.78</v>
@@ -2757,7 +2757,7 @@
         <v>1.71</v>
       </c>
       <c r="S9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
         <v>2.26</v>
@@ -2769,10 +2769,10 @@
         <v>1.06</v>
       </c>
       <c r="W9">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y9">
         <v>55</v>
@@ -2784,10 +2784,10 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AD9">
         <v>70</v>
@@ -2826,28 +2826,28 @@
         <v>500</v>
       </c>
       <c r="AP9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AR9">
+        <v>12</v>
+      </c>
+      <c r="AS9">
         <v>12.5</v>
       </c>
-      <c r="AS9">
-        <v>13.5</v>
-      </c>
       <c r="AT9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV9">
         <v>42</v>
       </c>
       <c r="AW9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX9">
         <v>7.2</v>
@@ -2859,7 +2859,7 @@
         <v>30</v>
       </c>
       <c r="BA9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB9">
         <v>8</v>
@@ -2871,13 +2871,13 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BF9">
         <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>4.5</v>
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="BN9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO9">
         <v>3.4</v>
@@ -2919,7 +2919,7 @@
         <v>18</v>
       </c>
       <c r="BU9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BV9">
         <v>180</v>
@@ -2963,7 +2963,7 @@
         <v>50</v>
       </c>
       <c r="G10">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H10">
         <v>1.06</v>
@@ -2978,34 +2978,34 @@
         <v>23</v>
       </c>
       <c r="L10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="O10">
         <v>1.12</v>
       </c>
       <c r="P10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="T10">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="U10">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V10">
         <v>15</v>
@@ -3014,40 +3014,40 @@
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AB10">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AC10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AD10">
         <v>25</v>
       </c>
       <c r="AE10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF10">
         <v>1000</v>
       </c>
       <c r="AG10">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AH10">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AI10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3065,121 +3065,121 @@
         <v>1000</v>
       </c>
       <c r="AO10">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AP10">
+        <v>10.5</v>
+      </c>
+      <c r="AQ10">
         <v>10</v>
       </c>
-      <c r="AQ10">
-        <v>10.5</v>
-      </c>
       <c r="AR10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS10">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV10">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY10">
         <v>12</v>
       </c>
       <c r="AZ10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA10">
         <v>11.5</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BH10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BK10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BL10">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
         <v>21</v>
       </c>
       <c r="BN10">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BO10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BP10">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>21</v>
       </c>
       <c r="BR10">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>21</v>
       </c>
       <c r="BT10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU10">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="BV10">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BW10">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="BX10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BY10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BZ10">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CA10">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="CB10" t="s">
         <v>138</v>
@@ -3208,10 +3208,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J11">
         <v>5.2</v>
@@ -3232,7 +3232,7 @@
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
         <v>1.75</v>
@@ -3247,16 +3247,16 @@
         <v>2.06</v>
       </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W11">
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y11">
         <v>8.800000000000001</v>
@@ -3292,10 +3292,10 @@
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AK11">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AL11">
         <v>130</v>
@@ -3307,7 +3307,7 @@
         <v>190</v>
       </c>
       <c r="AO11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP11">
         <v>17.5</v>
@@ -3331,13 +3331,13 @@
         <v>9.4</v>
       </c>
       <c r="AW11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX11">
         <v>75</v>
       </c>
       <c r="AY11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AZ11">
         <v>24</v>
@@ -3346,13 +3346,13 @@
         <v>32</v>
       </c>
       <c r="BB11">
+        <v>22</v>
+      </c>
+      <c r="BC11">
         <v>20</v>
       </c>
-      <c r="BC11">
-        <v>19</v>
-      </c>
       <c r="BD11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE11">
         <v>100</v>
@@ -3361,7 +3361,7 @@
         <v>140</v>
       </c>
       <c r="BG11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH11">
         <v>3.9</v>
@@ -3468,7 +3468,7 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O12">
         <v>1.33</v>
@@ -3480,7 +3480,7 @@
         <v>1.95</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
         <v>3.45</v>
@@ -3534,16 +3534,16 @@
         <v>330</v>
       </c>
       <c r="AJ12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL12">
         <v>65</v>
       </c>
       <c r="AM12">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AN12">
         <v>6.2</v>
@@ -3558,10 +3558,10 @@
         <v>32</v>
       </c>
       <c r="AR12">
+        <v>13</v>
+      </c>
+      <c r="AS12">
         <v>14</v>
-      </c>
-      <c r="AS12">
-        <v>15</v>
       </c>
       <c r="AT12">
         <v>6.2</v>
@@ -3570,10 +3570,10 @@
         <v>12.5</v>
       </c>
       <c r="AV12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX12">
         <v>6</v>
@@ -3585,7 +3585,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB12">
         <v>8.4</v>
@@ -3597,13 +3597,13 @@
         <v>50</v>
       </c>
       <c r="BE12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH12">
         <v>3.8</v>
@@ -3716,7 +3716,7 @@
         <v>1.48</v>
       </c>
       <c r="P13">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q13">
         <v>2.44</v>
@@ -3806,7 +3806,7 @@
         <v>13.5</v>
       </c>
       <c r="AT13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU13">
         <v>7.6</v>
@@ -3928,7 +3928,7 @@
         <v>127</v>
       </c>
       <c r="F14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G14">
         <v>4.5</v>
@@ -3961,7 +3961,7 @@
         <v>1.77</v>
       </c>
       <c r="Q14">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
         <v>1.29</v>
@@ -3994,7 +3994,7 @@
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC14">
         <v>8.199999999999999</v>
@@ -4060,7 +4060,7 @@
         <v>21</v>
       </c>
       <c r="AX14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY14">
         <v>16.5</v>
@@ -4072,7 +4072,7 @@
         <v>40</v>
       </c>
       <c r="BB14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC14">
         <v>50</v>
@@ -4081,7 +4081,7 @@
         <v>60</v>
       </c>
       <c r="BE14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF14">
         <v>65</v>
@@ -4090,64 +4090,64 @@
         <v>15</v>
       </c>
       <c r="BH14">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BI14">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL14">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>138</v>
@@ -4206,7 +4206,7 @@
         <v>1.55</v>
       </c>
       <c r="R15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
         <v>2.38</v>
@@ -4383,7 +4383,7 @@
         <v>32</v>
       </c>
       <c r="BY15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>18</v>
@@ -4415,16 +4415,16 @@
         <v>4</v>
       </c>
       <c r="G16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H16">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I16">
         <v>1.93</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
         <v>4.3</v>
@@ -4439,25 +4439,25 @@
         <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
         <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T16">
         <v>1.69</v>
       </c>
       <c r="U16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
         <v>2.06</v>
@@ -4475,7 +4475,7 @@
         <v>13.5</v>
       </c>
       <c r="AA16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB16">
         <v>18</v>
@@ -4496,13 +4496,13 @@
         <v>18</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK16">
         <v>50</v>
@@ -4517,13 +4517,13 @@
         <v>46</v>
       </c>
       <c r="AO16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP16">
         <v>15.5</v>
       </c>
       <c r="AQ16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16">
         <v>11</v>
@@ -4541,7 +4541,7 @@
         <v>9.4</v>
       </c>
       <c r="AW16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX16">
         <v>29</v>
@@ -4556,19 +4556,19 @@
         <v>26</v>
       </c>
       <c r="BB16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD16">
         <v>42</v>
       </c>
       <c r="BE16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG16">
         <v>9.6</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="BP16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BQ16">
         <v>1.02</v>
@@ -4613,10 +4613,10 @@
         <v>5</v>
       </c>
       <c r="BU16">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BV16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW16">
         <v>10</v>
@@ -4625,10 +4625,10 @@
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4696,7 +4696,7 @@
         <v>4.6</v>
       </c>
       <c r="T17">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U17">
         <v>1.72</v>
@@ -4777,7 +4777,7 @@
         <v>6</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17">
         <v>24</v>
@@ -4822,7 +4822,7 @@
         <v>2.56</v>
       </c>
       <c r="BJ17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
         <v>9.199999999999999</v>
@@ -4914,7 +4914,7 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M18">
         <v>1.02</v>
@@ -4926,7 +4926,7 @@
         <v>1.21</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q18">
         <v>1.62</v>
@@ -5079,7 +5079,7 @@
         <v>5.9</v>
       </c>
       <c r="BO18">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP18">
         <v>15.5</v>
@@ -5138,7 +5138,7 @@
         <v>132</v>
       </c>
       <c r="F19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G19">
         <v>2.36</v>
@@ -5162,22 +5162,22 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O19">
         <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T19">
         <v>1.61</v>
@@ -5324,7 +5324,7 @@
         <v>3.45</v>
       </c>
       <c r="BP19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
@@ -5333,7 +5333,7 @@
         <v>38</v>
       </c>
       <c r="BS19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
         <v>9.800000000000001</v>
@@ -5351,7 +5351,7 @@
         <v>50</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ19">
         <v>30</v>
@@ -5383,7 +5383,7 @@
         <v>1.76</v>
       </c>
       <c r="G20">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H20">
         <v>4.2</v>
@@ -5392,7 +5392,7 @@
         <v>4.9</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
         <v>4.8</v>
@@ -5404,7 +5404,7 @@
         <v>1.03</v>
       </c>
       <c r="N20">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O20">
         <v>1.16</v>
@@ -5431,7 +5431,7 @@
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X20">
         <v>30</v>
@@ -5557,7 +5557,7 @@
         <v>95</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN20">
         <v>6.6</v>
@@ -5569,7 +5569,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>28</v>
@@ -5593,7 +5593,7 @@
         <v>44</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ20">
         <v>17.5</v>
@@ -5646,7 +5646,7 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
         <v>1.26</v>
@@ -5691,7 +5691,7 @@
         <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD21">
         <v>16</v>
@@ -5724,7 +5724,7 @@
         <v>85</v>
       </c>
       <c r="AN21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO21">
         <v>30</v>
@@ -5751,7 +5751,7 @@
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX21">
         <v>13.5</v>
@@ -5763,7 +5763,7 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB21">
         <v>25</v>
@@ -5772,16 +5772,16 @@
         <v>20</v>
       </c>
       <c r="BD21">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF21">
         <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -6172,7 +6172,7 @@
         <v>20</v>
       </c>
       <c r="AB23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -6190,7 +6190,7 @@
         <v>18.5</v>
       </c>
       <c r="AH23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI23">
         <v>29</v>
@@ -6250,7 +6250,7 @@
         <v>24</v>
       </c>
       <c r="BB23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC23">
         <v>44</v>
@@ -6259,10 +6259,10 @@
         <v>44</v>
       </c>
       <c r="BE23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG23">
         <v>7.8</v>
@@ -6319,7 +6319,7 @@
         <v>32</v>
       </c>
       <c r="BY23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
         <v>23</v>
@@ -6354,7 +6354,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I24">
         <v>2.02</v>
@@ -6465,7 +6465,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS24">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AT24">
         <v>12.5</v>
@@ -6477,7 +6477,7 @@
         <v>9.4</v>
       </c>
       <c r="AW24">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="AX24">
         <v>5</v>
@@ -6489,16 +6489,16 @@
         <v>4.6</v>
       </c>
       <c r="BA24">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB24">
         <v>5.5</v>
       </c>
       <c r="BC24">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD24">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE24">
         <v>5.5</v>
@@ -6507,7 +6507,7 @@
         <v>5.5</v>
       </c>
       <c r="BG24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH24">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-09-29</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>Jamaica</t>
   </si>
   <si>
@@ -310,6 +316,9 @@
     <t>Boreham Wood</t>
   </si>
   <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
     <t>Luxembourg</t>
   </si>
   <si>
@@ -337,9 +346,6 @@
     <t>Hartlepool</t>
   </si>
   <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
     <t>Woking</t>
   </si>
   <si>
@@ -361,6 +367,9 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Honduras</t>
   </si>
   <si>
@@ -379,6 +388,9 @@
     <t>Kidderminster</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>Iceland</t>
   </si>
   <si>
@@ -406,9 +418,6 @@
     <t>Harrogate Town</t>
   </si>
   <si>
-    <t>North Macedonia</t>
-  </si>
-  <si>
     <t>Solihull Moors</t>
   </si>
   <si>
@@ -430,7 +439,10 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-09-27 23:08:39</t>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>2026-09-28 01:19:23</t>
   </si>
 </sst>
 </file>
@@ -762,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1012,43 +1024,43 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.4</v>
@@ -1057,7 +1069,7 @@
         <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
         <v>1.3</v>
@@ -1066,13 +1078,13 @@
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
         <v>1.71</v>
@@ -1081,7 +1093,7 @@
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
         <v>24</v>
@@ -1093,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>15.5</v>
@@ -1105,10 +1117,10 @@
         <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2">
         <v>65</v>
@@ -1126,7 +1138,7 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO2">
         <v>55</v>
@@ -1141,7 +1153,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
@@ -1153,7 +1165,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1162,28 +1174,28 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD2">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1246,7 +1258,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1254,70 +1266,70 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F3">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G3">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
         <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R3">
+        <v>1.33</v>
+      </c>
+      <c r="S3">
+        <v>3.7</v>
+      </c>
+      <c r="T3">
+        <v>1.82</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
         <v>1.32</v>
       </c>
-      <c r="S3">
-        <v>3.95</v>
-      </c>
-      <c r="T3">
-        <v>1.79</v>
-      </c>
-      <c r="U3">
-        <v>2.02</v>
-      </c>
-      <c r="V3">
-        <v>1.35</v>
-      </c>
       <c r="W3">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
         <v>16.5</v>
@@ -1341,13 +1353,13 @@
         <v>19</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
@@ -1356,10 +1368,10 @@
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL3">
         <v>48</v>
@@ -1380,22 +1392,22 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AV3">
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
         <v>4.1</v>
@@ -1407,26 +1419,26 @@
         <v>15.5</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
+        <v>4.8</v>
+      </c>
+      <c r="BC3">
         <v>4.7</v>
       </c>
-      <c r="BC3">
+      <c r="BD3">
+        <v>5.2</v>
+      </c>
+      <c r="BE3">
+        <v>5.6</v>
+      </c>
+      <c r="BF3">
         <v>4.5</v>
       </c>
-      <c r="BD3">
-        <v>4.9</v>
-      </c>
-      <c r="BE3">
+      <c r="BG3">
         <v>5.3</v>
       </c>
-      <c r="BF3">
-        <v>4.3</v>
-      </c>
-      <c r="BG3">
-        <v>5.1</v>
-      </c>
       <c r="BH3">
         <v>1000</v>
       </c>
@@ -1488,7 +1500,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1496,16 +1508,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F4">
         <v>1.1</v>
@@ -1520,7 +1532,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="K4">
         <v>920</v>
@@ -1532,7 +1544,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="O4">
         <v>1.42</v>
@@ -1556,10 +1568,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1730,7 +1742,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1738,16 +1750,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F5">
         <v>1.78</v>
@@ -1780,7 +1792,7 @@
         <v>1.5</v>
       </c>
       <c r="P5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q5">
         <v>2.48</v>
@@ -1828,7 +1840,7 @@
         <v>130</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1837,7 +1849,7 @@
         <v>30</v>
       </c>
       <c r="AI5">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
         <v>19</v>
@@ -1864,10 +1876,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -1879,7 +1891,7 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX5">
         <v>8</v>
@@ -1891,7 +1903,7 @@
         <v>25</v>
       </c>
       <c r="BA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB5">
         <v>16</v>
@@ -1915,7 +1927,7 @@
         <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
         <v>15</v>
@@ -1972,7 +1984,7 @@
         <v>24</v>
       </c>
       <c r="CB5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1980,16 +1992,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F6">
         <v>3.05</v>
@@ -2016,25 +2028,25 @@
         <v>1.14</v>
       </c>
       <c r="N6">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P6">
         <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R6">
         <v>1.19</v>
       </c>
       <c r="S6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
         <v>1.81</v>
@@ -2046,7 +2058,7 @@
         <v>1.46</v>
       </c>
       <c r="X6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y6">
         <v>8.6</v>
@@ -2070,7 +2082,7 @@
         <v>44</v>
       </c>
       <c r="AF6">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
         <v>14.5</v>
@@ -2088,7 +2100,7 @@
         <v>60</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AM6">
         <v>220</v>
@@ -2121,13 +2133,13 @@
         <v>12.5</v>
       </c>
       <c r="AW6">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AX6">
         <v>16</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
         <v>21</v>
@@ -2136,7 +2148,7 @@
         <v>60</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BC6">
         <v>34</v>
@@ -2175,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="BO6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BP6">
         <v>40</v>
@@ -2190,7 +2202,7 @@
         <v>21</v>
       </c>
       <c r="BT6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
         <v>4.7</v>
@@ -2214,7 +2226,7 @@
         <v>21</v>
       </c>
       <c r="CB6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2222,16 +2234,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F7">
         <v>1.51</v>
@@ -2258,7 +2270,7 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
         <v>1.19</v>
@@ -2291,7 +2303,7 @@
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
         <v>1000</v>
@@ -2306,13 +2318,13 @@
         <v>1000</v>
       </c>
       <c r="AD7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
         <v>1000</v>
@@ -2330,7 +2342,7 @@
         <v>1000</v>
       </c>
       <c r="AL7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2354,10 +2366,10 @@
         <v>1.45</v>
       </c>
       <c r="AT7">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7">
-        <v>1.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7">
         <v>17.5</v>
@@ -2366,7 +2378,7 @@
         <v>1.3</v>
       </c>
       <c r="AX7">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AY7">
         <v>1.45</v>
@@ -2384,7 +2396,7 @@
         <v>1.45</v>
       </c>
       <c r="BD7">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BE7">
         <v>1.3</v>
@@ -2393,7 +2405,7 @@
         <v>1.23</v>
       </c>
       <c r="BG7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2417,7 +2429,7 @@
         <v>6</v>
       </c>
       <c r="BO7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
@@ -2456,7 +2468,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2464,190 +2476,190 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="H8">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="I8">
-        <v>2.54</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.45</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P8">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="V8">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
-        <v>1.44</v>
+        <v>2.44</v>
       </c>
       <c r="X8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="AA8">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AE8">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AI8">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>16.5</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AL8">
         <v>55</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AN8">
+        <v>14</v>
+      </c>
+      <c r="AO8">
+        <v>220</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>14.5</v>
+      </c>
+      <c r="AR8">
+        <v>46</v>
+      </c>
+      <c r="AS8">
+        <v>13.5</v>
+      </c>
+      <c r="AT8">
+        <v>6</v>
+      </c>
+      <c r="AU8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV8">
+        <v>24</v>
+      </c>
+      <c r="AW8">
+        <v>14.5</v>
+      </c>
+      <c r="AX8">
+        <v>7.6</v>
+      </c>
+      <c r="AY8">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8">
+        <v>25</v>
+      </c>
+      <c r="BA8">
+        <v>13.5</v>
+      </c>
+      <c r="BB8">
+        <v>14.5</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
         <v>44</v>
-      </c>
-      <c r="AO8">
-        <v>29</v>
-      </c>
-      <c r="AP8">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR8">
-        <v>13.5</v>
-      </c>
-      <c r="AS8">
-        <v>30</v>
-      </c>
-      <c r="AT8">
-        <v>10.5</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>10.5</v>
-      </c>
-      <c r="AW8">
-        <v>25</v>
-      </c>
-      <c r="AX8">
-        <v>18.5</v>
-      </c>
-      <c r="AY8">
-        <v>13</v>
-      </c>
-      <c r="AZ8">
-        <v>16.5</v>
-      </c>
-      <c r="BA8">
-        <v>40</v>
-      </c>
-      <c r="BB8">
-        <v>50</v>
-      </c>
-      <c r="BC8">
-        <v>34</v>
-      </c>
-      <c r="BD8">
-        <v>46</v>
       </c>
       <c r="BE8">
         <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BG8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BH8">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2656,49 +2668,49 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO8">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP8">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BQ8">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS8">
         <v>21</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV8">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BX8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CA8">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2706,241 +2718,241 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F9">
-        <v>1.22</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
-        <v>1.23</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="I9">
-        <v>16.5</v>
+        <v>2.54</v>
       </c>
       <c r="J9">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>8.6</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="P9">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q9">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="U9">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
-        <v>1.06</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="X9">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="Y9">
+        <v>9.6</v>
+      </c>
+      <c r="Z9">
+        <v>15.5</v>
+      </c>
+      <c r="AA9">
+        <v>36</v>
+      </c>
+      <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
+        <v>7.6</v>
+      </c>
+      <c r="AD9">
+        <v>12</v>
+      </c>
+      <c r="AE9">
+        <v>34</v>
+      </c>
+      <c r="AF9">
+        <v>22</v>
+      </c>
+      <c r="AG9">
+        <v>14.5</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
         <v>55</v>
       </c>
-      <c r="Z9">
-        <v>200</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
+      <c r="AJ9">
+        <v>65</v>
+      </c>
+      <c r="AK9">
+        <v>42</v>
+      </c>
+      <c r="AL9">
+        <v>55</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
+        <v>44</v>
+      </c>
+      <c r="AO9">
+        <v>27</v>
+      </c>
+      <c r="AP9">
         <v>10.5</v>
       </c>
-      <c r="AC9">
+      <c r="AQ9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>30</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>6.8</v>
+      </c>
+      <c r="AV9">
+        <v>10.5</v>
+      </c>
+      <c r="AW9">
+        <v>25</v>
+      </c>
+      <c r="AX9">
+        <v>18.5</v>
+      </c>
+      <c r="AY9">
+        <v>13</v>
+      </c>
+      <c r="AZ9">
+        <v>17.5</v>
+      </c>
+      <c r="BA9">
+        <v>40</v>
+      </c>
+      <c r="BB9">
+        <v>12.5</v>
+      </c>
+      <c r="BC9">
+        <v>34</v>
+      </c>
+      <c r="BD9">
+        <v>46</v>
+      </c>
+      <c r="BE9">
+        <v>14</v>
+      </c>
+      <c r="BF9">
+        <v>12</v>
+      </c>
+      <c r="BG9">
         <v>22</v>
       </c>
-      <c r="AD9">
-        <v>70</v>
-      </c>
-      <c r="AE9">
-        <v>350</v>
-      </c>
-      <c r="AF9">
-        <v>8</v>
-      </c>
-      <c r="AG9">
-        <v>12.5</v>
-      </c>
-      <c r="AH9">
-        <v>50</v>
-      </c>
-      <c r="AI9">
-        <v>240</v>
-      </c>
-      <c r="AJ9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK9">
-        <v>14</v>
-      </c>
-      <c r="AL9">
-        <v>44</v>
-      </c>
-      <c r="AM9">
-        <v>270</v>
-      </c>
-      <c r="AN9">
-        <v>3.75</v>
-      </c>
-      <c r="AO9">
-        <v>500</v>
-      </c>
-      <c r="AP9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ9">
-        <v>36</v>
-      </c>
-      <c r="AR9">
+      <c r="BH9">
+        <v>3.4</v>
+      </c>
+      <c r="BI9">
+        <v>2.66</v>
+      </c>
+      <c r="BJ9">
         <v>12</v>
       </c>
-      <c r="AS9">
-        <v>12.5</v>
-      </c>
-      <c r="AT9">
-        <v>9.4</v>
-      </c>
-      <c r="AU9">
-        <v>16.5</v>
-      </c>
-      <c r="AV9">
-        <v>42</v>
-      </c>
-      <c r="AW9">
-        <v>12</v>
-      </c>
-      <c r="AX9">
+      <c r="BK9">
         <v>7.2</v>
       </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
-        <v>30</v>
-      </c>
-      <c r="BA9">
-        <v>12</v>
-      </c>
-      <c r="BB9">
-        <v>8</v>
-      </c>
-      <c r="BC9">
-        <v>12</v>
-      </c>
-      <c r="BD9">
-        <v>34</v>
-      </c>
-      <c r="BE9">
-        <v>12</v>
-      </c>
-      <c r="BF9">
-        <v>3.45</v>
-      </c>
-      <c r="BG9">
-        <v>12.5</v>
-      </c>
-      <c r="BH9">
-        <v>4.5</v>
-      </c>
-      <c r="BI9">
-        <v>4.1</v>
-      </c>
-      <c r="BJ9">
-        <v>14</v>
-      </c>
-      <c r="BK9">
-        <v>12.5</v>
-      </c>
       <c r="BL9">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
         <v>21</v>
       </c>
       <c r="BN9">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP9">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BQ9">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BR9">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BS9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BT9">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="BV9">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="BW9">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BX9">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="BY9">
         <v>21</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2948,241 +2960,241 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F10">
+        <v>1.22</v>
+      </c>
+      <c r="G10">
+        <v>1.23</v>
+      </c>
+      <c r="H10">
+        <v>16.5</v>
+      </c>
+      <c r="I10">
+        <v>17.5</v>
+      </c>
+      <c r="J10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K10">
+        <v>8.4</v>
+      </c>
+      <c r="L10">
+        <v>1.29</v>
+      </c>
+      <c r="M10">
+        <v>1.03</v>
+      </c>
+      <c r="N10">
+        <v>6.2</v>
+      </c>
+      <c r="O10">
+        <v>1.17</v>
+      </c>
+      <c r="P10">
+        <v>2.8</v>
+      </c>
+      <c r="Q10">
+        <v>1.53</v>
+      </c>
+      <c r="R10">
+        <v>1.72</v>
+      </c>
+      <c r="S10">
+        <v>2.3</v>
+      </c>
+      <c r="T10">
+        <v>2.26</v>
+      </c>
+      <c r="U10">
+        <v>1.75</v>
+      </c>
+      <c r="V10">
+        <v>1.06</v>
+      </c>
+      <c r="W10">
+        <v>5.4</v>
+      </c>
+      <c r="X10">
+        <v>38</v>
+      </c>
+      <c r="Y10">
         <v>50</v>
       </c>
-      <c r="G10">
-        <v>85</v>
-      </c>
-      <c r="H10">
-        <v>1.06</v>
-      </c>
-      <c r="I10">
-        <v>1.07</v>
-      </c>
-      <c r="J10">
-        <v>20</v>
-      </c>
-      <c r="K10">
-        <v>23</v>
-      </c>
-      <c r="L10">
-        <v>1.17</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>8.4</v>
-      </c>
-      <c r="O10">
-        <v>1.12</v>
-      </c>
-      <c r="P10">
-        <v>3.5</v>
-      </c>
-      <c r="Q10">
-        <v>1.36</v>
-      </c>
-      <c r="R10">
-        <v>1.99</v>
-      </c>
-      <c r="S10">
-        <v>1.92</v>
-      </c>
-      <c r="T10">
+      <c r="Z10">
+        <v>200</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>10.5</v>
+      </c>
+      <c r="AC10">
+        <v>22</v>
+      </c>
+      <c r="AD10">
+        <v>70</v>
+      </c>
+      <c r="AE10">
+        <v>350</v>
+      </c>
+      <c r="AF10">
+        <v>8</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>48</v>
+      </c>
+      <c r="AI10">
+        <v>240</v>
+      </c>
+      <c r="AJ10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK10">
+        <v>13.5</v>
+      </c>
+      <c r="AL10">
+        <v>44</v>
+      </c>
+      <c r="AM10">
+        <v>270</v>
+      </c>
+      <c r="AN10">
         <v>3.75</v>
       </c>
-      <c r="U10">
-        <v>1.34</v>
-      </c>
-      <c r="V10">
-        <v>15</v>
-      </c>
-      <c r="W10">
-        <v>1.01</v>
-      </c>
-      <c r="X10">
-        <v>60</v>
-      </c>
-      <c r="Y10">
+      <c r="AO10">
+        <v>490</v>
+      </c>
+      <c r="AP10">
+        <v>10</v>
+      </c>
+      <c r="AQ10">
+        <v>36</v>
+      </c>
+      <c r="AR10">
+        <v>12.5</v>
+      </c>
+      <c r="AS10">
         <v>13.5</v>
       </c>
-      <c r="Z10">
-        <v>7.6</v>
-      </c>
-      <c r="AA10">
-        <v>6.4</v>
-      </c>
-      <c r="AB10">
-        <v>160</v>
-      </c>
-      <c r="AC10">
-        <v>70</v>
-      </c>
-      <c r="AD10">
-        <v>25</v>
-      </c>
-      <c r="AE10">
-        <v>23</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>260</v>
-      </c>
-      <c r="AH10">
-        <v>180</v>
-      </c>
-      <c r="AI10">
-        <v>130</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>2.36</v>
-      </c>
-      <c r="AP10">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10">
-        <v>10</v>
-      </c>
-      <c r="AR10">
-        <v>6.4</v>
-      </c>
-      <c r="AS10">
-        <v>5.7</v>
-      </c>
       <c r="AT10">
+        <v>9.4</v>
+      </c>
+      <c r="AU10">
+        <v>16.5</v>
+      </c>
+      <c r="AV10">
+        <v>42</v>
+      </c>
+      <c r="AW10">
+        <v>13</v>
+      </c>
+      <c r="AX10">
+        <v>7.2</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>30</v>
+      </c>
+      <c r="BA10">
+        <v>12.5</v>
+      </c>
+      <c r="BB10">
+        <v>8</v>
+      </c>
+      <c r="BC10">
         <v>12</v>
       </c>
-      <c r="AU10">
-        <v>11</v>
-      </c>
-      <c r="AV10">
-        <v>18</v>
-      </c>
-      <c r="AW10">
-        <v>18</v>
-      </c>
-      <c r="AX10">
-        <v>13</v>
-      </c>
-      <c r="AY10">
-        <v>12</v>
-      </c>
-      <c r="AZ10">
-        <v>12</v>
-      </c>
-      <c r="BA10">
-        <v>11.5</v>
-      </c>
-      <c r="BB10">
-        <v>13</v>
-      </c>
-      <c r="BC10">
-        <v>13</v>
-      </c>
       <c r="BD10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BE10">
         <v>13</v>
       </c>
       <c r="BF10">
+        <v>3.4</v>
+      </c>
+      <c r="BG10">
         <v>13</v>
       </c>
-      <c r="BG10">
-        <v>2.16</v>
-      </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="BK10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM10">
         <v>21</v>
       </c>
       <c r="BN10">
-        <v>55</v>
+        <v>3.6</v>
       </c>
       <c r="BO10">
+        <v>3.35</v>
+      </c>
+      <c r="BP10">
+        <v>6.6</v>
+      </c>
+      <c r="BQ10">
+        <v>6</v>
+      </c>
+      <c r="BR10">
+        <v>29</v>
+      </c>
+      <c r="BS10">
+        <v>17</v>
+      </c>
+      <c r="BT10">
+        <v>22</v>
+      </c>
+      <c r="BU10">
+        <v>14</v>
+      </c>
+      <c r="BV10">
+        <v>170</v>
+      </c>
+      <c r="BW10">
         <v>21</v>
       </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
+      <c r="BX10">
+        <v>140</v>
+      </c>
+      <c r="BY10">
         <v>21</v>
       </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>21</v>
-      </c>
-      <c r="BT10">
-        <v>4.8</v>
-      </c>
-      <c r="BU10">
-        <v>2.62</v>
-      </c>
-      <c r="BV10">
-        <v>6.4</v>
-      </c>
-      <c r="BW10">
-        <v>3.35</v>
-      </c>
-      <c r="BX10">
-        <v>44</v>
-      </c>
-      <c r="BY10">
-        <v>19</v>
-      </c>
       <c r="BZ10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3190,241 +3202,241 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11">
-        <v>9.4</v>
-      </c>
-      <c r="G11">
-        <v>9.800000000000001</v>
-      </c>
       <c r="H11">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="I11">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="J11">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="R11">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="S11">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="T11">
-        <v>2.06</v>
+        <v>3.95</v>
       </c>
       <c r="U11">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="V11">
-        <v>3.35</v>
+        <v>15</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="Y11">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AA11">
+        <v>7</v>
+      </c>
+      <c r="AB11">
+        <v>170</v>
+      </c>
+      <c r="AC11">
+        <v>70</v>
+      </c>
+      <c r="AD11">
+        <v>23</v>
+      </c>
+      <c r="AE11">
+        <v>22</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>350</v>
+      </c>
+      <c r="AH11">
+        <v>200</v>
+      </c>
+      <c r="AI11">
+        <v>160</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>2.42</v>
+      </c>
+      <c r="AP11">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11">
+        <v>9.6</v>
+      </c>
+      <c r="AR11">
+        <v>6.2</v>
+      </c>
+      <c r="AS11">
+        <v>5.6</v>
+      </c>
+      <c r="AT11">
         <v>11.5</v>
-      </c>
-      <c r="AB11">
-        <v>32</v>
-      </c>
-      <c r="AC11">
-        <v>12</v>
-      </c>
-      <c r="AD11">
-        <v>10</v>
-      </c>
-      <c r="AE11">
-        <v>15</v>
-      </c>
-      <c r="AF11">
-        <v>90</v>
-      </c>
-      <c r="AG11">
-        <v>36</v>
-      </c>
-      <c r="AH11">
-        <v>26</v>
-      </c>
-      <c r="AI11">
-        <v>36</v>
-      </c>
-      <c r="AJ11">
-        <v>420</v>
-      </c>
-      <c r="AK11">
-        <v>190</v>
-      </c>
-      <c r="AL11">
-        <v>130</v>
-      </c>
-      <c r="AM11">
-        <v>180</v>
-      </c>
-      <c r="AN11">
-        <v>190</v>
-      </c>
-      <c r="AO11">
-        <v>6</v>
-      </c>
-      <c r="AP11">
-        <v>17.5</v>
-      </c>
-      <c r="AQ11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR11">
-        <v>7.6</v>
-      </c>
-      <c r="AS11">
-        <v>10.5</v>
-      </c>
-      <c r="AT11">
-        <v>28</v>
       </c>
       <c r="AU11">
         <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW11">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AX11">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="AY11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AZ11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BA11">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="BB11">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BC11">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BE11">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="BF11">
-        <v>140</v>
+        <v>12.5</v>
       </c>
       <c r="BG11">
-        <v>5.6</v>
+        <v>2.28</v>
       </c>
       <c r="BH11">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BK11">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BL11">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>14.5</v>
+        <v>70</v>
       </c>
       <c r="BO11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BP11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
         <v>21</v>
       </c>
       <c r="BR11">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
         <v>21</v>
       </c>
       <c r="BT11">
+        <v>4.5</v>
+      </c>
+      <c r="BU11">
+        <v>2.48</v>
+      </c>
+      <c r="BV11">
+        <v>6.2</v>
+      </c>
+      <c r="BW11">
+        <v>3.4</v>
+      </c>
+      <c r="BX11">
+        <v>50</v>
+      </c>
+      <c r="BY11">
+        <v>21</v>
+      </c>
+      <c r="BZ11">
+        <v>7.4</v>
+      </c>
+      <c r="CA11">
         <v>3.8</v>
       </c>
-      <c r="BU11">
-        <v>3.5</v>
-      </c>
-      <c r="BV11">
-        <v>9.4</v>
-      </c>
-      <c r="BW11">
-        <v>7.4</v>
-      </c>
-      <c r="BX11">
-        <v>28</v>
-      </c>
-      <c r="BY11">
-        <v>18.5</v>
-      </c>
-      <c r="BZ11">
-        <v>16</v>
-      </c>
-      <c r="CA11">
-        <v>10.5</v>
-      </c>
       <c r="CB11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3432,241 +3444,241 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12">
+        <v>9.6</v>
+      </c>
+      <c r="G12">
+        <v>10.5</v>
+      </c>
+      <c r="H12">
+        <v>1.4</v>
+      </c>
+      <c r="I12">
+        <v>1.42</v>
+      </c>
+      <c r="J12">
+        <v>5.2</v>
+      </c>
+      <c r="K12">
+        <v>5.4</v>
+      </c>
+      <c r="L12">
+        <v>1.3</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.7</v>
+      </c>
+      <c r="O12">
+        <v>1.25</v>
+      </c>
+      <c r="P12">
+        <v>2.26</v>
+      </c>
+      <c r="Q12">
+        <v>1.75</v>
+      </c>
+      <c r="R12">
+        <v>1.49</v>
+      </c>
+      <c r="S12">
+        <v>2.88</v>
+      </c>
+      <c r="T12">
+        <v>2.06</v>
+      </c>
+      <c r="U12">
+        <v>1.89</v>
+      </c>
+      <c r="V12">
+        <v>3.35</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>20</v>
+      </c>
+      <c r="Y12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA12">
+        <v>11.5</v>
+      </c>
+      <c r="AB12">
+        <v>32</v>
+      </c>
+      <c r="AC12">
+        <v>12</v>
+      </c>
+      <c r="AD12">
+        <v>10</v>
+      </c>
+      <c r="AE12">
+        <v>15</v>
+      </c>
+      <c r="AF12">
         <v>90</v>
       </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12">
-        <v>1.3</v>
-      </c>
-      <c r="G12">
-        <v>1.31</v>
-      </c>
-      <c r="H12">
+      <c r="AG12">
+        <v>36</v>
+      </c>
+      <c r="AH12">
+        <v>26</v>
+      </c>
+      <c r="AI12">
+        <v>36</v>
+      </c>
+      <c r="AJ12">
+        <v>420</v>
+      </c>
+      <c r="AK12">
+        <v>190</v>
+      </c>
+      <c r="AL12">
+        <v>130</v>
+      </c>
+      <c r="AM12">
+        <v>180</v>
+      </c>
+      <c r="AN12">
+        <v>190</v>
+      </c>
+      <c r="AO12">
+        <v>6</v>
+      </c>
+      <c r="AP12">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR12">
+        <v>7.6</v>
+      </c>
+      <c r="AS12">
+        <v>10.5</v>
+      </c>
+      <c r="AT12">
+        <v>28</v>
+      </c>
+      <c r="AU12">
+        <v>10.5</v>
+      </c>
+      <c r="AV12">
+        <v>9.4</v>
+      </c>
+      <c r="AW12">
         <v>14</v>
       </c>
-      <c r="I12">
-        <v>16.5</v>
-      </c>
-      <c r="J12">
-        <v>5.8</v>
-      </c>
-      <c r="K12">
-        <v>6.2</v>
-      </c>
-      <c r="L12">
-        <v>1.36</v>
-      </c>
-      <c r="M12">
-        <v>1.06</v>
-      </c>
-      <c r="N12">
-        <v>3.85</v>
-      </c>
-      <c r="O12">
-        <v>1.33</v>
-      </c>
-      <c r="P12">
-        <v>1.99</v>
-      </c>
-      <c r="Q12">
-        <v>1.95</v>
-      </c>
-      <c r="R12">
-        <v>1.38</v>
-      </c>
-      <c r="S12">
-        <v>3.45</v>
-      </c>
-      <c r="T12">
-        <v>2.7</v>
-      </c>
-      <c r="U12">
-        <v>1.54</v>
-      </c>
-      <c r="V12">
-        <v>1.06</v>
-      </c>
-      <c r="W12">
-        <v>4.1</v>
-      </c>
-      <c r="X12">
+      <c r="AX12">
+        <v>75</v>
+      </c>
+      <c r="AY12">
+        <v>32</v>
+      </c>
+      <c r="AZ12">
+        <v>24</v>
+      </c>
+      <c r="BA12">
+        <v>32</v>
+      </c>
+      <c r="BB12">
+        <v>21</v>
+      </c>
+      <c r="BC12">
+        <v>20</v>
+      </c>
+      <c r="BD12">
+        <v>20</v>
+      </c>
+      <c r="BE12">
+        <v>100</v>
+      </c>
+      <c r="BF12">
+        <v>140</v>
+      </c>
+      <c r="BG12">
+        <v>5.6</v>
+      </c>
+      <c r="BH12">
+        <v>3.9</v>
+      </c>
+      <c r="BI12">
+        <v>3.55</v>
+      </c>
+      <c r="BJ12">
+        <v>13.5</v>
+      </c>
+      <c r="BK12">
+        <v>10.5</v>
+      </c>
+      <c r="BL12">
+        <v>180</v>
+      </c>
+      <c r="BM12">
+        <v>21</v>
+      </c>
+      <c r="BN12">
+        <v>15</v>
+      </c>
+      <c r="BO12">
+        <v>11</v>
+      </c>
+      <c r="BP12">
+        <v>100</v>
+      </c>
+      <c r="BQ12">
+        <v>21</v>
+      </c>
+      <c r="BR12">
+        <v>90</v>
+      </c>
+      <c r="BS12">
+        <v>21</v>
+      </c>
+      <c r="BT12">
+        <v>3.8</v>
+      </c>
+      <c r="BU12">
+        <v>3.5</v>
+      </c>
+      <c r="BV12">
+        <v>9.4</v>
+      </c>
+      <c r="BW12">
+        <v>7.4</v>
+      </c>
+      <c r="BX12">
+        <v>28</v>
+      </c>
+      <c r="BY12">
+        <v>18</v>
+      </c>
+      <c r="BZ12">
         <v>16</v>
       </c>
-      <c r="Y12">
-        <v>38</v>
-      </c>
-      <c r="Z12">
-        <v>170</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>7</v>
-      </c>
-      <c r="AC12">
-        <v>14</v>
-      </c>
-      <c r="AD12">
-        <v>65</v>
-      </c>
-      <c r="AE12">
-        <v>410</v>
-      </c>
-      <c r="AF12">
-        <v>6.6</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>60</v>
-      </c>
-      <c r="AI12">
-        <v>330</v>
-      </c>
-      <c r="AJ12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK12">
-        <v>18.5</v>
-      </c>
-      <c r="AL12">
-        <v>65</v>
-      </c>
-      <c r="AM12">
-        <v>380</v>
-      </c>
-      <c r="AN12">
-        <v>6.2</v>
-      </c>
-      <c r="AO12">
-        <v>820</v>
-      </c>
-      <c r="AP12">
-        <v>14</v>
-      </c>
-      <c r="AQ12">
-        <v>32</v>
-      </c>
-      <c r="AR12">
-        <v>13</v>
-      </c>
-      <c r="AS12">
-        <v>14</v>
-      </c>
-      <c r="AT12">
-        <v>6.2</v>
-      </c>
-      <c r="AU12">
-        <v>12.5</v>
-      </c>
-      <c r="AV12">
-        <v>44</v>
-      </c>
-      <c r="AW12">
-        <v>13.5</v>
-      </c>
-      <c r="AX12">
-        <v>6</v>
-      </c>
-      <c r="AY12">
+      <c r="CA12">
         <v>10.5</v>
       </c>
-      <c r="AZ12">
-        <v>11.5</v>
-      </c>
-      <c r="BA12">
-        <v>13.5</v>
-      </c>
-      <c r="BB12">
-        <v>8.4</v>
-      </c>
-      <c r="BC12">
-        <v>15.5</v>
-      </c>
-      <c r="BD12">
-        <v>50</v>
-      </c>
-      <c r="BE12">
-        <v>13.5</v>
-      </c>
-      <c r="BF12">
-        <v>5.6</v>
-      </c>
-      <c r="BG12">
-        <v>14</v>
-      </c>
-      <c r="BH12">
-        <v>3.8</v>
-      </c>
-      <c r="BI12">
-        <v>2.92</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>10</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
-        <v>3.85</v>
-      </c>
-      <c r="BO12">
-        <v>2.92</v>
-      </c>
-      <c r="BP12">
-        <v>11</v>
-      </c>
-      <c r="BQ12">
-        <v>5.8</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.01</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>9.4</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.01</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.01</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.01</v>
-      </c>
       <c r="CB12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3674,209 +3686,209 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="G13">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="H13">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="I13">
+        <v>16.5</v>
+      </c>
+      <c r="J13">
+        <v>5.9</v>
+      </c>
+      <c r="K13">
+        <v>6.2</v>
+      </c>
+      <c r="L13">
+        <v>1.36</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.9</v>
+      </c>
+      <c r="O13">
+        <v>1.32</v>
+      </c>
+      <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
+        <v>1.95</v>
+      </c>
+      <c r="R13">
+        <v>1.39</v>
+      </c>
+      <c r="S13">
+        <v>3.45</v>
+      </c>
+      <c r="T13">
+        <v>2.7</v>
+      </c>
+      <c r="U13">
+        <v>1.54</v>
+      </c>
+      <c r="V13">
+        <v>1.06</v>
+      </c>
+      <c r="W13">
+        <v>4.1</v>
+      </c>
+      <c r="X13">
+        <v>16</v>
+      </c>
+      <c r="Y13">
+        <v>38</v>
+      </c>
+      <c r="Z13">
+        <v>170</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>7</v>
+      </c>
+      <c r="AC13">
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <v>60</v>
+      </c>
+      <c r="AE13">
+        <v>410</v>
+      </c>
+      <c r="AF13">
         <v>6.6</v>
       </c>
-      <c r="J13">
-        <v>3.65</v>
-      </c>
-      <c r="K13">
-        <v>3.75</v>
-      </c>
-      <c r="L13">
-        <v>1.49</v>
-      </c>
-      <c r="M13">
-        <v>1.11</v>
-      </c>
-      <c r="N13">
-        <v>2.94</v>
-      </c>
-      <c r="O13">
-        <v>1.48</v>
-      </c>
-      <c r="P13">
-        <v>1.63</v>
-      </c>
-      <c r="Q13">
-        <v>2.44</v>
-      </c>
-      <c r="R13">
-        <v>1.23</v>
-      </c>
-      <c r="S13">
-        <v>5</v>
-      </c>
-      <c r="T13">
-        <v>2.3</v>
-      </c>
-      <c r="U13">
-        <v>1.7</v>
-      </c>
-      <c r="V13">
-        <v>1.17</v>
-      </c>
-      <c r="W13">
-        <v>2.34</v>
-      </c>
-      <c r="X13">
-        <v>10</v>
-      </c>
-      <c r="Y13">
-        <v>16.5</v>
-      </c>
-      <c r="Z13">
-        <v>55</v>
-      </c>
-      <c r="AA13">
-        <v>280</v>
-      </c>
-      <c r="AB13">
-        <v>6.4</v>
-      </c>
-      <c r="AC13">
-        <v>8.6</v>
-      </c>
-      <c r="AD13">
-        <v>28</v>
-      </c>
-      <c r="AE13">
-        <v>160</v>
-      </c>
-      <c r="AF13">
-        <v>8.6</v>
-      </c>
       <c r="AG13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AI13">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="AJ13">
+        <v>9</v>
+      </c>
+      <c r="AK13">
         <v>17</v>
-      </c>
-      <c r="AK13">
-        <v>24</v>
       </c>
       <c r="AL13">
         <v>65</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="AN13">
+        <v>6</v>
+      </c>
+      <c r="AO13">
+        <v>760</v>
+      </c>
+      <c r="AP13">
+        <v>14</v>
+      </c>
+      <c r="AQ13">
+        <v>32</v>
+      </c>
+      <c r="AR13">
+        <v>16.5</v>
+      </c>
+      <c r="AS13">
+        <v>16.5</v>
+      </c>
+      <c r="AT13">
+        <v>6.4</v>
+      </c>
+      <c r="AU13">
+        <v>12.5</v>
+      </c>
+      <c r="AV13">
+        <v>44</v>
+      </c>
+      <c r="AW13">
+        <v>16.5</v>
+      </c>
+      <c r="AX13">
+        <v>6</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
+        <v>13</v>
+      </c>
+      <c r="BA13">
+        <v>17.5</v>
+      </c>
+      <c r="BB13">
+        <v>8.4</v>
+      </c>
+      <c r="BC13">
+        <v>15.5</v>
+      </c>
+      <c r="BD13">
+        <v>50</v>
+      </c>
+      <c r="BE13">
         <v>16</v>
       </c>
-      <c r="AO13">
-        <v>280</v>
-      </c>
-      <c r="AP13">
-        <v>9</v>
-      </c>
-      <c r="AQ13">
-        <v>14</v>
-      </c>
-      <c r="AR13">
+      <c r="BF13">
+        <v>5.6</v>
+      </c>
+      <c r="BG13">
+        <v>16.5</v>
+      </c>
+      <c r="BH13">
+        <v>3.8</v>
+      </c>
+      <c r="BI13">
+        <v>2.92</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>10</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>3.85</v>
+      </c>
+      <c r="BO13">
+        <v>2.92</v>
+      </c>
+      <c r="BP13">
         <v>11</v>
       </c>
-      <c r="AS13">
-        <v>13.5</v>
-      </c>
-      <c r="AT13">
+      <c r="BQ13">
         <v>5.8</v>
       </c>
-      <c r="AU13">
-        <v>7.6</v>
-      </c>
-      <c r="AV13">
-        <v>18.5</v>
-      </c>
-      <c r="AW13">
-        <v>13</v>
-      </c>
-      <c r="AX13">
-        <v>7.8</v>
-      </c>
-      <c r="AY13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13">
-        <v>21</v>
-      </c>
-      <c r="BA13">
-        <v>13</v>
-      </c>
-      <c r="BB13">
-        <v>15</v>
-      </c>
-      <c r="BC13">
-        <v>19</v>
-      </c>
-      <c r="BD13">
-        <v>11.5</v>
-      </c>
-      <c r="BE13">
-        <v>13.5</v>
-      </c>
-      <c r="BF13">
-        <v>13.5</v>
-      </c>
-      <c r="BG13">
-        <v>13.5</v>
-      </c>
-      <c r="BH13">
-        <v>3.05</v>
-      </c>
-      <c r="BI13">
-        <v>2.48</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>8.4</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>4.6</v>
-      </c>
-      <c r="BO13">
-        <v>3.35</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BR13">
         <v>1000</v>
       </c>
@@ -3887,7 +3899,7 @@
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3908,7 +3920,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3916,190 +3928,190 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="G14">
-        <v>4.5</v>
+        <v>1.74</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="I14">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="O14">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P14">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S14">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T14">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="V14">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="W14">
-        <v>1.28</v>
+        <v>2.34</v>
       </c>
       <c r="X14">
+        <v>10</v>
+      </c>
+      <c r="Y14">
+        <v>16.5</v>
+      </c>
+      <c r="Z14">
+        <v>65</v>
+      </c>
+      <c r="AA14">
+        <v>280</v>
+      </c>
+      <c r="AB14">
+        <v>6.4</v>
+      </c>
+      <c r="AC14">
+        <v>8.6</v>
+      </c>
+      <c r="AD14">
+        <v>28</v>
+      </c>
+      <c r="AE14">
+        <v>160</v>
+      </c>
+      <c r="AF14">
+        <v>8.6</v>
+      </c>
+      <c r="AG14">
+        <v>11</v>
+      </c>
+      <c r="AH14">
+        <v>29</v>
+      </c>
+      <c r="AI14">
+        <v>160</v>
+      </c>
+      <c r="AJ14">
+        <v>17</v>
+      </c>
+      <c r="AK14">
+        <v>23</v>
+      </c>
+      <c r="AL14">
+        <v>65</v>
+      </c>
+      <c r="AM14">
+        <v>260</v>
+      </c>
+      <c r="AN14">
+        <v>16</v>
+      </c>
+      <c r="AO14">
+        <v>280</v>
+      </c>
+      <c r="AP14">
+        <v>9</v>
+      </c>
+      <c r="AQ14">
+        <v>14</v>
+      </c>
+      <c r="AR14">
         <v>11.5</v>
       </c>
-      <c r="Y14">
-        <v>8</v>
-      </c>
-      <c r="Z14">
-        <v>11</v>
-      </c>
-      <c r="AA14">
-        <v>23</v>
-      </c>
-      <c r="AB14">
-        <v>13</v>
-      </c>
-      <c r="AC14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14">
-        <v>11</v>
-      </c>
-      <c r="AE14">
-        <v>23</v>
-      </c>
-      <c r="AF14">
-        <v>32</v>
-      </c>
-      <c r="AG14">
-        <v>18</v>
-      </c>
-      <c r="AH14">
-        <v>23</v>
-      </c>
-      <c r="AI14">
-        <v>46</v>
-      </c>
-      <c r="AJ14">
-        <v>110</v>
-      </c>
-      <c r="AK14">
-        <v>70</v>
-      </c>
-      <c r="AL14">
-        <v>75</v>
-      </c>
-      <c r="AM14">
-        <v>150</v>
-      </c>
-      <c r="AN14">
-        <v>85</v>
-      </c>
-      <c r="AO14">
-        <v>17.5</v>
-      </c>
-      <c r="AP14">
-        <v>11</v>
-      </c>
-      <c r="AQ14">
-        <v>7.6</v>
-      </c>
-      <c r="AR14">
-        <v>10</v>
-      </c>
       <c r="AS14">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AT14">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AU14">
         <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AX14">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="AY14">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BB14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC14">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="BD14">
-        <v>60</v>
+        <v>11.5</v>
       </c>
       <c r="BE14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BF14">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="BG14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH14">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BI14">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4108,16 +4120,16 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO14">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14">
         <v>1000</v>
@@ -4129,13 +4141,13 @@
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
@@ -4150,249 +4162,249 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15">
+        <v>4.4</v>
+      </c>
+      <c r="G15">
+        <v>4.5</v>
+      </c>
+      <c r="H15">
+        <v>1.99</v>
+      </c>
+      <c r="I15">
+        <v>2.02</v>
+      </c>
+      <c r="J15">
+        <v>3.6</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
+        <v>1.45</v>
+      </c>
+      <c r="M15">
+        <v>1.09</v>
+      </c>
+      <c r="N15">
+        <v>3.25</v>
+      </c>
+      <c r="O15">
+        <v>1.41</v>
+      </c>
+      <c r="P15">
+        <v>1.77</v>
+      </c>
+      <c r="Q15">
+        <v>2.24</v>
+      </c>
+      <c r="R15">
+        <v>1.29</v>
+      </c>
+      <c r="S15">
+        <v>4.2</v>
+      </c>
+      <c r="T15">
+        <v>2.02</v>
+      </c>
+      <c r="U15">
+        <v>1.91</v>
+      </c>
+      <c r="V15">
+        <v>1.98</v>
+      </c>
+      <c r="W15">
+        <v>1.28</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>8</v>
+      </c>
+      <c r="Z15">
+        <v>11</v>
+      </c>
+      <c r="AA15">
+        <v>23</v>
+      </c>
+      <c r="AB15">
+        <v>13</v>
+      </c>
+      <c r="AC15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>23</v>
+      </c>
+      <c r="AF15">
+        <v>32</v>
+      </c>
+      <c r="AG15">
+        <v>18</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>46</v>
+      </c>
+      <c r="AJ15">
+        <v>110</v>
+      </c>
+      <c r="AK15">
+        <v>70</v>
+      </c>
+      <c r="AL15">
+        <v>75</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
         <v>85</v>
       </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F15">
-        <v>2.24</v>
-      </c>
-      <c r="G15">
-        <v>2.34</v>
-      </c>
-      <c r="H15">
-        <v>2.98</v>
-      </c>
-      <c r="I15">
-        <v>3.3</v>
-      </c>
-      <c r="J15">
-        <v>3.95</v>
-      </c>
-      <c r="K15">
-        <v>4.3</v>
-      </c>
-      <c r="L15">
-        <v>1.23</v>
-      </c>
-      <c r="M15">
-        <v>1.02</v>
-      </c>
-      <c r="N15">
-        <v>5.6</v>
-      </c>
-      <c r="O15">
-        <v>1.18</v>
-      </c>
-      <c r="P15">
-        <v>2.56</v>
-      </c>
-      <c r="Q15">
-        <v>1.55</v>
-      </c>
-      <c r="R15">
-        <v>1.66</v>
-      </c>
-      <c r="S15">
-        <v>2.38</v>
-      </c>
-      <c r="T15">
-        <v>1.53</v>
-      </c>
-      <c r="U15">
-        <v>2.62</v>
-      </c>
-      <c r="V15">
-        <v>1.43</v>
-      </c>
-      <c r="W15">
-        <v>1.74</v>
-      </c>
-      <c r="X15">
-        <v>32</v>
-      </c>
-      <c r="Y15">
-        <v>23</v>
-      </c>
-      <c r="Z15">
-        <v>32</v>
-      </c>
-      <c r="AA15">
-        <v>60</v>
-      </c>
-      <c r="AB15">
-        <v>18.5</v>
-      </c>
-      <c r="AC15">
-        <v>10.5</v>
-      </c>
-      <c r="AD15">
-        <v>17.5</v>
-      </c>
-      <c r="AE15">
-        <v>36</v>
-      </c>
-      <c r="AF15">
-        <v>970</v>
-      </c>
-      <c r="AG15">
-        <v>14.5</v>
-      </c>
-      <c r="AH15">
-        <v>18</v>
-      </c>
-      <c r="AI15">
-        <v>40</v>
-      </c>
-      <c r="AJ15">
-        <v>36</v>
-      </c>
-      <c r="AK15">
-        <v>25</v>
-      </c>
-      <c r="AL15">
-        <v>34</v>
-      </c>
-      <c r="AM15">
-        <v>55</v>
-      </c>
-      <c r="AN15">
-        <v>13</v>
-      </c>
       <c r="AO15">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AP15">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AR15">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AS15">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AT15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AV15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW15">
         <v>21</v>
       </c>
       <c r="AX15">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>4.8</v>
+        <v>40</v>
       </c>
       <c r="BB15">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="BD15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="BE15">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="BF15">
-        <v>9.6</v>
+        <v>65</v>
       </c>
       <c r="BG15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH15">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="BI15">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BP15">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BV15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4400,483 +4412,483 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16">
+        <v>2.24</v>
+      </c>
+      <c r="G16">
+        <v>2.34</v>
+      </c>
+      <c r="H16">
+        <v>2.98</v>
+      </c>
+      <c r="I16">
+        <v>3.3</v>
+      </c>
+      <c r="J16">
+        <v>3.95</v>
+      </c>
+      <c r="K16">
+        <v>4.5</v>
+      </c>
+      <c r="L16">
+        <v>1.23</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>5.6</v>
+      </c>
+      <c r="O16">
+        <v>1.18</v>
+      </c>
+      <c r="P16">
+        <v>2.56</v>
+      </c>
+      <c r="Q16">
+        <v>1.55</v>
+      </c>
+      <c r="R16">
+        <v>1.63</v>
+      </c>
+      <c r="S16">
+        <v>2.38</v>
+      </c>
+      <c r="T16">
+        <v>1.53</v>
+      </c>
+      <c r="U16">
+        <v>2.62</v>
+      </c>
+      <c r="V16">
+        <v>1.43</v>
+      </c>
+      <c r="W16">
+        <v>1.74</v>
+      </c>
+      <c r="X16">
+        <v>32</v>
+      </c>
+      <c r="Y16">
+        <v>23</v>
+      </c>
+      <c r="Z16">
+        <v>32</v>
+      </c>
+      <c r="AA16">
+        <v>60</v>
+      </c>
+      <c r="AB16">
+        <v>18.5</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>17.5</v>
+      </c>
+      <c r="AE16">
+        <v>36</v>
+      </c>
+      <c r="AF16">
+        <v>970</v>
+      </c>
+      <c r="AG16">
+        <v>14.5</v>
+      </c>
+      <c r="AH16">
+        <v>18</v>
+      </c>
+      <c r="AI16">
+        <v>40</v>
+      </c>
+      <c r="AJ16">
+        <v>36</v>
+      </c>
+      <c r="AK16">
+        <v>25</v>
+      </c>
+      <c r="AL16">
+        <v>34</v>
+      </c>
+      <c r="AM16">
+        <v>55</v>
+      </c>
+      <c r="AN16">
+        <v>13</v>
+      </c>
+      <c r="AO16">
+        <v>970</v>
+      </c>
+      <c r="AP16">
+        <v>22</v>
+      </c>
+      <c r="AQ16">
+        <v>4.3</v>
+      </c>
+      <c r="AR16">
+        <v>22</v>
+      </c>
+      <c r="AS16">
+        <v>5</v>
+      </c>
+      <c r="AT16">
+        <v>13</v>
+      </c>
+      <c r="AU16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16">
+        <v>12</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>15.5</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>13</v>
+      </c>
+      <c r="BA16">
+        <v>4.8</v>
+      </c>
+      <c r="BB16">
+        <v>21</v>
+      </c>
+      <c r="BC16">
+        <v>4.5</v>
+      </c>
+      <c r="BD16">
+        <v>20</v>
+      </c>
+      <c r="BE16">
+        <v>5</v>
+      </c>
+      <c r="BF16">
+        <v>9.6</v>
+      </c>
+      <c r="BG16">
+        <v>16</v>
+      </c>
+      <c r="BH16">
+        <v>5.3</v>
+      </c>
+      <c r="BI16">
+        <v>3.5</v>
+      </c>
+      <c r="BJ16">
+        <v>10.5</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
         <v>85</v>
       </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F16">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>4.5</v>
-      </c>
-      <c r="H16">
-        <v>1.88</v>
-      </c>
-      <c r="I16">
-        <v>1.93</v>
-      </c>
-      <c r="J16">
-        <v>4.1</v>
-      </c>
-      <c r="K16">
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>6.8</v>
+      </c>
+      <c r="BO16">
         <v>4.3</v>
       </c>
-      <c r="L16">
-        <v>1.34</v>
-      </c>
-      <c r="M16">
-        <v>1.05</v>
-      </c>
-      <c r="N16">
-        <v>4.2</v>
-      </c>
-      <c r="O16">
-        <v>1.26</v>
-      </c>
-      <c r="P16">
-        <v>2.14</v>
-      </c>
-      <c r="Q16">
-        <v>1.73</v>
-      </c>
-      <c r="R16">
-        <v>1.48</v>
-      </c>
-      <c r="S16">
-        <v>2.88</v>
-      </c>
-      <c r="T16">
-        <v>1.69</v>
-      </c>
-      <c r="U16">
-        <v>2.2</v>
-      </c>
-      <c r="V16">
-        <v>2.06</v>
-      </c>
-      <c r="W16">
-        <v>1.29</v>
-      </c>
-      <c r="X16">
-        <v>19.5</v>
-      </c>
-      <c r="Y16">
-        <v>11</v>
-      </c>
-      <c r="Z16">
-        <v>13.5</v>
-      </c>
-      <c r="AA16">
+      <c r="BP16">
+        <v>18</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>27</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU16">
+        <v>6</v>
+      </c>
+      <c r="BV16">
         <v>26</v>
       </c>
-      <c r="AB16">
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>32</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
         <v>18</v>
       </c>
-      <c r="AC16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD16">
-        <v>11</v>
-      </c>
-      <c r="AE16">
-        <v>19.5</v>
-      </c>
-      <c r="AF16">
-        <v>34</v>
-      </c>
-      <c r="AG16">
-        <v>18</v>
-      </c>
-      <c r="AH16">
-        <v>19</v>
-      </c>
-      <c r="AI16">
-        <v>32</v>
-      </c>
-      <c r="AJ16">
-        <v>100</v>
-      </c>
-      <c r="AK16">
-        <v>50</v>
-      </c>
-      <c r="AL16">
-        <v>55</v>
-      </c>
-      <c r="AM16">
-        <v>90</v>
-      </c>
-      <c r="AN16">
-        <v>46</v>
-      </c>
-      <c r="AO16">
-        <v>12</v>
-      </c>
-      <c r="AP16">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR16">
-        <v>11</v>
-      </c>
-      <c r="AS16">
-        <v>18.5</v>
-      </c>
-      <c r="AT16">
-        <v>14.5</v>
-      </c>
-      <c r="AU16">
-        <v>8</v>
-      </c>
-      <c r="AV16">
-        <v>9.4</v>
-      </c>
-      <c r="AW16">
-        <v>16</v>
-      </c>
-      <c r="AX16">
-        <v>29</v>
-      </c>
-      <c r="AY16">
-        <v>15</v>
-      </c>
-      <c r="AZ16">
-        <v>15.5</v>
-      </c>
-      <c r="BA16">
-        <v>26</v>
-      </c>
-      <c r="BB16">
-        <v>11.5</v>
-      </c>
-      <c r="BC16">
-        <v>40</v>
-      </c>
-      <c r="BD16">
-        <v>42</v>
-      </c>
-      <c r="BE16">
-        <v>9.4</v>
-      </c>
-      <c r="BF16">
-        <v>9.4</v>
-      </c>
-      <c r="BG16">
-        <v>9.6</v>
-      </c>
-      <c r="BH16">
-        <v>4.3</v>
-      </c>
-      <c r="BI16">
-        <v>3.1</v>
-      </c>
-      <c r="BJ16">
-        <v>11</v>
-      </c>
-      <c r="BK16">
-        <v>7.2</v>
-      </c>
-      <c r="BL16">
-        <v>120</v>
-      </c>
-      <c r="BM16">
-        <v>1.02</v>
-      </c>
-      <c r="BN16">
-        <v>8.6</v>
-      </c>
-      <c r="BO16">
-        <v>6</v>
-      </c>
-      <c r="BP16">
-        <v>34</v>
-      </c>
-      <c r="BQ16">
-        <v>1.02</v>
-      </c>
-      <c r="BR16">
-        <v>46</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>5</v>
-      </c>
-      <c r="BU16">
-        <v>4.2</v>
-      </c>
-      <c r="BV16">
-        <v>15.5</v>
-      </c>
-      <c r="BW16">
-        <v>10</v>
-      </c>
-      <c r="BX16">
-        <v>29</v>
-      </c>
-      <c r="BY16">
-        <v>1.02</v>
-      </c>
-      <c r="BZ16">
-        <v>21</v>
-      </c>
       <c r="CA16">
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F17">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="H17">
-        <v>6.8</v>
+        <v>1.88</v>
       </c>
       <c r="I17">
-        <v>7.2</v>
+        <v>1.93</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="P17">
+        <v>2.14</v>
+      </c>
+      <c r="Q17">
+        <v>1.73</v>
+      </c>
+      <c r="R17">
+        <v>1.48</v>
+      </c>
+      <c r="S17">
+        <v>2.88</v>
+      </c>
+      <c r="T17">
         <v>1.69</v>
       </c>
-      <c r="Q17">
-        <v>2.32</v>
-      </c>
-      <c r="R17">
-        <v>1.26</v>
-      </c>
-      <c r="S17">
-        <v>4.6</v>
-      </c>
-      <c r="T17">
-        <v>2.26</v>
-      </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.16</v>
+        <v>2.06</v>
       </c>
       <c r="W17">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="X17">
+        <v>19.5</v>
+      </c>
+      <c r="Y17">
         <v>11</v>
       </c>
-      <c r="Y17">
-        <v>17</v>
-      </c>
       <c r="Z17">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="AA17">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="AB17">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AE17">
-        <v>140</v>
+        <v>19.5</v>
       </c>
       <c r="AF17">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AG17">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AH17">
+        <v>18.5</v>
+      </c>
+      <c r="AI17">
         <v>32</v>
       </c>
-      <c r="AI17">
-        <v>150</v>
-      </c>
       <c r="AJ17">
-        <v>16.5</v>
+        <v>100</v>
       </c>
       <c r="AK17">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AL17">
         <v>55</v>
       </c>
       <c r="AM17">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="AN17">
+        <v>46</v>
+      </c>
+      <c r="AO17">
+        <v>11.5</v>
+      </c>
+      <c r="AP17">
+        <v>16</v>
+      </c>
+      <c r="AQ17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR17">
+        <v>11</v>
+      </c>
+      <c r="AS17">
+        <v>18</v>
+      </c>
+      <c r="AT17">
+        <v>15</v>
+      </c>
+      <c r="AU17">
+        <v>8</v>
+      </c>
+      <c r="AV17">
+        <v>9.4</v>
+      </c>
+      <c r="AW17">
+        <v>15.5</v>
+      </c>
+      <c r="AX17">
+        <v>29</v>
+      </c>
+      <c r="AY17">
+        <v>15</v>
+      </c>
+      <c r="AZ17">
+        <v>15.5</v>
+      </c>
+      <c r="BA17">
+        <v>26</v>
+      </c>
+      <c r="BB17">
+        <v>11</v>
+      </c>
+      <c r="BC17">
+        <v>40</v>
+      </c>
+      <c r="BD17">
+        <v>42</v>
+      </c>
+      <c r="BE17">
+        <v>9.4</v>
+      </c>
+      <c r="BF17">
+        <v>9.6</v>
+      </c>
+      <c r="BG17">
+        <v>9.6</v>
+      </c>
+      <c r="BH17">
+        <v>4.3</v>
+      </c>
+      <c r="BI17">
+        <v>3.1</v>
+      </c>
+      <c r="BJ17">
+        <v>11</v>
+      </c>
+      <c r="BK17">
+        <v>7.2</v>
+      </c>
+      <c r="BL17">
+        <v>120</v>
+      </c>
+      <c r="BM17">
+        <v>1.02</v>
+      </c>
+      <c r="BN17">
+        <v>8</v>
+      </c>
+      <c r="BO17">
+        <v>6</v>
+      </c>
+      <c r="BP17">
+        <v>34</v>
+      </c>
+      <c r="BQ17">
+        <v>1.02</v>
+      </c>
+      <c r="BR17">
+        <v>46</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>5</v>
+      </c>
+      <c r="BU17">
+        <v>4.2</v>
+      </c>
+      <c r="BV17">
         <v>14</v>
       </c>
-      <c r="AO17">
-        <v>230</v>
-      </c>
-      <c r="AP17">
-        <v>10</v>
-      </c>
-      <c r="AQ17">
-        <v>14.5</v>
-      </c>
-      <c r="AR17">
-        <v>46</v>
-      </c>
-      <c r="AS17">
-        <v>13</v>
-      </c>
-      <c r="AT17">
-        <v>6</v>
-      </c>
-      <c r="AU17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17">
-        <v>24</v>
-      </c>
-      <c r="AW17">
-        <v>13</v>
-      </c>
-      <c r="AX17">
-        <v>7.6</v>
-      </c>
-      <c r="AY17">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17">
-        <v>25</v>
-      </c>
-      <c r="BA17">
-        <v>13</v>
-      </c>
-      <c r="BB17">
-        <v>14.5</v>
-      </c>
-      <c r="BC17">
-        <v>18</v>
-      </c>
-      <c r="BD17">
-        <v>44</v>
-      </c>
-      <c r="BE17">
-        <v>13</v>
-      </c>
-      <c r="BF17">
-        <v>12</v>
-      </c>
-      <c r="BG17">
-        <v>13</v>
-      </c>
-      <c r="BH17">
-        <v>3.25</v>
-      </c>
-      <c r="BI17">
-        <v>2.56</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>4.6</v>
-      </c>
-      <c r="BO17">
-        <v>3.45</v>
-      </c>
-      <c r="BP17">
-        <v>30</v>
-      </c>
-      <c r="BQ17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.01</v>
-      </c>
-      <c r="BT17">
-        <v>16</v>
-      </c>
-      <c r="BU17">
-        <v>7.4</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4884,16 +4896,16 @@
         <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F18">
         <v>2.02</v>
@@ -4914,7 +4926,7 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M18">
         <v>1.02</v>
@@ -4944,7 +4956,7 @@
         <v>2.46</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
         <v>1.88</v>
@@ -4968,7 +4980,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE18">
         <v>42</v>
@@ -4983,7 +4995,7 @@
         <v>16</v>
       </c>
       <c r="AI18">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ18">
         <v>29</v>
@@ -5010,10 +5022,10 @@
         <v>16</v>
       </c>
       <c r="AR18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5025,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="AW18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5037,7 +5049,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
         <v>19</v>
@@ -5049,7 +5061,7 @@
         <v>21</v>
       </c>
       <c r="BE18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF18">
         <v>9.199999999999999</v>
@@ -5118,7 +5130,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5126,34 +5138,34 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F19">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G19">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I19">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J19">
         <v>3.75</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5162,40 +5174,40 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="T19">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z19">
         <v>30</v>
@@ -5204,25 +5216,25 @@
         <v>80</v>
       </c>
       <c r="AB19">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC19">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AE19">
         <v>44</v>
       </c>
       <c r="AF19">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI19">
         <v>50</v>
@@ -5240,61 +5252,61 @@
         <v>100</v>
       </c>
       <c r="AN19">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AO19">
         <v>36</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT19">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU19">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX19">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY19">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB19">
         <v>20</v>
       </c>
       <c r="BC19">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD19">
         <v>24</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF19">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
         <v>19</v>
@@ -5360,7 +5372,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5368,22 +5380,22 @@
         <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F20">
         <v>1.76</v>
       </c>
       <c r="G20">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
         <v>4.2</v>
@@ -5392,7 +5404,7 @@
         <v>4.9</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20">
         <v>4.8</v>
@@ -5431,7 +5443,7 @@
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20">
         <v>30</v>
@@ -5572,7 +5584,7 @@
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
@@ -5602,7 +5614,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5610,16 +5622,16 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F21">
         <v>2.28</v>
@@ -5637,7 +5649,7 @@
         <v>3.6</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>1.32</v>
@@ -5646,7 +5658,7 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O21">
         <v>1.26</v>
@@ -5691,7 +5703,7 @@
         <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21">
         <v>16</v>
@@ -5724,7 +5736,7 @@
         <v>85</v>
       </c>
       <c r="AN21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO21">
         <v>30</v>
@@ -5751,7 +5763,7 @@
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX21">
         <v>13.5</v>
@@ -5763,7 +5775,7 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB21">
         <v>25</v>
@@ -5772,16 +5784,16 @@
         <v>20</v>
       </c>
       <c r="BD21">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BF21">
         <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -5844,7 +5856,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5852,16 +5864,16 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F22">
         <v>2.52</v>
@@ -5894,7 +5906,7 @@
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q22">
         <v>1.48</v>
@@ -6086,7 +6098,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6094,25 +6106,25 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G23">
         <v>4.9</v>
       </c>
       <c r="H23">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I23">
         <v>1.82</v>
@@ -6124,7 +6136,7 @@
         <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M23">
         <v>1.04</v>
@@ -6175,7 +6187,7 @@
         <v>24</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
         <v>10.5</v>
@@ -6202,7 +6214,7 @@
         <v>55</v>
       </c>
       <c r="AL23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM23">
         <v>85</v>
@@ -6328,7 +6340,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6336,25 +6348,25 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F24">
         <v>4.5</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I24">
         <v>2.02</v>
@@ -6375,13 +6387,13 @@
         <v>3.25</v>
       </c>
       <c r="O24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R24">
         <v>1.29</v>
@@ -6390,10 +6402,10 @@
         <v>4</v>
       </c>
       <c r="T24">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U24">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
         <v>1.98</v>
@@ -6414,10 +6426,10 @@
         <v>26</v>
       </c>
       <c r="AB24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC24">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24">
         <v>12.5</v>
@@ -6450,7 +6462,7 @@
         <v>160</v>
       </c>
       <c r="AN24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO24">
         <v>19</v>
@@ -6459,19 +6471,19 @@
         <v>10.5</v>
       </c>
       <c r="AQ24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR24">
         <v>9.800000000000001</v>
       </c>
       <c r="AS24">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="AT24">
         <v>12.5</v>
       </c>
       <c r="AU24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
         <v>9.4</v>
@@ -6480,97 +6492,339 @@
         <v>18.5</v>
       </c>
       <c r="AX24">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AY24">
         <v>16.5</v>
       </c>
       <c r="AZ24">
+        <v>17.5</v>
+      </c>
+      <c r="BA24">
+        <v>5.9</v>
+      </c>
+      <c r="BB24">
+        <v>6</v>
+      </c>
+      <c r="BC24">
+        <v>5.8</v>
+      </c>
+      <c r="BD24">
+        <v>5.9</v>
+      </c>
+      <c r="BE24">
+        <v>6</v>
+      </c>
+      <c r="BF24">
+        <v>6</v>
+      </c>
+      <c r="BG24">
+        <v>5</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25">
+        <v>1.24</v>
+      </c>
+      <c r="G25">
+        <v>1.28</v>
+      </c>
+      <c r="H25">
+        <v>15.5</v>
+      </c>
+      <c r="I25">
+        <v>22</v>
+      </c>
+      <c r="J25">
+        <v>6.4</v>
+      </c>
+      <c r="K25">
+        <v>7.4</v>
+      </c>
+      <c r="L25">
+        <v>1.27</v>
+      </c>
+      <c r="M25">
+        <v>1.04</v>
+      </c>
+      <c r="N25">
+        <v>4.8</v>
+      </c>
+      <c r="O25">
+        <v>1.22</v>
+      </c>
+      <c r="P25">
+        <v>2.34</v>
+      </c>
+      <c r="Q25">
+        <v>1.66</v>
+      </c>
+      <c r="R25">
+        <v>1.52</v>
+      </c>
+      <c r="S25">
+        <v>2.66</v>
+      </c>
+      <c r="T25">
+        <v>2.4</v>
+      </c>
+      <c r="U25">
+        <v>1.64</v>
+      </c>
+      <c r="V25">
+        <v>1.05</v>
+      </c>
+      <c r="W25">
         <v>4.6</v>
       </c>
-      <c r="BA24">
-        <v>5.5</v>
-      </c>
-      <c r="BB24">
-        <v>5.5</v>
-      </c>
-      <c r="BC24">
-        <v>5.7</v>
-      </c>
-      <c r="BD24">
-        <v>5.7</v>
-      </c>
-      <c r="BE24">
-        <v>5.5</v>
-      </c>
-      <c r="BF24">
-        <v>5.5</v>
-      </c>
-      <c r="BG24">
-        <v>4.6</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.01</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.01</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.01</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.01</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>1.01</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>1.01</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>1.01</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>1.01</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>138</v>
+      <c r="X25">
+        <v>25</v>
+      </c>
+      <c r="Y25">
+        <v>55</v>
+      </c>
+      <c r="Z25">
+        <v>210</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>10.5</v>
+      </c>
+      <c r="AC25">
+        <v>19</v>
+      </c>
+      <c r="AD25">
+        <v>75</v>
+      </c>
+      <c r="AE25">
+        <v>420</v>
+      </c>
+      <c r="AF25">
+        <v>7.4</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <v>55</v>
+      </c>
+      <c r="AI25">
+        <v>300</v>
+      </c>
+      <c r="AJ25">
+        <v>9</v>
+      </c>
+      <c r="AK25">
+        <v>15.5</v>
+      </c>
+      <c r="AL25">
+        <v>60</v>
+      </c>
+      <c r="AM25">
+        <v>330</v>
+      </c>
+      <c r="AN25">
+        <v>4.7</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>20</v>
+      </c>
+      <c r="AQ25">
+        <v>7.4</v>
+      </c>
+      <c r="AR25">
+        <v>7.8</v>
+      </c>
+      <c r="AS25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT25">
+        <v>7.4</v>
+      </c>
+      <c r="AU25">
+        <v>13.5</v>
+      </c>
+      <c r="AV25">
+        <v>7.4</v>
+      </c>
+      <c r="AW25">
+        <v>8</v>
+      </c>
+      <c r="AX25">
+        <v>6.4</v>
+      </c>
+      <c r="AY25">
+        <v>10</v>
+      </c>
+      <c r="AZ25">
+        <v>7.2</v>
+      </c>
+      <c r="BA25">
+        <v>8</v>
+      </c>
+      <c r="BB25">
+        <v>7.8</v>
+      </c>
+      <c r="BC25">
+        <v>13</v>
+      </c>
+      <c r="BD25">
+        <v>7.6</v>
+      </c>
+      <c r="BE25">
+        <v>8</v>
+      </c>
+      <c r="BF25">
+        <v>4.2</v>
+      </c>
+      <c r="BG25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>970</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>CONCACAF Nations League A</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Serbian First League</t>
   </si>
   <si>
@@ -301,6 +304,12 @@
     <t>Jamaica</t>
   </si>
   <si>
+    <t>St Kitts &amp; Nevis</t>
+  </si>
+  <si>
+    <t>St Lucia</t>
+  </si>
+  <si>
     <t>Guatemala</t>
   </si>
   <si>
@@ -340,15 +349,15 @@
     <t>Scotland</t>
   </si>
   <si>
+    <t>Woking</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
     <t>Yeovil</t>
   </si>
   <si>
-    <t>Hartlepool</t>
-  </si>
-  <si>
-    <t>Woking</t>
-  </si>
-  <si>
     <t>Barrow</t>
   </si>
   <si>
@@ -373,6 +382,12 @@
     <t>Honduras</t>
   </si>
   <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
     <t>El Salvador</t>
   </si>
   <si>
@@ -412,15 +427,15 @@
     <t>Switzerland</t>
   </si>
   <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
     <t>Worthing</t>
   </si>
   <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Solihull Moors</t>
-  </si>
-  <si>
     <t>Scunthorpe</t>
   </si>
   <si>
@@ -442,7 +457,7 @@
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>2026-09-28 01:19:23</t>
+    <t>2026-09-28 03:29:40</t>
   </si>
 </sst>
 </file>
@@ -774,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,25 +1039,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
         <v>3.55</v>
@@ -1051,10 +1066,10 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1066,10 +1081,10 @@
         <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
         <v>1.3</v>
@@ -1078,7 +1093,7 @@
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="U2">
         <v>1.98</v>
@@ -1087,13 +1102,13 @@
         <v>1.39</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
         <v>24</v>
@@ -1117,7 +1132,7 @@
         <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>22</v>
@@ -1129,16 +1144,16 @@
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO2">
         <v>55</v>
@@ -1153,7 +1168,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>7.8</v>
@@ -1165,7 +1180,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1174,333 +1189,333 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC2">
+        <v>23</v>
+      </c>
+      <c r="BD2">
+        <v>9</v>
+      </c>
+      <c r="BE2">
+        <v>10</v>
+      </c>
+      <c r="BF2">
+        <v>18</v>
+      </c>
+      <c r="BG2">
+        <v>9.4</v>
+      </c>
+      <c r="BH2">
+        <v>3.5</v>
+      </c>
+      <c r="BI2">
+        <v>2.62</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
         <v>7.6</v>
       </c>
-      <c r="BD2">
-        <v>8.4</v>
-      </c>
-      <c r="BE2">
-        <v>9.4</v>
-      </c>
-      <c r="BF2">
-        <v>7.2</v>
-      </c>
-      <c r="BG2">
-        <v>8.6</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.01</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.01</v>
-      </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="R3">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z3">
+        <v>19.5</v>
+      </c>
+      <c r="AA3">
         <v>32</v>
       </c>
-      <c r="AA3">
-        <v>90</v>
-      </c>
       <c r="AB3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
+        <v>85</v>
+      </c>
+      <c r="AK3">
+        <v>46</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>85</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>19</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>12.5</v>
+      </c>
+      <c r="AS3">
+        <v>15</v>
+      </c>
+      <c r="AT3">
+        <v>16</v>
+      </c>
+      <c r="AU3">
+        <v>8.4</v>
+      </c>
+      <c r="AV3">
+        <v>9.4</v>
+      </c>
+      <c r="AW3">
+        <v>16</v>
+      </c>
+      <c r="AX3">
+        <v>16</v>
+      </c>
+      <c r="AY3">
+        <v>13.5</v>
+      </c>
+      <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>17.5</v>
+      </c>
+      <c r="BB3">
         <v>29</v>
       </c>
-      <c r="AK3">
-        <v>25</v>
-      </c>
-      <c r="AL3">
-        <v>48</v>
-      </c>
-      <c r="AM3">
-        <v>130</v>
-      </c>
-      <c r="AN3">
+      <c r="BC3">
         <v>19.5</v>
       </c>
-      <c r="AO3">
-        <v>65</v>
-      </c>
-      <c r="AP3">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3">
-        <v>11</v>
-      </c>
-      <c r="AR3">
-        <v>4.9</v>
-      </c>
-      <c r="AS3">
-        <v>5.4</v>
-      </c>
-      <c r="AT3">
-        <v>3.8</v>
-      </c>
-      <c r="AU3">
+      <c r="BD3">
+        <v>22</v>
+      </c>
+      <c r="BE3">
+        <v>34</v>
+      </c>
+      <c r="BF3">
+        <v>21</v>
+      </c>
+      <c r="BG3">
+        <v>7.6</v>
+      </c>
+      <c r="BH3">
+        <v>4.8</v>
+      </c>
+      <c r="BI3">
         <v>3.45</v>
       </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>5.3</v>
-      </c>
-      <c r="AX3">
+      <c r="BJ3">
+        <v>10</v>
+      </c>
+      <c r="BK3">
+        <v>6.8</v>
+      </c>
+      <c r="BL3">
+        <v>95</v>
+      </c>
+      <c r="BM3">
+        <v>60</v>
+      </c>
+      <c r="BN3">
+        <v>8.6</v>
+      </c>
+      <c r="BO3">
+        <v>5.8</v>
+      </c>
+      <c r="BP3">
+        <v>32</v>
+      </c>
+      <c r="BQ3">
+        <v>20</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
+        <v>24</v>
+      </c>
+      <c r="BT3">
+        <v>5.8</v>
+      </c>
+      <c r="BU3">
         <v>4.1</v>
       </c>
-      <c r="AY3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3">
-        <v>15.5</v>
-      </c>
-      <c r="BA3">
-        <v>5.4</v>
-      </c>
-      <c r="BB3">
-        <v>4.8</v>
-      </c>
-      <c r="BC3">
-        <v>4.7</v>
-      </c>
-      <c r="BD3">
-        <v>5.2</v>
-      </c>
-      <c r="BE3">
-        <v>5.6</v>
-      </c>
-      <c r="BF3">
-        <v>4.5</v>
-      </c>
-      <c r="BG3">
-        <v>5.3</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.01</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.01</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.01</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.01</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.01</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.01</v>
-      </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,58 +1523,58 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>2.56</v>
       </c>
       <c r="J4">
-        <v>1.15</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>920</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
+        <v>1.67</v>
+      </c>
+      <c r="R4">
         <v>1.43</v>
       </c>
-      <c r="R4">
-        <v>1.08</v>
-      </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1568,10 +1583,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1589,16 +1604,16 @@
         <v>1000</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG4">
         <v>1000</v>
@@ -1628,43 +1643,43 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC4">
         <v>1.01</v>
@@ -1676,10 +1691,10 @@
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1742,249 +1757,249 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F5">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K5">
         <v>3.7</v>
       </c>
       <c r="L5">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AK5">
         <v>25</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AN5">
+        <v>18</v>
+      </c>
+      <c r="AO5">
+        <v>65</v>
+      </c>
+      <c r="AP5">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5">
+        <v>11.5</v>
+      </c>
+      <c r="AR5">
+        <v>6.8</v>
+      </c>
+      <c r="AS5">
+        <v>7.8</v>
+      </c>
+      <c r="AT5">
+        <v>7.8</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>14</v>
+      </c>
+      <c r="AW5">
+        <v>7.4</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
         <v>16.5</v>
       </c>
-      <c r="AO5">
-        <v>210</v>
-      </c>
-      <c r="AP5">
-        <v>9</v>
-      </c>
-      <c r="AQ5">
-        <v>13.5</v>
-      </c>
-      <c r="AR5">
-        <v>20</v>
-      </c>
-      <c r="AS5">
-        <v>11</v>
-      </c>
-      <c r="AT5">
-        <v>5.8</v>
-      </c>
-      <c r="AU5">
+      <c r="BA5">
         <v>7.6</v>
       </c>
-      <c r="AV5">
-        <v>22</v>
-      </c>
-      <c r="AW5">
-        <v>11</v>
-      </c>
-      <c r="AX5">
+      <c r="BB5">
+        <v>6.4</v>
+      </c>
+      <c r="BC5">
+        <v>6.4</v>
+      </c>
+      <c r="BD5">
+        <v>7.2</v>
+      </c>
+      <c r="BE5">
         <v>8</v>
       </c>
-      <c r="AY5">
-        <v>10</v>
-      </c>
-      <c r="AZ5">
-        <v>25</v>
-      </c>
-      <c r="BA5">
-        <v>11</v>
-      </c>
-      <c r="BB5">
-        <v>16</v>
-      </c>
-      <c r="BC5">
-        <v>20</v>
-      </c>
-      <c r="BD5">
-        <v>12.5</v>
-      </c>
-      <c r="BE5">
-        <v>11</v>
-      </c>
       <c r="BF5">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="BG5">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
         <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="BM5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5">
         <v>11</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BS5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BT5">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BX5">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BZ5">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="CA5">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,241 +2007,241 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>3.05</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>2.98</v>
+        <v>1.19</v>
       </c>
       <c r="K6">
-        <v>3.05</v>
+        <v>920</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>1.11</v>
       </c>
       <c r="O6">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="P6">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="Q6">
-        <v>2.66</v>
+        <v>1.43</v>
       </c>
       <c r="R6">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,432 +2249,432 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I7">
+        <v>6.4</v>
+      </c>
+      <c r="J7">
+        <v>3.65</v>
+      </c>
+      <c r="K7">
+        <v>3.7</v>
+      </c>
+      <c r="L7">
+        <v>1.54</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
+        <v>2.8</v>
+      </c>
+      <c r="O7">
+        <v>1.5</v>
+      </c>
+      <c r="P7">
+        <v>1.61</v>
+      </c>
+      <c r="Q7">
+        <v>2.48</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>5.1</v>
+      </c>
+      <c r="T7">
+        <v>2.32</v>
+      </c>
+      <c r="U7">
+        <v>1.69</v>
+      </c>
+      <c r="V7">
+        <v>1.18</v>
+      </c>
+      <c r="W7">
+        <v>2.28</v>
+      </c>
+      <c r="X7">
+        <v>10.5</v>
+      </c>
+      <c r="Y7">
+        <v>15.5</v>
+      </c>
+      <c r="Z7">
+        <v>46</v>
+      </c>
+      <c r="AA7">
+        <v>220</v>
+      </c>
+      <c r="AB7">
+        <v>6.4</v>
+      </c>
+      <c r="AC7">
+        <v>8.6</v>
+      </c>
+      <c r="AD7">
+        <v>26</v>
+      </c>
+      <c r="AE7">
+        <v>130</v>
+      </c>
+      <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>34</v>
+      </c>
+      <c r="AI7">
+        <v>150</v>
+      </c>
+      <c r="AJ7">
+        <v>18.5</v>
+      </c>
+      <c r="AK7">
+        <v>25</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>270</v>
+      </c>
+      <c r="AN7">
+        <v>16.5</v>
+      </c>
+      <c r="AO7">
+        <v>210</v>
+      </c>
+      <c r="AP7">
+        <v>9</v>
+      </c>
+      <c r="AQ7">
+        <v>13.5</v>
+      </c>
+      <c r="AR7">
+        <v>21</v>
+      </c>
+      <c r="AS7">
+        <v>11.5</v>
+      </c>
+      <c r="AT7">
+        <v>5.9</v>
+      </c>
+      <c r="AU7">
         <v>7.6</v>
       </c>
-      <c r="J7">
-        <v>4.6</v>
-      </c>
-      <c r="K7">
-        <v>5.3</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.02</v>
-      </c>
-      <c r="N7">
-        <v>2.32</v>
-      </c>
-      <c r="O7">
-        <v>1.19</v>
-      </c>
-      <c r="P7">
-        <v>2.3</v>
-      </c>
-      <c r="Q7">
-        <v>1.56</v>
-      </c>
-      <c r="R7">
-        <v>1.54</v>
-      </c>
-      <c r="S7">
-        <v>2.32</v>
-      </c>
-      <c r="T7">
-        <v>1.68</v>
-      </c>
-      <c r="U7">
-        <v>2.08</v>
-      </c>
-      <c r="V7">
-        <v>1.15</v>
-      </c>
-      <c r="W7">
+      <c r="AV7">
+        <v>22</v>
+      </c>
+      <c r="AW7">
+        <v>11</v>
+      </c>
+      <c r="AX7">
+        <v>8</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>25</v>
+      </c>
+      <c r="BA7">
+        <v>11</v>
+      </c>
+      <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
+        <v>20</v>
+      </c>
+      <c r="BD7">
+        <v>12.5</v>
+      </c>
+      <c r="BE7">
+        <v>11</v>
+      </c>
+      <c r="BF7">
+        <v>14.5</v>
+      </c>
+      <c r="BG7">
+        <v>10.5</v>
+      </c>
+      <c r="BH7">
+        <v>2.84</v>
+      </c>
+      <c r="BI7">
         <v>2.66</v>
       </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>970</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>11.5</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>95</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>970</v>
-      </c>
-      <c r="AO7">
-        <v>100</v>
-      </c>
-      <c r="AP7">
-        <v>1.3</v>
-      </c>
-      <c r="AQ7">
-        <v>19</v>
-      </c>
-      <c r="AR7">
-        <v>1.45</v>
-      </c>
-      <c r="AS7">
-        <v>1.45</v>
-      </c>
-      <c r="AT7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV7">
-        <v>17.5</v>
-      </c>
-      <c r="AW7">
-        <v>1.3</v>
-      </c>
-      <c r="AX7">
-        <v>1.29</v>
-      </c>
-      <c r="AY7">
-        <v>1.45</v>
-      </c>
-      <c r="AZ7">
-        <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>1.43</v>
-      </c>
-      <c r="BB7">
-        <v>1.45</v>
-      </c>
-      <c r="BC7">
-        <v>1.45</v>
-      </c>
-      <c r="BD7">
-        <v>1.46</v>
-      </c>
-      <c r="BE7">
-        <v>1.3</v>
-      </c>
-      <c r="BF7">
-        <v>1.23</v>
-      </c>
-      <c r="BG7">
-        <v>1.29</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.01</v>
-      </c>
       <c r="BJ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN7">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BO7">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BV7">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BW7">
-        <v>1.02</v>
+        <v>50</v>
       </c>
       <c r="BX7">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BY7">
-        <v>1.02</v>
+        <v>21</v>
       </c>
       <c r="BZ7">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="G8">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
+        <v>2.9</v>
+      </c>
+      <c r="I8">
+        <v>2.96</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>3.05</v>
+      </c>
+      <c r="L8">
+        <v>1.55</v>
+      </c>
+      <c r="M8">
+        <v>1.14</v>
+      </c>
+      <c r="N8">
+        <v>2.64</v>
+      </c>
+      <c r="O8">
+        <v>1.57</v>
+      </c>
+      <c r="P8">
+        <v>1.53</v>
+      </c>
+      <c r="Q8">
+        <v>2.72</v>
+      </c>
+      <c r="R8">
+        <v>1.19</v>
+      </c>
+      <c r="S8">
+        <v>5.7</v>
+      </c>
+      <c r="T8">
+        <v>2.16</v>
+      </c>
+      <c r="U8">
+        <v>1.81</v>
+      </c>
+      <c r="V8">
+        <v>1.51</v>
+      </c>
+      <c r="W8">
+        <v>1.47</v>
+      </c>
+      <c r="X8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y8">
+        <v>8.6</v>
+      </c>
+      <c r="Z8">
+        <v>17.5</v>
+      </c>
+      <c r="AA8">
+        <v>55</v>
+      </c>
+      <c r="AB8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC8">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>14.5</v>
+      </c>
+      <c r="AE8">
+        <v>44</v>
+      </c>
+      <c r="AF8">
+        <v>18.5</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>26</v>
+      </c>
+      <c r="AI8">
+        <v>75</v>
+      </c>
+      <c r="AJ8">
+        <v>60</v>
+      </c>
+      <c r="AK8">
+        <v>60</v>
+      </c>
+      <c r="AL8">
+        <v>120</v>
+      </c>
+      <c r="AM8">
+        <v>220</v>
+      </c>
+      <c r="AN8">
+        <v>60</v>
+      </c>
+      <c r="AO8">
+        <v>55</v>
+      </c>
+      <c r="AP8">
+        <v>7.4</v>
+      </c>
+      <c r="AQ8">
+        <v>7.6</v>
+      </c>
+      <c r="AR8">
+        <v>15</v>
+      </c>
+      <c r="AS8">
+        <v>42</v>
+      </c>
+      <c r="AT8">
+        <v>7.8</v>
+      </c>
+      <c r="AU8">
         <v>6.4</v>
       </c>
-      <c r="I8">
-        <v>6.8</v>
-      </c>
-      <c r="J8">
-        <v>3.9</v>
-      </c>
-      <c r="K8">
-        <v>3.95</v>
-      </c>
-      <c r="L8">
-        <v>1.45</v>
-      </c>
-      <c r="M8">
-        <v>1.1</v>
-      </c>
-      <c r="N8">
-        <v>3.05</v>
-      </c>
-      <c r="O8">
-        <v>1.45</v>
-      </c>
-      <c r="P8">
-        <v>1.69</v>
-      </c>
-      <c r="Q8">
-        <v>2.32</v>
-      </c>
-      <c r="R8">
-        <v>1.26</v>
-      </c>
-      <c r="S8">
-        <v>4.6</v>
-      </c>
-      <c r="T8">
-        <v>2.26</v>
-      </c>
-      <c r="U8">
-        <v>1.72</v>
-      </c>
-      <c r="V8">
-        <v>1.17</v>
-      </c>
-      <c r="W8">
-        <v>2.44</v>
-      </c>
-      <c r="X8">
-        <v>11</v>
-      </c>
-      <c r="Y8">
-        <v>17</v>
-      </c>
-      <c r="Z8">
-        <v>55</v>
-      </c>
-      <c r="AA8">
-        <v>260</v>
-      </c>
-      <c r="AB8">
-        <v>6.4</v>
-      </c>
-      <c r="AC8">
-        <v>9</v>
-      </c>
-      <c r="AD8">
-        <v>30</v>
-      </c>
-      <c r="AE8">
-        <v>130</v>
-      </c>
-      <c r="AF8">
-        <v>8.6</v>
-      </c>
-      <c r="AG8">
-        <v>11</v>
-      </c>
-      <c r="AH8">
-        <v>30</v>
-      </c>
-      <c r="AI8">
-        <v>150</v>
-      </c>
-      <c r="AJ8">
-        <v>16.5</v>
-      </c>
-      <c r="AK8">
-        <v>23</v>
-      </c>
-      <c r="AL8">
-        <v>55</v>
-      </c>
-      <c r="AM8">
-        <v>240</v>
-      </c>
-      <c r="AN8">
-        <v>14</v>
-      </c>
-      <c r="AO8">
-        <v>220</v>
-      </c>
-      <c r="AP8">
-        <v>10</v>
-      </c>
-      <c r="AQ8">
-        <v>14.5</v>
-      </c>
-      <c r="AR8">
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>22</v>
+      </c>
+      <c r="AX8">
+        <v>16</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>21</v>
+      </c>
+      <c r="BA8">
+        <v>60</v>
+      </c>
+      <c r="BB8">
         <v>46</v>
       </c>
-      <c r="AS8">
-        <v>13.5</v>
-      </c>
-      <c r="AT8">
-        <v>6</v>
-      </c>
-      <c r="AU8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV8">
-        <v>24</v>
-      </c>
-      <c r="AW8">
-        <v>14.5</v>
-      </c>
-      <c r="AX8">
-        <v>7.6</v>
-      </c>
-      <c r="AY8">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8">
-        <v>25</v>
-      </c>
-      <c r="BA8">
-        <v>13.5</v>
-      </c>
-      <c r="BB8">
-        <v>14.5</v>
-      </c>
       <c r="BC8">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="BD8">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BE8">
         <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BH8">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="BK8">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2668,1743 +2683,1743 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BO8">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BR8">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BS8">
         <v>21</v>
       </c>
       <c r="BT8">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="BW8">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8">
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="CA8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>1.51</v>
       </c>
       <c r="G9">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="H9">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
-        <v>2.54</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>5.3</v>
+      </c>
+      <c r="O9">
+        <v>1.19</v>
+      </c>
+      <c r="P9">
+        <v>2.3</v>
+      </c>
+      <c r="Q9">
+        <v>1.56</v>
+      </c>
+      <c r="R9">
+        <v>1.54</v>
+      </c>
+      <c r="S9">
+        <v>2.32</v>
+      </c>
+      <c r="T9">
+        <v>1.68</v>
+      </c>
+      <c r="U9">
+        <v>2.12</v>
+      </c>
+      <c r="V9">
+        <v>1.15</v>
+      </c>
+      <c r="W9">
+        <v>2.72</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>970</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>970</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>95</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>970</v>
+      </c>
+      <c r="AO9">
+        <v>100</v>
+      </c>
+      <c r="AP9">
+        <v>1.49</v>
+      </c>
+      <c r="AQ9">
+        <v>19</v>
+      </c>
+      <c r="AR9">
+        <v>1.69</v>
+      </c>
+      <c r="AS9">
+        <v>1.49</v>
+      </c>
+      <c r="AT9">
+        <v>1.48</v>
+      </c>
+      <c r="AU9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV9">
+        <v>17.5</v>
+      </c>
+      <c r="AW9">
+        <v>1.49</v>
+      </c>
+      <c r="AX9">
+        <v>9</v>
+      </c>
+      <c r="AY9">
         <v>1.45</v>
       </c>
-      <c r="M9">
-        <v>1.09</v>
-      </c>
-      <c r="N9">
-        <v>3.35</v>
-      </c>
-      <c r="O9">
+      <c r="AZ9">
+        <v>1.69</v>
+      </c>
+      <c r="BA9">
+        <v>1.55</v>
+      </c>
+      <c r="BB9">
+        <v>1.69</v>
+      </c>
+      <c r="BC9">
+        <v>1.68</v>
+      </c>
+      <c r="BD9">
+        <v>1.69</v>
+      </c>
+      <c r="BE9">
+        <v>1.49</v>
+      </c>
+      <c r="BF9">
         <v>1.39</v>
       </c>
-      <c r="P9">
-        <v>1.8</v>
-      </c>
-      <c r="Q9">
-        <v>2.18</v>
-      </c>
-      <c r="R9">
-        <v>1.3</v>
-      </c>
-      <c r="S9">
-        <v>4</v>
-      </c>
-      <c r="T9">
-        <v>1.91</v>
-      </c>
-      <c r="U9">
-        <v>2.04</v>
-      </c>
-      <c r="V9">
-        <v>1.64</v>
-      </c>
-      <c r="W9">
-        <v>1.44</v>
-      </c>
-      <c r="X9">
-        <v>12</v>
-      </c>
-      <c r="Y9">
-        <v>9.6</v>
-      </c>
-      <c r="Z9">
-        <v>15.5</v>
-      </c>
-      <c r="AA9">
-        <v>36</v>
-      </c>
-      <c r="AB9">
-        <v>11.5</v>
-      </c>
-      <c r="AC9">
-        <v>7.6</v>
-      </c>
-      <c r="AD9">
-        <v>12</v>
-      </c>
-      <c r="AE9">
-        <v>34</v>
-      </c>
-      <c r="AF9">
-        <v>22</v>
-      </c>
-      <c r="AG9">
+      <c r="BG9">
+        <v>1.47</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
         <v>14.5</v>
       </c>
-      <c r="AH9">
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>6</v>
+      </c>
+      <c r="BO9">
+        <v>3.1</v>
+      </c>
+      <c r="BP9">
+        <v>13.5</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>30</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>15</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>70</v>
+      </c>
+      <c r="BW9">
+        <v>1.02</v>
+      </c>
+      <c r="BX9">
+        <v>70</v>
+      </c>
+      <c r="BY9">
+        <v>1.02</v>
+      </c>
+      <c r="BZ9">
         <v>19</v>
       </c>
-      <c r="AI9">
-        <v>55</v>
-      </c>
-      <c r="AJ9">
-        <v>65</v>
-      </c>
-      <c r="AK9">
-        <v>42</v>
-      </c>
-      <c r="AL9">
-        <v>55</v>
-      </c>
-      <c r="AM9">
-        <v>120</v>
-      </c>
-      <c r="AN9">
-        <v>44</v>
-      </c>
-      <c r="AO9">
-        <v>27</v>
-      </c>
-      <c r="AP9">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9">
-        <v>13.5</v>
-      </c>
-      <c r="AS9">
-        <v>30</v>
-      </c>
-      <c r="AT9">
-        <v>10.5</v>
-      </c>
-      <c r="AU9">
-        <v>6.8</v>
-      </c>
-      <c r="AV9">
-        <v>10.5</v>
-      </c>
-      <c r="AW9">
-        <v>25</v>
-      </c>
-      <c r="AX9">
-        <v>18.5</v>
-      </c>
-      <c r="AY9">
-        <v>13</v>
-      </c>
-      <c r="AZ9">
-        <v>17.5</v>
-      </c>
-      <c r="BA9">
-        <v>40</v>
-      </c>
-      <c r="BB9">
-        <v>12.5</v>
-      </c>
-      <c r="BC9">
-        <v>34</v>
-      </c>
-      <c r="BD9">
-        <v>46</v>
-      </c>
-      <c r="BE9">
-        <v>14</v>
-      </c>
-      <c r="BF9">
-        <v>12</v>
-      </c>
-      <c r="BG9">
-        <v>22</v>
-      </c>
-      <c r="BH9">
-        <v>3.4</v>
-      </c>
-      <c r="BI9">
-        <v>2.66</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>7.2</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>21</v>
-      </c>
-      <c r="BN9">
-        <v>7.2</v>
-      </c>
-      <c r="BO9">
-        <v>5.3</v>
-      </c>
-      <c r="BP9">
-        <v>38</v>
-      </c>
-      <c r="BQ9">
-        <v>17.5</v>
-      </c>
-      <c r="BR9">
-        <v>55</v>
-      </c>
-      <c r="BS9">
-        <v>21</v>
-      </c>
-      <c r="BT9">
-        <v>6.2</v>
-      </c>
-      <c r="BU9">
-        <v>4.5</v>
-      </c>
-      <c r="BV9">
-        <v>26</v>
-      </c>
-      <c r="BW9">
-        <v>14</v>
-      </c>
-      <c r="BX9">
-        <v>48</v>
-      </c>
-      <c r="BY9">
-        <v>21</v>
-      </c>
-      <c r="BZ9">
-        <v>46</v>
-      </c>
       <c r="CA9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="G10">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="H10">
+        <v>6.6</v>
+      </c>
+      <c r="I10">
+        <v>6.8</v>
+      </c>
+      <c r="J10">
+        <v>3.9</v>
+      </c>
+      <c r="K10">
+        <v>3.95</v>
+      </c>
+      <c r="L10">
+        <v>1.45</v>
+      </c>
+      <c r="M10">
+        <v>1.1</v>
+      </c>
+      <c r="N10">
+        <v>3.05</v>
+      </c>
+      <c r="O10">
+        <v>1.45</v>
+      </c>
+      <c r="P10">
+        <v>1.69</v>
+      </c>
+      <c r="Q10">
+        <v>2.32</v>
+      </c>
+      <c r="R10">
+        <v>1.26</v>
+      </c>
+      <c r="S10">
+        <v>4.6</v>
+      </c>
+      <c r="T10">
+        <v>2.28</v>
+      </c>
+      <c r="U10">
+        <v>1.72</v>
+      </c>
+      <c r="V10">
+        <v>1.17</v>
+      </c>
+      <c r="W10">
+        <v>2.44</v>
+      </c>
+      <c r="X10">
+        <v>11</v>
+      </c>
+      <c r="Y10">
+        <v>17</v>
+      </c>
+      <c r="Z10">
+        <v>55</v>
+      </c>
+      <c r="AA10">
+        <v>260</v>
+      </c>
+      <c r="AB10">
+        <v>6.4</v>
+      </c>
+      <c r="AC10">
+        <v>9</v>
+      </c>
+      <c r="AD10">
+        <v>30</v>
+      </c>
+      <c r="AE10">
+        <v>130</v>
+      </c>
+      <c r="AF10">
+        <v>8.6</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>30</v>
+      </c>
+      <c r="AI10">
+        <v>150</v>
+      </c>
+      <c r="AJ10">
         <v>16.5</v>
       </c>
-      <c r="I10">
-        <v>17.5</v>
-      </c>
-      <c r="J10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K10">
-        <v>8.4</v>
-      </c>
-      <c r="L10">
-        <v>1.29</v>
-      </c>
-      <c r="M10">
-        <v>1.03</v>
-      </c>
-      <c r="N10">
-        <v>6.2</v>
-      </c>
-      <c r="O10">
-        <v>1.17</v>
-      </c>
-      <c r="P10">
-        <v>2.8</v>
-      </c>
-      <c r="Q10">
-        <v>1.53</v>
-      </c>
-      <c r="R10">
-        <v>1.72</v>
-      </c>
-      <c r="S10">
-        <v>2.3</v>
-      </c>
-      <c r="T10">
-        <v>2.26</v>
-      </c>
-      <c r="U10">
-        <v>1.75</v>
-      </c>
-      <c r="V10">
-        <v>1.06</v>
-      </c>
-      <c r="W10">
-        <v>5.4</v>
-      </c>
-      <c r="X10">
-        <v>38</v>
-      </c>
-      <c r="Y10">
-        <v>50</v>
-      </c>
-      <c r="Z10">
-        <v>200</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>10.5</v>
-      </c>
-      <c r="AC10">
-        <v>22</v>
-      </c>
-      <c r="AD10">
-        <v>70</v>
-      </c>
-      <c r="AE10">
-        <v>350</v>
-      </c>
-      <c r="AF10">
-        <v>8</v>
-      </c>
-      <c r="AG10">
-        <v>12.5</v>
-      </c>
-      <c r="AH10">
-        <v>48</v>
-      </c>
-      <c r="AI10">
+      <c r="AK10">
+        <v>23</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
         <v>240</v>
       </c>
-      <c r="AJ10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK10">
-        <v>13.5</v>
-      </c>
-      <c r="AL10">
-        <v>44</v>
-      </c>
-      <c r="AM10">
-        <v>270</v>
-      </c>
       <c r="AN10">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="AO10">
-        <v>490</v>
+        <v>220</v>
       </c>
       <c r="AP10">
         <v>10</v>
       </c>
       <c r="AQ10">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AR10">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="AS10">
+        <v>13</v>
+      </c>
+      <c r="AT10">
+        <v>6</v>
+      </c>
+      <c r="AU10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV10">
+        <v>24</v>
+      </c>
+      <c r="AW10">
+        <v>14.5</v>
+      </c>
+      <c r="AX10">
+        <v>7.6</v>
+      </c>
+      <c r="AY10">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10">
+        <v>25</v>
+      </c>
+      <c r="BA10">
         <v>13.5</v>
       </c>
-      <c r="AT10">
-        <v>9.4</v>
-      </c>
-      <c r="AU10">
-        <v>16.5</v>
-      </c>
-      <c r="AV10">
-        <v>42</v>
-      </c>
-      <c r="AW10">
-        <v>13</v>
-      </c>
-      <c r="AX10">
-        <v>7.2</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
-      <c r="AZ10">
-        <v>30</v>
-      </c>
-      <c r="BA10">
-        <v>12.5</v>
-      </c>
       <c r="BB10">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BC10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BD10">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE10">
         <v>13</v>
       </c>
       <c r="BF10">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="BG10">
         <v>13</v>
       </c>
       <c r="BH10">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="BI10">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="BK10">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
         <v>21</v>
       </c>
       <c r="BN10">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP10">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BQ10">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BS10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BT10">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="BW10">
         <v>21</v>
       </c>
       <c r="BX10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>21</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>85</v>
+        <v>3.3</v>
       </c>
       <c r="H11">
-        <v>1.06</v>
+        <v>2.48</v>
       </c>
       <c r="I11">
-        <v>1.07</v>
+        <v>2.54</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>23</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="Q11">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.92</v>
+        <v>1.31</v>
       </c>
       <c r="S11">
-        <v>1.99</v>
+        <v>4</v>
       </c>
       <c r="T11">
-        <v>3.95</v>
+        <v>1.88</v>
       </c>
       <c r="U11">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="V11">
-        <v>15</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X11">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="Y11">
+        <v>9.6</v>
+      </c>
+      <c r="Z11">
+        <v>15.5</v>
+      </c>
+      <c r="AA11">
+        <v>34</v>
+      </c>
+      <c r="AB11">
         <v>11.5</v>
       </c>
-      <c r="Z11">
-        <v>7.2</v>
-      </c>
-      <c r="AA11">
-        <v>7</v>
-      </c>
-      <c r="AB11">
-        <v>170</v>
-      </c>
       <c r="AC11">
-        <v>70</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AE11">
+        <v>34</v>
+      </c>
+      <c r="AF11">
         <v>22</v>
       </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
       <c r="AG11">
-        <v>350</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>200</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO11">
-        <v>2.42</v>
+        <v>25</v>
       </c>
       <c r="AP11">
         <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS11">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="AT11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
         <v>10.5</v>
       </c>
-      <c r="AV11">
+      <c r="AW11">
+        <v>25</v>
+      </c>
+      <c r="AX11">
         <v>18.5</v>
       </c>
-      <c r="AW11">
-        <v>18.5</v>
-      </c>
-      <c r="AX11">
+      <c r="AY11">
         <v>12.5</v>
       </c>
-      <c r="AY11">
-        <v>12</v>
-      </c>
       <c r="AZ11">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BB11">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BC11">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BD11">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BE11">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
         <v>12.5</v>
       </c>
       <c r="BG11">
-        <v>2.28</v>
+        <v>22</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BK11">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM11">
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>70</v>
+        <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BT11">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BU11">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="BV11">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BW11">
-        <v>3.4</v>
+        <v>16.5</v>
       </c>
       <c r="BX11">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BZ11">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>3.8</v>
+        <v>28</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>9.6</v>
+        <v>1.22</v>
       </c>
       <c r="G12">
+        <v>1.23</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
+      </c>
+      <c r="I12">
+        <v>16.5</v>
+      </c>
+      <c r="J12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K12">
+        <v>8.4</v>
+      </c>
+      <c r="L12">
+        <v>1.29</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>6.2</v>
+      </c>
+      <c r="O12">
+        <v>1.17</v>
+      </c>
+      <c r="P12">
+        <v>2.82</v>
+      </c>
+      <c r="Q12">
+        <v>1.53</v>
+      </c>
+      <c r="R12">
+        <v>1.72</v>
+      </c>
+      <c r="S12">
+        <v>2.3</v>
+      </c>
+      <c r="T12">
+        <v>2.26</v>
+      </c>
+      <c r="U12">
+        <v>1.75</v>
+      </c>
+      <c r="V12">
+        <v>1.06</v>
+      </c>
+      <c r="W12">
+        <v>5.4</v>
+      </c>
+      <c r="X12">
+        <v>38</v>
+      </c>
+      <c r="Y12">
+        <v>50</v>
+      </c>
+      <c r="Z12">
+        <v>200</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
         <v>10.5</v>
       </c>
-      <c r="H12">
-        <v>1.4</v>
-      </c>
-      <c r="I12">
-        <v>1.42</v>
-      </c>
-      <c r="J12">
-        <v>5.2</v>
-      </c>
-      <c r="K12">
-        <v>5.4</v>
-      </c>
-      <c r="L12">
-        <v>1.3</v>
-      </c>
-      <c r="M12">
-        <v>1.05</v>
-      </c>
-      <c r="N12">
-        <v>4.7</v>
-      </c>
-      <c r="O12">
-        <v>1.25</v>
-      </c>
-      <c r="P12">
-        <v>2.26</v>
-      </c>
-      <c r="Q12">
-        <v>1.75</v>
-      </c>
-      <c r="R12">
-        <v>1.49</v>
-      </c>
-      <c r="S12">
-        <v>2.88</v>
-      </c>
-      <c r="T12">
-        <v>2.06</v>
-      </c>
-      <c r="U12">
-        <v>1.89</v>
-      </c>
-      <c r="V12">
-        <v>3.35</v>
-      </c>
-      <c r="W12">
-        <v>1.11</v>
-      </c>
-      <c r="X12">
-        <v>20</v>
-      </c>
-      <c r="Y12">
+      <c r="AC12">
+        <v>22</v>
+      </c>
+      <c r="AD12">
+        <v>70</v>
+      </c>
+      <c r="AE12">
+        <v>340</v>
+      </c>
+      <c r="AF12">
+        <v>8</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>50</v>
+      </c>
+      <c r="AI12">
+        <v>230</v>
+      </c>
+      <c r="AJ12">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA12">
+      <c r="AK12">
+        <v>14</v>
+      </c>
+      <c r="AL12">
+        <v>44</v>
+      </c>
+      <c r="AM12">
+        <v>270</v>
+      </c>
+      <c r="AN12">
+        <v>3.75</v>
+      </c>
+      <c r="AO12">
+        <v>520</v>
+      </c>
+      <c r="AP12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>36</v>
+      </c>
+      <c r="AR12">
+        <v>12</v>
+      </c>
+      <c r="AS12">
+        <v>13</v>
+      </c>
+      <c r="AT12">
+        <v>9.4</v>
+      </c>
+      <c r="AU12">
+        <v>16.5</v>
+      </c>
+      <c r="AV12">
         <v>11.5</v>
       </c>
-      <c r="AB12">
-        <v>32</v>
-      </c>
-      <c r="AC12">
+      <c r="AW12">
+        <v>12.5</v>
+      </c>
+      <c r="AX12">
+        <v>7.2</v>
+      </c>
+      <c r="AY12">
+        <v>11</v>
+      </c>
+      <c r="AZ12">
+        <v>30</v>
+      </c>
+      <c r="BA12">
         <v>12</v>
       </c>
-      <c r="AD12">
-        <v>10</v>
-      </c>
-      <c r="AE12">
-        <v>15</v>
-      </c>
-      <c r="AF12">
-        <v>90</v>
-      </c>
-      <c r="AG12">
-        <v>36</v>
-      </c>
-      <c r="AH12">
-        <v>26</v>
-      </c>
-      <c r="AI12">
-        <v>36</v>
-      </c>
-      <c r="AJ12">
-        <v>420</v>
-      </c>
-      <c r="AK12">
-        <v>190</v>
-      </c>
-      <c r="AL12">
-        <v>130</v>
-      </c>
-      <c r="AM12">
-        <v>180</v>
-      </c>
-      <c r="AN12">
-        <v>190</v>
-      </c>
-      <c r="AO12">
-        <v>6</v>
-      </c>
-      <c r="AP12">
-        <v>17.5</v>
-      </c>
-      <c r="AQ12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR12">
-        <v>7.6</v>
-      </c>
-      <c r="AS12">
-        <v>10.5</v>
-      </c>
-      <c r="AT12">
-        <v>28</v>
-      </c>
-      <c r="AU12">
-        <v>10.5</v>
-      </c>
-      <c r="AV12">
-        <v>9.4</v>
-      </c>
-      <c r="AW12">
-        <v>14</v>
-      </c>
-      <c r="AX12">
-        <v>75</v>
-      </c>
-      <c r="AY12">
-        <v>32</v>
-      </c>
-      <c r="AZ12">
-        <v>24</v>
-      </c>
-      <c r="BA12">
-        <v>32</v>
-      </c>
       <c r="BB12">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE12">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="BF12">
-        <v>140</v>
+        <v>3.4</v>
       </c>
       <c r="BG12">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BI12">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BK12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BL12">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="BM12">
         <v>21</v>
       </c>
       <c r="BN12">
-        <v>15</v>
+        <v>3.6</v>
       </c>
       <c r="BO12">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="BP12">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="BQ12">
+        <v>6</v>
+      </c>
+      <c r="BR12">
+        <v>24</v>
+      </c>
+      <c r="BS12">
+        <v>17.5</v>
+      </c>
+      <c r="BT12">
+        <v>22</v>
+      </c>
+      <c r="BU12">
+        <v>14</v>
+      </c>
+      <c r="BV12">
+        <v>170</v>
+      </c>
+      <c r="BW12">
         <v>21</v>
       </c>
-      <c r="BR12">
-        <v>90</v>
-      </c>
-      <c r="BS12">
+      <c r="BX12">
+        <v>140</v>
+      </c>
+      <c r="BY12">
         <v>21</v>
       </c>
-      <c r="BT12">
-        <v>3.8</v>
-      </c>
-      <c r="BU12">
-        <v>3.5</v>
-      </c>
-      <c r="BV12">
-        <v>9.4</v>
-      </c>
-      <c r="BW12">
-        <v>7.4</v>
-      </c>
-      <c r="BX12">
-        <v>28</v>
-      </c>
-      <c r="BY12">
-        <v>18</v>
-      </c>
       <c r="BZ12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
+        <v>1.06</v>
+      </c>
+      <c r="I13">
+        <v>1.07</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <v>23</v>
+      </c>
+      <c r="L13">
+        <v>1.16</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>7.8</v>
+      </c>
+      <c r="O13">
+        <v>1.13</v>
+      </c>
+      <c r="P13">
+        <v>3.25</v>
+      </c>
+      <c r="Q13">
+        <v>1.39</v>
+      </c>
+      <c r="R13">
+        <v>1.88</v>
+      </c>
+      <c r="S13">
+        <v>2.04</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
         <v>1.3</v>
       </c>
-      <c r="G13">
-        <v>1.31</v>
-      </c>
-      <c r="H13">
-        <v>14</v>
-      </c>
-      <c r="I13">
-        <v>16.5</v>
-      </c>
-      <c r="J13">
-        <v>5.9</v>
-      </c>
-      <c r="K13">
+      <c r="V13">
+        <v>15</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>55</v>
+      </c>
+      <c r="Y13">
+        <v>11.5</v>
+      </c>
+      <c r="Z13">
+        <v>7</v>
+      </c>
+      <c r="AA13">
         <v>6.2</v>
       </c>
-      <c r="L13">
-        <v>1.36</v>
-      </c>
-      <c r="M13">
-        <v>1.06</v>
-      </c>
-      <c r="N13">
-        <v>3.9</v>
-      </c>
-      <c r="O13">
-        <v>1.32</v>
-      </c>
-      <c r="P13">
-        <v>2</v>
-      </c>
-      <c r="Q13">
-        <v>1.95</v>
-      </c>
-      <c r="R13">
-        <v>1.39</v>
-      </c>
-      <c r="S13">
-        <v>3.45</v>
-      </c>
-      <c r="T13">
-        <v>2.7</v>
-      </c>
-      <c r="U13">
-        <v>1.54</v>
-      </c>
-      <c r="V13">
-        <v>1.06</v>
-      </c>
-      <c r="W13">
-        <v>4.1</v>
-      </c>
-      <c r="X13">
-        <v>16</v>
-      </c>
-      <c r="Y13">
-        <v>38</v>
-      </c>
-      <c r="Z13">
+      <c r="AB13">
+        <v>180</v>
+      </c>
+      <c r="AC13">
+        <v>75</v>
+      </c>
+      <c r="AD13">
+        <v>23</v>
+      </c>
+      <c r="AE13">
+        <v>23</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>370</v>
+      </c>
+      <c r="AH13">
+        <v>220</v>
+      </c>
+      <c r="AI13">
         <v>170</v>
       </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>7</v>
-      </c>
-      <c r="AC13">
-        <v>14</v>
-      </c>
-      <c r="AD13">
-        <v>60</v>
-      </c>
-      <c r="AE13">
-        <v>410</v>
-      </c>
-      <c r="AF13">
-        <v>6.6</v>
-      </c>
-      <c r="AG13">
-        <v>12</v>
-      </c>
-      <c r="AH13">
-        <v>60</v>
-      </c>
-      <c r="AI13">
-        <v>330</v>
-      </c>
       <c r="AJ13">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>2.5</v>
+      </c>
+      <c r="AP13">
+        <v>11</v>
+      </c>
+      <c r="AQ13">
+        <v>9.4</v>
+      </c>
+      <c r="AR13">
         <v>6</v>
       </c>
-      <c r="AO13">
-        <v>760</v>
-      </c>
-      <c r="AP13">
-        <v>14</v>
-      </c>
-      <c r="AQ13">
-        <v>32</v>
-      </c>
-      <c r="AR13">
-        <v>16.5</v>
-      </c>
       <c r="AS13">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT13">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AU13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV13">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AW13">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX13">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
         <v>13</v>
       </c>
       <c r="BA13">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB13">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC13">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD13">
+        <v>13.5</v>
+      </c>
+      <c r="BE13">
+        <v>13.5</v>
+      </c>
+      <c r="BF13">
+        <v>13.5</v>
+      </c>
+      <c r="BG13">
+        <v>2.32</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>40</v>
+      </c>
+      <c r="BK13">
+        <v>18.5</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>21</v>
+      </c>
+      <c r="BN13">
+        <v>70</v>
+      </c>
+      <c r="BO13">
+        <v>21</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>21</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>21</v>
+      </c>
+      <c r="BT13">
+        <v>4.3</v>
+      </c>
+      <c r="BU13">
+        <v>2.48</v>
+      </c>
+      <c r="BV13">
+        <v>6.2</v>
+      </c>
+      <c r="BW13">
+        <v>3.4</v>
+      </c>
+      <c r="BX13">
         <v>50</v>
       </c>
-      <c r="BE13">
-        <v>16</v>
-      </c>
-      <c r="BF13">
-        <v>5.6</v>
-      </c>
-      <c r="BG13">
-        <v>16.5</v>
-      </c>
-      <c r="BH13">
-        <v>3.8</v>
-      </c>
-      <c r="BI13">
-        <v>2.92</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>10</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
+      <c r="BY13">
+        <v>21</v>
+      </c>
+      <c r="BZ13">
+        <v>7.6</v>
+      </c>
+      <c r="CA13">
         <v>3.85</v>
       </c>
-      <c r="BO13">
-        <v>2.92</v>
-      </c>
-      <c r="BP13">
-        <v>11</v>
-      </c>
-      <c r="BQ13">
-        <v>5.8</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>9.4</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>1.01</v>
-      </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F14">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>1.74</v>
+        <v>10.5</v>
       </c>
       <c r="H14">
-        <v>6.4</v>
+        <v>1.39</v>
       </c>
       <c r="I14">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="M14">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="P14">
-        <v>1.64</v>
+        <v>2.28</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="V14">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="W14">
-        <v>2.34</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
+        <v>19.5</v>
+      </c>
+      <c r="Y14">
+        <v>8.6</v>
+      </c>
+      <c r="Z14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA14">
+        <v>11.5</v>
+      </c>
+      <c r="AB14">
+        <v>32</v>
+      </c>
+      <c r="AC14">
+        <v>12</v>
+      </c>
+      <c r="AD14">
         <v>10</v>
       </c>
-      <c r="Y14">
-        <v>16.5</v>
-      </c>
-      <c r="Z14">
-        <v>65</v>
-      </c>
-      <c r="AA14">
-        <v>280</v>
-      </c>
-      <c r="AB14">
-        <v>6.4</v>
-      </c>
-      <c r="AC14">
-        <v>8.6</v>
-      </c>
-      <c r="AD14">
+      <c r="AE14">
+        <v>15</v>
+      </c>
+      <c r="AF14">
+        <v>110</v>
+      </c>
+      <c r="AG14">
+        <v>36</v>
+      </c>
+      <c r="AH14">
+        <v>26</v>
+      </c>
+      <c r="AI14">
+        <v>38</v>
+      </c>
+      <c r="AJ14">
+        <v>460</v>
+      </c>
+      <c r="AK14">
+        <v>190</v>
+      </c>
+      <c r="AL14">
+        <v>140</v>
+      </c>
+      <c r="AM14">
+        <v>170</v>
+      </c>
+      <c r="AN14">
+        <v>200</v>
+      </c>
+      <c r="AO14">
+        <v>5.9</v>
+      </c>
+      <c r="AP14">
+        <v>17.5</v>
+      </c>
+      <c r="AQ14">
+        <v>8</v>
+      </c>
+      <c r="AR14">
+        <v>7.6</v>
+      </c>
+      <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
         <v>28</v>
       </c>
-      <c r="AE14">
-        <v>160</v>
-      </c>
-      <c r="AF14">
-        <v>8.6</v>
-      </c>
-      <c r="AG14">
+      <c r="AU14">
+        <v>10.5</v>
+      </c>
+      <c r="AV14">
+        <v>9.4</v>
+      </c>
+      <c r="AW14">
+        <v>14</v>
+      </c>
+      <c r="AX14">
+        <v>75</v>
+      </c>
+      <c r="AY14">
+        <v>32</v>
+      </c>
+      <c r="AZ14">
+        <v>24</v>
+      </c>
+      <c r="BA14">
+        <v>32</v>
+      </c>
+      <c r="BB14">
+        <v>21</v>
+      </c>
+      <c r="BC14">
+        <v>21</v>
+      </c>
+      <c r="BD14">
+        <v>20</v>
+      </c>
+      <c r="BE14">
+        <v>100</v>
+      </c>
+      <c r="BF14">
+        <v>140</v>
+      </c>
+      <c r="BG14">
+        <v>5.6</v>
+      </c>
+      <c r="BH14">
+        <v>3.9</v>
+      </c>
+      <c r="BI14">
+        <v>3.55</v>
+      </c>
+      <c r="BJ14">
+        <v>14</v>
+      </c>
+      <c r="BK14">
+        <v>10.5</v>
+      </c>
+      <c r="BL14">
+        <v>180</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>15.5</v>
+      </c>
+      <c r="BO14">
         <v>11</v>
       </c>
-      <c r="AH14">
-        <v>29</v>
-      </c>
-      <c r="AI14">
-        <v>160</v>
-      </c>
-      <c r="AJ14">
-        <v>17</v>
-      </c>
-      <c r="AK14">
-        <v>23</v>
-      </c>
-      <c r="AL14">
-        <v>65</v>
-      </c>
-      <c r="AM14">
-        <v>260</v>
-      </c>
-      <c r="AN14">
-        <v>16</v>
-      </c>
-      <c r="AO14">
-        <v>280</v>
-      </c>
-      <c r="AP14">
+      <c r="BP14">
+        <v>100</v>
+      </c>
+      <c r="BQ14">
+        <v>21</v>
+      </c>
+      <c r="BR14">
+        <v>90</v>
+      </c>
+      <c r="BS14">
+        <v>21</v>
+      </c>
+      <c r="BT14">
+        <v>3.8</v>
+      </c>
+      <c r="BU14">
+        <v>3.5</v>
+      </c>
+      <c r="BV14">
         <v>9</v>
       </c>
-      <c r="AQ14">
-        <v>14</v>
-      </c>
-      <c r="AR14">
-        <v>11.5</v>
-      </c>
-      <c r="AS14">
-        <v>13.5</v>
-      </c>
-      <c r="AT14">
-        <v>5.7</v>
-      </c>
-      <c r="AU14">
-        <v>7.6</v>
-      </c>
-      <c r="AV14">
-        <v>18.5</v>
-      </c>
-      <c r="AW14">
-        <v>13</v>
-      </c>
-      <c r="AX14">
-        <v>7.6</v>
-      </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
-        <v>21</v>
-      </c>
-      <c r="BA14">
-        <v>13</v>
-      </c>
-      <c r="BB14">
-        <v>15</v>
-      </c>
-      <c r="BC14">
-        <v>19</v>
-      </c>
-      <c r="BD14">
-        <v>11.5</v>
-      </c>
-      <c r="BE14">
-        <v>13</v>
-      </c>
-      <c r="BF14">
-        <v>13.5</v>
-      </c>
-      <c r="BG14">
-        <v>13.5</v>
-      </c>
-      <c r="BH14">
-        <v>3.05</v>
-      </c>
-      <c r="BI14">
-        <v>2.48</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>8.4</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>4.6</v>
-      </c>
-      <c r="BO14">
-        <v>3.35</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.01</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
+      <c r="BW14">
         <v>7.2</v>
       </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.01</v>
-      </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="G15">
-        <v>4.5</v>
+        <v>1.31</v>
       </c>
       <c r="H15">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="I15">
-        <v>2.02</v>
+        <v>16.5</v>
       </c>
       <c r="J15">
+        <v>5.9</v>
+      </c>
+      <c r="K15">
+        <v>6.2</v>
+      </c>
+      <c r="L15">
+        <v>1.39</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>3.85</v>
+      </c>
+      <c r="O15">
+        <v>1.32</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>1.95</v>
+      </c>
+      <c r="R15">
+        <v>1.38</v>
+      </c>
+      <c r="S15">
+        <v>3.35</v>
+      </c>
+      <c r="T15">
+        <v>2.7</v>
+      </c>
+      <c r="U15">
+        <v>1.54</v>
+      </c>
+      <c r="V15">
+        <v>1.06</v>
+      </c>
+      <c r="W15">
+        <v>4.1</v>
+      </c>
+      <c r="X15">
+        <v>16</v>
+      </c>
+      <c r="Y15">
+        <v>38</v>
+      </c>
+      <c r="Z15">
+        <v>170</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>7</v>
+      </c>
+      <c r="AC15">
+        <v>14</v>
+      </c>
+      <c r="AD15">
+        <v>60</v>
+      </c>
+      <c r="AE15">
+        <v>410</v>
+      </c>
+      <c r="AF15">
+        <v>6.6</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>48</v>
+      </c>
+      <c r="AI15">
+        <v>290</v>
+      </c>
+      <c r="AJ15">
+        <v>9</v>
+      </c>
+      <c r="AK15">
+        <v>17.5</v>
+      </c>
+      <c r="AL15">
+        <v>65</v>
+      </c>
+      <c r="AM15">
+        <v>410</v>
+      </c>
+      <c r="AN15">
+        <v>6</v>
+      </c>
+      <c r="AO15">
+        <v>760</v>
+      </c>
+      <c r="AP15">
+        <v>14</v>
+      </c>
+      <c r="AQ15">
+        <v>32</v>
+      </c>
+      <c r="AR15">
+        <v>16.5</v>
+      </c>
+      <c r="AS15">
+        <v>16.5</v>
+      </c>
+      <c r="AT15">
+        <v>6.4</v>
+      </c>
+      <c r="AU15">
+        <v>12.5</v>
+      </c>
+      <c r="AV15">
+        <v>44</v>
+      </c>
+      <c r="AW15">
+        <v>16</v>
+      </c>
+      <c r="AX15">
+        <v>6</v>
+      </c>
+      <c r="AY15">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15">
+        <v>13</v>
+      </c>
+      <c r="BA15">
+        <v>17.5</v>
+      </c>
+      <c r="BB15">
+        <v>8.4</v>
+      </c>
+      <c r="BC15">
+        <v>15.5</v>
+      </c>
+      <c r="BD15">
+        <v>50</v>
+      </c>
+      <c r="BE15">
+        <v>16</v>
+      </c>
+      <c r="BF15">
+        <v>5.8</v>
+      </c>
+      <c r="BG15">
+        <v>16.5</v>
+      </c>
+      <c r="BH15">
         <v>3.6</v>
       </c>
-      <c r="K15">
-        <v>3.65</v>
-      </c>
-      <c r="L15">
-        <v>1.45</v>
-      </c>
-      <c r="M15">
-        <v>1.09</v>
-      </c>
-      <c r="N15">
-        <v>3.25</v>
-      </c>
-      <c r="O15">
-        <v>1.41</v>
-      </c>
-      <c r="P15">
-        <v>1.77</v>
-      </c>
-      <c r="Q15">
-        <v>2.24</v>
-      </c>
-      <c r="R15">
-        <v>1.29</v>
-      </c>
-      <c r="S15">
-        <v>4.2</v>
-      </c>
-      <c r="T15">
-        <v>2.02</v>
-      </c>
-      <c r="U15">
-        <v>1.91</v>
-      </c>
-      <c r="V15">
-        <v>1.98</v>
-      </c>
-      <c r="W15">
-        <v>1.28</v>
-      </c>
-      <c r="X15">
-        <v>11.5</v>
-      </c>
-      <c r="Y15">
-        <v>8</v>
-      </c>
-      <c r="Z15">
-        <v>11</v>
-      </c>
-      <c r="AA15">
+      <c r="BI15">
+        <v>3.2</v>
+      </c>
+      <c r="BJ15">
+        <v>16</v>
+      </c>
+      <c r="BK15">
+        <v>13</v>
+      </c>
+      <c r="BL15">
+        <v>330</v>
+      </c>
+      <c r="BM15">
+        <v>21</v>
+      </c>
+      <c r="BN15">
+        <v>3.4</v>
+      </c>
+      <c r="BO15">
+        <v>3.1</v>
+      </c>
+      <c r="BP15">
+        <v>7.6</v>
+      </c>
+      <c r="BQ15">
+        <v>6.6</v>
+      </c>
+      <c r="BR15">
+        <v>36</v>
+      </c>
+      <c r="BS15">
         <v>23</v>
       </c>
-      <c r="AB15">
-        <v>13</v>
-      </c>
-      <c r="AC15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD15">
-        <v>11</v>
-      </c>
-      <c r="AE15">
-        <v>23</v>
-      </c>
-      <c r="AF15">
-        <v>32</v>
-      </c>
-      <c r="AG15">
-        <v>18</v>
-      </c>
-      <c r="AH15">
-        <v>23</v>
-      </c>
-      <c r="AI15">
-        <v>46</v>
-      </c>
-      <c r="AJ15">
-        <v>110</v>
-      </c>
-      <c r="AK15">
-        <v>70</v>
-      </c>
-      <c r="AL15">
-        <v>75</v>
-      </c>
-      <c r="AM15">
-        <v>150</v>
-      </c>
-      <c r="AN15">
-        <v>85</v>
-      </c>
-      <c r="AO15">
-        <v>17</v>
-      </c>
-      <c r="AP15">
-        <v>11</v>
-      </c>
-      <c r="AQ15">
-        <v>7.6</v>
-      </c>
-      <c r="AR15">
-        <v>10</v>
-      </c>
-      <c r="AS15">
+      <c r="BT15">
+        <v>18.5</v>
+      </c>
+      <c r="BU15">
+        <v>9.4</v>
+      </c>
+      <c r="BV15">
+        <v>210</v>
+      </c>
+      <c r="BW15">
         <v>21</v>
       </c>
-      <c r="AT15">
-        <v>12.5</v>
-      </c>
-      <c r="AU15">
-        <v>7.6</v>
-      </c>
-      <c r="AV15">
-        <v>10</v>
-      </c>
-      <c r="AW15">
+      <c r="BX15">
+        <v>180</v>
+      </c>
+      <c r="BY15">
         <v>21</v>
       </c>
-      <c r="AX15">
-        <v>26</v>
-      </c>
-      <c r="AY15">
-        <v>16.5</v>
-      </c>
-      <c r="AZ15">
-        <v>21</v>
-      </c>
-      <c r="BA15">
-        <v>40</v>
-      </c>
-      <c r="BB15">
-        <v>16.5</v>
-      </c>
-      <c r="BC15">
-        <v>50</v>
-      </c>
-      <c r="BD15">
-        <v>60</v>
-      </c>
-      <c r="BE15">
-        <v>17.5</v>
-      </c>
-      <c r="BF15">
-        <v>65</v>
-      </c>
-      <c r="BG15">
+      <c r="BZ15">
         <v>15</v>
       </c>
-      <c r="BH15">
-        <v>3.3</v>
-      </c>
-      <c r="BI15">
-        <v>2.58</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>7.6</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>5.7</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>3.95</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4412,241 +4427,241 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="G16">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="H16">
-        <v>2.98</v>
+        <v>6.4</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
+        <v>1.49</v>
+      </c>
+      <c r="M16">
+        <v>1.11</v>
+      </c>
+      <c r="N16">
+        <v>2.9</v>
+      </c>
+      <c r="O16">
+        <v>1.48</v>
+      </c>
+      <c r="P16">
+        <v>1.64</v>
+      </c>
+      <c r="Q16">
+        <v>2.42</v>
+      </c>
+      <c r="R16">
         <v>1.23</v>
       </c>
-      <c r="M16">
-        <v>1.02</v>
-      </c>
-      <c r="N16">
-        <v>5.6</v>
-      </c>
-      <c r="O16">
-        <v>1.18</v>
-      </c>
-      <c r="P16">
-        <v>2.56</v>
-      </c>
-      <c r="Q16">
-        <v>1.55</v>
-      </c>
-      <c r="R16">
-        <v>1.63</v>
-      </c>
       <c r="S16">
+        <v>4.9</v>
+      </c>
+      <c r="T16">
+        <v>2.3</v>
+      </c>
+      <c r="U16">
+        <v>1.69</v>
+      </c>
+      <c r="V16">
+        <v>1.16</v>
+      </c>
+      <c r="W16">
         <v>2.38</v>
       </c>
-      <c r="T16">
-        <v>1.53</v>
-      </c>
-      <c r="U16">
-        <v>2.62</v>
-      </c>
-      <c r="V16">
-        <v>1.43</v>
-      </c>
-      <c r="W16">
-        <v>1.74</v>
-      </c>
       <c r="X16">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="Y16">
+        <v>16.5</v>
+      </c>
+      <c r="Z16">
+        <v>65</v>
+      </c>
+      <c r="AA16">
+        <v>280</v>
+      </c>
+      <c r="AB16">
+        <v>6.4</v>
+      </c>
+      <c r="AC16">
+        <v>8.6</v>
+      </c>
+      <c r="AD16">
+        <v>28</v>
+      </c>
+      <c r="AE16">
+        <v>160</v>
+      </c>
+      <c r="AF16">
+        <v>8.6</v>
+      </c>
+      <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>29</v>
+      </c>
+      <c r="AI16">
+        <v>160</v>
+      </c>
+      <c r="AJ16">
+        <v>17</v>
+      </c>
+      <c r="AK16">
         <v>23</v>
       </c>
-      <c r="Z16">
-        <v>32</v>
-      </c>
-      <c r="AA16">
-        <v>60</v>
-      </c>
-      <c r="AB16">
+      <c r="AL16">
+        <v>65</v>
+      </c>
+      <c r="AM16">
+        <v>260</v>
+      </c>
+      <c r="AN16">
+        <v>16</v>
+      </c>
+      <c r="AO16">
+        <v>280</v>
+      </c>
+      <c r="AP16">
+        <v>9</v>
+      </c>
+      <c r="AQ16">
+        <v>14</v>
+      </c>
+      <c r="AR16">
+        <v>11.5</v>
+      </c>
+      <c r="AS16">
+        <v>13</v>
+      </c>
+      <c r="AT16">
+        <v>5.7</v>
+      </c>
+      <c r="AU16">
+        <v>7.6</v>
+      </c>
+      <c r="AV16">
         <v>18.5</v>
       </c>
-      <c r="AC16">
-        <v>10.5</v>
-      </c>
-      <c r="AD16">
-        <v>17.5</v>
-      </c>
-      <c r="AE16">
-        <v>36</v>
-      </c>
-      <c r="AF16">
-        <v>970</v>
-      </c>
-      <c r="AG16">
-        <v>14.5</v>
-      </c>
-      <c r="AH16">
-        <v>18</v>
-      </c>
-      <c r="AI16">
-        <v>40</v>
-      </c>
-      <c r="AJ16">
-        <v>36</v>
-      </c>
-      <c r="AK16">
-        <v>25</v>
-      </c>
-      <c r="AL16">
-        <v>34</v>
-      </c>
-      <c r="AM16">
-        <v>55</v>
-      </c>
-      <c r="AN16">
+      <c r="AW16">
         <v>13</v>
       </c>
-      <c r="AO16">
-        <v>970</v>
-      </c>
-      <c r="AP16">
-        <v>22</v>
-      </c>
-      <c r="AQ16">
-        <v>4.3</v>
-      </c>
-      <c r="AR16">
-        <v>22</v>
-      </c>
-      <c r="AS16">
-        <v>5</v>
-      </c>
-      <c r="AT16">
+      <c r="AX16">
+        <v>7.6</v>
+      </c>
+      <c r="AY16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16">
+        <v>9.4</v>
+      </c>
+      <c r="BA16">
         <v>13</v>
       </c>
-      <c r="AU16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV16">
-        <v>12</v>
-      </c>
-      <c r="AW16">
-        <v>21</v>
-      </c>
-      <c r="AX16">
-        <v>15.5</v>
-      </c>
-      <c r="AY16">
-        <v>10</v>
-      </c>
-      <c r="AZ16">
+      <c r="BB16">
+        <v>15</v>
+      </c>
+      <c r="BC16">
+        <v>19</v>
+      </c>
+      <c r="BD16">
+        <v>11.5</v>
+      </c>
+      <c r="BE16">
         <v>13</v>
       </c>
-      <c r="BA16">
-        <v>4.8</v>
-      </c>
-      <c r="BB16">
-        <v>21</v>
-      </c>
-      <c r="BC16">
-        <v>4.5</v>
-      </c>
-      <c r="BD16">
-        <v>20</v>
-      </c>
-      <c r="BE16">
-        <v>5</v>
-      </c>
       <c r="BF16">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BH16">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="BI16">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO16">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BV16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4654,258 +4669,258 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H17">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="I17">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="J17">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="Q17">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="R17">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="T17">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="V17">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="W17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y17">
+        <v>8</v>
+      </c>
+      <c r="Z17">
         <v>11</v>
       </c>
-      <c r="Z17">
-        <v>13.5</v>
-      </c>
       <c r="AA17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17">
         <v>11</v>
       </c>
       <c r="AE17">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH17">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI17">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AJ17">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK17">
+        <v>65</v>
+      </c>
+      <c r="AL17">
+        <v>75</v>
+      </c>
+      <c r="AM17">
+        <v>150</v>
+      </c>
+      <c r="AN17">
+        <v>85</v>
+      </c>
+      <c r="AO17">
+        <v>17</v>
+      </c>
+      <c r="AP17">
+        <v>11</v>
+      </c>
+      <c r="AQ17">
+        <v>7.6</v>
+      </c>
+      <c r="AR17">
+        <v>10</v>
+      </c>
+      <c r="AS17">
+        <v>21</v>
+      </c>
+      <c r="AT17">
+        <v>12.5</v>
+      </c>
+      <c r="AU17">
+        <v>7.6</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>21</v>
+      </c>
+      <c r="AX17">
+        <v>26</v>
+      </c>
+      <c r="AY17">
+        <v>16.5</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>40</v>
+      </c>
+      <c r="BB17">
+        <v>17</v>
+      </c>
+      <c r="BC17">
         <v>50</v>
       </c>
-      <c r="AL17">
-        <v>55</v>
-      </c>
-      <c r="AM17">
-        <v>90</v>
-      </c>
-      <c r="AN17">
-        <v>46</v>
-      </c>
-      <c r="AO17">
-        <v>11.5</v>
-      </c>
-      <c r="AP17">
-        <v>16</v>
-      </c>
-      <c r="AQ17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR17">
-        <v>11</v>
-      </c>
-      <c r="AS17">
-        <v>18</v>
-      </c>
-      <c r="AT17">
+      <c r="BD17">
+        <v>60</v>
+      </c>
+      <c r="BE17">
+        <v>17.5</v>
+      </c>
+      <c r="BF17">
+        <v>65</v>
+      </c>
+      <c r="BG17">
         <v>15</v>
       </c>
-      <c r="AU17">
-        <v>8</v>
-      </c>
-      <c r="AV17">
-        <v>9.4</v>
-      </c>
-      <c r="AW17">
-        <v>15.5</v>
-      </c>
-      <c r="AX17">
-        <v>29</v>
-      </c>
-      <c r="AY17">
-        <v>15</v>
-      </c>
-      <c r="AZ17">
-        <v>15.5</v>
-      </c>
-      <c r="BA17">
-        <v>26</v>
-      </c>
-      <c r="BB17">
-        <v>11</v>
-      </c>
-      <c r="BC17">
-        <v>40</v>
-      </c>
-      <c r="BD17">
-        <v>42</v>
-      </c>
-      <c r="BE17">
-        <v>9.4</v>
-      </c>
-      <c r="BF17">
-        <v>9.6</v>
-      </c>
-      <c r="BG17">
-        <v>9.6</v>
-      </c>
       <c r="BH17">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BI17">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="BJ17">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BP17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
         <v>9.800000000000001</v>
       </c>
       <c r="BX17">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F18">
         <v>2.02</v>
@@ -4926,7 +4941,7 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M18">
         <v>1.02</v>
@@ -4980,7 +4995,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE18">
         <v>42</v>
@@ -5022,10 +5037,10 @@
         <v>16</v>
       </c>
       <c r="AR18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5037,7 +5052,7 @@
         <v>14</v>
       </c>
       <c r="AW18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5049,7 +5064,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB18">
         <v>19</v>
@@ -5061,7 +5076,7 @@
         <v>21</v>
       </c>
       <c r="BE18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF18">
         <v>9.199999999999999</v>
@@ -5130,589 +5145,589 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F19">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="H19">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="I19">
-        <v>3.7</v>
+        <v>1.93</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R19">
         <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T19">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="W19">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="X19">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z19">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AA19">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AB19">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AE19">
-        <v>44</v>
+        <v>19.5</v>
       </c>
       <c r="AF19">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AH19">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI19">
+        <v>32</v>
+      </c>
+      <c r="AJ19">
+        <v>100</v>
+      </c>
+      <c r="AK19">
         <v>50</v>
       </c>
-      <c r="AJ19">
-        <v>32</v>
-      </c>
-      <c r="AK19">
-        <v>26</v>
-      </c>
       <c r="AL19">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="AO19">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="AP19">
         <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AS19">
+        <v>18.5</v>
+      </c>
+      <c r="AT19">
+        <v>14.5</v>
+      </c>
+      <c r="AU19">
+        <v>8</v>
+      </c>
+      <c r="AV19">
+        <v>9.4</v>
+      </c>
+      <c r="AW19">
+        <v>16</v>
+      </c>
+      <c r="AX19">
+        <v>29</v>
+      </c>
+      <c r="AY19">
+        <v>15</v>
+      </c>
+      <c r="AZ19">
+        <v>15.5</v>
+      </c>
+      <c r="BA19">
+        <v>26</v>
+      </c>
+      <c r="BB19">
+        <v>11</v>
+      </c>
+      <c r="BC19">
+        <v>40</v>
+      </c>
+      <c r="BD19">
+        <v>42</v>
+      </c>
+      <c r="BE19">
+        <v>9.6</v>
+      </c>
+      <c r="BF19">
+        <v>28</v>
+      </c>
+      <c r="BG19">
+        <v>9.6</v>
+      </c>
+      <c r="BH19">
+        <v>4.3</v>
+      </c>
+      <c r="BI19">
+        <v>3.1</v>
+      </c>
+      <c r="BJ19">
+        <v>11</v>
+      </c>
+      <c r="BK19">
+        <v>7.2</v>
+      </c>
+      <c r="BL19">
+        <v>120</v>
+      </c>
+      <c r="BM19">
+        <v>1.02</v>
+      </c>
+      <c r="BN19">
+        <v>8</v>
+      </c>
+      <c r="BO19">
+        <v>6</v>
+      </c>
+      <c r="BP19">
         <v>34</v>
       </c>
-      <c r="AT19">
-        <v>10</v>
-      </c>
-      <c r="AU19">
-        <v>7.4</v>
-      </c>
-      <c r="AV19">
-        <v>12.5</v>
-      </c>
-      <c r="AW19">
-        <v>27</v>
-      </c>
-      <c r="AX19">
-        <v>13</v>
-      </c>
-      <c r="AY19">
-        <v>9.4</v>
-      </c>
-      <c r="AZ19">
-        <v>13.5</v>
-      </c>
-      <c r="BA19">
-        <v>30</v>
-      </c>
-      <c r="BB19">
-        <v>20</v>
-      </c>
-      <c r="BC19">
-        <v>18.5</v>
-      </c>
-      <c r="BD19">
-        <v>24</v>
-      </c>
-      <c r="BE19">
-        <v>8.6</v>
-      </c>
-      <c r="BF19">
-        <v>11.5</v>
-      </c>
-      <c r="BG19">
-        <v>19</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19">
-        <v>13</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.01</v>
-      </c>
-      <c r="BN19">
-        <v>7.4</v>
-      </c>
-      <c r="BO19">
-        <v>3.45</v>
-      </c>
-      <c r="BP19">
-        <v>23</v>
-      </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
+        <v>5</v>
+      </c>
+      <c r="BU19">
+        <v>4.2</v>
+      </c>
+      <c r="BV19">
+        <v>14</v>
+      </c>
+      <c r="BW19">
         <v>9.800000000000001</v>
       </c>
-      <c r="BU19">
-        <v>4.4</v>
-      </c>
-      <c r="BV19">
-        <v>38</v>
-      </c>
-      <c r="BW19">
-        <v>1.01</v>
-      </c>
       <c r="BX19">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BY19">
         <v>1.02</v>
       </c>
       <c r="BZ19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F20">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="G20">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="I20">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q20">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T20">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="X20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y20">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA20">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE20">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF20">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG20">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI20">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ20">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AK20">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AL20">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AM20">
         <v>55</v>
       </c>
       <c r="AN20">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AP20">
+        <v>22</v>
+      </c>
+      <c r="AQ20">
+        <v>4.4</v>
+      </c>
+      <c r="AR20">
+        <v>22</v>
+      </c>
+      <c r="AS20">
+        <v>5.2</v>
+      </c>
+      <c r="AT20">
+        <v>13</v>
+      </c>
+      <c r="AU20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20">
+        <v>12</v>
+      </c>
+      <c r="AW20">
         <v>21</v>
       </c>
-      <c r="AQ20">
-        <v>21</v>
-      </c>
-      <c r="AR20">
-        <v>7.4</v>
-      </c>
-      <c r="AS20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20">
-        <v>12</v>
-      </c>
-      <c r="AU20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>16</v>
-      </c>
-      <c r="AW20">
-        <v>7.6</v>
-      </c>
       <c r="AX20">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB20">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC20">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="BD20">
         <v>20</v>
       </c>
       <c r="BE20">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF20">
+        <v>9.6</v>
+      </c>
+      <c r="BG20">
+        <v>16</v>
+      </c>
+      <c r="BH20">
+        <v>5.3</v>
+      </c>
+      <c r="BI20">
+        <v>3.5</v>
+      </c>
+      <c r="BJ20">
+        <v>10.5</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>85</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>6.8</v>
+      </c>
+      <c r="BO20">
+        <v>4.3</v>
+      </c>
+      <c r="BP20">
+        <v>18</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>27</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU20">
         <v>6</v>
       </c>
-      <c r="BG20">
-        <v>7.6</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>12</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>95</v>
-      </c>
-      <c r="BM20">
-        <v>1.02</v>
-      </c>
-      <c r="BN20">
-        <v>6.6</v>
-      </c>
-      <c r="BO20">
-        <v>3.45</v>
-      </c>
-      <c r="BP20">
-        <v>15.5</v>
-      </c>
-      <c r="BQ20">
-        <v>1.01</v>
-      </c>
-      <c r="BR20">
+      <c r="BV20">
         <v>26</v>
       </c>
-      <c r="BS20">
-        <v>1.01</v>
-      </c>
-      <c r="BT20">
-        <v>11.5</v>
-      </c>
-      <c r="BU20">
-        <v>1.01</v>
-      </c>
-      <c r="BV20">
-        <v>40</v>
-      </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BY20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="H21">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I21">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="T21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U21">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="X21">
         <v>20</v>
       </c>
       <c r="Y21">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA21">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD21">
+        <v>15.5</v>
+      </c>
+      <c r="AE21">
+        <v>44</v>
+      </c>
+      <c r="AF21">
         <v>16</v>
-      </c>
-      <c r="AE21">
-        <v>36</v>
-      </c>
-      <c r="AF21">
-        <v>17</v>
       </c>
       <c r="AG21">
         <v>12</v>
@@ -5721,177 +5736,177 @@
         <v>17</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ21">
         <v>32</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM21">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN21">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ21">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS21">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT21">
         <v>10</v>
       </c>
       <c r="AU21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="AX21">
         <v>13.5</v>
       </c>
       <c r="AY21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21">
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BB21">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BC21">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD21">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BE21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF21">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG21">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BH21">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP21">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BS21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV21">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BY21">
         <v>1.02</v>
       </c>
       <c r="BZ21">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F22">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="G22">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="H22">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="I22">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J22">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5900,142 +5915,142 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R22">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="S22">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T22">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U22">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="W22">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="X22">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z22">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AA22">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AB22">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AC22">
         <v>11</v>
       </c>
       <c r="AD22">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AE22">
+        <v>46</v>
+      </c>
+      <c r="AF22">
+        <v>16</v>
+      </c>
+      <c r="AG22">
+        <v>11.5</v>
+      </c>
+      <c r="AH22">
+        <v>16</v>
+      </c>
+      <c r="AI22">
+        <v>44</v>
+      </c>
+      <c r="AJ22">
+        <v>22</v>
+      </c>
+      <c r="AK22">
+        <v>18</v>
+      </c>
+      <c r="AL22">
         <v>25</v>
       </c>
-      <c r="AF22">
-        <v>24</v>
-      </c>
-      <c r="AG22">
-        <v>15</v>
-      </c>
-      <c r="AH22">
-        <v>17</v>
-      </c>
-      <c r="AI22">
+      <c r="AM22">
+        <v>60</v>
+      </c>
+      <c r="AN22">
+        <v>7.8</v>
+      </c>
+      <c r="AO22">
+        <v>34</v>
+      </c>
+      <c r="AP22">
+        <v>20</v>
+      </c>
+      <c r="AQ22">
+        <v>20</v>
+      </c>
+      <c r="AR22">
+        <v>8</v>
+      </c>
+      <c r="AS22">
+        <v>8.4</v>
+      </c>
+      <c r="AT22">
+        <v>11.5</v>
+      </c>
+      <c r="AU22">
+        <v>9</v>
+      </c>
+      <c r="AV22">
+        <v>15.5</v>
+      </c>
+      <c r="AW22">
         <v>29</v>
       </c>
-      <c r="AJ22">
+      <c r="AX22">
+        <v>12.5</v>
+      </c>
+      <c r="AY22">
+        <v>9</v>
+      </c>
+      <c r="AZ22">
+        <v>13</v>
+      </c>
+      <c r="BA22">
+        <v>7.6</v>
+      </c>
+      <c r="BB22">
+        <v>17.5</v>
+      </c>
+      <c r="BC22">
+        <v>14.5</v>
+      </c>
+      <c r="BD22">
+        <v>20</v>
+      </c>
+      <c r="BE22">
         <v>40</v>
       </c>
-      <c r="AK22">
-        <v>26</v>
-      </c>
-      <c r="AL22">
-        <v>29</v>
-      </c>
-      <c r="AM22">
-        <v>50</v>
-      </c>
-      <c r="AN22">
-        <v>12.5</v>
-      </c>
-      <c r="AO22">
-        <v>12.5</v>
-      </c>
-      <c r="AP22">
-        <v>8.4</v>
-      </c>
-      <c r="AQ22">
-        <v>16</v>
-      </c>
-      <c r="AR22">
-        <v>19</v>
-      </c>
-      <c r="AS22">
-        <v>6.6</v>
-      </c>
-      <c r="AT22">
-        <v>16</v>
-      </c>
-      <c r="AU22">
-        <v>9.4</v>
-      </c>
-      <c r="AV22">
-        <v>11</v>
-      </c>
-      <c r="AW22">
-        <v>20</v>
-      </c>
-      <c r="AX22">
-        <v>19.5</v>
-      </c>
-      <c r="AY22">
-        <v>11</v>
-      </c>
-      <c r="AZ22">
-        <v>12.5</v>
-      </c>
-      <c r="BA22">
-        <v>8</v>
-      </c>
-      <c r="BB22">
-        <v>32</v>
-      </c>
-      <c r="BC22">
-        <v>21</v>
-      </c>
-      <c r="BD22">
-        <v>8</v>
-      </c>
-      <c r="BE22">
+      <c r="BF22">
         <v>6.4</v>
       </c>
-      <c r="BF22">
-        <v>10.5</v>
-      </c>
       <c r="BG22">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6044,303 +6059,303 @@
         <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BM22">
         <v>1.02</v>
       </c>
       <c r="BN22">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BO22">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP22">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BU22">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ22">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F23">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="G23">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="H23">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="I23">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="J23">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="R23">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="T23">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U23">
         <v>2.26</v>
       </c>
       <c r="V23">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="X23">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z23">
+        <v>26</v>
+      </c>
+      <c r="AA23">
+        <v>60</v>
+      </c>
+      <c r="AB23">
         <v>12.5</v>
-      </c>
-      <c r="AA23">
-        <v>20</v>
-      </c>
-      <c r="AB23">
-        <v>24</v>
       </c>
       <c r="AC23">
         <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE23">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AF23">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AG23">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI23">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AJ23">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AK23">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AL23">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM23">
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="AO23">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AP23">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23">
+        <v>12</v>
+      </c>
+      <c r="AR23">
+        <v>20</v>
+      </c>
+      <c r="AS23">
+        <v>34</v>
+      </c>
+      <c r="AT23">
+        <v>10</v>
+      </c>
+      <c r="AU23">
+        <v>7.4</v>
+      </c>
+      <c r="AV23">
+        <v>12</v>
+      </c>
+      <c r="AW23">
+        <v>6.6</v>
+      </c>
+      <c r="AX23">
+        <v>14</v>
+      </c>
+      <c r="AY23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23">
+        <v>13.5</v>
+      </c>
+      <c r="BA23">
+        <v>27</v>
+      </c>
+      <c r="BB23">
+        <v>6.6</v>
+      </c>
+      <c r="BC23">
+        <v>20</v>
+      </c>
+      <c r="BD23">
+        <v>6.6</v>
+      </c>
+      <c r="BE23">
+        <v>7.4</v>
+      </c>
+      <c r="BF23">
+        <v>13.5</v>
+      </c>
+      <c r="BG23">
+        <v>21</v>
+      </c>
+      <c r="BH23">
+        <v>4.2</v>
+      </c>
+      <c r="BI23">
+        <v>3.05</v>
+      </c>
+      <c r="BJ23">
+        <v>10.5</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>110</v>
+      </c>
+      <c r="BM23">
+        <v>1.02</v>
+      </c>
+      <c r="BN23">
+        <v>6.2</v>
+      </c>
+      <c r="BO23">
+        <v>4.3</v>
+      </c>
+      <c r="BP23">
         <v>19</v>
       </c>
-      <c r="AQ23">
-        <v>10</v>
-      </c>
-      <c r="AR23">
-        <v>10.5</v>
-      </c>
-      <c r="AS23">
-        <v>17.5</v>
-      </c>
-      <c r="AT23">
-        <v>18</v>
-      </c>
-      <c r="AU23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV23">
-        <v>9</v>
-      </c>
-      <c r="AW23">
-        <v>15</v>
-      </c>
-      <c r="AX23">
-        <v>34</v>
-      </c>
-      <c r="AY23">
-        <v>16</v>
-      </c>
-      <c r="AZ23">
-        <v>15.5</v>
-      </c>
-      <c r="BA23">
-        <v>24</v>
-      </c>
-      <c r="BB23">
-        <v>11.5</v>
-      </c>
-      <c r="BC23">
-        <v>44</v>
-      </c>
-      <c r="BD23">
-        <v>44</v>
-      </c>
-      <c r="BE23">
-        <v>13</v>
-      </c>
-      <c r="BF23">
-        <v>10.5</v>
-      </c>
-      <c r="BG23">
-        <v>7.8</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23">
-        <v>13</v>
-      </c>
-      <c r="BK23">
-        <v>1.01</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>11.5</v>
-      </c>
-      <c r="BO23">
-        <v>5.3</v>
-      </c>
-      <c r="BP23">
-        <v>50</v>
-      </c>
       <c r="BQ23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BS23">
         <v>1.02</v>
       </c>
       <c r="BT23">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU23">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BV23">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6348,279 +6363,279 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
         <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F24">
+        <v>2.52</v>
+      </c>
+      <c r="G24">
+        <v>2.6</v>
+      </c>
+      <c r="H24">
+        <v>2.54</v>
+      </c>
+      <c r="I24">
+        <v>2.7</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>4.6</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>6.2</v>
+      </c>
+      <c r="O24">
+        <v>1.15</v>
+      </c>
+      <c r="P24">
+        <v>2.86</v>
+      </c>
+      <c r="Q24">
+        <v>1.48</v>
+      </c>
+      <c r="R24">
+        <v>1.73</v>
+      </c>
+      <c r="S24">
+        <v>2.18</v>
+      </c>
+      <c r="T24">
+        <v>1.47</v>
+      </c>
+      <c r="U24">
+        <v>2.84</v>
+      </c>
+      <c r="V24">
+        <v>1.58</v>
+      </c>
+      <c r="W24">
+        <v>1.62</v>
+      </c>
+      <c r="X24">
+        <v>36</v>
+      </c>
+      <c r="Y24">
+        <v>20</v>
+      </c>
+      <c r="Z24">
+        <v>24</v>
+      </c>
+      <c r="AA24">
+        <v>38</v>
+      </c>
+      <c r="AB24">
+        <v>20</v>
+      </c>
+      <c r="AC24">
+        <v>11</v>
+      </c>
+      <c r="AD24">
+        <v>13.5</v>
+      </c>
+      <c r="AE24">
+        <v>25</v>
+      </c>
+      <c r="AF24">
+        <v>24</v>
+      </c>
+      <c r="AG24">
+        <v>13</v>
+      </c>
+      <c r="AH24">
+        <v>15.5</v>
+      </c>
+      <c r="AI24">
+        <v>29</v>
+      </c>
+      <c r="AJ24">
+        <v>38</v>
+      </c>
+      <c r="AK24">
+        <v>26</v>
+      </c>
+      <c r="AL24">
+        <v>29</v>
+      </c>
+      <c r="AM24">
+        <v>50</v>
+      </c>
+      <c r="AN24">
+        <v>12.5</v>
+      </c>
+      <c r="AO24">
+        <v>12.5</v>
+      </c>
+      <c r="AP24">
+        <v>7.8</v>
+      </c>
+      <c r="AQ24">
+        <v>16.5</v>
+      </c>
+      <c r="AR24">
+        <v>20</v>
+      </c>
+      <c r="AS24">
+        <v>7.8</v>
+      </c>
+      <c r="AT24">
+        <v>16.5</v>
+      </c>
+      <c r="AU24">
+        <v>9.4</v>
+      </c>
+      <c r="AV24">
+        <v>11</v>
+      </c>
+      <c r="AW24">
+        <v>20</v>
+      </c>
+      <c r="AX24">
+        <v>20</v>
+      </c>
+      <c r="AY24">
+        <v>11</v>
+      </c>
+      <c r="AZ24">
+        <v>12.5</v>
+      </c>
+      <c r="BA24">
+        <v>21</v>
+      </c>
+      <c r="BB24">
+        <v>7.8</v>
+      </c>
+      <c r="BC24">
+        <v>21</v>
+      </c>
+      <c r="BD24">
+        <v>7.4</v>
+      </c>
+      <c r="BE24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF24">
+        <v>10</v>
+      </c>
+      <c r="BG24">
+        <v>10.5</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>11</v>
+      </c>
+      <c r="BK24">
+        <v>5.4</v>
+      </c>
+      <c r="BL24">
+        <v>85</v>
+      </c>
+      <c r="BM24">
+        <v>1.02</v>
+      </c>
+      <c r="BN24">
+        <v>8.6</v>
+      </c>
+      <c r="BO24">
         <v>4.5</v>
       </c>
-      <c r="G24">
-        <v>5.1</v>
-      </c>
-      <c r="H24">
-        <v>1.92</v>
-      </c>
-      <c r="I24">
-        <v>2.02</v>
-      </c>
-      <c r="J24">
-        <v>3.45</v>
-      </c>
-      <c r="K24">
-        <v>3.7</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.09</v>
-      </c>
-      <c r="N24">
-        <v>3.25</v>
-      </c>
-      <c r="O24">
-        <v>1.4</v>
-      </c>
-      <c r="P24">
-        <v>1.78</v>
-      </c>
-      <c r="Q24">
-        <v>2.16</v>
-      </c>
-      <c r="R24">
-        <v>1.29</v>
-      </c>
-      <c r="S24">
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <v>1.96</v>
-      </c>
-      <c r="U24">
-        <v>1.95</v>
-      </c>
-      <c r="V24">
-        <v>1.98</v>
-      </c>
-      <c r="W24">
-        <v>1.25</v>
-      </c>
-      <c r="X24">
-        <v>14</v>
-      </c>
-      <c r="Y24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z24">
-        <v>13</v>
-      </c>
-      <c r="AA24">
-        <v>26</v>
-      </c>
-      <c r="AB24">
-        <v>16.5</v>
-      </c>
-      <c r="AC24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD24">
-        <v>12.5</v>
-      </c>
-      <c r="AE24">
-        <v>26</v>
-      </c>
-      <c r="AF24">
-        <v>40</v>
-      </c>
-      <c r="AG24">
-        <v>22</v>
-      </c>
-      <c r="AH24">
-        <v>24</v>
-      </c>
-      <c r="AI24">
-        <v>50</v>
-      </c>
-      <c r="AJ24">
-        <v>130</v>
-      </c>
-      <c r="AK24">
-        <v>80</v>
-      </c>
-      <c r="AL24">
-        <v>90</v>
-      </c>
-      <c r="AM24">
-        <v>160</v>
-      </c>
-      <c r="AN24">
-        <v>100</v>
-      </c>
-      <c r="AO24">
-        <v>19</v>
-      </c>
-      <c r="AP24">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24">
-        <v>7.2</v>
-      </c>
-      <c r="AR24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS24">
-        <v>18.5</v>
-      </c>
-      <c r="AT24">
-        <v>12.5</v>
-      </c>
-      <c r="AU24">
-        <v>7.2</v>
-      </c>
-      <c r="AV24">
-        <v>9.4</v>
-      </c>
-      <c r="AW24">
-        <v>18.5</v>
-      </c>
-      <c r="AX24">
-        <v>5.5</v>
-      </c>
-      <c r="AY24">
-        <v>16.5</v>
-      </c>
-      <c r="AZ24">
-        <v>17.5</v>
-      </c>
-      <c r="BA24">
-        <v>5.9</v>
-      </c>
-      <c r="BB24">
-        <v>6</v>
-      </c>
-      <c r="BC24">
-        <v>5.8</v>
-      </c>
-      <c r="BD24">
-        <v>5.9</v>
-      </c>
-      <c r="BE24">
-        <v>6</v>
-      </c>
-      <c r="BF24">
-        <v>6</v>
-      </c>
-      <c r="BG24">
-        <v>5</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.01</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.01</v>
-      </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ24">
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY24">
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F25">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="G25">
-        <v>1.28</v>
+        <v>4.9</v>
       </c>
       <c r="H25">
-        <v>15.5</v>
+        <v>1.78</v>
       </c>
       <c r="I25">
-        <v>22</v>
+        <v>1.82</v>
       </c>
       <c r="J25">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="K25">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="L25">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M25">
         <v>1.04</v>
@@ -6629,202 +6644,686 @@
         <v>4.8</v>
       </c>
       <c r="O25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P25">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
         <v>1.66</v>
       </c>
       <c r="R25">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S25">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T25">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="U25">
-        <v>1.64</v>
+        <v>2.26</v>
       </c>
       <c r="V25">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="W25">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y25">
+        <v>11.5</v>
+      </c>
+      <c r="Z25">
+        <v>12.5</v>
+      </c>
+      <c r="AA25">
+        <v>20</v>
+      </c>
+      <c r="AB25">
+        <v>24</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>10.5</v>
+      </c>
+      <c r="AE25">
+        <v>17.5</v>
+      </c>
+      <c r="AF25">
+        <v>40</v>
+      </c>
+      <c r="AG25">
+        <v>18.5</v>
+      </c>
+      <c r="AH25">
+        <v>22</v>
+      </c>
+      <c r="AI25">
+        <v>29</v>
+      </c>
+      <c r="AJ25">
+        <v>130</v>
+      </c>
+      <c r="AK25">
         <v>55</v>
-      </c>
-      <c r="Z25">
-        <v>210</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
-        <v>10.5</v>
-      </c>
-      <c r="AC25">
-        <v>19</v>
-      </c>
-      <c r="AD25">
-        <v>75</v>
-      </c>
-      <c r="AE25">
-        <v>420</v>
-      </c>
-      <c r="AF25">
-        <v>7.4</v>
-      </c>
-      <c r="AG25">
-        <v>12</v>
-      </c>
-      <c r="AH25">
-        <v>55</v>
-      </c>
-      <c r="AI25">
-        <v>300</v>
-      </c>
-      <c r="AJ25">
-        <v>9</v>
-      </c>
-      <c r="AK25">
-        <v>15.5</v>
       </c>
       <c r="AL25">
         <v>60</v>
       </c>
       <c r="AM25">
+        <v>85</v>
+      </c>
+      <c r="AN25">
+        <v>48</v>
+      </c>
+      <c r="AO25">
+        <v>9</v>
+      </c>
+      <c r="AP25">
+        <v>19</v>
+      </c>
+      <c r="AQ25">
+        <v>10</v>
+      </c>
+      <c r="AR25">
+        <v>10.5</v>
+      </c>
+      <c r="AS25">
+        <v>17.5</v>
+      </c>
+      <c r="AT25">
+        <v>18</v>
+      </c>
+      <c r="AU25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV25">
+        <v>9</v>
+      </c>
+      <c r="AW25">
+        <v>15</v>
+      </c>
+      <c r="AX25">
+        <v>34</v>
+      </c>
+      <c r="AY25">
+        <v>16</v>
+      </c>
+      <c r="AZ25">
+        <v>15.5</v>
+      </c>
+      <c r="BA25">
+        <v>24</v>
+      </c>
+      <c r="BB25">
+        <v>11.5</v>
+      </c>
+      <c r="BC25">
+        <v>44</v>
+      </c>
+      <c r="BD25">
+        <v>44</v>
+      </c>
+      <c r="BE25">
+        <v>13</v>
+      </c>
+      <c r="BF25">
+        <v>10.5</v>
+      </c>
+      <c r="BG25">
+        <v>7.8</v>
+      </c>
+      <c r="BH25">
+        <v>4.7</v>
+      </c>
+      <c r="BI25">
+        <v>3.15</v>
+      </c>
+      <c r="BJ25">
+        <v>9.6</v>
+      </c>
+      <c r="BK25">
+        <v>5.8</v>
+      </c>
+      <c r="BL25">
+        <v>120</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>8.6</v>
+      </c>
+      <c r="BO25">
+        <v>5.3</v>
+      </c>
+      <c r="BP25">
+        <v>36</v>
+      </c>
+      <c r="BQ25">
+        <v>1.02</v>
+      </c>
+      <c r="BR25">
+        <v>50</v>
+      </c>
+      <c r="BS25">
+        <v>1.02</v>
+      </c>
+      <c r="BT25">
+        <v>4.9</v>
+      </c>
+      <c r="BU25">
+        <v>4.1</v>
+      </c>
+      <c r="BV25">
+        <v>12.5</v>
+      </c>
+      <c r="BW25">
+        <v>7.4</v>
+      </c>
+      <c r="BX25">
+        <v>24</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>17.5</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26">
+        <v>4.5</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>1.93</v>
+      </c>
+      <c r="I26">
+        <v>2.02</v>
+      </c>
+      <c r="J26">
+        <v>3.45</v>
+      </c>
+      <c r="K26">
+        <v>3.7</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.09</v>
+      </c>
+      <c r="N26">
+        <v>3.25</v>
+      </c>
+      <c r="O26">
+        <v>1.4</v>
+      </c>
+      <c r="P26">
+        <v>1.79</v>
+      </c>
+      <c r="Q26">
+        <v>2.16</v>
+      </c>
+      <c r="R26">
+        <v>1.29</v>
+      </c>
+      <c r="S26">
+        <v>4</v>
+      </c>
+      <c r="T26">
+        <v>1.94</v>
+      </c>
+      <c r="U26">
+        <v>1.93</v>
+      </c>
+      <c r="V26">
+        <v>1.98</v>
+      </c>
+      <c r="W26">
+        <v>1.25</v>
+      </c>
+      <c r="X26">
+        <v>14</v>
+      </c>
+      <c r="Y26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z26">
+        <v>13</v>
+      </c>
+      <c r="AA26">
+        <v>26</v>
+      </c>
+      <c r="AB26">
+        <v>16.5</v>
+      </c>
+      <c r="AC26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>12.5</v>
+      </c>
+      <c r="AE26">
+        <v>26</v>
+      </c>
+      <c r="AF26">
+        <v>40</v>
+      </c>
+      <c r="AG26">
+        <v>22</v>
+      </c>
+      <c r="AH26">
+        <v>24</v>
+      </c>
+      <c r="AI26">
+        <v>50</v>
+      </c>
+      <c r="AJ26">
+        <v>130</v>
+      </c>
+      <c r="AK26">
+        <v>80</v>
+      </c>
+      <c r="AL26">
+        <v>90</v>
+      </c>
+      <c r="AM26">
+        <v>160</v>
+      </c>
+      <c r="AN26">
+        <v>100</v>
+      </c>
+      <c r="AO26">
+        <v>19</v>
+      </c>
+      <c r="AP26">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26">
+        <v>7.2</v>
+      </c>
+      <c r="AR26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS26">
+        <v>5.1</v>
+      </c>
+      <c r="AT26">
+        <v>12.5</v>
+      </c>
+      <c r="AU26">
+        <v>7.2</v>
+      </c>
+      <c r="AV26">
+        <v>9.6</v>
+      </c>
+      <c r="AW26">
+        <v>5.1</v>
+      </c>
+      <c r="AX26">
+        <v>5.5</v>
+      </c>
+      <c r="AY26">
+        <v>16.5</v>
+      </c>
+      <c r="AZ26">
+        <v>17.5</v>
+      </c>
+      <c r="BA26">
+        <v>5.6</v>
+      </c>
+      <c r="BB26">
+        <v>6</v>
+      </c>
+      <c r="BC26">
+        <v>5.8</v>
+      </c>
+      <c r="BD26">
+        <v>5.9</v>
+      </c>
+      <c r="BE26">
+        <v>6</v>
+      </c>
+      <c r="BF26">
+        <v>6</v>
+      </c>
+      <c r="BG26">
+        <v>5</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27">
+        <v>1.24</v>
+      </c>
+      <c r="G27">
+        <v>1.28</v>
+      </c>
+      <c r="H27">
+        <v>15.5</v>
+      </c>
+      <c r="I27">
+        <v>22</v>
+      </c>
+      <c r="J27">
+        <v>6.4</v>
+      </c>
+      <c r="K27">
+        <v>7.4</v>
+      </c>
+      <c r="L27">
+        <v>1.3</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>4.8</v>
+      </c>
+      <c r="O27">
+        <v>1.22</v>
+      </c>
+      <c r="P27">
+        <v>2.32</v>
+      </c>
+      <c r="Q27">
+        <v>1.66</v>
+      </c>
+      <c r="R27">
+        <v>1.52</v>
+      </c>
+      <c r="S27">
+        <v>2.68</v>
+      </c>
+      <c r="T27">
+        <v>2.4</v>
+      </c>
+      <c r="U27">
+        <v>1.64</v>
+      </c>
+      <c r="V27">
+        <v>1.05</v>
+      </c>
+      <c r="W27">
+        <v>4.6</v>
+      </c>
+      <c r="X27">
+        <v>25</v>
+      </c>
+      <c r="Y27">
+        <v>55</v>
+      </c>
+      <c r="Z27">
+        <v>210</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>10.5</v>
+      </c>
+      <c r="AC27">
+        <v>19</v>
+      </c>
+      <c r="AD27">
+        <v>75</v>
+      </c>
+      <c r="AE27">
+        <v>420</v>
+      </c>
+      <c r="AF27">
+        <v>7.4</v>
+      </c>
+      <c r="AG27">
+        <v>12</v>
+      </c>
+      <c r="AH27">
+        <v>55</v>
+      </c>
+      <c r="AI27">
+        <v>300</v>
+      </c>
+      <c r="AJ27">
+        <v>9</v>
+      </c>
+      <c r="AK27">
+        <v>15.5</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
         <v>330</v>
       </c>
-      <c r="AN25">
+      <c r="AN27">
         <v>4.7</v>
       </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
         <v>20</v>
       </c>
-      <c r="AQ25">
+      <c r="AQ27">
         <v>7.4</v>
       </c>
-      <c r="AR25">
+      <c r="AR27">
         <v>7.8</v>
       </c>
-      <c r="AS25">
+      <c r="AS27">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT25">
+      <c r="AT27">
         <v>7.4</v>
       </c>
-      <c r="AU25">
+      <c r="AU27">
         <v>13.5</v>
       </c>
-      <c r="AV25">
+      <c r="AV27">
         <v>7.4</v>
       </c>
-      <c r="AW25">
+      <c r="AW27">
         <v>8</v>
       </c>
-      <c r="AX25">
+      <c r="AX27">
         <v>6.4</v>
       </c>
-      <c r="AY25">
+      <c r="AY27">
         <v>10</v>
       </c>
-      <c r="AZ25">
+      <c r="AZ27">
         <v>7.2</v>
       </c>
-      <c r="BA25">
+      <c r="BA27">
         <v>8</v>
       </c>
-      <c r="BB25">
+      <c r="BB27">
         <v>7.8</v>
       </c>
-      <c r="BC25">
+      <c r="BC27">
         <v>13</v>
       </c>
-      <c r="BD25">
-        <v>7.6</v>
-      </c>
-      <c r="BE25">
+      <c r="BD27">
+        <v>7.4</v>
+      </c>
+      <c r="BE27">
         <v>8</v>
       </c>
-      <c r="BF25">
-        <v>4.2</v>
-      </c>
-      <c r="BG25">
+      <c r="BF27">
+        <v>4.3</v>
+      </c>
+      <c r="BG27">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.01</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.01</v>
-      </c>
-      <c r="BN25">
-        <v>970</v>
-      </c>
-      <c r="BO25">
-        <v>1.01</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.01</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.01</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>1.01</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>1.01</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.01</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
-      <c r="CA25">
-        <v>1.01</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>142</v>
+      <c r="BH27">
+        <v>4.9</v>
+      </c>
+      <c r="BI27">
+        <v>3.25</v>
+      </c>
+      <c r="BJ27">
+        <v>17.5</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>260</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>3.55</v>
+      </c>
+      <c r="BO27">
+        <v>3.2</v>
+      </c>
+      <c r="BP27">
+        <v>8</v>
+      </c>
+      <c r="BQ27">
+        <v>5.1</v>
+      </c>
+      <c r="BR27">
+        <v>32</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>22</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>190</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>150</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>13</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="150">
   <si>
     <t>League</t>
   </si>
@@ -361,6 +361,9 @@
     <t>Barrow</t>
   </si>
   <si>
+    <t>Hornchurch</t>
+  </si>
+  <si>
     <t>Forest Green</t>
   </si>
   <si>
@@ -439,6 +442,9 @@
     <t>Scunthorpe</t>
   </si>
   <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
     <t>Wealdstone</t>
   </si>
   <si>
@@ -457,7 +463,7 @@
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>2026-09-28 03:29:40</t>
+    <t>2026-09-28 05:41:51</t>
   </si>
 </sst>
 </file>
@@ -789,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,25 +1054,25 @@
         <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -1093,16 +1099,16 @@
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
         <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
         <v>12.5</v>
@@ -1123,13 +1129,13 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE2">
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1153,7 +1159,7 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AO2">
         <v>55</v>
@@ -1171,7 +1177,7 @@
         <v>9.6</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1180,7 +1186,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1192,16 +1198,16 @@
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
         <v>10</v>
@@ -1210,70 +1216,70 @@
         <v>18</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,118 +1296,118 @@
         <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G3">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K3">
+        <v>4.3</v>
+      </c>
+      <c r="L3">
+        <v>1.3</v>
+      </c>
+      <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
         <v>5.2</v>
       </c>
-      <c r="L3">
-        <v>1.26</v>
-      </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>4.7</v>
-      </c>
       <c r="O3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="Q3">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="R3">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W3">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y3">
         <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF3">
         <v>36</v>
       </c>
       <c r="AG3">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>85</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1410,10 +1416,10 @@
         <v>12.5</v>
       </c>
       <c r="AS3">
+        <v>20</v>
+      </c>
+      <c r="AT3">
         <v>15</v>
-      </c>
-      <c r="AT3">
-        <v>16</v>
       </c>
       <c r="AU3">
         <v>8.4</v>
@@ -1422,37 +1428,37 @@
         <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3">
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
         <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
         <v>4.8</v>
@@ -1467,40 +1473,40 @@
         <v>6.8</v>
       </c>
       <c r="BL3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BT3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>26</v>
@@ -1509,13 +1515,13 @@
         <v>17</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,163 +1538,163 @@
         <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F4">
         <v>2.86</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
         <v>2.56</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
         <v>1.64</v>
       </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP4">
         <v>14.5</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
         <v>15.5</v>
       </c>
       <c r="AS4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4">
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB4">
         <v>32</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF4">
         <v>15.5</v>
@@ -1757,7 +1763,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1774,19 +1780,19 @@
         <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
         <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1801,13 +1807,13 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1816,16 +1822,16 @@
         <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
         <v>1.83</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
         <v>1.89</v>
@@ -1843,7 +1849,7 @@
         <v>90</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>8.4</v>
@@ -1855,7 +1861,7 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1891,13 +1897,13 @@
         <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
         <v>7</v>
@@ -1906,13 +1912,13 @@
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
@@ -1921,16 +1927,16 @@
         <v>7.6</v>
       </c>
       <c r="BB5">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>6.4</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
         <v>5.9</v>
@@ -1939,67 +1945,67 @@
         <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
         <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2016,22 +2022,22 @@
         <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="K6">
         <v>920</v>
@@ -2067,10 +2073,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2241,7 +2247,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2258,13 +2264,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G7">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -2273,196 +2279,196 @@
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="M7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
         <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X7">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
         <v>46</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF7">
         <v>10</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AK7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="AN7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AP7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT7">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD7">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="BE7">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BF7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BG7">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7">
         <v>15</v>
       </c>
       <c r="BK7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BL7">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>3.95</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT7">
         <v>12</v>
       </c>
       <c r="BU7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV7">
         <v>90</v>
@@ -2477,13 +2483,13 @@
         <v>21</v>
       </c>
       <c r="BZ7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CB7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2500,16 +2506,16 @@
         <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2521,7 +2527,7 @@
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M8">
         <v>1.14</v>
@@ -2536,7 +2542,7 @@
         <v>1.53</v>
       </c>
       <c r="Q8">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
         <v>1.19</v>
@@ -2545,7 +2551,7 @@
         <v>5.7</v>
       </c>
       <c r="T8">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
         <v>1.81</v>
@@ -2554,10 +2560,10 @@
         <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X8">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8">
         <v>8.6</v>
@@ -2578,7 +2584,7 @@
         <v>14.5</v>
       </c>
       <c r="AE8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>18.5</v>
@@ -2599,7 +2605,7 @@
         <v>60</v>
       </c>
       <c r="AL8">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>220</v>
@@ -2617,7 +2623,7 @@
         <v>7.6</v>
       </c>
       <c r="AR8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
         <v>42</v>
@@ -2638,7 +2644,7 @@
         <v>16</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>21</v>
@@ -2650,82 +2656,82 @@
         <v>46</v>
       </c>
       <c r="BC8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BD8">
         <v>60</v>
       </c>
       <c r="BE8">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF8">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH8">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BI8">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="BJ8">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BK8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM8">
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BQ8">
         <v>17.5</v>
       </c>
       <c r="BR8">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BS8">
         <v>21</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW8">
         <v>16.5</v>
       </c>
       <c r="BX8">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BY8">
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="CA8">
         <v>21</v>
       </c>
       <c r="CB8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2742,169 +2748,169 @@
         <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G9">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H9">
         <v>6.4</v>
       </c>
       <c r="I9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R9">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V9">
         <v>1.15</v>
       </c>
       <c r="W9">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AO9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP9">
-        <v>1.49</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR9">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="AS9">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="AT9">
-        <v>1.48</v>
+        <v>9.6</v>
       </c>
       <c r="AU9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9">
+        <v>18.5</v>
+      </c>
+      <c r="AW9">
+        <v>6.2</v>
+      </c>
+      <c r="AX9">
+        <v>9.4</v>
+      </c>
+      <c r="AY9">
+        <v>8.6</v>
+      </c>
+      <c r="AZ9">
         <v>17.5</v>
       </c>
-      <c r="AW9">
-        <v>1.49</v>
-      </c>
-      <c r="AX9">
-        <v>9</v>
-      </c>
-      <c r="AY9">
-        <v>1.45</v>
-      </c>
-      <c r="AZ9">
-        <v>1.69</v>
-      </c>
       <c r="BA9">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BB9">
-        <v>1.69</v>
+        <v>12</v>
       </c>
       <c r="BC9">
-        <v>1.68</v>
+        <v>13</v>
       </c>
       <c r="BD9">
-        <v>1.69</v>
+        <v>21</v>
       </c>
       <c r="BE9">
-        <v>1.49</v>
+        <v>6.2</v>
       </c>
       <c r="BF9">
-        <v>1.39</v>
+        <v>5.5</v>
       </c>
       <c r="BG9">
-        <v>1.47</v>
+        <v>6.2</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2928,7 +2934,7 @@
         <v>6</v>
       </c>
       <c r="BO9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
@@ -2967,7 +2973,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2984,13 +2990,13 @@
         <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F10">
         <v>1.67</v>
       </c>
       <c r="G10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H10">
         <v>6.6</v>
@@ -3029,7 +3035,7 @@
         <v>4.6</v>
       </c>
       <c r="T10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U10">
         <v>1.72</v>
@@ -3038,7 +3044,7 @@
         <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X10">
         <v>11</v>
@@ -3050,7 +3056,7 @@
         <v>55</v>
       </c>
       <c r="AA10">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB10">
         <v>6.4</v>
@@ -3068,10 +3074,10 @@
         <v>8.6</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI10">
         <v>150</v>
@@ -3080,13 +3086,13 @@
         <v>16.5</v>
       </c>
       <c r="AK10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL10">
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN10">
         <v>14</v>
@@ -3104,22 +3110,22 @@
         <v>46</v>
       </c>
       <c r="AS10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AT10">
         <v>6</v>
       </c>
       <c r="AU10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV10">
         <v>24</v>
       </c>
       <c r="AW10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY10">
         <v>9.6</v>
@@ -3128,7 +3134,7 @@
         <v>25</v>
       </c>
       <c r="BA10">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BB10">
         <v>14.5</v>
@@ -3140,13 +3146,13 @@
         <v>46</v>
       </c>
       <c r="BE10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BF10">
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH10">
         <v>3.25</v>
@@ -3155,7 +3161,7 @@
         <v>2.56</v>
       </c>
       <c r="BJ10">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="BK10">
         <v>8.800000000000001</v>
@@ -3173,7 +3179,7 @@
         <v>3.5</v>
       </c>
       <c r="BP10">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10">
         <v>8.800000000000001</v>
@@ -3185,7 +3191,7 @@
         <v>21</v>
       </c>
       <c r="BT10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU10">
         <v>7.4</v>
@@ -3206,10 +3212,10 @@
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CB10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3226,16 +3232,16 @@
         <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I11">
         <v>2.54</v>
@@ -3247,7 +3253,7 @@
         <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3271,16 +3277,16 @@
         <v>4</v>
       </c>
       <c r="T11">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X11">
         <v>12</v>
@@ -3292,7 +3298,7 @@
         <v>15.5</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
@@ -3304,7 +3310,7 @@
         <v>12</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF11">
         <v>22</v>
@@ -3319,7 +3325,7 @@
         <v>55</v>
       </c>
       <c r="AJ11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK11">
         <v>40</v>
@@ -3334,7 +3340,7 @@
         <v>44</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP11">
         <v>10.5</v>
@@ -3352,13 +3358,13 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11">
         <v>18.5</v>
@@ -3373,31 +3379,31 @@
         <v>40</v>
       </c>
       <c r="BB11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC11">
         <v>34</v>
       </c>
       <c r="BD11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF11">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BG11">
         <v>22</v>
       </c>
       <c r="BH11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI11">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11">
         <v>8.6</v>
@@ -3412,19 +3418,19 @@
         <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BR11">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BS11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BT11">
         <v>5.3</v>
@@ -3442,16 +3448,16 @@
         <v>40</v>
       </c>
       <c r="BY11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CB11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3468,7 +3474,7 @@
         <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F12">
         <v>1.22</v>
@@ -3480,7 +3486,7 @@
         <v>16</v>
       </c>
       <c r="I12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J12">
         <v>8.199999999999999</v>
@@ -3489,34 +3495,34 @@
         <v>8.4</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O12">
         <v>1.17</v>
       </c>
       <c r="P12">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V12">
         <v>1.06</v>
@@ -3528,7 +3534,7 @@
         <v>38</v>
       </c>
       <c r="Y12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z12">
         <v>200</v>
@@ -3537,82 +3543,82 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AD12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE12">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI12">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ12">
         <v>8.800000000000001</v>
       </c>
       <c r="AK12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM12">
         <v>270</v>
       </c>
       <c r="AN12">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AO12">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="AP12">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AQ12">
         <v>36</v>
       </c>
       <c r="AR12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12">
         <v>16.5</v>
       </c>
       <c r="AV12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX12">
         <v>7.2</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>30</v>
       </c>
       <c r="BA12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12">
         <v>8</v>
@@ -3624,49 +3630,49 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
         <v>4.6</v>
       </c>
       <c r="BI12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BK12">
         <v>12.5</v>
       </c>
       <c r="BL12">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM12">
         <v>21</v>
       </c>
       <c r="BN12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BO12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP12">
         <v>6.6</v>
       </c>
       <c r="BQ12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BS12">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT12">
         <v>22</v>
@@ -3681,7 +3687,7 @@
         <v>21</v>
       </c>
       <c r="BX12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY12">
         <v>21</v>
@@ -3693,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3710,13 +3716,13 @@
         <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H13">
         <v>1.06</v>
@@ -3731,13 +3737,13 @@
         <v>23</v>
       </c>
       <c r="L13">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
         <v>1.13</v>
@@ -3746,28 +3752,28 @@
         <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S13">
         <v>2.04</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U13">
         <v>1.3</v>
       </c>
       <c r="V13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y13">
         <v>11.5</v>
@@ -3779,7 +3785,7 @@
         <v>6.2</v>
       </c>
       <c r="AB13">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AC13">
         <v>75</v>
@@ -3794,7 +3800,7 @@
         <v>1000</v>
       </c>
       <c r="AG13">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AH13">
         <v>220</v>
@@ -3818,25 +3824,25 @@
         <v>1000</v>
       </c>
       <c r="AO13">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AP13">
+        <v>21</v>
+      </c>
+      <c r="AQ13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR13">
+        <v>6.4</v>
+      </c>
+      <c r="AS13">
+        <v>5.4</v>
+      </c>
+      <c r="AT13">
         <v>11</v>
       </c>
-      <c r="AQ13">
-        <v>9.4</v>
-      </c>
-      <c r="AR13">
-        <v>6</v>
-      </c>
-      <c r="AS13">
-        <v>4.8</v>
-      </c>
-      <c r="AT13">
-        <v>12.5</v>
-      </c>
       <c r="AU13">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV13">
         <v>18</v>
@@ -3845,31 +3851,31 @@
         <v>18</v>
       </c>
       <c r="AX13">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="AY13">
-        <v>13</v>
+        <v>2.08</v>
       </c>
       <c r="AZ13">
-        <v>13</v>
+        <v>2.1</v>
       </c>
       <c r="BA13">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="BB13">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="BC13">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE13">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF13">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="BG13">
         <v>2.32</v>
@@ -3881,34 +3887,34 @@
         <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
         <v>4.3</v>
@@ -3917,25 +3923,25 @@
         <v>2.48</v>
       </c>
       <c r="BV13">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BX13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="CB13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3952,25 +3958,25 @@
         <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G14">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="J14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -3979,7 +3985,7 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
         <v>1.25</v>
@@ -3991,25 +3997,25 @@
         <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S14">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
         <v>1.87</v>
       </c>
       <c r="V14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y14">
         <v>8.6</v>
@@ -4027,13 +4033,13 @@
         <v>12</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE14">
         <v>15</v>
       </c>
       <c r="AF14">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AG14">
         <v>36</v>
@@ -4045,10 +4051,10 @@
         <v>38</v>
       </c>
       <c r="AJ14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AK14">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL14">
         <v>140</v>
@@ -4063,10 +4069,10 @@
         <v>5.9</v>
       </c>
       <c r="AP14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14">
         <v>7.6</v>
@@ -4078,10 +4084,10 @@
         <v>28</v>
       </c>
       <c r="AU14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14">
         <v>14</v>
@@ -4099,16 +4105,16 @@
         <v>32</v>
       </c>
       <c r="BB14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC14">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="BE14">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="BF14">
         <v>140</v>
@@ -4117,67 +4123,67 @@
         <v>5.6</v>
       </c>
       <c r="BH14">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BL14">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BV14">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BX14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4194,7 +4200,7 @@
         <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F15">
         <v>1.3</v>
@@ -4206,49 +4212,49 @@
         <v>14</v>
       </c>
       <c r="I15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>6.2</v>
       </c>
       <c r="L15">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M15">
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="U15">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
         <v>1.06</v>
       </c>
       <c r="W15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X15">
         <v>16</v>
@@ -4263,7 +4269,7 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC15">
         <v>14</v>
@@ -4272,10 +4278,10 @@
         <v>60</v>
       </c>
       <c r="AE15">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AF15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG15">
         <v>12</v>
@@ -4290,19 +4296,19 @@
         <v>9</v>
       </c>
       <c r="AK15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL15">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AM15">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AN15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO15">
-        <v>760</v>
+        <v>660</v>
       </c>
       <c r="AP15">
         <v>14</v>
@@ -4311,13 +4317,13 @@
         <v>32</v>
       </c>
       <c r="AR15">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU15">
         <v>12.5</v>
@@ -4335,52 +4341,52 @@
         <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BA15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB15">
         <v>8.4</v>
       </c>
       <c r="BC15">
+        <v>14.5</v>
+      </c>
+      <c r="BD15">
+        <v>29</v>
+      </c>
+      <c r="BE15">
+        <v>16.5</v>
+      </c>
+      <c r="BF15">
+        <v>5.3</v>
+      </c>
+      <c r="BG15">
+        <v>16</v>
+      </c>
+      <c r="BH15">
+        <v>3.7</v>
+      </c>
+      <c r="BI15">
+        <v>3.3</v>
+      </c>
+      <c r="BJ15">
         <v>15.5</v>
-      </c>
-      <c r="BD15">
-        <v>50</v>
-      </c>
-      <c r="BE15">
-        <v>16</v>
-      </c>
-      <c r="BF15">
-        <v>5.8</v>
-      </c>
-      <c r="BG15">
-        <v>16.5</v>
-      </c>
-      <c r="BH15">
-        <v>3.6</v>
-      </c>
-      <c r="BI15">
-        <v>3.2</v>
-      </c>
-      <c r="BJ15">
-        <v>16</v>
       </c>
       <c r="BK15">
         <v>13</v>
       </c>
       <c r="BL15">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="BM15">
         <v>21</v>
       </c>
       <c r="BN15">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BO15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP15">
         <v>7.6</v>
@@ -4389,37 +4395,37 @@
         <v>6.6</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS15">
         <v>23</v>
       </c>
       <c r="BT15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU15">
         <v>9.4</v>
       </c>
       <c r="BV15">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BW15">
         <v>21</v>
       </c>
       <c r="BX15">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BY15">
         <v>21</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA15">
         <v>10.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4436,10 +4442,10 @@
         <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F16">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G16">
         <v>1.73</v>
@@ -4463,7 +4469,7 @@
         <v>1.11</v>
       </c>
       <c r="N16">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O16">
         <v>1.48</v>
@@ -4472,16 +4478,16 @@
         <v>1.64</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R16">
         <v>1.23</v>
       </c>
       <c r="S16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U16">
         <v>1.69</v>
@@ -4490,19 +4496,19 @@
         <v>1.16</v>
       </c>
       <c r="W16">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z16">
         <v>65</v>
       </c>
       <c r="AA16">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AB16">
         <v>6.4</v>
@@ -4511,10 +4517,10 @@
         <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE16">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF16">
         <v>8.6</v>
@@ -4523,7 +4529,7 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI16">
         <v>160</v>
@@ -4538,28 +4544,28 @@
         <v>65</v>
       </c>
       <c r="AM16">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN16">
         <v>16</v>
       </c>
       <c r="AO16">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AP16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16">
         <v>14</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AS16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT16">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU16">
         <v>7.6</v>
@@ -4568,100 +4574,100 @@
         <v>18.5</v>
       </c>
       <c r="AW16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX16">
         <v>7.6</v>
       </c>
       <c r="AY16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BA16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BE16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF16">
         <v>13.5</v>
       </c>
       <c r="BG16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI16">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK16">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO16">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ16">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU16">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="CB16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4678,10 +4684,10 @@
         <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G17">
         <v>4.5</v>
@@ -4711,13 +4717,13 @@
         <v>1.41</v>
       </c>
       <c r="P17">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q17">
         <v>2.24</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
         <v>4.2</v>
@@ -4726,7 +4732,7 @@
         <v>2.02</v>
       </c>
       <c r="U17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V17">
         <v>1.98</v>
@@ -4747,7 +4753,7 @@
         <v>23</v>
       </c>
       <c r="AB17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
         <v>8.199999999999999</v>
@@ -4774,7 +4780,7 @@
         <v>110</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL17">
         <v>75</v>
@@ -4789,7 +4795,7 @@
         <v>17</v>
       </c>
       <c r="AP17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17">
         <v>7.6</v>
@@ -4813,7 +4819,7 @@
         <v>21</v>
       </c>
       <c r="AX17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY17">
         <v>16.5</v>
@@ -4825,22 +4831,22 @@
         <v>40</v>
       </c>
       <c r="BB17">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BC17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD17">
         <v>60</v>
       </c>
       <c r="BE17">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BF17">
         <v>65</v>
       </c>
       <c r="BG17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH17">
         <v>3.3</v>
@@ -4903,7 +4909,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4920,22 +4926,22 @@
         <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F18">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H18">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I18">
         <v>3.9</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
         <v>4.2</v>
@@ -4944,7 +4950,7 @@
         <v>1.28</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
         <v>5.1</v>
@@ -4953,7 +4959,7 @@
         <v>1.21</v>
       </c>
       <c r="P18">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q18">
         <v>1.62</v>
@@ -4962,7 +4968,7 @@
         <v>1.57</v>
       </c>
       <c r="S18">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T18">
         <v>1.59</v>
@@ -4971,10 +4977,10 @@
         <v>2.46</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="X18">
         <v>26</v>
@@ -5034,13 +5040,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5052,7 +5058,7 @@
         <v>14</v>
       </c>
       <c r="AW18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5064,10 +5070,10 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC18">
         <v>16.5</v>
@@ -5079,7 +5085,7 @@
         <v>6.6</v>
       </c>
       <c r="BF18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG18">
         <v>21</v>
@@ -5103,7 +5109,7 @@
         <v>1.02</v>
       </c>
       <c r="BN18">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO18">
         <v>4.6</v>
@@ -5124,7 +5130,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>27</v>
@@ -5145,7 +5151,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5162,22 +5168,22 @@
         <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19">
         <v>4</v>
       </c>
       <c r="G19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H19">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I19">
         <v>1.93</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>4.3</v>
@@ -5189,7 +5195,7 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
         <v>1.26</v>
@@ -5198,16 +5204,16 @@
         <v>2.14</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S19">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U19">
         <v>2.18</v>
@@ -5216,7 +5222,7 @@
         <v>2.06</v>
       </c>
       <c r="W19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X19">
         <v>19.5</v>
@@ -5225,19 +5231,19 @@
         <v>11</v>
       </c>
       <c r="Z19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA19">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB19">
         <v>18</v>
       </c>
       <c r="AC19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE19">
         <v>19.5</v>
@@ -5246,7 +5252,7 @@
         <v>34</v>
       </c>
       <c r="AG19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH19">
         <v>18.5</v>
@@ -5267,25 +5273,25 @@
         <v>90</v>
       </c>
       <c r="AN19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO19">
         <v>11.5</v>
       </c>
       <c r="AP19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR19">
         <v>11</v>
       </c>
       <c r="AS19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5318,13 +5324,13 @@
         <v>42</v>
       </c>
       <c r="BE19">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF19">
         <v>28</v>
       </c>
       <c r="BG19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19">
         <v>4.3</v>
@@ -5345,7 +5351,7 @@
         <v>1.02</v>
       </c>
       <c r="BN19">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO19">
         <v>6</v>
@@ -5387,7 +5393,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5404,25 +5410,25 @@
         <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F20">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G20">
         <v>2.34</v>
       </c>
       <c r="H20">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J20">
         <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.23</v>
@@ -5431,31 +5437,31 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
         <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R20">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S20">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.74</v>
@@ -5509,7 +5515,7 @@
         <v>55</v>
       </c>
       <c r="AN20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO20">
         <v>970</v>
@@ -5518,22 +5524,22 @@
         <v>22</v>
       </c>
       <c r="AQ20">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="AR20">
         <v>22</v>
       </c>
       <c r="AS20">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU20">
         <v>8.800000000000001</v>
       </c>
       <c r="AV20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW20">
         <v>21</v>
@@ -5548,19 +5554,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB20">
         <v>21</v>
       </c>
       <c r="BC20">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD20">
         <v>20</v>
       </c>
       <c r="BE20">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF20">
         <v>9.6</v>
@@ -5629,7 +5635,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5646,25 +5652,25 @@
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F21">
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H21">
         <v>3.25</v>
       </c>
       <c r="I21">
+        <v>3.6</v>
+      </c>
+      <c r="J21">
         <v>3.7</v>
       </c>
-      <c r="J21">
-        <v>3.75</v>
-      </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5679,13 +5685,13 @@
         <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R21">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S21">
         <v>2.74</v>
@@ -5694,13 +5700,13 @@
         <v>1.62</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X21">
         <v>20</v>
@@ -5733,7 +5739,7 @@
         <v>12</v>
       </c>
       <c r="AH21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI21">
         <v>42</v>
@@ -5742,7 +5748,7 @@
         <v>32</v>
       </c>
       <c r="AK21">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL21">
         <v>38</v>
@@ -5757,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="AP21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21">
         <v>13.5</v>
@@ -5769,10 +5775,10 @@
         <v>34</v>
       </c>
       <c r="AT21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
         <v>12.5</v>
@@ -5784,7 +5790,7 @@
         <v>13.5</v>
       </c>
       <c r="AY21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21">
         <v>13.5</v>
@@ -5802,7 +5808,7 @@
         <v>24</v>
       </c>
       <c r="BE21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF21">
         <v>11.5</v>
@@ -5829,19 +5835,19 @@
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
@@ -5865,13 +5871,13 @@
         <v>1.02</v>
       </c>
       <c r="BZ21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5888,169 +5894,169 @@
         <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F22">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="G22">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="H22">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I22">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="T22">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U22">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="V22">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="X22">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y22">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="Z22">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA22">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB22">
         <v>15</v>
       </c>
       <c r="AC22">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE22">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH22">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI22">
         <v>44</v>
       </c>
       <c r="AJ22">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AK22">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AL22">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AM22">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AN22">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AO22">
         <v>34</v>
       </c>
       <c r="AP22">
+        <v>16.5</v>
+      </c>
+      <c r="AQ22">
+        <v>13.5</v>
+      </c>
+      <c r="AR22">
+        <v>21</v>
+      </c>
+      <c r="AS22">
+        <v>5.5</v>
+      </c>
+      <c r="AT22">
+        <v>10.5</v>
+      </c>
+      <c r="AU22">
+        <v>7.8</v>
+      </c>
+      <c r="AV22">
+        <v>12</v>
+      </c>
+      <c r="AW22">
+        <v>5.1</v>
+      </c>
+      <c r="AX22">
+        <v>13.5</v>
+      </c>
+      <c r="AY22">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22">
+        <v>13.5</v>
+      </c>
+      <c r="BA22">
+        <v>5.2</v>
+      </c>
+      <c r="BB22">
         <v>20</v>
       </c>
-      <c r="AQ22">
-        <v>20</v>
-      </c>
-      <c r="AR22">
-        <v>8</v>
-      </c>
-      <c r="AS22">
-        <v>8.4</v>
-      </c>
-      <c r="AT22">
+      <c r="BC22">
+        <v>18.5</v>
+      </c>
+      <c r="BD22">
+        <v>5.1</v>
+      </c>
+      <c r="BE22">
+        <v>5.6</v>
+      </c>
+      <c r="BF22">
         <v>11.5</v>
       </c>
-      <c r="AU22">
-        <v>9</v>
-      </c>
-      <c r="AV22">
-        <v>15.5</v>
-      </c>
-      <c r="AW22">
-        <v>29</v>
-      </c>
-      <c r="AX22">
-        <v>12.5</v>
-      </c>
-      <c r="AY22">
-        <v>9</v>
-      </c>
-      <c r="AZ22">
-        <v>13</v>
-      </c>
-      <c r="BA22">
-        <v>7.6</v>
-      </c>
-      <c r="BB22">
-        <v>17.5</v>
-      </c>
-      <c r="BC22">
-        <v>14.5</v>
-      </c>
-      <c r="BD22">
-        <v>20</v>
-      </c>
-      <c r="BE22">
-        <v>40</v>
-      </c>
-      <c r="BF22">
-        <v>6.4</v>
-      </c>
       <c r="BG22">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6059,61 +6065,61 @@
         <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
         <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6130,232 +6136,232 @@
         <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F23">
+        <v>1.78</v>
+      </c>
+      <c r="G23">
+        <v>1.87</v>
+      </c>
+      <c r="H23">
+        <v>4.3</v>
+      </c>
+      <c r="I23">
+        <v>4.8</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4.5</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
+      <c r="O23">
+        <v>1.17</v>
+      </c>
+      <c r="P23">
+        <v>2.6</v>
+      </c>
+      <c r="Q23">
+        <v>1.52</v>
+      </c>
+      <c r="R23">
+        <v>1.7</v>
+      </c>
+      <c r="S23">
         <v>2.28</v>
       </c>
-      <c r="G23">
-        <v>2.48</v>
-      </c>
-      <c r="H23">
-        <v>3.05</v>
-      </c>
-      <c r="I23">
-        <v>3.3</v>
-      </c>
-      <c r="J23">
-        <v>3.6</v>
-      </c>
-      <c r="K23">
-        <v>3.9</v>
-      </c>
-      <c r="L23">
-        <v>1.32</v>
-      </c>
-      <c r="M23">
-        <v>1.05</v>
-      </c>
-      <c r="N23">
-        <v>4.1</v>
-      </c>
-      <c r="O23">
+      <c r="T23">
+        <v>1.54</v>
+      </c>
+      <c r="U23">
+        <v>2.54</v>
+      </c>
+      <c r="V23">
         <v>1.26</v>
       </c>
-      <c r="P23">
-        <v>2.12</v>
-      </c>
-      <c r="Q23">
-        <v>1.79</v>
-      </c>
-      <c r="R23">
-        <v>1.43</v>
-      </c>
-      <c r="S23">
-        <v>2.94</v>
-      </c>
-      <c r="T23">
-        <v>1.65</v>
-      </c>
-      <c r="U23">
-        <v>2.26</v>
-      </c>
-      <c r="V23">
-        <v>1.43</v>
-      </c>
       <c r="W23">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="X23">
+        <v>28</v>
+      </c>
+      <c r="Y23">
+        <v>26</v>
+      </c>
+      <c r="Z23">
+        <v>42</v>
+      </c>
+      <c r="AA23">
+        <v>90</v>
+      </c>
+      <c r="AB23">
+        <v>14.5</v>
+      </c>
+      <c r="AC23">
+        <v>11</v>
+      </c>
+      <c r="AD23">
+        <v>19.5</v>
+      </c>
+      <c r="AE23">
+        <v>46</v>
+      </c>
+      <c r="AF23">
+        <v>15.5</v>
+      </c>
+      <c r="AG23">
+        <v>11</v>
+      </c>
+      <c r="AH23">
+        <v>16</v>
+      </c>
+      <c r="AI23">
+        <v>44</v>
+      </c>
+      <c r="AJ23">
+        <v>22</v>
+      </c>
+      <c r="AK23">
+        <v>18</v>
+      </c>
+      <c r="AL23">
+        <v>25</v>
+      </c>
+      <c r="AM23">
+        <v>60</v>
+      </c>
+      <c r="AN23">
+        <v>7.6</v>
+      </c>
+      <c r="AO23">
+        <v>34</v>
+      </c>
+      <c r="AP23">
         <v>20</v>
       </c>
-      <c r="Y23">
-        <v>15</v>
-      </c>
-      <c r="Z23">
-        <v>26</v>
-      </c>
-      <c r="AA23">
-        <v>60</v>
-      </c>
-      <c r="AB23">
+      <c r="AQ23">
+        <v>21</v>
+      </c>
+      <c r="AR23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23">
+        <v>12</v>
+      </c>
+      <c r="AU23">
+        <v>9</v>
+      </c>
+      <c r="AV23">
+        <v>16</v>
+      </c>
+      <c r="AW23">
+        <v>29</v>
+      </c>
+      <c r="AX23">
         <v>12.5</v>
       </c>
-      <c r="AC23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD23">
+      <c r="AY23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23">
+        <v>13</v>
+      </c>
+      <c r="BA23">
+        <v>8.4</v>
+      </c>
+      <c r="BB23">
+        <v>17.5</v>
+      </c>
+      <c r="BC23">
         <v>14.5</v>
       </c>
-      <c r="AE23">
-        <v>36</v>
-      </c>
-      <c r="AF23">
-        <v>17</v>
-      </c>
-      <c r="AG23">
+      <c r="BD23">
+        <v>21</v>
+      </c>
+      <c r="BE23">
+        <v>40</v>
+      </c>
+      <c r="BF23">
+        <v>6.4</v>
+      </c>
+      <c r="BG23">
+        <v>7.8</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
         <v>12</v>
       </c>
-      <c r="AH23">
-        <v>17</v>
-      </c>
-      <c r="AI23">
-        <v>48</v>
-      </c>
-      <c r="AJ23">
-        <v>32</v>
-      </c>
-      <c r="AK23">
-        <v>25</v>
-      </c>
-      <c r="AL23">
-        <v>36</v>
-      </c>
-      <c r="AM23">
-        <v>85</v>
-      </c>
-      <c r="AN23">
-        <v>17</v>
-      </c>
-      <c r="AO23">
-        <v>30</v>
-      </c>
-      <c r="AP23">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23">
-        <v>12</v>
-      </c>
-      <c r="AR23">
-        <v>20</v>
-      </c>
-      <c r="AS23">
-        <v>34</v>
-      </c>
-      <c r="AT23">
-        <v>10</v>
-      </c>
-      <c r="AU23">
-        <v>7.4</v>
-      </c>
-      <c r="AV23">
-        <v>12</v>
-      </c>
-      <c r="AW23">
-        <v>6.6</v>
-      </c>
-      <c r="AX23">
-        <v>14</v>
-      </c>
-      <c r="AY23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23">
-        <v>13.5</v>
-      </c>
-      <c r="BA23">
-        <v>27</v>
-      </c>
-      <c r="BB23">
-        <v>6.6</v>
-      </c>
-      <c r="BC23">
-        <v>20</v>
-      </c>
-      <c r="BD23">
-        <v>6.6</v>
-      </c>
-      <c r="BE23">
-        <v>7.4</v>
-      </c>
-      <c r="BF23">
-        <v>13.5</v>
-      </c>
-      <c r="BG23">
-        <v>21</v>
-      </c>
-      <c r="BH23">
-        <v>4.2</v>
-      </c>
-      <c r="BI23">
-        <v>3.05</v>
-      </c>
-      <c r="BJ23">
-        <v>10.5</v>
-      </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM23">
         <v>1.02</v>
       </c>
       <c r="BN23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO23">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="BP23">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BS23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BU23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BY23">
         <v>1.02</v>
       </c>
       <c r="BZ23">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6372,232 +6378,232 @@
         <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F24">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="H24">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="I24">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="P24">
-        <v>2.86</v>
+        <v>2.08</v>
       </c>
       <c r="Q24">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="R24">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="S24">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="T24">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="U24">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="X24">
+        <v>21</v>
+      </c>
+      <c r="Y24">
+        <v>15</v>
+      </c>
+      <c r="Z24">
+        <v>25</v>
+      </c>
+      <c r="AA24">
+        <v>60</v>
+      </c>
+      <c r="AB24">
+        <v>12.5</v>
+      </c>
+      <c r="AC24">
+        <v>9</v>
+      </c>
+      <c r="AD24">
+        <v>14.5</v>
+      </c>
+      <c r="AE24">
         <v>36</v>
       </c>
-      <c r="Y24">
-        <v>20</v>
-      </c>
-      <c r="Z24">
-        <v>24</v>
-      </c>
-      <c r="AA24">
-        <v>38</v>
-      </c>
-      <c r="AB24">
-        <v>20</v>
-      </c>
-      <c r="AC24">
-        <v>11</v>
-      </c>
-      <c r="AD24">
-        <v>13.5</v>
-      </c>
-      <c r="AE24">
+      <c r="AF24">
+        <v>17</v>
+      </c>
+      <c r="AG24">
+        <v>12</v>
+      </c>
+      <c r="AH24">
+        <v>17</v>
+      </c>
+      <c r="AI24">
+        <v>48</v>
+      </c>
+      <c r="AJ24">
+        <v>32</v>
+      </c>
+      <c r="AK24">
         <v>25</v>
       </c>
-      <c r="AF24">
-        <v>24</v>
-      </c>
-      <c r="AG24">
-        <v>13</v>
-      </c>
-      <c r="AH24">
-        <v>15.5</v>
-      </c>
-      <c r="AI24">
-        <v>29</v>
-      </c>
-      <c r="AJ24">
-        <v>38</v>
-      </c>
-      <c r="AK24">
-        <v>26</v>
-      </c>
       <c r="AL24">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AM24">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AN24">
+        <v>17</v>
+      </c>
+      <c r="AO24">
+        <v>30</v>
+      </c>
+      <c r="AP24">
+        <v>14.5</v>
+      </c>
+      <c r="AQ24">
         <v>12.5</v>
-      </c>
-      <c r="AO24">
-        <v>12.5</v>
-      </c>
-      <c r="AP24">
-        <v>7.8</v>
-      </c>
-      <c r="AQ24">
-        <v>16.5</v>
       </c>
       <c r="AR24">
         <v>20</v>
       </c>
       <c r="AS24">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AT24">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AU24">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW24">
+        <v>7.2</v>
+      </c>
+      <c r="AX24">
+        <v>14</v>
+      </c>
+      <c r="AY24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24">
+        <v>13.5</v>
+      </c>
+      <c r="BA24">
+        <v>27</v>
+      </c>
+      <c r="BB24">
+        <v>7</v>
+      </c>
+      <c r="BC24">
         <v>20</v>
       </c>
-      <c r="AX24">
-        <v>20</v>
-      </c>
-      <c r="AY24">
-        <v>11</v>
-      </c>
-      <c r="AZ24">
-        <v>12.5</v>
-      </c>
-      <c r="BA24">
+      <c r="BD24">
+        <v>7.2</v>
+      </c>
+      <c r="BE24">
+        <v>8</v>
+      </c>
+      <c r="BF24">
+        <v>13.5</v>
+      </c>
+      <c r="BG24">
         <v>21</v>
       </c>
-      <c r="BB24">
-        <v>7.8</v>
-      </c>
-      <c r="BC24">
-        <v>21</v>
-      </c>
-      <c r="BD24">
-        <v>7.4</v>
-      </c>
-      <c r="BE24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF24">
-        <v>10</v>
-      </c>
-      <c r="BG24">
+      <c r="BH24">
+        <v>4.2</v>
+      </c>
+      <c r="BI24">
+        <v>3.05</v>
+      </c>
+      <c r="BJ24">
         <v>10.5</v>
       </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24">
-        <v>11</v>
-      </c>
       <c r="BK24">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BM24">
         <v>1.02</v>
       </c>
       <c r="BN24">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO24">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP24">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BQ24">
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT24">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU24">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ24">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6614,716 +6620,958 @@
         <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F25">
+        <v>2.48</v>
+      </c>
+      <c r="G25">
+        <v>2.58</v>
+      </c>
+      <c r="H25">
+        <v>2.56</v>
+      </c>
+      <c r="I25">
+        <v>2.72</v>
+      </c>
+      <c r="J25">
+        <v>4.1</v>
+      </c>
+      <c r="K25">
         <v>4.5</v>
       </c>
-      <c r="G25">
-        <v>4.9</v>
-      </c>
-      <c r="H25">
-        <v>1.78</v>
-      </c>
-      <c r="I25">
-        <v>1.82</v>
-      </c>
-      <c r="J25">
-        <v>4.2</v>
-      </c>
-      <c r="K25">
-        <v>4.4</v>
-      </c>
       <c r="L25">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="S25">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="T25">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="U25">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="V25">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="W25">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="X25">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Y25">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="Z25">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AA25">
+        <v>38</v>
+      </c>
+      <c r="AB25">
         <v>20</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
+        <v>11</v>
+      </c>
+      <c r="AD25">
+        <v>13.5</v>
+      </c>
+      <c r="AE25">
+        <v>25</v>
+      </c>
+      <c r="AF25">
         <v>24</v>
       </c>
-      <c r="AC25">
-        <v>10</v>
-      </c>
-      <c r="AD25">
-        <v>10.5</v>
-      </c>
-      <c r="AE25">
-        <v>17.5</v>
-      </c>
-      <c r="AF25">
-        <v>40</v>
-      </c>
       <c r="AG25">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AH25">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AI25">
         <v>29</v>
       </c>
       <c r="AJ25">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="AK25">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AL25">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AM25">
+        <v>50</v>
+      </c>
+      <c r="AN25">
+        <v>12.5</v>
+      </c>
+      <c r="AO25">
+        <v>12.5</v>
+      </c>
+      <c r="AP25">
+        <v>8</v>
+      </c>
+      <c r="AQ25">
+        <v>17</v>
+      </c>
+      <c r="AR25">
+        <v>20</v>
+      </c>
+      <c r="AS25">
+        <v>8</v>
+      </c>
+      <c r="AT25">
+        <v>16</v>
+      </c>
+      <c r="AU25">
+        <v>9.4</v>
+      </c>
+      <c r="AV25">
+        <v>11</v>
+      </c>
+      <c r="AW25">
+        <v>21</v>
+      </c>
+      <c r="AX25">
+        <v>7.2</v>
+      </c>
+      <c r="AY25">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25">
+        <v>13</v>
+      </c>
+      <c r="BA25">
+        <v>21</v>
+      </c>
+      <c r="BB25">
+        <v>8</v>
+      </c>
+      <c r="BC25">
+        <v>20</v>
+      </c>
+      <c r="BD25">
+        <v>7.6</v>
+      </c>
+      <c r="BE25">
+        <v>8.6</v>
+      </c>
+      <c r="BF25">
+        <v>10</v>
+      </c>
+      <c r="BG25">
+        <v>10.5</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>5.4</v>
+      </c>
+      <c r="BL25">
         <v>85</v>
       </c>
-      <c r="AN25">
-        <v>48</v>
-      </c>
-      <c r="AO25">
-        <v>9</v>
-      </c>
-      <c r="AP25">
-        <v>19</v>
-      </c>
-      <c r="AQ25">
-        <v>10</v>
-      </c>
-      <c r="AR25">
-        <v>10.5</v>
-      </c>
-      <c r="AS25">
-        <v>17.5</v>
-      </c>
-      <c r="AT25">
-        <v>18</v>
-      </c>
-      <c r="AU25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV25">
-        <v>9</v>
-      </c>
-      <c r="AW25">
-        <v>15</v>
-      </c>
-      <c r="AX25">
-        <v>34</v>
-      </c>
-      <c r="AY25">
-        <v>16</v>
-      </c>
-      <c r="AZ25">
-        <v>15.5</v>
-      </c>
-      <c r="BA25">
-        <v>24</v>
-      </c>
-      <c r="BB25">
-        <v>11.5</v>
-      </c>
-      <c r="BC25">
-        <v>44</v>
-      </c>
-      <c r="BD25">
-        <v>44</v>
-      </c>
-      <c r="BE25">
-        <v>13</v>
-      </c>
-      <c r="BF25">
-        <v>10.5</v>
-      </c>
-      <c r="BG25">
-        <v>7.8</v>
-      </c>
-      <c r="BH25">
-        <v>4.7</v>
-      </c>
-      <c r="BI25">
-        <v>3.15</v>
-      </c>
-      <c r="BJ25">
-        <v>9.6</v>
-      </c>
-      <c r="BK25">
-        <v>5.8</v>
-      </c>
-      <c r="BL25">
-        <v>120</v>
-      </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN25">
         <v>8.6</v>
       </c>
       <c r="BO25">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP25">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BQ25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BS25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BU25">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV25">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BW25">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
         <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H26">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="I26">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K26">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="O26">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="P26">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q26">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="T26">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="U26">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="W26">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X26">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Y26">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA26">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AB26">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AC26">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AD26">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE26">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AF26">
         <v>40</v>
       </c>
       <c r="AG26">
+        <v>18.5</v>
+      </c>
+      <c r="AH26">
         <v>22</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
+        <v>29</v>
+      </c>
+      <c r="AJ26">
+        <v>110</v>
+      </c>
+      <c r="AK26">
+        <v>55</v>
+      </c>
+      <c r="AL26">
+        <v>55</v>
+      </c>
+      <c r="AM26">
+        <v>85</v>
+      </c>
+      <c r="AN26">
+        <v>48</v>
+      </c>
+      <c r="AO26">
+        <v>9</v>
+      </c>
+      <c r="AP26">
+        <v>19</v>
+      </c>
+      <c r="AQ26">
+        <v>10</v>
+      </c>
+      <c r="AR26">
+        <v>11</v>
+      </c>
+      <c r="AS26">
+        <v>17</v>
+      </c>
+      <c r="AT26">
+        <v>18</v>
+      </c>
+      <c r="AU26">
+        <v>9</v>
+      </c>
+      <c r="AV26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26">
+        <v>15</v>
+      </c>
+      <c r="AX26">
+        <v>32</v>
+      </c>
+      <c r="AY26">
+        <v>16</v>
+      </c>
+      <c r="AZ26">
+        <v>15.5</v>
+      </c>
+      <c r="BA26">
         <v>24</v>
       </c>
-      <c r="AI26">
-        <v>50</v>
-      </c>
-      <c r="AJ26">
-        <v>130</v>
-      </c>
-      <c r="AK26">
-        <v>80</v>
-      </c>
-      <c r="AL26">
-        <v>90</v>
-      </c>
-      <c r="AM26">
-        <v>160</v>
-      </c>
-      <c r="AN26">
-        <v>100</v>
-      </c>
-      <c r="AO26">
-        <v>19</v>
-      </c>
-      <c r="AP26">
+      <c r="BB26">
+        <v>12.5</v>
+      </c>
+      <c r="BC26">
+        <v>44</v>
+      </c>
+      <c r="BD26">
+        <v>44</v>
+      </c>
+      <c r="BE26">
+        <v>13.5</v>
+      </c>
+      <c r="BF26">
         <v>10.5</v>
       </c>
-      <c r="AQ26">
-        <v>7.2</v>
-      </c>
-      <c r="AR26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS26">
-        <v>5.1</v>
-      </c>
-      <c r="AT26">
+      <c r="BG26">
+        <v>8</v>
+      </c>
+      <c r="BH26">
+        <v>4.7</v>
+      </c>
+      <c r="BI26">
+        <v>3.2</v>
+      </c>
+      <c r="BJ26">
+        <v>9.6</v>
+      </c>
+      <c r="BK26">
+        <v>5.8</v>
+      </c>
+      <c r="BL26">
+        <v>120</v>
+      </c>
+      <c r="BM26">
+        <v>1.02</v>
+      </c>
+      <c r="BN26">
+        <v>8.6</v>
+      </c>
+      <c r="BO26">
+        <v>5.3</v>
+      </c>
+      <c r="BP26">
+        <v>36</v>
+      </c>
+      <c r="BQ26">
+        <v>1.02</v>
+      </c>
+      <c r="BR26">
+        <v>42</v>
+      </c>
+      <c r="BS26">
+        <v>1.02</v>
+      </c>
+      <c r="BT26">
+        <v>4.9</v>
+      </c>
+      <c r="BU26">
+        <v>4.1</v>
+      </c>
+      <c r="BV26">
         <v>12.5</v>
       </c>
-      <c r="AU26">
-        <v>7.2</v>
-      </c>
-      <c r="AV26">
-        <v>9.6</v>
-      </c>
-      <c r="AW26">
-        <v>5.1</v>
-      </c>
-      <c r="AX26">
-        <v>5.5</v>
-      </c>
-      <c r="AY26">
-        <v>16.5</v>
-      </c>
-      <c r="AZ26">
+      <c r="BW26">
+        <v>7.4</v>
+      </c>
+      <c r="BX26">
+        <v>24</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
         <v>17.5</v>
       </c>
-      <c r="BA26">
-        <v>5.6</v>
-      </c>
-      <c r="BB26">
-        <v>6</v>
-      </c>
-      <c r="BC26">
-        <v>5.8</v>
-      </c>
-      <c r="BD26">
-        <v>5.9</v>
-      </c>
-      <c r="BE26">
-        <v>6</v>
-      </c>
-      <c r="BF26">
-        <v>6</v>
-      </c>
-      <c r="BG26">
-        <v>5</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.01</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.01</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
-      <c r="BQ26">
-        <v>1.01</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
-      <c r="BS26">
-        <v>1.01</v>
-      </c>
-      <c r="BT26">
-        <v>1000</v>
-      </c>
-      <c r="BU26">
-        <v>1.01</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>1.01</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>1.01</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
       <c r="CA26">
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
         <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F27">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="G27">
+        <v>5.1</v>
+      </c>
+      <c r="H27">
+        <v>1.87</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>3.45</v>
+      </c>
+      <c r="K27">
+        <v>3.75</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.09</v>
+      </c>
+      <c r="N27">
+        <v>3.25</v>
+      </c>
+      <c r="O27">
+        <v>1.4</v>
+      </c>
+      <c r="P27">
+        <v>1.78</v>
+      </c>
+      <c r="Q27">
+        <v>2.16</v>
+      </c>
+      <c r="R27">
+        <v>1.29</v>
+      </c>
+      <c r="S27">
+        <v>4</v>
+      </c>
+      <c r="T27">
+        <v>1.95</v>
+      </c>
+      <c r="U27">
+        <v>1.94</v>
+      </c>
+      <c r="V27">
+        <v>2</v>
+      </c>
+      <c r="W27">
+        <v>1.25</v>
+      </c>
+      <c r="X27">
+        <v>14.5</v>
+      </c>
+      <c r="Y27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z27">
+        <v>13</v>
+      </c>
+      <c r="AA27">
+        <v>26</v>
+      </c>
+      <c r="AB27">
+        <v>16.5</v>
+      </c>
+      <c r="AC27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>12.5</v>
+      </c>
+      <c r="AE27">
+        <v>26</v>
+      </c>
+      <c r="AF27">
+        <v>40</v>
+      </c>
+      <c r="AG27">
+        <v>22</v>
+      </c>
+      <c r="AH27">
+        <v>24</v>
+      </c>
+      <c r="AI27">
+        <v>50</v>
+      </c>
+      <c r="AJ27">
+        <v>130</v>
+      </c>
+      <c r="AK27">
+        <v>85</v>
+      </c>
+      <c r="AL27">
+        <v>90</v>
+      </c>
+      <c r="AM27">
+        <v>160</v>
+      </c>
+      <c r="AN27">
+        <v>100</v>
+      </c>
+      <c r="AO27">
+        <v>19</v>
+      </c>
+      <c r="AP27">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27">
+        <v>7.2</v>
+      </c>
+      <c r="AR27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS27">
+        <v>18.5</v>
+      </c>
+      <c r="AT27">
+        <v>12.5</v>
+      </c>
+      <c r="AU27">
+        <v>7.2</v>
+      </c>
+      <c r="AV27">
+        <v>9.4</v>
+      </c>
+      <c r="AW27">
+        <v>18.5</v>
+      </c>
+      <c r="AX27">
+        <v>5.7</v>
+      </c>
+      <c r="AY27">
+        <v>16.5</v>
+      </c>
+      <c r="AZ27">
+        <v>17.5</v>
+      </c>
+      <c r="BA27">
+        <v>5.9</v>
+      </c>
+      <c r="BB27">
+        <v>6</v>
+      </c>
+      <c r="BC27">
+        <v>6</v>
+      </c>
+      <c r="BD27">
+        <v>6.2</v>
+      </c>
+      <c r="BE27">
+        <v>6</v>
+      </c>
+      <c r="BF27">
+        <v>5.9</v>
+      </c>
+      <c r="BG27">
+        <v>14.5</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28">
+        <v>1.23</v>
+      </c>
+      <c r="G28">
         <v>1.28</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>15.5</v>
       </c>
-      <c r="I27">
+      <c r="I28">
         <v>22</v>
       </c>
-      <c r="J27">
+      <c r="J28">
         <v>6.4</v>
       </c>
-      <c r="K27">
+      <c r="K28">
+        <v>7.8</v>
+      </c>
+      <c r="L28">
+        <v>1.29</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
+        <v>4.8</v>
+      </c>
+      <c r="O28">
+        <v>1.22</v>
+      </c>
+      <c r="P28">
+        <v>2.32</v>
+      </c>
+      <c r="Q28">
+        <v>1.66</v>
+      </c>
+      <c r="R28">
+        <v>1.52</v>
+      </c>
+      <c r="S28">
+        <v>2.58</v>
+      </c>
+      <c r="T28">
+        <v>2.34</v>
+      </c>
+      <c r="U28">
+        <v>1.62</v>
+      </c>
+      <c r="V28">
+        <v>1.05</v>
+      </c>
+      <c r="W28">
+        <v>4.5</v>
+      </c>
+      <c r="X28">
+        <v>28</v>
+      </c>
+      <c r="Y28">
+        <v>55</v>
+      </c>
+      <c r="Z28">
+        <v>210</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>10.5</v>
+      </c>
+      <c r="AC28">
+        <v>17</v>
+      </c>
+      <c r="AD28">
+        <v>75</v>
+      </c>
+      <c r="AE28">
+        <v>420</v>
+      </c>
+      <c r="AF28">
         <v>7.4</v>
       </c>
-      <c r="L27">
+      <c r="AG28">
+        <v>12</v>
+      </c>
+      <c r="AH28">
+        <v>50</v>
+      </c>
+      <c r="AI28">
+        <v>300</v>
+      </c>
+      <c r="AJ28">
+        <v>9</v>
+      </c>
+      <c r="AK28">
+        <v>15.5</v>
+      </c>
+      <c r="AL28">
+        <v>60</v>
+      </c>
+      <c r="AM28">
+        <v>330</v>
+      </c>
+      <c r="AN28">
+        <v>4.7</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>20</v>
+      </c>
+      <c r="AQ28">
+        <v>7.6</v>
+      </c>
+      <c r="AR28">
+        <v>8</v>
+      </c>
+      <c r="AS28">
+        <v>8.4</v>
+      </c>
+      <c r="AT28">
+        <v>7.4</v>
+      </c>
+      <c r="AU28">
+        <v>13.5</v>
+      </c>
+      <c r="AV28">
+        <v>7.4</v>
+      </c>
+      <c r="AW28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX28">
+        <v>6.4</v>
+      </c>
+      <c r="AY28">
+        <v>10</v>
+      </c>
+      <c r="AZ28">
+        <v>7.8</v>
+      </c>
+      <c r="BA28">
+        <v>8</v>
+      </c>
+      <c r="BB28">
+        <v>7.6</v>
+      </c>
+      <c r="BC28">
+        <v>13</v>
+      </c>
+      <c r="BD28">
+        <v>8</v>
+      </c>
+      <c r="BE28">
+        <v>8</v>
+      </c>
+      <c r="BF28">
+        <v>4.1</v>
+      </c>
+      <c r="BG28">
+        <v>8.4</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
         <v>1.3</v>
       </c>
-      <c r="M27">
-        <v>1.04</v>
-      </c>
-      <c r="N27">
-        <v>4.8</v>
-      </c>
-      <c r="O27">
-        <v>1.22</v>
-      </c>
-      <c r="P27">
-        <v>2.32</v>
-      </c>
-      <c r="Q27">
-        <v>1.66</v>
-      </c>
-      <c r="R27">
-        <v>1.52</v>
-      </c>
-      <c r="S27">
-        <v>2.68</v>
-      </c>
-      <c r="T27">
-        <v>2.4</v>
-      </c>
-      <c r="U27">
-        <v>1.64</v>
-      </c>
-      <c r="V27">
-        <v>1.05</v>
-      </c>
-      <c r="W27">
-        <v>4.6</v>
-      </c>
-      <c r="X27">
-        <v>25</v>
-      </c>
-      <c r="Y27">
-        <v>55</v>
-      </c>
-      <c r="Z27">
-        <v>210</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>10.5</v>
-      </c>
-      <c r="AC27">
-        <v>19</v>
-      </c>
-      <c r="AD27">
-        <v>75</v>
-      </c>
-      <c r="AE27">
-        <v>420</v>
-      </c>
-      <c r="AF27">
-        <v>7.4</v>
-      </c>
-      <c r="AG27">
-        <v>12</v>
-      </c>
-      <c r="AH27">
-        <v>55</v>
-      </c>
-      <c r="AI27">
-        <v>300</v>
-      </c>
-      <c r="AJ27">
-        <v>9</v>
-      </c>
-      <c r="AK27">
-        <v>15.5</v>
-      </c>
-      <c r="AL27">
-        <v>60</v>
-      </c>
-      <c r="AM27">
-        <v>330</v>
-      </c>
-      <c r="AN27">
-        <v>4.7</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
-      <c r="AP27">
-        <v>20</v>
-      </c>
-      <c r="AQ27">
-        <v>7.4</v>
-      </c>
-      <c r="AR27">
-        <v>7.8</v>
-      </c>
-      <c r="AS27">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT27">
-        <v>7.4</v>
-      </c>
-      <c r="AU27">
-        <v>13.5</v>
-      </c>
-      <c r="AV27">
-        <v>7.4</v>
-      </c>
-      <c r="AW27">
-        <v>8</v>
-      </c>
-      <c r="AX27">
-        <v>6.4</v>
-      </c>
-      <c r="AY27">
-        <v>10</v>
-      </c>
-      <c r="AZ27">
-        <v>7.2</v>
-      </c>
-      <c r="BA27">
-        <v>8</v>
-      </c>
-      <c r="BB27">
-        <v>7.8</v>
-      </c>
-      <c r="BC27">
-        <v>13</v>
-      </c>
-      <c r="BD27">
-        <v>7.4</v>
-      </c>
-      <c r="BE27">
-        <v>8</v>
-      </c>
-      <c r="BF27">
-        <v>4.3</v>
-      </c>
-      <c r="BG27">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH27">
-        <v>4.9</v>
-      </c>
-      <c r="BI27">
-        <v>3.25</v>
-      </c>
-      <c r="BJ27">
-        <v>17.5</v>
-      </c>
-      <c r="BK27">
-        <v>1.01</v>
-      </c>
-      <c r="BL27">
-        <v>260</v>
-      </c>
-      <c r="BM27">
-        <v>1.01</v>
-      </c>
-      <c r="BN27">
-        <v>3.55</v>
-      </c>
-      <c r="BO27">
-        <v>3.2</v>
-      </c>
-      <c r="BP27">
-        <v>8</v>
-      </c>
-      <c r="BQ27">
-        <v>5.1</v>
-      </c>
-      <c r="BR27">
-        <v>32</v>
-      </c>
-      <c r="BS27">
-        <v>1.01</v>
-      </c>
-      <c r="BT27">
-        <v>22</v>
-      </c>
-      <c r="BU27">
-        <v>1.01</v>
-      </c>
-      <c r="BV27">
-        <v>190</v>
-      </c>
-      <c r="BW27">
-        <v>1.01</v>
-      </c>
-      <c r="BX27">
-        <v>150</v>
-      </c>
-      <c r="BY27">
-        <v>1.01</v>
-      </c>
-      <c r="BZ27">
-        <v>13</v>
-      </c>
-      <c r="CA27">
-        <v>1.01</v>
-      </c>
-      <c r="CB27" t="s">
-        <v>147</v>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.3</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.31</v>
+      </c>
+      <c r="BN28">
+        <v>970</v>
+      </c>
+      <c r="BO28">
+        <v>1.02</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.3</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.31</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.31</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.31</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.31</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.3</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="154">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>2026-09-29</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>22:30:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Jamaica</t>
   </si>
   <si>
@@ -382,6 +388,9 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Union Magdalena</t>
+  </si>
+  <si>
     <t>Honduras</t>
   </si>
   <si>
@@ -463,7 +472,10 @@
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>2026-09-28 05:41:51</t>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
+    <t>2026-09-28 07:53:38</t>
   </si>
 </sst>
 </file>
@@ -795,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1045,25 +1057,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
         <v>3.45</v>
@@ -1087,7 +1099,7 @@
         <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
         <v>2.2</v>
@@ -1102,13 +1114,13 @@
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>12.5</v>
@@ -1123,7 +1135,7 @@
         <v>75</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8</v>
@@ -1135,7 +1147,7 @@
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1159,10 +1171,10 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1174,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
         <v>8</v>
@@ -1186,7 +1198,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1198,88 +1210,88 @@
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
         <v>18</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1287,16 +1299,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>3.25</v>
@@ -1305,13 +1317,13 @@
         <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I3">
         <v>2.22</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1320,16 +1332,16 @@
         <v>1.3</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
         <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
         <v>1.61</v>
@@ -1344,7 +1356,7 @@
         <v>1.57</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
         <v>1.81</v>
@@ -1359,10 +1371,10 @@
         <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AA3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AB3">
         <v>19</v>
@@ -1371,10 +1383,10 @@
         <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF3">
         <v>36</v>
@@ -1386,7 +1398,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
         <v>95</v>
@@ -1404,34 +1416,34 @@
         <v>29</v>
       </c>
       <c r="AO3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP3">
         <v>17.5</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
         <v>20</v>
       </c>
       <c r="AT3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3">
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY3">
         <v>12.5</v>
@@ -1443,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BC3">
         <v>19.5</v>
@@ -1452,10 +1464,10 @@
         <v>32</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG3">
         <v>8.4</v>
@@ -1521,7 +1533,7 @@
         <v>12.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1529,28 +1541,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F4">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J4">
         <v>3.65</v>
@@ -1592,7 +1604,7 @@
         <v>1.64</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X4">
         <v>24</v>
@@ -1607,22 +1619,22 @@
         <v>38</v>
       </c>
       <c r="AB4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC4">
         <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE4">
         <v>28</v>
       </c>
       <c r="AF4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>16</v>
@@ -1634,7 +1646,7 @@
         <v>55</v>
       </c>
       <c r="AK4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL4">
         <v>44</v>
@@ -1643,7 +1655,7 @@
         <v>80</v>
       </c>
       <c r="AN4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4">
         <v>17.5</v>
@@ -1661,22 +1673,22 @@
         <v>28</v>
       </c>
       <c r="AT4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW4">
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
         <v>11</v>
@@ -1688,7 +1700,7 @@
         <v>32</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD4">
         <v>30</v>
@@ -1700,70 +1712,70 @@
         <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1771,34 +1783,34 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
         <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
         <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5">
         <v>1.42</v>
@@ -1831,7 +1843,7 @@
         <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
         <v>1.89</v>
@@ -1885,7 +1897,7 @@
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1924,7 +1936,7 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
         <v>21</v>
@@ -1942,7 +1954,7 @@
         <v>5.9</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2005,7 +2017,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2013,31 +2025,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="K6">
         <v>920</v>
@@ -2052,7 +2064,7 @@
         <v>1.11</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P6">
         <v>1.09</v>
@@ -2073,10 +2085,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2247,7 +2259,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2255,16 +2267,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>1.74</v>
@@ -2276,13 +2288,13 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.51</v>
@@ -2291,16 +2303,16 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
         <v>1.25</v>
@@ -2309,22 +2321,22 @@
         <v>4.6</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
         <v>46</v>
@@ -2333,10 +2345,10 @@
         <v>210</v>
       </c>
       <c r="AB7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>25</v>
@@ -2345,25 +2357,25 @@
         <v>120</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>120</v>
       </c>
       <c r="AJ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK7">
         <v>24</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>200</v>
@@ -2372,31 +2384,31 @@
         <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
         <v>40</v>
       </c>
       <c r="AS7">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AX7">
         <v>8.199999999999999</v>
@@ -2405,49 +2417,49 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BB7">
         <v>14.5</v>
       </c>
       <c r="BC7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD7">
         <v>42</v>
       </c>
       <c r="BE7">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BF7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BH7">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK7">
         <v>10.5</v>
       </c>
       <c r="BL7">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO7">
         <v>3.6</v>
@@ -2462,25 +2474,25 @@
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT7">
         <v>12</v>
       </c>
       <c r="BU7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BW7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BX7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="BZ7">
         <v>36</v>
@@ -2489,7 +2501,7 @@
         <v>21</v>
       </c>
       <c r="CB7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2497,16 +2509,16 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -2515,7 +2527,7 @@
         <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2539,7 +2551,7 @@
         <v>1.57</v>
       </c>
       <c r="P8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8">
         <v>2.7</v>
@@ -2560,10 +2572,10 @@
         <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X8">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y8">
         <v>8.6</v>
@@ -2593,7 +2605,7 @@
         <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8">
         <v>75</v>
@@ -2605,7 +2617,7 @@
         <v>60</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AM8">
         <v>220</v>
@@ -2656,13 +2668,13 @@
         <v>46</v>
       </c>
       <c r="BC8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD8">
         <v>60</v>
       </c>
       <c r="BE8">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF8">
         <v>11.5</v>
@@ -2671,7 +2683,7 @@
         <v>42</v>
       </c>
       <c r="BH8">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="BI8">
         <v>2.46</v>
@@ -2680,7 +2692,7 @@
         <v>13</v>
       </c>
       <c r="BK8">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL8">
         <v>240</v>
@@ -2692,19 +2704,19 @@
         <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BR8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BT8">
         <v>5.7</v>
@@ -2713,25 +2725,25 @@
         <v>5</v>
       </c>
       <c r="BV8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BW8">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BZ8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="CA8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="CB8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2739,19 +2751,19 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G9">
         <v>1.54</v>
@@ -2844,7 +2856,7 @@
         <v>17.5</v>
       </c>
       <c r="AK9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL9">
         <v>36</v>
@@ -2859,7 +2871,7 @@
         <v>85</v>
       </c>
       <c r="AP9">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9">
         <v>20</v>
@@ -2886,13 +2898,13 @@
         <v>9.4</v>
       </c>
       <c r="AY9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
         <v>17.5</v>
       </c>
       <c r="BA9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB9">
         <v>12</v>
@@ -2904,7 +2916,7 @@
         <v>21</v>
       </c>
       <c r="BE9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF9">
         <v>5.5</v>
@@ -2934,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="BO9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
@@ -2973,7 +2985,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2981,16 +2993,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F10">
         <v>1.67</v>
@@ -3002,16 +3014,16 @@
         <v>6.6</v>
       </c>
       <c r="I10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
         <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M10">
         <v>1.1</v>
@@ -3041,7 +3053,7 @@
         <v>1.72</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
         <v>2.46</v>
@@ -3122,7 +3134,7 @@
         <v>24</v>
       </c>
       <c r="AW10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX10">
         <v>7.8</v>
@@ -3143,7 +3155,7 @@
         <v>18</v>
       </c>
       <c r="BD10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE10">
         <v>16.5</v>
@@ -3212,10 +3224,10 @@
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3223,16 +3235,16 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F11">
         <v>3.15</v>
@@ -3241,13 +3253,13 @@
         <v>3.25</v>
       </c>
       <c r="H11">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I11">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
         <v>3.45</v>
@@ -3271,22 +3283,22 @@
         <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
         <v>4</v>
       </c>
       <c r="T11">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V11">
         <v>1.64</v>
       </c>
       <c r="W11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X11">
         <v>12</v>
@@ -3295,19 +3307,19 @@
         <v>9.6</v>
       </c>
       <c r="Z11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA11">
         <v>36</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE11">
         <v>32</v>
@@ -3316,10 +3328,10 @@
         <v>22</v>
       </c>
       <c r="AG11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>55</v>
@@ -3340,7 +3352,7 @@
         <v>44</v>
       </c>
       <c r="AO11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP11">
         <v>10.5</v>
@@ -3349,7 +3361,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS11">
         <v>30</v>
@@ -3358,13 +3370,13 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX11">
         <v>18.5</v>
@@ -3379,7 +3391,7 @@
         <v>40</v>
       </c>
       <c r="BB11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC11">
         <v>34</v>
@@ -3400,10 +3412,10 @@
         <v>3.15</v>
       </c>
       <c r="BI11">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK11">
         <v>8.6</v>
@@ -3418,7 +3430,7 @@
         <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BP11">
         <v>32</v>
@@ -3439,7 +3451,7 @@
         <v>4.7</v>
       </c>
       <c r="BV11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW11">
         <v>16.5</v>
@@ -3454,10 +3466,10 @@
         <v>38</v>
       </c>
       <c r="CA11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CB11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3465,34 +3477,34 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G12">
         <v>1.23</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
         <v>8.199999999999999</v>
-      </c>
-      <c r="K12">
-        <v>8.4</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3513,10 +3525,10 @@
         <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T12">
         <v>2.24</v>
@@ -3546,7 +3558,7 @@
         <v>11</v>
       </c>
       <c r="AC12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD12">
         <v>65</v>
@@ -3561,16 +3573,16 @@
         <v>13</v>
       </c>
       <c r="AH12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI12">
         <v>220</v>
       </c>
       <c r="AJ12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL12">
         <v>42</v>
@@ -3582,7 +3594,7 @@
         <v>3.65</v>
       </c>
       <c r="AO12">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AP12">
         <v>19.5</v>
@@ -3591,22 +3603,22 @@
         <v>36</v>
       </c>
       <c r="AR12">
+        <v>12.5</v>
+      </c>
+      <c r="AS12">
         <v>13</v>
-      </c>
-      <c r="AS12">
-        <v>14</v>
       </c>
       <c r="AT12">
         <v>9.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AV12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX12">
         <v>7.2</v>
@@ -3618,7 +3630,7 @@
         <v>30</v>
       </c>
       <c r="BA12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
         <v>8</v>
@@ -3630,25 +3642,25 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF12">
         <v>3.35</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
         <v>4.6</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ12">
         <v>17</v>
       </c>
       <c r="BK12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BL12">
         <v>210</v>
@@ -3657,10 +3669,10 @@
         <v>21</v>
       </c>
       <c r="BN12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP12">
         <v>6.6</v>
@@ -3669,13 +3681,13 @@
         <v>5.9</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BS12">
         <v>16.5</v>
       </c>
       <c r="BT12">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BU12">
         <v>14</v>
@@ -3699,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3707,22 +3719,22 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F13">
         <v>60</v>
       </c>
       <c r="G13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H13">
         <v>1.06</v>
@@ -3731,10 +3743,10 @@
         <v>1.07</v>
       </c>
       <c r="J13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3752,34 +3764,34 @@
         <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R13">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S13">
         <v>2.04</v>
       </c>
       <c r="T13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y13">
         <v>11.5</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA13">
         <v>6.2</v>
@@ -3788,22 +3800,22 @@
         <v>190</v>
       </c>
       <c r="AC13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AD13">
         <v>23</v>
       </c>
       <c r="AE13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF13">
         <v>1000</v>
       </c>
       <c r="AG13">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="AH13">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AI13">
         <v>170</v>
@@ -3824,25 +3836,25 @@
         <v>1000</v>
       </c>
       <c r="AO13">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="AP13">
         <v>21</v>
       </c>
       <c r="AQ13">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS13">
         <v>5.4</v>
       </c>
       <c r="AT13">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AV13">
         <v>18</v>
@@ -3851,31 +3863,31 @@
         <v>18</v>
       </c>
       <c r="AX13">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="AY13">
-        <v>2.08</v>
+        <v>14</v>
       </c>
       <c r="AZ13">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="BB13">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC13">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD13">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BE13">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BF13">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="BG13">
         <v>2.32</v>
@@ -3917,10 +3929,10 @@
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BU13">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3941,7 +3953,7 @@
         <v>3.9</v>
       </c>
       <c r="CB13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3949,34 +3961,34 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H14">
         <v>1.4</v>
       </c>
       <c r="I14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J14">
+        <v>5.3</v>
+      </c>
+      <c r="K14">
         <v>5.4</v>
-      </c>
-      <c r="K14">
-        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -3985,22 +3997,22 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
         <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T14">
         <v>2.1</v>
@@ -4012,13 +4024,13 @@
         <v>3.4</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>8.199999999999999</v>
@@ -4048,34 +4060,34 @@
         <v>26</v>
       </c>
       <c r="AI14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ14">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AK14">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AL14">
         <v>140</v>
       </c>
       <c r="AM14">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN14">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AO14">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AP14">
         <v>18</v>
       </c>
       <c r="AQ14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS14">
         <v>10.5</v>
@@ -4087,7 +4099,7 @@
         <v>11</v>
       </c>
       <c r="AV14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW14">
         <v>14</v>
@@ -4096,16 +4108,16 @@
         <v>75</v>
       </c>
       <c r="AY14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AZ14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC14">
         <v>120</v>
@@ -4120,7 +4132,7 @@
         <v>140</v>
       </c>
       <c r="BG14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4183,7 +4195,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4191,16 +4203,16 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F15">
         <v>1.3</v>
@@ -4209,10 +4221,10 @@
         <v>1.31</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -4221,7 +4233,7 @@
         <v>6.2</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M15">
         <v>1.06</v>
@@ -4239,7 +4251,7 @@
         <v>1.88</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15">
         <v>3.25</v>
@@ -4251,7 +4263,7 @@
         <v>1.57</v>
       </c>
       <c r="V15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W15">
         <v>4.2</v>
@@ -4299,7 +4311,7 @@
         <v>17</v>
       </c>
       <c r="AL15">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM15">
         <v>380</v>
@@ -4332,7 +4344,7 @@
         <v>44</v>
       </c>
       <c r="AW15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX15">
         <v>6</v>
@@ -4353,13 +4365,13 @@
         <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BE15">
         <v>16.5</v>
       </c>
       <c r="BF15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG15">
         <v>16</v>
@@ -4425,7 +4437,7 @@
         <v>10.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4433,22 +4445,22 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F16">
         <v>1.7</v>
       </c>
       <c r="G16">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H16">
         <v>6.4</v>
@@ -4463,28 +4475,28 @@
         <v>3.85</v>
       </c>
       <c r="L16">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M16">
         <v>1.11</v>
       </c>
       <c r="N16">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O16">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P16">
         <v>1.64</v>
       </c>
       <c r="Q16">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R16">
         <v>1.23</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T16">
         <v>2.38</v>
@@ -4520,7 +4532,7 @@
         <v>29</v>
       </c>
       <c r="AE16">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF16">
         <v>8.6</v>
@@ -4529,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI16">
         <v>160</v>
@@ -4550,22 +4562,22 @@
         <v>16</v>
       </c>
       <c r="AO16">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ16">
         <v>14</v>
       </c>
       <c r="AR16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT16">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU16">
         <v>7.6</v>
@@ -4574,19 +4586,19 @@
         <v>18.5</v>
       </c>
       <c r="AW16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX16">
         <v>7.6</v>
       </c>
       <c r="AY16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16">
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB16">
         <v>14.5</v>
@@ -4598,25 +4610,25 @@
         <v>24</v>
       </c>
       <c r="BE16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF16">
         <v>13.5</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH16">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BL16">
         <v>280</v>
@@ -4625,16 +4637,16 @@
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO16">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BQ16">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR16">
         <v>42</v>
@@ -4643,10 +4655,10 @@
         <v>27</v>
       </c>
       <c r="BT16">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BU16">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BV16">
         <v>90</v>
@@ -4667,7 +4679,7 @@
         <v>23</v>
       </c>
       <c r="CB16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4675,28 +4687,28 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H17">
+        <v>1.97</v>
+      </c>
+      <c r="I17">
         <v>1.99</v>
-      </c>
-      <c r="I17">
-        <v>2.02</v>
       </c>
       <c r="J17">
         <v>3.6</v>
@@ -4726,7 +4738,7 @@
         <v>1.28</v>
       </c>
       <c r="S17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T17">
         <v>2.02</v>
@@ -4735,16 +4747,16 @@
         <v>1.91</v>
       </c>
       <c r="V17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X17">
         <v>11.5</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z17">
         <v>11</v>
@@ -4759,7 +4771,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE17">
         <v>23</v>
@@ -4768,7 +4780,7 @@
         <v>32</v>
       </c>
       <c r="AG17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH17">
         <v>23</v>
@@ -4780,16 +4792,16 @@
         <v>110</v>
       </c>
       <c r="AK17">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL17">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AM17">
         <v>150</v>
       </c>
       <c r="AN17">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AO17">
         <v>17</v>
@@ -4798,13 +4810,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR17">
         <v>10</v>
       </c>
       <c r="AS17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT17">
         <v>12.5</v>
@@ -4819,10 +4831,10 @@
         <v>21</v>
       </c>
       <c r="AX17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ17">
         <v>21</v>
@@ -4831,19 +4843,19 @@
         <v>40</v>
       </c>
       <c r="BB17">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="BC17">
         <v>55</v>
       </c>
       <c r="BD17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE17">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="BF17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG17">
         <v>15.5</v>
@@ -4909,7 +4921,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4917,16 +4929,16 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -4947,7 +4959,7 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M18">
         <v>1.04</v>
@@ -4974,7 +4986,7 @@
         <v>1.59</v>
       </c>
       <c r="U18">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V18">
         <v>1.35</v>
@@ -5022,7 +5034,7 @@
         <v>29</v>
       </c>
       <c r="AK18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL18">
         <v>32</v>
@@ -5043,10 +5055,10 @@
         <v>16.5</v>
       </c>
       <c r="AR18">
+        <v>6.4</v>
+      </c>
+      <c r="AS18">
         <v>6.6</v>
-      </c>
-      <c r="AS18">
-        <v>6.8</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5058,7 +5070,7 @@
         <v>14</v>
       </c>
       <c r="AW18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX18">
         <v>13</v>
@@ -5070,7 +5082,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB18">
         <v>21</v>
@@ -5091,7 +5103,7 @@
         <v>21</v>
       </c>
       <c r="BH18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI18">
         <v>3.4</v>
@@ -5109,7 +5121,7 @@
         <v>1.02</v>
       </c>
       <c r="BN18">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO18">
         <v>4.6</v>
@@ -5118,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR18">
         <v>26</v>
@@ -5127,19 +5139,19 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV18">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY18">
         <v>1.02</v>
@@ -5151,7 +5163,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5159,28 +5171,28 @@
         <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G19">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H19">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="I19">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5201,7 +5213,7 @@
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q19">
         <v>1.74</v>
@@ -5210,7 +5222,7 @@
         <v>1.44</v>
       </c>
       <c r="S19">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T19">
         <v>1.7</v>
@@ -5219,10 +5231,10 @@
         <v>2.18</v>
       </c>
       <c r="V19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X19">
         <v>19.5</v>
@@ -5240,7 +5252,7 @@
         <v>18</v>
       </c>
       <c r="AC19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
         <v>10.5</v>
@@ -5252,7 +5264,7 @@
         <v>34</v>
       </c>
       <c r="AG19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH19">
         <v>18.5</v>
@@ -5273,7 +5285,7 @@
         <v>90</v>
       </c>
       <c r="AN19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO19">
         <v>11.5</v>
@@ -5282,22 +5294,22 @@
         <v>16</v>
       </c>
       <c r="AQ19">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19">
         <v>11</v>
       </c>
       <c r="AS19">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU19">
         <v>8</v>
       </c>
       <c r="AV19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19">
         <v>16</v>
@@ -5324,7 +5336,7 @@
         <v>42</v>
       </c>
       <c r="BE19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF19">
         <v>28</v>
@@ -5375,7 +5387,7 @@
         <v>4.2</v>
       </c>
       <c r="BV19">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BW19">
         <v>9.800000000000001</v>
@@ -5393,7 +5405,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5401,16 +5413,16 @@
         <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F20">
         <v>2.18</v>
@@ -5428,7 +5440,7 @@
         <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>1.23</v>
@@ -5491,7 +5503,7 @@
         <v>36</v>
       </c>
       <c r="AF20">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG20">
         <v>14.5</v>
@@ -5512,31 +5524,31 @@
         <v>34</v>
       </c>
       <c r="AM20">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN20">
         <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AP20">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ20">
         <v>16</v>
       </c>
       <c r="AR20">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS20">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT20">
         <v>13.5</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV20">
         <v>12.5</v>
@@ -5554,19 +5566,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB20">
         <v>21</v>
       </c>
       <c r="BC20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE20">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF20">
         <v>9.6</v>
@@ -5632,10 +5644,10 @@
         <v>18</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5643,19 +5655,19 @@
         <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F21">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G21">
         <v>2.3</v>
@@ -5685,7 +5697,7 @@
         <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q21">
         <v>1.69</v>
@@ -5709,16 +5721,16 @@
         <v>1.76</v>
       </c>
       <c r="X21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y21">
         <v>17</v>
       </c>
       <c r="Z21">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB21">
         <v>13</v>
@@ -5733,16 +5745,16 @@
         <v>44</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG21">
         <v>12</v>
       </c>
       <c r="AH21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI21">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ21">
         <v>32</v>
@@ -5751,7 +5763,7 @@
         <v>23</v>
       </c>
       <c r="AL21">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM21">
         <v>100</v>
@@ -5760,7 +5772,7 @@
         <v>14</v>
       </c>
       <c r="AO21">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AP21">
         <v>16.5</v>
@@ -5769,7 +5781,7 @@
         <v>13.5</v>
       </c>
       <c r="AR21">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AS21">
         <v>34</v>
@@ -5787,7 +5799,7 @@
         <v>27</v>
       </c>
       <c r="AX21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY21">
         <v>9.6</v>
@@ -5802,16 +5814,16 @@
         <v>20</v>
       </c>
       <c r="BC21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD21">
         <v>24</v>
       </c>
       <c r="BE21">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG21">
         <v>18.5</v>
@@ -5835,7 +5847,7 @@
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO21">
         <v>1.01</v>
@@ -5877,7 +5889,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5885,31 +5897,31 @@
         <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F22">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G22">
         <v>2.36</v>
       </c>
       <c r="H22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J22">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K22">
         <v>4.1</v>
@@ -5921,7 +5933,7 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
         <v>1.24</v>
@@ -5933,10 +5945,10 @@
         <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T22">
         <v>1.62</v>
@@ -5951,7 +5963,7 @@
         <v>1.73</v>
       </c>
       <c r="X22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y22">
         <v>16.5</v>
@@ -5978,7 +5990,7 @@
         <v>17</v>
       </c>
       <c r="AG22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH22">
         <v>16.5</v>
@@ -6119,7 +6131,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6127,22 +6139,22 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F23">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G23">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H23">
         <v>4.3</v>
@@ -6151,7 +6163,7 @@
         <v>4.8</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K23">
         <v>4.5</v>
@@ -6169,13 +6181,13 @@
         <v>1.17</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
         <v>1.52</v>
       </c>
       <c r="R23">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="S23">
         <v>2.28</v>
@@ -6184,13 +6196,13 @@
         <v>1.54</v>
       </c>
       <c r="U23">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
         <v>1.26</v>
       </c>
       <c r="W23">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="X23">
         <v>28</v>
@@ -6202,7 +6214,7 @@
         <v>42</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB23">
         <v>14.5</v>
@@ -6238,13 +6250,13 @@
         <v>25</v>
       </c>
       <c r="AM23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN23">
         <v>7.6</v>
       </c>
       <c r="AO23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP23">
         <v>20</v>
@@ -6253,10 +6265,10 @@
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS23">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT23">
         <v>12</v>
@@ -6280,16 +6292,16 @@
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC23">
         <v>14.5</v>
       </c>
       <c r="BD23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE23">
         <v>40</v>
@@ -6298,7 +6310,7 @@
         <v>6.4</v>
       </c>
       <c r="BG23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6361,7 +6373,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6369,37 +6381,37 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F24">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H24">
         <v>3.05</v>
       </c>
       <c r="I24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K24">
         <v>3.9</v>
       </c>
       <c r="L24">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M24">
         <v>1.05</v>
@@ -6414,13 +6426,13 @@
         <v>2.08</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R24">
         <v>1.43</v>
       </c>
       <c r="S24">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T24">
         <v>1.66</v>
@@ -6429,10 +6441,10 @@
         <v>2.28</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X24">
         <v>21</v>
@@ -6441,13 +6453,13 @@
         <v>15</v>
       </c>
       <c r="Z24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA24">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB24">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -6456,25 +6468,25 @@
         <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF24">
         <v>17</v>
       </c>
       <c r="AG24">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI24">
         <v>48</v>
       </c>
       <c r="AJ24">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL24">
         <v>36</v>
@@ -6483,10 +6495,10 @@
         <v>85</v>
       </c>
       <c r="AN24">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO24">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP24">
         <v>14.5</v>
@@ -6495,10 +6507,10 @@
         <v>12.5</v>
       </c>
       <c r="AR24">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS24">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AT24">
         <v>10</v>
@@ -6510,10 +6522,10 @@
         <v>12</v>
       </c>
       <c r="AW24">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY24">
         <v>9.800000000000001</v>
@@ -6522,19 +6534,19 @@
         <v>13.5</v>
       </c>
       <c r="BA24">
-        <v>27</v>
+        <v>5.9</v>
       </c>
       <c r="BB24">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD24">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE24">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BF24">
         <v>13.5</v>
@@ -6603,7 +6615,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6611,16 +6623,16 @@
         <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F25">
         <v>2.48</v>
@@ -6629,16 +6641,16 @@
         <v>2.58</v>
       </c>
       <c r="H25">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I25">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K25">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6653,13 +6665,13 @@
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
         <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S25">
         <v>2.2</v>
@@ -6671,7 +6683,7 @@
         <v>2.84</v>
       </c>
       <c r="V25">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
         <v>1.63</v>
@@ -6755,7 +6767,7 @@
         <v>21</v>
       </c>
       <c r="AX25">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AY25">
         <v>10.5</v>
@@ -6824,7 +6836,7 @@
         <v>8.6</v>
       </c>
       <c r="BU25">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV25">
         <v>23</v>
@@ -6845,7 +6857,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6853,28 +6865,28 @@
         <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H26">
         <v>1.8</v>
       </c>
       <c r="I26">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J26">
         <v>4.2</v>
@@ -6886,7 +6898,7 @@
         <v>1.31</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
         <v>4.8</v>
@@ -6898,7 +6910,7 @@
         <v>2.32</v>
       </c>
       <c r="Q26">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
         <v>1.52</v>
@@ -6916,7 +6928,7 @@
         <v>2.2</v>
       </c>
       <c r="W26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X26">
         <v>22</v>
@@ -6982,7 +6994,7 @@
         <v>11</v>
       </c>
       <c r="AS26">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT26">
         <v>18</v>
@@ -7009,7 +7021,7 @@
         <v>24</v>
       </c>
       <c r="BB26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC26">
         <v>44</v>
@@ -7018,22 +7030,22 @@
         <v>44</v>
       </c>
       <c r="BE26">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="BF26">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG26">
         <v>8</v>
       </c>
       <c r="BH26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI26">
         <v>3.2</v>
       </c>
       <c r="BJ26">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK26">
         <v>5.8</v>
@@ -7045,19 +7057,19 @@
         <v>1.02</v>
       </c>
       <c r="BN26">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO26">
         <v>5.3</v>
       </c>
       <c r="BP26">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BQ26">
         <v>1.02</v>
       </c>
       <c r="BR26">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BS26">
         <v>1.02</v>
@@ -7069,25 +7081,25 @@
         <v>4.1</v>
       </c>
       <c r="BV26">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW26">
         <v>7.4</v>
       </c>
       <c r="BX26">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7095,34 +7107,34 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G27">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J27">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7131,7 +7143,7 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
         <v>1.4</v>
@@ -7140,16 +7152,16 @@
         <v>1.78</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T27">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U27">
         <v>1.94</v>
@@ -7161,10 +7173,10 @@
         <v>1.25</v>
       </c>
       <c r="X27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>13</v>
@@ -7176,7 +7188,7 @@
         <v>16.5</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>12.5</v>
@@ -7191,7 +7203,7 @@
         <v>22</v>
       </c>
       <c r="AH27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI27">
         <v>50</v>
@@ -7212,7 +7224,7 @@
         <v>100</v>
       </c>
       <c r="AO27">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
@@ -7239,31 +7251,31 @@
         <v>18.5</v>
       </c>
       <c r="AX27">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY27">
         <v>16.5</v>
       </c>
       <c r="AZ27">
-        <v>17.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA27">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC27">
         <v>6</v>
       </c>
       <c r="BD27">
+        <v>6</v>
+      </c>
+      <c r="BE27">
         <v>6.2</v>
       </c>
-      <c r="BE27">
-        <v>6</v>
-      </c>
       <c r="BF27">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG27">
         <v>14.5</v>
@@ -7329,7 +7341,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7337,19 +7349,19 @@
         <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F28">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G28">
         <v>1.28</v>
@@ -7361,10 +7373,10 @@
         <v>22</v>
       </c>
       <c r="J28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K28">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L28">
         <v>1.29</v>
@@ -7388,19 +7400,19 @@
         <v>1.52</v>
       </c>
       <c r="S28">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T28">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U28">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V28">
         <v>1.05</v>
       </c>
       <c r="W28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X28">
         <v>28</v>
@@ -7415,10 +7427,10 @@
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD28">
         <v>75</v>
@@ -7451,7 +7463,7 @@
         <v>330</v>
       </c>
       <c r="AN28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO28">
         <v>1000</v>
@@ -7460,13 +7472,13 @@
         <v>20</v>
       </c>
       <c r="AQ28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS28">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT28">
         <v>7.4</v>
@@ -7475,10 +7487,10 @@
         <v>13.5</v>
       </c>
       <c r="AV28">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW28">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX28">
         <v>6.4</v>
@@ -7490,10 +7502,10 @@
         <v>7.8</v>
       </c>
       <c r="BA28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC28">
         <v>13</v>
@@ -7502,31 +7514,31 @@
         <v>8</v>
       </c>
       <c r="BE28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG28">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
         <v>970</v>
@@ -7538,40 +7550,282 @@
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29">
+        <v>2.3</v>
+      </c>
+      <c r="G29">
+        <v>2.66</v>
+      </c>
+      <c r="H29">
+        <v>3.1</v>
+      </c>
+      <c r="I29">
+        <v>3.85</v>
+      </c>
+      <c r="J29">
+        <v>3.05</v>
+      </c>
+      <c r="K29">
+        <v>4.2</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>2.96</v>
+      </c>
+      <c r="O29">
+        <v>1.35</v>
+      </c>
+      <c r="P29">
+        <v>1.64</v>
+      </c>
+      <c r="Q29">
+        <v>2.16</v>
+      </c>
+      <c r="R29">
+        <v>1.2</v>
+      </c>
+      <c r="S29">
+        <v>3.15</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
+        <v>1.35</v>
+      </c>
+      <c r="W29">
+        <v>1.6</v>
+      </c>
+      <c r="X29">
+        <v>1000</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29">
+        <v>1000</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>1000</v>
+      </c>
+      <c r="AG29">
+        <v>1000</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29">
+        <v>1.01</v>
+      </c>
+      <c r="AR29">
+        <v>1.01</v>
+      </c>
+      <c r="AS29">
+        <v>1.01</v>
+      </c>
+      <c r="AT29">
+        <v>1.01</v>
+      </c>
+      <c r="AU29">
+        <v>1.01</v>
+      </c>
+      <c r="AV29">
+        <v>1.01</v>
+      </c>
+      <c r="AW29">
+        <v>1.01</v>
+      </c>
+      <c r="AX29">
+        <v>1.01</v>
+      </c>
+      <c r="AY29">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29">
+        <v>1.01</v>
+      </c>
+      <c r="BA29">
+        <v>1.01</v>
+      </c>
+      <c r="BB29">
+        <v>1.01</v>
+      </c>
+      <c r="BC29">
+        <v>1.01</v>
+      </c>
+      <c r="BD29">
+        <v>1.01</v>
+      </c>
+      <c r="BE29">
+        <v>1.01</v>
+      </c>
+      <c r="BF29">
+        <v>1.01</v>
+      </c>
+      <c r="BG29">
+        <v>1.01</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.01</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.01</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.01</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.01</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.01</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.01</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.01</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.01</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.01</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -487,7 +487,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-28 10:05:42</t>
+    <t>2026-09-28 12:18:17</t>
   </si>
 </sst>
 </file>
@@ -1081,85 +1081,85 @@
         <v>128</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE2">
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1168,10 +1168,10 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK2">
         <v>28</v>
@@ -1183,13 +1183,13 @@
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1198,28 +1198,28 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
         <v>38</v>
@@ -1234,73 +1234,73 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG2">
         <v>30</v>
       </c>
       <c r="BH2">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>157</v>
@@ -1329,16 +1329,16 @@
         <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
         <v>2.18</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.3</v>
@@ -1362,10 +1362,10 @@
         <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
         <v>2.48</v>
@@ -1377,7 +1377,7 @@
         <v>1.4</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y3">
         <v>14</v>
@@ -1404,13 +1404,13 @@
         <v>36</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ3">
         <v>95</v>
@@ -1440,7 +1440,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT3">
         <v>15</v>
@@ -1464,31 +1464,31 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB3">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BC3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="BF3">
         <v>18.5</v>
       </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
         <v>4.8</v>
       </c>
       <c r="BI3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3">
         <v>10</v>
@@ -1515,10 +1515,10 @@
         <v>18.5</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT3">
         <v>6</v>
@@ -1533,13 +1533,13 @@
         <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY3">
         <v>17</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
         <v>12.5</v>
@@ -1565,22 +1565,22 @@
         <v>130</v>
       </c>
       <c r="F4">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
+        <v>2.26</v>
+      </c>
+      <c r="I4">
         <v>2.36</v>
       </c>
-      <c r="I4">
-        <v>2.54</v>
-      </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.33</v>
@@ -1595,28 +1595,28 @@
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
+        <v>1.73</v>
+      </c>
+      <c r="R4">
+        <v>1.49</v>
+      </c>
+      <c r="S4">
+        <v>2.88</v>
+      </c>
+      <c r="T4">
+        <v>1.63</v>
+      </c>
+      <c r="U4">
+        <v>2.34</v>
+      </c>
+      <c r="V4">
         <v>1.72</v>
       </c>
-      <c r="R4">
-        <v>1.5</v>
-      </c>
-      <c r="S4">
-        <v>2.86</v>
-      </c>
-      <c r="T4">
-        <v>1.61</v>
-      </c>
-      <c r="U4">
-        <v>2.38</v>
-      </c>
-      <c r="V4">
-        <v>1.65</v>
-      </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>24</v>
@@ -1625,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="Z4">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AA4">
         <v>40</v>
@@ -1634,7 +1634,7 @@
         <v>17.5</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
         <v>13</v>
@@ -1679,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
         <v>24</v>
@@ -1691,7 +1691,7 @@
         <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>17.5</v>
@@ -1727,16 +1727,16 @@
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>110</v>
@@ -1745,16 +1745,16 @@
         <v>60</v>
       </c>
       <c r="BN4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BR4">
         <v>36</v>
@@ -1763,28 +1763,28 @@
         <v>21</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>157</v>
@@ -1807,7 +1807,7 @@
         <v>131</v>
       </c>
       <c r="F5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
         <v>2.14</v>
@@ -1837,22 +1837,22 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.32</v>
@@ -1867,7 +1867,7 @@
         <v>14.5</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -1888,13 +1888,13 @@
         <v>13</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>27</v>
@@ -1903,7 +1903,7 @@
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM5">
         <v>140</v>
@@ -1918,37 +1918,37 @@
         <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AT5">
         <v>7.6</v>
       </c>
       <c r="AU5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="BB5">
         <v>21</v>
@@ -1960,73 +1960,73 @@
         <v>32</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>80</v>
       </c>
       <c r="BF5">
         <v>14.5</v>
       </c>
       <c r="BG5">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>157</v>
@@ -2049,121 +2049,121 @@
         <v>132</v>
       </c>
       <c r="F6">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H6">
         <v>3.4</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
@@ -2172,43 +2172,43 @@
         <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW6">
         <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE6">
         <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2318,10 +2318,10 @@
         <v>1.11</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q7">
         <v>1.43</v>
@@ -2533,22 +2533,22 @@
         <v>134</v>
       </c>
       <c r="F8">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G8">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H8">
         <v>6.2</v>
       </c>
       <c r="I8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.51</v>
@@ -2560,7 +2560,7 @@
         <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P8">
         <v>1.71</v>
@@ -2575,16 +2575,16 @@
         <v>4.6</v>
       </c>
       <c r="T8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
         <v>1.18</v>
       </c>
       <c r="W8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X8">
         <v>10.5</v>
@@ -2593,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA8">
         <v>210</v>
@@ -2617,13 +2617,13 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI8">
         <v>130</v>
       </c>
       <c r="AJ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -2635,10 +2635,10 @@
         <v>210</v>
       </c>
       <c r="AN8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO8">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP8">
         <v>9.800000000000001</v>
@@ -2662,7 +2662,7 @@
         <v>22</v>
       </c>
       <c r="AW8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX8">
         <v>8</v>
@@ -2674,16 +2674,16 @@
         <v>25</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="BB8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE8">
         <v>48</v>
@@ -2692,13 +2692,13 @@
         <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8">
         <v>14.5</v>
@@ -2713,10 +2713,10 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP8">
         <v>14.5</v>
@@ -2734,7 +2734,7 @@
         <v>11.5</v>
       </c>
       <c r="BU8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV8">
         <v>85</v>
@@ -2749,7 +2749,7 @@
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA8">
         <v>21</v>
@@ -2775,16 +2775,16 @@
         <v>135</v>
       </c>
       <c r="F9">
+        <v>2.96</v>
+      </c>
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="G9">
-        <v>3.05</v>
-      </c>
       <c r="H9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J9">
         <v>3.05</v>
@@ -2796,7 +2796,7 @@
         <v>1.55</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
         <v>2.64</v>
@@ -2805,10 +2805,10 @@
         <v>1.57</v>
       </c>
       <c r="P9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R9">
         <v>1.19</v>
@@ -2817,7 +2817,7 @@
         <v>5.7</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9">
         <v>1.81</v>
@@ -2826,10 +2826,10 @@
         <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y9">
         <v>8.6</v>
@@ -2850,7 +2850,7 @@
         <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2886,7 +2886,7 @@
         <v>7.4</v>
       </c>
       <c r="AQ9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR9">
         <v>15.5</v>
@@ -2904,19 +2904,19 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AX9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB9">
         <v>46</v>
@@ -2928,22 +2928,22 @@
         <v>60</v>
       </c>
       <c r="BE9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BK9">
         <v>7.6</v>
@@ -2955,10 +2955,10 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
         <v>1000</v>
@@ -2973,10 +2973,10 @@
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3032,7 +3032,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3041,7 +3041,7 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
         <v>1.2</v>
@@ -3050,19 +3050,19 @@
         <v>2.46</v>
       </c>
       <c r="Q10">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S10">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
         <v>1.15</v>
@@ -3107,10 +3107,10 @@
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL10">
         <v>36</v>
@@ -3119,7 +3119,7 @@
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO10">
         <v>85</v>
@@ -3131,10 +3131,10 @@
         <v>20</v>
       </c>
       <c r="AR10">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS10">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT10">
         <v>9.6</v>
@@ -3146,7 +3146,7 @@
         <v>18.5</v>
       </c>
       <c r="AW10">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3155,10 +3155,10 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA10">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB10">
         <v>12</v>
@@ -3170,13 +3170,13 @@
         <v>21</v>
       </c>
       <c r="BE10">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10">
         <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3200,10 +3200,10 @@
         <v>6</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
@@ -3224,13 +3224,13 @@
         <v>70</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX10">
         <v>70</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ10">
         <v>19</v>
@@ -3259,19 +3259,19 @@
         <v>137</v>
       </c>
       <c r="F11">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G11">
         <v>1.68</v>
       </c>
       <c r="H11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
         <v>3.95</v>
@@ -3289,7 +3289,7 @@
         <v>1.45</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q11">
         <v>2.34</v>
@@ -3301,22 +3301,22 @@
         <v>4.6</v>
       </c>
       <c r="T11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U11">
         <v>1.73</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W11">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X11">
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z11">
         <v>55</v>
@@ -3325,19 +3325,19 @@
         <v>240</v>
       </c>
       <c r="AB11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE11">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3367,28 +3367,28 @@
         <v>220</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT11">
         <v>6</v>
       </c>
       <c r="AU11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11">
         <v>24</v>
       </c>
       <c r="AW11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AX11">
         <v>7.6</v>
@@ -3400,7 +3400,7 @@
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3412,22 +3412,22 @@
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF11">
         <v>12</v>
       </c>
       <c r="BG11">
+        <v>15.5</v>
+      </c>
+      <c r="BH11">
+        <v>3.2</v>
+      </c>
+      <c r="BI11">
+        <v>2.52</v>
+      </c>
+      <c r="BJ11">
         <v>14.5</v>
-      </c>
-      <c r="BH11">
-        <v>3.25</v>
-      </c>
-      <c r="BI11">
-        <v>2.56</v>
-      </c>
-      <c r="BJ11">
-        <v>14</v>
       </c>
       <c r="BK11">
         <v>8.800000000000001</v>
@@ -3439,13 +3439,13 @@
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
         <v>8.800000000000001</v>
@@ -3478,7 +3478,7 @@
         <v>40</v>
       </c>
       <c r="CA11">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CB11" t="s">
         <v>157</v>
@@ -3501,25 +3501,25 @@
         <v>138</v>
       </c>
       <c r="F12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H12">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I12">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J12">
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3540,7 +3540,7 @@
         <v>1.3</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
         <v>1.89</v>
@@ -3549,19 +3549,19 @@
         <v>2.06</v>
       </c>
       <c r="V12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA12">
         <v>36</v>
@@ -3570,13 +3570,13 @@
         <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF12">
         <v>22</v>
@@ -3585,7 +3585,7 @@
         <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12">
         <v>55</v>
@@ -3606,7 +3606,7 @@
         <v>44</v>
       </c>
       <c r="AO12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP12">
         <v>10.5</v>
@@ -3615,7 +3615,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
         <v>30</v>
@@ -3627,13 +3627,13 @@
         <v>7</v>
       </c>
       <c r="AV12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
         <v>25</v>
       </c>
       <c r="AX12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY12">
         <v>12.5</v>
@@ -3654,7 +3654,7 @@
         <v>46</v>
       </c>
       <c r="BE12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF12">
         <v>34</v>
@@ -3666,16 +3666,16 @@
         <v>3.1</v>
       </c>
       <c r="BI12">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM12">
         <v>21</v>
@@ -3684,13 +3684,13 @@
         <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP12">
         <v>32</v>
       </c>
       <c r="BQ12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR12">
         <v>50</v>
@@ -3699,7 +3699,7 @@
         <v>30</v>
       </c>
       <c r="BT12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU12">
         <v>4.7</v>
@@ -3708,13 +3708,13 @@
         <v>23</v>
       </c>
       <c r="BW12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BX12">
         <v>42</v>
       </c>
       <c r="BY12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BZ12">
         <v>40</v>
@@ -3758,10 +3758,10 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3773,13 +3773,13 @@
         <v>1.17</v>
       </c>
       <c r="P13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q13">
         <v>1.52</v>
       </c>
       <c r="R13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S13">
         <v>2.28</v>
@@ -3788,16 +3788,16 @@
         <v>2.24</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W13">
         <v>5.4</v>
       </c>
       <c r="X13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y13">
         <v>55</v>
@@ -3821,13 +3821,13 @@
         <v>320</v>
       </c>
       <c r="AF13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>13</v>
       </c>
       <c r="AH13">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3839,28 +3839,28 @@
         <v>14</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM13">
         <v>270</v>
       </c>
       <c r="AN13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO13">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="AP13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ13">
         <v>36</v>
       </c>
       <c r="AR13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS13">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT13">
         <v>9.800000000000001</v>
@@ -3869,10 +3869,10 @@
         <v>16</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW13">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3884,7 +3884,7 @@
         <v>30</v>
       </c>
       <c r="BA13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB13">
         <v>8</v>
@@ -3896,13 +3896,13 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF13">
         <v>3.35</v>
       </c>
       <c r="BG13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH13">
         <v>4.6</v>
@@ -3914,7 +3914,7 @@
         <v>16.5</v>
       </c>
       <c r="BK13">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BL13">
         <v>210</v>
@@ -3923,16 +3923,16 @@
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BO13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR13">
         <v>23</v>
@@ -3985,7 +3985,7 @@
         <v>140</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>95</v>
@@ -4000,10 +4000,10 @@
         <v>21</v>
       </c>
       <c r="K14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L14">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.02</v>
@@ -4018,10 +4018,10 @@
         <v>3.25</v>
       </c>
       <c r="Q14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R14">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
         <v>2.04</v>
@@ -4033,7 +4033,7 @@
         <v>1.28</v>
       </c>
       <c r="V14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4042,19 +4042,19 @@
         <v>55</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AB14">
         <v>190</v>
       </c>
       <c r="AC14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AD14">
         <v>24</v>
@@ -4066,10 +4066,10 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AH14">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AI14">
         <v>190</v>
@@ -4090,25 +4090,25 @@
         <v>1000</v>
       </c>
       <c r="AO14">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AP14">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="AQ14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AS14">
         <v>5.4</v>
       </c>
       <c r="AT14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AV14">
         <v>18</v>
@@ -4117,31 +4117,31 @@
         <v>18</v>
       </c>
       <c r="AX14">
+        <v>14.5</v>
+      </c>
+      <c r="AY14">
+        <v>14</v>
+      </c>
+      <c r="AZ14">
         <v>13.5</v>
       </c>
-      <c r="AY14">
-        <v>13</v>
-      </c>
-      <c r="AZ14">
-        <v>12.5</v>
-      </c>
       <c r="BA14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE14">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BF14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG14">
         <v>2.32</v>
@@ -4183,10 +4183,10 @@
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BU14">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BV14">
         <v>1000</v>
@@ -4227,22 +4227,22 @@
         <v>141</v>
       </c>
       <c r="F15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="I15">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="J15">
         <v>5.4</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
         <v>1.3</v>
@@ -4263,25 +4263,25 @@
         <v>1.72</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
         <v>2.1</v>
       </c>
       <c r="U15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -4290,7 +4290,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AA15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB15">
         <v>32</v>
@@ -4308,34 +4308,34 @@
         <v>95</v>
       </c>
       <c r="AG15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH15">
         <v>26</v>
       </c>
       <c r="AI15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ15">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AK15">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AL15">
         <v>140</v>
       </c>
       <c r="AM15">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN15">
         <v>240</v>
       </c>
       <c r="AO15">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AP15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ15">
         <v>8.6</v>
@@ -4344,7 +4344,7 @@
         <v>7.8</v>
       </c>
       <c r="AS15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT15">
         <v>28</v>
@@ -4356,7 +4356,7 @@
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX15">
         <v>75</v>
@@ -4368,10 +4368,10 @@
         <v>25</v>
       </c>
       <c r="BA15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC15">
         <v>120</v>
@@ -4386,67 +4386,67 @@
         <v>140</v>
       </c>
       <c r="BG15">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>8.4</v>
+        <v>2.22</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.15</v>
+        <v>1.47</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>6</v>
+        <v>1.87</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="CB15" t="s">
         <v>157</v>
@@ -4493,7 +4493,7 @@
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
         <v>1.3</v>
@@ -4508,7 +4508,7 @@
         <v>1.41</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
         <v>2.64</v>
@@ -4547,7 +4547,7 @@
         <v>400</v>
       </c>
       <c r="AF16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG16">
         <v>12</v>
@@ -4571,22 +4571,22 @@
         <v>380</v>
       </c>
       <c r="AN16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO16">
         <v>660</v>
       </c>
       <c r="AP16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
         <v>32</v>
       </c>
       <c r="AR16">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS16">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT16">
         <v>6.6</v>
@@ -4598,7 +4598,7 @@
         <v>44</v>
       </c>
       <c r="AW16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX16">
         <v>6</v>
@@ -4610,7 +4610,7 @@
         <v>38</v>
       </c>
       <c r="BA16">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BB16">
         <v>8.4</v>
@@ -4622,22 +4622,22 @@
         <v>46</v>
       </c>
       <c r="BE16">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BF16">
         <v>5.4</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BH16">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BI16">
         <v>3.3</v>
       </c>
       <c r="BJ16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BK16">
         <v>13</v>
@@ -4667,13 +4667,13 @@
         <v>23</v>
       </c>
       <c r="BT16">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BU16">
         <v>9.4</v>
       </c>
       <c r="BV16">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="BW16">
         <v>21</v>
@@ -4685,7 +4685,7 @@
         <v>21</v>
       </c>
       <c r="BZ16">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA16">
         <v>10.5</v>
@@ -4711,19 +4711,19 @@
         <v>143</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G17">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H17">
         <v>6.4</v>
       </c>
       <c r="I17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
         <v>3.8</v>
@@ -4735,16 +4735,16 @@
         <v>1.11</v>
       </c>
       <c r="N17">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O17">
         <v>1.48</v>
       </c>
       <c r="P17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R17">
         <v>1.23</v>
@@ -4753,25 +4753,25 @@
         <v>4.9</v>
       </c>
       <c r="T17">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W17">
         <v>2.34</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA17">
         <v>290</v>
@@ -4783,7 +4783,7 @@
         <v>8.6</v>
       </c>
       <c r="AD17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE17">
         <v>160</v>
@@ -4795,7 +4795,7 @@
         <v>11</v>
       </c>
       <c r="AH17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI17">
         <v>160</v>
@@ -4813,28 +4813,28 @@
         <v>260</v>
       </c>
       <c r="AN17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO17">
         <v>290</v>
       </c>
       <c r="AP17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17">
         <v>14</v>
       </c>
       <c r="AR17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS17">
         <v>13</v>
       </c>
       <c r="AT17">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV17">
         <v>18.5</v>
@@ -4861,7 +4861,7 @@
         <v>18.5</v>
       </c>
       <c r="BD17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE17">
         <v>13</v>
@@ -4873,25 +4873,25 @@
         <v>13</v>
       </c>
       <c r="BH17">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BI17">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK17">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL17">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="BM17">
         <v>21</v>
       </c>
       <c r="BN17">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO17">
         <v>3.55</v>
@@ -4900,10 +4900,10 @@
         <v>12.5</v>
       </c>
       <c r="BQ17">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS17">
         <v>27</v>
@@ -4912,7 +4912,7 @@
         <v>10.5</v>
       </c>
       <c r="BU17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV17">
         <v>90</v>
@@ -4927,10 +4927,10 @@
         <v>21</v>
       </c>
       <c r="BZ17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4953,16 +4953,16 @@
         <v>144</v>
       </c>
       <c r="F18">
+        <v>4.6</v>
+      </c>
+      <c r="G18">
         <v>4.7</v>
       </c>
-      <c r="G18">
-        <v>4.8</v>
-      </c>
       <c r="H18">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I18">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J18">
         <v>3.65</v>
@@ -4971,7 +4971,7 @@
         <v>3.7</v>
       </c>
       <c r="L18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M18">
         <v>1.09</v>
@@ -4980,10 +4980,10 @@
         <v>3.25</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q18">
         <v>2.26</v>
@@ -4998,13 +4998,13 @@
         <v>2.04</v>
       </c>
       <c r="U18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V18">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X18">
         <v>11.5</v>
@@ -5031,10 +5031,10 @@
         <v>23</v>
       </c>
       <c r="AF18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH18">
         <v>24</v>
@@ -5043,7 +5043,7 @@
         <v>46</v>
       </c>
       <c r="AJ18">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AK18">
         <v>75</v>
@@ -5064,13 +5064,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR18">
         <v>10</v>
       </c>
       <c r="AS18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT18">
         <v>12.5</v>
@@ -5097,10 +5097,10 @@
         <v>40</v>
       </c>
       <c r="BB18">
-        <v>100</v>
+        <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BD18">
         <v>70</v>
@@ -5118,7 +5118,7 @@
         <v>3.3</v>
       </c>
       <c r="BI18">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
@@ -5136,7 +5136,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5151,16 +5151,16 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX18">
         <v>1000</v>
@@ -5195,58 +5195,58 @@
         <v>145</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G19">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I19">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O19">
         <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T19">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X19">
         <v>26</v>
@@ -5288,7 +5288,7 @@
         <v>29</v>
       </c>
       <c r="AK19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19">
         <v>32</v>
@@ -5303,115 +5303,115 @@
         <v>32</v>
       </c>
       <c r="AP19">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="AQ19">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS19">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT19">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AU19">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AV19">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="AW19">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX19">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="AY19">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB19">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BC19">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD19">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BE19">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF19">
+        <v>9</v>
+      </c>
+      <c r="BG19">
+        <v>21</v>
+      </c>
+      <c r="BH19">
         <v>4.3</v>
       </c>
-      <c r="BG19">
-        <v>5.9</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK19">
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM19">
         <v>1.02</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
@@ -5440,19 +5440,19 @@
         <v>4.1</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H20">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I20">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>1.32</v>
@@ -5467,28 +5467,28 @@
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q20">
         <v>1.74</v>
       </c>
       <c r="R20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T20">
         <v>1.7</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>2.08</v>
       </c>
       <c r="W20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X20">
         <v>19.5</v>
@@ -5497,7 +5497,7 @@
         <v>11</v>
       </c>
       <c r="Z20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA20">
         <v>23</v>
@@ -5506,7 +5506,7 @@
         <v>18</v>
       </c>
       <c r="AC20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20">
         <v>10.5</v>
@@ -5527,7 +5527,7 @@
         <v>32</v>
       </c>
       <c r="AJ20">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AK20">
         <v>50</v>
@@ -5536,7 +5536,7 @@
         <v>55</v>
       </c>
       <c r="AM20">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN20">
         <v>55</v>
@@ -5545,13 +5545,13 @@
         <v>11.5</v>
       </c>
       <c r="AP20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ20">
         <v>9.199999999999999</v>
       </c>
       <c r="AR20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS20">
         <v>19</v>
@@ -5560,10 +5560,10 @@
         <v>15.5</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW20">
         <v>16</v>
@@ -5581,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="BB20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC20">
         <v>40</v>
       </c>
       <c r="BD20">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BE20">
         <v>11</v>
@@ -5596,7 +5596,7 @@
         <v>30</v>
       </c>
       <c r="BG20">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20">
         <v>4.3</v>
@@ -5641,19 +5641,19 @@
         <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW20">
         <v>9.800000000000001</v>
       </c>
       <c r="BX20">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BY20">
         <v>1.02</v>
       </c>
       <c r="BZ20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5679,10 +5679,10 @@
         <v>147</v>
       </c>
       <c r="F21">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G21">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -5691,16 +5691,16 @@
         <v>3.25</v>
       </c>
       <c r="J21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>4.4</v>
       </c>
       <c r="L21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
         <v>5.7</v>
@@ -5709,7 +5709,7 @@
         <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q21">
         <v>1.56</v>
@@ -5724,13 +5724,13 @@
         <v>1.53</v>
       </c>
       <c r="U21">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X21">
         <v>32</v>
@@ -5757,7 +5757,7 @@
         <v>36</v>
       </c>
       <c r="AF21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21">
         <v>14.5</v>
@@ -5772,7 +5772,7 @@
         <v>36</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21">
         <v>34</v>
@@ -5796,13 +5796,13 @@
         <v>21</v>
       </c>
       <c r="AS21">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT21">
         <v>13.5</v>
       </c>
       <c r="AU21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21">
         <v>12.5</v>
@@ -5820,19 +5820,19 @@
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB21">
         <v>21</v>
       </c>
       <c r="BC21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD21">
         <v>19.5</v>
       </c>
       <c r="BE21">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BF21">
         <v>9.6</v>
@@ -5921,7 +5921,7 @@
         <v>148</v>
       </c>
       <c r="F22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G22">
         <v>2.32</v>
@@ -5939,7 +5939,7 @@
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -5954,7 +5954,7 @@
         <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R22">
         <v>1.48</v>
@@ -5963,16 +5963,16 @@
         <v>2.74</v>
       </c>
       <c r="T22">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U22">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
         <v>1.39</v>
       </c>
       <c r="W22">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X22">
         <v>24</v>
@@ -5981,7 +5981,7 @@
         <v>17</v>
       </c>
       <c r="Z22">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA22">
         <v>80</v>
@@ -6005,13 +6005,13 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI22">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK22">
         <v>23</v>
@@ -6026,61 +6026,61 @@
         <v>13.5</v>
       </c>
       <c r="AO22">
+        <v>29</v>
+      </c>
+      <c r="AP22">
+        <v>16.5</v>
+      </c>
+      <c r="AQ22">
+        <v>13.5</v>
+      </c>
+      <c r="AR22">
+        <v>19</v>
+      </c>
+      <c r="AS22">
         <v>36</v>
       </c>
-      <c r="AP22">
-        <v>6.2</v>
-      </c>
-      <c r="AQ22">
-        <v>5.6</v>
-      </c>
-      <c r="AR22">
-        <v>6</v>
-      </c>
-      <c r="AS22">
-        <v>7</v>
-      </c>
       <c r="AT22">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AU22">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV22">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW22">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="AX22">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AY22">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA22">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BB22">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BC22">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="BD22">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BE22">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF22">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BG22">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6113,7 +6113,7 @@
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
@@ -6122,7 +6122,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU22">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV22">
         <v>38</v>
@@ -6131,7 +6131,7 @@
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BY22">
         <v>1.02</v>
@@ -6163,22 +6163,22 @@
         <v>149</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G23">
         <v>2.36</v>
       </c>
       <c r="H23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J23">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.29</v>
@@ -6187,13 +6187,13 @@
         <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O23">
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q23">
         <v>1.7</v>
@@ -6202,13 +6202,13 @@
         <v>1.48</v>
       </c>
       <c r="S23">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V23">
         <v>1.4</v>
@@ -6259,70 +6259,70 @@
         <v>27</v>
       </c>
       <c r="AL23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM23">
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO23">
         <v>34</v>
       </c>
       <c r="AP23">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AQ23">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AR23">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AS23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT23">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AU23">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW23">
         <v>5.1</v>
       </c>
       <c r="AX23">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AY23">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ23">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA23">
+        <v>32</v>
+      </c>
+      <c r="BB23">
+        <v>20</v>
+      </c>
+      <c r="BC23">
+        <v>18.5</v>
+      </c>
+      <c r="BD23">
         <v>5.1</v>
       </c>
-      <c r="BB23">
-        <v>5</v>
-      </c>
-      <c r="BC23">
-        <v>4.8</v>
-      </c>
-      <c r="BD23">
-        <v>5</v>
-      </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF23">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG23">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BH23">
         <v>4.6</v>
@@ -6405,19 +6405,19 @@
         <v>150</v>
       </c>
       <c r="F24">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G24">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H24">
         <v>4.3</v>
       </c>
       <c r="I24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J24">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>4.5</v>
@@ -6438,25 +6438,25 @@
         <v>2.62</v>
       </c>
       <c r="Q24">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S24">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
         <v>1.54</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W24">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X24">
         <v>28</v>
@@ -6507,64 +6507,64 @@
         <v>55</v>
       </c>
       <c r="AN24">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO24">
         <v>32</v>
       </c>
       <c r="AP24">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AR24">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT24">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AU24">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AV24">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AW24">
+        <v>32</v>
+      </c>
+      <c r="AX24">
+        <v>12.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24">
+        <v>13</v>
+      </c>
+      <c r="BA24">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX24">
+      <c r="BB24">
+        <v>18</v>
+      </c>
+      <c r="BC24">
+        <v>14.5</v>
+      </c>
+      <c r="BD24">
+        <v>18.5</v>
+      </c>
+      <c r="BE24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF24">
         <v>6.4</v>
       </c>
-      <c r="AY24">
-        <v>5.4</v>
-      </c>
-      <c r="AZ24">
-        <v>6.4</v>
-      </c>
-      <c r="BA24">
-        <v>8.6</v>
-      </c>
-      <c r="BB24">
-        <v>7.2</v>
-      </c>
-      <c r="BC24">
-        <v>6.6</v>
-      </c>
-      <c r="BD24">
-        <v>7.4</v>
-      </c>
-      <c r="BE24">
-        <v>9</v>
-      </c>
-      <c r="BF24">
-        <v>4.4</v>
-      </c>
       <c r="BG24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6647,25 +6647,25 @@
         <v>151</v>
       </c>
       <c r="F25">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G25">
         <v>2.46</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -6677,19 +6677,19 @@
         <v>1.27</v>
       </c>
       <c r="P25">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R25">
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T25">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U25">
         <v>2.28</v>
@@ -6698,13 +6698,13 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X25">
         <v>21</v>
       </c>
       <c r="Y25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z25">
         <v>28</v>
@@ -6713,19 +6713,19 @@
         <v>65</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC25">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD25">
         <v>14.5</v>
       </c>
       <c r="AE25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG25">
         <v>12</v>
@@ -6740,7 +6740,7 @@
         <v>36</v>
       </c>
       <c r="AK25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL25">
         <v>36</v>
@@ -6749,64 +6749,64 @@
         <v>90</v>
       </c>
       <c r="AN25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO25">
         <v>30</v>
       </c>
       <c r="AP25">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AR25">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="AS25">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="AT25">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AU25">
         <v>7.4</v>
       </c>
       <c r="AV25">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="AW25">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX25">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA25">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BB25">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC25">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BD25">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE25">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF25">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG25">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BH25">
         <v>4.2</v>
@@ -6892,7 +6892,7 @@
         <v>2.5</v>
       </c>
       <c r="G26">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H26">
         <v>2.6</v>
@@ -6901,7 +6901,7 @@
         <v>2.7</v>
       </c>
       <c r="J26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K26">
         <v>4.6</v>
@@ -6931,7 +6931,7 @@
         <v>2.2</v>
       </c>
       <c r="T26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U26">
         <v>2.86</v>
@@ -6940,7 +6940,7 @@
         <v>1.58</v>
       </c>
       <c r="W26">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X26">
         <v>36</v>
@@ -6991,22 +6991,22 @@
         <v>50</v>
       </c>
       <c r="AN26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO26">
         <v>12.5</v>
       </c>
       <c r="AP26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ26">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR26">
         <v>19.5</v>
       </c>
       <c r="AS26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT26">
         <v>16</v>
@@ -7015,13 +7015,13 @@
         <v>9.6</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW26">
         <v>20</v>
       </c>
       <c r="AX26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY26">
         <v>11</v>
@@ -7030,19 +7030,19 @@
         <v>13</v>
       </c>
       <c r="BA26">
+        <v>8</v>
+      </c>
+      <c r="BB26">
+        <v>8.4</v>
+      </c>
+      <c r="BC26">
+        <v>19.5</v>
+      </c>
+      <c r="BD26">
         <v>7.8</v>
       </c>
-      <c r="BB26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC26">
-        <v>19</v>
-      </c>
-      <c r="BD26">
-        <v>7.6</v>
-      </c>
       <c r="BE26">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF26">
         <v>10</v>
@@ -7105,7 +7105,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
@@ -7185,7 +7185,7 @@
         <v>1.26</v>
       </c>
       <c r="X27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y27">
         <v>11.5</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27">
         <v>10.5</v>
@@ -7239,16 +7239,16 @@
         <v>9</v>
       </c>
       <c r="AP27">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ27">
         <v>10</v>
       </c>
       <c r="AR27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS27">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AT27">
         <v>18</v>
@@ -7257,7 +7257,7 @@
         <v>9</v>
       </c>
       <c r="AV27">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW27">
         <v>15</v>
@@ -7275,16 +7275,16 @@
         <v>24</v>
       </c>
       <c r="BB27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC27">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BD27">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BE27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF27">
         <v>30</v>
@@ -7296,10 +7296,10 @@
         <v>4.8</v>
       </c>
       <c r="BI27">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ27">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK27">
         <v>5.8</v>
@@ -7308,7 +7308,7 @@
         <v>120</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN27">
         <v>9.800000000000001</v>
@@ -7373,7 +7373,7 @@
         <v>154</v>
       </c>
       <c r="F28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -7385,7 +7385,7 @@
         <v>1.99</v>
       </c>
       <c r="J28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
         <v>3.75</v>
@@ -7397,16 +7397,16 @@
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q28">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R28">
         <v>1.3</v>
@@ -7415,7 +7415,7 @@
         <v>4</v>
       </c>
       <c r="T28">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U28">
         <v>1.94</v>
@@ -7457,7 +7457,7 @@
         <v>22</v>
       </c>
       <c r="AH28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI28">
         <v>50</v>
@@ -7478,7 +7478,7 @@
         <v>110</v>
       </c>
       <c r="AO28">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP28">
         <v>10.5</v>
@@ -7505,7 +7505,7 @@
         <v>17</v>
       </c>
       <c r="AX28">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY28">
         <v>16.5</v>
@@ -7514,22 +7514,22 @@
         <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BB28">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC28">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD28">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF28">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG28">
         <v>14</v>
@@ -7618,19 +7618,19 @@
         <v>1.24</v>
       </c>
       <c r="G29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H29">
         <v>15.5</v>
       </c>
       <c r="I29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K29">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L29">
         <v>1.31</v>
@@ -7657,16 +7657,16 @@
         <v>2.66</v>
       </c>
       <c r="T29">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="U29">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V29">
         <v>1.05</v>
       </c>
       <c r="W29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X29">
         <v>28</v>
@@ -7684,7 +7684,7 @@
         <v>10.5</v>
       </c>
       <c r="AC29">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AD29">
         <v>170</v>
@@ -7717,7 +7717,7 @@
         <v>330</v>
       </c>
       <c r="AN29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO29">
         <v>1000</v>
@@ -7726,13 +7726,13 @@
         <v>20</v>
       </c>
       <c r="AQ29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AR29">
         <v>36</v>
       </c>
       <c r="AS29">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7741,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="AV29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW29">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AX29">
         <v>6.4</v>
@@ -7753,10 +7753,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BA29">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BB29">
         <v>7.8</v>
@@ -7765,16 +7765,16 @@
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BE29">
         <v>36</v>
       </c>
       <c r="BF29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG29">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH29">
         <v>970</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -487,7 +487,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-28 12:18:17</t>
+    <t>2026-09-28 14:30:34</t>
   </si>
 </sst>
 </file>
@@ -1081,22 +1081,22 @@
         <v>128</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1105,13 +1105,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
         <v>2.24</v>
@@ -1132,7 +1132,7 @@
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>12</v>
@@ -1147,7 +1147,7 @@
         <v>85</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1168,10 +1168,10 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>28</v>
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
@@ -1201,7 +1201,7 @@
         <v>50</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1210,7 +1210,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1219,88 +1219,88 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BB2">
         <v>24</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF2">
         <v>20</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="CB2" t="s">
         <v>157</v>
@@ -1323,76 +1323,76 @@
         <v>129</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="I3">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.3</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
         <v>5.3</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
         <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V3">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3">
         <v>32</v>
       </c>
       <c r="AB3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>12</v>
@@ -1401,13 +1401,13 @@
         <v>22</v>
       </c>
       <c r="AF3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>32</v>
@@ -1416,7 +1416,7 @@
         <v>95</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1425,10 +1425,10 @@
         <v>85</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AP3">
         <v>19</v>
@@ -1440,10 +1440,10 @@
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU3">
         <v>8.4</v>
@@ -1455,43 +1455,43 @@
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB3">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BC3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BF3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
         <v>3.5</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
         <v>6.8</v>
@@ -1503,13 +1503,13 @@
         <v>55</v>
       </c>
       <c r="BN3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
         <v>5.6</v>
       </c>
       <c r="BP3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
         <v>18.5</v>
@@ -1524,7 +1524,7 @@
         <v>6</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
         <v>16</v>
@@ -1568,13 +1568,13 @@
         <v>3.2</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J4">
         <v>3.7</v>
@@ -1583,7 +1583,7 @@
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1595,52 +1595,52 @@
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
         <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
         <v>1.63</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB4">
         <v>17.5</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF4">
         <v>26</v>
@@ -1652,7 +1652,7 @@
         <v>19</v>
       </c>
       <c r="AI4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
         <v>55</v>
@@ -1664,25 +1664,25 @@
         <v>44</v>
       </c>
       <c r="AM4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4">
         <v>13</v>
@@ -1694,49 +1694,49 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="BB4">
-        <v>32</v>
+        <v>5.6</v>
       </c>
       <c r="BC4">
-        <v>22</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>5.5</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>5.8</v>
       </c>
       <c r="BF4">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BG4">
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>110</v>
@@ -1745,31 +1745,31 @@
         <v>60</v>
       </c>
       <c r="BN4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BQ4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW4">
         <v>11.5</v>
@@ -1781,10 +1781,10 @@
         <v>18.5</v>
       </c>
       <c r="BZ4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="s">
         <v>157</v>
@@ -1807,13 +1807,13 @@
         <v>131</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
         <v>2.14</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I5">
         <v>4.1</v>
@@ -1825,7 +1825,7 @@
         <v>3.7</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1834,10 +1834,10 @@
         <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1849,10 +1849,10 @@
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>1.32</v>
@@ -1864,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="Y5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z5">
         <v>30</v>
@@ -1873,13 +1873,13 @@
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE5">
         <v>65</v>
@@ -1909,10 +1909,10 @@
         <v>140</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>11.5</v>
@@ -1927,7 +1927,7 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
@@ -1942,10 +1942,10 @@
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
         <v>40</v>
@@ -1969,64 +1969,64 @@
         <v>34</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB5" t="s">
         <v>157</v>
@@ -2061,10 +2061,10 @@
         <v>3.8</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2079,19 +2079,19 @@
         <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U6">
         <v>2.12</v>
@@ -2103,7 +2103,7 @@
         <v>1.74</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>16.5</v>
@@ -2115,7 +2115,7 @@
         <v>80</v>
       </c>
       <c r="AB6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
@@ -2142,7 +2142,7 @@
         <v>30</v>
       </c>
       <c r="AK6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6">
         <v>40</v>
@@ -2157,7 +2157,7 @@
         <v>48</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
         <v>12</v>
@@ -2169,7 +2169,7 @@
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU6">
         <v>7.2</v>
@@ -2291,19 +2291,19 @@
         <v>133</v>
       </c>
       <c r="F7">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="I7">
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="K7">
         <v>920</v>
@@ -2321,7 +2321,7 @@
         <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q7">
         <v>1.43</v>
@@ -2339,10 +2339,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2533,154 +2533,154 @@
         <v>134</v>
       </c>
       <c r="F8">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="G8">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T8">
         <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X8">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA8">
         <v>210</v>
       </c>
       <c r="AB8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
         <v>28</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AN8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AS8">
         <v>46</v>
       </c>
       <c r="AT8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW8">
         <v>40</v>
       </c>
       <c r="AX8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY8">
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="BB8">
         <v>14.5</v>
       </c>
       <c r="BC8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD8">
         <v>44</v>
@@ -2689,61 +2689,61 @@
         <v>48</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
         <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK8">
         <v>10.5</v>
       </c>
       <c r="BL8">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="BM8">
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS8">
         <v>24</v>
       </c>
       <c r="BT8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV8">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BW8">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="BX8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BY8">
         <v>21</v>
@@ -2752,7 +2752,7 @@
         <v>34</v>
       </c>
       <c r="CA8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CB8" t="s">
         <v>157</v>
@@ -2775,25 +2775,25 @@
         <v>135</v>
       </c>
       <c r="F9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G9">
+        <v>3.1</v>
+      </c>
+      <c r="H9">
+        <v>2.92</v>
+      </c>
+      <c r="I9">
+        <v>2.94</v>
+      </c>
+      <c r="J9">
         <v>3</v>
       </c>
-      <c r="H9">
-        <v>2.94</v>
-      </c>
-      <c r="I9">
-        <v>2.96</v>
-      </c>
-      <c r="J9">
+      <c r="K9">
         <v>3.05</v>
       </c>
-      <c r="K9">
-        <v>3.1</v>
-      </c>
       <c r="L9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
         <v>1.13</v>
@@ -2802,10 +2802,10 @@
         <v>2.64</v>
       </c>
       <c r="O9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
         <v>2.68</v>
@@ -2817,7 +2817,7 @@
         <v>5.7</v>
       </c>
       <c r="T9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
         <v>1.81</v>
@@ -2826,10 +2826,10 @@
         <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y9">
         <v>8.6</v>
@@ -2850,7 +2850,7 @@
         <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2865,7 +2865,7 @@
         <v>75</v>
       </c>
       <c r="AJ9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK9">
         <v>46</v>
@@ -2874,7 +2874,7 @@
         <v>120</v>
       </c>
       <c r="AM9">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN9">
         <v>60</v>
@@ -2889,13 +2889,13 @@
         <v>8</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS9">
         <v>42</v>
       </c>
       <c r="AT9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
@@ -2904,7 +2904,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
@@ -2928,13 +2928,13 @@
         <v>60</v>
       </c>
       <c r="BE9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH9">
         <v>2.84</v>
@@ -3023,7 +3023,7 @@
         <v>1.54</v>
       </c>
       <c r="H10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I10">
         <v>7.4</v>
@@ -3032,7 +3032,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3056,13 +3056,13 @@
         <v>1.59</v>
       </c>
       <c r="S10">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T10">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.15</v>
@@ -3143,7 +3143,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW10">
         <v>8</v>
@@ -3155,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA10">
         <v>7.8</v>
@@ -3176,7 +3176,7 @@
         <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3200,10 +3200,10 @@
         <v>6</v>
       </c>
       <c r="BO10">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
@@ -3259,22 +3259,22 @@
         <v>137</v>
       </c>
       <c r="F11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G11">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>1.48</v>
@@ -3304,7 +3304,7 @@
         <v>2.28</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
         <v>1.15</v>
@@ -3316,13 +3316,13 @@
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA11">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AB11">
         <v>6.4</v>
@@ -3331,10 +3331,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF11">
         <v>8.4</v>
@@ -3343,7 +3343,7 @@
         <v>11</v>
       </c>
       <c r="AH11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI11">
         <v>150</v>
@@ -3370,13 +3370,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR11">
         <v>48</v>
       </c>
       <c r="AS11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3385,10 +3385,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX11">
         <v>7.6</v>
@@ -3400,7 +3400,7 @@
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3418,7 +3418,7 @@
         <v>12</v>
       </c>
       <c r="BG11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH11">
         <v>3.2</v>
@@ -3516,10 +3516,10 @@
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3540,13 +3540,13 @@
         <v>1.3</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>1.89</v>
       </c>
       <c r="U12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
         <v>1.64</v>
@@ -3570,10 +3570,10 @@
         <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE12">
         <v>32</v>
@@ -3585,7 +3585,7 @@
         <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
         <v>55</v>
@@ -3594,10 +3594,10 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM12">
         <v>120</v>
@@ -3606,7 +3606,7 @@
         <v>44</v>
       </c>
       <c r="AO12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP12">
         <v>10.5</v>
@@ -3615,7 +3615,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS12">
         <v>30</v>
@@ -3627,7 +3627,7 @@
         <v>7</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW12">
         <v>25</v>
@@ -3654,7 +3654,7 @@
         <v>46</v>
       </c>
       <c r="BE12">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BF12">
         <v>34</v>
@@ -3684,7 +3684,7 @@
         <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP12">
         <v>32</v>
@@ -3693,7 +3693,7 @@
         <v>21</v>
       </c>
       <c r="BR12">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BS12">
         <v>30</v>
@@ -3705,19 +3705,19 @@
         <v>4.7</v>
       </c>
       <c r="BV12">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BW12">
         <v>16.5</v>
       </c>
       <c r="BX12">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BY12">
         <v>26</v>
       </c>
       <c r="BZ12">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA12">
         <v>25</v>
@@ -3752,16 +3752,16 @@
         <v>17</v>
       </c>
       <c r="I13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3776,19 +3776,19 @@
         <v>2.84</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S13">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T13">
         <v>2.24</v>
       </c>
       <c r="U13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V13">
         <v>1.06</v>
@@ -3803,7 +3803,7 @@
         <v>55</v>
       </c>
       <c r="Z13">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA13">
         <v>1000</v>
@@ -3815,7 +3815,7 @@
         <v>18.5</v>
       </c>
       <c r="AD13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE13">
         <v>320</v>
@@ -3827,7 +3827,7 @@
         <v>13</v>
       </c>
       <c r="AH13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3839,40 +3839,40 @@
         <v>14</v>
       </c>
       <c r="AL13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AO13">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AP13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ13">
         <v>36</v>
       </c>
       <c r="AR13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT13">
         <v>9.800000000000001</v>
       </c>
       <c r="AU13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="AW13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3899,25 +3899,25 @@
         <v>13.5</v>
       </c>
       <c r="BF13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
         <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK13">
         <v>10.5</v>
       </c>
       <c r="BL13">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM13">
         <v>21</v>
@@ -3932,28 +3932,28 @@
         <v>6.4</v>
       </c>
       <c r="BQ13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS13">
         <v>16.5</v>
       </c>
       <c r="BT13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU13">
         <v>14</v>
       </c>
       <c r="BV13">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BW13">
         <v>21</v>
       </c>
       <c r="BX13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BY13">
         <v>21</v>
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="K14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4021,7 +4021,7 @@
         <v>1.4</v>
       </c>
       <c r="R14">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S14">
         <v>2.04</v>
@@ -4033,7 +4033,7 @@
         <v>1.28</v>
       </c>
       <c r="V14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4066,13 +4066,13 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="AH14">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AI14">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AJ14">
         <v>1000</v>
@@ -4090,25 +4090,25 @@
         <v>1000</v>
       </c>
       <c r="AO14">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AP14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AQ14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR14">
         <v>5.9</v>
       </c>
       <c r="AS14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT14">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="AU14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AV14">
         <v>18</v>
@@ -4117,31 +4117,31 @@
         <v>18</v>
       </c>
       <c r="AX14">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BB14">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BE14">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BF14">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG14">
         <v>2.32</v>
@@ -4233,16 +4233,16 @@
         <v>10.5</v>
       </c>
       <c r="H15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="J15">
         <v>5.4</v>
       </c>
       <c r="K15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
         <v>1.3</v>
@@ -4251,37 +4251,37 @@
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O15">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15">
         <v>2.32</v>
       </c>
       <c r="Q15">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V15">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="W15">
         <v>1.1</v>
       </c>
       <c r="X15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -4296,7 +4296,7 @@
         <v>32</v>
       </c>
       <c r="AC15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD15">
         <v>10.5</v>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="AG15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH15">
         <v>26</v>
@@ -4317,16 +4317,16 @@
         <v>36</v>
       </c>
       <c r="AJ15">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AK15">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL15">
         <v>140</v>
       </c>
       <c r="AM15">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN15">
         <v>240</v>
@@ -4344,7 +4344,7 @@
         <v>7.8</v>
       </c>
       <c r="AS15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT15">
         <v>28</v>
@@ -4368,10 +4368,10 @@
         <v>25</v>
       </c>
       <c r="BA15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BC15">
         <v>120</v>
@@ -4475,10 +4475,10 @@
         <v>1.31</v>
       </c>
       <c r="H16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -4508,7 +4508,7 @@
         <v>1.41</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
         <v>2.64</v>
@@ -4517,7 +4517,7 @@
         <v>1.57</v>
       </c>
       <c r="V16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W16">
         <v>4.2</v>
@@ -4535,7 +4535,7 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC16">
         <v>14</v>
@@ -4547,7 +4547,7 @@
         <v>400</v>
       </c>
       <c r="AF16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG16">
         <v>12</v>
@@ -4565,13 +4565,13 @@
         <v>17</v>
       </c>
       <c r="AL16">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AM16">
         <v>380</v>
       </c>
       <c r="AN16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AO16">
         <v>660</v>
@@ -4583,10 +4583,10 @@
         <v>32</v>
       </c>
       <c r="AR16">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AS16">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AT16">
         <v>6.6</v>
@@ -4598,7 +4598,7 @@
         <v>44</v>
       </c>
       <c r="AW16">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX16">
         <v>6</v>
@@ -4610,7 +4610,7 @@
         <v>38</v>
       </c>
       <c r="BA16">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BB16">
         <v>8.4</v>
@@ -4619,31 +4619,31 @@
         <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BE16">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BF16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG16">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BH16">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BI16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK16">
         <v>13</v>
       </c>
       <c r="BL16">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="BM16">
         <v>21</v>
@@ -4655,7 +4655,7 @@
         <v>3.15</v>
       </c>
       <c r="BP16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ16">
         <v>6.4</v>
@@ -4667,13 +4667,13 @@
         <v>23</v>
       </c>
       <c r="BT16">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BU16">
         <v>9.4</v>
       </c>
       <c r="BV16">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BW16">
         <v>21</v>
@@ -4685,7 +4685,7 @@
         <v>21</v>
       </c>
       <c r="BZ16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA16">
         <v>10.5</v>
@@ -4711,16 +4711,16 @@
         <v>143</v>
       </c>
       <c r="F17">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G17">
         <v>1.73</v>
       </c>
       <c r="H17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
         <v>3.7</v>
@@ -4729,40 +4729,40 @@
         <v>3.8</v>
       </c>
       <c r="L17">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q17">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T17">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V17">
         <v>1.17</v>
       </c>
       <c r="W17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X17">
         <v>10.5</v>
@@ -4771,13 +4771,13 @@
         <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA17">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC17">
         <v>8.6</v>
@@ -4786,7 +4786,7 @@
         <v>28</v>
       </c>
       <c r="AE17">
-        <v>160</v>
+        <v>670</v>
       </c>
       <c r="AF17">
         <v>8.6</v>
@@ -4798,7 +4798,7 @@
         <v>28</v>
       </c>
       <c r="AI17">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ17">
         <v>17</v>
@@ -4810,22 +4810,22 @@
         <v>65</v>
       </c>
       <c r="AM17">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN17">
         <v>15.5</v>
       </c>
       <c r="AO17">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17">
         <v>14</v>
       </c>
       <c r="AR17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS17">
         <v>13</v>
@@ -4837,7 +4837,7 @@
         <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW17">
         <v>12.5</v>
@@ -4849,7 +4849,7 @@
         <v>10</v>
       </c>
       <c r="AZ17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA17">
         <v>12.5</v>
@@ -4861,7 +4861,7 @@
         <v>18.5</v>
       </c>
       <c r="BD17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE17">
         <v>13</v>
@@ -4873,64 +4873,64 @@
         <v>13</v>
       </c>
       <c r="BH17">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BI17">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK17">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL17">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM17">
         <v>21</v>
       </c>
       <c r="BN17">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP17">
         <v>12.5</v>
       </c>
       <c r="BQ17">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BS17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BT17">
         <v>10.5</v>
       </c>
       <c r="BU17">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BV17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BW17">
         <v>21</v>
       </c>
       <c r="BX17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY17">
         <v>21</v>
       </c>
       <c r="BZ17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4956,19 +4956,19 @@
         <v>4.6</v>
       </c>
       <c r="G18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H18">
+        <v>1.94</v>
+      </c>
+      <c r="I18">
         <v>1.95</v>
       </c>
-      <c r="I18">
-        <v>1.97</v>
-      </c>
       <c r="J18">
+        <v>3.6</v>
+      </c>
+      <c r="K18">
         <v>3.65</v>
-      </c>
-      <c r="K18">
-        <v>3.7</v>
       </c>
       <c r="L18">
         <v>1.44</v>
@@ -5001,10 +5001,10 @@
         <v>1.9</v>
       </c>
       <c r="V18">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X18">
         <v>11.5</v>
@@ -5019,7 +5019,7 @@
         <v>23</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC18">
         <v>8.199999999999999</v>
@@ -5031,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="AF18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG18">
         <v>19</v>
@@ -5043,7 +5043,7 @@
         <v>46</v>
       </c>
       <c r="AJ18">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AK18">
         <v>75</v>
@@ -5082,7 +5082,7 @@
         <v>10</v>
       </c>
       <c r="AW18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX18">
         <v>30</v>
@@ -5112,7 +5112,7 @@
         <v>75</v>
       </c>
       <c r="BG18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH18">
         <v>3.3</v>
@@ -5204,16 +5204,16 @@
         <v>3.6</v>
       </c>
       <c r="I19">
+        <v>3.9</v>
+      </c>
+      <c r="J19">
         <v>3.85</v>
-      </c>
-      <c r="J19">
-        <v>3.9</v>
       </c>
       <c r="K19">
         <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M19">
         <v>1.04</v>
@@ -5225,7 +5225,7 @@
         <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q19">
         <v>1.63</v>
@@ -5237,13 +5237,13 @@
         <v>2.54</v>
       </c>
       <c r="T19">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
         <v>1.94</v>
@@ -5270,7 +5270,7 @@
         <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF19">
         <v>18</v>
@@ -5309,10 +5309,10 @@
         <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT19">
         <v>11</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="AW19">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX19">
         <v>13</v>
@@ -5336,7 +5336,7 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB19">
         <v>21</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF19">
         <v>9</v>
@@ -5357,10 +5357,10 @@
         <v>21</v>
       </c>
       <c r="BH19">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BI19">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BJ19">
         <v>10</v>
@@ -5378,13 +5378,13 @@
         <v>5.9</v>
       </c>
       <c r="BO19">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP19">
         <v>15.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR19">
         <v>26</v>
@@ -5396,13 +5396,13 @@
         <v>8.4</v>
       </c>
       <c r="BU19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
         <v>30</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX19">
         <v>38</v>
@@ -5414,7 +5414,7 @@
         <v>19</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB19" t="s">
         <v>157</v>
@@ -5440,13 +5440,13 @@
         <v>4.1</v>
       </c>
       <c r="G20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I20">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J20">
         <v>4.1</v>
@@ -5455,28 +5455,28 @@
         <v>4.4</v>
       </c>
       <c r="L20">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20">
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
         <v>1.74</v>
       </c>
       <c r="R20">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S20">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T20">
         <v>1.7</v>
@@ -5485,7 +5485,7 @@
         <v>2.2</v>
       </c>
       <c r="V20">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W20">
         <v>1.29</v>
@@ -5500,7 +5500,7 @@
         <v>13</v>
       </c>
       <c r="AA20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB20">
         <v>18</v>
@@ -5518,7 +5518,7 @@
         <v>34</v>
       </c>
       <c r="AG20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH20">
         <v>18.5</v>
@@ -5554,7 +5554,7 @@
         <v>11</v>
       </c>
       <c r="AS20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT20">
         <v>15.5</v>
@@ -5563,7 +5563,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW20">
         <v>16</v>
@@ -5587,13 +5587,13 @@
         <v>40</v>
       </c>
       <c r="BD20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF20">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BG20">
         <v>9.199999999999999</v>
@@ -5650,7 +5650,7 @@
         <v>26</v>
       </c>
       <c r="BY20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>23</v>
@@ -5694,13 +5694,13 @@
         <v>4</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L21">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
         <v>5.7</v>
@@ -5924,7 +5924,7 @@
         <v>2.14</v>
       </c>
       <c r="G22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H22">
         <v>3.25</v>
@@ -5933,13 +5933,13 @@
         <v>3.6</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -5963,13 +5963,13 @@
         <v>2.74</v>
       </c>
       <c r="T22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U22">
         <v>2.32</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.78</v>
@@ -5981,10 +5981,10 @@
         <v>17</v>
       </c>
       <c r="Z22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA22">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB22">
         <v>13</v>
@@ -6005,10 +6005,10 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI22">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ22">
         <v>34</v>
@@ -6017,16 +6017,16 @@
         <v>23</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM22">
         <v>100</v>
       </c>
       <c r="AN22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP22">
         <v>16.5</v>
@@ -6035,13 +6035,13 @@
         <v>13.5</v>
       </c>
       <c r="AR22">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AS22">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="AT22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU22">
         <v>7.8</v>
@@ -6074,13 +6074,13 @@
         <v>19</v>
       </c>
       <c r="BE22">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF22">
         <v>11</v>
       </c>
       <c r="BG22">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6101,13 +6101,13 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO22">
         <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
@@ -6163,22 +6163,22 @@
         <v>149</v>
       </c>
       <c r="F23">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G23">
         <v>2.36</v>
       </c>
       <c r="H23">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>1.29</v>
@@ -6193,13 +6193,13 @@
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R23">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S23">
         <v>2.78</v>
@@ -6265,43 +6265,43 @@
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO23">
         <v>34</v>
       </c>
       <c r="AP23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ23">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR23">
         <v>18.5</v>
       </c>
       <c r="AS23">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU23">
         <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW23">
         <v>5.1</v>
       </c>
       <c r="AX23">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA23">
         <v>32</v>
@@ -6316,7 +6316,7 @@
         <v>5.1</v>
       </c>
       <c r="BE23">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF23">
         <v>11.5</v>
@@ -6376,7 +6376,7 @@
         <v>40</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ23">
         <v>24</v>
@@ -6408,7 +6408,7 @@
         <v>1.78</v>
       </c>
       <c r="G24">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H24">
         <v>4.3</v>
@@ -6417,7 +6417,7 @@
         <v>4.7</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K24">
         <v>4.5</v>
@@ -6456,7 +6456,7 @@
         <v>1.27</v>
       </c>
       <c r="W24">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X24">
         <v>28</v>
@@ -6507,7 +6507,7 @@
         <v>55</v>
       </c>
       <c r="AN24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO24">
         <v>32</v>
@@ -6519,13 +6519,13 @@
         <v>19</v>
       </c>
       <c r="AR24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU24">
         <v>9</v>
@@ -6546,7 +6546,7 @@
         <v>13</v>
       </c>
       <c r="BA24">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB24">
         <v>18</v>
@@ -6558,13 +6558,13 @@
         <v>18.5</v>
       </c>
       <c r="BE24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF24">
         <v>6.4</v>
       </c>
       <c r="BG24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6653,19 +6653,19 @@
         <v>2.46</v>
       </c>
       <c r="H25">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J25">
         <v>3.55</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L25">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -6680,13 +6680,13 @@
         <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R25">
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T25">
         <v>1.66</v>
@@ -6704,7 +6704,7 @@
         <v>21</v>
       </c>
       <c r="Y25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z25">
         <v>28</v>
@@ -6716,7 +6716,7 @@
         <v>12.5</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25">
         <v>14.5</v>
@@ -6725,7 +6725,7 @@
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG25">
         <v>12</v>
@@ -6776,7 +6776,7 @@
         <v>12</v>
       </c>
       <c r="AW25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX25">
         <v>13.5</v>
@@ -6800,7 +6800,7 @@
         <v>6.6</v>
       </c>
       <c r="BE25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF25">
         <v>13.5</v>
@@ -6889,13 +6889,13 @@
         <v>152</v>
       </c>
       <c r="F26">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G26">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H26">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I26">
         <v>2.7</v>
@@ -6931,7 +6931,7 @@
         <v>2.2</v>
       </c>
       <c r="T26">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U26">
         <v>2.86</v>
@@ -6940,7 +6940,7 @@
         <v>1.58</v>
       </c>
       <c r="W26">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X26">
         <v>36</v>
@@ -7105,7 +7105,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
@@ -7140,19 +7140,19 @@
         <v>1.79</v>
       </c>
       <c r="I27">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J27">
         <v>4.2</v>
       </c>
       <c r="K27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>1.31</v>
       </c>
       <c r="M27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N27">
         <v>4.8</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AC27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>10.5</v>
@@ -7326,7 +7326,7 @@
         <v>48</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT27">
         <v>4.9</v>
@@ -7382,13 +7382,13 @@
         <v>1.9</v>
       </c>
       <c r="I28">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7397,31 +7397,31 @@
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q28">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T28">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U28">
         <v>1.94</v>
       </c>
       <c r="V28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W28">
         <v>1.25</v>
@@ -7433,7 +7433,7 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA28">
         <v>26</v>
@@ -7445,7 +7445,7 @@
         <v>8</v>
       </c>
       <c r="AD28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE28">
         <v>26</v>
@@ -7466,19 +7466,19 @@
         <v>140</v>
       </c>
       <c r="AK28">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL28">
         <v>90</v>
       </c>
       <c r="AM28">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP28">
         <v>10.5</v>
@@ -7502,34 +7502,34 @@
         <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY28">
         <v>16.5</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC28">
         <v>6.6</v>
       </c>
       <c r="BD28">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE28">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF28">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG28">
         <v>14</v>
@@ -7615,7 +7615,7 @@
         <v>155</v>
       </c>
       <c r="F29">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G29">
         <v>1.27</v>
@@ -7627,13 +7627,13 @@
         <v>22</v>
       </c>
       <c r="J29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K29">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L29">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M29">
         <v>1.04</v>
@@ -7645,22 +7645,22 @@
         <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q29">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="R29">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S29">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T29">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="U29">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V29">
         <v>1.05</v>
@@ -7681,19 +7681,19 @@
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AD29">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AE29">
         <v>420</v>
       </c>
       <c r="AF29">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7717,22 +7717,22 @@
         <v>330</v>
       </c>
       <c r="AN29">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO29">
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AQ29">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AR29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7741,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="AV29">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="AW29">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX29">
         <v>6.4</v>
@@ -7753,28 +7753,28 @@
         <v>10</v>
       </c>
       <c r="AZ29">
+        <v>5.7</v>
+      </c>
+      <c r="BA29">
+        <v>6.4</v>
+      </c>
+      <c r="BB29">
         <v>8</v>
-      </c>
-      <c r="BA29">
-        <v>8.6</v>
-      </c>
-      <c r="BB29">
-        <v>7.8</v>
       </c>
       <c r="BC29">
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BE29">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF29">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BG29">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BH29">
         <v>970</v>
@@ -7804,7 +7804,7 @@
         <v>8</v>
       </c>
       <c r="BQ29">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BR29">
         <v>32</v>
@@ -7857,28 +7857,28 @@
         <v>156</v>
       </c>
       <c r="F30">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G30">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H30">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J30">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K30">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
         <v>2.96</v>
@@ -7890,13 +7890,13 @@
         <v>1.64</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R30">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S30">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="T30">
         <v>1.01</v>
@@ -7905,10 +7905,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X30">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -487,7 +487,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-28 14:30:34</t>
+    <t>2026-09-28 16:40:20</t>
   </si>
 </sst>
 </file>
@@ -1081,31 +1081,31 @@
         <v>128</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
         <v>3.65</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
         <v>1.41</v>
@@ -1114,7 +1114,7 @@
         <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1123,25 +1123,25 @@
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
         <v>12</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA2">
         <v>85</v>
@@ -1165,7 +1165,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>80</v>
@@ -1174,16 +1174,16 @@
         <v>32</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2">
         <v>90</v>
@@ -1192,16 +1192,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
         <v>50</v>
       </c>
       <c r="AT2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BB2">
         <v>24</v>
@@ -1234,13 +1234,13 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF2">
         <v>20</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1282,7 +1282,7 @@
         <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>36</v>
@@ -1323,19 +1323,19 @@
         <v>129</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1347,7 +1347,7 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>1.21</v>
@@ -1356,28 +1356,28 @@
         <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
         <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1425,10 +1425,10 @@
         <v>85</v>
       </c>
       <c r="AN3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP3">
         <v>19</v>
@@ -1440,7 +1440,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1455,7 +1455,7 @@
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3">
         <v>12</v>
@@ -1467,16 +1467,16 @@
         <v>22</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD3">
         <v>25</v>
       </c>
       <c r="BE3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>17</v>
@@ -1515,7 +1515,7 @@
         <v>18.5</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS3">
         <v>22</v>
@@ -1565,16 +1565,16 @@
         <v>130</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I4">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
         <v>3.7</v>
@@ -1595,13 +1595,13 @@
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
         <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
         <v>2.84</v>
@@ -1610,13 +1610,13 @@
         <v>1.63</v>
       </c>
       <c r="U4">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1625,10 +1625,10 @@
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB4">
         <v>17.5</v>
@@ -1652,7 +1652,7 @@
         <v>19</v>
       </c>
       <c r="AI4">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AJ4">
         <v>55</v>
@@ -1664,10 +1664,10 @@
         <v>44</v>
       </c>
       <c r="AM4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO4">
         <v>17</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="AX4">
         <v>21</v>
@@ -1706,19 +1706,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BB4">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BC4">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BD4">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1727,7 +1727,7 @@
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI4">
         <v>3.05</v>
@@ -1748,13 +1748,13 @@
         <v>8</v>
       </c>
       <c r="BO4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP4">
         <v>29</v>
       </c>
       <c r="BQ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BR4">
         <v>40</v>
@@ -1769,10 +1769,10 @@
         <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>32</v>
@@ -1781,10 +1781,10 @@
         <v>18.5</v>
       </c>
       <c r="BZ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>157</v>
@@ -1810,7 +1810,7 @@
         <v>2.08</v>
       </c>
       <c r="G5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
         <v>3.85</v>
@@ -1822,22 +1822,22 @@
         <v>3.55</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5">
         <v>1.43</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1849,28 +1849,28 @@
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
         <v>14</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -1879,10 +1879,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>13</v>
@@ -1891,58 +1891,58 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK5">
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS5">
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
         <v>17</v>
@@ -1951,37 +1951,37 @@
         <v>40</v>
       </c>
       <c r="BB5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE5">
         <v>80</v>
       </c>
       <c r="BF5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BH5">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
@@ -2023,7 +2023,7 @@
         <v>32</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA5">
         <v>20</v>
@@ -2049,10 +2049,10 @@
         <v>132</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H6">
         <v>3.4</v>
@@ -2064,7 +2064,7 @@
         <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2073,43 +2073,43 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T6">
         <v>1.81</v>
       </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V6">
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X6">
         <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>80</v>
@@ -2118,16 +2118,16 @@
         <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
         <v>13.5</v>
@@ -2151,34 +2151,34 @@
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP6">
+        <v>12</v>
+      </c>
+      <c r="AQ6">
         <v>11.5</v>
       </c>
-      <c r="AQ6">
-        <v>12</v>
-      </c>
       <c r="AR6">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
@@ -2199,16 +2199,16 @@
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE6">
         <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG6">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2303,7 +2303,7 @@
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="K7">
         <v>920</v>
@@ -2542,13 +2542,13 @@
         <v>6.6</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>1.5</v>
@@ -2557,16 +2557,16 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
         <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
         <v>1.27</v>
@@ -2578,10 +2578,10 @@
         <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
         <v>2.48</v>
@@ -2590,7 +2590,7 @@
         <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z8">
         <v>55</v>
@@ -2602,19 +2602,19 @@
         <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF8">
         <v>8.199999999999999</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
         <v>28</v>
@@ -2635,7 +2635,7 @@
         <v>230</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO8">
         <v>190</v>
@@ -2656,7 +2656,7 @@
         <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV8">
         <v>24</v>
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8">
         <v>42</v>
@@ -2689,7 +2689,7 @@
         <v>48</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG8">
         <v>46</v>
@@ -2701,13 +2701,13 @@
         <v>2.8</v>
       </c>
       <c r="BJ8">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
         <v>10.5</v>
       </c>
       <c r="BL8">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM8">
         <v>21</v>
@@ -2716,31 +2716,31 @@
         <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP8">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8">
         <v>10</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS8">
         <v>24</v>
       </c>
       <c r="BT8">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU8">
         <v>8.800000000000001</v>
       </c>
       <c r="BV8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BW8">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BX8">
         <v>110</v>
@@ -2749,10 +2749,10 @@
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="CA8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CB8" t="s">
         <v>157</v>
@@ -2775,37 +2775,37 @@
         <v>135</v>
       </c>
       <c r="F9">
+        <v>2.98</v>
+      </c>
+      <c r="G9">
         <v>3</v>
-      </c>
-      <c r="G9">
-        <v>3.1</v>
       </c>
       <c r="H9">
         <v>2.92</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="M9">
         <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O9">
         <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
         <v>2.68</v>
@@ -2823,10 +2823,10 @@
         <v>1.81</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
         <v>8.6</v>
@@ -2859,7 +2859,7 @@
         <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>75</v>
@@ -2874,7 +2874,7 @@
         <v>120</v>
       </c>
       <c r="AM9">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN9">
         <v>60</v>
@@ -2889,13 +2889,13 @@
         <v>8</v>
       </c>
       <c r="AR9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
@@ -2904,7 +2904,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
@@ -2916,7 +2916,7 @@
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB9">
         <v>46</v>
@@ -2931,70 +2931,70 @@
         <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG9">
         <v>11</v>
       </c>
       <c r="BH9">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="BI9">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN9">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BT9">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="CB9" t="s">
         <v>157</v>
@@ -3017,25 +3017,25 @@
         <v>136</v>
       </c>
       <c r="F10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
         <v>1.54</v>
       </c>
       <c r="H10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -3044,22 +3044,22 @@
         <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
         <v>1.59</v>
       </c>
       <c r="R10">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="U10">
         <v>2.18</v>
@@ -3071,7 +3071,7 @@
         <v>2.84</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y10">
         <v>34</v>
@@ -3101,10 +3101,10 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ10">
         <v>14.5</v>
@@ -3113,7 +3113,7 @@
         <v>15.5</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM10">
         <v>110</v>
@@ -3122,13 +3122,13 @@
         <v>6.2</v>
       </c>
       <c r="AO10">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP10">
         <v>17.5</v>
       </c>
       <c r="AQ10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AR10">
         <v>7.8</v>
@@ -3137,13 +3137,13 @@
         <v>8.4</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AW10">
         <v>8</v>
@@ -3152,22 +3152,22 @@
         <v>9.4</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BE10">
         <v>8.199999999999999</v>
@@ -3176,64 +3176,64 @@
         <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3259,22 +3259,22 @@
         <v>137</v>
       </c>
       <c r="F11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I11">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>3.8</v>
       </c>
       <c r="K11">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11">
         <v>1.48</v>
@@ -3292,7 +3292,7 @@
         <v>1.71</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
         <v>1.26</v>
@@ -3301,16 +3301,16 @@
         <v>4.6</v>
       </c>
       <c r="T11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W11">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3319,22 +3319,22 @@
         <v>18</v>
       </c>
       <c r="Z11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA11">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AB11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC11">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF11">
         <v>8.4</v>
@@ -3358,7 +3358,7 @@
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN11">
         <v>14</v>
@@ -3370,10 +3370,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR11">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS11">
         <v>15</v>
@@ -3382,25 +3382,25 @@
         <v>6</v>
       </c>
       <c r="AU11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX11">
         <v>7.6</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3412,13 +3412,13 @@
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
         <v>12</v>
       </c>
       <c r="BG11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
         <v>3.2</v>
@@ -3427,16 +3427,16 @@
         <v>2.52</v>
       </c>
       <c r="BJ11">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BK11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
@@ -3445,40 +3445,40 @@
         <v>3.45</v>
       </c>
       <c r="BP11">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BQ11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BU11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>157</v>
@@ -3501,19 +3501,19 @@
         <v>138</v>
       </c>
       <c r="F12">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G12">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="I12">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.45</v>
@@ -3525,13 +3525,13 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
         <v>1.39</v>
       </c>
       <c r="P12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q12">
         <v>2.18</v>
@@ -3540,49 +3540,49 @@
         <v>1.3</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U12">
         <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W12">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X12">
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC12">
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH12">
         <v>19.5</v>
@@ -3591,10 +3591,10 @@
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL12">
         <v>60</v>
@@ -3603,16 +3603,16 @@
         <v>120</v>
       </c>
       <c r="AN12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO12">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR12">
         <v>13</v>
@@ -3627,16 +3627,16 @@
         <v>7</v>
       </c>
       <c r="AV12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
         <v>25</v>
       </c>
       <c r="AX12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ12">
         <v>17.5</v>
@@ -3645,28 +3645,28 @@
         <v>40</v>
       </c>
       <c r="BB12">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BC12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD12">
         <v>46</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH12">
         <v>3.1</v>
       </c>
       <c r="BI12">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12">
         <v>10</v>
@@ -3675,49 +3675,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BL12">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM12">
         <v>21</v>
       </c>
       <c r="BN12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BP12">
+        <v>34</v>
+      </c>
+      <c r="BQ12">
+        <v>22</v>
+      </c>
+      <c r="BR12">
+        <v>55</v>
+      </c>
+      <c r="BS12">
         <v>32</v>
       </c>
-      <c r="BQ12">
+      <c r="BT12">
+        <v>5.1</v>
+      </c>
+      <c r="BU12">
+        <v>4.5</v>
+      </c>
+      <c r="BV12">
         <v>21</v>
       </c>
-      <c r="BR12">
-        <v>44</v>
-      </c>
-      <c r="BS12">
-        <v>30</v>
-      </c>
-      <c r="BT12">
-        <v>5.3</v>
-      </c>
-      <c r="BU12">
-        <v>4.7</v>
-      </c>
-      <c r="BV12">
-        <v>19.5</v>
-      </c>
       <c r="BW12">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY12">
         <v>26</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA12">
         <v>25</v>
@@ -3743,10 +3743,10 @@
         <v>139</v>
       </c>
       <c r="F13">
+        <v>1.21</v>
+      </c>
+      <c r="G13">
         <v>1.22</v>
-      </c>
-      <c r="G13">
-        <v>1.23</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -3758,58 +3758,58 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P13">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="Q13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R13">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S13">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V13">
         <v>1.06</v>
       </c>
       <c r="W13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="X13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y13">
         <v>55</v>
       </c>
       <c r="Z13">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC13">
         <v>18.5</v>
@@ -3821,19 +3821,19 @@
         <v>320</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG13">
         <v>13</v>
       </c>
       <c r="AH13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI13">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK13">
         <v>14</v>
@@ -3842,49 +3842,49 @@
         <v>42</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN13">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AO13">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="AP13">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AQ13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AV13">
         <v>42</v>
       </c>
       <c r="AW13">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>30</v>
       </c>
       <c r="BA13">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BB13">
         <v>8</v>
@@ -3896,16 +3896,16 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI13">
         <v>4.1</v>
@@ -3914,16 +3914,16 @@
         <v>16</v>
       </c>
       <c r="BK13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BL13">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM13">
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BO13">
         <v>3.55</v>
@@ -3932,7 +3932,7 @@
         <v>6.4</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR13">
         <v>22</v>
@@ -3988,16 +3988,16 @@
         <v>55</v>
       </c>
       <c r="G14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I14">
         <v>1.07</v>
       </c>
       <c r="J14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K14">
         <v>24</v>
@@ -4009,31 +4009,31 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O14">
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R14">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="S14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="U14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4042,34 +4042,34 @@
         <v>55</v>
       </c>
       <c r="Y14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>190</v>
       </c>
       <c r="AC14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AD14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF14">
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AI14">
         <v>230</v>
@@ -4093,19 +4093,19 @@
         <v>2.46</v>
       </c>
       <c r="AP14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ14">
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AU14">
         <v>29</v>
@@ -4117,34 +4117,34 @@
         <v>18</v>
       </c>
       <c r="AX14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY14">
         <v>15</v>
       </c>
       <c r="AZ14">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
         <v>40</v>
       </c>
       <c r="BB14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BD14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BE14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG14">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4227,67 +4227,67 @@
         <v>141</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H15">
+        <v>1.38</v>
+      </c>
+      <c r="I15">
         <v>1.39</v>
       </c>
-      <c r="I15">
-        <v>1.4</v>
-      </c>
       <c r="J15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K15">
         <v>5.5</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P15">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
         <v>2.08</v>
       </c>
       <c r="U15">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="W15">
         <v>1.1</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>11</v>
@@ -4317,10 +4317,10 @@
         <v>36</v>
       </c>
       <c r="AJ15">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="AK15">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AL15">
         <v>140</v>
@@ -4332,10 +4332,10 @@
         <v>240</v>
       </c>
       <c r="AO15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AP15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ15">
         <v>8.6</v>
@@ -4356,10 +4356,10 @@
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AY15">
         <v>30</v>
@@ -4371,10 +4371,10 @@
         <v>34</v>
       </c>
       <c r="BB15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BD15">
         <v>120</v>
@@ -4383,70 +4383,70 @@
         <v>140</v>
       </c>
       <c r="BF15">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BG15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK15">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM15">
-        <v>2.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BO15">
-        <v>2.22</v>
+        <v>11</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ15">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BS15">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BU15">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BW15">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY15">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA15">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="s">
         <v>157</v>
@@ -4472,13 +4472,13 @@
         <v>1.3</v>
       </c>
       <c r="G16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -4508,7 +4508,7 @@
         <v>1.41</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
         <v>2.64</v>
@@ -4517,7 +4517,7 @@
         <v>1.57</v>
       </c>
       <c r="V16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W16">
         <v>4.2</v>
@@ -4529,7 +4529,7 @@
         <v>38</v>
       </c>
       <c r="Z16">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AA16">
         <v>1000</v>
@@ -4544,7 +4544,7 @@
         <v>60</v>
       </c>
       <c r="AE16">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AF16">
         <v>6.8</v>
@@ -4553,28 +4553,28 @@
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI16">
         <v>290</v>
       </c>
       <c r="AJ16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK16">
         <v>17</v>
       </c>
       <c r="AL16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM16">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AN16">
         <v>5.8</v>
       </c>
       <c r="AO16">
-        <v>660</v>
+        <v>600</v>
       </c>
       <c r="AP16">
         <v>15</v>
@@ -4598,7 +4598,7 @@
         <v>44</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX16">
         <v>6</v>
@@ -4607,7 +4607,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BA16">
         <v>15.5</v>
@@ -4619,19 +4619,19 @@
         <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE16">
         <v>15.5</v>
       </c>
       <c r="BF16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG16">
         <v>16</v>
       </c>
       <c r="BH16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI16">
         <v>3.35</v>
@@ -4643,7 +4643,7 @@
         <v>13</v>
       </c>
       <c r="BL16">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="BM16">
         <v>21</v>
@@ -4667,25 +4667,25 @@
         <v>23</v>
       </c>
       <c r="BT16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BU16">
         <v>9.4</v>
       </c>
       <c r="BV16">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="BW16">
         <v>21</v>
       </c>
       <c r="BX16">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BY16">
         <v>21</v>
       </c>
       <c r="BZ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA16">
         <v>10.5</v>
@@ -4711,7 +4711,7 @@
         <v>143</v>
       </c>
       <c r="F17">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G17">
         <v>1.73</v>
@@ -4720,37 +4720,37 @@
         <v>6.2</v>
       </c>
       <c r="I17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K17">
         <v>3.8</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q17">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R17">
         <v>1.24</v>
       </c>
       <c r="S17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
         <v>2.32</v>
@@ -4774,7 +4774,7 @@
         <v>55</v>
       </c>
       <c r="AA17">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB17">
         <v>6.6</v>
@@ -4783,13 +4783,13 @@
         <v>8.6</v>
       </c>
       <c r="AD17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE17">
-        <v>670</v>
+        <v>130</v>
       </c>
       <c r="AF17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG17">
         <v>11</v>
@@ -4798,139 +4798,139 @@
         <v>28</v>
       </c>
       <c r="AI17">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ17">
         <v>17</v>
       </c>
       <c r="AK17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN17">
         <v>15.5</v>
       </c>
       <c r="AO17">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AP17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AS17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU17">
         <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW17">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AX17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY17">
         <v>10</v>
       </c>
       <c r="AZ17">
+        <v>25</v>
+      </c>
+      <c r="BA17">
+        <v>15</v>
+      </c>
+      <c r="BB17">
+        <v>15</v>
+      </c>
+      <c r="BC17">
         <v>20</v>
       </c>
-      <c r="BA17">
-        <v>12.5</v>
-      </c>
-      <c r="BB17">
-        <v>14.5</v>
-      </c>
-      <c r="BC17">
-        <v>18.5</v>
-      </c>
       <c r="BD17">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="BE17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF17">
         <v>13.5</v>
       </c>
       <c r="BG17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH17">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BI17">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BJ17">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL17">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BO17">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BP17">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BU17">
         <v>7.2</v>
       </c>
       <c r="BV17">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4953,16 +4953,16 @@
         <v>144</v>
       </c>
       <c r="F18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H18">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I18">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J18">
         <v>3.6</v>
@@ -4986,7 +4986,7 @@
         <v>1.74</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
         <v>1.28</v>
@@ -5001,10 +5001,10 @@
         <v>1.9</v>
       </c>
       <c r="V18">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X18">
         <v>11.5</v>
@@ -5031,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="AF18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG18">
         <v>19</v>
@@ -5046,7 +5046,7 @@
         <v>130</v>
       </c>
       <c r="AK18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL18">
         <v>85</v>
@@ -5064,7 +5064,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR18">
         <v>10</v>
@@ -5073,7 +5073,7 @@
         <v>21</v>
       </c>
       <c r="AT18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU18">
         <v>7.6</v>
@@ -5082,10 +5082,10 @@
         <v>10</v>
       </c>
       <c r="AW18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY18">
         <v>17.5</v>
@@ -5097,10 +5097,10 @@
         <v>40</v>
       </c>
       <c r="BB18">
-        <v>15.5</v>
+        <v>100</v>
       </c>
       <c r="BC18">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BD18">
         <v>70</v>
@@ -5109,10 +5109,10 @@
         <v>130</v>
       </c>
       <c r="BF18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BG18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH18">
         <v>3.3</v>
@@ -5124,13 +5124,13 @@
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>7.6</v>
+        <v>2.58</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BN18">
         <v>1000</v>
@@ -5142,13 +5142,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BT18">
         <v>5.3</v>
@@ -5160,19 +5160,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="CB18" t="s">
         <v>157</v>
@@ -5207,13 +5207,13 @@
         <v>3.9</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
         <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M19">
         <v>1.04</v>
@@ -5234,7 +5234,7 @@
         <v>1.57</v>
       </c>
       <c r="S19">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T19">
         <v>1.6</v>
@@ -5270,16 +5270,16 @@
         <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19">
         <v>18</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI19">
         <v>40</v>
@@ -5288,7 +5288,7 @@
         <v>29</v>
       </c>
       <c r="AK19">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL19">
         <v>32</v>
@@ -5309,13 +5309,13 @@
         <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS19">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU19">
         <v>8.4</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="AW19">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX19">
         <v>13</v>
@@ -5336,7 +5336,7 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB19">
         <v>21</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19">
         <v>9</v>
@@ -5378,13 +5378,13 @@
         <v>5.9</v>
       </c>
       <c r="BO19">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP19">
         <v>15.5</v>
       </c>
       <c r="BQ19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
         <v>26</v>
@@ -5396,7 +5396,7 @@
         <v>8.4</v>
       </c>
       <c r="BU19">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>30</v>
@@ -5408,7 +5408,7 @@
         <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
         <v>19</v>
@@ -5440,13 +5440,13 @@
         <v>4.1</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H20">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I20">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="J20">
         <v>4.1</v>
@@ -5467,13 +5467,13 @@
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
         <v>1.74</v>
       </c>
       <c r="R20">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S20">
         <v>2.88</v>
@@ -5485,10 +5485,10 @@
         <v>2.2</v>
       </c>
       <c r="V20">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X20">
         <v>19.5</v>
@@ -5539,22 +5539,22 @@
         <v>100</v>
       </c>
       <c r="AN20">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO20">
         <v>11.5</v>
       </c>
       <c r="AP20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR20">
         <v>11</v>
       </c>
       <c r="AS20">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT20">
         <v>15.5</v>
@@ -5563,7 +5563,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW20">
         <v>16</v>
@@ -5581,7 +5581,7 @@
         <v>26</v>
       </c>
       <c r="BB20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC20">
         <v>40</v>
@@ -5590,13 +5590,13 @@
         <v>44</v>
       </c>
       <c r="BE20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF20">
         <v>10.5</v>
       </c>
       <c r="BG20">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH20">
         <v>4.3</v>
@@ -5608,7 +5608,7 @@
         <v>11</v>
       </c>
       <c r="BK20">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL20">
         <v>120</v>
@@ -5620,10 +5620,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BQ20">
         <v>1.02</v>
@@ -5635,7 +5635,7 @@
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU20">
         <v>4.2</v>
@@ -5644,10 +5644,10 @@
         <v>15</v>
       </c>
       <c r="BW20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX20">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
@@ -5679,16 +5679,16 @@
         <v>147</v>
       </c>
       <c r="F21">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G21">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -5709,34 +5709,34 @@
         <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q21">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R21">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S21">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T21">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U21">
         <v>2.72</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X21">
         <v>32</v>
       </c>
       <c r="Y21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z21">
         <v>32</v>
@@ -5751,7 +5751,7 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE21">
         <v>36</v>
@@ -5760,10 +5760,10 @@
         <v>23</v>
       </c>
       <c r="AG21">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI21">
         <v>40</v>
@@ -5775,7 +5775,7 @@
         <v>26</v>
       </c>
       <c r="AL21">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM21">
         <v>65</v>
@@ -5784,25 +5784,25 @@
         <v>13.5</v>
       </c>
       <c r="AO21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ21">
         <v>16</v>
       </c>
       <c r="AR21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS21">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="AT21">
         <v>13.5</v>
       </c>
       <c r="AU21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV21">
         <v>12.5</v>
@@ -5820,22 +5820,22 @@
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BB21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BC21">
-        <v>17.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD21">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF21">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21">
         <v>16</v>
@@ -5865,7 +5865,7 @@
         <v>4.3</v>
       </c>
       <c r="BP21">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
@@ -5921,16 +5921,16 @@
         <v>148</v>
       </c>
       <c r="F22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G22">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H22">
         <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <v>3.8</v>
@@ -5945,13 +5945,13 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
         <v>1.24</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
         <v>1.7</v>
@@ -5960,22 +5960,22 @@
         <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T22">
         <v>1.62</v>
       </c>
       <c r="U22">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y22">
         <v>17</v>
@@ -5984,16 +5984,16 @@
         <v>32</v>
       </c>
       <c r="AA22">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
         <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE22">
         <v>44</v>
@@ -6005,10 +6005,10 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI22">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ22">
         <v>34</v>
@@ -6017,7 +6017,7 @@
         <v>23</v>
       </c>
       <c r="AL22">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM22">
         <v>100</v>
@@ -6032,7 +6032,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR22">
         <v>16.5</v>
@@ -6074,10 +6074,10 @@
         <v>19</v>
       </c>
       <c r="BE22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG22">
         <v>17.5</v>
@@ -6101,19 +6101,19 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
         <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
@@ -6122,7 +6122,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV22">
         <v>38</v>
@@ -6166,13 +6166,13 @@
         <v>2.18</v>
       </c>
       <c r="G23">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H23">
         <v>3.2</v>
       </c>
       <c r="I23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J23">
         <v>3.75</v>
@@ -6202,19 +6202,19 @@
         <v>1.47</v>
       </c>
       <c r="S23">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U23">
         <v>2.32</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X23">
         <v>20</v>
@@ -6223,19 +6223,19 @@
         <v>16.5</v>
       </c>
       <c r="Z23">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA23">
         <v>70</v>
       </c>
       <c r="AB23">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC23">
         <v>9.4</v>
       </c>
       <c r="AD23">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE23">
         <v>40</v>
@@ -6244,13 +6244,13 @@
         <v>17</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH23">
         <v>17</v>
       </c>
       <c r="AI23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ23">
         <v>36</v>
@@ -6265,40 +6265,40 @@
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO23">
         <v>34</v>
       </c>
       <c r="AP23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ23">
         <v>13.5</v>
       </c>
       <c r="AR23">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS23">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT23">
         <v>10.5</v>
       </c>
       <c r="AU23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23">
         <v>12</v>
       </c>
       <c r="AW23">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX23">
         <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23">
         <v>13.5</v>
@@ -6313,10 +6313,10 @@
         <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BE23">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF23">
         <v>11.5</v>
@@ -6417,7 +6417,7 @@
         <v>4.7</v>
       </c>
       <c r="J24">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24">
         <v>4.5</v>
@@ -6435,16 +6435,16 @@
         <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q24">
         <v>1.51</v>
       </c>
       <c r="R24">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S24">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T24">
         <v>1.54</v>
@@ -6498,7 +6498,7 @@
         <v>22</v>
       </c>
       <c r="AK24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL24">
         <v>25</v>
@@ -6516,13 +6516,13 @@
         <v>20</v>
       </c>
       <c r="AQ24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR24">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24">
         <v>12</v>
@@ -6546,7 +6546,7 @@
         <v>13</v>
       </c>
       <c r="BA24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB24">
         <v>18</v>
@@ -6555,16 +6555,16 @@
         <v>14.5</v>
       </c>
       <c r="BD24">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF24">
         <v>6.4</v>
       </c>
       <c r="BG24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6647,25 +6647,25 @@
         <v>151</v>
       </c>
       <c r="F25">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G25">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I25">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -6674,40 +6674,40 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
         <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R25">
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T25">
         <v>1.66</v>
       </c>
       <c r="U25">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
         <v>1.7</v>
       </c>
       <c r="X25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z25">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA25">
         <v>65</v>
@@ -6746,7 +6746,7 @@
         <v>36</v>
       </c>
       <c r="AM25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN25">
         <v>16.5</v>
@@ -6761,10 +6761,10 @@
         <v>12.5</v>
       </c>
       <c r="AR25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS25">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="AT25">
         <v>10</v>
@@ -6776,7 +6776,7 @@
         <v>12</v>
       </c>
       <c r="AW25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX25">
         <v>13.5</v>
@@ -6785,22 +6785,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA25">
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF25">
         <v>13.5</v>
@@ -6898,16 +6898,16 @@
         <v>2.58</v>
       </c>
       <c r="I26">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J26">
         <v>4.2</v>
       </c>
       <c r="K26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M26">
         <v>1.03</v>
@@ -6934,10 +6934,10 @@
         <v>1.47</v>
       </c>
       <c r="U26">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W26">
         <v>1.63</v>
@@ -7030,7 +7030,7 @@
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BB26">
         <v>8.4</v>
@@ -7051,64 +7051,64 @@
         <v>10.5</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ26">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>70</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>7.2</v>
+      </c>
+      <c r="BO26">
         <v>5.4</v>
       </c>
-      <c r="BL26">
-        <v>85</v>
-      </c>
-      <c r="BM26">
-        <v>1.02</v>
-      </c>
-      <c r="BN26">
-        <v>8.6</v>
-      </c>
-      <c r="BO26">
-        <v>4.5</v>
-      </c>
       <c r="BP26">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU26">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV26">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BW26">
         <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB26" t="s">
         <v>157</v>
@@ -7131,13 +7131,13 @@
         <v>153</v>
       </c>
       <c r="F27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I27">
         <v>1.82</v>
@@ -7146,7 +7146,7 @@
         <v>4.2</v>
       </c>
       <c r="K27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L27">
         <v>1.31</v>
@@ -7176,16 +7176,16 @@
         <v>1.69</v>
       </c>
       <c r="U27">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V27">
         <v>2.2</v>
       </c>
       <c r="W27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X27">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Y27">
         <v>11.5</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27">
         <v>10.5</v>
@@ -7212,10 +7212,10 @@
         <v>40</v>
       </c>
       <c r="AG27">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH27">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI27">
         <v>29</v>
@@ -7275,7 +7275,7 @@
         <v>24</v>
       </c>
       <c r="BB27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC27">
         <v>44</v>
@@ -7284,7 +7284,7 @@
         <v>44</v>
       </c>
       <c r="BE27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF27">
         <v>30</v>
@@ -7296,7 +7296,7 @@
         <v>4.8</v>
       </c>
       <c r="BI27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ27">
         <v>9.6</v>
@@ -7347,7 +7347,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA27">
         <v>1.01</v>
@@ -7379,7 +7379,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I28">
         <v>1.97</v>
@@ -7400,22 +7400,22 @@
         <v>3.35</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P28">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q28">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
         <v>3.95</v>
       </c>
       <c r="T28">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U28">
         <v>1.94</v>
@@ -7445,7 +7445,7 @@
         <v>8</v>
       </c>
       <c r="AD28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE28">
         <v>26</v>
@@ -7502,7 +7502,7 @@
         <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX28">
         <v>6.2</v>
@@ -7511,25 +7511,25 @@
         <v>16.5</v>
       </c>
       <c r="AZ28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB28">
+        <v>7.2</v>
+      </c>
+      <c r="BC28">
+        <v>6.8</v>
+      </c>
+      <c r="BD28">
         <v>7</v>
       </c>
-      <c r="BC28">
-        <v>6.6</v>
-      </c>
-      <c r="BD28">
-        <v>6.8</v>
-      </c>
       <c r="BE28">
+        <v>7.2</v>
+      </c>
+      <c r="BF28">
         <v>7</v>
-      </c>
-      <c r="BF28">
-        <v>6.8</v>
       </c>
       <c r="BG28">
         <v>14</v>
@@ -7624,13 +7624,13 @@
         <v>15.5</v>
       </c>
       <c r="I29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29">
         <v>6.6</v>
       </c>
       <c r="K29">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L29">
         <v>1.3</v>
@@ -7642,13 +7642,13 @@
         <v>4.8</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q29">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
         <v>1.51</v>
@@ -7669,7 +7669,7 @@
         <v>4.7</v>
       </c>
       <c r="X29">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y29">
         <v>55</v>
@@ -7681,13 +7681,13 @@
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AC29">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AD29">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AE29">
         <v>420</v>
@@ -7723,16 +7723,16 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AR29">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="AS29">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7741,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="AV29">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="AW29">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX29">
         <v>6.4</v>
@@ -7753,10 +7753,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA29">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB29">
         <v>8</v>
@@ -7765,16 +7765,16 @@
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BE29">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BF29">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BG29">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BH29">
         <v>970</v>
@@ -7804,7 +7804,7 @@
         <v>8</v>
       </c>
       <c r="BQ29">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BR29">
         <v>32</v>
@@ -7857,145 +7857,145 @@
         <v>156</v>
       </c>
       <c r="F30">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G30">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H30">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I30">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="O30">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P30">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Q30">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R30">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S30">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS30">
         <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW30">
         <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA30">
         <v>1.01</v>
@@ -8004,16 +8004,16 @@
         <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD30">
         <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG30">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -343,9 +343,15 @@
     <t>Slovenia</t>
   </si>
   <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
     <t>Luxembourg</t>
   </si>
   <si>
+    <t>Scotland</t>
+  </si>
+  <si>
     <t>Spain</t>
   </si>
   <si>
@@ -358,12 +364,6 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Bulgaria</t>
-  </si>
-  <si>
-    <t>Scotland</t>
-  </si>
-  <si>
     <t>Woking</t>
   </si>
   <si>
@@ -430,9 +430,15 @@
     <t>North Macedonia</t>
   </si>
   <si>
+    <t>Estonia</t>
+  </si>
+  <si>
     <t>Iceland</t>
   </si>
   <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
     <t>Croatia</t>
   </si>
   <si>
@@ -445,12 +451,6 @@
     <t>Kazakhstan</t>
   </si>
   <si>
-    <t>Estonia</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
     <t>Solihull Moors</t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-28 16:40:20</t>
+    <t>2026-09-28 18:51:05</t>
   </si>
 </sst>
 </file>
@@ -1081,178 +1081,178 @@
         <v>128</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U2">
+        <v>1.93</v>
+      </c>
+      <c r="V2">
+        <v>1.3</v>
+      </c>
+      <c r="W2">
         <v>1.96</v>
       </c>
-      <c r="V2">
-        <v>1.37</v>
-      </c>
-      <c r="W2">
-        <v>1.74</v>
-      </c>
       <c r="X2">
+        <v>13</v>
+      </c>
+      <c r="Y2">
+        <v>13</v>
+      </c>
+      <c r="Z2">
+        <v>30</v>
+      </c>
+      <c r="AA2">
+        <v>120</v>
+      </c>
+      <c r="AB2">
+        <v>8.4</v>
+      </c>
+      <c r="AC2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>18</v>
+      </c>
+      <c r="AE2">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
+        <v>11</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>85</v>
+      </c>
+      <c r="AJ2">
+        <v>25</v>
+      </c>
+      <c r="AK2">
+        <v>23</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
+        <v>150</v>
+      </c>
+      <c r="AN2">
+        <v>18</v>
+      </c>
+      <c r="AO2">
+        <v>120</v>
+      </c>
+      <c r="AP2">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2">
         <v>12</v>
       </c>
-      <c r="Y2">
-        <v>11.5</v>
-      </c>
-      <c r="Z2">
-        <v>25</v>
-      </c>
-      <c r="AA2">
-        <v>85</v>
-      </c>
-      <c r="AB2">
-        <v>8.6</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
-      </c>
-      <c r="AD2">
+      <c r="AR2">
+        <v>23</v>
+      </c>
+      <c r="AS2">
+        <v>55</v>
+      </c>
+      <c r="AT2">
+        <v>7.4</v>
+      </c>
+      <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
+        <v>36</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>19</v>
+      </c>
+      <c r="BA2">
+        <v>50</v>
+      </c>
+      <c r="BB2">
+        <v>21</v>
+      </c>
+      <c r="BC2">
+        <v>20</v>
+      </c>
+      <c r="BD2">
+        <v>38</v>
+      </c>
+      <c r="BE2">
+        <v>90</v>
+      </c>
+      <c r="BF2">
         <v>16</v>
       </c>
-      <c r="AE2">
-        <v>50</v>
-      </c>
-      <c r="AF2">
-        <v>13.5</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>25</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>29</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>200</v>
-      </c>
-      <c r="AN2">
-        <v>24</v>
-      </c>
-      <c r="AO2">
-        <v>90</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>10</v>
-      </c>
-      <c r="AR2">
-        <v>19.5</v>
-      </c>
-      <c r="AS2">
-        <v>50</v>
-      </c>
-      <c r="AT2">
-        <v>7.6</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>13.5</v>
-      </c>
-      <c r="AW2">
-        <v>34</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>40</v>
-      </c>
-      <c r="BB2">
-        <v>24</v>
-      </c>
-      <c r="BC2">
-        <v>22</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>12</v>
-      </c>
-      <c r="BF2">
-        <v>20</v>
-      </c>
       <c r="BG2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BL2">
         <v>170</v>
@@ -1261,46 +1261,46 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS2">
+        <v>25</v>
+      </c>
+      <c r="BT2">
+        <v>8.6</v>
+      </c>
+      <c r="BU2">
+        <v>6.4</v>
+      </c>
+      <c r="BV2">
+        <v>42</v>
+      </c>
+      <c r="BW2">
         <v>26</v>
       </c>
-      <c r="BT2">
-        <v>7.6</v>
-      </c>
-      <c r="BU2">
-        <v>5.9</v>
-      </c>
-      <c r="BV2">
+      <c r="BX2">
+        <v>60</v>
+      </c>
+      <c r="BY2">
         <v>36</v>
       </c>
-      <c r="BW2">
-        <v>23</v>
-      </c>
-      <c r="BX2">
-        <v>55</v>
-      </c>
-      <c r="BY2">
-        <v>34</v>
-      </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="s">
         <v>157</v>
@@ -1323,43 +1323,43 @@
         <v>129</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I3">
         <v>2.32</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
         <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
         <v>2.6</v>
@@ -1368,16 +1368,16 @@
         <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
         <v>1.75</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1386,19 +1386,19 @@
         <v>18</v>
       </c>
       <c r="AA3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC3">
         <v>10</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF3">
         <v>27</v>
@@ -1428,34 +1428,34 @@
         <v>23</v>
       </c>
       <c r="AO3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP3">
         <v>19</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS3">
         <v>22</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW3">
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY3">
         <v>12</v>
@@ -1464,16 +1464,16 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB3">
         <v>34</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1482,13 +1482,13 @@
         <v>17</v>
       </c>
       <c r="BG3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
@@ -1568,19 +1568,19 @@
         <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
         <v>1.34</v>
@@ -1589,43 +1589,43 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
         <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="V4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
         <v>23</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AA4">
         <v>36</v>
@@ -1634,13 +1634,13 @@
         <v>17.5</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF4">
         <v>26</v>
@@ -1649,13 +1649,13 @@
         <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AK4">
         <v>36</v>
@@ -1664,7 +1664,7 @@
         <v>44</v>
       </c>
       <c r="AM4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN4">
         <v>29</v>
@@ -1673,28 +1673,28 @@
         <v>17</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS4">
         <v>25</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
         <v>21</v>
@@ -1706,31 +1706,31 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB4">
         <v>38</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1778,7 +1778,7 @@
         <v>32</v>
       </c>
       <c r="BY4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BZ4">
         <v>24</v>
@@ -1807,58 +1807,58 @@
         <v>131</v>
       </c>
       <c r="F5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>3.6</v>
+      </c>
+      <c r="L5">
+        <v>1.44</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
         <v>3.55</v>
       </c>
-      <c r="K5">
-        <v>3.75</v>
-      </c>
-      <c r="L5">
-        <v>1.43</v>
-      </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>3.65</v>
-      </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1867,7 +1867,7 @@
         <v>14</v>
       </c>
       <c r="Z5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA5">
         <v>85</v>
@@ -1891,34 +1891,34 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI5">
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK5">
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO5">
         <v>60</v>
       </c>
       <c r="AP5">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5">
         <v>12</v>
-      </c>
-      <c r="AQ5">
-        <v>12.5</v>
       </c>
       <c r="AR5">
         <v>24</v>
@@ -1927,7 +1927,7 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
@@ -1945,10 +1945,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>22</v>
@@ -1960,25 +1960,25 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>160</v>
@@ -1987,16 +1987,16 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
         <v>19</v>
       </c>
       <c r="BQ5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR5">
         <v>38</v>
@@ -2011,10 +2011,10 @@
         <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BX5">
         <v>55</v>
@@ -2023,7 +2023,7 @@
         <v>32</v>
       </c>
       <c r="BZ5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA5">
         <v>20</v>
@@ -2052,16 +2052,16 @@
         <v>2.2</v>
       </c>
       <c r="G6">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
         <v>3.8</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.65</v>
@@ -2070,43 +2070,43 @@
         <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U6">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>26</v>
@@ -2115,10 +2115,10 @@
         <v>80</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -2133,55 +2133,55 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI6">
         <v>60</v>
       </c>
       <c r="AJ6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AM6">
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO6">
         <v>50</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
+        <v>11</v>
+      </c>
+      <c r="AR6">
         <v>11.5</v>
       </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>5.7</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY6">
         <v>9.800000000000001</v>
@@ -2190,7 +2190,7 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB6">
         <v>16</v>
@@ -2199,16 +2199,16 @@
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2291,22 +2291,22 @@
         <v>133</v>
       </c>
       <c r="F7">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.24</v>
+        <v>2.54</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
-        <v>1.46</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
-        <v>920</v>
+        <v>75</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2339,10 +2339,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2360,7 +2360,7 @@
         <v>1000</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2393,10 +2393,10 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP7">
         <v>1.01</v>
@@ -2414,7 +2414,7 @@
         <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV7">
         <v>1.01</v>
@@ -2447,7 +2447,7 @@
         <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG7">
         <v>1.01</v>
@@ -2533,25 +2533,25 @@
         <v>134</v>
       </c>
       <c r="F8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H8">
         <v>6.6</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M8">
         <v>1.09</v>
@@ -2563,10 +2563,10 @@
         <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
         <v>1.27</v>
@@ -2575,28 +2575,28 @@
         <v>4.4</v>
       </c>
       <c r="T8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U8">
         <v>1.74</v>
       </c>
       <c r="V8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X8">
         <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z8">
         <v>55</v>
       </c>
       <c r="AA8">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AB8">
         <v>6.6</v>
@@ -2617,19 +2617,19 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI8">
         <v>140</v>
       </c>
       <c r="AJ8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8">
         <v>230</v>
@@ -2638,13 +2638,13 @@
         <v>13</v>
       </c>
       <c r="AO8">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AP8">
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR8">
         <v>48</v>
@@ -2665,13 +2665,13 @@
         <v>40</v>
       </c>
       <c r="AX8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY8">
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA8">
         <v>42</v>
@@ -2686,22 +2686,22 @@
         <v>44</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
         <v>46</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK8">
         <v>10.5</v>
@@ -2713,28 +2713,28 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP8">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
         <v>10</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BS8">
         <v>24</v>
       </c>
       <c r="BT8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BV8">
         <v>90</v>
@@ -2749,7 +2749,7 @@
         <v>21</v>
       </c>
       <c r="BZ8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CA8">
         <v>20</v>
@@ -2775,16 +2775,16 @@
         <v>135</v>
       </c>
       <c r="F9">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J9">
         <v>3.05</v>
@@ -2793,7 +2793,7 @@
         <v>3.1</v>
       </c>
       <c r="L9">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M9">
         <v>1.13</v>
@@ -2805,10 +2805,10 @@
         <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R9">
         <v>1.19</v>
@@ -2820,13 +2820,13 @@
         <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X9">
         <v>8.6</v>
@@ -2850,7 +2850,7 @@
         <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2892,7 +2892,7 @@
         <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -2904,7 +2904,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
@@ -2919,7 +2919,7 @@
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="BC9">
         <v>38</v>
@@ -2934,67 +2934,67 @@
         <v>44</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BH9">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BI9">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="BK9">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BL9">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BO9">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>157</v>
@@ -3026,7 +3026,7 @@
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -3044,13 +3044,13 @@
         <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10">
         <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R10">
         <v>1.6</v>
@@ -3059,7 +3059,7 @@
         <v>2.46</v>
       </c>
       <c r="T10">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
         <v>2.18</v>
@@ -3071,13 +3071,13 @@
         <v>2.84</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="Y10">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="Z10">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AA10">
         <v>210</v>
@@ -3092,7 +3092,7 @@
         <v>32</v>
       </c>
       <c r="AE10">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3101,10 +3101,10 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AJ10">
         <v>14.5</v>
@@ -3113,16 +3113,16 @@
         <v>15.5</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN10">
         <v>6.2</v>
       </c>
       <c r="AO10">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AP10">
         <v>17.5</v>
@@ -3131,10 +3131,10 @@
         <v>24</v>
       </c>
       <c r="AR10">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10">
         <v>9.800000000000001</v>
@@ -3143,22 +3143,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AW10">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10">
         <v>12.5</v>
@@ -3167,34 +3167,34 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE10">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF10">
         <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>4.5</v>
       </c>
       <c r="BI10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL10">
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
@@ -3206,37 +3206,37 @@
         <v>9.6</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT10">
         <v>11</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB10" t="s">
         <v>157</v>
@@ -3259,19 +3259,19 @@
         <v>137</v>
       </c>
       <c r="F11">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G11">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H11">
+        <v>6.4</v>
+      </c>
+      <c r="I11">
         <v>6.8</v>
       </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
         <v>3.85</v>
@@ -3289,7 +3289,7 @@
         <v>1.45</v>
       </c>
       <c r="P11">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q11">
         <v>2.36</v>
@@ -3298,25 +3298,25 @@
         <v>1.26</v>
       </c>
       <c r="S11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U11">
         <v>1.73</v>
       </c>
       <c r="V11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X11">
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z11">
         <v>55</v>
@@ -3331,13 +3331,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE11">
         <v>140</v>
       </c>
       <c r="AF11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3364,16 +3364,16 @@
         <v>14</v>
       </c>
       <c r="AO11">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP11">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS11">
         <v>15</v>
@@ -3385,13 +3385,13 @@
         <v>8</v>
       </c>
       <c r="AV11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY11">
         <v>9.800000000000001</v>
@@ -3400,7 +3400,7 @@
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3412,7 +3412,7 @@
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF11">
         <v>12</v>
@@ -3501,226 +3501,226 @@
         <v>138</v>
       </c>
       <c r="F12">
-        <v>3.35</v>
+        <v>1.75</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="H12">
-        <v>2.42</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
         <v>1.48</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="O12">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="P12">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="T12">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="V12">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="X12">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="Z12">
+        <v>55</v>
+      </c>
+      <c r="AA12">
+        <v>220</v>
+      </c>
+      <c r="AB12">
+        <v>6.6</v>
+      </c>
+      <c r="AC12">
+        <v>8.6</v>
+      </c>
+      <c r="AD12">
+        <v>27</v>
+      </c>
+      <c r="AE12">
+        <v>130</v>
+      </c>
+      <c r="AF12">
+        <v>8.6</v>
+      </c>
+      <c r="AG12">
+        <v>11.5</v>
+      </c>
+      <c r="AH12">
+        <v>27</v>
+      </c>
+      <c r="AI12">
+        <v>130</v>
+      </c>
+      <c r="AJ12">
+        <v>17.5</v>
+      </c>
+      <c r="AK12">
+        <v>22</v>
+      </c>
+      <c r="AL12">
+        <v>55</v>
+      </c>
+      <c r="AM12">
+        <v>210</v>
+      </c>
+      <c r="AN12">
+        <v>16</v>
+      </c>
+      <c r="AO12">
+        <v>200</v>
+      </c>
+      <c r="AP12">
+        <v>9.6</v>
+      </c>
+      <c r="AQ12">
         <v>14.5</v>
       </c>
-      <c r="AA12">
-        <v>34</v>
-      </c>
-      <c r="AB12">
-        <v>12</v>
-      </c>
-      <c r="AC12">
-        <v>7.6</v>
-      </c>
-      <c r="AD12">
-        <v>12</v>
-      </c>
-      <c r="AE12">
-        <v>28</v>
-      </c>
-      <c r="AF12">
+      <c r="AR12">
+        <v>42</v>
+      </c>
+      <c r="AS12">
+        <v>15</v>
+      </c>
+      <c r="AT12">
+        <v>6</v>
+      </c>
+      <c r="AU12">
+        <v>8</v>
+      </c>
+      <c r="AV12">
         <v>23</v>
       </c>
-      <c r="AG12">
+      <c r="AW12">
+        <v>14.5</v>
+      </c>
+      <c r="AX12">
+        <v>7.8</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>25</v>
+      </c>
+      <c r="BA12">
+        <v>14.5</v>
+      </c>
+      <c r="BB12">
         <v>15</v>
       </c>
-      <c r="AH12">
-        <v>19.5</v>
-      </c>
-      <c r="AI12">
-        <v>55</v>
-      </c>
-      <c r="AJ12">
-        <v>65</v>
-      </c>
-      <c r="AK12">
-        <v>44</v>
-      </c>
-      <c r="AL12">
-        <v>60</v>
-      </c>
-      <c r="AM12">
-        <v>120</v>
-      </c>
-      <c r="AN12">
-        <v>50</v>
-      </c>
-      <c r="AO12">
-        <v>25</v>
-      </c>
-      <c r="AP12">
-        <v>11</v>
-      </c>
-      <c r="AQ12">
-        <v>8</v>
-      </c>
-      <c r="AR12">
-        <v>13</v>
-      </c>
-      <c r="AS12">
-        <v>30</v>
-      </c>
-      <c r="AT12">
-        <v>10.5</v>
-      </c>
-      <c r="AU12">
-        <v>7</v>
-      </c>
-      <c r="AV12">
-        <v>10.5</v>
-      </c>
-      <c r="AW12">
-        <v>25</v>
-      </c>
-      <c r="AX12">
+      <c r="BC12">
         <v>20</v>
-      </c>
-      <c r="AY12">
-        <v>13</v>
-      </c>
-      <c r="AZ12">
-        <v>17.5</v>
-      </c>
-      <c r="BA12">
-        <v>40</v>
-      </c>
-      <c r="BB12">
-        <v>55</v>
-      </c>
-      <c r="BC12">
-        <v>38</v>
       </c>
       <c r="BD12">
         <v>46</v>
       </c>
       <c r="BE12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF12">
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="BG12">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BH12">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BI12">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL12">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="BP12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BU12">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BV12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
         <v>157</v>
@@ -3743,226 +3743,226 @@
         <v>139</v>
       </c>
       <c r="F13">
-        <v>1.21</v>
+        <v>3.55</v>
       </c>
       <c r="G13">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>2.32</v>
       </c>
       <c r="I13">
+        <v>2.36</v>
+      </c>
+      <c r="J13">
+        <v>3.4</v>
+      </c>
+      <c r="K13">
+        <v>3.45</v>
+      </c>
+      <c r="L13">
+        <v>1.48</v>
+      </c>
+      <c r="M13">
+        <v>1.09</v>
+      </c>
+      <c r="N13">
+        <v>3.35</v>
+      </c>
+      <c r="O13">
+        <v>1.4</v>
+      </c>
+      <c r="P13">
+        <v>1.8</v>
+      </c>
+      <c r="Q13">
+        <v>2.18</v>
+      </c>
+      <c r="R13">
+        <v>1.3</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>1.91</v>
+      </c>
+      <c r="U13">
+        <v>2.04</v>
+      </c>
+      <c r="V13">
+        <v>1.73</v>
+      </c>
+      <c r="W13">
+        <v>1.38</v>
+      </c>
+      <c r="X13">
+        <v>12</v>
+      </c>
+      <c r="Y13">
+        <v>9</v>
+      </c>
+      <c r="Z13">
+        <v>13.5</v>
+      </c>
+      <c r="AA13">
+        <v>30</v>
+      </c>
+      <c r="AB13">
+        <v>12.5</v>
+      </c>
+      <c r="AC13">
+        <v>7.6</v>
+      </c>
+      <c r="AD13">
+        <v>12</v>
+      </c>
+      <c r="AE13">
+        <v>29</v>
+      </c>
+      <c r="AF13">
+        <v>25</v>
+      </c>
+      <c r="AG13">
+        <v>15.5</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>55</v>
+      </c>
+      <c r="AJ13">
+        <v>70</v>
+      </c>
+      <c r="AK13">
+        <v>48</v>
+      </c>
+      <c r="AL13">
+        <v>60</v>
+      </c>
+      <c r="AM13">
+        <v>120</v>
+      </c>
+      <c r="AN13">
+        <v>55</v>
+      </c>
+      <c r="AO13">
+        <v>23</v>
+      </c>
+      <c r="AP13">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13">
+        <v>8.4</v>
+      </c>
+      <c r="AR13">
+        <v>12</v>
+      </c>
+      <c r="AS13">
+        <v>25</v>
+      </c>
+      <c r="AT13">
+        <v>10.5</v>
+      </c>
+      <c r="AU13">
+        <v>7</v>
+      </c>
+      <c r="AV13">
+        <v>10.5</v>
+      </c>
+      <c r="AW13">
+        <v>23</v>
+      </c>
+      <c r="AX13">
+        <v>20</v>
+      </c>
+      <c r="AY13">
+        <v>13.5</v>
+      </c>
+      <c r="AZ13">
         <v>17.5</v>
       </c>
-      <c r="J13">
-        <v>8</v>
-      </c>
-      <c r="K13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L13">
-        <v>1.27</v>
-      </c>
-      <c r="M13">
-        <v>1.03</v>
-      </c>
-      <c r="N13">
-        <v>6.6</v>
-      </c>
-      <c r="O13">
-        <v>1.16</v>
-      </c>
-      <c r="P13">
-        <v>2.94</v>
-      </c>
-      <c r="Q13">
-        <v>1.5</v>
-      </c>
-      <c r="R13">
-        <v>1.76</v>
-      </c>
-      <c r="S13">
-        <v>2.26</v>
-      </c>
-      <c r="T13">
-        <v>2.22</v>
-      </c>
-      <c r="U13">
-        <v>1.79</v>
-      </c>
-      <c r="V13">
-        <v>1.06</v>
-      </c>
-      <c r="W13">
-        <v>5.5</v>
-      </c>
-      <c r="X13">
-        <v>34</v>
-      </c>
-      <c r="Y13">
+      <c r="BA13">
+        <v>38</v>
+      </c>
+      <c r="BB13">
         <v>55</v>
       </c>
-      <c r="Z13">
-        <v>180</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>11.5</v>
-      </c>
-      <c r="AC13">
+      <c r="BC13">
+        <v>38</v>
+      </c>
+      <c r="BD13">
+        <v>46</v>
+      </c>
+      <c r="BE13">
+        <v>13.5</v>
+      </c>
+      <c r="BF13">
+        <v>40</v>
+      </c>
+      <c r="BG13">
         <v>18.5</v>
       </c>
-      <c r="AD13">
-        <v>60</v>
-      </c>
-      <c r="AE13">
-        <v>320</v>
-      </c>
-      <c r="AF13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>40</v>
-      </c>
-      <c r="AI13">
-        <v>210</v>
-      </c>
-      <c r="AJ13">
+      <c r="BH13">
+        <v>3.1</v>
+      </c>
+      <c r="BI13">
+        <v>2.84</v>
+      </c>
+      <c r="BJ13">
+        <v>10.5</v>
+      </c>
+      <c r="BK13">
         <v>8.800000000000001</v>
       </c>
-      <c r="AK13">
-        <v>14</v>
-      </c>
-      <c r="AL13">
-        <v>42</v>
-      </c>
-      <c r="AM13">
-        <v>250</v>
-      </c>
-      <c r="AN13">
-        <v>3.55</v>
-      </c>
-      <c r="AO13">
-        <v>490</v>
-      </c>
-      <c r="AP13">
-        <v>29</v>
-      </c>
-      <c r="AQ13">
-        <v>38</v>
-      </c>
-      <c r="AR13">
-        <v>15</v>
-      </c>
-      <c r="AS13">
-        <v>16</v>
-      </c>
-      <c r="AT13">
-        <v>10</v>
-      </c>
-      <c r="AU13">
-        <v>16</v>
-      </c>
-      <c r="AV13">
-        <v>42</v>
-      </c>
-      <c r="AW13">
-        <v>15.5</v>
-      </c>
-      <c r="AX13">
-        <v>7.4</v>
-      </c>
-      <c r="AY13">
-        <v>11</v>
-      </c>
-      <c r="AZ13">
-        <v>30</v>
-      </c>
-      <c r="BA13">
-        <v>15</v>
-      </c>
-      <c r="BB13">
-        <v>8</v>
-      </c>
-      <c r="BC13">
-        <v>12</v>
-      </c>
-      <c r="BD13">
-        <v>34</v>
-      </c>
-      <c r="BE13">
-        <v>15</v>
-      </c>
-      <c r="BF13">
-        <v>3.35</v>
-      </c>
-      <c r="BG13">
-        <v>15.5</v>
-      </c>
-      <c r="BH13">
-        <v>4.7</v>
-      </c>
-      <c r="BI13">
-        <v>4.1</v>
-      </c>
-      <c r="BJ13">
-        <v>16</v>
-      </c>
-      <c r="BK13">
-        <v>11.5</v>
-      </c>
       <c r="BL13">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="BM13">
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO13">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="BP13">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BQ13">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="BR13">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="BS13">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="BT13">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="BU13">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="BV13">
-        <v>160</v>
+        <v>17.5</v>
       </c>
       <c r="BW13">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BX13">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="BY13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CB13" t="s">
         <v>157</v>
@@ -3985,226 +3985,226 @@
         <v>140</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>4.7</v>
       </c>
       <c r="H14">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="I14">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="J14">
-        <v>22</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
-        <v>24</v>
+        <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N14">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="P14">
-        <v>3.35</v>
+        <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="R14">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
+        <v>4.3</v>
+      </c>
+      <c r="T14">
+        <v>2.04</v>
+      </c>
+      <c r="U14">
+        <v>1.91</v>
+      </c>
+      <c r="V14">
         <v>2.02</v>
       </c>
-      <c r="T14">
-        <v>4.4</v>
-      </c>
-      <c r="U14">
+      <c r="W14">
         <v>1.27</v>
       </c>
-      <c r="V14">
-        <v>16</v>
-      </c>
-      <c r="W14">
-        <v>1.01</v>
-      </c>
       <c r="X14">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AB14">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>80</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AE14">
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH14">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="AI14">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO14">
-        <v>2.46</v>
+        <v>17</v>
       </c>
       <c r="AP14">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14">
+        <v>7.2</v>
+      </c>
+      <c r="AR14">
         <v>10</v>
       </c>
-      <c r="AR14">
-        <v>6.2</v>
-      </c>
       <c r="AS14">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AT14">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AU14">
+        <v>7.8</v>
+      </c>
+      <c r="AV14">
+        <v>10</v>
+      </c>
+      <c r="AW14">
+        <v>21</v>
+      </c>
+      <c r="AX14">
         <v>29</v>
       </c>
-      <c r="AV14">
-        <v>18</v>
-      </c>
-      <c r="AW14">
-        <v>18</v>
-      </c>
-      <c r="AX14">
-        <v>15</v>
-      </c>
       <c r="AY14">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA14">
         <v>40</v>
       </c>
       <c r="BB14">
+        <v>100</v>
+      </c>
+      <c r="BC14">
+        <v>55</v>
+      </c>
+      <c r="BD14">
+        <v>50</v>
+      </c>
+      <c r="BE14">
+        <v>130</v>
+      </c>
+      <c r="BF14">
+        <v>80</v>
+      </c>
+      <c r="BG14">
         <v>15</v>
       </c>
-      <c r="BC14">
-        <v>15</v>
-      </c>
-      <c r="BD14">
-        <v>15</v>
-      </c>
-      <c r="BE14">
-        <v>15</v>
-      </c>
-      <c r="BF14">
-        <v>15</v>
-      </c>
-      <c r="BG14">
-        <v>2.28</v>
-      </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BT14">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="BU14">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>3.9</v>
+        <v>2.98</v>
       </c>
       <c r="CB14" t="s">
         <v>157</v>
@@ -4227,226 +4227,226 @@
         <v>141</v>
       </c>
       <c r="F15">
-        <v>10.5</v>
+        <v>1.22</v>
       </c>
       <c r="G15">
+        <v>1.23</v>
+      </c>
+      <c r="H15">
+        <v>17</v>
+      </c>
+      <c r="I15">
+        <v>17.5</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <v>8.4</v>
+      </c>
+      <c r="L15">
+        <v>1.27</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>6.6</v>
+      </c>
+      <c r="O15">
+        <v>1.16</v>
+      </c>
+      <c r="P15">
+        <v>2.96</v>
+      </c>
+      <c r="Q15">
+        <v>1.5</v>
+      </c>
+      <c r="R15">
+        <v>1.79</v>
+      </c>
+      <c r="S15">
+        <v>2.22</v>
+      </c>
+      <c r="T15">
+        <v>2.18</v>
+      </c>
+      <c r="U15">
+        <v>1.8</v>
+      </c>
+      <c r="V15">
+        <v>1.06</v>
+      </c>
+      <c r="W15">
+        <v>5.4</v>
+      </c>
+      <c r="X15">
+        <v>34</v>
+      </c>
+      <c r="Y15">
+        <v>55</v>
+      </c>
+      <c r="Z15">
+        <v>200</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>11.5</v>
+      </c>
+      <c r="AC15">
+        <v>18.5</v>
+      </c>
+      <c r="AD15">
+        <v>60</v>
+      </c>
+      <c r="AE15">
+        <v>320</v>
+      </c>
+      <c r="AF15">
+        <v>8.4</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>40</v>
+      </c>
+      <c r="AI15">
+        <v>210</v>
+      </c>
+      <c r="AJ15">
+        <v>9</v>
+      </c>
+      <c r="AK15">
+        <v>14</v>
+      </c>
+      <c r="AL15">
+        <v>42</v>
+      </c>
+      <c r="AM15">
+        <v>230</v>
+      </c>
+      <c r="AN15">
+        <v>3.55</v>
+      </c>
+      <c r="AO15">
+        <v>460</v>
+      </c>
+      <c r="AP15">
+        <v>29</v>
+      </c>
+      <c r="AQ15">
+        <v>44</v>
+      </c>
+      <c r="AR15">
+        <v>16</v>
+      </c>
+      <c r="AS15">
+        <v>16</v>
+      </c>
+      <c r="AT15">
+        <v>10</v>
+      </c>
+      <c r="AU15">
+        <v>16</v>
+      </c>
+      <c r="AV15">
+        <v>44</v>
+      </c>
+      <c r="AW15">
+        <v>44</v>
+      </c>
+      <c r="AX15">
+        <v>7.6</v>
+      </c>
+      <c r="AY15">
         <v>11</v>
       </c>
-      <c r="H15">
-        <v>1.38</v>
-      </c>
-      <c r="I15">
-        <v>1.39</v>
-      </c>
-      <c r="J15">
-        <v>5.3</v>
-      </c>
-      <c r="K15">
-        <v>5.5</v>
-      </c>
-      <c r="L15">
-        <v>1.34</v>
-      </c>
-      <c r="M15">
-        <v>1.05</v>
-      </c>
-      <c r="N15">
-        <v>4.8</v>
-      </c>
-      <c r="O15">
-        <v>1.24</v>
-      </c>
-      <c r="P15">
-        <v>2.34</v>
-      </c>
-      <c r="Q15">
-        <v>1.71</v>
-      </c>
-      <c r="R15">
-        <v>1.51</v>
-      </c>
-      <c r="S15">
-        <v>2.78</v>
-      </c>
-      <c r="T15">
-        <v>2.08</v>
-      </c>
-      <c r="U15">
-        <v>1.87</v>
-      </c>
-      <c r="V15">
+      <c r="AZ15">
+        <v>34</v>
+      </c>
+      <c r="BA15">
+        <v>15.5</v>
+      </c>
+      <c r="BB15">
+        <v>8.4</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
+        <v>36</v>
+      </c>
+      <c r="BE15">
+        <v>15.5</v>
+      </c>
+      <c r="BF15">
+        <v>3.3</v>
+      </c>
+      <c r="BG15">
+        <v>85</v>
+      </c>
+      <c r="BH15">
+        <v>4.7</v>
+      </c>
+      <c r="BI15">
+        <v>4.3</v>
+      </c>
+      <c r="BJ15">
+        <v>13</v>
+      </c>
+      <c r="BK15">
+        <v>11.5</v>
+      </c>
+      <c r="BL15">
+        <v>190</v>
+      </c>
+      <c r="BM15">
+        <v>13.5</v>
+      </c>
+      <c r="BN15">
+        <v>3.8</v>
+      </c>
+      <c r="BO15">
         <v>3.55</v>
       </c>
-      <c r="W15">
-        <v>1.1</v>
-      </c>
-      <c r="X15">
-        <v>19.5</v>
-      </c>
-      <c r="Y15">
+      <c r="BP15">
+        <v>6.4</v>
+      </c>
+      <c r="BQ15">
+        <v>5.8</v>
+      </c>
+      <c r="BR15">
+        <v>22</v>
+      </c>
+      <c r="BS15">
         <v>9</v>
       </c>
-      <c r="Z15">
-        <v>8</v>
-      </c>
-      <c r="AA15">
-        <v>11</v>
-      </c>
-      <c r="AB15">
-        <v>32</v>
-      </c>
-      <c r="AC15">
-        <v>12.5</v>
-      </c>
-      <c r="AD15">
-        <v>10.5</v>
-      </c>
-      <c r="AE15">
-        <v>14.5</v>
-      </c>
-      <c r="AF15">
-        <v>95</v>
-      </c>
-      <c r="AG15">
-        <v>38</v>
-      </c>
-      <c r="AH15">
-        <v>26</v>
-      </c>
-      <c r="AI15">
-        <v>36</v>
-      </c>
-      <c r="AJ15">
-        <v>460</v>
-      </c>
-      <c r="AK15">
-        <v>180</v>
-      </c>
-      <c r="AL15">
-        <v>140</v>
-      </c>
-      <c r="AM15">
+      <c r="BT15">
+        <v>17</v>
+      </c>
+      <c r="BU15">
+        <v>8.6</v>
+      </c>
+      <c r="BV15">
         <v>160</v>
       </c>
-      <c r="AN15">
-        <v>240</v>
-      </c>
-      <c r="AO15">
-        <v>5.5</v>
-      </c>
-      <c r="AP15">
-        <v>19</v>
-      </c>
-      <c r="AQ15">
-        <v>8.6</v>
-      </c>
-      <c r="AR15">
-        <v>7.8</v>
-      </c>
-      <c r="AS15">
-        <v>10.5</v>
-      </c>
-      <c r="AT15">
-        <v>28</v>
-      </c>
-      <c r="AU15">
-        <v>11.5</v>
-      </c>
-      <c r="AV15">
-        <v>10</v>
-      </c>
-      <c r="AW15">
+      <c r="BW15">
         <v>13.5</v>
       </c>
-      <c r="AX15">
-        <v>80</v>
-      </c>
-      <c r="AY15">
-        <v>30</v>
-      </c>
-      <c r="AZ15">
-        <v>25</v>
-      </c>
-      <c r="BA15">
-        <v>34</v>
-      </c>
-      <c r="BB15">
-        <v>25</v>
-      </c>
-      <c r="BC15">
-        <v>140</v>
-      </c>
-      <c r="BD15">
+      <c r="BX15">
         <v>120</v>
       </c>
-      <c r="BE15">
-        <v>140</v>
-      </c>
-      <c r="BF15">
-        <v>150</v>
-      </c>
-      <c r="BG15">
-        <v>5.1</v>
-      </c>
-      <c r="BH15">
-        <v>3.8</v>
-      </c>
-      <c r="BI15">
-        <v>3.6</v>
-      </c>
-      <c r="BJ15">
-        <v>14</v>
-      </c>
-      <c r="BK15">
-        <v>10.5</v>
-      </c>
-      <c r="BL15">
-        <v>180</v>
-      </c>
-      <c r="BM15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN15">
-        <v>15.5</v>
-      </c>
-      <c r="BO15">
-        <v>11</v>
-      </c>
-      <c r="BP15">
-        <v>110</v>
-      </c>
-      <c r="BQ15">
-        <v>9.4</v>
-      </c>
-      <c r="BR15">
-        <v>95</v>
-      </c>
-      <c r="BS15">
-        <v>9.4</v>
-      </c>
-      <c r="BT15">
-        <v>3.8</v>
-      </c>
-      <c r="BU15">
-        <v>3.5</v>
-      </c>
-      <c r="BV15">
-        <v>8</v>
-      </c>
-      <c r="BW15">
-        <v>7</v>
-      </c>
-      <c r="BX15">
-        <v>28</v>
-      </c>
       <c r="BY15">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
         <v>157</v>
@@ -4469,226 +4469,226 @@
         <v>142</v>
       </c>
       <c r="F16">
-        <v>1.3</v>
+        <v>60</v>
       </c>
       <c r="G16">
-        <v>1.32</v>
+        <v>110</v>
       </c>
       <c r="H16">
-        <v>13.5</v>
+        <v>1.05</v>
       </c>
       <c r="I16">
-        <v>15</v>
+        <v>1.06</v>
       </c>
       <c r="J16">
+        <v>22</v>
+      </c>
+      <c r="K16">
+        <v>25</v>
+      </c>
+      <c r="L16">
+        <v>1.17</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>7.8</v>
+      </c>
+      <c r="O16">
+        <v>1.12</v>
+      </c>
+      <c r="P16">
+        <v>3.35</v>
+      </c>
+      <c r="Q16">
+        <v>1.39</v>
+      </c>
+      <c r="R16">
+        <v>1.91</v>
+      </c>
+      <c r="S16">
+        <v>2.04</v>
+      </c>
+      <c r="T16">
+        <v>4.4</v>
+      </c>
+      <c r="U16">
+        <v>1.27</v>
+      </c>
+      <c r="V16">
+        <v>17.5</v>
+      </c>
+      <c r="W16">
+        <v>1.01</v>
+      </c>
+      <c r="X16">
+        <v>55</v>
+      </c>
+      <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>7</v>
+      </c>
+      <c r="AA16">
         <v>6</v>
       </c>
-      <c r="K16">
-        <v>6.2</v>
-      </c>
-      <c r="L16">
-        <v>1.38</v>
-      </c>
-      <c r="M16">
-        <v>1.06</v>
-      </c>
-      <c r="N16">
-        <v>4.1</v>
-      </c>
-      <c r="O16">
-        <v>1.3</v>
-      </c>
-      <c r="P16">
-        <v>2.06</v>
-      </c>
-      <c r="Q16">
-        <v>1.88</v>
-      </c>
-      <c r="R16">
-        <v>1.41</v>
-      </c>
-      <c r="S16">
-        <v>3.2</v>
-      </c>
-      <c r="T16">
-        <v>2.64</v>
-      </c>
-      <c r="U16">
-        <v>1.57</v>
-      </c>
-      <c r="V16">
-        <v>1.07</v>
-      </c>
-      <c r="W16">
-        <v>4.2</v>
-      </c>
-      <c r="X16">
-        <v>16</v>
-      </c>
-      <c r="Y16">
-        <v>38</v>
-      </c>
-      <c r="Z16">
-        <v>180</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
       <c r="AB16">
-        <v>7.4</v>
+        <v>200</v>
       </c>
       <c r="AC16">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="AD16">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AE16">
-        <v>370</v>
+        <v>24</v>
       </c>
       <c r="AF16">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>450</v>
       </c>
       <c r="AH16">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="AI16">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AJ16">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>600</v>
+        <v>2.62</v>
       </c>
       <c r="AP16">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AQ16">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="AS16">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="AT16">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AU16">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AV16">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AW16">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AX16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA16">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="BB16">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BC16">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="BE16">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BF16">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>2.26</v>
       </c>
       <c r="BH16">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="BN16">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>6.4</v>
+        <v>150</v>
       </c>
       <c r="BR16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="BT16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>9.4</v>
+        <v>2.86</v>
       </c>
       <c r="BV16">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="CB16" t="s">
         <v>157</v>
@@ -4711,226 +4711,226 @@
         <v>143</v>
       </c>
       <c r="F17">
-        <v>1.71</v>
+        <v>10.5</v>
       </c>
       <c r="G17">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="H17">
-        <v>6.2</v>
+        <v>1.36</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>1.38</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="K17">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="L17">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>2.68</v>
       </c>
       <c r="T17">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="U17">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="V17">
-        <v>1.17</v>
+        <v>3.65</v>
       </c>
       <c r="W17">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
+        <v>22</v>
+      </c>
+      <c r="Y17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z17">
+        <v>8.4</v>
+      </c>
+      <c r="AA17">
         <v>10.5</v>
       </c>
-      <c r="Y17">
-        <v>16.5</v>
-      </c>
-      <c r="Z17">
-        <v>55</v>
-      </c>
-      <c r="AA17">
+      <c r="AB17">
+        <v>36</v>
+      </c>
+      <c r="AC17">
+        <v>13</v>
+      </c>
+      <c r="AD17">
+        <v>10.5</v>
+      </c>
+      <c r="AE17">
+        <v>14.5</v>
+      </c>
+      <c r="AF17">
+        <v>110</v>
+      </c>
+      <c r="AG17">
+        <v>38</v>
+      </c>
+      <c r="AH17">
+        <v>26</v>
+      </c>
+      <c r="AI17">
+        <v>36</v>
+      </c>
+      <c r="AJ17">
+        <v>430</v>
+      </c>
+      <c r="AK17">
+        <v>170</v>
+      </c>
+      <c r="AL17">
+        <v>140</v>
+      </c>
+      <c r="AM17">
+        <v>160</v>
+      </c>
+      <c r="AN17">
         <v>240</v>
       </c>
-      <c r="AB17">
-        <v>6.6</v>
-      </c>
-      <c r="AC17">
+      <c r="AO17">
+        <v>5.3</v>
+      </c>
+      <c r="AP17">
+        <v>20</v>
+      </c>
+      <c r="AQ17">
         <v>8.6</v>
       </c>
-      <c r="AD17">
-        <v>27</v>
-      </c>
-      <c r="AE17">
-        <v>130</v>
-      </c>
-      <c r="AF17">
-        <v>8.4</v>
-      </c>
-      <c r="AG17">
-        <v>11</v>
-      </c>
-      <c r="AH17">
-        <v>28</v>
-      </c>
-      <c r="AI17">
-        <v>140</v>
-      </c>
-      <c r="AJ17">
-        <v>17</v>
-      </c>
-      <c r="AK17">
-        <v>22</v>
-      </c>
-      <c r="AL17">
-        <v>60</v>
-      </c>
-      <c r="AM17">
-        <v>220</v>
-      </c>
-      <c r="AN17">
-        <v>15.5</v>
-      </c>
-      <c r="AO17">
-        <v>220</v>
-      </c>
-      <c r="AP17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ17">
-        <v>14.5</v>
-      </c>
       <c r="AR17">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AS17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AT17">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AU17">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AV17">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AW17">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AX17">
-        <v>7.8</v>
+        <v>85</v>
       </c>
       <c r="AY17">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AZ17">
         <v>25</v>
       </c>
       <c r="BA17">
+        <v>34</v>
+      </c>
+      <c r="BB17">
+        <v>24</v>
+      </c>
+      <c r="BC17">
+        <v>130</v>
+      </c>
+      <c r="BD17">
+        <v>120</v>
+      </c>
+      <c r="BE17">
+        <v>140</v>
+      </c>
+      <c r="BF17">
+        <v>140</v>
+      </c>
+      <c r="BG17">
+        <v>5.1</v>
+      </c>
+      <c r="BH17">
+        <v>3.85</v>
+      </c>
+      <c r="BI17">
+        <v>3.7</v>
+      </c>
+      <c r="BJ17">
+        <v>14</v>
+      </c>
+      <c r="BK17">
+        <v>10.5</v>
+      </c>
+      <c r="BL17">
+        <v>180</v>
+      </c>
+      <c r="BM17">
+        <v>9.4</v>
+      </c>
+      <c r="BN17">
+        <v>15.5</v>
+      </c>
+      <c r="BO17">
+        <v>11</v>
+      </c>
+      <c r="BP17">
+        <v>110</v>
+      </c>
+      <c r="BQ17">
+        <v>9</v>
+      </c>
+      <c r="BR17">
+        <v>95</v>
+      </c>
+      <c r="BS17">
+        <v>9</v>
+      </c>
+      <c r="BT17">
+        <v>3.8</v>
+      </c>
+      <c r="BU17">
+        <v>3.5</v>
+      </c>
+      <c r="BV17">
+        <v>8</v>
+      </c>
+      <c r="BW17">
+        <v>7</v>
+      </c>
+      <c r="BX17">
+        <v>28</v>
+      </c>
+      <c r="BY17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ17">
         <v>15</v>
       </c>
-      <c r="BB17">
-        <v>15</v>
-      </c>
-      <c r="BC17">
-        <v>20</v>
-      </c>
-      <c r="BD17">
-        <v>48</v>
-      </c>
-      <c r="BE17">
-        <v>15</v>
-      </c>
-      <c r="BF17">
-        <v>13.5</v>
-      </c>
-      <c r="BG17">
-        <v>15</v>
-      </c>
-      <c r="BH17">
-        <v>2.96</v>
-      </c>
-      <c r="BI17">
-        <v>2.58</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>8.6</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>4.5</v>
-      </c>
-      <c r="BO17">
-        <v>3.35</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.01</v>
-      </c>
-      <c r="BT17">
-        <v>20</v>
-      </c>
-      <c r="BU17">
-        <v>7.2</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.01</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.01</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4953,226 +4953,226 @@
         <v>144</v>
       </c>
       <c r="F18">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="G18">
-        <v>4.7</v>
+        <v>1.31</v>
       </c>
       <c r="H18">
-        <v>1.96</v>
+        <v>14</v>
       </c>
       <c r="I18">
-        <v>1.97</v>
+        <v>16.5</v>
       </c>
       <c r="J18">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>1.3</v>
+      </c>
+      <c r="P18">
+        <v>2.08</v>
+      </c>
+      <c r="Q18">
+        <v>1.87</v>
+      </c>
+      <c r="R18">
+        <v>1.41</v>
+      </c>
+      <c r="S18">
         <v>3.25</v>
       </c>
-      <c r="O18">
-        <v>1.42</v>
-      </c>
-      <c r="P18">
-        <v>1.74</v>
-      </c>
-      <c r="Q18">
-        <v>2.28</v>
-      </c>
-      <c r="R18">
-        <v>1.28</v>
-      </c>
-      <c r="S18">
-        <v>4.3</v>
-      </c>
       <c r="T18">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="U18">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="V18">
-        <v>2.02</v>
+        <v>1.06</v>
       </c>
       <c r="W18">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="X18">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y18">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="Z18">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>7.4</v>
+      </c>
+      <c r="AC18">
+        <v>14</v>
+      </c>
+      <c r="AD18">
+        <v>60</v>
+      </c>
+      <c r="AE18">
+        <v>370</v>
+      </c>
+      <c r="AF18">
+        <v>6.8</v>
+      </c>
+      <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>48</v>
+      </c>
+      <c r="AI18">
+        <v>300</v>
+      </c>
+      <c r="AJ18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK18">
+        <v>17</v>
+      </c>
+      <c r="AL18">
+        <v>95</v>
+      </c>
+      <c r="AM18">
+        <v>390</v>
+      </c>
+      <c r="AN18">
+        <v>5.8</v>
+      </c>
+      <c r="AO18">
+        <v>600</v>
+      </c>
+      <c r="AP18">
+        <v>15</v>
+      </c>
+      <c r="AQ18">
+        <v>32</v>
+      </c>
+      <c r="AR18">
+        <v>13</v>
+      </c>
+      <c r="AS18">
+        <v>14</v>
+      </c>
+      <c r="AT18">
+        <v>6.6</v>
+      </c>
+      <c r="AU18">
+        <v>12.5</v>
+      </c>
+      <c r="AV18">
+        <v>44</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+      <c r="AX18">
+        <v>6</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>36</v>
+      </c>
+      <c r="BA18">
+        <v>13.5</v>
+      </c>
+      <c r="BB18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC18">
+        <v>14.5</v>
+      </c>
+      <c r="BD18">
+        <v>46</v>
+      </c>
+      <c r="BE18">
+        <v>14</v>
+      </c>
+      <c r="BF18">
+        <v>5.2</v>
+      </c>
+      <c r="BG18">
+        <v>14</v>
+      </c>
+      <c r="BH18">
+        <v>3.7</v>
+      </c>
+      <c r="BI18">
+        <v>3.35</v>
+      </c>
+      <c r="BJ18">
+        <v>15.5</v>
+      </c>
+      <c r="BK18">
+        <v>13</v>
+      </c>
+      <c r="BL18">
+        <v>330</v>
+      </c>
+      <c r="BM18">
+        <v>21</v>
+      </c>
+      <c r="BN18">
+        <v>3.45</v>
+      </c>
+      <c r="BO18">
+        <v>3.15</v>
+      </c>
+      <c r="BP18">
+        <v>7.4</v>
+      </c>
+      <c r="BQ18">
+        <v>6.4</v>
+      </c>
+      <c r="BR18">
+        <v>32</v>
+      </c>
+      <c r="BS18">
         <v>23</v>
       </c>
-      <c r="AB18">
+      <c r="BT18">
+        <v>18</v>
+      </c>
+      <c r="BU18">
+        <v>9.4</v>
+      </c>
+      <c r="BV18">
+        <v>220</v>
+      </c>
+      <c r="BW18">
+        <v>21</v>
+      </c>
+      <c r="BX18">
+        <v>180</v>
+      </c>
+      <c r="BY18">
+        <v>21</v>
+      </c>
+      <c r="BZ18">
         <v>14</v>
       </c>
-      <c r="AC18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD18">
+      <c r="CA18">
         <v>10.5</v>
-      </c>
-      <c r="AE18">
-        <v>23</v>
-      </c>
-      <c r="AF18">
-        <v>34</v>
-      </c>
-      <c r="AG18">
-        <v>19</v>
-      </c>
-      <c r="AH18">
-        <v>24</v>
-      </c>
-      <c r="AI18">
-        <v>46</v>
-      </c>
-      <c r="AJ18">
-        <v>130</v>
-      </c>
-      <c r="AK18">
-        <v>70</v>
-      </c>
-      <c r="AL18">
-        <v>85</v>
-      </c>
-      <c r="AM18">
-        <v>150</v>
-      </c>
-      <c r="AN18">
-        <v>100</v>
-      </c>
-      <c r="AO18">
-        <v>17</v>
-      </c>
-      <c r="AP18">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18">
-        <v>7.4</v>
-      </c>
-      <c r="AR18">
-        <v>10</v>
-      </c>
-      <c r="AS18">
-        <v>21</v>
-      </c>
-      <c r="AT18">
-        <v>13</v>
-      </c>
-      <c r="AU18">
-        <v>7.6</v>
-      </c>
-      <c r="AV18">
-        <v>10</v>
-      </c>
-      <c r="AW18">
-        <v>21</v>
-      </c>
-      <c r="AX18">
-        <v>29</v>
-      </c>
-      <c r="AY18">
-        <v>17.5</v>
-      </c>
-      <c r="AZ18">
-        <v>21</v>
-      </c>
-      <c r="BA18">
-        <v>40</v>
-      </c>
-      <c r="BB18">
-        <v>100</v>
-      </c>
-      <c r="BC18">
-        <v>46</v>
-      </c>
-      <c r="BD18">
-        <v>70</v>
-      </c>
-      <c r="BE18">
-        <v>130</v>
-      </c>
-      <c r="BF18">
-        <v>70</v>
-      </c>
-      <c r="BG18">
-        <v>16</v>
-      </c>
-      <c r="BH18">
-        <v>3.3</v>
-      </c>
-      <c r="BI18">
-        <v>2.6</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>2.58</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>2.92</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>5.9</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>2.96</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>2.96</v>
-      </c>
-      <c r="BT18">
-        <v>5.3</v>
-      </c>
-      <c r="BU18">
-        <v>3.7</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>2.8</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>2.96</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
-      <c r="CA18">
-        <v>2.96</v>
       </c>
       <c r="CB18" t="s">
         <v>157</v>
@@ -5204,7 +5204,7 @@
         <v>3.6</v>
       </c>
       <c r="I19">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J19">
         <v>3.9</v>
@@ -5225,7 +5225,7 @@
         <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q19">
         <v>1.63</v>
@@ -5234,7 +5234,7 @@
         <v>1.57</v>
       </c>
       <c r="S19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T19">
         <v>1.6</v>
@@ -5261,10 +5261,10 @@
         <v>75</v>
       </c>
       <c r="AB19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
         <v>18.5</v>
@@ -5273,7 +5273,7 @@
         <v>38</v>
       </c>
       <c r="AF19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG19">
         <v>11.5</v>
@@ -5294,7 +5294,7 @@
         <v>32</v>
       </c>
       <c r="AM19">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN19">
         <v>10.5</v>
@@ -5309,10 +5309,10 @@
         <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT19">
         <v>11.5</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="AW19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX19">
         <v>13</v>
@@ -5336,7 +5336,7 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB19">
         <v>21</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF19">
         <v>9</v>
@@ -5384,7 +5384,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR19">
         <v>26</v>
@@ -5408,13 +5408,13 @@
         <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ19">
         <v>19</v>
       </c>
       <c r="CA19">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>157</v>
@@ -5437,22 +5437,22 @@
         <v>146</v>
       </c>
       <c r="F20">
+        <v>3.65</v>
+      </c>
+      <c r="G20">
+        <v>3.85</v>
+      </c>
+      <c r="H20">
+        <v>2.04</v>
+      </c>
+      <c r="I20">
+        <v>2.06</v>
+      </c>
+      <c r="J20">
+        <v>3.9</v>
+      </c>
+      <c r="K20">
         <v>4.1</v>
-      </c>
-      <c r="G20">
-        <v>4.3</v>
-      </c>
-      <c r="H20">
-        <v>1.88</v>
-      </c>
-      <c r="I20">
-        <v>1.92</v>
-      </c>
-      <c r="J20">
-        <v>4.1</v>
-      </c>
-      <c r="K20">
-        <v>4.4</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5461,151 +5461,151 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q20">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R20">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S20">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V20">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="W20">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X20">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y20">
+        <v>12</v>
+      </c>
+      <c r="Z20">
+        <v>14.5</v>
+      </c>
+      <c r="AA20">
+        <v>26</v>
+      </c>
+      <c r="AB20">
+        <v>15.5</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
         <v>11</v>
       </c>
-      <c r="Z20">
+      <c r="AE20">
+        <v>21</v>
+      </c>
+      <c r="AF20">
+        <v>28</v>
+      </c>
+      <c r="AG20">
+        <v>15</v>
+      </c>
+      <c r="AH20">
+        <v>17.5</v>
+      </c>
+      <c r="AI20">
+        <v>36</v>
+      </c>
+      <c r="AJ20">
+        <v>75</v>
+      </c>
+      <c r="AK20">
+        <v>42</v>
+      </c>
+      <c r="AL20">
+        <v>46</v>
+      </c>
+      <c r="AM20">
+        <v>90</v>
+      </c>
+      <c r="AN20">
+        <v>40</v>
+      </c>
+      <c r="AO20">
         <v>13</v>
       </c>
-      <c r="AA20">
+      <c r="AP20">
+        <v>16</v>
+      </c>
+      <c r="AQ20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR20">
+        <v>12</v>
+      </c>
+      <c r="AS20">
         <v>22</v>
       </c>
-      <c r="AB20">
-        <v>18</v>
-      </c>
-      <c r="AC20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD20">
-        <v>10.5</v>
-      </c>
-      <c r="AE20">
-        <v>19.5</v>
-      </c>
-      <c r="AF20">
-        <v>34</v>
-      </c>
-      <c r="AG20">
-        <v>17.5</v>
-      </c>
-      <c r="AH20">
+      <c r="AT20">
+        <v>14.5</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>9.6</v>
+      </c>
+      <c r="AW20">
         <v>18.5</v>
       </c>
-      <c r="AI20">
-        <v>32</v>
-      </c>
-      <c r="AJ20">
-        <v>110</v>
-      </c>
-      <c r="AK20">
-        <v>50</v>
-      </c>
-      <c r="AL20">
-        <v>55</v>
-      </c>
-      <c r="AM20">
-        <v>100</v>
-      </c>
-      <c r="AN20">
-        <v>48</v>
-      </c>
-      <c r="AO20">
-        <v>11.5</v>
-      </c>
-      <c r="AP20">
-        <v>16.5</v>
-      </c>
-      <c r="AQ20">
-        <v>9.4</v>
-      </c>
-      <c r="AR20">
-        <v>11</v>
-      </c>
-      <c r="AS20">
-        <v>19</v>
-      </c>
-      <c r="AT20">
-        <v>15.5</v>
-      </c>
-      <c r="AU20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>9</v>
-      </c>
-      <c r="AW20">
-        <v>16</v>
-      </c>
       <c r="AX20">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AY20">
+        <v>13.5</v>
+      </c>
+      <c r="AZ20">
         <v>15</v>
-      </c>
-      <c r="AZ20">
-        <v>15.5</v>
       </c>
       <c r="BA20">
         <v>26</v>
       </c>
       <c r="BB20">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BC20">
+        <v>32</v>
+      </c>
+      <c r="BD20">
         <v>40</v>
       </c>
-      <c r="BD20">
-        <v>44</v>
-      </c>
       <c r="BE20">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="BF20">
+        <v>28</v>
+      </c>
+      <c r="BG20">
+        <v>11</v>
+      </c>
+      <c r="BH20">
+        <v>4.2</v>
+      </c>
+      <c r="BI20">
+        <v>3.05</v>
+      </c>
+      <c r="BJ20">
         <v>10.5</v>
-      </c>
-      <c r="BG20">
-        <v>9.6</v>
-      </c>
-      <c r="BH20">
-        <v>4.3</v>
-      </c>
-      <c r="BI20">
-        <v>3.1</v>
-      </c>
-      <c r="BJ20">
-        <v>11</v>
       </c>
       <c r="BK20">
         <v>7.4</v>
@@ -5617,31 +5617,31 @@
         <v>1.02</v>
       </c>
       <c r="BN20">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BO20">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BP20">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BQ20">
         <v>1.02</v>
       </c>
       <c r="BR20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW20">
         <v>10</v>
@@ -5653,7 +5653,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5679,7 +5679,7 @@
         <v>147</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G21">
         <v>2.34</v>
@@ -5688,7 +5688,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -5712,10 +5712,10 @@
         <v>2.64</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S21">
         <v>2.4</v>
@@ -5757,7 +5757,7 @@
         <v>36</v>
       </c>
       <c r="AF21">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG21">
         <v>13</v>
@@ -5778,7 +5778,7 @@
         <v>29</v>
       </c>
       <c r="AM21">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN21">
         <v>13.5</v>
@@ -5808,7 +5808,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX21">
         <v>15.5</v>
@@ -5826,13 +5826,13 @@
         <v>25</v>
       </c>
       <c r="BC21">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD21">
         <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF21">
         <v>9.800000000000001</v>
@@ -5921,19 +5921,19 @@
         <v>148</v>
       </c>
       <c r="F22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H22">
         <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
         <v>4.1</v>
@@ -5951,13 +5951,13 @@
         <v>1.24</v>
       </c>
       <c r="P22">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
         <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S22">
         <v>2.76</v>
@@ -5972,7 +5972,7 @@
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X22">
         <v>23</v>
@@ -5990,7 +5990,7 @@
         <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22">
         <v>17.5</v>
@@ -6005,7 +6005,7 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI22">
         <v>48</v>
@@ -6020,7 +6020,7 @@
         <v>38</v>
       </c>
       <c r="AM22">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN22">
         <v>14</v>
@@ -6038,7 +6038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT22">
         <v>10.5</v>
@@ -6074,7 +6074,7 @@
         <v>19</v>
       </c>
       <c r="BE22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF22">
         <v>11.5</v>
@@ -6101,7 +6101,7 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO22">
         <v>1.01</v>
@@ -6163,7 +6163,7 @@
         <v>149</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G23">
         <v>2.34</v>
@@ -6178,10 +6178,10 @@
         <v>3.75</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M23">
         <v>1.05</v>
@@ -6196,10 +6196,10 @@
         <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S23">
         <v>2.82</v>
@@ -6241,7 +6241,7 @@
         <v>40</v>
       </c>
       <c r="AF23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
         <v>12</v>
@@ -6250,7 +6250,7 @@
         <v>17</v>
       </c>
       <c r="AI23">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ23">
         <v>36</v>
@@ -6280,7 +6280,7 @@
         <v>21</v>
       </c>
       <c r="AS23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT23">
         <v>10.5</v>
@@ -6316,7 +6316,7 @@
         <v>6.2</v>
       </c>
       <c r="BE23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF23">
         <v>11.5</v>
@@ -6405,10 +6405,10 @@
         <v>150</v>
       </c>
       <c r="F24">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G24">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H24">
         <v>4.3</v>
@@ -6441,10 +6441,10 @@
         <v>1.51</v>
       </c>
       <c r="R24">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S24">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
         <v>1.54</v>
@@ -6453,10 +6453,10 @@
         <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W24">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X24">
         <v>28</v>
@@ -6465,10 +6465,10 @@
         <v>26</v>
       </c>
       <c r="Z24">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB24">
         <v>14.5</v>
@@ -6480,7 +6480,7 @@
         <v>19.5</v>
       </c>
       <c r="AE24">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AF24">
         <v>15.5</v>
@@ -6504,7 +6504,7 @@
         <v>25</v>
       </c>
       <c r="AM24">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AN24">
         <v>7.6</v>
@@ -6647,25 +6647,25 @@
         <v>151</v>
       </c>
       <c r="F25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G25">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H25">
         <v>3.1</v>
       </c>
       <c r="I25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J25">
         <v>3.65</v>
       </c>
       <c r="K25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -6674,31 +6674,31 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
         <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R25">
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U25">
         <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X25">
         <v>20</v>
@@ -6725,7 +6725,7 @@
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG25">
         <v>12</v>
@@ -6743,10 +6743,10 @@
         <v>25</v>
       </c>
       <c r="AL25">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN25">
         <v>16.5</v>
@@ -6764,7 +6764,7 @@
         <v>20</v>
       </c>
       <c r="AS25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT25">
         <v>10</v>
@@ -6776,7 +6776,7 @@
         <v>12</v>
       </c>
       <c r="AW25">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX25">
         <v>13.5</v>
@@ -6791,16 +6791,16 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC25">
         <v>20</v>
       </c>
       <c r="BD25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF25">
         <v>13.5</v>
@@ -6848,7 +6848,7 @@
         <v>7.4</v>
       </c>
       <c r="BU25">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV25">
         <v>28</v>
@@ -6889,16 +6889,16 @@
         <v>152</v>
       </c>
       <c r="F26">
+        <v>2.46</v>
+      </c>
+      <c r="G26">
         <v>2.52</v>
       </c>
-      <c r="G26">
-        <v>2.58</v>
-      </c>
       <c r="H26">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I26">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J26">
         <v>4.2</v>
@@ -6907,7 +6907,7 @@
         <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M26">
         <v>1.03</v>
@@ -6937,10 +6937,10 @@
         <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X26">
         <v>36</v>
@@ -6952,7 +6952,7 @@
         <v>24</v>
       </c>
       <c r="AA26">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB26">
         <v>19.5</v>
@@ -6967,7 +6967,7 @@
         <v>25</v>
       </c>
       <c r="AF26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG26">
         <v>13</v>
@@ -6994,10 +6994,10 @@
         <v>12</v>
       </c>
       <c r="AO26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26">
         <v>17</v>
@@ -7006,7 +7006,7 @@
         <v>19.5</v>
       </c>
       <c r="AS26">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT26">
         <v>16</v>
@@ -7042,13 +7042,13 @@
         <v>7.8</v>
       </c>
       <c r="BE26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26">
         <v>10</v>
       </c>
       <c r="BG26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH26">
         <v>5.6</v>
@@ -7075,13 +7075,13 @@
         <v>5.4</v>
       </c>
       <c r="BP26">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
@@ -7108,7 +7108,7 @@
         <v>15</v>
       </c>
       <c r="CA26">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>157</v>
@@ -7131,22 +7131,22 @@
         <v>153</v>
       </c>
       <c r="F27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H27">
+        <v>1.78</v>
+      </c>
+      <c r="I27">
         <v>1.8</v>
-      </c>
-      <c r="I27">
-        <v>1.82</v>
       </c>
       <c r="J27">
         <v>4.2</v>
       </c>
       <c r="K27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>1.31</v>
@@ -7179,10 +7179,10 @@
         <v>2.34</v>
       </c>
       <c r="V27">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X27">
         <v>27</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AC27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>10.5</v>
@@ -7221,19 +7221,19 @@
         <v>29</v>
       </c>
       <c r="AJ27">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AK27">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AL27">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AM27">
         <v>85</v>
       </c>
       <c r="AN27">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="AO27">
         <v>9</v>
@@ -7275,7 +7275,7 @@
         <v>24</v>
       </c>
       <c r="BB27">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC27">
         <v>44</v>
@@ -7284,10 +7284,10 @@
         <v>44</v>
       </c>
       <c r="BE27">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF27">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BG27">
         <v>8</v>
@@ -7347,7 +7347,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA27">
         <v>1.01</v>
@@ -7376,13 +7376,13 @@
         <v>4.6</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H28">
         <v>1.89</v>
       </c>
       <c r="I28">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J28">
         <v>3.5</v>
@@ -7400,10 +7400,10 @@
         <v>3.35</v>
       </c>
       <c r="O28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q28">
         <v>2.14</v>
@@ -7412,34 +7412,34 @@
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T28">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U28">
         <v>1.94</v>
       </c>
       <c r="V28">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W28">
         <v>1.25</v>
       </c>
       <c r="X28">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y28">
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA28">
         <v>26</v>
       </c>
       <c r="AB28">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -7454,7 +7454,7 @@
         <v>42</v>
       </c>
       <c r="AG28">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH28">
         <v>24</v>
@@ -7463,19 +7463,19 @@
         <v>50</v>
       </c>
       <c r="AJ28">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AK28">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AL28">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM28">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN28">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO28">
         <v>18.5</v>
@@ -7490,10 +7490,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS28">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU28">
         <v>7.2</v>
@@ -7505,34 +7505,34 @@
         <v>18.5</v>
       </c>
       <c r="AX28">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY28">
         <v>16.5</v>
       </c>
       <c r="AZ28">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA28">
         <v>6.6</v>
       </c>
       <c r="BB28">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC28">
+        <v>6.6</v>
+      </c>
+      <c r="BD28">
         <v>6.8</v>
       </c>
-      <c r="BD28">
+      <c r="BE28">
         <v>7</v>
-      </c>
-      <c r="BE28">
-        <v>7.2</v>
       </c>
       <c r="BF28">
         <v>7</v>
       </c>
       <c r="BG28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7615,7 +7615,7 @@
         <v>155</v>
       </c>
       <c r="F29">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G29">
         <v>1.27</v>
@@ -7624,16 +7624,16 @@
         <v>15.5</v>
       </c>
       <c r="I29">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J29">
         <v>6.6</v>
       </c>
       <c r="K29">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M29">
         <v>1.04</v>
@@ -7642,19 +7642,19 @@
         <v>4.8</v>
       </c>
       <c r="O29">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q29">
         <v>1.67</v>
       </c>
       <c r="R29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S29">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
         <v>2.42</v>
@@ -7669,25 +7669,25 @@
         <v>4.7</v>
       </c>
       <c r="X29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y29">
         <v>55</v>
       </c>
       <c r="Z29">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA29">
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>16.5</v>
       </c>
       <c r="AD29">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AE29">
         <v>420</v>
@@ -7702,7 +7702,7 @@
         <v>55</v>
       </c>
       <c r="AI29">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AJ29">
         <v>9</v>
@@ -7711,7 +7711,7 @@
         <v>15.5</v>
       </c>
       <c r="AL29">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="AM29">
         <v>330</v>
@@ -7723,16 +7723,16 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AQ29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR29">
+        <v>9.4</v>
+      </c>
+      <c r="AS29">
         <v>10</v>
-      </c>
-      <c r="AR29">
-        <v>11</v>
-      </c>
-      <c r="AS29">
-        <v>12</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7741,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="AV29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW29">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX29">
         <v>6.4</v>
@@ -7753,10 +7753,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BA29">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB29">
         <v>8</v>
@@ -7765,76 +7765,76 @@
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE29">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF29">
         <v>4.2</v>
       </c>
       <c r="BG29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BH29">
         <v>970</v>
       </c>
       <c r="BI29">
-        <v>3.8</v>
+        <v>1.34</v>
       </c>
       <c r="BJ29">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>3.55</v>
+        <v>970</v>
       </c>
       <c r="BO29">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="BP29">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>157</v>
@@ -7860,7 +7860,7 @@
         <v>2.32</v>
       </c>
       <c r="G30">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H30">
         <v>3.15</v>
@@ -7872,7 +7872,7 @@
         <v>3.2</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -7899,7 +7899,7 @@
         <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U30">
         <v>1.98</v>
@@ -7908,7 +7908,7 @@
         <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X30">
         <v>14</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -487,7 +487,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-28 18:51:05</t>
+    <t>2026-09-28 21:01:45</t>
   </si>
 </sst>
 </file>
@@ -1081,226 +1081,226 @@
         <v>128</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="G2">
+        <v>1.88</v>
+      </c>
+      <c r="H2">
+        <v>4.3</v>
+      </c>
+      <c r="I2">
+        <v>4.5</v>
+      </c>
+      <c r="J2">
+        <v>4.1</v>
+      </c>
+      <c r="K2">
+        <v>4.4</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.7</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.94</v>
+      </c>
+      <c r="Q2">
         <v>2.04</v>
       </c>
-      <c r="H2">
-        <v>4.2</v>
-      </c>
-      <c r="I2">
-        <v>4.3</v>
-      </c>
-      <c r="J2">
-        <v>3.7</v>
-      </c>
-      <c r="K2">
+      <c r="R2">
+        <v>1.32</v>
+      </c>
+      <c r="S2">
         <v>3.85</v>
       </c>
-      <c r="L2">
-        <v>1.47</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.3</v>
-      </c>
-      <c r="O2">
-        <v>1.4</v>
-      </c>
-      <c r="P2">
-        <v>1.79</v>
-      </c>
-      <c r="Q2">
-        <v>2.18</v>
-      </c>
-      <c r="R2">
-        <v>1.29</v>
-      </c>
-      <c r="S2">
-        <v>4.1</v>
-      </c>
       <c r="T2">
+        <v>1.92</v>
+      </c>
+      <c r="U2">
         <v>1.98</v>
       </c>
-      <c r="U2">
-        <v>1.93</v>
-      </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="X2">
+        <v>16</v>
+      </c>
+      <c r="Y2">
+        <v>23</v>
+      </c>
+      <c r="Z2">
+        <v>960</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>10.5</v>
+      </c>
+      <c r="AG2">
+        <v>10</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>960</v>
+      </c>
+      <c r="AJ2">
+        <v>22</v>
+      </c>
+      <c r="AK2">
+        <v>22</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>230</v>
+      </c>
+      <c r="AN2">
+        <v>15.5</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>14</v>
+      </c>
+      <c r="AQ2">
         <v>13</v>
       </c>
-      <c r="Y2">
-        <v>13</v>
-      </c>
-      <c r="Z2">
-        <v>30</v>
-      </c>
-      <c r="AA2">
-        <v>120</v>
-      </c>
-      <c r="AB2">
-        <v>8.4</v>
-      </c>
-      <c r="AC2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>18</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>11.5</v>
-      </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>85</v>
-      </c>
-      <c r="AJ2">
-        <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
-      </c>
-      <c r="AL2">
-        <v>48</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>18</v>
-      </c>
-      <c r="AO2">
-        <v>120</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
       <c r="AR2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AT2">
         <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA2">
+        <v>55</v>
+      </c>
+      <c r="BB2">
+        <v>17</v>
+      </c>
+      <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>30</v>
+      </c>
+      <c r="BE2">
+        <v>100</v>
+      </c>
+      <c r="BF2">
+        <v>12.5</v>
+      </c>
+      <c r="BG2">
+        <v>7.6</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>3.05</v>
+      </c>
+      <c r="BJ2">
+        <v>29</v>
+      </c>
+      <c r="BK2">
+        <v>3.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>130</v>
+      </c>
+      <c r="BN2">
+        <v>5.1</v>
+      </c>
+      <c r="BO2">
+        <v>4.1</v>
+      </c>
+      <c r="BP2">
+        <v>110</v>
+      </c>
+      <c r="BQ2">
+        <v>3.9</v>
+      </c>
+      <c r="BR2">
+        <v>400</v>
+      </c>
+      <c r="BS2">
+        <v>4.2</v>
+      </c>
+      <c r="BT2">
+        <v>14</v>
+      </c>
+      <c r="BU2">
+        <v>3.15</v>
+      </c>
+      <c r="BV2">
         <v>50</v>
       </c>
-      <c r="BB2">
-        <v>21</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>38</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2">
-        <v>16</v>
-      </c>
-      <c r="BG2">
-        <v>48</v>
-      </c>
-      <c r="BH2">
-        <v>3.45</v>
-      </c>
-      <c r="BI2">
-        <v>2.88</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
-      </c>
-      <c r="BK2">
-        <v>9</v>
-      </c>
-      <c r="BL2">
-        <v>170</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>5.2</v>
-      </c>
-      <c r="BO2">
-        <v>4.2</v>
-      </c>
-      <c r="BP2">
-        <v>17.5</v>
-      </c>
-      <c r="BQ2">
-        <v>12</v>
-      </c>
-      <c r="BR2">
-        <v>38</v>
-      </c>
-      <c r="BS2">
-        <v>25</v>
-      </c>
-      <c r="BT2">
-        <v>8.6</v>
-      </c>
-      <c r="BU2">
-        <v>6.4</v>
-      </c>
-      <c r="BV2">
-        <v>42</v>
-      </c>
       <c r="BW2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>36</v>
+        <v>1.92</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="CB2" t="s">
         <v>157</v>
@@ -1332,52 +1332,52 @@
         <v>2.28</v>
       </c>
       <c r="I3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="V3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W3">
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1386,163 +1386,163 @@
         <v>18</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AF3">
         <v>27</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3">
+        <v>15.5</v>
+      </c>
+      <c r="AI3">
+        <v>29</v>
+      </c>
+      <c r="AJ3">
+        <v>55</v>
+      </c>
+      <c r="AK3">
+        <v>32</v>
+      </c>
+      <c r="AL3">
+        <v>36</v>
+      </c>
+      <c r="AM3">
+        <v>75</v>
+      </c>
+      <c r="AN3">
+        <v>21</v>
+      </c>
+      <c r="AO3">
+        <v>12.5</v>
+      </c>
+      <c r="AP3">
+        <v>21</v>
+      </c>
+      <c r="AQ3">
+        <v>13</v>
+      </c>
+      <c r="AR3">
+        <v>15.5</v>
+      </c>
+      <c r="AS3">
+        <v>28</v>
+      </c>
+      <c r="AT3">
         <v>16</v>
       </c>
-      <c r="AI3">
-        <v>32</v>
-      </c>
-      <c r="AJ3">
-        <v>95</v>
-      </c>
-      <c r="AK3">
-        <v>36</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>85</v>
-      </c>
-      <c r="AN3">
-        <v>23</v>
-      </c>
-      <c r="AO3">
-        <v>13</v>
-      </c>
-      <c r="AP3">
-        <v>19</v>
-      </c>
-      <c r="AQ3">
-        <v>11.5</v>
-      </c>
-      <c r="AR3">
-        <v>15</v>
-      </c>
-      <c r="AS3">
-        <v>22</v>
-      </c>
-      <c r="AT3">
-        <v>14</v>
-      </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV3">
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AX3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY3">
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BC3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG3">
         <v>10.5</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BI3">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL3">
-        <v>90</v>
+        <v>940</v>
       </c>
       <c r="BM3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BN3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BO3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BP3">
         <v>25</v>
       </c>
       <c r="BQ3">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BT3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX3">
         <v>26</v>
       </c>
       <c r="BY3">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3">
         <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="s">
         <v>157</v>
@@ -1565,22 +1565,22 @@
         <v>130</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H4">
+        <v>2.2</v>
+      </c>
+      <c r="I4">
         <v>2.26</v>
       </c>
-      <c r="I4">
-        <v>2.34</v>
-      </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.34</v>
@@ -1589,10 +1589,10 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
         <v>2.28</v>
@@ -1601,190 +1601,190 @@
         <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V4">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>20</v>
       </c>
       <c r="AA4">
+        <v>46</v>
+      </c>
+      <c r="AB4">
+        <v>18</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
+        <v>27</v>
+      </c>
+      <c r="AF4">
         <v>36</v>
-      </c>
-      <c r="AB4">
-        <v>17.5</v>
-      </c>
-      <c r="AC4">
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <v>11.5</v>
-      </c>
-      <c r="AE4">
-        <v>26</v>
-      </c>
-      <c r="AF4">
-        <v>26</v>
       </c>
       <c r="AG4">
         <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>990</v>
       </c>
       <c r="AO4">
         <v>17</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS4">
         <v>25</v>
       </c>
       <c r="AT4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BC4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BG4">
         <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
-        <v>110</v>
+        <v>940</v>
       </c>
       <c r="BM4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BN4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BP4">
         <v>29</v>
       </c>
       <c r="BQ4">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS4">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>18.5</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="BX4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY4">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="s">
         <v>157</v>
@@ -1807,22 +1807,22 @@
         <v>131</v>
       </c>
       <c r="F5">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1831,52 +1831,52 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="X5">
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z5">
         <v>28</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>16.5</v>
@@ -1885,19 +1885,19 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK5">
         <v>24</v>
@@ -1906,10 +1906,10 @@
         <v>42</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO5">
         <v>60</v>
@@ -1918,16 +1918,16 @@
         <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
         <v>24</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
@@ -1936,13 +1936,13 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>17.5</v>
@@ -1960,73 +1960,73 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR5">
         <v>38</v>
       </c>
       <c r="BS5">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY5">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>36</v>
       </c>
       <c r="CA5">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
         <v>157</v>
@@ -2052,28 +2052,28 @@
         <v>2.2</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
         <v>1.36</v>
@@ -2094,19 +2094,19 @@
         <v>1.82</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
         <v>26</v>
@@ -2115,25 +2115,25 @@
         <v>80</v>
       </c>
       <c r="AB6">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>60</v>
@@ -2142,10 +2142,10 @@
         <v>32</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL6">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM6">
         <v>110</v>
@@ -2154,31 +2154,31 @@
         <v>22</v>
       </c>
       <c r="AO6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
         <v>11</v>
       </c>
       <c r="AR6">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS6">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2190,85 +2190,85 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB6">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="BF6">
         <v>17</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="s">
         <v>157</v>
@@ -2291,22 +2291,22 @@
         <v>133</v>
       </c>
       <c r="F7">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>2.68</v>
       </c>
       <c r="H7">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="I7">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>2.84</v>
       </c>
       <c r="K7">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2342,7 +2342,7 @@
         <v>1.21</v>
       </c>
       <c r="W7">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2354,7 +2354,7 @@
         <v>1000</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7">
         <v>1000</v>
@@ -2381,7 +2381,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7">
         <v>1000</v>
@@ -2396,7 +2396,7 @@
         <v>46</v>
       </c>
       <c r="AO7">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
         <v>1.01</v>
@@ -2450,7 +2450,7 @@
         <v>5.2</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2533,22 +2533,22 @@
         <v>134</v>
       </c>
       <c r="F8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G8">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.49</v>
@@ -2557,16 +2557,16 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
         <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
         <v>1.27</v>
@@ -2575,22 +2575,22 @@
         <v>4.4</v>
       </c>
       <c r="T8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
         <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X8">
         <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
         <v>55</v>
@@ -2617,19 +2617,19 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI8">
         <v>140</v>
       </c>
       <c r="AJ8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK8">
         <v>20</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>230</v>
@@ -2638,7 +2638,7 @@
         <v>13</v>
       </c>
       <c r="AO8">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP8">
         <v>10.5</v>
@@ -2653,13 +2653,13 @@
         <v>46</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU8">
         <v>8.4</v>
       </c>
       <c r="AV8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW8">
         <v>40</v>
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA8">
         <v>42</v>
@@ -2686,7 +2686,7 @@
         <v>44</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BF8">
         <v>11.5</v>
@@ -2713,10 +2713,10 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP8">
         <v>13.5</v>
@@ -2728,7 +2728,7 @@
         <v>40</v>
       </c>
       <c r="BS8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BT8">
         <v>12.5</v>
@@ -2752,7 +2752,7 @@
         <v>32</v>
       </c>
       <c r="CA8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CB8" t="s">
         <v>157</v>
@@ -2781,10 +2781,10 @@
         <v>3.05</v>
       </c>
       <c r="H9">
+        <v>2.92</v>
+      </c>
+      <c r="I9">
         <v>2.94</v>
-      </c>
-      <c r="I9">
-        <v>2.96</v>
       </c>
       <c r="J9">
         <v>3.05</v>
@@ -2808,10 +2808,10 @@
         <v>1.55</v>
       </c>
       <c r="Q9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
         <v>5.7</v>
@@ -2829,7 +2829,7 @@
         <v>1.49</v>
       </c>
       <c r="X9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
         <v>8.6</v>
@@ -2853,7 +2853,7 @@
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2871,10 +2871,10 @@
         <v>46</v>
       </c>
       <c r="AL9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AM9">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AN9">
         <v>60</v>
@@ -2892,7 +2892,7 @@
         <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -2919,7 +2919,7 @@
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BC9">
         <v>38</v>
@@ -2928,7 +2928,7 @@
         <v>60</v>
       </c>
       <c r="BE9">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BF9">
         <v>44</v>
@@ -2940,7 +2940,7 @@
         <v>2.7</v>
       </c>
       <c r="BI9">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9">
         <v>25</v>
@@ -3026,7 +3026,7 @@
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -3050,7 +3050,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
         <v>1.6</v>
@@ -3071,7 +3071,7 @@
         <v>2.84</v>
       </c>
       <c r="X10">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y10">
         <v>70</v>
@@ -3101,7 +3101,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>390</v>
@@ -3128,13 +3128,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AR10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT10">
         <v>9.800000000000001</v>
@@ -3152,10 +3152,10 @@
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA10">
         <v>9.199999999999999</v>
@@ -3170,7 +3170,7 @@
         <v>14.5</v>
       </c>
       <c r="BE10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF10">
         <v>5.5</v>
@@ -3179,7 +3179,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BI10">
         <v>3.8</v>
@@ -3188,13 +3188,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BL10">
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
@@ -3206,37 +3206,37 @@
         <v>9.6</v>
       </c>
       <c r="BQ10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR10">
         <v>25</v>
       </c>
       <c r="BS10">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT10">
         <v>11</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
         <v>60</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BX10">
         <v>60</v>
       </c>
       <c r="BY10">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BZ10">
         <v>16</v>
       </c>
       <c r="CA10">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="CB10" t="s">
         <v>157</v>
@@ -3265,7 +3265,7 @@
         <v>1.72</v>
       </c>
       <c r="H11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
         <v>6.8</v>
@@ -3286,22 +3286,22 @@
         <v>3.05</v>
       </c>
       <c r="O11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
         <v>4.7</v>
       </c>
       <c r="T11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11">
         <v>1.73</v>
@@ -3313,10 +3313,10 @@
         <v>2.38</v>
       </c>
       <c r="X11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z11">
         <v>55</v>
@@ -3328,7 +3328,7 @@
         <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD11">
         <v>27</v>
@@ -3352,31 +3352,31 @@
         <v>16.5</v>
       </c>
       <c r="AK11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL11">
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO11">
         <v>210</v>
       </c>
       <c r="AP11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR11">
         <v>44</v>
       </c>
       <c r="AS11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3388,7 +3388,7 @@
         <v>24</v>
       </c>
       <c r="AW11">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX11">
         <v>7.8</v>
@@ -3400,7 +3400,7 @@
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3412,13 +3412,13 @@
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BF11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH11">
         <v>3.2</v>
@@ -3501,37 +3501,37 @@
         <v>138</v>
       </c>
       <c r="F12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O12">
         <v>1.48</v>
       </c>
       <c r="P12">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q12">
         <v>2.44</v>
@@ -3543,13 +3543,13 @@
         <v>4.9</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U12">
         <v>1.71</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W12">
         <v>2.28</v>
@@ -3561,13 +3561,13 @@
         <v>15.5</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA12">
         <v>220</v>
       </c>
       <c r="AB12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC12">
         <v>8.6</v>
@@ -3582,34 +3582,34 @@
         <v>8.6</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12">
         <v>27</v>
       </c>
       <c r="AI12">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12">
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO12">
         <v>200</v>
       </c>
       <c r="AP12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12">
         <v>14.5</v>
@@ -3618,7 +3618,7 @@
         <v>42</v>
       </c>
       <c r="AS12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT12">
         <v>6</v>
@@ -3630,10 +3630,10 @@
         <v>23</v>
       </c>
       <c r="AW12">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AX12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3642,31 +3642,31 @@
         <v>25</v>
       </c>
       <c r="BA12">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BB12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC12">
         <v>20</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BF12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
         <v>2.96</v>
       </c>
       <c r="BI12">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3743,10 +3743,10 @@
         <v>139</v>
       </c>
       <c r="F13">
+        <v>3.5</v>
+      </c>
+      <c r="G13">
         <v>3.55</v>
-      </c>
-      <c r="G13">
-        <v>3.6</v>
       </c>
       <c r="H13">
         <v>2.32</v>
@@ -3761,7 +3761,7 @@
         <v>3.45</v>
       </c>
       <c r="L13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M13">
         <v>1.09</v>
@@ -3770,7 +3770,7 @@
         <v>3.35</v>
       </c>
       <c r="O13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P13">
         <v>1.8</v>
@@ -3779,7 +3779,7 @@
         <v>2.18</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13">
         <v>4</v>
@@ -3788,13 +3788,13 @@
         <v>1.91</v>
       </c>
       <c r="U13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
         <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X13">
         <v>12</v>
@@ -3809,7 +3809,7 @@
         <v>30</v>
       </c>
       <c r="AB13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC13">
         <v>7.6</v>
@@ -3818,16 +3818,16 @@
         <v>12</v>
       </c>
       <c r="AE13">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13">
         <v>15.5</v>
       </c>
       <c r="AH13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13">
         <v>55</v>
@@ -3896,19 +3896,19 @@
         <v>46</v>
       </c>
       <c r="BE13">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="BF13">
         <v>40</v>
       </c>
       <c r="BG13">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH13">
         <v>3.1</v>
       </c>
       <c r="BI13">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ13">
         <v>10.5</v>
@@ -3923,7 +3923,7 @@
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO13">
         <v>6</v>
@@ -3947,7 +3947,7 @@
         <v>4.4</v>
       </c>
       <c r="BV13">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BW13">
         <v>15</v>
@@ -3988,13 +3988,13 @@
         <v>4.5</v>
       </c>
       <c r="G14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I14">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -4003,7 +4003,7 @@
         <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -4015,7 +4015,7 @@
         <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q14">
         <v>2.26</v>
@@ -4024,13 +4024,13 @@
         <v>1.28</v>
       </c>
       <c r="S14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T14">
         <v>2.04</v>
       </c>
       <c r="U14">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V14">
         <v>2.02</v>
@@ -4045,16 +4045,16 @@
         <v>7.4</v>
       </c>
       <c r="Z14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA14">
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4066,40 +4066,40 @@
         <v>32</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14">
         <v>46</v>
       </c>
       <c r="AJ14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK14">
         <v>70</v>
       </c>
       <c r="AL14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM14">
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO14">
         <v>17</v>
       </c>
       <c r="AP14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
         <v>7.2</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS14">
         <v>21</v>
@@ -4126,16 +4126,16 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB14">
         <v>100</v>
       </c>
       <c r="BC14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD14">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BE14">
         <v>130</v>
@@ -4144,7 +4144,7 @@
         <v>80</v>
       </c>
       <c r="BG14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH14">
         <v>3.3</v>
@@ -4227,13 +4227,13 @@
         <v>141</v>
       </c>
       <c r="F15">
+        <v>1.21</v>
+      </c>
+      <c r="G15">
         <v>1.22</v>
       </c>
-      <c r="G15">
-        <v>1.23</v>
-      </c>
       <c r="H15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I15">
         <v>17.5</v>
@@ -4251,43 +4251,43 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O15">
         <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V15">
         <v>1.06</v>
       </c>
       <c r="W15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="X15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y15">
         <v>55</v>
       </c>
       <c r="Z15">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4320,43 +4320,43 @@
         <v>9</v>
       </c>
       <c r="AK15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM15">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN15">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AO15">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AP15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AR15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AS15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU15">
         <v>16</v>
       </c>
       <c r="AV15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW15">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AX15">
         <v>7.6</v>
@@ -4368,10 +4368,10 @@
         <v>34</v>
       </c>
       <c r="BA15">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BB15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC15">
         <v>12</v>
@@ -4380,7 +4380,7 @@
         <v>36</v>
       </c>
       <c r="BE15">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BF15">
         <v>3.3</v>
@@ -4404,43 +4404,43 @@
         <v>190</v>
       </c>
       <c r="BM15">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP15">
         <v>6.4</v>
       </c>
       <c r="BQ15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BS15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BU15">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BV15">
         <v>160</v>
       </c>
       <c r="BW15">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BX15">
         <v>120</v>
       </c>
       <c r="BY15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4469,22 +4469,22 @@
         <v>142</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="J16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L16">
         <v>1.17</v>
@@ -4493,31 +4493,31 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="O16">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P16">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q16">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R16">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S16">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T16">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V16">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="W16">
         <v>1.01</v>
@@ -4526,22 +4526,22 @@
         <v>55</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AB16">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AC16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE16">
         <v>24</v>
@@ -4550,13 +4550,13 @@
         <v>1000</v>
       </c>
       <c r="AG16">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="AH16">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AI16">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AJ16">
         <v>1000</v>
@@ -4577,118 +4577,118 @@
         <v>2.62</v>
       </c>
       <c r="AP16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS16">
         <v>5.1</v>
       </c>
       <c r="AT16">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="AU16">
+        <v>27</v>
+      </c>
+      <c r="AV16">
+        <v>13</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>4.2</v>
+      </c>
+      <c r="AY16">
+        <v>4.2</v>
+      </c>
+      <c r="AZ16">
+        <v>2.54</v>
+      </c>
+      <c r="BA16">
+        <v>2.52</v>
+      </c>
+      <c r="BB16">
+        <v>13.5</v>
+      </c>
+      <c r="BC16">
+        <v>24</v>
+      </c>
+      <c r="BD16">
+        <v>24</v>
+      </c>
+      <c r="BE16">
         <v>20</v>
       </c>
-      <c r="AV16">
-        <v>18</v>
-      </c>
-      <c r="AW16">
-        <v>18</v>
-      </c>
-      <c r="AX16">
-        <v>10</v>
-      </c>
-      <c r="AY16">
-        <v>10</v>
-      </c>
-      <c r="AZ16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA16">
-        <v>50</v>
-      </c>
-      <c r="BB16">
-        <v>10</v>
-      </c>
-      <c r="BC16">
-        <v>20</v>
-      </c>
-      <c r="BD16">
-        <v>19</v>
-      </c>
-      <c r="BE16">
-        <v>10</v>
-      </c>
       <c r="BF16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG16">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>150</v>
+        <v>1.37</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>150</v>
+        <v>1.37</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>150</v>
+        <v>1.37</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BU16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>3.9</v>
+        <v>1.37</v>
       </c>
       <c r="CB16" t="s">
         <v>157</v>
@@ -4711,16 +4711,16 @@
         <v>143</v>
       </c>
       <c r="F17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H17">
+        <v>1.35</v>
+      </c>
+      <c r="I17">
         <v>1.36</v>
-      </c>
-      <c r="I17">
-        <v>1.38</v>
       </c>
       <c r="J17">
         <v>5.6</v>
@@ -4729,19 +4729,19 @@
         <v>5.7</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
         <v>1.67</v>
@@ -4750,7 +4750,7 @@
         <v>1.54</v>
       </c>
       <c r="S17">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T17">
         <v>2.08</v>
@@ -4759,25 +4759,25 @@
         <v>1.89</v>
       </c>
       <c r="V17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA17">
         <v>10.5</v>
       </c>
       <c r="AB17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC17">
         <v>13</v>
@@ -4789,10 +4789,10 @@
         <v>14.5</v>
       </c>
       <c r="AF17">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH17">
         <v>26</v>
@@ -4801,7 +4801,7 @@
         <v>36</v>
       </c>
       <c r="AJ17">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="AK17">
         <v>170</v>
@@ -4813,10 +4813,10 @@
         <v>160</v>
       </c>
       <c r="AN17">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AO17">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AP17">
         <v>20</v>
@@ -4825,7 +4825,7 @@
         <v>8.6</v>
       </c>
       <c r="AR17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS17">
         <v>10</v>
@@ -4834,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AU17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV17">
         <v>10</v>
@@ -4843,10 +4843,10 @@
         <v>13.5</v>
       </c>
       <c r="AX17">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AY17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AZ17">
         <v>25</v>
@@ -4855,7 +4855,7 @@
         <v>34</v>
       </c>
       <c r="BB17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BC17">
         <v>130</v>
@@ -4867,7 +4867,7 @@
         <v>140</v>
       </c>
       <c r="BF17">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="BG17">
         <v>5.1</v>
@@ -4876,61 +4876,61 @@
         <v>3.85</v>
       </c>
       <c r="BI17">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BJ17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>10.5</v>
+        <v>2.66</v>
       </c>
       <c r="BL17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>9.4</v>
+        <v>2.86</v>
       </c>
       <c r="BN17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>11</v>
+        <v>2.74</v>
       </c>
       <c r="BP17">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="BR17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="BT17">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BU17">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BV17">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BX17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="BZ17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4962,7 +4962,7 @@
         <v>14</v>
       </c>
       <c r="I18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -4983,10 +4983,10 @@
         <v>1.3</v>
       </c>
       <c r="P18">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q18">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
         <v>1.41</v>
@@ -4995,10 +4995,10 @@
         <v>3.25</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V18">
         <v>1.06</v>
@@ -5052,7 +5052,7 @@
         <v>95</v>
       </c>
       <c r="AM18">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AN18">
         <v>5.8</v>
@@ -5070,7 +5070,7 @@
         <v>13</v>
       </c>
       <c r="AS18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT18">
         <v>6.6</v>
@@ -5091,13 +5091,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
@@ -5127,7 +5127,7 @@
         <v>13</v>
       </c>
       <c r="BL18">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="BM18">
         <v>21</v>
@@ -5157,7 +5157,7 @@
         <v>9.4</v>
       </c>
       <c r="BV18">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BW18">
         <v>21</v>
@@ -5204,7 +5204,7 @@
         <v>3.6</v>
       </c>
       <c r="I19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J19">
         <v>3.9</v>
@@ -5213,7 +5213,7 @@
         <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M19">
         <v>1.04</v>
@@ -5231,16 +5231,16 @@
         <v>1.63</v>
       </c>
       <c r="R19">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S19">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T19">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U19">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.34</v>
@@ -5258,7 +5258,7 @@
         <v>32</v>
       </c>
       <c r="AA19">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB19">
         <v>13</v>
@@ -5267,10 +5267,10 @@
         <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE19">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF19">
         <v>17.5</v>
@@ -5282,7 +5282,7 @@
         <v>15.5</v>
       </c>
       <c r="AI19">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ19">
         <v>29</v>
@@ -5294,7 +5294,7 @@
         <v>32</v>
       </c>
       <c r="AM19">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN19">
         <v>10.5</v>
@@ -5309,10 +5309,10 @@
         <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS19">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19">
         <v>11.5</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="AW19">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AX19">
         <v>13</v>
@@ -5336,7 +5336,7 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB19">
         <v>21</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19">
         <v>9</v>
@@ -5378,7 +5378,7 @@
         <v>5.9</v>
       </c>
       <c r="BO19">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP19">
         <v>15.5</v>
@@ -5461,7 +5461,7 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20">
         <v>1.27</v>
@@ -5470,13 +5470,13 @@
         <v>2.14</v>
       </c>
       <c r="Q20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S20">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T20">
         <v>1.71</v>
@@ -5524,10 +5524,10 @@
         <v>17.5</v>
       </c>
       <c r="AI20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK20">
         <v>42</v>
@@ -5536,10 +5536,10 @@
         <v>46</v>
       </c>
       <c r="AM20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO20">
         <v>13</v>
@@ -5548,19 +5548,19 @@
         <v>16</v>
       </c>
       <c r="AQ20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR20">
         <v>12</v>
       </c>
       <c r="AS20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20">
         <v>14.5</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV20">
         <v>9.6</v>
@@ -5679,7 +5679,7 @@
         <v>147</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G21">
         <v>2.34</v>
@@ -5688,7 +5688,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -5703,7 +5703,7 @@
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O21">
         <v>1.18</v>
@@ -5712,19 +5712,19 @@
         <v>2.64</v>
       </c>
       <c r="Q21">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R21">
         <v>1.66</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T21">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U21">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V21">
         <v>1.46</v>
@@ -5766,7 +5766,7 @@
         <v>15</v>
       </c>
       <c r="AI21">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AJ21">
         <v>36</v>
@@ -5778,7 +5778,7 @@
         <v>29</v>
       </c>
       <c r="AM21">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN21">
         <v>13.5</v>
@@ -5790,7 +5790,7 @@
         <v>19</v>
       </c>
       <c r="AQ21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR21">
         <v>22</v>
@@ -5811,13 +5811,13 @@
         <v>25</v>
       </c>
       <c r="AX21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY21">
         <v>10</v>
       </c>
       <c r="AZ21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA21">
         <v>23</v>
@@ -5826,19 +5826,19 @@
         <v>25</v>
       </c>
       <c r="BC21">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BD21">
         <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BF21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH21">
         <v>5.3</v>
@@ -5862,7 +5862,7 @@
         <v>6.8</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BP21">
         <v>15</v>
@@ -5921,16 +5921,16 @@
         <v>148</v>
       </c>
       <c r="F22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G22">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H22">
         <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J22">
         <v>3.7</v>
@@ -5939,7 +5939,7 @@
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -5951,16 +5951,16 @@
         <v>1.24</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q22">
         <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T22">
         <v>1.62</v>
@@ -5972,7 +5972,7 @@
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X22">
         <v>23</v>
@@ -6023,7 +6023,7 @@
         <v>200</v>
       </c>
       <c r="AN22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO22">
         <v>30</v>
@@ -6038,7 +6038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS22">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AT22">
         <v>10.5</v>
@@ -6163,7 +6163,7 @@
         <v>149</v>
       </c>
       <c r="F23">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G23">
         <v>2.34</v>
@@ -6172,7 +6172,7 @@
         <v>3.2</v>
       </c>
       <c r="I23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J23">
         <v>3.75</v>
@@ -6187,7 +6187,7 @@
         <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
         <v>1.24</v>
@@ -6196,10 +6196,10 @@
         <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R23">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S23">
         <v>2.82</v>
@@ -6211,13 +6211,13 @@
         <v>2.32</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X23">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y23">
         <v>16.5</v>
@@ -6229,7 +6229,7 @@
         <v>70</v>
       </c>
       <c r="AB23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC23">
         <v>9.4</v>
@@ -6250,7 +6250,7 @@
         <v>17</v>
       </c>
       <c r="AI23">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ23">
         <v>36</v>
@@ -6292,7 +6292,7 @@
         <v>12</v>
       </c>
       <c r="AW23">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AX23">
         <v>13.5</v>
@@ -6313,10 +6313,10 @@
         <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE23">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF23">
         <v>11.5</v>
@@ -6325,7 +6325,7 @@
         <v>20</v>
       </c>
       <c r="BH23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI23">
         <v>3.05</v>
@@ -6349,7 +6349,7 @@
         <v>4.1</v>
       </c>
       <c r="BP23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
@@ -6379,7 +6379,7 @@
         <v>1.02</v>
       </c>
       <c r="BZ23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
@@ -6405,22 +6405,22 @@
         <v>150</v>
       </c>
       <c r="F24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G24">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H24">
         <v>4.3</v>
       </c>
       <c r="I24">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J24">
         <v>4.2</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6435,16 +6435,16 @@
         <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q24">
         <v>1.51</v>
       </c>
       <c r="R24">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S24">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T24">
         <v>1.54</v>
@@ -6456,7 +6456,7 @@
         <v>1.28</v>
       </c>
       <c r="W24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X24">
         <v>28</v>
@@ -6465,7 +6465,7 @@
         <v>26</v>
       </c>
       <c r="Z24">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AA24">
         <v>500</v>
@@ -6480,7 +6480,7 @@
         <v>19.5</v>
       </c>
       <c r="AE24">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AF24">
         <v>15.5</v>
@@ -6528,7 +6528,7 @@
         <v>12</v>
       </c>
       <c r="AU24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV24">
         <v>16</v>
@@ -6558,7 +6558,7 @@
         <v>21</v>
       </c>
       <c r="BE24">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF24">
         <v>6.4</v>
@@ -6647,7 +6647,7 @@
         <v>151</v>
       </c>
       <c r="F25">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G25">
         <v>2.46</v>
@@ -6656,7 +6656,7 @@
         <v>3.1</v>
       </c>
       <c r="I25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J25">
         <v>3.65</v>
@@ -6686,16 +6686,16 @@
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T25">
         <v>1.67</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
         <v>1.69</v>
@@ -6725,7 +6725,7 @@
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG25">
         <v>12</v>
@@ -6743,16 +6743,16 @@
         <v>25</v>
       </c>
       <c r="AL25">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM25">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN25">
         <v>16.5</v>
       </c>
       <c r="AO25">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AP25">
         <v>15</v>
@@ -6776,7 +6776,7 @@
         <v>12</v>
       </c>
       <c r="AW25">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AX25">
         <v>13.5</v>
@@ -6791,7 +6791,7 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BC25">
         <v>20</v>
@@ -6830,7 +6830,7 @@
         <v>6.2</v>
       </c>
       <c r="BO25">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP25">
         <v>19</v>
@@ -6848,7 +6848,7 @@
         <v>7.4</v>
       </c>
       <c r="BU25">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV25">
         <v>28</v>
@@ -6889,13 +6889,13 @@
         <v>152</v>
       </c>
       <c r="F26">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G26">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H26">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I26">
         <v>2.76</v>
@@ -6940,10 +6940,10 @@
         <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y26">
         <v>20</v>
@@ -6997,7 +6997,7 @@
         <v>13</v>
       </c>
       <c r="AP26">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26">
         <v>17</v>
@@ -7039,7 +7039,7 @@
         <v>19.5</v>
       </c>
       <c r="BD26">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BE26">
         <v>8.800000000000001</v>
@@ -7087,13 +7087,13 @@
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU26">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW26">
         <v>1.01</v>
@@ -7137,10 +7137,10 @@
         <v>4.8</v>
       </c>
       <c r="H27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J27">
         <v>4.2</v>
@@ -7176,10 +7176,10 @@
         <v>1.69</v>
       </c>
       <c r="U27">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W27">
         <v>1.26</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD27">
         <v>10.5</v>
@@ -7212,7 +7212,7 @@
         <v>40</v>
       </c>
       <c r="AG27">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH27">
         <v>19</v>
@@ -7224,19 +7224,19 @@
         <v>700</v>
       </c>
       <c r="AK27">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AL27">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AM27">
         <v>85</v>
       </c>
       <c r="AN27">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AO27">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP27">
         <v>18.5</v>
@@ -7257,7 +7257,7 @@
         <v>9</v>
       </c>
       <c r="AV27">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW27">
         <v>15</v>
@@ -7275,7 +7275,7 @@
         <v>24</v>
       </c>
       <c r="BB27">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC27">
         <v>44</v>
@@ -7284,13 +7284,13 @@
         <v>44</v>
       </c>
       <c r="BE27">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF27">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BG27">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH27">
         <v>4.8</v>
@@ -7341,13 +7341,13 @@
         <v>7.4</v>
       </c>
       <c r="BX27">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BY27">
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="CA27">
         <v>1.01</v>
@@ -7376,7 +7376,7 @@
         <v>4.6</v>
       </c>
       <c r="G28">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>1.89</v>
@@ -7406,16 +7406,16 @@
         <v>1.8</v>
       </c>
       <c r="Q28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R28">
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U28">
         <v>1.94</v>
@@ -7427,7 +7427,7 @@
         <v>1.25</v>
       </c>
       <c r="X28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -7439,7 +7439,7 @@
         <v>26</v>
       </c>
       <c r="AB28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -7454,10 +7454,10 @@
         <v>42</v>
       </c>
       <c r="AG28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AH28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI28">
         <v>50</v>
@@ -7466,19 +7466,19 @@
         <v>500</v>
       </c>
       <c r="AK28">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="AL28">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AM28">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN28">
         <v>500</v>
       </c>
       <c r="AO28">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AP28">
         <v>10.5</v>
@@ -7511,28 +7511,28 @@
         <v>16.5</v>
       </c>
       <c r="AZ28">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BA28">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC28">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE28">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF28">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG28">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7627,13 +7627,13 @@
         <v>18</v>
       </c>
       <c r="J29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K29">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="L29">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M29">
         <v>1.04</v>
@@ -7642,22 +7642,22 @@
         <v>4.8</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P29">
         <v>2.32</v>
       </c>
       <c r="Q29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R29">
         <v>1.52</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T29">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U29">
         <v>1.63</v>
@@ -7669,10 +7669,10 @@
         <v>4.7</v>
       </c>
       <c r="X29">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y29">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Z29">
         <v>200</v>
@@ -7681,7 +7681,7 @@
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AC29">
         <v>16.5</v>
@@ -7690,7 +7690,7 @@
         <v>210</v>
       </c>
       <c r="AE29">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AF29">
         <v>7.2</v>
@@ -7711,7 +7711,7 @@
         <v>15.5</v>
       </c>
       <c r="AL29">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="AM29">
         <v>330</v>
@@ -7723,16 +7723,16 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS29">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7741,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="AV29">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW29">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX29">
         <v>6.4</v>
@@ -7753,10 +7753,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BA29">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB29">
         <v>8</v>
@@ -7765,76 +7765,76 @@
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE29">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF29">
+        <v>3.75</v>
+      </c>
+      <c r="BG29">
+        <v>12.5</v>
+      </c>
+      <c r="BH29">
         <v>4.2</v>
       </c>
-      <c r="BG29">
-        <v>10</v>
-      </c>
-      <c r="BH29">
-        <v>970</v>
-      </c>
       <c r="BI29">
-        <v>1.34</v>
+        <v>3.8</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BN29">
-        <v>970</v>
+        <v>3.55</v>
       </c>
       <c r="BO29">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB29" t="s">
         <v>157</v>
@@ -7857,61 +7857,61 @@
         <v>156</v>
       </c>
       <c r="F30">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G30">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H30">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I30">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O30">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P30">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q30">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S30">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T30">
         <v>1.85</v>
       </c>
       <c r="U30">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y30">
         <v>13.5</v>
@@ -7965,58 +7965,58 @@
         <v>55</v>
       </c>
       <c r="AP30">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR30">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT30">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU30">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV30">
         <v>11</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE30">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BF30">
         <v>19</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH30">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="150">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Brazilian Serie B</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>22:30:00</t>
   </si>
   <si>
@@ -370,6 +376,9 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
+    <t>French Guyana</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -445,13 +454,16 @@
     <t>Santa Fe</t>
   </si>
   <si>
+    <t>Sint Maarten</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 01:21:48</t>
+    <t>2026-09-29 03:32:40</t>
   </si>
 </sst>
 </file>
@@ -783,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1033,19 +1045,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
         <v>2.3</v>
@@ -1054,13 +1066,13 @@
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.43</v>
@@ -1069,7 +1081,7 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.36</v>
@@ -1078,7 +1090,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>1.33</v>
@@ -1087,13 +1099,13 @@
         <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
         <v>1.76</v>
@@ -1114,7 +1126,7 @@
         <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -1147,7 +1159,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO2">
         <v>55</v>
@@ -1156,7 +1168,7 @@
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>21</v>
@@ -1183,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
         <v>40</v>
@@ -1222,7 +1234,7 @@
         <v>150</v>
       </c>
       <c r="BM2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN2">
         <v>5.9</v>
@@ -1231,7 +1243,7 @@
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
         <v>4.1</v>
@@ -1258,16 +1270,16 @@
         <v>50</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2">
         <v>34</v>
       </c>
       <c r="CA2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1275,178 +1287,178 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
         <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
         <v>11</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI3">
-        <v>340</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
         <v>75</v>
       </c>
-      <c r="AK3">
-        <v>65</v>
-      </c>
       <c r="AL3">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3">
         <v>6.8</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AT3">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>4.9</v>
       </c>
       <c r="AV3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
         <v>5.2</v>
       </c>
       <c r="AZ3">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BA3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB3">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BC3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BD3">
         <v>7.8</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>3.4</v>
@@ -1455,7 +1467,7 @@
         <v>2.4</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1467,40 +1479,40 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BO3">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>46</v>
@@ -1509,7 +1521,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1517,40 +1529,40 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.5</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
         <v>3.2</v>
@@ -1565,7 +1577,7 @@
         <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
         <v>4.5</v>
@@ -1574,40 +1586,40 @@
         <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>55</v>
       </c>
       <c r="AA4">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE4">
         <v>150</v>
       </c>
       <c r="AF4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1616,22 +1628,22 @@
         <v>28</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
         <v>15</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
         <v>210</v>
@@ -1640,25 +1652,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS4">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
         <v>26</v>
       </c>
       <c r="AW4">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AX4">
         <v>7.8</v>
@@ -1667,16 +1679,16 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BB4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD4">
         <v>44</v>
@@ -1685,7 +1697,7 @@
         <v>120</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG4">
         <v>130</v>
@@ -1694,64 +1706,64 @@
         <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO4">
         <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4">
         <v>40</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV4">
         <v>95</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
         <v>110</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1759,16 +1771,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>3.05</v>
@@ -1789,7 +1801,7 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
         <v>1.13</v>
@@ -1804,19 +1816,19 @@
         <v>1.57</v>
       </c>
       <c r="Q5">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
         <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
         <v>1.53</v>
@@ -1831,7 +1843,7 @@
         <v>8.6</v>
       </c>
       <c r="Z5">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA5">
         <v>48</v>
@@ -1843,7 +1855,7 @@
         <v>7</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>42</v>
@@ -1858,7 +1870,7 @@
         <v>23</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>55</v>
@@ -1867,10 +1879,10 @@
         <v>46</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AM5">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN5">
         <v>55</v>
@@ -1879,7 +1891,7 @@
         <v>48</v>
       </c>
       <c r="AP5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ5">
         <v>8</v>
@@ -1891,7 +1903,7 @@
         <v>42</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -1903,10 +1915,10 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
         <v>21</v>
@@ -1915,13 +1927,13 @@
         <v>55</v>
       </c>
       <c r="BB5">
+        <v>48</v>
+      </c>
+      <c r="BC5">
+        <v>40</v>
+      </c>
+      <c r="BD5">
         <v>46</v>
-      </c>
-      <c r="BC5">
-        <v>38</v>
-      </c>
-      <c r="BD5">
-        <v>55</v>
       </c>
       <c r="BE5">
         <v>110</v>
@@ -1930,43 +1942,43 @@
         <v>46</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI5">
         <v>2.54</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BL5">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BR5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>5.6</v>
@@ -1975,25 +1987,25 @@
         <v>5</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX5">
+        <v>55</v>
+      </c>
+      <c r="BY5">
+        <v>9.4</v>
+      </c>
+      <c r="BZ5">
+        <v>60</v>
+      </c>
+      <c r="CA5">
         <v>9.6</v>
       </c>
-      <c r="BX5">
-        <v>48</v>
-      </c>
-      <c r="BY5">
-        <v>11.5</v>
-      </c>
-      <c r="BZ5">
-        <v>55</v>
-      </c>
-      <c r="CA5">
-        <v>11.5</v>
-      </c>
       <c r="CB5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2001,223 +2013,223 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R6">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="X6">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="Y6">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="Z6">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="AA6">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AE6">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="AF6">
+        <v>10.5</v>
+      </c>
+      <c r="AG6">
         <v>11</v>
       </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
       <c r="AH6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="AJ6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL6">
         <v>48</v>
       </c>
       <c r="AM6">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6">
         <v>13</v>
       </c>
       <c r="AR6">
+        <v>9</v>
+      </c>
+      <c r="AS6">
+        <v>9.6</v>
+      </c>
+      <c r="AT6">
+        <v>10</v>
+      </c>
+      <c r="AU6">
+        <v>11</v>
+      </c>
+      <c r="AV6">
+        <v>13.5</v>
+      </c>
+      <c r="AW6">
+        <v>9.4</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6">
+        <v>19.5</v>
+      </c>
+      <c r="BA6">
+        <v>9</v>
+      </c>
+      <c r="BB6">
+        <v>10.5</v>
+      </c>
+      <c r="BC6">
+        <v>12.5</v>
+      </c>
+      <c r="BD6">
+        <v>7.6</v>
+      </c>
+      <c r="BE6">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS6">
-        <v>10</v>
-      </c>
-      <c r="AT6">
-        <v>9.6</v>
-      </c>
-      <c r="AU6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV6">
-        <v>13</v>
-      </c>
-      <c r="AW6">
-        <v>9.6</v>
-      </c>
-      <c r="AX6">
-        <v>9.6</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
-      </c>
-      <c r="AZ6">
-        <v>17</v>
-      </c>
-      <c r="BA6">
-        <v>9.4</v>
-      </c>
-      <c r="BB6">
-        <v>12.5</v>
-      </c>
-      <c r="BC6">
-        <v>13</v>
-      </c>
-      <c r="BD6">
-        <v>23</v>
-      </c>
-      <c r="BE6">
-        <v>9.6</v>
-      </c>
       <c r="BF6">
+        <v>4.5</v>
+      </c>
+      <c r="BG6">
+        <v>15</v>
+      </c>
+      <c r="BH6">
         <v>5.4</v>
       </c>
-      <c r="BG6">
-        <v>10.5</v>
-      </c>
-      <c r="BH6">
-        <v>4.5</v>
-      </c>
       <c r="BI6">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL6">
         <v>120</v>
       </c>
       <c r="BM6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
         <v>3.8</v>
       </c>
       <c r="BP6">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BR6">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BS6">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BU6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BW6">
         <v>7.2</v>
@@ -2226,16 +2238,16 @@
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CA6">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2243,34 +2255,34 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F7">
+        <v>1.69</v>
+      </c>
+      <c r="G7">
         <v>1.7</v>
       </c>
-      <c r="G7">
-        <v>1.72</v>
-      </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>1.55</v>
@@ -2279,37 +2291,37 @@
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
         <v>1.23</v>
       </c>
       <c r="S7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>2.36</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W7">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>16.5</v>
@@ -2324,7 +2336,7 @@
         <v>6.2</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
         <v>28</v>
@@ -2339,7 +2351,7 @@
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI7">
         <v>160</v>
@@ -2357,10 +2369,10 @@
         <v>700</v>
       </c>
       <c r="AN7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP7">
         <v>9</v>
@@ -2369,22 +2381,22 @@
         <v>15</v>
       </c>
       <c r="AR7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT7">
         <v>5.7</v>
       </c>
       <c r="AU7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX7">
         <v>7.6</v>
@@ -2396,7 +2408,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB7">
         <v>14.5</v>
@@ -2405,22 +2417,22 @@
         <v>20</v>
       </c>
       <c r="BD7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BF7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH7">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
@@ -2429,13 +2441,13 @@
         <v>11</v>
       </c>
       <c r="BL7">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BN7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO7">
         <v>3.6</v>
@@ -2447,7 +2459,7 @@
         <v>10.5</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS7">
         <v>28</v>
@@ -2456,19 +2468,19 @@
         <v>10</v>
       </c>
       <c r="BU7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV7">
         <v>90</v>
       </c>
       <c r="BW7">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="BX7">
         <v>110</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BZ7">
         <v>38</v>
@@ -2477,7 +2489,7 @@
         <v>24</v>
       </c>
       <c r="CB7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2485,16 +2497,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>3.55</v>
@@ -2503,7 +2515,7 @@
         <v>3.6</v>
       </c>
       <c r="H8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I8">
         <v>2.34</v>
@@ -2518,31 +2530,31 @@
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V8">
         <v>1.74</v>
@@ -2554,7 +2566,7 @@
         <v>11.5</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z8">
         <v>13.5</v>
@@ -2563,31 +2575,31 @@
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG8">
         <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK8">
         <v>48</v>
@@ -2596,25 +2608,25 @@
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP8">
         <v>10</v>
       </c>
       <c r="AQ8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -2626,43 +2638,43 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB8">
         <v>55</v>
       </c>
       <c r="BC8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BD8">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE8">
         <v>29</v>
       </c>
       <c r="BF8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BG8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2683,10 +2695,10 @@
         <v>6</v>
       </c>
       <c r="BP8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ8">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BR8">
         <v>48</v>
@@ -2701,13 +2713,13 @@
         <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BX8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BY8">
         <v>30</v>
@@ -2719,7 +2731,7 @@
         <v>30</v>
       </c>
       <c r="CB8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2727,19 +2739,19 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G9">
         <v>1.25</v>
@@ -2769,22 +2781,22 @@
         <v>1.16</v>
       </c>
       <c r="P9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q9">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V9">
         <v>1.07</v>
@@ -2814,7 +2826,7 @@
         <v>50</v>
       </c>
       <c r="AE9">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AF9">
         <v>8.6</v>
@@ -2823,13 +2835,13 @@
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AJ9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AK9">
         <v>13.5</v>
@@ -2841,22 +2853,22 @@
         <v>200</v>
       </c>
       <c r="AN9">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AO9">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="AP9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR9">
         <v>29</v>
       </c>
       <c r="AS9">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -2865,22 +2877,22 @@
         <v>16</v>
       </c>
       <c r="AV9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA9">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BB9">
         <v>8.800000000000001</v>
@@ -2892,19 +2904,19 @@
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF9">
         <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9">
         <v>12.5</v>
@@ -2916,7 +2928,7 @@
         <v>170</v>
       </c>
       <c r="BM9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN9">
         <v>3.9</v>
@@ -2934,25 +2946,25 @@
         <v>25</v>
       </c>
       <c r="BS9">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BT9">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BU9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BV9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>110</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2961,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2969,22 +2981,22 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>55</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="H10">
         <v>1.06</v>
@@ -2993,7 +3005,7 @@
         <v>1.07</v>
       </c>
       <c r="J10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="K10">
         <v>22</v>
@@ -3005,22 +3017,22 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O10">
         <v>1.14</v>
       </c>
       <c r="P10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R10">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S10">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T10">
         <v>4.6</v>
@@ -3035,40 +3047,40 @@
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Y10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AB10">
-        <v>190</v>
+        <v>470</v>
       </c>
       <c r="AC10">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AE10">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AF10">
         <v>1000</v>
       </c>
       <c r="AG10">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3086,124 +3098,124 @@
         <v>1000</v>
       </c>
       <c r="AO10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AP10">
         <v>34</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR10">
         <v>6</v>
       </c>
       <c r="AS10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AU10">
         <v>20</v>
       </c>
       <c r="AV10">
+        <v>23</v>
+      </c>
+      <c r="AW10">
         <v>21</v>
       </c>
-      <c r="AW10">
-        <v>20</v>
-      </c>
       <c r="AX10">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY10">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="BA10">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="BB10">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BC10">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD10">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE10">
         <v>20</v>
       </c>
       <c r="BF10">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI10">
-        <v>1.37</v>
+        <v>4.9</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BK10">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.37</v>
+        <v>6.2</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BO10">
-        <v>1.37</v>
+        <v>5.7</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.37</v>
+        <v>6.2</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="BS10">
-        <v>1.37</v>
+        <v>6.2</v>
       </c>
       <c r="BT10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BU10">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BW10">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>1.37</v>
+        <v>5.5</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="CA10">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3211,16 +3223,16 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F11">
         <v>11</v>
@@ -3229,7 +3241,7 @@
         <v>11.5</v>
       </c>
       <c r="H11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I11">
         <v>1.36</v>
@@ -3241,37 +3253,37 @@
         <v>5.9</v>
       </c>
       <c r="L11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R11">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="V11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="W11">
         <v>1.09</v>
@@ -3280,16 +3292,16 @@
         <v>22</v>
       </c>
       <c r="Y11">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC11">
         <v>13</v>
@@ -3298,55 +3310,55 @@
         <v>10.5</v>
       </c>
       <c r="AE11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG11">
         <v>38</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="AK11">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AL11">
         <v>150</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN11">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AO11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AP11">
         <v>20</v>
       </c>
       <c r="AQ11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AU11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV11">
         <v>10</v>
@@ -3355,22 +3367,22 @@
         <v>13.5</v>
       </c>
       <c r="AX11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AY11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AZ11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BA11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC11">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BD11">
         <v>120</v>
@@ -3379,10 +3391,10 @@
         <v>140</v>
       </c>
       <c r="BF11">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="BG11">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH11">
         <v>4</v>
@@ -3391,7 +3403,7 @@
         <v>3.75</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK11">
         <v>11</v>
@@ -3400,52 +3412,52 @@
         <v>190</v>
       </c>
       <c r="BM11">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BO11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BP11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BQ11">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
         <v>110</v>
       </c>
       <c r="BS11">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BT11">
         <v>3.7</v>
       </c>
       <c r="BU11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BV11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BW11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BY11">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3453,25 +3465,25 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F12">
+        <v>1.29</v>
+      </c>
+      <c r="G12">
         <v>1.3</v>
       </c>
-      <c r="G12">
-        <v>1.32</v>
-      </c>
       <c r="H12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I12">
         <v>15.5</v>
@@ -3480,7 +3492,7 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L12">
         <v>1.38</v>
@@ -3492,10 +3504,10 @@
         <v>4.2</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>1.88</v>
@@ -3504,34 +3516,34 @@
         <v>1.42</v>
       </c>
       <c r="S12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U12">
         <v>1.61</v>
       </c>
       <c r="V12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W12">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="X12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z12">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC12">
         <v>14</v>
@@ -3540,7 +3552,7 @@
         <v>60</v>
       </c>
       <c r="AE12">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AF12">
         <v>6.8</v>
@@ -3549,106 +3561,106 @@
         <v>11.5</v>
       </c>
       <c r="AH12">
+        <v>46</v>
+      </c>
+      <c r="AI12">
+        <v>280</v>
+      </c>
+      <c r="AJ12">
+        <v>9</v>
+      </c>
+      <c r="AK12">
+        <v>16</v>
+      </c>
+      <c r="AL12">
         <v>55</v>
       </c>
-      <c r="AI12">
-        <v>270</v>
-      </c>
-      <c r="AJ12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK12">
-        <v>17</v>
-      </c>
-      <c r="AL12">
-        <v>130</v>
-      </c>
       <c r="AM12">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AN12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO12">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="AP12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12">
         <v>32</v>
       </c>
       <c r="AR12">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS12">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AT12">
         <v>6.8</v>
       </c>
       <c r="AU12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV12">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AW12">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AX12">
         <v>6.2</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
         <v>38</v>
       </c>
       <c r="BA12">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB12">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12">
         <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BF12">
         <v>5.4</v>
       </c>
       <c r="BG12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH12">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BI12">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
         <v>15.5</v>
       </c>
       <c r="BK12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BL12">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BN12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BO12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP12">
         <v>7.4</v>
@@ -3657,10 +3669,10 @@
         <v>6.4</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BT12">
         <v>17</v>
@@ -3672,22 +3684,22 @@
         <v>190</v>
       </c>
       <c r="BW12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BX12">
         <v>160</v>
       </c>
       <c r="BY12">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BZ12">
         <v>14</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3695,40 +3707,40 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J13">
         <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
         <v>1.53</v>
       </c>
       <c r="M13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -3749,10 +3761,10 @@
         <v>4.9</v>
       </c>
       <c r="T13">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V13">
         <v>1.2</v>
@@ -3764,22 +3776,22 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z13">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA13">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB13">
         <v>6.6</v>
       </c>
       <c r="AC13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE13">
         <v>110</v>
@@ -3794,7 +3806,7 @@
         <v>26</v>
       </c>
       <c r="AI13">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AJ13">
         <v>18.5</v>
@@ -3806,37 +3818,37 @@
         <v>55</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO13">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AP13">
         <v>9.4</v>
       </c>
       <c r="AQ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AT13">
         <v>6.2</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
         <v>22</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AX13">
         <v>8.6</v>
@@ -3845,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA13">
         <v>29</v>
@@ -3860,31 +3872,31 @@
         <v>48</v>
       </c>
       <c r="BE13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BF13">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BH13">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="BI13">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BJ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BL13">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BN13">
         <v>4.1</v>
@@ -3893,43 +3905,43 @@
         <v>3.75</v>
       </c>
       <c r="BP13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BT13">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU13">
         <v>8</v>
       </c>
       <c r="BV13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BX13">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY13">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="BZ13">
         <v>38</v>
       </c>
       <c r="CA13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CB13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3937,19 +3949,19 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G14">
         <v>4.9</v>
@@ -3958,67 +3970,67 @@
         <v>1.94</v>
       </c>
       <c r="I14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J14">
+        <v>3.55</v>
+      </c>
+      <c r="K14">
         <v>3.6</v>
       </c>
-      <c r="K14">
-        <v>3.7</v>
-      </c>
       <c r="L14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P14">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V14">
         <v>2.04</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA14">
         <v>22</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4039,19 +4051,19 @@
         <v>46</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK14">
         <v>70</v>
       </c>
       <c r="AL14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM14">
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO14">
         <v>17</v>
@@ -4060,13 +4072,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14">
         <v>13</v>
@@ -4081,7 +4093,7 @@
         <v>21</v>
       </c>
       <c r="AX14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY14">
         <v>18</v>
@@ -4105,73 +4117,73 @@
         <v>130</v>
       </c>
       <c r="BF14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BG14">
         <v>16</v>
       </c>
       <c r="BH14">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BI14">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>2.52</v>
+        <v>9.6</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM14">
-        <v>2.82</v>
+        <v>10</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ14">
-        <v>2.86</v>
+        <v>9.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS14">
-        <v>2.86</v>
+        <v>9.6</v>
       </c>
       <c r="BT14">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BU14">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW14">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY14">
-        <v>2.86</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA14">
-        <v>2.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4179,37 +4191,37 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="I15">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="J15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -4221,43 +4233,43 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q15">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S15">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="T15">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U15">
         <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="W15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X15">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB15">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -4269,37 +4281,37 @@
         <v>21</v>
       </c>
       <c r="AF15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI15">
         <v>32</v>
       </c>
       <c r="AJ15">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AK15">
         <v>42</v>
       </c>
       <c r="AL15">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM15">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AN15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4308,31 +4320,31 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT15">
         <v>14.5</v>
       </c>
       <c r="AU15">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW15">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AX15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AY15">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ15">
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB15">
         <v>55</v>
@@ -4341,16 +4353,16 @@
         <v>32</v>
       </c>
       <c r="BD15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE15">
         <v>65</v>
       </c>
       <c r="BF15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BG15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH15">
         <v>4.2</v>
@@ -4365,7 +4377,7 @@
         <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM15">
         <v>1.02</v>
@@ -4380,10 +4392,10 @@
         <v>30</v>
       </c>
       <c r="BQ15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
@@ -4395,7 +4407,7 @@
         <v>4.3</v>
       </c>
       <c r="BV15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
@@ -4413,7 +4425,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4421,19 +4433,19 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G16">
         <v>2.34</v>
@@ -4442,7 +4454,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4457,22 +4469,22 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q16">
         <v>1.54</v>
       </c>
       <c r="R16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
         <v>1.51</v>
@@ -4490,7 +4502,7 @@
         <v>32</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z16">
         <v>32</v>
@@ -4520,7 +4532,7 @@
         <v>15</v>
       </c>
       <c r="AI16">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
         <v>36</v>
@@ -4529,7 +4541,7 @@
         <v>65</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AM16">
         <v>250</v>
@@ -4550,7 +4562,7 @@
         <v>13</v>
       </c>
       <c r="AS16">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT16">
         <v>14</v>
@@ -4574,10 +4586,10 @@
         <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB16">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC16">
         <v>17.5</v>
@@ -4586,7 +4598,7 @@
         <v>13</v>
       </c>
       <c r="BE16">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF16">
         <v>9.4</v>
@@ -4598,7 +4610,7 @@
         <v>5.3</v>
       </c>
       <c r="BI16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
@@ -4625,16 +4637,16 @@
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV16">
         <v>26</v>
@@ -4649,13 +4661,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4663,19 +4675,19 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
         <v>2.06</v>
@@ -4684,7 +4696,7 @@
         <v>3.7</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J17">
         <v>3.95</v>
@@ -4705,13 +4717,13 @@
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q17">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S17">
         <v>2.58</v>
@@ -4723,55 +4735,55 @@
         <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.94</v>
       </c>
       <c r="X17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z17">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AA17">
         <v>160</v>
       </c>
       <c r="AB17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE17">
         <v>85</v>
       </c>
       <c r="AF17">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG17">
         <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI17">
         <v>85</v>
       </c>
       <c r="AJ17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK17">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM17">
         <v>200</v>
@@ -4780,10 +4792,10 @@
         <v>10</v>
       </c>
       <c r="AO17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ17">
         <v>16.5</v>
@@ -4792,7 +4804,7 @@
         <v>14.5</v>
       </c>
       <c r="AS17">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AT17">
         <v>11.5</v>
@@ -4804,7 +4816,7 @@
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX17">
         <v>13.5</v>
@@ -4816,7 +4828,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4825,16 +4837,16 @@
         <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE17">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BH17">
         <v>4.8</v>
@@ -4879,13 +4891,13 @@
         <v>5.8</v>
       </c>
       <c r="BV17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW17">
         <v>1.02</v>
       </c>
       <c r="BX17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY17">
         <v>1.02</v>
@@ -4897,7 +4909,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4905,19 +4917,19 @@
         <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F18">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G18">
         <v>2.26</v>
@@ -4935,7 +4947,7 @@
         <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M18">
         <v>1.05</v>
@@ -4950,19 +4962,19 @@
         <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T18">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -4971,16 +4983,16 @@
         <v>1.79</v>
       </c>
       <c r="X18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z18">
         <v>32</v>
       </c>
       <c r="AA18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB18">
         <v>12.5</v>
@@ -4989,25 +5001,25 @@
         <v>9.4</v>
       </c>
       <c r="AD18">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE18">
         <v>38</v>
       </c>
       <c r="AF18">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI18">
         <v>150</v>
       </c>
       <c r="AJ18">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK18">
         <v>23</v>
@@ -5016,7 +5028,7 @@
         <v>75</v>
       </c>
       <c r="AM18">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN18">
         <v>13.5</v>
@@ -5031,7 +5043,7 @@
         <v>14</v>
       </c>
       <c r="AR18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS18">
         <v>7.4</v>
@@ -5046,7 +5058,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
         <v>13.5</v>
@@ -5058,7 +5070,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
         <v>13</v>
@@ -5070,7 +5082,7 @@
         <v>14.5</v>
       </c>
       <c r="BE18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF18">
         <v>11</v>
@@ -5097,7 +5109,7 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
@@ -5139,7 +5151,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5147,25 +5159,25 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F19">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G19">
         <v>2.32</v>
       </c>
       <c r="H19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I19">
         <v>3.4</v>
@@ -5174,7 +5186,7 @@
         <v>3.75</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L19">
         <v>1.34</v>
@@ -5201,25 +5213,25 @@
         <v>2.92</v>
       </c>
       <c r="T19">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X19">
         <v>23</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z19">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AA19">
         <v>70</v>
@@ -5231,7 +5243,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE19">
         <v>90</v>
@@ -5240,7 +5252,7 @@
         <v>16.5</v>
       </c>
       <c r="AG19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH19">
         <v>17</v>
@@ -5252,7 +5264,7 @@
         <v>36</v>
       </c>
       <c r="AK19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19">
         <v>38</v>
@@ -5267,7 +5279,7 @@
         <v>34</v>
       </c>
       <c r="AP19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ19">
         <v>13.5</v>
@@ -5303,13 +5315,13 @@
         <v>5.9</v>
       </c>
       <c r="BB19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC19">
         <v>18.5</v>
       </c>
       <c r="BD19">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BE19">
         <v>6.4</v>
@@ -5342,10 +5354,10 @@
         <v>6.4</v>
       </c>
       <c r="BO19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP19">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
@@ -5360,10 +5372,10 @@
         <v>8</v>
       </c>
       <c r="BU19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
@@ -5375,13 +5387,13 @@
         <v>1.02</v>
       </c>
       <c r="BZ19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5389,22 +5401,22 @@
         <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H20">
         <v>4.3</v>
@@ -5431,7 +5443,7 @@
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
         <v>1.52</v>
@@ -5515,7 +5527,7 @@
         <v>21</v>
       </c>
       <c r="AR20">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AS20">
         <v>10</v>
@@ -5530,7 +5542,7 @@
         <v>16</v>
       </c>
       <c r="AW20">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AX20">
         <v>12.5</v>
@@ -5542,7 +5554,7 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BB20">
         <v>18</v>
@@ -5554,7 +5566,7 @@
         <v>21</v>
       </c>
       <c r="BE20">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BF20">
         <v>6.4</v>
@@ -5563,67 +5575,67 @@
         <v>8.6</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BM20">
         <v>1.02</v>
       </c>
       <c r="BN20">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO20">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP20">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BU20">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BY20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5631,40 +5643,40 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G21">
         <v>2.32</v>
       </c>
       <c r="H21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
         <v>3.7</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>1.35</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
         <v>4.4</v>
@@ -5682,7 +5694,7 @@
         <v>1.45</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T21">
         <v>1.66</v>
@@ -5691,49 +5703,49 @@
         <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
         <v>1.75</v>
       </c>
       <c r="X21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y21">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z21">
         <v>25</v>
       </c>
       <c r="AA21">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
         <v>8.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AF21">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG21">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AJ21">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK21">
         <v>25</v>
@@ -5742,13 +5754,13 @@
         <v>75</v>
       </c>
       <c r="AM21">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AP21">
         <v>15</v>
@@ -5760,22 +5772,22 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AT21">
         <v>10</v>
       </c>
       <c r="AU21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV21">
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY21">
         <v>9.800000000000001</v>
@@ -5784,25 +5796,25 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BB21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC21">
         <v>20</v>
       </c>
       <c r="BD21">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BE21">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF21">
         <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -5844,7 +5856,7 @@
         <v>7.4</v>
       </c>
       <c r="BU21">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
         <v>28</v>
@@ -5865,7 +5877,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5873,28 +5885,28 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="G22">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="H22">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="I22">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -5903,55 +5915,55 @@
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q22">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="S22">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T22">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="X22">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y22">
         <v>21</v>
       </c>
       <c r="Z22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA22">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB22">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC22">
         <v>11</v>
@@ -5960,10 +5972,10 @@
         <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
@@ -5972,10 +5984,10 @@
         <v>15</v>
       </c>
       <c r="AI22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ22">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK22">
         <v>23</v>
@@ -5984,13 +5996,13 @@
         <v>27</v>
       </c>
       <c r="AM22">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN22">
         <v>11.5</v>
       </c>
       <c r="AO22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP22">
         <v>24</v>
@@ -6002,25 +6014,25 @@
         <v>21</v>
       </c>
       <c r="AS22">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT22">
         <v>16.5</v>
       </c>
       <c r="AU22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX22">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AY22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
         <v>13</v>
@@ -6032,82 +6044,82 @@
         <v>32</v>
       </c>
       <c r="BC22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD22">
         <v>23</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF22">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG22">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH22">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI22">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BJ22">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK22">
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO22">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP22">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
+        <v>23</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>7</v>
+      </c>
+      <c r="BU22">
+        <v>5.7</v>
+      </c>
+      <c r="BV22">
+        <v>19.5</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
         <v>25</v>
       </c>
-      <c r="BS22">
-        <v>1.01</v>
-      </c>
-      <c r="BT22">
-        <v>7.4</v>
-      </c>
-      <c r="BU22">
-        <v>5.1</v>
-      </c>
-      <c r="BV22">
-        <v>20</v>
-      </c>
-      <c r="BW22">
-        <v>1.01</v>
-      </c>
-      <c r="BX22">
-        <v>26</v>
-      </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB22" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6115,22 +6127,22 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F23">
         <v>4.6</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H23">
         <v>1.77</v>
@@ -6145,10 +6157,10 @@
         <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
         <v>4.9</v>
@@ -6157,7 +6169,7 @@
         <v>1.23</v>
       </c>
       <c r="P23">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q23">
         <v>1.68</v>
@@ -6172,7 +6184,7 @@
         <v>1.69</v>
       </c>
       <c r="U23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
         <v>2.26</v>
@@ -6193,10 +6205,10 @@
         <v>20</v>
       </c>
       <c r="AB23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC23">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD23">
         <v>10.5</v>
@@ -6271,7 +6283,7 @@
         <v>24</v>
       </c>
       <c r="BB23">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="BC23">
         <v>44</v>
@@ -6280,7 +6292,7 @@
         <v>44</v>
       </c>
       <c r="BE23">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF23">
         <v>40</v>
@@ -6310,7 +6322,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BP23">
         <v>42</v>
@@ -6334,7 +6346,7 @@
         <v>14</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX23">
         <v>27</v>
@@ -6349,7 +6361,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6357,19 +6369,19 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -6378,7 +6390,7 @@
         <v>1.93</v>
       </c>
       <c r="I24">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J24">
         <v>3.45</v>
@@ -6393,16 +6405,16 @@
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
         <v>1.41</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q24">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R24">
         <v>1.28</v>
@@ -6411,13 +6423,13 @@
         <v>4.3</v>
       </c>
       <c r="T24">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U24">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W24">
         <v>1.25</v>
@@ -6450,7 +6462,7 @@
         <v>40</v>
       </c>
       <c r="AG24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH24">
         <v>22</v>
@@ -6474,13 +6486,13 @@
         <v>500</v>
       </c>
       <c r="AO24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP24">
         <v>10.5</v>
       </c>
       <c r="AQ24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR24">
         <v>9.800000000000001</v>
@@ -6501,7 +6513,7 @@
         <v>19.5</v>
       </c>
       <c r="AX24">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY24">
         <v>16.5</v>
@@ -6513,13 +6525,13 @@
         <v>8</v>
       </c>
       <c r="BB24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC24">
         <v>7</v>
       </c>
       <c r="BD24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE24">
         <v>7.6</v>
@@ -6591,7 +6603,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6599,241 +6611,241 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F25">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="G25">
+        <v>1.95</v>
+      </c>
+      <c r="H25">
+        <v>3.85</v>
+      </c>
+      <c r="I25">
+        <v>5.4</v>
+      </c>
+      <c r="J25">
+        <v>3.85</v>
+      </c>
+      <c r="K25">
+        <v>4.6</v>
+      </c>
+      <c r="L25">
+        <v>1.31</v>
+      </c>
+      <c r="M25">
+        <v>1.03</v>
+      </c>
+      <c r="N25">
+        <v>4.4</v>
+      </c>
+      <c r="O25">
+        <v>1.22</v>
+      </c>
+      <c r="P25">
+        <v>2.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.65</v>
+      </c>
+      <c r="R25">
+        <v>1.47</v>
+      </c>
+      <c r="S25">
+        <v>2.5</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
         <v>1.27</v>
       </c>
-      <c r="H25">
-        <v>15</v>
-      </c>
-      <c r="I25">
-        <v>19</v>
-      </c>
-      <c r="J25">
-        <v>6.6</v>
-      </c>
-      <c r="K25">
-        <v>7.2</v>
-      </c>
-      <c r="L25">
-        <v>1.34</v>
-      </c>
-      <c r="M25">
-        <v>1.04</v>
-      </c>
-      <c r="N25">
-        <v>4.7</v>
-      </c>
-      <c r="O25">
-        <v>1.24</v>
-      </c>
-      <c r="P25">
-        <v>2.3</v>
-      </c>
-      <c r="Q25">
-        <v>1.74</v>
-      </c>
-      <c r="R25">
-        <v>1.5</v>
-      </c>
-      <c r="S25">
-        <v>2.92</v>
-      </c>
-      <c r="T25">
-        <v>2.52</v>
-      </c>
-      <c r="U25">
-        <v>1.59</v>
-      </c>
-      <c r="V25">
-        <v>1.05</v>
-      </c>
       <c r="W25">
-        <v>4.7</v>
+        <v>2.04</v>
       </c>
       <c r="X25">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>32</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>7.4</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>24</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>4.6</v>
+      </c>
+      <c r="BI25">
+        <v>3.3</v>
+      </c>
+      <c r="BJ25">
         <v>10.5</v>
       </c>
-      <c r="AQ25">
-        <v>11</v>
-      </c>
-      <c r="AR25">
+      <c r="BK25">
+        <v>7</v>
+      </c>
+      <c r="BL25">
+        <v>110</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>5.4</v>
+      </c>
+      <c r="BO25">
+        <v>3.85</v>
+      </c>
+      <c r="BP25">
+        <v>14</v>
+      </c>
+      <c r="BQ25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR25">
+        <v>27</v>
+      </c>
+      <c r="BS25">
+        <v>17</v>
+      </c>
+      <c r="BT25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU25">
+        <v>6.2</v>
+      </c>
+      <c r="BV25">
+        <v>38</v>
+      </c>
+      <c r="BW25">
+        <v>25</v>
+      </c>
+      <c r="BX25">
+        <v>44</v>
+      </c>
+      <c r="BY25">
+        <v>28</v>
+      </c>
+      <c r="BZ25">
+        <v>19.5</v>
+      </c>
+      <c r="CA25">
         <v>13</v>
       </c>
-      <c r="AS25">
-        <v>13.5</v>
-      </c>
-      <c r="AT25">
-        <v>6.8</v>
-      </c>
-      <c r="AU25">
-        <v>14</v>
-      </c>
-      <c r="AV25">
-        <v>12</v>
-      </c>
-      <c r="AW25">
-        <v>13</v>
-      </c>
-      <c r="AX25">
-        <v>6.2</v>
-      </c>
-      <c r="AY25">
-        <v>10.5</v>
-      </c>
-      <c r="AZ25">
-        <v>11.5</v>
-      </c>
-      <c r="BA25">
-        <v>13</v>
-      </c>
-      <c r="BB25">
-        <v>7.8</v>
-      </c>
-      <c r="BC25">
-        <v>13.5</v>
-      </c>
-      <c r="BD25">
-        <v>11.5</v>
-      </c>
-      <c r="BE25">
-        <v>13</v>
-      </c>
-      <c r="BF25">
-        <v>4.4</v>
-      </c>
-      <c r="BG25">
-        <v>15</v>
-      </c>
-      <c r="BH25">
-        <v>4.1</v>
-      </c>
-      <c r="BI25">
-        <v>3.65</v>
-      </c>
-      <c r="BJ25">
-        <v>17</v>
-      </c>
-      <c r="BK25">
-        <v>5.4</v>
-      </c>
-      <c r="BL25">
-        <v>290</v>
-      </c>
-      <c r="BM25">
-        <v>7.8</v>
-      </c>
-      <c r="BN25">
-        <v>3.5</v>
-      </c>
-      <c r="BO25">
-        <v>3.15</v>
-      </c>
-      <c r="BP25">
-        <v>8</v>
-      </c>
-      <c r="BQ25">
-        <v>5.3</v>
-      </c>
-      <c r="BR25">
-        <v>34</v>
-      </c>
-      <c r="BS25">
-        <v>6.4</v>
-      </c>
-      <c r="BT25">
-        <v>22</v>
-      </c>
-      <c r="BU25">
-        <v>5.9</v>
-      </c>
-      <c r="BV25">
-        <v>210</v>
-      </c>
-      <c r="BW25">
-        <v>7.6</v>
-      </c>
-      <c r="BX25">
-        <v>170</v>
-      </c>
-      <c r="BY25">
-        <v>7.6</v>
-      </c>
-      <c r="BZ25">
-        <v>13.5</v>
-      </c>
-      <c r="CA25">
-        <v>5</v>
-      </c>
       <c r="CB25" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6841,241 +6853,483 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F26">
-        <v>2.36</v>
+        <v>1.28</v>
       </c>
       <c r="G26">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="H26">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="I26">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="K26">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="L26">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="O26">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="P26">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="T26">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="U26">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="W26">
-        <v>1.67</v>
+        <v>4.3</v>
       </c>
       <c r="X26">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="Y26">
-        <v>13.5</v>
+        <v>120</v>
       </c>
       <c r="Z26">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="AA26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC26">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AD26">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="AE26">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="AF26">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="AI26">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AJ26">
-        <v>40</v>
+        <v>9.6</v>
       </c>
       <c r="AK26">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="AL26">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="AM26">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AN26">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AO26">
-        <v>55</v>
+        <v>530</v>
       </c>
       <c r="AP26">
         <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AR26">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AS26">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AT26">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU26">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AV26">
         <v>11</v>
       </c>
       <c r="AW26">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AX26">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY26">
         <v>10</v>
       </c>
       <c r="AZ26">
+        <v>14.5</v>
+      </c>
+      <c r="BA26">
+        <v>12.5</v>
+      </c>
+      <c r="BB26">
+        <v>8.4</v>
+      </c>
+      <c r="BC26">
+        <v>13.5</v>
+      </c>
+      <c r="BD26">
+        <v>17.5</v>
+      </c>
+      <c r="BE26">
+        <v>12.5</v>
+      </c>
+      <c r="BF26">
+        <v>4.6</v>
+      </c>
+      <c r="BG26">
+        <v>13.5</v>
+      </c>
+      <c r="BH26">
+        <v>4.8</v>
+      </c>
+      <c r="BI26">
+        <v>3.2</v>
+      </c>
+      <c r="BJ26">
+        <v>16</v>
+      </c>
+      <c r="BK26">
+        <v>4.7</v>
+      </c>
+      <c r="BL26">
+        <v>250</v>
+      </c>
+      <c r="BM26">
+        <v>6.4</v>
+      </c>
+      <c r="BN26">
+        <v>3.6</v>
+      </c>
+      <c r="BO26">
+        <v>2.86</v>
+      </c>
+      <c r="BP26">
+        <v>8</v>
+      </c>
+      <c r="BQ26">
+        <v>5.3</v>
+      </c>
+      <c r="BR26">
+        <v>32</v>
+      </c>
+      <c r="BS26">
+        <v>5.4</v>
+      </c>
+      <c r="BT26">
+        <v>19</v>
+      </c>
+      <c r="BU26">
+        <v>4.9</v>
+      </c>
+      <c r="BV26">
+        <v>170</v>
+      </c>
+      <c r="BW26">
+        <v>6.4</v>
+      </c>
+      <c r="BX26">
+        <v>140</v>
+      </c>
+      <c r="BY26">
+        <v>6.2</v>
+      </c>
+      <c r="BZ26">
+        <v>13.5</v>
+      </c>
+      <c r="CA26">
+        <v>4.4</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27">
+        <v>2.34</v>
+      </c>
+      <c r="G27">
+        <v>2.48</v>
+      </c>
+      <c r="H27">
+        <v>3.3</v>
+      </c>
+      <c r="I27">
+        <v>3.55</v>
+      </c>
+      <c r="J27">
+        <v>3.3</v>
+      </c>
+      <c r="K27">
+        <v>3.5</v>
+      </c>
+      <c r="L27">
+        <v>1.45</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>3.35</v>
+      </c>
+      <c r="O27">
+        <v>1.39</v>
+      </c>
+      <c r="P27">
+        <v>1.79</v>
+      </c>
+      <c r="Q27">
+        <v>2.16</v>
+      </c>
+      <c r="R27">
+        <v>1.3</v>
+      </c>
+      <c r="S27">
+        <v>4</v>
+      </c>
+      <c r="T27">
+        <v>1.89</v>
+      </c>
+      <c r="U27">
+        <v>2.04</v>
+      </c>
+      <c r="V27">
+        <v>1.4</v>
+      </c>
+      <c r="W27">
+        <v>1.67</v>
+      </c>
+      <c r="X27">
+        <v>13</v>
+      </c>
+      <c r="Y27">
+        <v>13.5</v>
+      </c>
+      <c r="Z27">
+        <v>27</v>
+      </c>
+      <c r="AA27">
+        <v>75</v>
+      </c>
+      <c r="AB27">
+        <v>11</v>
+      </c>
+      <c r="AC27">
+        <v>8</v>
+      </c>
+      <c r="AD27">
+        <v>17</v>
+      </c>
+      <c r="AE27">
+        <v>50</v>
+      </c>
+      <c r="AF27">
+        <v>17.5</v>
+      </c>
+      <c r="AG27">
+        <v>13.5</v>
+      </c>
+      <c r="AH27">
+        <v>22</v>
+      </c>
+      <c r="AI27">
+        <v>65</v>
+      </c>
+      <c r="AJ27">
+        <v>40</v>
+      </c>
+      <c r="AK27">
+        <v>32</v>
+      </c>
+      <c r="AL27">
+        <v>50</v>
+      </c>
+      <c r="AM27">
+        <v>130</v>
+      </c>
+      <c r="AN27">
+        <v>27</v>
+      </c>
+      <c r="AO27">
+        <v>55</v>
+      </c>
+      <c r="AP27">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27">
+        <v>10.5</v>
+      </c>
+      <c r="AR27">
+        <v>19.5</v>
+      </c>
+      <c r="AS27">
+        <v>5.3</v>
+      </c>
+      <c r="AT27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27">
+        <v>6.8</v>
+      </c>
+      <c r="AV27">
+        <v>12.5</v>
+      </c>
+      <c r="AW27">
+        <v>5.3</v>
+      </c>
+      <c r="AX27">
+        <v>11.5</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
         <v>14</v>
       </c>
-      <c r="BA26">
+      <c r="BA27">
         <v>5.4</v>
       </c>
-      <c r="BB26">
+      <c r="BB27">
         <v>5.2</v>
       </c>
-      <c r="BC26">
+      <c r="BC27">
         <v>5.3</v>
       </c>
-      <c r="BD26">
+      <c r="BD27">
         <v>5.3</v>
       </c>
-      <c r="BE26">
+      <c r="BE27">
         <v>5.5</v>
       </c>
-      <c r="BF26">
+      <c r="BF27">
         <v>19</v>
       </c>
-      <c r="BG26">
+      <c r="BG27">
         <v>5.4</v>
       </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.01</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.01</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
-      <c r="BQ26">
-        <v>1.01</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
-      <c r="BS26">
-        <v>1.01</v>
-      </c>
-      <c r="BT26">
-        <v>1000</v>
-      </c>
-      <c r="BU26">
-        <v>1.01</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>1.01</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>1.01</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>1.01</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>145</v>
+      <c r="BH27">
+        <v>3.55</v>
+      </c>
+      <c r="BI27">
+        <v>2.64</v>
+      </c>
+      <c r="BJ27">
+        <v>11.5</v>
+      </c>
+      <c r="BK27">
+        <v>7.6</v>
+      </c>
+      <c r="BL27">
+        <v>160</v>
+      </c>
+      <c r="BM27">
+        <v>21</v>
+      </c>
+      <c r="BN27">
+        <v>5.8</v>
+      </c>
+      <c r="BO27">
+        <v>4.2</v>
+      </c>
+      <c r="BP27">
+        <v>21</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>40</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>7.2</v>
+      </c>
+      <c r="BU27">
+        <v>5.2</v>
+      </c>
+      <c r="BV27">
+        <v>32</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>48</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>36</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -463,7 +463,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 03:32:40</t>
+    <t>2026-09-29 05:48:08</t>
   </si>
 </sst>
 </file>
@@ -1057,22 +1057,22 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.43</v>
@@ -1081,16 +1081,16 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.33</v>
@@ -1099,70 +1099,70 @@
         <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN2">
         <v>21</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP2">
         <v>11</v>
@@ -1171,10 +1171,10 @@
         <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1186,97 +1186,97 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
         <v>29</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF2">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>970</v>
       </c>
       <c r="BI2">
-        <v>2.98</v>
+        <v>1.38</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="BL2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>1.59</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>1.81</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>4.7</v>
+        <v>2.22</v>
       </c>
       <c r="BZ2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,22 +1299,22 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.5</v>
@@ -1323,13 +1323,13 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
         <v>2.34</v>
@@ -1341,181 +1341,181 @@
         <v>4.4</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AA3">
         <v>150</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>46</v>
+      </c>
+      <c r="AF3">
         <v>15.5</v>
       </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>970</v>
-      </c>
       <c r="AG3">
+        <v>14</v>
+      </c>
+      <c r="AH3">
         <v>36</v>
       </c>
-      <c r="AH3">
-        <v>60</v>
-      </c>
       <c r="AI3">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK3">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AL3">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT3">
+        <v>4.7</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>13</v>
+      </c>
+      <c r="AW3">
+        <v>8.4</v>
+      </c>
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>9</v>
+      </c>
+      <c r="BB3">
         <v>6</v>
       </c>
-      <c r="AT3">
-        <v>7.4</v>
-      </c>
-      <c r="AU3">
-        <v>4.9</v>
-      </c>
-      <c r="AV3">
-        <v>12</v>
-      </c>
-      <c r="AW3">
-        <v>5.8</v>
-      </c>
-      <c r="AX3">
-        <v>5.7</v>
-      </c>
-      <c r="AY3">
-        <v>5.2</v>
-      </c>
-      <c r="AZ3">
-        <v>10</v>
-      </c>
-      <c r="BA3">
-        <v>6</v>
-      </c>
-      <c r="BB3">
-        <v>29</v>
-      </c>
       <c r="BC3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BD3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE3">
+        <v>9.6</v>
+      </c>
+      <c r="BF3">
         <v>7.8</v>
       </c>
-      <c r="BE3">
-        <v>6.2</v>
-      </c>
-      <c r="BF3">
-        <v>6.6</v>
-      </c>
       <c r="BG3">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BL3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1541,16 +1541,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1562,37 +1562,37 @@
         <v>1.5</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
         <v>1.28</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1601,7 +1601,7 @@
         <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA4">
         <v>250</v>
@@ -1610,13 +1610,13 @@
         <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>29</v>
       </c>
       <c r="AE4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF4">
         <v>8</v>
@@ -1625,7 +1625,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI4">
         <v>140</v>
@@ -1634,7 +1634,7 @@
         <v>15</v>
       </c>
       <c r="AK4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL4">
         <v>48</v>
@@ -1643,7 +1643,7 @@
         <v>210</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO4">
         <v>210</v>
@@ -1658,28 +1658,28 @@
         <v>50</v>
       </c>
       <c r="AS4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV4">
         <v>26</v>
       </c>
       <c r="AW4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AX4">
         <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA4">
         <v>100</v>
@@ -1688,10 +1688,10 @@
         <v>14</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE4">
         <v>120</v>
@@ -1703,64 +1703,64 @@
         <v>130</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BK4">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BN4">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BQ4">
-        <v>9.800000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="BR4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BU4">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BV4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BX4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1786,13 +1786,13 @@
         <v>3.05</v>
       </c>
       <c r="G5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
+        <v>2.82</v>
+      </c>
+      <c r="I5">
         <v>2.86</v>
-      </c>
-      <c r="I5">
-        <v>2.88</v>
       </c>
       <c r="J5">
         <v>3.05</v>
@@ -1801,7 +1801,7 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M5">
         <v>1.13</v>
@@ -1810,22 +1810,22 @@
         <v>2.74</v>
       </c>
       <c r="O5">
+        <v>1.56</v>
+      </c>
+      <c r="P5">
         <v>1.55</v>
       </c>
-      <c r="P5">
-        <v>1.57</v>
-      </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
         <v>1.86</v>
@@ -1852,25 +1852,25 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
         <v>42</v>
       </c>
       <c r="AF5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
         <v>14.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
         <v>55</v>
@@ -1879,16 +1879,16 @@
         <v>46</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN5">
+        <v>60</v>
+      </c>
+      <c r="AO5">
         <v>55</v>
-      </c>
-      <c r="AO5">
-        <v>48</v>
       </c>
       <c r="AP5">
         <v>8</v>
@@ -1900,10 +1900,10 @@
         <v>15</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -1912,97 +1912,97 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>17</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB5">
         <v>48</v>
       </c>
       <c r="BC5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BE5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF5">
         <v>46</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BK5">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BL5">
-        <v>230</v>
+        <v>620</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BN5">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BO5">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="BR5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="BT5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV5">
         <v>29</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>3.65</v>
       </c>
       <c r="BZ5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="s">
         <v>149</v>
@@ -2028,19 +2028,19 @@
         <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="K6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L6">
         <v>1.27</v>
@@ -2049,28 +2049,28 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V6">
         <v>1.11</v>
@@ -2085,166 +2085,166 @@
         <v>85</v>
       </c>
       <c r="Z6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC6">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD6">
         <v>80</v>
       </c>
       <c r="AE6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
         <v>260</v>
       </c>
       <c r="AJ6">
-        <v>12.5</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AO6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6">
+        <v>4.2</v>
+      </c>
+      <c r="AR6">
+        <v>4.2</v>
+      </c>
+      <c r="AS6">
+        <v>2.52</v>
+      </c>
+      <c r="AT6">
+        <v>5.3</v>
+      </c>
+      <c r="AU6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6">
         <v>13</v>
       </c>
-      <c r="AR6">
-        <v>9</v>
-      </c>
-      <c r="AS6">
-        <v>9.6</v>
-      </c>
-      <c r="AT6">
-        <v>10</v>
-      </c>
-      <c r="AU6">
-        <v>11</v>
-      </c>
-      <c r="AV6">
-        <v>13.5</v>
-      </c>
       <c r="AW6">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX6">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6">
-        <v>19.5</v>
+        <v>2.16</v>
       </c>
       <c r="BA6">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BC6">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD6">
+        <v>2.08</v>
+      </c>
+      <c r="BE6">
+        <v>2.16</v>
+      </c>
+      <c r="BF6">
+        <v>1.59</v>
+      </c>
+      <c r="BG6">
+        <v>4.2</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
         <v>7.6</v>
       </c>
-      <c r="BE6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF6">
-        <v>4.5</v>
-      </c>
-      <c r="BG6">
-        <v>15</v>
-      </c>
-      <c r="BH6">
-        <v>5.4</v>
-      </c>
-      <c r="BI6">
-        <v>4</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>4.5</v>
-      </c>
       <c r="BL6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>6.4</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
         <v>8.4</v>
       </c>
-      <c r="BQ6">
-        <v>4.1</v>
-      </c>
-      <c r="BR6">
-        <v>21</v>
-      </c>
-      <c r="BS6">
-        <v>5.8</v>
-      </c>
-      <c r="BT6">
-        <v>12.5</v>
-      </c>
-      <c r="BU6">
-        <v>4.8</v>
-      </c>
       <c r="BV6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BZ6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>149</v>
@@ -2273,10 +2273,10 @@
         <v>1.7</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>3.75</v>
@@ -2291,16 +2291,16 @@
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
         <v>1.49</v>
       </c>
       <c r="P7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
         <v>1.23</v>
@@ -2318,13 +2318,13 @@
         <v>1.16</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X7">
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z7">
         <v>55</v>
@@ -2336,10 +2336,10 @@
         <v>6.2</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE7">
         <v>140</v>
@@ -2348,7 +2348,7 @@
         <v>8.4</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>30</v>
@@ -2360,10 +2360,10 @@
         <v>16.5</v>
       </c>
       <c r="AK7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>700</v>
@@ -2384,22 +2384,22 @@
         <v>50</v>
       </c>
       <c r="AS7">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AT7">
         <v>5.7</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
         <v>25</v>
       </c>
       <c r="AW7">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
@@ -2408,10 +2408,10 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="BB7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC7">
         <v>20</v>
@@ -2420,73 +2420,73 @@
         <v>50</v>
       </c>
       <c r="BE7">
-        <v>18.5</v>
+        <v>100</v>
       </c>
       <c r="BF7">
         <v>13.5</v>
       </c>
       <c r="BG7">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="BH7">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="BK7">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL7">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>38</v>
+        <v>3.25</v>
       </c>
       <c r="BN7">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>28</v>
+        <v>3.25</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BU7">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BV7">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>55</v>
+        <v>3.25</v>
       </c>
       <c r="BX7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>65</v>
+        <v>3.25</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>24</v>
+        <v>3.25</v>
       </c>
       <c r="CB7" t="s">
         <v>149</v>
@@ -2509,10 +2509,10 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
         <v>2.32</v>
@@ -2533,16 +2533,16 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
         <v>1.27</v>
@@ -2554,22 +2554,22 @@
         <v>1.97</v>
       </c>
       <c r="U8">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V8">
         <v>1.74</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA8">
         <v>32</v>
@@ -2593,37 +2593,37 @@
         <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL8">
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN8">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP8">
         <v>10</v>
       </c>
       <c r="AQ8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS8">
         <v>28</v>
@@ -2632,7 +2632,7 @@
         <v>10.5</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>10.5</v>
@@ -2641,7 +2641,7 @@
         <v>25</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2650,85 +2650,85 @@
         <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC8">
         <v>42</v>
       </c>
       <c r="BD8">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BE8">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="BF8">
         <v>48</v>
       </c>
       <c r="BG8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BK8">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>3.05</v>
       </c>
       <c r="BN8">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>28</v>
+        <v>3.05</v>
       </c>
       <c r="BR8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>40</v>
+        <v>3.05</v>
       </c>
       <c r="BT8">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>15.5</v>
+        <v>2.86</v>
       </c>
       <c r="BX8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>30</v>
+        <v>3.05</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>30</v>
+        <v>3.05</v>
       </c>
       <c r="CB8" t="s">
         <v>149</v>
@@ -2751,16 +2751,16 @@
         <v>130</v>
       </c>
       <c r="F9">
+        <v>1.23</v>
+      </c>
+      <c r="G9">
         <v>1.24</v>
       </c>
-      <c r="G9">
-        <v>1.25</v>
-      </c>
       <c r="H9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9">
         <v>7.8</v>
@@ -2778,7 +2778,7 @@
         <v>6.8</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P9">
         <v>3</v>
@@ -2796,10 +2796,10 @@
         <v>2.08</v>
       </c>
       <c r="U9">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W9">
         <v>5.1</v>
@@ -2811,7 +2811,7 @@
         <v>55</v>
       </c>
       <c r="Z9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2820,13 +2820,13 @@
         <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AD9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE9">
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="AF9">
         <v>8.6</v>
@@ -2835,16 +2835,16 @@
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI9">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ9">
         <v>9.4</v>
       </c>
       <c r="AK9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL9">
         <v>36</v>
@@ -2853,34 +2853,34 @@
         <v>200</v>
       </c>
       <c r="AN9">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AO9">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AP9">
         <v>30</v>
       </c>
       <c r="AQ9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AR9">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AS9">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AW9">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AX9">
         <v>8.199999999999999</v>
@@ -2889,13 +2889,13 @@
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA9">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BB9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC9">
         <v>12</v>
@@ -2904,67 +2904,67 @@
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF9">
         <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="BH9">
+        <v>5.7</v>
+      </c>
+      <c r="BI9">
+        <v>4</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>8.6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.81</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>3.4</v>
+      </c>
+      <c r="BP9">
+        <v>6.4</v>
+      </c>
+      <c r="BQ9">
         <v>4.9</v>
       </c>
-      <c r="BI9">
-        <v>4.5</v>
-      </c>
-      <c r="BJ9">
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
         <v>12.5</v>
       </c>
-      <c r="BK9">
-        <v>11</v>
-      </c>
-      <c r="BL9">
-        <v>170</v>
-      </c>
-      <c r="BM9">
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
         <v>10</v>
       </c>
-      <c r="BN9">
-        <v>3.9</v>
-      </c>
-      <c r="BO9">
-        <v>3.6</v>
-      </c>
-      <c r="BP9">
-        <v>6.6</v>
-      </c>
-      <c r="BQ9">
-        <v>6</v>
-      </c>
-      <c r="BR9">
-        <v>25</v>
-      </c>
-      <c r="BS9">
-        <v>18</v>
-      </c>
-      <c r="BT9">
-        <v>19.5</v>
-      </c>
-      <c r="BU9">
-        <v>14</v>
-      </c>
       <c r="BV9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>1.06</v>
@@ -3005,7 +3005,7 @@
         <v>1.07</v>
       </c>
       <c r="J10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <v>22</v>
@@ -3026,7 +3026,7 @@
         <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
         <v>1.86</v>
@@ -3035,10 +3035,10 @@
         <v>2.12</v>
       </c>
       <c r="T10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V10">
         <v>15.5</v>
@@ -3047,28 +3047,28 @@
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Y10">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA10">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB10">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AD10">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AF10">
         <v>1000</v>
@@ -3080,7 +3080,7 @@
         <v>1000</v>
       </c>
       <c r="AI10">
-        <v>420</v>
+        <v>260</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3098,121 +3098,121 @@
         <v>1000</v>
       </c>
       <c r="AO10">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="AP10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ10">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AS10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT10">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="AU10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AV10">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AW10">
+        <v>9.4</v>
+      </c>
+      <c r="AX10">
+        <v>130</v>
+      </c>
+      <c r="AY10">
+        <v>60</v>
+      </c>
+      <c r="AZ10">
         <v>21</v>
       </c>
-      <c r="AX10">
-        <v>4.2</v>
-      </c>
-      <c r="AY10">
-        <v>4.2</v>
-      </c>
-      <c r="AZ10">
-        <v>3.5</v>
-      </c>
       <c r="BA10">
-        <v>3.5</v>
+        <v>22</v>
       </c>
       <c r="BB10">
         <v>4.2</v>
       </c>
       <c r="BC10">
-        <v>8.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="BD10">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BE10">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BH10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="BJ10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="BN10">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="BR10">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="BT10">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.05</v>
+        <v>1.2</v>
       </c>
       <c r="BV10">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BW10">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="BZ10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="CB10" t="s">
         <v>149</v>
@@ -3235,67 +3235,67 @@
         <v>132</v>
       </c>
       <c r="F11">
+        <v>10.5</v>
+      </c>
+      <c r="G11">
         <v>11</v>
       </c>
-      <c r="G11">
-        <v>11.5</v>
-      </c>
       <c r="H11">
+        <v>1.34</v>
+      </c>
+      <c r="I11">
         <v>1.35</v>
       </c>
-      <c r="I11">
-        <v>1.36</v>
-      </c>
       <c r="J11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R11">
         <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>22</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -3319,16 +3319,16 @@
         <v>38</v>
       </c>
       <c r="AH11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="AK11">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AL11">
         <v>150</v>
@@ -3337,19 +3337,19 @@
         <v>170</v>
       </c>
       <c r="AN11">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS11">
         <v>9.800000000000001</v>
@@ -3367,22 +3367,22 @@
         <v>13.5</v>
       </c>
       <c r="AX11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AY11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AZ11">
         <v>28</v>
       </c>
       <c r="BA11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB11">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="BC11">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BD11">
         <v>120</v>
@@ -3394,7 +3394,7 @@
         <v>200</v>
       </c>
       <c r="BG11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH11">
         <v>4</v>
@@ -3403,58 +3403,58 @@
         <v>3.75</v>
       </c>
       <c r="BJ11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="BL11">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="BN11">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>12.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BR11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT11">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BU11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>2.52</v>
       </c>
       <c r="BX11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="s">
         <v>149</v>
@@ -3483,58 +3483,58 @@
         <v>1.3</v>
       </c>
       <c r="H12">
+        <v>14</v>
+      </c>
+      <c r="I12">
         <v>15</v>
       </c>
-      <c r="I12">
-        <v>15.5</v>
-      </c>
       <c r="J12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L12">
         <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W12">
         <v>4.3</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Z12">
         <v>150</v>
@@ -3543,7 +3543,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC12">
         <v>14</v>
@@ -3552,7 +3552,7 @@
         <v>60</v>
       </c>
       <c r="AE12">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AF12">
         <v>6.8</v>
@@ -3564,22 +3564,22 @@
         <v>46</v>
       </c>
       <c r="AI12">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AJ12">
         <v>9</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM12">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AN12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO12">
         <v>550</v>
@@ -3591,10 +3591,10 @@
         <v>32</v>
       </c>
       <c r="AR12">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS12">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AT12">
         <v>6.8</v>
@@ -3606,97 +3606,97 @@
         <v>50</v>
       </c>
       <c r="AW12">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="AX12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
         <v>38</v>
       </c>
       <c r="BA12">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="BB12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BE12">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BF12">
         <v>5.4</v>
       </c>
       <c r="BG12">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BH12">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
+        <v>2.58</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.6</v>
+      </c>
+      <c r="BN12">
+        <v>3.85</v>
+      </c>
+      <c r="BO12">
+        <v>3.05</v>
+      </c>
+      <c r="BP12">
+        <v>8.6</v>
+      </c>
+      <c r="BQ12">
+        <v>2.02</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>2.6</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>2.64</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>2.6</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
         <v>13</v>
       </c>
-      <c r="BL12">
-        <v>300</v>
-      </c>
-      <c r="BM12">
-        <v>23</v>
-      </c>
-      <c r="BN12">
-        <v>3.4</v>
-      </c>
-      <c r="BO12">
-        <v>3.15</v>
-      </c>
-      <c r="BP12">
-        <v>7.4</v>
-      </c>
-      <c r="BQ12">
-        <v>6.4</v>
-      </c>
-      <c r="BR12">
-        <v>34</v>
-      </c>
-      <c r="BS12">
-        <v>21</v>
-      </c>
-      <c r="BT12">
-        <v>17</v>
-      </c>
-      <c r="BU12">
-        <v>13.5</v>
-      </c>
-      <c r="BV12">
-        <v>190</v>
-      </c>
-      <c r="BW12">
-        <v>23</v>
-      </c>
-      <c r="BX12">
-        <v>160</v>
-      </c>
-      <c r="BY12">
-        <v>17.5</v>
-      </c>
       <c r="BZ12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="CB12" t="s">
         <v>149</v>
@@ -3719,61 +3719,61 @@
         <v>134</v>
       </c>
       <c r="F13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G13">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I13">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
         <v>1.53</v>
       </c>
       <c r="M13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="O13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R13">
         <v>1.24</v>
       </c>
       <c r="S13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W13">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y13">
         <v>14</v>
@@ -3788,16 +3788,16 @@
         <v>6.6</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>23</v>
       </c>
       <c r="AE13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3809,34 +3809,34 @@
         <v>120</v>
       </c>
       <c r="AJ13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM13">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO13">
         <v>160</v>
       </c>
       <c r="AP13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ13">
         <v>13</v>
       </c>
       <c r="AR13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS13">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="AT13">
         <v>6.2</v>
@@ -3845,10 +3845,10 @@
         <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW13">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AX13">
         <v>8.6</v>
@@ -3860,85 +3860,85 @@
         <v>23</v>
       </c>
       <c r="BA13">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BB13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE13">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="BF13">
         <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="BH13">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BI13">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL13">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BP13">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BV13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>149</v>
@@ -3967,16 +3967,16 @@
         <v>4.9</v>
       </c>
       <c r="H14">
+        <v>1.93</v>
+      </c>
+      <c r="I14">
         <v>1.94</v>
       </c>
-      <c r="I14">
-        <v>1.95</v>
-      </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L14">
         <v>1.51</v>
@@ -3985,7 +3985,7 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14">
         <v>1.43</v>
@@ -4003,13 +4003,13 @@
         <v>4.5</v>
       </c>
       <c r="T14">
+        <v>2.08</v>
+      </c>
+      <c r="U14">
+        <v>1.89</v>
+      </c>
+      <c r="V14">
         <v>2.06</v>
-      </c>
-      <c r="U14">
-        <v>1.9</v>
-      </c>
-      <c r="V14">
-        <v>2.04</v>
       </c>
       <c r="W14">
         <v>1.25</v>
@@ -4018,7 +4018,7 @@
         <v>11</v>
       </c>
       <c r="Y14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z14">
         <v>10.5</v>
@@ -4030,7 +4030,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4042,31 +4042,31 @@
         <v>34</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK14">
         <v>70</v>
       </c>
       <c r="AL14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM14">
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AO14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP14">
         <v>10.5</v>
@@ -4075,7 +4075,7 @@
         <v>7</v>
       </c>
       <c r="AR14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS14">
         <v>20</v>
@@ -4084,7 +4084,7 @@
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV14">
         <v>10</v>
@@ -4102,85 +4102,85 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BB14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BC14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE14">
         <v>130</v>
       </c>
       <c r="BF14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BG14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH14">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BI14">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>8.6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>60</v>
+      </c>
+      <c r="BN14">
         <v>11.5</v>
       </c>
-      <c r="BK14">
-        <v>9.6</v>
-      </c>
-      <c r="BL14">
-        <v>210</v>
-      </c>
-      <c r="BM14">
-        <v>10</v>
-      </c>
-      <c r="BN14">
-        <v>8</v>
-      </c>
       <c r="BO14">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="BR14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="BT14">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BV14">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="BZ14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4203,25 +4203,25 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J15">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -4230,7 +4230,7 @@
         <v>4.5</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
         <v>2.22</v>
@@ -4239,37 +4239,37 @@
         <v>1.76</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T15">
         <v>1.68</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="Y15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z15">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AA15">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -4284,7 +4284,7 @@
         <v>30</v>
       </c>
       <c r="AG15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH15">
         <v>18</v>
@@ -4296,22 +4296,22 @@
         <v>90</v>
       </c>
       <c r="AK15">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="AL15">
         <v>55</v>
       </c>
       <c r="AM15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN15">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AO15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP15">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4320,19 +4320,19 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AT15">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV15">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AW15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX15">
         <v>26</v>
@@ -4341,85 +4341,85 @@
         <v>14.5</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA15">
         <v>27</v>
       </c>
       <c r="BB15">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BC15">
         <v>32</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE15">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF15">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BG15">
         <v>10</v>
       </c>
       <c r="BH15">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
         <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
         <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4445,10 +4445,10 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H16">
         <v>3</v>
@@ -4463,7 +4463,7 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
         <v>1.03</v>
@@ -4472,22 +4472,22 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q16">
         <v>1.54</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S16">
         <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U16">
         <v>2.74</v>
@@ -4496,172 +4496,172 @@
         <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X16">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y16">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="Z16">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AD16">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE16">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AF16">
         <v>19</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AI16">
         <v>85</v>
       </c>
       <c r="AJ16">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK16">
         <v>65</v>
       </c>
       <c r="AL16">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN16">
-        <v>13.5</v>
+        <v>600</v>
       </c>
       <c r="AO16">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AP16">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR16">
         <v>13</v>
       </c>
       <c r="AS16">
-        <v>6.2</v>
+        <v>2.36</v>
       </c>
       <c r="AT16">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16">
+        <v>7.6</v>
+      </c>
+      <c r="AW16">
+        <v>2.34</v>
+      </c>
+      <c r="AX16">
         <v>9</v>
       </c>
-      <c r="AV16">
-        <v>12.5</v>
-      </c>
-      <c r="AW16">
-        <v>25</v>
-      </c>
-      <c r="AX16">
-        <v>16</v>
-      </c>
       <c r="AY16">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA16">
-        <v>5.7</v>
+        <v>2.32</v>
       </c>
       <c r="BB16">
-        <v>25</v>
+        <v>2.34</v>
       </c>
       <c r="BC16">
-        <v>17.5</v>
+        <v>2.3</v>
       </c>
       <c r="BD16">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="BE16">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="BF16">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="BG16">
-        <v>15</v>
+        <v>3.55</v>
       </c>
       <c r="BH16">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4687,19 +4687,19 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G17">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I17">
+        <v>4.1</v>
+      </c>
+      <c r="J17">
         <v>3.9</v>
-      </c>
-      <c r="J17">
-        <v>3.95</v>
       </c>
       <c r="K17">
         <v>4.2</v>
@@ -4708,7 +4708,7 @@
         <v>1.3</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
         <v>5.3</v>
@@ -4717,193 +4717,193 @@
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q17">
         <v>1.63</v>
       </c>
       <c r="R17">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S17">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T17">
         <v>1.59</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X17">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Y17">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z17">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AA17">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB17">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC17">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD17">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE17">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AF17">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AI17">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ17">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK17">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL17">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AO17">
-        <v>28</v>
+        <v>600</v>
       </c>
       <c r="AP17">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="AQ17">
-        <v>16.5</v>
+        <v>2.04</v>
       </c>
       <c r="AR17">
-        <v>14.5</v>
+        <v>2.12</v>
       </c>
       <c r="AS17">
-        <v>13</v>
+        <v>2.14</v>
       </c>
       <c r="AT17">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AU17">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV17">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW17">
-        <v>11</v>
+        <v>2.12</v>
       </c>
       <c r="AX17">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="AY17">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ17">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA17">
-        <v>11</v>
+        <v>2.12</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>2.08</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BD17">
-        <v>14.5</v>
+        <v>2.1</v>
       </c>
       <c r="BE17">
-        <v>11.5</v>
+        <v>2.16</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="BG17">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BH17">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
         <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
@@ -4929,28 +4929,28 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G18">
         <v>2.26</v>
       </c>
       <c r="H18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I18">
         <v>3.5</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
         <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
         <v>4.8</v>
@@ -4959,22 +4959,22 @@
         <v>1.24</v>
       </c>
       <c r="P18">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R18">
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T18">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -4983,112 +4983,112 @@
         <v>1.79</v>
       </c>
       <c r="X18">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Y18">
         <v>19.5</v>
       </c>
       <c r="Z18">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AA18">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB18">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC18">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="AD18">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AE18">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AF18">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG18">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH18">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AI18">
         <v>150</v>
       </c>
       <c r="AJ18">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK18">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AL18">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN18">
-        <v>13.5</v>
+        <v>600</v>
       </c>
       <c r="AO18">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP18">
+        <v>6.8</v>
+      </c>
+      <c r="AQ18">
+        <v>11</v>
+      </c>
+      <c r="AR18">
         <v>17</v>
       </c>
-      <c r="AQ18">
-        <v>14</v>
-      </c>
-      <c r="AR18">
-        <v>6.6</v>
-      </c>
       <c r="AS18">
-        <v>7.4</v>
+        <v>2.94</v>
       </c>
       <c r="AT18">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AV18">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AX18">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BA18">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="BB18">
         <v>13</v>
       </c>
       <c r="BC18">
+        <v>13</v>
+      </c>
+      <c r="BD18">
         <v>18</v>
       </c>
-      <c r="BD18">
-        <v>14.5</v>
-      </c>
       <c r="BE18">
-        <v>7.4</v>
+        <v>2.96</v>
       </c>
       <c r="BF18">
-        <v>11</v>
+        <v>2.94</v>
       </c>
       <c r="BG18">
-        <v>6.8</v>
+        <v>2.68</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5097,7 +5097,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5109,43 +5109,43 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5177,7 +5177,7 @@
         <v>2.32</v>
       </c>
       <c r="H19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I19">
         <v>3.4</v>
@@ -5186,13 +5186,13 @@
         <v>3.75</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>1.34</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
         <v>4.5</v>
@@ -5204,19 +5204,19 @@
         <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T19">
         <v>1.63</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
         <v>1.41</v>
@@ -5225,169 +5225,169 @@
         <v>1.75</v>
       </c>
       <c r="X19">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Y19">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z19">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AA19">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB19">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE19">
         <v>90</v>
       </c>
       <c r="AF19">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG19">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AH19">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AI19">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ19">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK19">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL19">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM19">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN19">
-        <v>14.5</v>
+        <v>600</v>
       </c>
       <c r="AO19">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AP19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AQ19">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR19">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS19">
+        <v>2.32</v>
+      </c>
+      <c r="AT19">
+        <v>6.4</v>
+      </c>
+      <c r="AU19">
+        <v>7.4</v>
+      </c>
+      <c r="AV19">
+        <v>8.4</v>
+      </c>
+      <c r="AW19">
+        <v>2.28</v>
+      </c>
+      <c r="AX19">
+        <v>12</v>
+      </c>
+      <c r="AY19">
         <v>6.2</v>
       </c>
-      <c r="AT19">
-        <v>10.5</v>
-      </c>
-      <c r="AU19">
-        <v>7.8</v>
-      </c>
-      <c r="AV19">
-        <v>12</v>
-      </c>
-      <c r="AW19">
-        <v>16</v>
-      </c>
-      <c r="AX19">
-        <v>13.5</v>
-      </c>
-      <c r="AY19">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA19">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB19">
-        <v>24</v>
+        <v>2.28</v>
       </c>
       <c r="BC19">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BD19">
-        <v>26</v>
+        <v>2.26</v>
       </c>
       <c r="BE19">
-        <v>6.4</v>
+        <v>2.32</v>
       </c>
       <c r="BF19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="BG19">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="BH19">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BP19">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BV19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
         <v>1.02</v>
       </c>
       <c r="BZ19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
@@ -5413,22 +5413,22 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J20">
         <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>1.26</v>
@@ -5440,196 +5440,196 @@
         <v>6.2</v>
       </c>
       <c r="O20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P20">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q20">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S20">
         <v>2.28</v>
       </c>
       <c r="T20">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V20">
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="Y20">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="Z20">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AA20">
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC20">
+        <v>13</v>
+      </c>
+      <c r="AD20">
+        <v>970</v>
+      </c>
+      <c r="AE20">
+        <v>190</v>
+      </c>
+      <c r="AF20">
+        <v>40</v>
+      </c>
+      <c r="AG20">
+        <v>13</v>
+      </c>
+      <c r="AH20">
+        <v>25</v>
+      </c>
+      <c r="AI20">
+        <v>150</v>
+      </c>
+      <c r="AJ20">
+        <v>900</v>
+      </c>
+      <c r="AK20">
+        <v>65</v>
+      </c>
+      <c r="AL20">
+        <v>48</v>
+      </c>
+      <c r="AM20">
+        <v>580</v>
+      </c>
+      <c r="AN20">
+        <v>85</v>
+      </c>
+      <c r="AO20">
+        <v>260</v>
+      </c>
+      <c r="AP20">
+        <v>2.68</v>
+      </c>
+      <c r="AQ20">
+        <v>16</v>
+      </c>
+      <c r="AR20">
+        <v>2.68</v>
+      </c>
+      <c r="AS20">
+        <v>2.76</v>
+      </c>
+      <c r="AT20">
+        <v>7.6</v>
+      </c>
+      <c r="AU20">
+        <v>7.8</v>
+      </c>
+      <c r="AV20">
+        <v>12.5</v>
+      </c>
+      <c r="AW20">
+        <v>2.7</v>
+      </c>
+      <c r="AX20">
+        <v>7.6</v>
+      </c>
+      <c r="AY20">
+        <v>7.8</v>
+      </c>
+      <c r="AZ20">
         <v>11</v>
       </c>
-      <c r="AD20">
-        <v>19.5</v>
-      </c>
-      <c r="AE20">
-        <v>100</v>
-      </c>
-      <c r="AF20">
-        <v>15.5</v>
-      </c>
-      <c r="AG20">
-        <v>11</v>
-      </c>
-      <c r="AH20">
-        <v>15.5</v>
-      </c>
-      <c r="AI20">
-        <v>44</v>
-      </c>
-      <c r="AJ20">
-        <v>22</v>
-      </c>
-      <c r="AK20">
-        <v>17.5</v>
-      </c>
-      <c r="AL20">
-        <v>25</v>
-      </c>
-      <c r="AM20">
-        <v>250</v>
-      </c>
-      <c r="AN20">
-        <v>7.6</v>
-      </c>
-      <c r="AO20">
-        <v>32</v>
-      </c>
-      <c r="AP20">
-        <v>20</v>
-      </c>
-      <c r="AQ20">
-        <v>21</v>
-      </c>
-      <c r="AR20">
-        <v>18</v>
-      </c>
-      <c r="AS20">
-        <v>10</v>
-      </c>
-      <c r="AT20">
-        <v>12</v>
-      </c>
-      <c r="AU20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>16</v>
-      </c>
-      <c r="AW20">
-        <v>20</v>
-      </c>
-      <c r="AX20">
-        <v>12.5</v>
-      </c>
-      <c r="AY20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20">
-        <v>13</v>
-      </c>
       <c r="BA20">
-        <v>20</v>
+        <v>2.7</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BC20">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD20">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BE20">
-        <v>23</v>
+        <v>2.74</v>
       </c>
       <c r="BF20">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>2.58</v>
       </c>
       <c r="BH20">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
         <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5655,7 +5655,7 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G21">
         <v>2.32</v>
@@ -5664,13 +5664,13 @@
         <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.35</v>
@@ -5679,199 +5679,199 @@
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T21">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
         <v>1.75</v>
       </c>
       <c r="X21">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y21">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Z21">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AA21">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC21">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AE21">
         <v>90</v>
       </c>
       <c r="AF21">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH21">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AI21">
         <v>150</v>
       </c>
       <c r="AJ21">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL21">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM21">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN21">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="AO21">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP21">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
+        <v>11</v>
+      </c>
+      <c r="AR21">
+        <v>14</v>
+      </c>
+      <c r="AS21">
+        <v>3</v>
+      </c>
+      <c r="AT21">
+        <v>8.6</v>
+      </c>
+      <c r="AU21">
+        <v>6.6</v>
+      </c>
+      <c r="AV21">
+        <v>9.4</v>
+      </c>
+      <c r="AW21">
+        <v>19</v>
+      </c>
+      <c r="AX21">
+        <v>11</v>
+      </c>
+      <c r="AY21">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21">
         <v>12.5</v>
       </c>
-      <c r="AR21">
-        <v>20</v>
-      </c>
-      <c r="AS21">
-        <v>23</v>
-      </c>
-      <c r="AT21">
-        <v>10</v>
-      </c>
-      <c r="AU21">
-        <v>7.6</v>
-      </c>
-      <c r="AV21">
-        <v>12</v>
-      </c>
-      <c r="AW21">
-        <v>16.5</v>
-      </c>
-      <c r="AX21">
+      <c r="BA21">
+        <v>21</v>
+      </c>
+      <c r="BB21">
+        <v>14.5</v>
+      </c>
+      <c r="BC21">
         <v>14</v>
-      </c>
-      <c r="AY21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21">
-        <v>14</v>
-      </c>
-      <c r="BA21">
-        <v>34</v>
-      </c>
-      <c r="BB21">
-        <v>15</v>
-      </c>
-      <c r="BC21">
-        <v>20</v>
       </c>
       <c r="BD21">
         <v>16</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="BF21">
-        <v>13.5</v>
+        <v>3.1</v>
       </c>
       <c r="BG21">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BH21">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
@@ -5897,22 +5897,22 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G22">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H22">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="I22">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="J22">
         <v>4.2</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
         <v>1.26</v>
@@ -5921,91 +5921,91 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R22">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T22">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="U22">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X22">
         <v>29</v>
       </c>
       <c r="Y22">
+        <v>25</v>
+      </c>
+      <c r="Z22">
+        <v>26</v>
+      </c>
+      <c r="AA22">
+        <v>50</v>
+      </c>
+      <c r="AB22">
         <v>21</v>
       </c>
-      <c r="Z22">
-        <v>25</v>
-      </c>
-      <c r="AA22">
-        <v>46</v>
-      </c>
-      <c r="AB22">
-        <v>18.5</v>
-      </c>
       <c r="AC22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD22">
         <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AF22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AJ22">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK22">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AL22">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AM22">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AN22">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AO22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP22">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22">
         <v>17.5</v>
@@ -6026,16 +6026,16 @@
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AX22">
         <v>18</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA22">
         <v>24</v>
@@ -6050,73 +6050,73 @@
         <v>23</v>
       </c>
       <c r="BE22">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BF22">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG22">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BH22">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>149</v>
@@ -6151,19 +6151,19 @@
         <v>1.79</v>
       </c>
       <c r="J23">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>1.32</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>1.23</v>
@@ -6172,16 +6172,16 @@
         <v>2.36</v>
       </c>
       <c r="Q23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R23">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T23">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="U23">
         <v>2.34</v>
@@ -6190,28 +6190,28 @@
         <v>2.26</v>
       </c>
       <c r="W23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X23">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y23">
         <v>11.5</v>
       </c>
       <c r="Z23">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AA23">
         <v>20</v>
       </c>
       <c r="AB23">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AC23">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD23">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE23">
         <v>17.5</v>
@@ -6220,34 +6220,34 @@
         <v>40</v>
       </c>
       <c r="AG23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI23">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AJ23">
+        <v>900</v>
+      </c>
+      <c r="AK23">
         <v>700</v>
       </c>
-      <c r="AK23">
-        <v>190</v>
-      </c>
       <c r="AL23">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AM23">
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AO23">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AP23">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23">
         <v>10</v>
@@ -6256,13 +6256,13 @@
         <v>11</v>
       </c>
       <c r="AS23">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23">
         <v>18</v>
       </c>
       <c r="AU23">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AV23">
         <v>9</v>
@@ -6283,79 +6283,79 @@
         <v>24</v>
       </c>
       <c r="BB23">
-        <v>46</v>
+        <v>7.6</v>
       </c>
       <c r="BC23">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BD23">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BE23">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG23">
         <v>8</v>
       </c>
       <c r="BH23">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
@@ -6384,16 +6384,16 @@
         <v>4.6</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H24">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I24">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
         <v>3.65</v>
@@ -6405,16 +6405,16 @@
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
         <v>1.28</v>
@@ -6423,10 +6423,10 @@
         <v>4.3</v>
       </c>
       <c r="T24">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U24">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V24">
         <v>2</v>
@@ -6435,112 +6435,112 @@
         <v>1.25</v>
       </c>
       <c r="X24">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y24">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA24">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="AB24">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE24">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AF24">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AG24">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AH24">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AI24">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AJ24">
         <v>500</v>
       </c>
       <c r="AK24">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AL24">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM24">
         <v>580</v>
       </c>
       <c r="AN24">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AP24">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AQ24">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AR24">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS24">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AT24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU24">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV24">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW24">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AX24">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AY24">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ24">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA24">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BB24">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BC24">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BD24">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BE24">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BF24">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BG24">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6623,226 +6623,226 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="G25">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="H25">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I25">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K25">
+        <v>4.3</v>
+      </c>
+      <c r="L25">
+        <v>1.32</v>
+      </c>
+      <c r="M25">
+        <v>1.04</v>
+      </c>
+      <c r="N25">
         <v>4.6</v>
-      </c>
-      <c r="L25">
-        <v>1.31</v>
-      </c>
-      <c r="M25">
-        <v>1.03</v>
-      </c>
-      <c r="N25">
-        <v>4.4</v>
       </c>
       <c r="O25">
         <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q25">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S25">
+        <v>2.7</v>
+      </c>
+      <c r="T25">
+        <v>1.64</v>
+      </c>
+      <c r="U25">
+        <v>2.32</v>
+      </c>
+      <c r="V25">
+        <v>1.32</v>
+      </c>
+      <c r="W25">
+        <v>1.94</v>
+      </c>
+      <c r="X25">
+        <v>42</v>
+      </c>
+      <c r="Y25">
+        <v>34</v>
+      </c>
+      <c r="Z25">
+        <v>85</v>
+      </c>
+      <c r="AA25">
+        <v>900</v>
+      </c>
+      <c r="AB25">
+        <v>19</v>
+      </c>
+      <c r="AC25">
+        <v>42</v>
+      </c>
+      <c r="AD25">
+        <v>85</v>
+      </c>
+      <c r="AE25">
+        <v>120</v>
+      </c>
+      <c r="AF25">
+        <v>40</v>
+      </c>
+      <c r="AG25">
+        <v>36</v>
+      </c>
+      <c r="AH25">
+        <v>60</v>
+      </c>
+      <c r="AI25">
+        <v>130</v>
+      </c>
+      <c r="AJ25">
+        <v>900</v>
+      </c>
+      <c r="AK25">
+        <v>65</v>
+      </c>
+      <c r="AL25">
+        <v>180</v>
+      </c>
+      <c r="AM25">
+        <v>580</v>
+      </c>
+      <c r="AN25">
+        <v>85</v>
+      </c>
+      <c r="AO25">
+        <v>230</v>
+      </c>
+      <c r="AP25">
         <v>2.5</v>
       </c>
-      <c r="T25">
-        <v>1.01</v>
-      </c>
-      <c r="U25">
-        <v>1.01</v>
-      </c>
-      <c r="V25">
-        <v>1.27</v>
-      </c>
-      <c r="W25">
-        <v>2.04</v>
-      </c>
-      <c r="X25">
-        <v>1000</v>
-      </c>
-      <c r="Y25">
-        <v>1000</v>
-      </c>
-      <c r="Z25">
-        <v>1000</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
-        <v>1000</v>
-      </c>
-      <c r="AC25">
-        <v>1000</v>
-      </c>
-      <c r="AD25">
-        <v>1000</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>11.5</v>
-      </c>
-      <c r="AH25">
-        <v>1000</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
-        <v>1.01</v>
-      </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS25">
-        <v>32</v>
+        <v>2.5</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AU25">
         <v>7.4</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA25">
-        <v>24</v>
+        <v>2.5</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH25">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>149</v>
@@ -6874,16 +6874,16 @@
         <v>13</v>
       </c>
       <c r="I26">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="J26">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M26">
         <v>1.04</v>
@@ -6895,196 +6895,196 @@
         <v>1.24</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q26">
         <v>1.73</v>
       </c>
       <c r="R26">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S26">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T26">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U26">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V26">
         <v>1.07</v>
       </c>
       <c r="W26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X26">
         <v>60</v>
       </c>
       <c r="Y26">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="Z26">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AC26">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD26">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="AE26">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AH26">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AI26">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AK26">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AL26">
         <v>330</v>
       </c>
       <c r="AM26">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AO26">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AQ26">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR26">
+        <v>23</v>
+      </c>
+      <c r="AS26">
+        <v>4.2</v>
+      </c>
+      <c r="AT26">
+        <v>6.2</v>
+      </c>
+      <c r="AU26">
         <v>12</v>
       </c>
-      <c r="AS26">
-        <v>13.5</v>
-      </c>
-      <c r="AT26">
+      <c r="AV26">
+        <v>10</v>
+      </c>
+      <c r="AW26">
+        <v>38</v>
+      </c>
+      <c r="AX26">
+        <v>6.4</v>
+      </c>
+      <c r="AY26">
+        <v>6.6</v>
+      </c>
+      <c r="AZ26">
+        <v>8.6</v>
+      </c>
+      <c r="BA26">
+        <v>4.2</v>
+      </c>
+      <c r="BB26">
+        <v>7.6</v>
+      </c>
+      <c r="BC26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD26">
         <v>7.2</v>
       </c>
-      <c r="AU26">
-        <v>12.5</v>
-      </c>
-      <c r="AV26">
-        <v>11</v>
-      </c>
-      <c r="AW26">
-        <v>12.5</v>
-      </c>
-      <c r="AX26">
-        <v>6.6</v>
-      </c>
-      <c r="AY26">
-        <v>10</v>
-      </c>
-      <c r="AZ26">
-        <v>14.5</v>
-      </c>
-      <c r="BA26">
-        <v>12.5</v>
-      </c>
-      <c r="BB26">
-        <v>8.4</v>
-      </c>
-      <c r="BC26">
-        <v>13.5</v>
-      </c>
-      <c r="BD26">
-        <v>17.5</v>
-      </c>
       <c r="BE26">
-        <v>12.5</v>
+        <v>2.46</v>
       </c>
       <c r="BF26">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG26">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH26">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>3.6</v>
+        <v>970</v>
       </c>
       <c r="BO26">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>149</v>
@@ -7107,16 +7107,16 @@
         <v>148</v>
       </c>
       <c r="F27">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G27">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J27">
         <v>3.3</v>
@@ -7134,7 +7134,7 @@
         <v>3.35</v>
       </c>
       <c r="O27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P27">
         <v>1.79</v>
@@ -7149,181 +7149,181 @@
         <v>4</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="U27">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V27">
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X27">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
-        <v>19.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS27">
-        <v>5.3</v>
+        <v>1.21</v>
       </c>
       <c r="AT27">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AU27">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="AV27">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="AW27">
-        <v>5.3</v>
+        <v>1.21</v>
       </c>
       <c r="AX27">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>1.23</v>
       </c>
       <c r="BA27">
-        <v>5.4</v>
+        <v>1.21</v>
       </c>
       <c r="BB27">
-        <v>5.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC27">
-        <v>5.3</v>
+        <v>1.21</v>
       </c>
       <c r="BD27">
-        <v>5.3</v>
+        <v>1.21</v>
       </c>
       <c r="BE27">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="BF27">
-        <v>19</v>
+        <v>1.21</v>
       </c>
       <c r="BG27">
-        <v>5.4</v>
+        <v>1.21</v>
       </c>
       <c r="BH27">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
         <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
         <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
         <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -328,12 +328,12 @@
     <t>Luxembourg</t>
   </si>
   <si>
+    <t>San Marino</t>
+  </si>
+  <si>
     <t>Spain</t>
   </si>
   <si>
-    <t>San Marino</t>
-  </si>
-  <si>
     <t>Czechia</t>
   </si>
   <si>
@@ -406,12 +406,12 @@
     <t>Iceland</t>
   </si>
   <si>
+    <t>Albania</t>
+  </si>
+  <si>
     <t>Croatia</t>
   </si>
   <si>
-    <t>Albania</t>
-  </si>
-  <si>
     <t>England</t>
   </si>
   <si>
@@ -463,7 +463,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 05:48:08</t>
+    <t>2026-09-29 07:59:09</t>
   </si>
 </sst>
 </file>
@@ -1057,226 +1057,226 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL2">
+        <v>46</v>
+      </c>
+      <c r="AM2">
+        <v>140</v>
+      </c>
+      <c r="AN2">
+        <v>20</v>
+      </c>
+      <c r="AO2">
         <v>95</v>
       </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
-      <c r="AN2">
-        <v>21</v>
-      </c>
-      <c r="AO2">
-        <v>600</v>
-      </c>
       <c r="AP2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS2">
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW2">
+        <v>55</v>
+      </c>
+      <c r="AX2">
+        <v>11</v>
+      </c>
+      <c r="AY2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>60</v>
+      </c>
+      <c r="BB2">
+        <v>22</v>
+      </c>
+      <c r="BC2">
+        <v>21</v>
+      </c>
+      <c r="BD2">
         <v>36</v>
       </c>
-      <c r="AX2">
+      <c r="BE2">
+        <v>95</v>
+      </c>
+      <c r="BF2">
+        <v>17.5</v>
+      </c>
+      <c r="BG2">
+        <v>24</v>
+      </c>
+      <c r="BH2">
+        <v>3.1</v>
+      </c>
+      <c r="BI2">
+        <v>2.74</v>
+      </c>
+      <c r="BJ2">
         <v>10.5</v>
       </c>
-      <c r="AY2">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>44</v>
-      </c>
-      <c r="BB2">
+      <c r="BK2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL2">
+        <v>190</v>
+      </c>
+      <c r="BM2">
+        <v>120</v>
+      </c>
+      <c r="BN2">
+        <v>6.2</v>
+      </c>
+      <c r="BO2">
+        <v>4.3</v>
+      </c>
+      <c r="BP2">
         <v>19.5</v>
       </c>
-      <c r="BC2">
-        <v>19.5</v>
-      </c>
-      <c r="BD2">
-        <v>29</v>
-      </c>
-      <c r="BE2">
-        <v>80</v>
-      </c>
-      <c r="BF2">
+      <c r="BQ2">
         <v>13.5</v>
       </c>
-      <c r="BG2">
-        <v>34</v>
-      </c>
-      <c r="BH2">
-        <v>970</v>
-      </c>
-      <c r="BI2">
-        <v>1.38</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>2.2</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>2.22</v>
-      </c>
-      <c r="BN2">
-        <v>970</v>
-      </c>
-      <c r="BO2">
-        <v>1.59</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>2.2</v>
-      </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BT2">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>1.81</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW2">
-        <v>2.22</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>2.22</v>
+        <v>5.9</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,226 +1299,226 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="J3">
         <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
+        <v>11.5</v>
+      </c>
+      <c r="Z3">
+        <v>27</v>
+      </c>
+      <c r="AA3">
         <v>75</v>
       </c>
-      <c r="Z3">
-        <v>970</v>
-      </c>
-      <c r="AA3">
-        <v>150</v>
-      </c>
       <c r="AB3">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH3">
+        <v>22</v>
+      </c>
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
         <v>36</v>
       </c>
-      <c r="AI3">
+      <c r="AK3">
+        <v>32</v>
+      </c>
+      <c r="AL3">
+        <v>55</v>
+      </c>
+      <c r="AM3">
         <v>160</v>
       </c>
-      <c r="AJ3">
+      <c r="AN3">
+        <v>27</v>
+      </c>
+      <c r="AO3">
+        <v>65</v>
+      </c>
+      <c r="AP3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ3">
+        <v>10</v>
+      </c>
+      <c r="AR3">
+        <v>19.5</v>
+      </c>
+      <c r="AS3">
+        <v>55</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>12</v>
+      </c>
+      <c r="AW3">
+        <v>38</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>18.5</v>
+      </c>
+      <c r="BA3">
+        <v>44</v>
+      </c>
+      <c r="BB3">
+        <v>26</v>
+      </c>
+      <c r="BC3">
+        <v>24</v>
+      </c>
+      <c r="BD3">
+        <v>32</v>
+      </c>
+      <c r="BE3">
+        <v>90</v>
+      </c>
+      <c r="BF3">
+        <v>21</v>
+      </c>
+      <c r="BG3">
+        <v>36</v>
+      </c>
+      <c r="BH3">
+        <v>3.1</v>
+      </c>
+      <c r="BI3">
+        <v>2.68</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>5.6</v>
+      </c>
+      <c r="BL3">
+        <v>180</v>
+      </c>
+      <c r="BM3">
+        <v>9.6</v>
+      </c>
+      <c r="BN3">
+        <v>5.1</v>
+      </c>
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
+        <v>970</v>
+      </c>
+      <c r="BQ3">
+        <v>6.4</v>
+      </c>
+      <c r="BR3">
+        <v>42</v>
+      </c>
+      <c r="BS3">
+        <v>8</v>
+      </c>
+      <c r="BT3">
+        <v>7.2</v>
+      </c>
+      <c r="BU3">
+        <v>4.5</v>
+      </c>
+      <c r="BV3">
         <v>40</v>
       </c>
-      <c r="AK3">
-        <v>120</v>
-      </c>
-      <c r="AL3">
-        <v>65</v>
-      </c>
-      <c r="AM3">
-        <v>580</v>
-      </c>
-      <c r="AN3">
-        <v>600</v>
-      </c>
-      <c r="AO3">
-        <v>600</v>
-      </c>
-      <c r="AP3">
-        <v>5.2</v>
-      </c>
-      <c r="AQ3">
-        <v>9.6</v>
-      </c>
-      <c r="AR3">
-        <v>17.5</v>
-      </c>
-      <c r="AS3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT3">
-        <v>4.7</v>
-      </c>
-      <c r="AU3">
-        <v>6.4</v>
-      </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
+      <c r="BW3">
+        <v>8</v>
+      </c>
+      <c r="BX3">
+        <v>55</v>
+      </c>
+      <c r="BY3">
         <v>8.4</v>
       </c>
-      <c r="AX3">
-        <v>13</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>12</v>
-      </c>
-      <c r="BA3">
-        <v>9</v>
-      </c>
-      <c r="BB3">
-        <v>6</v>
-      </c>
-      <c r="BC3">
-        <v>14</v>
-      </c>
-      <c r="BD3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE3">
-        <v>9.6</v>
-      </c>
-      <c r="BF3">
-        <v>7.8</v>
-      </c>
-      <c r="BG3">
-        <v>8.6</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.02</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.02</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.01</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.02</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.02</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.01</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.02</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>1.01</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>1.01</v>
-      </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>149</v>
@@ -1541,16 +1541,16 @@
         <v>125</v>
       </c>
       <c r="F4">
+        <v>1.63</v>
+      </c>
+      <c r="G4">
         <v>1.64</v>
       </c>
-      <c r="G4">
-        <v>1.65</v>
-      </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1559,43 +1559,43 @@
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4.3</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
         <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>18.5</v>
@@ -1607,49 +1607,49 @@
         <v>250</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>29</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI4">
         <v>140</v>
       </c>
       <c r="AJ4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO4">
         <v>210</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>17</v>
@@ -1658,109 +1658,109 @@
         <v>50</v>
       </c>
       <c r="AS4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA4">
         <v>100</v>
       </c>
       <c r="BB4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE4">
+        <v>160</v>
+      </c>
+      <c r="BF4">
+        <v>10.5</v>
+      </c>
+      <c r="BG4">
         <v>120</v>
       </c>
-      <c r="BF4">
+      <c r="BH4">
+        <v>3.05</v>
+      </c>
+      <c r="BI4">
+        <v>2.9</v>
+      </c>
+      <c r="BJ4">
+        <v>12.5</v>
+      </c>
+      <c r="BK4">
         <v>11</v>
       </c>
-      <c r="BG4">
-        <v>130</v>
-      </c>
-      <c r="BH4">
-        <v>3.35</v>
-      </c>
-      <c r="BI4">
-        <v>2.66</v>
-      </c>
-      <c r="BJ4">
-        <v>27</v>
-      </c>
-      <c r="BK4">
-        <v>8.6</v>
-      </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM4">
         <v>60</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
-        <v>2.68</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS4">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA4">
-        <v>3.15</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1783,16 +1783,16 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G5">
         <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J5">
         <v>3.05</v>
@@ -1801,7 +1801,7 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M5">
         <v>1.13</v>
@@ -1810,13 +1810,13 @@
         <v>2.74</v>
       </c>
       <c r="O5">
+        <v>1.55</v>
+      </c>
+      <c r="P5">
         <v>1.56</v>
       </c>
-      <c r="P5">
-        <v>1.55</v>
-      </c>
       <c r="Q5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.2</v>
@@ -1831,16 +1831,16 @@
         <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
         <v>8.6</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5">
         <v>16</v>
@@ -1855,7 +1855,7 @@
         <v>6.8</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>42</v>
@@ -1870,7 +1870,7 @@
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>55</v>
@@ -1882,28 +1882,28 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
         <v>15</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -1912,7 +1912,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX5">
         <v>17</v>
@@ -1924,10 +1924,10 @@
         <v>20</v>
       </c>
       <c r="BA5">
+        <v>55</v>
+      </c>
+      <c r="BB5">
         <v>50</v>
-      </c>
-      <c r="BB5">
-        <v>48</v>
       </c>
       <c r="BC5">
         <v>42</v>
@@ -1939,70 +1939,70 @@
         <v>120</v>
       </c>
       <c r="BF5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG5">
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="BI5">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5">
-        <v>620</v>
+        <v>230</v>
       </c>
       <c r="BM5">
         <v>60</v>
       </c>
       <c r="BN5">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ5">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BU5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW5">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA5">
-        <v>3.65</v>
+        <v>23</v>
       </c>
       <c r="CB5" t="s">
         <v>149</v>
@@ -2025,22 +2025,22 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.27</v>
@@ -2055,7 +2055,7 @@
         <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q6">
         <v>1.56</v>
@@ -2064,187 +2064,187 @@
         <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U6">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
         <v>1.11</v>
       </c>
       <c r="W6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X6">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD6">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF6">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG6">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6">
         <v>260</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>13</v>
       </c>
       <c r="AK6">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AL6">
+        <v>36</v>
+      </c>
+      <c r="AM6">
+        <v>140</v>
+      </c>
+      <c r="AN6">
+        <v>5.2</v>
+      </c>
+      <c r="AO6">
+        <v>150</v>
+      </c>
+      <c r="AP6">
+        <v>23</v>
+      </c>
+      <c r="AQ6">
+        <v>28</v>
+      </c>
+      <c r="AR6">
+        <v>11</v>
+      </c>
+      <c r="AS6">
+        <v>12.5</v>
+      </c>
+      <c r="AT6">
+        <v>10</v>
+      </c>
+      <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>26</v>
+      </c>
+      <c r="AW6">
+        <v>12</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>19</v>
+      </c>
+      <c r="BA6">
+        <v>11.5</v>
+      </c>
+      <c r="BB6">
+        <v>11</v>
+      </c>
+      <c r="BC6">
+        <v>12.5</v>
+      </c>
+      <c r="BD6">
+        <v>23</v>
+      </c>
+      <c r="BE6">
+        <v>28</v>
+      </c>
+      <c r="BF6">
+        <v>4.6</v>
+      </c>
+      <c r="BG6">
+        <v>15</v>
+      </c>
+      <c r="BH6">
+        <v>4.7</v>
+      </c>
+      <c r="BI6">
+        <v>4.1</v>
+      </c>
+      <c r="BJ6">
+        <v>10.5</v>
+      </c>
+      <c r="BK6">
+        <v>6</v>
+      </c>
+      <c r="BL6">
+        <v>130</v>
+      </c>
+      <c r="BM6">
+        <v>12.5</v>
+      </c>
+      <c r="BN6">
+        <v>4.1</v>
+      </c>
+      <c r="BO6">
+        <v>3.7</v>
+      </c>
+      <c r="BP6">
+        <v>8</v>
+      </c>
+      <c r="BQ6">
+        <v>5.1</v>
+      </c>
+      <c r="BR6">
+        <v>22</v>
+      </c>
+      <c r="BS6">
+        <v>8.4</v>
+      </c>
+      <c r="BT6">
+        <v>12.5</v>
+      </c>
+      <c r="BU6">
+        <v>6.6</v>
+      </c>
+      <c r="BV6">
+        <v>65</v>
+      </c>
+      <c r="BW6">
+        <v>11.5</v>
+      </c>
+      <c r="BX6">
         <v>60</v>
       </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>29</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>2.1</v>
-      </c>
-      <c r="AQ6">
-        <v>4.2</v>
-      </c>
-      <c r="AR6">
-        <v>4.2</v>
-      </c>
-      <c r="AS6">
-        <v>2.52</v>
-      </c>
-      <c r="AT6">
-        <v>5.3</v>
-      </c>
-      <c r="AU6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV6">
-        <v>13</v>
-      </c>
-      <c r="AW6">
-        <v>4.2</v>
-      </c>
-      <c r="AX6">
-        <v>4.8</v>
-      </c>
-      <c r="AY6">
-        <v>5.1</v>
-      </c>
-      <c r="AZ6">
-        <v>2.16</v>
-      </c>
-      <c r="BA6">
-        <v>4.2</v>
-      </c>
-      <c r="BB6">
-        <v>6</v>
-      </c>
-      <c r="BC6">
-        <v>6.8</v>
-      </c>
-      <c r="BD6">
-        <v>2.08</v>
-      </c>
-      <c r="BE6">
-        <v>2.16</v>
-      </c>
-      <c r="BF6">
-        <v>1.59</v>
-      </c>
-      <c r="BG6">
-        <v>4.2</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>7.6</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>3.3</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>6.4</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.01</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>8.4</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
+      <c r="BY6">
+        <v>11</v>
+      </c>
+      <c r="BZ6">
+        <v>11.5</v>
+      </c>
+      <c r="CA6">
         <v>6.2</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>6.2</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>149</v>
@@ -2267,22 +2267,22 @@
         <v>128</v>
       </c>
       <c r="F7">
+        <v>1.68</v>
+      </c>
+      <c r="G7">
         <v>1.69</v>
       </c>
-      <c r="G7">
-        <v>1.7</v>
-      </c>
       <c r="H7">
+        <v>6.8</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="I7">
-        <v>7.2</v>
-      </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
         <v>1.55</v>
@@ -2300,7 +2300,7 @@
         <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
         <v>1.23</v>
@@ -2309,7 +2309,7 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
         <v>1.7</v>
@@ -2330,85 +2330,85 @@
         <v>55</v>
       </c>
       <c r="AA7">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB7">
         <v>6.2</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE7">
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>160</v>
       </c>
       <c r="AJ7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM7">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO7">
         <v>250</v>
       </c>
       <c r="AP7">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR7">
         <v>50</v>
       </c>
       <c r="AS7">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="AT7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU7">
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW7">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AX7">
         <v>7.8</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA7">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BB7">
         <v>15</v>
@@ -2420,73 +2420,73 @@
         <v>50</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="BF7">
         <v>13.5</v>
       </c>
       <c r="BG7">
+        <v>170</v>
+      </c>
+      <c r="BH7">
+        <v>2.82</v>
+      </c>
+      <c r="BI7">
+        <v>2.68</v>
+      </c>
+      <c r="BJ7">
+        <v>13</v>
+      </c>
+      <c r="BK7">
+        <v>11</v>
+      </c>
+      <c r="BL7">
+        <v>280</v>
+      </c>
+      <c r="BM7">
+        <v>17</v>
+      </c>
+      <c r="BN7">
+        <v>3.9</v>
+      </c>
+      <c r="BO7">
+        <v>3.6</v>
+      </c>
+      <c r="BP7">
+        <v>12</v>
+      </c>
+      <c r="BQ7">
+        <v>10.5</v>
+      </c>
+      <c r="BR7">
+        <v>38</v>
+      </c>
+      <c r="BS7">
+        <v>13</v>
+      </c>
+      <c r="BT7">
+        <v>10</v>
+      </c>
+      <c r="BU7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV7">
+        <v>95</v>
+      </c>
+      <c r="BW7">
+        <v>15</v>
+      </c>
+      <c r="BX7">
         <v>110</v>
       </c>
-      <c r="BH7">
-        <v>3.1</v>
-      </c>
-      <c r="BI7">
-        <v>2.5</v>
-      </c>
-      <c r="BJ7">
-        <v>29</v>
-      </c>
-      <c r="BK7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>3.25</v>
-      </c>
-      <c r="BN7">
-        <v>4.6</v>
-      </c>
-      <c r="BO7">
-        <v>3.4</v>
-      </c>
-      <c r="BP7">
-        <v>27</v>
-      </c>
-      <c r="BQ7">
-        <v>8.4</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>3.25</v>
-      </c>
-      <c r="BT7">
-        <v>16</v>
-      </c>
-      <c r="BU7">
-        <v>7.2</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>3.25</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
       <c r="BY7">
-        <v>3.25</v>
+        <v>15.5</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA7">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>149</v>
@@ -2509,16 +2509,16 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I8">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J8">
         <v>3.4</v>
@@ -2536,19 +2536,19 @@
         <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
         <v>1.27</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T8">
         <v>1.97</v>
@@ -2557,13 +2557,13 @@
         <v>2</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W8">
         <v>1.37</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
         <v>8.4</v>
@@ -2572,10 +2572,10 @@
         <v>13</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2590,7 +2590,7 @@
         <v>25</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH8">
         <v>19.5</v>
@@ -2599,25 +2599,25 @@
         <v>46</v>
       </c>
       <c r="AJ8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL8">
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
         <v>8</v>
@@ -2626,7 +2626,7 @@
         <v>12</v>
       </c>
       <c r="AS8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -2644,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="AY8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
         <v>18.5</v>
@@ -2671,64 +2671,64 @@
         <v>23</v>
       </c>
       <c r="BH8">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM8">
-        <v>3.05</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ8">
-        <v>3.05</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS8">
-        <v>3.05</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BU8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW8">
-        <v>2.86</v>
+        <v>9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY8">
-        <v>3.05</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA8">
-        <v>3.05</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>149</v>
@@ -2751,226 +2751,226 @@
         <v>130</v>
       </c>
       <c r="F9">
-        <v>1.23</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>1.24</v>
+        <v>80</v>
       </c>
       <c r="H9">
+        <v>1.06</v>
+      </c>
+      <c r="I9">
+        <v>1.07</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>21</v>
+      </c>
+      <c r="L9">
+        <v>1.22</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>7.8</v>
+      </c>
+      <c r="O9">
+        <v>1.13</v>
+      </c>
+      <c r="P9">
+        <v>3.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.43</v>
+      </c>
+      <c r="R9">
+        <v>1.88</v>
+      </c>
+      <c r="S9">
+        <v>2.1</v>
+      </c>
+      <c r="T9">
+        <v>4.7</v>
+      </c>
+      <c r="U9">
+        <v>1.25</v>
+      </c>
+      <c r="V9">
         <v>15</v>
       </c>
-      <c r="I9">
-        <v>16</v>
-      </c>
-      <c r="J9">
-        <v>7.8</v>
-      </c>
-      <c r="K9">
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>50</v>
+      </c>
+      <c r="Y9">
+        <v>11</v>
+      </c>
+      <c r="Z9">
+        <v>6.6</v>
+      </c>
+      <c r="AA9">
+        <v>6</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>120</v>
+      </c>
+      <c r="AD9">
+        <v>24</v>
+      </c>
+      <c r="AE9">
+        <v>28</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>2.52</v>
+      </c>
+      <c r="AP9">
+        <v>40</v>
+      </c>
+      <c r="AQ9">
+        <v>10.5</v>
+      </c>
+      <c r="AR9">
+        <v>6.2</v>
+      </c>
+      <c r="AS9">
+        <v>5.6</v>
+      </c>
+      <c r="AT9">
+        <v>60</v>
+      </c>
+      <c r="AU9">
+        <v>46</v>
+      </c>
+      <c r="AV9">
+        <v>21</v>
+      </c>
+      <c r="AW9">
+        <v>19.5</v>
+      </c>
+      <c r="AX9">
+        <v>130</v>
+      </c>
+      <c r="AY9">
+        <v>32</v>
+      </c>
+      <c r="AZ9">
+        <v>48</v>
+      </c>
+      <c r="BA9">
+        <v>13</v>
+      </c>
+      <c r="BB9">
+        <v>14</v>
+      </c>
+      <c r="BC9">
+        <v>95</v>
+      </c>
+      <c r="BD9">
+        <v>32</v>
+      </c>
+      <c r="BE9">
+        <v>65</v>
+      </c>
+      <c r="BF9">
+        <v>12.5</v>
+      </c>
+      <c r="BG9">
+        <v>2.32</v>
+      </c>
+      <c r="BH9">
+        <v>6.2</v>
+      </c>
+      <c r="BI9">
+        <v>5</v>
+      </c>
+      <c r="BJ9">
+        <v>38</v>
+      </c>
+      <c r="BK9">
         <v>8</v>
-      </c>
-      <c r="L9">
-        <v>1.26</v>
-      </c>
-      <c r="M9">
-        <v>1.03</v>
-      </c>
-      <c r="N9">
-        <v>6.8</v>
-      </c>
-      <c r="O9">
-        <v>1.15</v>
-      </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9">
-        <v>1.48</v>
-      </c>
-      <c r="R9">
-        <v>1.79</v>
-      </c>
-      <c r="S9">
-        <v>2.24</v>
-      </c>
-      <c r="T9">
-        <v>2.08</v>
-      </c>
-      <c r="U9">
-        <v>1.9</v>
-      </c>
-      <c r="V9">
-        <v>1.06</v>
-      </c>
-      <c r="W9">
-        <v>5.1</v>
-      </c>
-      <c r="X9">
-        <v>36</v>
-      </c>
-      <c r="Y9">
-        <v>55</v>
-      </c>
-      <c r="Z9">
-        <v>200</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>11.5</v>
-      </c>
-      <c r="AC9">
-        <v>21</v>
-      </c>
-      <c r="AD9">
-        <v>48</v>
-      </c>
-      <c r="AE9">
-        <v>420</v>
-      </c>
-      <c r="AF9">
-        <v>8.6</v>
-      </c>
-      <c r="AG9">
-        <v>11.5</v>
-      </c>
-      <c r="AH9">
-        <v>38</v>
-      </c>
-      <c r="AI9">
-        <v>180</v>
-      </c>
-      <c r="AJ9">
-        <v>9.4</v>
-      </c>
-      <c r="AK9">
-        <v>13</v>
-      </c>
-      <c r="AL9">
-        <v>36</v>
-      </c>
-      <c r="AM9">
-        <v>200</v>
-      </c>
-      <c r="AN9">
-        <v>3.7</v>
-      </c>
-      <c r="AO9">
-        <v>330</v>
-      </c>
-      <c r="AP9">
-        <v>30</v>
-      </c>
-      <c r="AQ9">
-        <v>44</v>
-      </c>
-      <c r="AR9">
-        <v>14.5</v>
-      </c>
-      <c r="AS9">
-        <v>16</v>
-      </c>
-      <c r="AT9">
-        <v>10.5</v>
-      </c>
-      <c r="AU9">
-        <v>16.5</v>
-      </c>
-      <c r="AV9">
-        <v>40</v>
-      </c>
-      <c r="AW9">
-        <v>16.5</v>
-      </c>
-      <c r="AX9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
-        <v>32</v>
-      </c>
-      <c r="BA9">
-        <v>32</v>
-      </c>
-      <c r="BB9">
-        <v>9</v>
-      </c>
-      <c r="BC9">
-        <v>12</v>
-      </c>
-      <c r="BD9">
-        <v>30</v>
-      </c>
-      <c r="BE9">
-        <v>55</v>
-      </c>
-      <c r="BF9">
-        <v>3.45</v>
-      </c>
-      <c r="BG9">
-        <v>85</v>
-      </c>
-      <c r="BH9">
-        <v>5.7</v>
-      </c>
-      <c r="BI9">
-        <v>4</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>8.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.81</v>
+        <v>10</v>
       </c>
       <c r="BN9">
+        <v>70</v>
+      </c>
+      <c r="BO9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BP9">
         <v>1000</v>
       </c>
-      <c r="BO9">
-        <v>3.4</v>
-      </c>
-      <c r="BP9">
+      <c r="BQ9">
+        <v>10</v>
+      </c>
+      <c r="BR9">
+        <v>840</v>
+      </c>
+      <c r="BS9">
+        <v>10</v>
+      </c>
+      <c r="BT9">
+        <v>3.35</v>
+      </c>
+      <c r="BU9">
+        <v>3.1</v>
+      </c>
+      <c r="BV9">
+        <v>4.5</v>
+      </c>
+      <c r="BW9">
+        <v>4</v>
+      </c>
+      <c r="BX9">
+        <v>44</v>
+      </c>
+      <c r="BY9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ9">
         <v>6.4</v>
       </c>
-      <c r="BQ9">
-        <v>4.9</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>12.5</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
-      <c r="BU9">
-        <v>10</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>10.5</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>10.5</v>
-      </c>
-      <c r="BZ9">
-        <v>0</v>
-      </c>
       <c r="CA9">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="CB9" t="s">
         <v>149</v>
@@ -2993,226 +2993,226 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>1.25</v>
       </c>
       <c r="G10">
-        <v>75</v>
+        <v>1.26</v>
       </c>
       <c r="H10">
-        <v>1.06</v>
+        <v>14.5</v>
       </c>
       <c r="I10">
+        <v>15</v>
+      </c>
+      <c r="J10">
+        <v>7.6</v>
+      </c>
+      <c r="K10">
+        <v>7.8</v>
+      </c>
+      <c r="L10">
+        <v>1.26</v>
+      </c>
+      <c r="M10">
+        <v>1.03</v>
+      </c>
+      <c r="N10">
+        <v>6.8</v>
+      </c>
+      <c r="O10">
+        <v>1.16</v>
+      </c>
+      <c r="P10">
+        <v>3.05</v>
+      </c>
+      <c r="Q10">
+        <v>1.48</v>
+      </c>
+      <c r="R10">
+        <v>1.8</v>
+      </c>
+      <c r="S10">
+        <v>2.22</v>
+      </c>
+      <c r="T10">
+        <v>2.1</v>
+      </c>
+      <c r="U10">
+        <v>1.87</v>
+      </c>
+      <c r="V10">
         <v>1.07</v>
       </c>
-      <c r="J10">
-        <v>20</v>
-      </c>
-      <c r="K10">
-        <v>22</v>
-      </c>
-      <c r="L10">
-        <v>1.23</v>
-      </c>
-      <c r="M10">
-        <v>1.02</v>
-      </c>
-      <c r="N10">
-        <v>7.6</v>
-      </c>
-      <c r="O10">
-        <v>1.14</v>
-      </c>
-      <c r="P10">
-        <v>3.2</v>
-      </c>
-      <c r="Q10">
-        <v>1.43</v>
-      </c>
-      <c r="R10">
-        <v>1.86</v>
-      </c>
-      <c r="S10">
-        <v>2.12</v>
-      </c>
-      <c r="T10">
+      <c r="W10">
+        <v>4.9</v>
+      </c>
+      <c r="X10">
+        <v>36</v>
+      </c>
+      <c r="Y10">
+        <v>55</v>
+      </c>
+      <c r="Z10">
+        <v>170</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>11.5</v>
+      </c>
+      <c r="AC10">
+        <v>17</v>
+      </c>
+      <c r="AD10">
+        <v>48</v>
+      </c>
+      <c r="AE10">
+        <v>280</v>
+      </c>
+      <c r="AF10">
+        <v>8.6</v>
+      </c>
+      <c r="AG10">
+        <v>12</v>
+      </c>
+      <c r="AH10">
+        <v>34</v>
+      </c>
+      <c r="AI10">
+        <v>160</v>
+      </c>
+      <c r="AJ10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK10">
+        <v>13</v>
+      </c>
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>160</v>
+      </c>
+      <c r="AN10">
+        <v>3.55</v>
+      </c>
+      <c r="AO10">
+        <v>370</v>
+      </c>
+      <c r="AP10">
+        <v>30</v>
+      </c>
+      <c r="AQ10">
+        <v>48</v>
+      </c>
+      <c r="AR10">
+        <v>120</v>
+      </c>
+      <c r="AS10">
+        <v>30</v>
+      </c>
+      <c r="AT10">
+        <v>10.5</v>
+      </c>
+      <c r="AU10">
+        <v>16.5</v>
+      </c>
+      <c r="AV10">
+        <v>44</v>
+      </c>
+      <c r="AW10">
+        <v>28</v>
+      </c>
+      <c r="AX10">
+        <v>8.4</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>32</v>
+      </c>
+      <c r="BA10">
+        <v>110</v>
+      </c>
+      <c r="BB10">
+        <v>9</v>
+      </c>
+      <c r="BC10">
+        <v>12</v>
+      </c>
+      <c r="BD10">
+        <v>30</v>
+      </c>
+      <c r="BE10">
+        <v>110</v>
+      </c>
+      <c r="BF10">
+        <v>3.45</v>
+      </c>
+      <c r="BG10">
+        <v>85</v>
+      </c>
+      <c r="BH10">
+        <v>4.9</v>
+      </c>
+      <c r="BI10">
         <v>4.4</v>
       </c>
-      <c r="U10">
-        <v>1.27</v>
-      </c>
-      <c r="V10">
+      <c r="BJ10">
+        <v>12.5</v>
+      </c>
+      <c r="BK10">
+        <v>11</v>
+      </c>
+      <c r="BL10">
+        <v>170</v>
+      </c>
+      <c r="BM10">
+        <v>13</v>
+      </c>
+      <c r="BN10">
+        <v>3.95</v>
+      </c>
+      <c r="BO10">
+        <v>3.65</v>
+      </c>
+      <c r="BP10">
+        <v>6.4</v>
+      </c>
+      <c r="BQ10">
+        <v>5.9</v>
+      </c>
+      <c r="BR10">
+        <v>21</v>
+      </c>
+      <c r="BS10">
+        <v>17.5</v>
+      </c>
+      <c r="BT10">
         <v>15.5</v>
       </c>
-      <c r="W10">
-        <v>1.01</v>
-      </c>
-      <c r="X10">
-        <v>50</v>
-      </c>
-      <c r="Y10">
-        <v>17</v>
-      </c>
-      <c r="Z10">
-        <v>7.2</v>
-      </c>
-      <c r="AA10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>110</v>
-      </c>
-      <c r="AD10">
-        <v>42</v>
-      </c>
-      <c r="AE10">
-        <v>32</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>260</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>5.2</v>
-      </c>
-      <c r="AP10">
-        <v>36</v>
-      </c>
-      <c r="AQ10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR10">
-        <v>5.7</v>
-      </c>
-      <c r="AS10">
-        <v>5.5</v>
-      </c>
-      <c r="AT10">
-        <v>48</v>
-      </c>
-      <c r="AU10">
-        <v>25</v>
-      </c>
-      <c r="AV10">
-        <v>19.5</v>
-      </c>
-      <c r="AW10">
-        <v>9.4</v>
-      </c>
-      <c r="AX10">
+      <c r="BU10">
+        <v>14</v>
+      </c>
+      <c r="BV10">
         <v>130</v>
       </c>
-      <c r="AY10">
-        <v>60</v>
-      </c>
-      <c r="AZ10">
-        <v>21</v>
-      </c>
-      <c r="BA10">
-        <v>22</v>
-      </c>
-      <c r="BB10">
-        <v>4.2</v>
-      </c>
-      <c r="BC10">
-        <v>85</v>
-      </c>
-      <c r="BD10">
-        <v>6</v>
-      </c>
-      <c r="BE10">
-        <v>6</v>
-      </c>
-      <c r="BF10">
-        <v>10.5</v>
-      </c>
-      <c r="BG10">
-        <v>2.4</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.2</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.2</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.2</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.2</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>1.2</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.2</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>1.2</v>
-      </c>
-      <c r="BV10">
-        <v>6</v>
-      </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY10">
-        <v>1.2</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
         <v>149</v>
@@ -3235,10 +3235,10 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H11">
         <v>1.34</v>
@@ -3247,10 +3247,10 @@
         <v>1.35</v>
       </c>
       <c r="J11">
+        <v>5.9</v>
+      </c>
+      <c r="K11">
         <v>6</v>
-      </c>
-      <c r="K11">
-        <v>6.2</v>
       </c>
       <c r="L11">
         <v>1.33</v>
@@ -3259,19 +3259,19 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11">
         <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
         <v>2.78</v>
@@ -3280,19 +3280,19 @@
         <v>2.1</v>
       </c>
       <c r="U11">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
         <v>3.85</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
         <v>22</v>
       </c>
       <c r="Y11">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>7.8</v>
@@ -3304,7 +3304,7 @@
         <v>34</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD11">
         <v>10.5</v>
@@ -3319,40 +3319,40 @@
         <v>38</v>
       </c>
       <c r="AH11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI11">
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="AK11">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AL11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM11">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AO11">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AP11">
         <v>21</v>
       </c>
       <c r="AQ11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR11">
         <v>7.6</v>
       </c>
       <c r="AS11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT11">
         <v>30</v>
@@ -3379,10 +3379,10 @@
         <v>34</v>
       </c>
       <c r="BB11">
+        <v>300</v>
+      </c>
+      <c r="BC11">
         <v>150</v>
-      </c>
-      <c r="BC11">
-        <v>160</v>
       </c>
       <c r="BD11">
         <v>120</v>
@@ -3391,70 +3391,70 @@
         <v>140</v>
       </c>
       <c r="BF11">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="BG11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
+        <v>3.8</v>
+      </c>
+      <c r="BJ11">
+        <v>12</v>
+      </c>
+      <c r="BK11">
+        <v>10.5</v>
+      </c>
+      <c r="BL11">
+        <v>170</v>
+      </c>
+      <c r="BM11">
+        <v>11.5</v>
+      </c>
+      <c r="BN11">
+        <v>16</v>
+      </c>
+      <c r="BO11">
+        <v>12</v>
+      </c>
+      <c r="BP11">
+        <v>110</v>
+      </c>
+      <c r="BQ11">
+        <v>10.5</v>
+      </c>
+      <c r="BR11">
+        <v>95</v>
+      </c>
+      <c r="BS11">
+        <v>10.5</v>
+      </c>
+      <c r="BT11">
         <v>3.75</v>
       </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>3.2</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>3.65</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>3.45</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>7.6</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>7.6</v>
-      </c>
-      <c r="BT11">
-        <v>4.3</v>
-      </c>
       <c r="BU11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BV11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BW11">
-        <v>2.52</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY11">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA11">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
         <v>149</v>
@@ -3483,28 +3483,28 @@
         <v>1.3</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="I12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
         <v>6.2</v>
-      </c>
-      <c r="K12">
-        <v>6.4</v>
       </c>
       <c r="L12">
         <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
         <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
         <v>2.14</v>
@@ -3513,28 +3513,28 @@
         <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U12">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W12">
         <v>4.3</v>
       </c>
       <c r="X12">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Z12">
         <v>150</v>
@@ -3543,7 +3543,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC12">
         <v>14</v>
@@ -3564,37 +3564,37 @@
         <v>46</v>
       </c>
       <c r="AI12">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AJ12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM12">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AN12">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO12">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="AP12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR12">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="AS12">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="AT12">
         <v>6.8</v>
@@ -3606,97 +3606,97 @@
         <v>50</v>
       </c>
       <c r="AW12">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AX12">
         <v>6.4</v>
       </c>
       <c r="AY12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
+        <v>42</v>
+      </c>
+      <c r="BA12">
         <v>38</v>
       </c>
-      <c r="BA12">
-        <v>95</v>
-      </c>
       <c r="BB12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE12">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BF12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG12">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI12">
+        <v>3.4</v>
+      </c>
+      <c r="BJ12">
+        <v>15.5</v>
+      </c>
+      <c r="BK12">
+        <v>8</v>
+      </c>
+      <c r="BL12">
+        <v>290</v>
+      </c>
+      <c r="BM12">
+        <v>16</v>
+      </c>
+      <c r="BN12">
+        <v>3.4</v>
+      </c>
+      <c r="BO12">
         <v>3.1</v>
       </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>2.58</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.6</v>
-      </c>
-      <c r="BN12">
-        <v>3.85</v>
-      </c>
-      <c r="BO12">
-        <v>3.05</v>
-      </c>
       <c r="BP12">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ12">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS12">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU12">
-        <v>2.64</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BW12">
-        <v>2.6</v>
+        <v>15.5</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BY12">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA12">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="s">
         <v>149</v>
@@ -3719,22 +3719,22 @@
         <v>134</v>
       </c>
       <c r="F13">
+        <v>1.84</v>
+      </c>
+      <c r="G13">
         <v>1.85</v>
       </c>
-      <c r="G13">
-        <v>1.86</v>
-      </c>
       <c r="H13">
+        <v>5.3</v>
+      </c>
+      <c r="I13">
         <v>5.5</v>
       </c>
-      <c r="I13">
-        <v>5.6</v>
-      </c>
       <c r="J13">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
         <v>1.53</v>
@@ -3746,28 +3746,28 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P13">
         <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R13">
         <v>1.24</v>
       </c>
       <c r="S13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
         <v>2.16</v>
@@ -3776,58 +3776,58 @@
         <v>10.5</v>
       </c>
       <c r="Y13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z13">
         <v>42</v>
       </c>
       <c r="AA13">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE13">
         <v>100</v>
       </c>
       <c r="AF13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG13">
         <v>11</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN13">
         <v>17.5</v>
       </c>
       <c r="AO13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
         <v>13</v>
@@ -3839,19 +3839,19 @@
         <v>110</v>
       </c>
       <c r="AT13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU13">
         <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AX13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY13">
         <v>10</v>
@@ -3860,85 +3860,85 @@
         <v>23</v>
       </c>
       <c r="BA13">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB13">
         <v>18</v>
       </c>
       <c r="BC13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD13">
         <v>46</v>
       </c>
       <c r="BE13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF13">
         <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BH13">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN13">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO13">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB13" t="s">
         <v>149</v>
@@ -3961,16 +3961,16 @@
         <v>135</v>
       </c>
       <c r="F14">
+        <v>4.7</v>
+      </c>
+      <c r="G14">
         <v>4.8</v>
       </c>
-      <c r="G14">
-        <v>4.9</v>
-      </c>
       <c r="H14">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -3979,49 +3979,49 @@
         <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
         <v>1.43</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q14">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T14">
         <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y14">
         <v>7.4</v>
       </c>
       <c r="Z14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>22</v>
@@ -4030,7 +4030,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4042,10 +4042,10 @@
         <v>34</v>
       </c>
       <c r="AG14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI14">
         <v>44</v>
@@ -4063,10 +4063,10 @@
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AO14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP14">
         <v>10.5</v>
@@ -4075,7 +4075,7 @@
         <v>7</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14">
         <v>20</v>
@@ -4099,22 +4099,22 @@
         <v>18</v>
       </c>
       <c r="AZ14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BC14">
         <v>60</v>
       </c>
       <c r="BD14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BF14">
         <v>90</v>
@@ -4123,64 +4123,64 @@
         <v>16.5</v>
       </c>
       <c r="BH14">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BI14">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM14">
         <v>60</v>
       </c>
       <c r="BN14">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ14">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS14">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="BT14">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BU14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW14">
+        <v>12.5</v>
+      </c>
+      <c r="BX14">
+        <v>40</v>
+      </c>
+      <c r="BY14">
         <v>11</v>
       </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>3.3</v>
-      </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA14">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4203,76 +4203,76 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G15">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H15">
+        <v>1.99</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="I15">
-        <v>2.02</v>
-      </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.35</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O15">
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
         <v>1.68</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W15">
         <v>1.34</v>
       </c>
       <c r="X15">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Y15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AA15">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15">
         <v>11</v>
@@ -4281,10 +4281,10 @@
         <v>21</v>
       </c>
       <c r="AF15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH15">
         <v>18</v>
@@ -4296,22 +4296,22 @@
         <v>90</v>
       </c>
       <c r="AK15">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AL15">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM15">
         <v>80</v>
       </c>
       <c r="AN15">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4320,16 +4320,16 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AT15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AU15">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV15">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AW15">
         <v>17.5</v>
@@ -4341,85 +4341,85 @@
         <v>14.5</v>
       </c>
       <c r="AZ15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA15">
         <v>27</v>
       </c>
       <c r="BB15">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BC15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD15">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE15">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BF15">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BG15">
         <v>10</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4445,16 +4445,16 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
         <v>2.32</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4463,205 +4463,205 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S16">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
         <v>1.75</v>
       </c>
       <c r="X16">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="Y16">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="Z16">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AA16">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB16">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
         <v>14</v>
       </c>
-      <c r="AD16">
-        <v>970</v>
-      </c>
       <c r="AE16">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AF16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AI16">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AJ16">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK16">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN16">
-        <v>600</v>
+        <v>10.5</v>
       </c>
       <c r="AO16">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AR16">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AS16">
-        <v>2.36</v>
+        <v>24</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AU16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>2.34</v>
+        <v>23</v>
       </c>
       <c r="AX16">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AY16">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>2.32</v>
+        <v>25</v>
       </c>
       <c r="BB16">
-        <v>2.34</v>
+        <v>25</v>
       </c>
       <c r="BC16">
-        <v>2.3</v>
+        <v>17</v>
       </c>
       <c r="BD16">
-        <v>2.3</v>
+        <v>21</v>
       </c>
       <c r="BE16">
-        <v>2.4</v>
+        <v>36</v>
       </c>
       <c r="BF16">
-        <v>2.56</v>
+        <v>9.4</v>
       </c>
       <c r="BG16">
+        <v>15.5</v>
+      </c>
+      <c r="BH16">
+        <v>5.4</v>
+      </c>
+      <c r="BI16">
         <v>3.55</v>
       </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4687,25 +4687,25 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G17">
         <v>2.02</v>
       </c>
       <c r="H17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4717,7 +4717,7 @@
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q17">
         <v>1.63</v>
@@ -4726,184 +4726,184 @@
         <v>1.59</v>
       </c>
       <c r="S17">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.98</v>
       </c>
       <c r="X17">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Y17">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z17">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB17">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17">
+        <v>16.5</v>
+      </c>
+      <c r="AE17">
+        <v>42</v>
+      </c>
+      <c r="AF17">
+        <v>15</v>
+      </c>
+      <c r="AG17">
+        <v>11</v>
+      </c>
+      <c r="AH17">
+        <v>16</v>
+      </c>
+      <c r="AI17">
+        <v>44</v>
+      </c>
+      <c r="AJ17">
+        <v>25</v>
+      </c>
+      <c r="AK17">
+        <v>19</v>
+      </c>
+      <c r="AL17">
+        <v>29</v>
+      </c>
+      <c r="AM17">
+        <v>65</v>
+      </c>
+      <c r="AN17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO17">
+        <v>29</v>
+      </c>
+      <c r="AP17">
+        <v>20</v>
+      </c>
+      <c r="AQ17">
+        <v>17</v>
+      </c>
+      <c r="AR17">
+        <v>26</v>
+      </c>
+      <c r="AS17">
+        <v>29</v>
+      </c>
+      <c r="AT17">
+        <v>11.5</v>
+      </c>
+      <c r="AU17">
+        <v>8.6</v>
+      </c>
+      <c r="AV17">
         <v>14</v>
       </c>
-      <c r="AD17">
-        <v>970</v>
-      </c>
-      <c r="AE17">
-        <v>120</v>
-      </c>
-      <c r="AF17">
-        <v>970</v>
-      </c>
-      <c r="AG17">
-        <v>970</v>
-      </c>
-      <c r="AH17">
-        <v>26</v>
-      </c>
-      <c r="AI17">
-        <v>150</v>
-      </c>
-      <c r="AJ17">
-        <v>900</v>
-      </c>
-      <c r="AK17">
-        <v>970</v>
-      </c>
-      <c r="AL17">
-        <v>75</v>
-      </c>
-      <c r="AM17">
-        <v>580</v>
-      </c>
-      <c r="AN17">
-        <v>55</v>
-      </c>
-      <c r="AO17">
-        <v>600</v>
-      </c>
-      <c r="AP17">
-        <v>2.06</v>
-      </c>
-      <c r="AQ17">
-        <v>2.04</v>
-      </c>
-      <c r="AR17">
-        <v>2.12</v>
-      </c>
-      <c r="AS17">
-        <v>2.14</v>
-      </c>
-      <c r="AT17">
-        <v>7</v>
-      </c>
-      <c r="AU17">
-        <v>5.1</v>
-      </c>
-      <c r="AV17">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW17">
-        <v>2.12</v>
+        <v>32</v>
       </c>
       <c r="AX17">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BA17">
-        <v>2.12</v>
+        <v>30</v>
       </c>
       <c r="BB17">
-        <v>2.08</v>
+        <v>21</v>
       </c>
       <c r="BC17">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>2.1</v>
+        <v>22</v>
       </c>
       <c r="BE17">
-        <v>2.16</v>
+        <v>29</v>
       </c>
       <c r="BF17">
-        <v>2.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK17">
         <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU17">
         <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
@@ -4932,7 +4932,7 @@
         <v>2.16</v>
       </c>
       <c r="G18">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H18">
         <v>3.25</v>
@@ -4950,10 +4950,10 @@
         <v>1.33</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O18">
         <v>1.24</v>
@@ -4962,190 +4962,190 @@
         <v>2.32</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T18">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="U18">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
         <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X18">
+        <v>22</v>
+      </c>
+      <c r="Y18">
+        <v>17.5</v>
+      </c>
+      <c r="Z18">
+        <v>32</v>
+      </c>
+      <c r="AA18">
+        <v>70</v>
+      </c>
+      <c r="AB18">
+        <v>13</v>
+      </c>
+      <c r="AC18">
+        <v>9.4</v>
+      </c>
+      <c r="AD18">
+        <v>16.5</v>
+      </c>
+      <c r="AE18">
+        <v>42</v>
+      </c>
+      <c r="AF18">
+        <v>18</v>
+      </c>
+      <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>16.5</v>
+      </c>
+      <c r="AI18">
+        <v>46</v>
+      </c>
+      <c r="AJ18">
+        <v>32</v>
+      </c>
+      <c r="AK18">
+        <v>26</v>
+      </c>
+      <c r="AL18">
+        <v>34</v>
+      </c>
+      <c r="AM18">
+        <v>85</v>
+      </c>
+      <c r="AN18">
+        <v>13.5</v>
+      </c>
+      <c r="AO18">
+        <v>30</v>
+      </c>
+      <c r="AP18">
+        <v>17.5</v>
+      </c>
+      <c r="AQ18">
+        <v>14.5</v>
+      </c>
+      <c r="AR18">
+        <v>22</v>
+      </c>
+      <c r="AS18">
+        <v>32</v>
+      </c>
+      <c r="AT18">
+        <v>11</v>
+      </c>
+      <c r="AU18">
+        <v>8</v>
+      </c>
+      <c r="AV18">
+        <v>12.5</v>
+      </c>
+      <c r="AW18">
+        <v>27</v>
+      </c>
+      <c r="AX18">
+        <v>13.5</v>
+      </c>
+      <c r="AY18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>13.5</v>
+      </c>
+      <c r="BA18">
+        <v>29</v>
+      </c>
+      <c r="BB18">
+        <v>21</v>
+      </c>
+      <c r="BC18">
+        <v>18</v>
+      </c>
+      <c r="BD18">
+        <v>23</v>
+      </c>
+      <c r="BE18">
         <v>40</v>
       </c>
-      <c r="Y18">
-        <v>19.5</v>
-      </c>
-      <c r="Z18">
-        <v>70</v>
-      </c>
-      <c r="AA18">
-        <v>900</v>
-      </c>
-      <c r="AB18">
-        <v>15.5</v>
-      </c>
-      <c r="AC18">
-        <v>42</v>
-      </c>
-      <c r="AD18">
-        <v>29</v>
-      </c>
-      <c r="AE18">
-        <v>90</v>
-      </c>
-      <c r="AF18">
-        <v>970</v>
-      </c>
-      <c r="AG18">
-        <v>14.5</v>
-      </c>
-      <c r="AH18">
-        <v>25</v>
-      </c>
-      <c r="AI18">
-        <v>150</v>
-      </c>
-      <c r="AJ18">
-        <v>900</v>
-      </c>
-      <c r="AK18">
-        <v>46</v>
-      </c>
-      <c r="AL18">
-        <v>60</v>
-      </c>
-      <c r="AM18">
-        <v>580</v>
-      </c>
-      <c r="AN18">
-        <v>600</v>
-      </c>
-      <c r="AO18">
-        <v>600</v>
-      </c>
-      <c r="AP18">
-        <v>6.8</v>
-      </c>
-      <c r="AQ18">
+      <c r="BF18">
         <v>11</v>
       </c>
-      <c r="AR18">
-        <v>17</v>
-      </c>
-      <c r="AS18">
-        <v>2.94</v>
-      </c>
-      <c r="AT18">
-        <v>6.4</v>
-      </c>
-      <c r="AU18">
-        <v>4.2</v>
-      </c>
-      <c r="AV18">
-        <v>11</v>
-      </c>
-      <c r="AW18">
-        <v>11</v>
-      </c>
-      <c r="AX18">
-        <v>11</v>
-      </c>
-      <c r="AY18">
-        <v>8.6</v>
-      </c>
-      <c r="AZ18">
-        <v>11</v>
-      </c>
-      <c r="BA18">
-        <v>2.9</v>
-      </c>
-      <c r="BB18">
-        <v>13</v>
-      </c>
-      <c r="BC18">
-        <v>13</v>
-      </c>
-      <c r="BD18">
-        <v>18</v>
-      </c>
-      <c r="BE18">
-        <v>2.96</v>
-      </c>
-      <c r="BF18">
-        <v>2.94</v>
-      </c>
       <c r="BG18">
-        <v>2.68</v>
+        <v>22</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5174,19 +5174,19 @@
         <v>2.24</v>
       </c>
       <c r="G19">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
         <v>1.34</v>
@@ -5195,202 +5195,202 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R19">
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T19">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X19">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z19">
+        <v>26</v>
+      </c>
+      <c r="AA19">
         <v>65</v>
       </c>
-      <c r="AA19">
-        <v>900</v>
-      </c>
       <c r="AB19">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE19">
+        <v>40</v>
+      </c>
+      <c r="AF19">
+        <v>17</v>
+      </c>
+      <c r="AG19">
+        <v>12</v>
+      </c>
+      <c r="AH19">
+        <v>17</v>
+      </c>
+      <c r="AI19">
+        <v>48</v>
+      </c>
+      <c r="AJ19">
+        <v>36</v>
+      </c>
+      <c r="AK19">
+        <v>25</v>
+      </c>
+      <c r="AL19">
+        <v>38</v>
+      </c>
+      <c r="AM19">
         <v>90</v>
       </c>
-      <c r="AF19">
-        <v>970</v>
-      </c>
-      <c r="AG19">
-        <v>36</v>
-      </c>
-      <c r="AH19">
-        <v>60</v>
-      </c>
-      <c r="AI19">
-        <v>500</v>
-      </c>
-      <c r="AJ19">
-        <v>900</v>
-      </c>
-      <c r="AK19">
-        <v>65</v>
-      </c>
-      <c r="AL19">
-        <v>85</v>
-      </c>
-      <c r="AM19">
-        <v>580</v>
-      </c>
       <c r="AN19">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="AO19">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AP19">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AR19">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS19">
-        <v>2.32</v>
+        <v>40</v>
       </c>
       <c r="AT19">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV19">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AW19">
-        <v>2.28</v>
+        <v>27</v>
       </c>
       <c r="AX19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY19">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>2.3</v>
+        <v>32</v>
       </c>
       <c r="BB19">
-        <v>2.28</v>
+        <v>24</v>
       </c>
       <c r="BC19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BD19">
-        <v>2.26</v>
+        <v>25</v>
       </c>
       <c r="BE19">
-        <v>2.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK19">
         <v>5.1</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ19">
         <v>8.199999999999999</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU19">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.02</v>
+        <v>16.5</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="s">
         <v>149</v>
@@ -5416,19 +5416,19 @@
         <v>1.8</v>
       </c>
       <c r="G20">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H20">
         <v>4.4</v>
       </c>
       <c r="I20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J20">
         <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>1.26</v>
@@ -5440,196 +5440,196 @@
         <v>6.2</v>
       </c>
       <c r="O20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P20">
         <v>2.8</v>
       </c>
       <c r="Q20">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R20">
         <v>1.72</v>
       </c>
       <c r="S20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U20">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X20">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="Z20">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB20">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC20">
+        <v>11</v>
+      </c>
+      <c r="AD20">
+        <v>19.5</v>
+      </c>
+      <c r="AE20">
+        <v>50</v>
+      </c>
+      <c r="AF20">
+        <v>15.5</v>
+      </c>
+      <c r="AG20">
+        <v>11</v>
+      </c>
+      <c r="AH20">
+        <v>15.5</v>
+      </c>
+      <c r="AI20">
+        <v>48</v>
+      </c>
+      <c r="AJ20">
+        <v>21</v>
+      </c>
+      <c r="AK20">
+        <v>17.5</v>
+      </c>
+      <c r="AL20">
+        <v>25</v>
+      </c>
+      <c r="AM20">
+        <v>65</v>
+      </c>
+      <c r="AN20">
+        <v>7.6</v>
+      </c>
+      <c r="AO20">
+        <v>32</v>
+      </c>
+      <c r="AP20">
+        <v>15</v>
+      </c>
+      <c r="AQ20">
+        <v>20</v>
+      </c>
+      <c r="AR20">
+        <v>30</v>
+      </c>
+      <c r="AS20">
+        <v>44</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV20">
+        <v>16.5</v>
+      </c>
+      <c r="AW20">
+        <v>34</v>
+      </c>
+      <c r="AX20">
         <v>13</v>
       </c>
-      <c r="AD20">
-        <v>970</v>
-      </c>
-      <c r="AE20">
-        <v>190</v>
-      </c>
-      <c r="AF20">
-        <v>40</v>
-      </c>
-      <c r="AG20">
-        <v>13</v>
-      </c>
-      <c r="AH20">
-        <v>25</v>
-      </c>
-      <c r="AI20">
-        <v>150</v>
-      </c>
-      <c r="AJ20">
-        <v>900</v>
-      </c>
-      <c r="AK20">
-        <v>65</v>
-      </c>
-      <c r="AL20">
-        <v>48</v>
-      </c>
-      <c r="AM20">
-        <v>580</v>
-      </c>
-      <c r="AN20">
+      <c r="AY20">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20">
+        <v>13.5</v>
+      </c>
+      <c r="BA20">
+        <v>36</v>
+      </c>
+      <c r="BB20">
+        <v>18</v>
+      </c>
+      <c r="BC20">
+        <v>14.5</v>
+      </c>
+      <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
+        <v>28</v>
+      </c>
+      <c r="BF20">
+        <v>6.4</v>
+      </c>
+      <c r="BG20">
+        <v>24</v>
+      </c>
+      <c r="BH20">
+        <v>5.3</v>
+      </c>
+      <c r="BI20">
+        <v>3.75</v>
+      </c>
+      <c r="BJ20">
+        <v>10</v>
+      </c>
+      <c r="BK20">
+        <v>6.8</v>
+      </c>
+      <c r="BL20">
         <v>85</v>
-      </c>
-      <c r="AO20">
-        <v>260</v>
-      </c>
-      <c r="AP20">
-        <v>2.68</v>
-      </c>
-      <c r="AQ20">
-        <v>16</v>
-      </c>
-      <c r="AR20">
-        <v>2.68</v>
-      </c>
-      <c r="AS20">
-        <v>2.76</v>
-      </c>
-      <c r="AT20">
-        <v>7.6</v>
-      </c>
-      <c r="AU20">
-        <v>7.8</v>
-      </c>
-      <c r="AV20">
-        <v>12.5</v>
-      </c>
-      <c r="AW20">
-        <v>2.7</v>
-      </c>
-      <c r="AX20">
-        <v>7.6</v>
-      </c>
-      <c r="AY20">
-        <v>7.8</v>
-      </c>
-      <c r="AZ20">
-        <v>11</v>
-      </c>
-      <c r="BA20">
-        <v>2.7</v>
-      </c>
-      <c r="BB20">
-        <v>10.5</v>
-      </c>
-      <c r="BC20">
-        <v>8.4</v>
-      </c>
-      <c r="BD20">
-        <v>15</v>
-      </c>
-      <c r="BE20">
-        <v>2.74</v>
-      </c>
-      <c r="BF20">
-        <v>5.4</v>
-      </c>
-      <c r="BG20">
-        <v>2.58</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
       </c>
       <c r="BM20">
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU20">
         <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5655,16 +5655,16 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H21">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
         <v>3.75</v>
@@ -5682,199 +5682,199 @@
         <v>4.5</v>
       </c>
       <c r="O21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q21">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X21">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y21">
+        <v>16.5</v>
+      </c>
+      <c r="Z21">
+        <v>26</v>
+      </c>
+      <c r="AA21">
+        <v>65</v>
+      </c>
+      <c r="AB21">
+        <v>12.5</v>
+      </c>
+      <c r="AC21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>14.5</v>
+      </c>
+      <c r="AE21">
+        <v>40</v>
+      </c>
+      <c r="AF21">
+        <v>16.5</v>
+      </c>
+      <c r="AG21">
+        <v>11.5</v>
+      </c>
+      <c r="AH21">
+        <v>16.5</v>
+      </c>
+      <c r="AI21">
+        <v>48</v>
+      </c>
+      <c r="AJ21">
+        <v>36</v>
+      </c>
+      <c r="AK21">
         <v>25</v>
       </c>
-      <c r="Z21">
-        <v>65</v>
-      </c>
-      <c r="AA21">
-        <v>900</v>
-      </c>
-      <c r="AB21">
-        <v>14.5</v>
-      </c>
-      <c r="AC21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD21">
-        <v>20</v>
-      </c>
-      <c r="AE21">
-        <v>90</v>
-      </c>
-      <c r="AF21">
-        <v>970</v>
-      </c>
-      <c r="AG21">
-        <v>16</v>
-      </c>
-      <c r="AH21">
+      <c r="AL21">
+        <v>38</v>
+      </c>
+      <c r="AM21">
+        <v>95</v>
+      </c>
+      <c r="AN21">
+        <v>15</v>
+      </c>
+      <c r="AO21">
+        <v>32</v>
+      </c>
+      <c r="AP21">
+        <v>15.5</v>
+      </c>
+      <c r="AQ21">
+        <v>13</v>
+      </c>
+      <c r="AR21">
+        <v>21</v>
+      </c>
+      <c r="AS21">
+        <v>42</v>
+      </c>
+      <c r="AT21">
+        <v>10.5</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>12</v>
+      </c>
+      <c r="AW21">
+        <v>28</v>
+      </c>
+      <c r="AX21">
+        <v>14</v>
+      </c>
+      <c r="AY21">
+        <v>10</v>
+      </c>
+      <c r="AZ21">
+        <v>14</v>
+      </c>
+      <c r="BA21">
+        <v>30</v>
+      </c>
+      <c r="BB21">
+        <v>24</v>
+      </c>
+      <c r="BC21">
+        <v>19</v>
+      </c>
+      <c r="BD21">
         <v>26</v>
       </c>
-      <c r="AI21">
-        <v>150</v>
-      </c>
-      <c r="AJ21">
-        <v>900</v>
-      </c>
-      <c r="AK21">
-        <v>65</v>
-      </c>
-      <c r="AL21">
-        <v>500</v>
-      </c>
-      <c r="AM21">
-        <v>580</v>
-      </c>
-      <c r="AN21">
-        <v>600</v>
-      </c>
-      <c r="AO21">
-        <v>600</v>
-      </c>
-      <c r="AP21">
-        <v>9</v>
-      </c>
-      <c r="AQ21">
-        <v>11</v>
-      </c>
-      <c r="AR21">
-        <v>14</v>
-      </c>
-      <c r="AS21">
-        <v>3</v>
-      </c>
-      <c r="AT21">
-        <v>8.6</v>
-      </c>
-      <c r="AU21">
-        <v>6.6</v>
-      </c>
-      <c r="AV21">
-        <v>9.4</v>
-      </c>
-      <c r="AW21">
-        <v>19</v>
-      </c>
-      <c r="AX21">
-        <v>11</v>
-      </c>
-      <c r="AY21">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21">
-        <v>12.5</v>
-      </c>
-      <c r="BA21">
-        <v>21</v>
-      </c>
-      <c r="BB21">
-        <v>14.5</v>
-      </c>
-      <c r="BC21">
-        <v>14</v>
-      </c>
-      <c r="BD21">
-        <v>16</v>
-      </c>
       <c r="BE21">
-        <v>2.88</v>
+        <v>46</v>
       </c>
       <c r="BF21">
+        <v>13</v>
+      </c>
+      <c r="BG21">
+        <v>24</v>
+      </c>
+      <c r="BH21">
+        <v>4.3</v>
+      </c>
+      <c r="BI21">
         <v>3.1</v>
       </c>
-      <c r="BG21">
-        <v>4.6</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.01</v>
-      </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB21" t="s">
         <v>149</v>
@@ -5897,22 +5897,22 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G22">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H22">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I22">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J22">
         <v>4.2</v>
       </c>
       <c r="K22">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22">
         <v>1.26</v>
@@ -5927,85 +5927,85 @@
         <v>1.16</v>
       </c>
       <c r="P22">
+        <v>2.82</v>
+      </c>
+      <c r="Q22">
+        <v>1.51</v>
+      </c>
+      <c r="R22">
+        <v>1.74</v>
+      </c>
+      <c r="S22">
+        <v>2.26</v>
+      </c>
+      <c r="T22">
+        <v>1.5</v>
+      </c>
+      <c r="U22">
         <v>2.9</v>
       </c>
-      <c r="Q22">
-        <v>1.49</v>
-      </c>
-      <c r="R22">
-        <v>1.76</v>
-      </c>
-      <c r="S22">
-        <v>2.22</v>
-      </c>
-      <c r="T22">
-        <v>1.46</v>
-      </c>
-      <c r="U22">
-        <v>2.7</v>
-      </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W22">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X22">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y22">
+        <v>19.5</v>
+      </c>
+      <c r="Z22">
         <v>25</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
+        <v>44</v>
+      </c>
+      <c r="AB22">
+        <v>19</v>
+      </c>
+      <c r="AC22">
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <v>13</v>
+      </c>
+      <c r="AE22">
         <v>26</v>
       </c>
-      <c r="AA22">
-        <v>50</v>
-      </c>
-      <c r="AB22">
-        <v>21</v>
-      </c>
-      <c r="AC22">
-        <v>10.5</v>
-      </c>
-      <c r="AD22">
-        <v>13.5</v>
-      </c>
-      <c r="AE22">
-        <v>55</v>
-      </c>
       <c r="AF22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK22">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AL22">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AM22">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AN22">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AO22">
         <v>14</v>
       </c>
       <c r="AP22">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ22">
         <v>17.5</v>
@@ -6020,103 +6020,103 @@
         <v>16.5</v>
       </c>
       <c r="AU22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AX22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY22">
         <v>11</v>
       </c>
       <c r="AZ22">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB22">
         <v>32</v>
       </c>
       <c r="BC22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE22">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BF22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG22">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
         <v>149</v>
@@ -6139,31 +6139,31 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G23">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H23">
+        <v>1.75</v>
+      </c>
+      <c r="I23">
         <v>1.77</v>
-      </c>
-      <c r="I23">
-        <v>1.79</v>
       </c>
       <c r="J23">
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
         <v>1.32</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O23">
         <v>1.23</v>
@@ -6172,46 +6172,46 @@
         <v>2.36</v>
       </c>
       <c r="Q23">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R23">
         <v>1.54</v>
       </c>
       <c r="S23">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T23">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="U23">
         <v>2.34</v>
       </c>
       <c r="V23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X23">
         <v>22</v>
       </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z23">
+        <v>13.5</v>
+      </c>
+      <c r="AA23">
+        <v>19.5</v>
+      </c>
+      <c r="AB23">
         <v>21</v>
       </c>
-      <c r="AA23">
-        <v>20</v>
-      </c>
-      <c r="AB23">
-        <v>40</v>
-      </c>
       <c r="AC23">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD23">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE23">
         <v>17.5</v>
@@ -6223,142 +6223,142 @@
         <v>19</v>
       </c>
       <c r="AH23">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AI23">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AJ23">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK23">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AL23">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AM23">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN23">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AO23">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP23">
-        <v>9.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AQ23">
         <v>10</v>
       </c>
       <c r="AR23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS23">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AT23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU23">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AV23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23">
         <v>15</v>
       </c>
       <c r="AX23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY23">
+        <v>16.5</v>
+      </c>
+      <c r="AZ23">
         <v>16</v>
-      </c>
-      <c r="AZ23">
-        <v>15.5</v>
       </c>
       <c r="BA23">
         <v>24</v>
       </c>
       <c r="BB23">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BC23">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BD23">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BE23">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="BF23">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BG23">
         <v>8</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="s">
         <v>149</v>
@@ -6381,166 +6381,166 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G24">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H24">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J24">
         <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M24">
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P24">
         <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
         <v>4.3</v>
       </c>
       <c r="T24">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U24">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X24">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z24">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="AB24">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AC24">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD24">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE24">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AF24">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AG24">
-        <v>46</v>
+        <v>19.5</v>
       </c>
       <c r="AH24">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AI24">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AJ24">
         <v>500</v>
       </c>
       <c r="AK24">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AL24">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM24">
         <v>580</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO24">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AP24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR24">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU24">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV24">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW24">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AX24">
+        <v>27</v>
+      </c>
+      <c r="AY24">
         <v>16</v>
       </c>
-      <c r="AY24">
-        <v>14.5</v>
-      </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA24">
         <v>32</v>
       </c>
       <c r="BB24">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BC24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD24">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE24">
         <v>34</v>
       </c>
       <c r="BF24">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BG24">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6623,226 +6623,226 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G25">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H25">
         <v>3.75</v>
       </c>
       <c r="I25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O25">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P25">
         <v>2.28</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S25">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T25">
         <v>1.64</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X25">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="Y25">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="Z25">
         <v>85</v>
       </c>
       <c r="AA25">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB25">
+        <v>12</v>
+      </c>
+      <c r="AC25">
+        <v>9.4</v>
+      </c>
+      <c r="AD25">
+        <v>20</v>
+      </c>
+      <c r="AE25">
+        <v>48</v>
+      </c>
+      <c r="AF25">
+        <v>15</v>
+      </c>
+      <c r="AG25">
+        <v>11</v>
+      </c>
+      <c r="AH25">
         <v>19</v>
       </c>
-      <c r="AC25">
+      <c r="AI25">
+        <v>50</v>
+      </c>
+      <c r="AJ25">
+        <v>29</v>
+      </c>
+      <c r="AK25">
+        <v>21</v>
+      </c>
+      <c r="AL25">
         <v>42</v>
       </c>
-      <c r="AD25">
-        <v>85</v>
-      </c>
-      <c r="AE25">
-        <v>120</v>
-      </c>
-      <c r="AF25">
+      <c r="AM25">
+        <v>200</v>
+      </c>
+      <c r="AN25">
+        <v>12</v>
+      </c>
+      <c r="AO25">
         <v>40</v>
       </c>
-      <c r="AG25">
-        <v>36</v>
-      </c>
-      <c r="AH25">
-        <v>60</v>
-      </c>
-      <c r="AI25">
-        <v>130</v>
-      </c>
-      <c r="AJ25">
-        <v>900</v>
-      </c>
-      <c r="AK25">
+      <c r="AP25">
+        <v>17</v>
+      </c>
+      <c r="AQ25">
+        <v>14.5</v>
+      </c>
+      <c r="AR25">
+        <v>23</v>
+      </c>
+      <c r="AS25">
+        <v>50</v>
+      </c>
+      <c r="AT25">
+        <v>10</v>
+      </c>
+      <c r="AU25">
+        <v>8</v>
+      </c>
+      <c r="AV25">
+        <v>13.5</v>
+      </c>
+      <c r="AW25">
+        <v>27</v>
+      </c>
+      <c r="AX25">
+        <v>13</v>
+      </c>
+      <c r="AY25">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>29</v>
+      </c>
+      <c r="BB25">
+        <v>21</v>
+      </c>
+      <c r="BC25">
+        <v>17.5</v>
+      </c>
+      <c r="BD25">
+        <v>22</v>
+      </c>
+      <c r="BE25">
+        <v>55</v>
+      </c>
+      <c r="BF25">
+        <v>10</v>
+      </c>
+      <c r="BG25">
+        <v>21</v>
+      </c>
+      <c r="BH25">
+        <v>4.5</v>
+      </c>
+      <c r="BI25">
+        <v>3.25</v>
+      </c>
+      <c r="BJ25">
+        <v>10.5</v>
+      </c>
+      <c r="BK25">
+        <v>7</v>
+      </c>
+      <c r="BL25">
+        <v>110</v>
+      </c>
+      <c r="BM25">
         <v>65</v>
       </c>
-      <c r="AL25">
-        <v>180</v>
-      </c>
-      <c r="AM25">
-        <v>580</v>
-      </c>
-      <c r="AN25">
-        <v>85</v>
-      </c>
-      <c r="AO25">
-        <v>230</v>
-      </c>
-      <c r="AP25">
-        <v>2.5</v>
-      </c>
-      <c r="AQ25">
-        <v>2.5</v>
-      </c>
-      <c r="AR25">
-        <v>2.5</v>
-      </c>
-      <c r="AS25">
-        <v>2.5</v>
-      </c>
-      <c r="AT25">
-        <v>2.5</v>
-      </c>
-      <c r="AU25">
-        <v>7.4</v>
-      </c>
-      <c r="AV25">
-        <v>2.5</v>
-      </c>
-      <c r="AW25">
-        <v>2.5</v>
-      </c>
-      <c r="AX25">
-        <v>2.5</v>
-      </c>
-      <c r="AY25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25">
-        <v>12</v>
-      </c>
-      <c r="BA25">
-        <v>2.5</v>
-      </c>
-      <c r="BB25">
-        <v>17</v>
-      </c>
-      <c r="BC25">
-        <v>2.5</v>
-      </c>
-      <c r="BD25">
-        <v>2.5</v>
-      </c>
-      <c r="BE25">
+      <c r="BN25">
+        <v>5.6</v>
+      </c>
+      <c r="BO25">
+        <v>4</v>
+      </c>
+      <c r="BP25">
+        <v>15.5</v>
+      </c>
+      <c r="BQ25">
+        <v>10</v>
+      </c>
+      <c r="BR25">
         <v>28</v>
       </c>
-      <c r="BF25">
-        <v>1.55</v>
-      </c>
-      <c r="BG25">
-        <v>1.55</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.01</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.01</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.01</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.01</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB25" t="s">
         <v>149</v>
@@ -6865,25 +6865,25 @@
         <v>147</v>
       </c>
       <c r="F26">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="G26">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="H26">
+        <v>11.5</v>
+      </c>
+      <c r="I26">
         <v>13</v>
       </c>
-      <c r="I26">
-        <v>17</v>
-      </c>
       <c r="J26">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.04</v>
@@ -6895,196 +6895,196 @@
         <v>1.24</v>
       </c>
       <c r="P26">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
         <v>1.73</v>
       </c>
       <c r="R26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S26">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T26">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="U26">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W26">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="X26">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Y26">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB26">
-        <v>40</v>
+        <v>8.6</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD26">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF26">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="AG26">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AH26">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK26">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="AL26">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN26">
         <v>5.3</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP26">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AR26">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AS26">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AT26">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU26">
         <v>12</v>
       </c>
       <c r="AV26">
+        <v>10.5</v>
+      </c>
+      <c r="AW26">
+        <v>11.5</v>
+      </c>
+      <c r="AX26">
+        <v>6.8</v>
+      </c>
+      <c r="AY26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ26">
         <v>10</v>
       </c>
-      <c r="AW26">
-        <v>38</v>
-      </c>
-      <c r="AX26">
-        <v>6.4</v>
-      </c>
-      <c r="AY26">
-        <v>6.6</v>
-      </c>
-      <c r="AZ26">
-        <v>8.6</v>
-      </c>
       <c r="BA26">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BB26">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BC26">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BD26">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BE26">
-        <v>2.46</v>
+        <v>11.5</v>
       </c>
       <c r="BF26">
+        <v>4.7</v>
+      </c>
+      <c r="BG26">
+        <v>13</v>
+      </c>
+      <c r="BH26">
+        <v>4.7</v>
+      </c>
+      <c r="BI26">
+        <v>3.15</v>
+      </c>
+      <c r="BJ26">
+        <v>15</v>
+      </c>
+      <c r="BK26">
         <v>4.4</v>
       </c>
-      <c r="BG26">
-        <v>4.2</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN26">
-        <v>970</v>
+        <v>3.7</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB26" t="s">
         <v>149</v>
@@ -7113,13 +7113,13 @@
         <v>2.46</v>
       </c>
       <c r="H27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I27">
         <v>3.5</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K27">
         <v>3.5</v>
@@ -7152,7 +7152,7 @@
         <v>1.85</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -7161,172 +7161,172 @@
         <v>1.68</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC27">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="AT27">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU27">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="AV27">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AW27">
-        <v>1.21</v>
+        <v>34</v>
       </c>
       <c r="AX27">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="AY27">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>1.23</v>
+        <v>16</v>
       </c>
       <c r="BA27">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="BB27">
-        <v>1.21</v>
+        <v>5.3</v>
       </c>
       <c r="BC27">
-        <v>1.21</v>
+        <v>5.6</v>
       </c>
       <c r="BD27">
-        <v>1.21</v>
+        <v>34</v>
       </c>
       <c r="BE27">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF27">
-        <v>1.21</v>
+        <v>19</v>
       </c>
       <c r="BG27">
-        <v>1.21</v>
+        <v>5.6</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK27">
         <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM27">
         <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ27">
         <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY27">
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB27" t="s">
         <v>149</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="146">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Chinese League 1</t>
-  </si>
-  <si>
     <t>Serbian First League</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>2026-09-29</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -307,9 +301,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Wuxi Wugou</t>
-  </si>
-  <si>
     <t>Vozdovac</t>
   </si>
   <si>
@@ -328,12 +319,12 @@
     <t>Luxembourg</t>
   </si>
   <si>
+    <t>Spain</t>
+  </si>
+  <si>
     <t>San Marino</t>
   </si>
   <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>Czechia</t>
   </si>
   <si>
@@ -346,6 +337,9 @@
     <t>Scotland</t>
   </si>
   <si>
+    <t>Gateshead</t>
+  </si>
+  <si>
     <t>Hartlepool</t>
   </si>
   <si>
@@ -370,9 +364,6 @@
     <t>AFC Fylde</t>
   </si>
   <si>
-    <t>Gateshead</t>
-  </si>
-  <si>
     <t>Deportivo Pereira</t>
   </si>
   <si>
@@ -385,9 +376,6 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>Ningbo Professional</t>
-  </si>
-  <si>
     <t>FK Napredak</t>
   </si>
   <si>
@@ -406,12 +394,12 @@
     <t>Iceland</t>
   </si>
   <si>
+    <t>Croatia</t>
+  </si>
+  <si>
     <t>Albania</t>
   </si>
   <si>
-    <t>Croatia</t>
-  </si>
-  <si>
     <t>England</t>
   </si>
   <si>
@@ -424,6 +412,9 @@
     <t>Switzerland</t>
   </si>
   <si>
+    <t>Altrincham</t>
+  </si>
+  <si>
     <t>Harrogate Town</t>
   </si>
   <si>
@@ -448,9 +439,6 @@
     <t>Carlisle</t>
   </si>
   <si>
-    <t>Altrincham</t>
-  </si>
-  <si>
     <t>Santa Fe</t>
   </si>
   <si>
@@ -463,7 +451,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 07:59:09</t>
+    <t>2026-09-29 10:10:53</t>
   </si>
 </sst>
 </file>
@@ -795,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1045,241 +1033,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AB2">
+        <v>9.4</v>
+      </c>
+      <c r="AC2">
         <v>8</v>
       </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>9.4</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>44</v>
+      </c>
+      <c r="AT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>34</v>
+      </c>
+      <c r="AX2">
+        <v>13.5</v>
+      </c>
+      <c r="AY2">
         <v>10.5</v>
       </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
+      <c r="AZ2">
+        <v>18</v>
+      </c>
+      <c r="BA2">
+        <v>42</v>
+      </c>
+      <c r="BB2">
+        <v>30</v>
+      </c>
+      <c r="BC2">
         <v>26</v>
       </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
-        <v>7.4</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>15</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>11</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
-      <c r="BB2">
-        <v>22</v>
-      </c>
-      <c r="BC2">
-        <v>21</v>
-      </c>
       <c r="BD2">
+        <v>38</v>
+      </c>
+      <c r="BE2">
+        <v>90</v>
+      </c>
+      <c r="BF2">
+        <v>24</v>
+      </c>
+      <c r="BG2">
         <v>36</v>
       </c>
-      <c r="BE2">
-        <v>95</v>
-      </c>
-      <c r="BF2">
-        <v>17.5</v>
-      </c>
-      <c r="BG2">
-        <v>24</v>
-      </c>
       <c r="BH2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>120</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BW2">
         <v>5.6</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY2">
         <v>5.9</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1287,483 +1275,483 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="X3">
         <v>12.5</v>
       </c>
       <c r="Y3">
+        <v>19</v>
+      </c>
+      <c r="Z3">
+        <v>60</v>
+      </c>
+      <c r="AA3">
+        <v>290</v>
+      </c>
+      <c r="AB3">
+        <v>7</v>
+      </c>
+      <c r="AC3">
+        <v>9.4</v>
+      </c>
+      <c r="AD3">
+        <v>28</v>
+      </c>
+      <c r="AE3">
+        <v>140</v>
+      </c>
+      <c r="AF3">
+        <v>8</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
+        <v>28</v>
+      </c>
+      <c r="AI3">
+        <v>130</v>
+      </c>
+      <c r="AJ3">
+        <v>13.5</v>
+      </c>
+      <c r="AK3">
+        <v>19.5</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>180</v>
+      </c>
+      <c r="AN3">
+        <v>10.5</v>
+      </c>
+      <c r="AO3">
+        <v>200</v>
+      </c>
+      <c r="AP3">
         <v>11.5</v>
       </c>
-      <c r="Z3">
+      <c r="AQ3">
+        <v>17.5</v>
+      </c>
+      <c r="AR3">
+        <v>50</v>
+      </c>
+      <c r="AS3">
+        <v>150</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3">
         <v>27</v>
       </c>
-      <c r="AA3">
-        <v>75</v>
-      </c>
-      <c r="AB3">
-        <v>9</v>
-      </c>
-      <c r="AC3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>16</v>
-      </c>
-      <c r="AE3">
-        <v>50</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>22</v>
-      </c>
-      <c r="AI3">
-        <v>60</v>
-      </c>
-      <c r="AJ3">
-        <v>36</v>
-      </c>
-      <c r="AK3">
-        <v>32</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>160</v>
-      </c>
-      <c r="AN3">
-        <v>27</v>
-      </c>
-      <c r="AO3">
-        <v>65</v>
-      </c>
-      <c r="AP3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>19.5</v>
-      </c>
-      <c r="AS3">
-        <v>55</v>
-      </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
-        <v>12</v>
-      </c>
       <c r="AW3">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
+        <v>26</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
         <v>18.5</v>
       </c>
-      <c r="BA3">
+      <c r="BD3">
         <v>44</v>
       </c>
-      <c r="BB3">
-        <v>26</v>
-      </c>
-      <c r="BC3">
-        <v>24</v>
-      </c>
-      <c r="BD3">
-        <v>32</v>
-      </c>
       <c r="BE3">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="BF3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="BH3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BJ3">
+        <v>12</v>
+      </c>
+      <c r="BK3">
+        <v>10.5</v>
+      </c>
+      <c r="BL3">
+        <v>240</v>
+      </c>
+      <c r="BM3">
+        <v>150</v>
+      </c>
+      <c r="BN3">
+        <v>3.85</v>
+      </c>
+      <c r="BO3">
+        <v>3.55</v>
+      </c>
+      <c r="BP3">
+        <v>10.5</v>
+      </c>
+      <c r="BQ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
+        <v>10</v>
+      </c>
+      <c r="BT3">
         <v>11</v>
       </c>
-      <c r="BK3">
-        <v>5.6</v>
-      </c>
-      <c r="BL3">
-        <v>180</v>
-      </c>
-      <c r="BM3">
-        <v>9.6</v>
-      </c>
-      <c r="BN3">
-        <v>5.1</v>
-      </c>
-      <c r="BO3">
-        <v>4.2</v>
-      </c>
-      <c r="BP3">
-        <v>970</v>
-      </c>
-      <c r="BQ3">
-        <v>6.4</v>
-      </c>
-      <c r="BR3">
-        <v>42</v>
-      </c>
-      <c r="BS3">
-        <v>8</v>
-      </c>
-      <c r="BT3">
-        <v>7.2</v>
-      </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
         <v>88</v>
       </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="G4">
+        <v>3.1</v>
+      </c>
+      <c r="H4">
+        <v>2.84</v>
+      </c>
+      <c r="I4">
+        <v>2.88</v>
+      </c>
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.1</v>
+      </c>
+      <c r="L4">
         <v>1.64</v>
       </c>
-      <c r="H4">
-        <v>7</v>
-      </c>
-      <c r="I4">
-        <v>7.2</v>
-      </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>4.1</v>
-      </c>
-      <c r="L4">
-        <v>1.49</v>
-      </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>2.56</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AA4">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="AB4">
+        <v>8.6</v>
+      </c>
+      <c r="AC4">
         <v>6.8</v>
       </c>
-      <c r="AC4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AD4">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="AF4">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>65</v>
+      </c>
+      <c r="AO4">
+        <v>55</v>
+      </c>
+      <c r="AP4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>8</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>42</v>
+      </c>
+      <c r="AT4">
+        <v>8.4</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>12.5</v>
+      </c>
+      <c r="AW4">
+        <v>36</v>
+      </c>
+      <c r="AX4">
+        <v>17</v>
+      </c>
+      <c r="AY4">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4">
+        <v>21</v>
+      </c>
+      <c r="BA4">
+        <v>55</v>
+      </c>
+      <c r="BB4">
         <v>50</v>
       </c>
-      <c r="AM4">
-        <v>200</v>
-      </c>
-      <c r="AN4">
-        <v>11.5</v>
-      </c>
-      <c r="AO4">
-        <v>210</v>
-      </c>
-      <c r="AP4">
-        <v>11</v>
-      </c>
-      <c r="AQ4">
-        <v>17</v>
-      </c>
-      <c r="AR4">
-        <v>50</v>
-      </c>
-      <c r="AS4">
-        <v>160</v>
-      </c>
-      <c r="AT4">
-        <v>6.4</v>
-      </c>
-      <c r="AU4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4">
-        <v>27</v>
-      </c>
-      <c r="AW4">
-        <v>110</v>
-      </c>
-      <c r="AX4">
-        <v>7.6</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>27</v>
-      </c>
-      <c r="BA4">
-        <v>100</v>
-      </c>
-      <c r="BB4">
-        <v>13</v>
-      </c>
       <c r="BC4">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="BD4">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BE4">
         <v>160</v>
       </c>
       <c r="BF4">
+        <v>50</v>
+      </c>
+      <c r="BG4">
+        <v>44</v>
+      </c>
+      <c r="BH4">
+        <v>2.64</v>
+      </c>
+      <c r="BI4">
+        <v>2.48</v>
+      </c>
+      <c r="BJ4">
+        <v>11.5</v>
+      </c>
+      <c r="BK4">
+        <v>10</v>
+      </c>
+      <c r="BL4">
+        <v>230</v>
+      </c>
+      <c r="BM4">
+        <v>200</v>
+      </c>
+      <c r="BN4">
+        <v>5.8</v>
+      </c>
+      <c r="BO4">
+        <v>5.3</v>
+      </c>
+      <c r="BP4">
+        <v>34</v>
+      </c>
+      <c r="BQ4">
         <v>10.5</v>
       </c>
-      <c r="BG4">
-        <v>120</v>
-      </c>
-      <c r="BH4">
-        <v>3.05</v>
-      </c>
-      <c r="BI4">
-        <v>2.9</v>
-      </c>
-      <c r="BJ4">
-        <v>12.5</v>
-      </c>
-      <c r="BK4">
-        <v>11</v>
-      </c>
-      <c r="BL4">
-        <v>260</v>
-      </c>
-      <c r="BM4">
+      <c r="BR4">
+        <v>55</v>
+      </c>
+      <c r="BS4">
+        <v>11.5</v>
+      </c>
+      <c r="BT4">
+        <v>5.6</v>
+      </c>
+      <c r="BU4">
+        <v>5.1</v>
+      </c>
+      <c r="BV4">
+        <v>32</v>
+      </c>
+      <c r="BW4">
+        <v>10.5</v>
+      </c>
+      <c r="BX4">
+        <v>55</v>
+      </c>
+      <c r="BY4">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4">
         <v>60</v>
       </c>
-      <c r="BN4">
-        <v>3.85</v>
-      </c>
-      <c r="BO4">
-        <v>3.55</v>
-      </c>
-      <c r="BP4">
-        <v>11</v>
-      </c>
-      <c r="BQ4">
-        <v>9.6</v>
-      </c>
-      <c r="BR4">
-        <v>40</v>
-      </c>
-      <c r="BS4">
-        <v>10</v>
-      </c>
-      <c r="BT4">
-        <v>10.5</v>
-      </c>
-      <c r="BU4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BV4">
-        <v>100</v>
-      </c>
-      <c r="BW4">
+      <c r="CA4">
         <v>12</v>
       </c>
-      <c r="BX4">
-        <v>110</v>
-      </c>
-      <c r="BY4">
-        <v>13.5</v>
-      </c>
-      <c r="BZ4">
-        <v>30</v>
-      </c>
-      <c r="CA4">
-        <v>9.6</v>
-      </c>
       <c r="CB4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1771,990 +1759,990 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>3.1</v>
+        <v>1.42</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="H5">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>2.84</v>
+        <v>9.6</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>2.74</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="X5">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="Z5">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="AA5">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AM5">
+        <v>110</v>
+      </c>
+      <c r="AN5">
+        <v>5.2</v>
+      </c>
+      <c r="AO5">
         <v>180</v>
       </c>
-      <c r="AN5">
-        <v>65</v>
-      </c>
-      <c r="AO5">
-        <v>50</v>
-      </c>
       <c r="AP5">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AR5">
+        <v>60</v>
+      </c>
+      <c r="AS5">
         <v>15</v>
       </c>
-      <c r="AS5">
-        <v>42</v>
-      </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AY5">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB5">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="BD5">
+        <v>25</v>
+      </c>
+      <c r="BE5">
+        <v>70</v>
+      </c>
+      <c r="BF5">
+        <v>4.7</v>
+      </c>
+      <c r="BG5">
+        <v>16</v>
+      </c>
+      <c r="BH5">
+        <v>4.7</v>
+      </c>
+      <c r="BI5">
+        <v>4.1</v>
+      </c>
+      <c r="BJ5">
+        <v>11</v>
+      </c>
+      <c r="BK5">
+        <v>5.8</v>
+      </c>
+      <c r="BL5">
+        <v>130</v>
+      </c>
+      <c r="BM5">
+        <v>10.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.2</v>
+      </c>
+      <c r="BO5">
+        <v>3.7</v>
+      </c>
+      <c r="BP5">
+        <v>8.4</v>
+      </c>
+      <c r="BQ5">
+        <v>5</v>
+      </c>
+      <c r="BR5">
+        <v>22</v>
+      </c>
+      <c r="BS5">
+        <v>7.4</v>
+      </c>
+      <c r="BT5">
+        <v>12.5</v>
+      </c>
+      <c r="BU5">
+        <v>6.2</v>
+      </c>
+      <c r="BV5">
+        <v>65</v>
+      </c>
+      <c r="BW5">
+        <v>9.6</v>
+      </c>
+      <c r="BX5">
         <v>60</v>
       </c>
-      <c r="BE5">
-        <v>120</v>
-      </c>
-      <c r="BF5">
-        <v>50</v>
-      </c>
-      <c r="BG5">
-        <v>42</v>
-      </c>
-      <c r="BH5">
-        <v>2.68</v>
-      </c>
-      <c r="BI5">
-        <v>2.52</v>
-      </c>
-      <c r="BJ5">
+      <c r="BY5">
+        <v>9.6</v>
+      </c>
+      <c r="BZ5">
         <v>11.5</v>
       </c>
-      <c r="BK5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL5">
-        <v>230</v>
-      </c>
-      <c r="BM5">
-        <v>60</v>
-      </c>
-      <c r="BN5">
-        <v>6</v>
-      </c>
-      <c r="BO5">
-        <v>5.3</v>
-      </c>
-      <c r="BP5">
-        <v>34</v>
-      </c>
-      <c r="BQ5">
-        <v>10</v>
-      </c>
-      <c r="BR5">
-        <v>60</v>
-      </c>
-      <c r="BS5">
-        <v>10.5</v>
-      </c>
-      <c r="BT5">
-        <v>5.5</v>
-      </c>
-      <c r="BU5">
-        <v>4.9</v>
-      </c>
-      <c r="BV5">
-        <v>30</v>
-      </c>
-      <c r="BW5">
-        <v>9.4</v>
-      </c>
-      <c r="BX5">
-        <v>55</v>
-      </c>
-      <c r="BY5">
-        <v>10.5</v>
-      </c>
-      <c r="BZ5">
-        <v>60</v>
-      </c>
       <c r="CA5">
-        <v>23</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="G6">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="I6">
+        <v>7.2</v>
+      </c>
+      <c r="J6">
+        <v>3.8</v>
+      </c>
+      <c r="K6">
+        <v>3.85</v>
+      </c>
+      <c r="L6">
+        <v>1.55</v>
+      </c>
+      <c r="M6">
+        <v>1.11</v>
+      </c>
+      <c r="N6">
+        <v>2.94</v>
+      </c>
+      <c r="O6">
+        <v>1.49</v>
+      </c>
+      <c r="P6">
+        <v>1.65</v>
+      </c>
+      <c r="Q6">
+        <v>2.5</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <v>2.42</v>
+      </c>
+      <c r="U6">
+        <v>1.69</v>
+      </c>
+      <c r="V6">
+        <v>1.16</v>
+      </c>
+      <c r="W6">
+        <v>2.46</v>
+      </c>
+      <c r="X6">
         <v>10</v>
       </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5.4</v>
-      </c>
-      <c r="L6">
-        <v>1.27</v>
-      </c>
-      <c r="M6">
-        <v>1.03</v>
-      </c>
-      <c r="N6">
-        <v>6</v>
-      </c>
-      <c r="O6">
-        <v>1.18</v>
-      </c>
-      <c r="P6">
-        <v>2.68</v>
-      </c>
-      <c r="Q6">
-        <v>1.56</v>
-      </c>
-      <c r="R6">
-        <v>1.67</v>
-      </c>
-      <c r="S6">
-        <v>2.4</v>
-      </c>
-      <c r="T6">
-        <v>1.8</v>
-      </c>
-      <c r="U6">
-        <v>2.12</v>
-      </c>
-      <c r="V6">
-        <v>1.11</v>
-      </c>
-      <c r="W6">
-        <v>3.25</v>
-      </c>
-      <c r="X6">
+      <c r="Y6">
+        <v>16.5</v>
+      </c>
+      <c r="Z6">
+        <v>55</v>
+      </c>
+      <c r="AA6">
+        <v>280</v>
+      </c>
+      <c r="AB6">
+        <v>6.2</v>
+      </c>
+      <c r="AC6">
+        <v>8.6</v>
+      </c>
+      <c r="AD6">
         <v>29</v>
       </c>
-      <c r="Y6">
-        <v>48</v>
-      </c>
-      <c r="Z6">
-        <v>100</v>
-      </c>
-      <c r="AA6">
-        <v>310</v>
-      </c>
-      <c r="AB6">
-        <v>11.5</v>
-      </c>
-      <c r="AC6">
-        <v>12</v>
-      </c>
-      <c r="AD6">
-        <v>38</v>
-      </c>
       <c r="AE6">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
+        <v>30</v>
+      </c>
+      <c r="AI6">
+        <v>150</v>
+      </c>
+      <c r="AJ6">
+        <v>15.5</v>
+      </c>
+      <c r="AK6">
         <v>22</v>
       </c>
-      <c r="AI6">
-        <v>260</v>
-      </c>
-      <c r="AJ6">
-        <v>13</v>
-      </c>
-      <c r="AK6">
-        <v>14.5</v>
-      </c>
       <c r="AL6">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="AO6">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AR6">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AS6">
-        <v>12.5</v>
+        <v>180</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
         <v>26</v>
       </c>
       <c r="AW6">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="AX6">
+        <v>7.8</v>
+      </c>
+      <c r="AY6">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6">
+        <v>27</v>
+      </c>
+      <c r="BA6">
+        <v>80</v>
+      </c>
+      <c r="BB6">
+        <v>15</v>
+      </c>
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
+        <v>50</v>
+      </c>
+      <c r="BE6">
+        <v>120</v>
+      </c>
+      <c r="BF6">
+        <v>13.5</v>
+      </c>
+      <c r="BG6">
+        <v>170</v>
+      </c>
+      <c r="BH6">
+        <v>2.82</v>
+      </c>
+      <c r="BI6">
+        <v>2.68</v>
+      </c>
+      <c r="BJ6">
+        <v>13</v>
+      </c>
+      <c r="BK6">
+        <v>11</v>
+      </c>
+      <c r="BL6">
+        <v>280</v>
+      </c>
+      <c r="BM6">
+        <v>75</v>
+      </c>
+      <c r="BN6">
+        <v>3.85</v>
+      </c>
+      <c r="BO6">
+        <v>3.65</v>
+      </c>
+      <c r="BP6">
+        <v>12.5</v>
+      </c>
+      <c r="BQ6">
+        <v>10.5</v>
+      </c>
+      <c r="BR6">
+        <v>38</v>
+      </c>
+      <c r="BS6">
+        <v>13</v>
+      </c>
+      <c r="BT6">
+        <v>10</v>
+      </c>
+      <c r="BU6">
         <v>9</v>
       </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>19</v>
-      </c>
-      <c r="BA6">
-        <v>11.5</v>
-      </c>
-      <c r="BB6">
-        <v>11</v>
-      </c>
-      <c r="BC6">
+      <c r="BV6">
+        <v>95</v>
+      </c>
+      <c r="BW6">
+        <v>15.5</v>
+      </c>
+      <c r="BX6">
+        <v>110</v>
+      </c>
+      <c r="BY6">
+        <v>16</v>
+      </c>
+      <c r="BZ6">
+        <v>32</v>
+      </c>
+      <c r="CA6">
         <v>12.5</v>
       </c>
-      <c r="BD6">
-        <v>23</v>
-      </c>
-      <c r="BE6">
-        <v>28</v>
-      </c>
-      <c r="BF6">
-        <v>4.6</v>
-      </c>
-      <c r="BG6">
-        <v>15</v>
-      </c>
-      <c r="BH6">
-        <v>4.7</v>
-      </c>
-      <c r="BI6">
-        <v>4.1</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>6</v>
-      </c>
-      <c r="BL6">
-        <v>130</v>
-      </c>
-      <c r="BM6">
-        <v>12.5</v>
-      </c>
-      <c r="BN6">
-        <v>4.1</v>
-      </c>
-      <c r="BO6">
-        <v>3.7</v>
-      </c>
-      <c r="BP6">
-        <v>8</v>
-      </c>
-      <c r="BQ6">
-        <v>5.1</v>
-      </c>
-      <c r="BR6">
-        <v>22</v>
-      </c>
-      <c r="BS6">
-        <v>8.4</v>
-      </c>
-      <c r="BT6">
-        <v>12.5</v>
-      </c>
-      <c r="BU6">
-        <v>6.6</v>
-      </c>
-      <c r="BV6">
-        <v>65</v>
-      </c>
-      <c r="BW6">
-        <v>11.5</v>
-      </c>
-      <c r="BX6">
-        <v>60</v>
-      </c>
-      <c r="BY6">
-        <v>11</v>
-      </c>
-      <c r="BZ6">
-        <v>11.5</v>
-      </c>
-      <c r="CA6">
-        <v>6.2</v>
-      </c>
       <c r="CB6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
+        <v>3.45</v>
+      </c>
+      <c r="H7">
+        <v>2.42</v>
+      </c>
+      <c r="I7">
+        <v>2.44</v>
+      </c>
+      <c r="J7">
+        <v>3.35</v>
+      </c>
+      <c r="K7">
+        <v>3.4</v>
+      </c>
+      <c r="L7">
+        <v>1.5</v>
+      </c>
+      <c r="M7">
+        <v>1.1</v>
+      </c>
+      <c r="N7">
+        <v>3.2</v>
+      </c>
+      <c r="O7">
+        <v>1.43</v>
+      </c>
+      <c r="P7">
+        <v>1.74</v>
+      </c>
+      <c r="Q7">
+        <v>2.3</v>
+      </c>
+      <c r="R7">
+        <v>1.27</v>
+      </c>
+      <c r="S7">
+        <v>4.4</v>
+      </c>
+      <c r="T7">
+        <v>1.94</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
         <v>1.69</v>
       </c>
-      <c r="H7">
-        <v>6.8</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>3.8</v>
-      </c>
-      <c r="K7">
-        <v>3.85</v>
-      </c>
-      <c r="L7">
-        <v>1.55</v>
-      </c>
-      <c r="M7">
-        <v>1.11</v>
-      </c>
-      <c r="N7">
-        <v>2.94</v>
-      </c>
-      <c r="O7">
-        <v>1.49</v>
-      </c>
-      <c r="P7">
-        <v>1.65</v>
-      </c>
-      <c r="Q7">
-        <v>2.48</v>
-      </c>
-      <c r="R7">
-        <v>1.23</v>
-      </c>
-      <c r="S7">
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <v>2.4</v>
-      </c>
-      <c r="U7">
-        <v>1.7</v>
-      </c>
-      <c r="V7">
-        <v>1.16</v>
-      </c>
       <c r="W7">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="AA7">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AB7">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
+        <v>11.5</v>
+      </c>
+      <c r="AE7">
         <v>29</v>
       </c>
-      <c r="AE7">
-        <v>140</v>
-      </c>
       <c r="AF7">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AO7">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="AP7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR7">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="AS7">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AU7">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="AX7">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ7">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BD7">
         <v>50</v>
       </c>
       <c r="BE7">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="BF7">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BG7">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="BH7">
+        <v>3</v>
+      </c>
+      <c r="BI7">
         <v>2.82</v>
       </c>
-      <c r="BI7">
-        <v>2.68</v>
-      </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
+        <v>9</v>
+      </c>
+      <c r="BL7">
+        <v>180</v>
+      </c>
+      <c r="BM7">
+        <v>120</v>
+      </c>
+      <c r="BN7">
+        <v>6.4</v>
+      </c>
+      <c r="BO7">
+        <v>5.7</v>
+      </c>
+      <c r="BP7">
+        <v>29</v>
+      </c>
+      <c r="BQ7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR7">
+        <v>55</v>
+      </c>
+      <c r="BS7">
         <v>11</v>
       </c>
-      <c r="BL7">
-        <v>280</v>
-      </c>
-      <c r="BM7">
-        <v>17</v>
-      </c>
-      <c r="BN7">
-        <v>3.9</v>
-      </c>
-      <c r="BO7">
-        <v>3.6</v>
-      </c>
-      <c r="BP7">
-        <v>12</v>
-      </c>
-      <c r="BQ7">
+      <c r="BT7">
+        <v>5.1</v>
+      </c>
+      <c r="BU7">
+        <v>4.7</v>
+      </c>
+      <c r="BV7">
+        <v>19.5</v>
+      </c>
+      <c r="BW7">
+        <v>8.6</v>
+      </c>
+      <c r="BX7">
+        <v>44</v>
+      </c>
+      <c r="BY7">
         <v>10.5</v>
       </c>
-      <c r="BR7">
-        <v>38</v>
-      </c>
-      <c r="BS7">
-        <v>13</v>
-      </c>
-      <c r="BT7">
+      <c r="BZ7">
+        <v>42</v>
+      </c>
+      <c r="CA7">
         <v>10</v>
       </c>
-      <c r="BU7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BV7">
-        <v>95</v>
-      </c>
-      <c r="BW7">
-        <v>15</v>
-      </c>
-      <c r="BX7">
-        <v>110</v>
-      </c>
-      <c r="BY7">
-        <v>15.5</v>
-      </c>
-      <c r="BZ7">
-        <v>32</v>
-      </c>
-      <c r="CA7">
-        <v>12.5</v>
-      </c>
       <c r="CB7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>3.65</v>
+        <v>1.22</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>1.23</v>
       </c>
       <c r="H8">
-        <v>2.28</v>
+        <v>16.5</v>
       </c>
       <c r="I8">
-        <v>2.3</v>
+        <v>17</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="V8">
-        <v>1.76</v>
+        <v>1.06</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="X8">
+        <v>34</v>
+      </c>
+      <c r="Y8">
+        <v>60</v>
+      </c>
+      <c r="Z8">
+        <v>200</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
         <v>11.5</v>
       </c>
-      <c r="Y8">
-        <v>8.4</v>
-      </c>
-      <c r="Z8">
+      <c r="AC8">
+        <v>17.5</v>
+      </c>
+      <c r="AD8">
+        <v>55</v>
+      </c>
+      <c r="AE8">
+        <v>310</v>
+      </c>
+      <c r="AF8">
+        <v>8.6</v>
+      </c>
+      <c r="AG8">
+        <v>12</v>
+      </c>
+      <c r="AH8">
+        <v>36</v>
+      </c>
+      <c r="AI8">
+        <v>170</v>
+      </c>
+      <c r="AJ8">
+        <v>9.4</v>
+      </c>
+      <c r="AK8">
         <v>13</v>
       </c>
-      <c r="AA8">
+      <c r="AL8">
+        <v>36</v>
+      </c>
+      <c r="AM8">
+        <v>170</v>
+      </c>
+      <c r="AN8">
+        <v>3.5</v>
+      </c>
+      <c r="AO8">
+        <v>390</v>
+      </c>
+      <c r="AP8">
         <v>30</v>
       </c>
-      <c r="AB8">
-        <v>12</v>
-      </c>
-      <c r="AC8">
-        <v>7.4</v>
-      </c>
-      <c r="AD8">
-        <v>11.5</v>
-      </c>
-      <c r="AE8">
-        <v>28</v>
-      </c>
-      <c r="AF8">
-        <v>25</v>
-      </c>
-      <c r="AG8">
-        <v>15</v>
-      </c>
-      <c r="AH8">
-        <v>19.5</v>
-      </c>
-      <c r="AI8">
-        <v>46</v>
-      </c>
-      <c r="AJ8">
-        <v>75</v>
-      </c>
-      <c r="AK8">
+      <c r="AQ8">
         <v>48</v>
       </c>
-      <c r="AL8">
-        <v>65</v>
-      </c>
-      <c r="AM8">
-        <v>130</v>
-      </c>
-      <c r="AN8">
-        <v>65</v>
-      </c>
-      <c r="AO8">
-        <v>24</v>
-      </c>
-      <c r="AP8">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8">
-        <v>8</v>
-      </c>
       <c r="AR8">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="AS8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AW8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX8">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BB8">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="BC8">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BD8">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BE8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF8">
-        <v>48</v>
+        <v>3.35</v>
       </c>
       <c r="BG8">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BL8">
         <v>180</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN8">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BP8">
-        <v>34</v>
+        <v>6.4</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR8">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BT8">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="BV8">
-        <v>17.5</v>
+        <v>130</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BX8">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="BY8">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F9">
+        <v>55</v>
+      </c>
+      <c r="G9">
         <v>60</v>
-      </c>
-      <c r="G9">
-        <v>80</v>
       </c>
       <c r="H9">
         <v>1.06</v>
@@ -2763,34 +2751,34 @@
         <v>1.07</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M9">
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P9">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q9">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="S9">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T9">
         <v>4.7</v>
@@ -2805,28 +2793,28 @@
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Y9">
         <v>11</v>
       </c>
       <c r="Z9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AB9">
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AD9">
+        <v>25</v>
+      </c>
+      <c r="AE9">
         <v>24</v>
-      </c>
-      <c r="AE9">
-        <v>28</v>
       </c>
       <c r="AF9">
         <v>1000</v>
@@ -2835,10 +2823,10 @@
         <v>1000</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ9">
         <v>1000</v>
@@ -2856,312 +2844,312 @@
         <v>1000</v>
       </c>
       <c r="AO9">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AP9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AQ9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS9">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT9">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AU9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AV9">
+        <v>22</v>
+      </c>
+      <c r="AW9">
         <v>21</v>
       </c>
-      <c r="AW9">
-        <v>19.5</v>
-      </c>
       <c r="AX9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AY9">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AZ9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="BA9">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="BB9">
-        <v>14</v>
+        <v>600</v>
       </c>
       <c r="BC9">
+        <v>90</v>
+      </c>
+      <c r="BD9">
         <v>95</v>
       </c>
-      <c r="BD9">
-        <v>32</v>
-      </c>
       <c r="BE9">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BG9">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BH9">
         <v>6.2</v>
       </c>
       <c r="BI9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BK9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
+        <v>12</v>
+      </c>
+      <c r="BN9">
+        <v>60</v>
+      </c>
+      <c r="BO9">
         <v>10</v>
-      </c>
-      <c r="BN9">
-        <v>70</v>
-      </c>
-      <c r="BO9">
-        <v>8.800000000000001</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BR9">
-        <v>840</v>
+        <v>920</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BU9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BV9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BW9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BX9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY9">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="CA9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.25</v>
+        <v>11.5</v>
       </c>
       <c r="G10">
-        <v>1.26</v>
+        <v>12</v>
       </c>
       <c r="H10">
-        <v>14.5</v>
+        <v>1.33</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>1.34</v>
       </c>
       <c r="J10">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="O10">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="S10">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
-        <v>1.07</v>
+        <v>3.9</v>
       </c>
       <c r="W10">
+        <v>1.09</v>
+      </c>
+      <c r="X10">
+        <v>22</v>
+      </c>
+      <c r="Y10">
+        <v>9</v>
+      </c>
+      <c r="Z10">
+        <v>7.8</v>
+      </c>
+      <c r="AA10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AB10">
+        <v>38</v>
+      </c>
+      <c r="AC10">
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <v>10.5</v>
+      </c>
+      <c r="AE10">
+        <v>13.5</v>
+      </c>
+      <c r="AF10">
+        <v>120</v>
+      </c>
+      <c r="AG10">
+        <v>38</v>
+      </c>
+      <c r="AH10">
+        <v>28</v>
+      </c>
+      <c r="AI10">
+        <v>36</v>
+      </c>
+      <c r="AJ10">
+        <v>510</v>
+      </c>
+      <c r="AK10">
+        <v>180</v>
+      </c>
+      <c r="AL10">
+        <v>140</v>
+      </c>
+      <c r="AM10">
+        <v>150</v>
+      </c>
+      <c r="AN10">
+        <v>260</v>
+      </c>
+      <c r="AO10">
+        <v>5</v>
+      </c>
+      <c r="AP10">
+        <v>21</v>
+      </c>
+      <c r="AQ10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR10">
+        <v>7.6</v>
+      </c>
+      <c r="AS10">
+        <v>9.6</v>
+      </c>
+      <c r="AT10">
+        <v>36</v>
+      </c>
+      <c r="AU10">
+        <v>13</v>
+      </c>
+      <c r="AV10">
+        <v>10</v>
+      </c>
+      <c r="AW10">
+        <v>13</v>
+      </c>
+      <c r="AX10">
+        <v>100</v>
+      </c>
+      <c r="AY10">
+        <v>34</v>
+      </c>
+      <c r="AZ10">
+        <v>27</v>
+      </c>
+      <c r="BA10">
+        <v>34</v>
+      </c>
+      <c r="BB10">
+        <v>300</v>
+      </c>
+      <c r="BC10">
+        <v>160</v>
+      </c>
+      <c r="BD10">
+        <v>120</v>
+      </c>
+      <c r="BE10">
+        <v>140</v>
+      </c>
+      <c r="BF10">
+        <v>240</v>
+      </c>
+      <c r="BG10">
         <v>4.9</v>
       </c>
-      <c r="X10">
-        <v>36</v>
-      </c>
-      <c r="Y10">
-        <v>55</v>
-      </c>
-      <c r="Z10">
-        <v>170</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>11.5</v>
-      </c>
-      <c r="AC10">
-        <v>17</v>
-      </c>
-      <c r="AD10">
-        <v>48</v>
-      </c>
-      <c r="AE10">
-        <v>280</v>
-      </c>
-      <c r="AF10">
-        <v>8.6</v>
-      </c>
-      <c r="AG10">
+      <c r="BH10">
+        <v>4.1</v>
+      </c>
+      <c r="BI10">
+        <v>3.85</v>
+      </c>
+      <c r="BJ10">
         <v>12</v>
-      </c>
-      <c r="AH10">
-        <v>34</v>
-      </c>
-      <c r="AI10">
-        <v>160</v>
-      </c>
-      <c r="AJ10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK10">
-        <v>13</v>
-      </c>
-      <c r="AL10">
-        <v>36</v>
-      </c>
-      <c r="AM10">
-        <v>160</v>
-      </c>
-      <c r="AN10">
-        <v>3.55</v>
-      </c>
-      <c r="AO10">
-        <v>370</v>
-      </c>
-      <c r="AP10">
-        <v>30</v>
-      </c>
-      <c r="AQ10">
-        <v>48</v>
-      </c>
-      <c r="AR10">
-        <v>120</v>
-      </c>
-      <c r="AS10">
-        <v>30</v>
-      </c>
-      <c r="AT10">
-        <v>10.5</v>
-      </c>
-      <c r="AU10">
-        <v>16.5</v>
-      </c>
-      <c r="AV10">
-        <v>44</v>
-      </c>
-      <c r="AW10">
-        <v>28</v>
-      </c>
-      <c r="AX10">
-        <v>8.4</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
-      <c r="AZ10">
-        <v>32</v>
-      </c>
-      <c r="BA10">
-        <v>110</v>
-      </c>
-      <c r="BB10">
-        <v>9</v>
-      </c>
-      <c r="BC10">
-        <v>12</v>
-      </c>
-      <c r="BD10">
-        <v>30</v>
-      </c>
-      <c r="BE10">
-        <v>110</v>
-      </c>
-      <c r="BF10">
-        <v>3.45</v>
-      </c>
-      <c r="BG10">
-        <v>85</v>
-      </c>
-      <c r="BH10">
-        <v>4.9</v>
-      </c>
-      <c r="BI10">
-        <v>4.4</v>
-      </c>
-      <c r="BJ10">
-        <v>12.5</v>
       </c>
       <c r="BK10">
         <v>11</v>
@@ -3170,778 +3158,778 @@
         <v>170</v>
       </c>
       <c r="BM10">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="BN10">
-        <v>3.95</v>
+        <v>14</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="BP10">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="BQ10">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="BR10">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="BS10">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT10">
-        <v>15.5</v>
+        <v>3.75</v>
       </c>
       <c r="BU10">
-        <v>14</v>
+        <v>3.45</v>
       </c>
       <c r="BV10">
-        <v>130</v>
+        <v>7.4</v>
       </c>
       <c r="BW10">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BX10">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="BY10">
         <v>11.5</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="G11">
+        <v>1.29</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>6.4</v>
+      </c>
+      <c r="K11">
+        <v>6.6</v>
+      </c>
+      <c r="L11">
+        <v>1.35</v>
+      </c>
+      <c r="M11">
+        <v>1.05</v>
+      </c>
+      <c r="N11">
+        <v>4.5</v>
+      </c>
+      <c r="O11">
+        <v>1.27</v>
+      </c>
+      <c r="P11">
+        <v>2.22</v>
+      </c>
+      <c r="Q11">
+        <v>1.79</v>
+      </c>
+      <c r="R11">
+        <v>1.47</v>
+      </c>
+      <c r="S11">
+        <v>3.05</v>
+      </c>
+      <c r="T11">
+        <v>2.48</v>
+      </c>
+      <c r="U11">
+        <v>1.64</v>
+      </c>
+      <c r="V11">
+        <v>1.06</v>
+      </c>
+      <c r="W11">
+        <v>4.5</v>
+      </c>
+      <c r="X11">
+        <v>19</v>
+      </c>
+      <c r="Y11">
+        <v>40</v>
+      </c>
+      <c r="Z11">
+        <v>150</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>7.6</v>
+      </c>
+      <c r="AC11">
+        <v>14.5</v>
+      </c>
+      <c r="AD11">
+        <v>60</v>
+      </c>
+      <c r="AE11">
+        <v>340</v>
+      </c>
+      <c r="AF11">
+        <v>6.8</v>
+      </c>
+      <c r="AG11">
         <v>11.5</v>
       </c>
-      <c r="H11">
-        <v>1.34</v>
-      </c>
-      <c r="I11">
-        <v>1.35</v>
-      </c>
-      <c r="J11">
-        <v>5.9</v>
-      </c>
-      <c r="K11">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>1.33</v>
-      </c>
-      <c r="M11">
-        <v>1.04</v>
-      </c>
-      <c r="N11">
-        <v>5.1</v>
-      </c>
-      <c r="O11">
-        <v>1.23</v>
-      </c>
-      <c r="P11">
-        <v>2.42</v>
-      </c>
-      <c r="Q11">
-        <v>1.69</v>
-      </c>
-      <c r="R11">
-        <v>1.55</v>
-      </c>
-      <c r="S11">
-        <v>2.78</v>
-      </c>
-      <c r="T11">
-        <v>2.1</v>
-      </c>
-      <c r="U11">
-        <v>1.88</v>
-      </c>
-      <c r="V11">
+      <c r="AH11">
+        <v>42</v>
+      </c>
+      <c r="AI11">
+        <v>260</v>
+      </c>
+      <c r="AJ11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK11">
+        <v>16</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>300</v>
+      </c>
+      <c r="AN11">
+        <v>5.3</v>
+      </c>
+      <c r="AO11">
+        <v>520</v>
+      </c>
+      <c r="AP11">
+        <v>18</v>
+      </c>
+      <c r="AQ11">
+        <v>34</v>
+      </c>
+      <c r="AR11">
+        <v>95</v>
+      </c>
+      <c r="AS11">
+        <v>23</v>
+      </c>
+      <c r="AT11">
+        <v>7.2</v>
+      </c>
+      <c r="AU11">
+        <v>13.5</v>
+      </c>
+      <c r="AV11">
+        <v>50</v>
+      </c>
+      <c r="AW11">
+        <v>21</v>
+      </c>
+      <c r="AX11">
+        <v>6.4</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>40</v>
+      </c>
+      <c r="BA11">
+        <v>38</v>
+      </c>
+      <c r="BB11">
+        <v>8.4</v>
+      </c>
+      <c r="BC11">
+        <v>14.5</v>
+      </c>
+      <c r="BD11">
+        <v>50</v>
+      </c>
+      <c r="BE11">
+        <v>46</v>
+      </c>
+      <c r="BF11">
+        <v>5</v>
+      </c>
+      <c r="BG11">
+        <v>23</v>
+      </c>
+      <c r="BH11">
         <v>3.85</v>
       </c>
-      <c r="W11">
-        <v>1.09</v>
-      </c>
-      <c r="X11">
-        <v>22</v>
-      </c>
-      <c r="Y11">
-        <v>9</v>
-      </c>
-      <c r="Z11">
-        <v>7.8</v>
-      </c>
-      <c r="AA11">
-        <v>10</v>
-      </c>
-      <c r="AB11">
-        <v>34</v>
-      </c>
-      <c r="AC11">
-        <v>13.5</v>
-      </c>
-      <c r="AD11">
-        <v>10.5</v>
-      </c>
-      <c r="AE11">
-        <v>14</v>
-      </c>
-      <c r="AF11">
-        <v>120</v>
-      </c>
-      <c r="AG11">
-        <v>38</v>
-      </c>
-      <c r="AH11">
+      <c r="BI11">
+        <v>3.6</v>
+      </c>
+      <c r="BJ11">
+        <v>15</v>
+      </c>
+      <c r="BK11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL11">
+        <v>270</v>
+      </c>
+      <c r="BM11">
+        <v>75</v>
+      </c>
+      <c r="BN11">
+        <v>3.45</v>
+      </c>
+      <c r="BO11">
+        <v>3.2</v>
+      </c>
+      <c r="BP11">
+        <v>7</v>
+      </c>
+      <c r="BQ11">
+        <v>6.2</v>
+      </c>
+      <c r="BR11">
         <v>29</v>
-      </c>
-      <c r="AI11">
-        <v>36</v>
-      </c>
-      <c r="AJ11">
-        <v>490</v>
-      </c>
-      <c r="AK11">
-        <v>180</v>
-      </c>
-      <c r="AL11">
-        <v>140</v>
-      </c>
-      <c r="AM11">
-        <v>160</v>
-      </c>
-      <c r="AN11">
-        <v>270</v>
-      </c>
-      <c r="AO11">
-        <v>5.2</v>
-      </c>
-      <c r="AP11">
-        <v>21</v>
-      </c>
-      <c r="AQ11">
-        <v>8.6</v>
-      </c>
-      <c r="AR11">
-        <v>7.6</v>
-      </c>
-      <c r="AS11">
-        <v>9.6</v>
-      </c>
-      <c r="AT11">
-        <v>30</v>
-      </c>
-      <c r="AU11">
-        <v>12.5</v>
-      </c>
-      <c r="AV11">
-        <v>10</v>
-      </c>
-      <c r="AW11">
-        <v>13.5</v>
-      </c>
-      <c r="AX11">
-        <v>95</v>
-      </c>
-      <c r="AY11">
-        <v>34</v>
-      </c>
-      <c r="AZ11">
-        <v>28</v>
-      </c>
-      <c r="BA11">
-        <v>34</v>
-      </c>
-      <c r="BB11">
-        <v>300</v>
-      </c>
-      <c r="BC11">
-        <v>150</v>
-      </c>
-      <c r="BD11">
-        <v>120</v>
-      </c>
-      <c r="BE11">
-        <v>140</v>
-      </c>
-      <c r="BF11">
-        <v>220</v>
-      </c>
-      <c r="BG11">
-        <v>5.1</v>
-      </c>
-      <c r="BH11">
-        <v>4.1</v>
-      </c>
-      <c r="BI11">
-        <v>3.8</v>
-      </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>10.5</v>
-      </c>
-      <c r="BL11">
-        <v>170</v>
-      </c>
-      <c r="BM11">
-        <v>11.5</v>
-      </c>
-      <c r="BN11">
-        <v>16</v>
-      </c>
-      <c r="BO11">
-        <v>12</v>
-      </c>
-      <c r="BP11">
-        <v>110</v>
-      </c>
-      <c r="BQ11">
-        <v>10.5</v>
-      </c>
-      <c r="BR11">
-        <v>95</v>
       </c>
       <c r="BS11">
         <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>3.75</v>
+        <v>17</v>
       </c>
       <c r="BU11">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="BV11">
-        <v>7.8</v>
+        <v>180</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BX11">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="BY11">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BZ11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="G12">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="H12">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>5.6</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="T12">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="V12">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="W12">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="X12">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB12">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC12">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AE12">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="AF12">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AJ12">
-        <v>8.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AL12">
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="AN12">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="AO12">
-        <v>590</v>
+        <v>150</v>
       </c>
       <c r="AP12">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AR12">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AS12">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AT12">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AW12">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="AX12">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="BA12">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BB12">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BC12">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE12">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="BF12">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="BG12">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="BH12">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="BI12">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="BJ12">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BL12">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="BM12">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="BN12">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BO12">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP12">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BS12">
+        <v>11</v>
+      </c>
+      <c r="BT12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU12">
+        <v>7.8</v>
+      </c>
+      <c r="BV12">
+        <v>70</v>
+      </c>
+      <c r="BW12">
+        <v>13</v>
+      </c>
+      <c r="BX12">
+        <v>85</v>
+      </c>
+      <c r="BY12">
+        <v>13.5</v>
+      </c>
+      <c r="BZ12">
+        <v>34</v>
+      </c>
+      <c r="CA12">
         <v>10.5</v>
       </c>
-      <c r="BT12">
-        <v>18</v>
-      </c>
-      <c r="BU12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV12">
-        <v>190</v>
-      </c>
-      <c r="BW12">
-        <v>15.5</v>
-      </c>
-      <c r="BX12">
-        <v>160</v>
-      </c>
-      <c r="BY12">
-        <v>15.5</v>
-      </c>
-      <c r="BZ12">
-        <v>13.5</v>
-      </c>
-      <c r="CA12">
-        <v>7.4</v>
-      </c>
       <c r="CB12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>1.84</v>
+        <v>4.6</v>
       </c>
       <c r="G13">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="H13">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="J13">
+        <v>3.6</v>
+      </c>
+      <c r="K13">
         <v>3.65</v>
       </c>
-      <c r="K13">
-        <v>3.7</v>
-      </c>
       <c r="L13">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P13">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q13">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="U13">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="W13">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="X13">
+        <v>11.5</v>
+      </c>
+      <c r="Y13">
+        <v>7.4</v>
+      </c>
+      <c r="Z13">
         <v>10.5</v>
       </c>
-      <c r="Y13">
-        <v>15</v>
-      </c>
-      <c r="Z13">
+      <c r="AA13">
+        <v>22</v>
+      </c>
+      <c r="AB13">
+        <v>13.5</v>
+      </c>
+      <c r="AC13">
+        <v>7.8</v>
+      </c>
+      <c r="AD13">
+        <v>10.5</v>
+      </c>
+      <c r="AE13">
+        <v>22</v>
+      </c>
+      <c r="AF13">
+        <v>34</v>
+      </c>
+      <c r="AG13">
+        <v>18</v>
+      </c>
+      <c r="AH13">
+        <v>22</v>
+      </c>
+      <c r="AI13">
+        <v>44</v>
+      </c>
+      <c r="AJ13">
+        <v>120</v>
+      </c>
+      <c r="AK13">
+        <v>65</v>
+      </c>
+      <c r="AL13">
+        <v>75</v>
+      </c>
+      <c r="AM13">
+        <v>140</v>
+      </c>
+      <c r="AN13">
+        <v>100</v>
+      </c>
+      <c r="AO13">
+        <v>17.5</v>
+      </c>
+      <c r="AP13">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13">
+        <v>7.2</v>
+      </c>
+      <c r="AR13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS13">
+        <v>20</v>
+      </c>
+      <c r="AT13">
+        <v>13</v>
+      </c>
+      <c r="AU13">
+        <v>7.6</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13">
+        <v>21</v>
+      </c>
+      <c r="AX13">
+        <v>30</v>
+      </c>
+      <c r="AY13">
+        <v>17.5</v>
+      </c>
+      <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
         <v>42</v>
       </c>
-      <c r="AA13">
-        <v>160</v>
-      </c>
-      <c r="AB13">
-        <v>6.8</v>
-      </c>
-      <c r="AC13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD13">
-        <v>22</v>
-      </c>
-      <c r="AE13">
+      <c r="BB13">
         <v>100</v>
       </c>
-      <c r="AF13">
-        <v>9.4</v>
-      </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
-      <c r="AH13">
-        <v>25</v>
-      </c>
-      <c r="AI13">
-        <v>110</v>
-      </c>
-      <c r="AJ13">
-        <v>19.5</v>
-      </c>
-      <c r="AK13">
-        <v>23</v>
-      </c>
-      <c r="AL13">
-        <v>55</v>
-      </c>
-      <c r="AM13">
-        <v>190</v>
-      </c>
-      <c r="AN13">
-        <v>17.5</v>
-      </c>
-      <c r="AO13">
-        <v>150</v>
-      </c>
-      <c r="AP13">
-        <v>10</v>
-      </c>
-      <c r="AQ13">
-        <v>13</v>
-      </c>
-      <c r="AR13">
-        <v>36</v>
-      </c>
-      <c r="AS13">
-        <v>110</v>
-      </c>
-      <c r="AT13">
-        <v>6.4</v>
-      </c>
-      <c r="AU13">
-        <v>7.8</v>
-      </c>
-      <c r="AV13">
-        <v>21</v>
-      </c>
-      <c r="AW13">
-        <v>80</v>
-      </c>
-      <c r="AX13">
-        <v>9</v>
-      </c>
-      <c r="AY13">
-        <v>10</v>
-      </c>
-      <c r="AZ13">
-        <v>23</v>
-      </c>
-      <c r="BA13">
-        <v>85</v>
-      </c>
-      <c r="BB13">
-        <v>18</v>
-      </c>
       <c r="BC13">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BD13">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BE13">
         <v>120</v>
       </c>
       <c r="BF13">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="BG13">
-        <v>95</v>
+        <v>16.5</v>
       </c>
       <c r="BH13">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BJ13">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL13">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="BM13">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BN13">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>7.2</v>
       </c>
       <c r="BP13">
+        <v>60</v>
+      </c>
+      <c r="BQ13">
+        <v>11</v>
+      </c>
+      <c r="BR13">
+        <v>75</v>
+      </c>
+      <c r="BS13">
+        <v>11</v>
+      </c>
+      <c r="BT13">
+        <v>4.4</v>
+      </c>
+      <c r="BU13">
+        <v>4</v>
+      </c>
+      <c r="BV13">
         <v>14</v>
       </c>
-      <c r="BQ13">
-        <v>7</v>
-      </c>
-      <c r="BR13">
+      <c r="BW13">
+        <v>12.5</v>
+      </c>
+      <c r="BX13">
         <v>40</v>
       </c>
-      <c r="BS13">
-        <v>9.6</v>
-      </c>
-      <c r="BT13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU13">
-        <v>8</v>
-      </c>
-      <c r="BV13">
-        <v>60</v>
-      </c>
-      <c r="BW13">
-        <v>10.5</v>
-      </c>
-      <c r="BX13">
-        <v>75</v>
-      </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
         <v>38</v>
       </c>
       <c r="CA13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3949,258 +3937,258 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>5.2</v>
+      </c>
+      <c r="H14">
+        <v>1.68</v>
+      </c>
+      <c r="I14">
+        <v>1.7</v>
+      </c>
+      <c r="J14">
+        <v>4.6</v>
+      </c>
+      <c r="K14">
         <v>4.7</v>
       </c>
-      <c r="G14">
-        <v>4.8</v>
-      </c>
-      <c r="H14">
-        <v>1.95</v>
-      </c>
-      <c r="I14">
-        <v>1.96</v>
-      </c>
-      <c r="J14">
-        <v>3.6</v>
-      </c>
-      <c r="K14">
-        <v>3.65</v>
-      </c>
       <c r="L14">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="S14">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="U14">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA14">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AC14">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE14">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AF14">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK14">
         <v>70</v>
       </c>
       <c r="AL14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AN14">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AO14">
+        <v>8</v>
+      </c>
+      <c r="AP14">
+        <v>19.5</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>10.5</v>
+      </c>
+      <c r="AS14">
+        <v>16</v>
+      </c>
+      <c r="AT14">
+        <v>18.5</v>
+      </c>
+      <c r="AU14">
+        <v>9.4</v>
+      </c>
+      <c r="AV14">
+        <v>9</v>
+      </c>
+      <c r="AW14">
+        <v>14.5</v>
+      </c>
+      <c r="AX14">
+        <v>34</v>
+      </c>
+      <c r="AY14">
         <v>17.5</v>
       </c>
-      <c r="AP14">
-        <v>10.5</v>
-      </c>
-      <c r="AQ14">
+      <c r="AZ14">
+        <v>16.5</v>
+      </c>
+      <c r="BA14">
+        <v>25</v>
+      </c>
+      <c r="BB14">
+        <v>95</v>
+      </c>
+      <c r="BC14">
+        <v>46</v>
+      </c>
+      <c r="BD14">
+        <v>44</v>
+      </c>
+      <c r="BE14">
+        <v>70</v>
+      </c>
+      <c r="BF14">
+        <v>42</v>
+      </c>
+      <c r="BG14">
+        <v>7.4</v>
+      </c>
+      <c r="BH14">
+        <v>4.9</v>
+      </c>
+      <c r="BI14">
+        <v>3.75</v>
+      </c>
+      <c r="BJ14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK14">
         <v>7</v>
       </c>
-      <c r="AR14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS14">
-        <v>20</v>
-      </c>
-      <c r="AT14">
-        <v>13</v>
-      </c>
-      <c r="AU14">
-        <v>7.8</v>
-      </c>
-      <c r="AV14">
-        <v>10</v>
-      </c>
-      <c r="AW14">
-        <v>21</v>
-      </c>
-      <c r="AX14">
-        <v>30</v>
-      </c>
-      <c r="AY14">
-        <v>18</v>
-      </c>
-      <c r="AZ14">
-        <v>22</v>
-      </c>
-      <c r="BA14">
-        <v>40</v>
-      </c>
-      <c r="BB14">
-        <v>100</v>
-      </c>
-      <c r="BC14">
-        <v>60</v>
-      </c>
-      <c r="BD14">
-        <v>70</v>
-      </c>
-      <c r="BE14">
+      <c r="BL14">
         <v>120</v>
       </c>
-      <c r="BF14">
-        <v>90</v>
-      </c>
-      <c r="BG14">
-        <v>16.5</v>
-      </c>
-      <c r="BH14">
-        <v>3</v>
-      </c>
-      <c r="BI14">
-        <v>2.84</v>
-      </c>
-      <c r="BJ14">
+      <c r="BM14">
+        <v>7.2</v>
+      </c>
+      <c r="BN14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO14">
+        <v>6.4</v>
+      </c>
+      <c r="BP14">
+        <v>42</v>
+      </c>
+      <c r="BQ14">
+        <v>6.4</v>
+      </c>
+      <c r="BR14">
+        <v>55</v>
+      </c>
+      <c r="BS14">
+        <v>6.6</v>
+      </c>
+      <c r="BT14">
+        <v>4.8</v>
+      </c>
+      <c r="BU14">
+        <v>4.1</v>
+      </c>
+      <c r="BV14">
         <v>11.5</v>
       </c>
-      <c r="BK14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL14">
-        <v>210</v>
-      </c>
-      <c r="BM14">
-        <v>60</v>
-      </c>
-      <c r="BN14">
-        <v>8</v>
-      </c>
-      <c r="BO14">
-        <v>7.2</v>
-      </c>
-      <c r="BP14">
-        <v>60</v>
-      </c>
-      <c r="BQ14">
-        <v>12</v>
-      </c>
-      <c r="BR14">
-        <v>75</v>
-      </c>
-      <c r="BS14">
-        <v>13</v>
-      </c>
-      <c r="BT14">
-        <v>4.3</v>
-      </c>
-      <c r="BU14">
-        <v>4</v>
-      </c>
-      <c r="BV14">
-        <v>14</v>
-      </c>
       <c r="BW14">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX14">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BY14">
         <v>11</v>
       </c>
       <c r="BZ14">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="CA14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F15">
         <v>3.8</v>
@@ -4233,13 +4221,13 @@
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
         <v>2.88</v>
@@ -4248,7 +4236,7 @@
         <v>1.68</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
         <v>2</v>
@@ -4263,25 +4251,25 @@
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA15">
         <v>25</v>
       </c>
       <c r="AB15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC15">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG15">
         <v>16</v>
@@ -4296,7 +4284,7 @@
         <v>90</v>
       </c>
       <c r="AK15">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL15">
         <v>46</v>
@@ -4311,7 +4299,7 @@
         <v>11.5</v>
       </c>
       <c r="AP15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4326,16 +4314,16 @@
         <v>15</v>
       </c>
       <c r="AU15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
         <v>9.6</v>
       </c>
       <c r="AW15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY15">
         <v>14.5</v>
@@ -4344,7 +4332,7 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15">
         <v>60</v>
@@ -4356,7 +4344,7 @@
         <v>40</v>
       </c>
       <c r="BE15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF15">
         <v>30</v>
@@ -4365,10 +4353,10 @@
         <v>10</v>
       </c>
       <c r="BH15">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BI15">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ15">
         <v>10.5</v>
@@ -4380,10 +4368,10 @@
         <v>110</v>
       </c>
       <c r="BM15">
-        <v>1.02</v>
+        <v>7.4</v>
       </c>
       <c r="BN15">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO15">
         <v>5.9</v>
@@ -4392,13 +4380,13 @@
         <v>34</v>
       </c>
       <c r="BQ15">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="BR15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT15">
         <v>5</v>
@@ -4407,42 +4395,42 @@
         <v>4.4</v>
       </c>
       <c r="BV15">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX15">
         <v>28</v>
       </c>
       <c r="BY15">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="BZ15">
         <v>22</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F16">
         <v>2.22</v>
@@ -4463,7 +4451,7 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
         <v>1.03</v>
@@ -4475,7 +4463,7 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q16">
         <v>1.55</v>
@@ -4484,19 +4472,19 @@
         <v>1.7</v>
       </c>
       <c r="S16">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
         <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4523,7 +4511,7 @@
         <v>30</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG16">
         <v>11.5</v>
@@ -4544,7 +4532,7 @@
         <v>28</v>
       </c>
       <c r="AM16">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN16">
         <v>10.5</v>
@@ -4577,7 +4565,7 @@
         <v>23</v>
       </c>
       <c r="AX16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY16">
         <v>10</v>
@@ -4592,7 +4580,7 @@
         <v>25</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD16">
         <v>21</v>
@@ -4616,7 +4604,7 @@
         <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
         <v>85</v>
@@ -4628,13 +4616,13 @@
         <v>6.8</v>
       </c>
       <c r="BO16">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BP16">
         <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR16">
         <v>27</v>
@@ -4667,36 +4655,36 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4723,7 +4711,7 @@
         <v>1.63</v>
       </c>
       <c r="R17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S17">
         <v>2.58</v>
@@ -4732,55 +4720,55 @@
         <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X17">
         <v>23</v>
       </c>
       <c r="Y17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z17">
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AB17">
         <v>13</v>
       </c>
       <c r="AC17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE17">
         <v>42</v>
       </c>
       <c r="AF17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL17">
         <v>29</v>
@@ -4792,7 +4780,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP17">
         <v>20</v>
@@ -4801,28 +4789,28 @@
         <v>17</v>
       </c>
       <c r="AR17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS17">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AT17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV17">
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
         <v>14</v>
@@ -4831,7 +4819,7 @@
         <v>30</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC17">
         <v>16.5</v>
@@ -4843,93 +4831,93 @@
         <v>29</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG17">
         <v>22</v>
       </c>
       <c r="BH17">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BI17">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL17">
         <v>95</v>
       </c>
       <c r="BM17">
-        <v>1.02</v>
+        <v>7</v>
       </c>
       <c r="BN17">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO17">
         <v>4.6</v>
       </c>
       <c r="BP17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR17">
         <v>26</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BT17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV17">
         <v>32</v>
       </c>
       <c r="BW17">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="BZ17">
         <v>19</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F18">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G18">
         <v>2.24</v>
@@ -4941,7 +4929,7 @@
         <v>3.5</v>
       </c>
       <c r="J18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
         <v>4.1</v>
@@ -4959,22 +4947,22 @@
         <v>1.24</v>
       </c>
       <c r="P18">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S18">
         <v>2.8</v>
       </c>
       <c r="T18">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -4983,13 +4971,13 @@
         <v>1.8</v>
       </c>
       <c r="X18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA18">
         <v>70</v>
@@ -4998,19 +4986,19 @@
         <v>13</v>
       </c>
       <c r="AC18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE18">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF18">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
         <v>16.5</v>
@@ -5019,10 +5007,10 @@
         <v>46</v>
       </c>
       <c r="AJ18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK18">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL18">
         <v>34</v>
@@ -5031,19 +5019,19 @@
         <v>85</v>
       </c>
       <c r="AN18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP18">
         <v>17.5</v>
       </c>
       <c r="AQ18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS18">
         <v>32</v>
@@ -5052,13 +5040,13 @@
         <v>11</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18">
         <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX18">
         <v>13.5</v>
@@ -5070,7 +5058,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB18">
         <v>21</v>
@@ -5079,102 +5067,102 @@
         <v>18</v>
       </c>
       <c r="BD18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE18">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF18">
         <v>11</v>
       </c>
       <c r="BG18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH18">
         <v>4.7</v>
       </c>
       <c r="BI18">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL18">
         <v>110</v>
       </c>
       <c r="BM18">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
       </c>
       <c r="BO18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP18">
         <v>18</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR18">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BU18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV18">
         <v>30</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX18">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY18">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="BZ18">
         <v>23</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F19">
         <v>2.24</v>
       </c>
       <c r="G19">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H19">
         <v>3.15</v>
@@ -5183,10 +5171,10 @@
         <v>3.35</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>1.34</v>
@@ -5195,25 +5183,25 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R19">
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19">
         <v>2.36</v>
@@ -5225,7 +5213,7 @@
         <v>1.74</v>
       </c>
       <c r="X19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y19">
         <v>16</v>
@@ -5249,10 +5237,10 @@
         <v>40</v>
       </c>
       <c r="AF19">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>17</v>
@@ -5261,10 +5249,10 @@
         <v>48</v>
       </c>
       <c r="AJ19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19">
         <v>38</v>
@@ -5276,10 +5264,10 @@
         <v>15</v>
       </c>
       <c r="AO19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ19">
         <v>13</v>
@@ -5288,7 +5276,7 @@
         <v>21</v>
       </c>
       <c r="AS19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT19">
         <v>10.5</v>
@@ -5303,58 +5291,58 @@
         <v>27</v>
       </c>
       <c r="AX19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY19">
         <v>10</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
         <v>32</v>
       </c>
       <c r="BB19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD19">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE19">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BF19">
         <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>4.5</v>
       </c>
       <c r="BI19">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19">
         <v>9.199999999999999</v>
       </c>
       <c r="BK19">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL19">
         <v>110</v>
       </c>
       <c r="BM19">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="BN19">
         <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP19">
         <v>16.5</v>
@@ -5366,10 +5354,10 @@
         <v>32</v>
       </c>
       <c r="BS19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BT19">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BU19">
         <v>5.7</v>
@@ -5387,39 +5375,39 @@
         <v>16.5</v>
       </c>
       <c r="BZ19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA19">
         <v>10.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I20">
         <v>4.7</v>
@@ -5443,25 +5431,25 @@
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
         <v>1.52</v>
       </c>
       <c r="R20">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
         <v>2.16</v>
@@ -5479,7 +5467,7 @@
         <v>170</v>
       </c>
       <c r="AB20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC20">
         <v>11</v>
@@ -5491,7 +5479,7 @@
         <v>50</v>
       </c>
       <c r="AF20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG20">
         <v>11</v>
@@ -5518,10 +5506,10 @@
         <v>7.6</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP20">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AQ20">
         <v>20</v>
@@ -5548,10 +5536,10 @@
         <v>13</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA20">
         <v>36</v>
@@ -5584,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="BK20">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>85</v>
@@ -5617,7 +5605,7 @@
         <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW20">
         <v>1.02</v>
@@ -5629,168 +5617,168 @@
         <v>1.02</v>
       </c>
       <c r="BZ20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G21">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="H21">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="I21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>1.35</v>
       </c>
       <c r="M21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O21">
         <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q21">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R21">
         <v>1.48</v>
       </c>
       <c r="S21">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="X21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA21">
         <v>65</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD21">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF21">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ21">
+        <v>27</v>
+      </c>
+      <c r="AK21">
+        <v>23</v>
+      </c>
+      <c r="AL21">
         <v>36</v>
-      </c>
-      <c r="AK21">
-        <v>25</v>
-      </c>
-      <c r="AL21">
-        <v>38</v>
       </c>
       <c r="AM21">
         <v>95</v>
       </c>
       <c r="AN21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO21">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ21">
+        <v>14</v>
+      </c>
+      <c r="AR21">
+        <v>22</v>
+      </c>
+      <c r="AS21">
+        <v>46</v>
+      </c>
+      <c r="AT21">
+        <v>10</v>
+      </c>
+      <c r="AU21">
+        <v>8</v>
+      </c>
+      <c r="AV21">
         <v>13</v>
       </c>
-      <c r="AR21">
-        <v>21</v>
-      </c>
-      <c r="AS21">
-        <v>42</v>
-      </c>
-      <c r="AT21">
-        <v>10.5</v>
-      </c>
-      <c r="AU21">
-        <v>7.8</v>
-      </c>
-      <c r="AV21">
-        <v>12</v>
-      </c>
       <c r="AW21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21">
         <v>14</v>
@@ -5799,19 +5787,19 @@
         <v>30</v>
       </c>
       <c r="BB21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE21">
         <v>46</v>
       </c>
       <c r="BF21">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG21">
         <v>24</v>
@@ -5820,96 +5808,96 @@
         <v>4.3</v>
       </c>
       <c r="BI21">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="BK21">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="BL21">
         <v>110</v>
       </c>
       <c r="BM21">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN21">
+        <v>5.8</v>
+      </c>
+      <c r="BO21">
+        <v>4.6</v>
+      </c>
+      <c r="BP21">
+        <v>15</v>
+      </c>
+      <c r="BQ21">
+        <v>5.2</v>
+      </c>
+      <c r="BR21">
+        <v>26</v>
+      </c>
+      <c r="BS21">
         <v>6</v>
       </c>
-      <c r="BO21">
-        <v>4.2</v>
-      </c>
-      <c r="BP21">
-        <v>18.5</v>
-      </c>
-      <c r="BQ21">
-        <v>4.3</v>
-      </c>
-      <c r="BR21">
-        <v>32</v>
-      </c>
-      <c r="BS21">
-        <v>4.8</v>
-      </c>
       <c r="BT21">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU21">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV21">
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY21">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BZ21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA21">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F22">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G22">
         <v>2.5</v>
       </c>
       <c r="H22">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I22">
         <v>2.78</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
         <v>4.4</v>
@@ -5927,7 +5915,7 @@
         <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q22">
         <v>1.51</v>
@@ -5936,13 +5924,13 @@
         <v>1.74</v>
       </c>
       <c r="S22">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T22">
         <v>1.5</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V22">
         <v>1.56</v>
@@ -5957,16 +5945,16 @@
         <v>19.5</v>
       </c>
       <c r="Z22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA22">
         <v>44</v>
       </c>
       <c r="AB22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD22">
         <v>13</v>
@@ -5984,7 +5972,7 @@
         <v>15</v>
       </c>
       <c r="AI22">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ22">
         <v>36</v>
@@ -6005,7 +5993,7 @@
         <v>14</v>
       </c>
       <c r="AP22">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AQ22">
         <v>17.5</v>
@@ -6020,7 +6008,7 @@
         <v>16.5</v>
       </c>
       <c r="AU22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6059,7 +6047,7 @@
         <v>12</v>
       </c>
       <c r="BH22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI22">
         <v>3.85</v>
@@ -6077,13 +6065,13 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO22">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP22">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
@@ -6092,19 +6080,19 @@
         <v>25</v>
       </c>
       <c r="BS22">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU22">
         <v>5.6</v>
       </c>
       <c r="BV22">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BW22">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
         <v>27</v>
@@ -6113,13 +6101,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="CA22">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6127,241 +6115,241 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H23">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="I23">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="J23">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="L23">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="O23">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="R23">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="S23">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="T23">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="V23">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="W23">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X23">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Y23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z23">
+        <v>12</v>
+      </c>
+      <c r="AA23">
+        <v>28</v>
+      </c>
+      <c r="AB23">
+        <v>14</v>
+      </c>
+      <c r="AC23">
+        <v>7.8</v>
+      </c>
+      <c r="AD23">
         <v>11</v>
       </c>
-      <c r="Z23">
-        <v>13.5</v>
-      </c>
-      <c r="AA23">
+      <c r="AE23">
+        <v>32</v>
+      </c>
+      <c r="AF23">
+        <v>38</v>
+      </c>
+      <c r="AG23">
+        <v>18.5</v>
+      </c>
+      <c r="AH23">
+        <v>21</v>
+      </c>
+      <c r="AI23">
+        <v>55</v>
+      </c>
+      <c r="AJ23">
+        <v>120</v>
+      </c>
+      <c r="AK23">
+        <v>75</v>
+      </c>
+      <c r="AL23">
+        <v>90</v>
+      </c>
+      <c r="AM23">
+        <v>450</v>
+      </c>
+      <c r="AN23">
+        <v>95</v>
+      </c>
+      <c r="AO23">
+        <v>19</v>
+      </c>
+      <c r="AP23">
+        <v>10.5</v>
+      </c>
+      <c r="AQ23">
+        <v>7.4</v>
+      </c>
+      <c r="AR23">
+        <v>10</v>
+      </c>
+      <c r="AS23">
+        <v>18.5</v>
+      </c>
+      <c r="AT23">
+        <v>12</v>
+      </c>
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23">
+        <v>9.6</v>
+      </c>
+      <c r="AW23">
+        <v>20</v>
+      </c>
+      <c r="AX23">
+        <v>25</v>
+      </c>
+      <c r="AY23">
+        <v>16</v>
+      </c>
+      <c r="AZ23">
         <v>19.5</v>
       </c>
-      <c r="AB23">
-        <v>21</v>
-      </c>
-      <c r="AC23">
-        <v>10.5</v>
-      </c>
-      <c r="AD23">
-        <v>10.5</v>
-      </c>
-      <c r="AE23">
-        <v>17.5</v>
-      </c>
-      <c r="AF23">
-        <v>40</v>
-      </c>
-      <c r="AG23">
-        <v>19</v>
-      </c>
-      <c r="AH23">
-        <v>19.5</v>
-      </c>
-      <c r="AI23">
-        <v>29</v>
-      </c>
-      <c r="AJ23">
-        <v>110</v>
-      </c>
-      <c r="AK23">
+      <c r="BA23">
+        <v>32</v>
+      </c>
+      <c r="BB23">
+        <v>60</v>
+      </c>
+      <c r="BC23">
+        <v>42</v>
+      </c>
+      <c r="BD23">
+        <v>50</v>
+      </c>
+      <c r="BE23">
+        <v>34</v>
+      </c>
+      <c r="BF23">
         <v>55</v>
       </c>
-      <c r="AL23">
-        <v>55</v>
-      </c>
-      <c r="AM23">
-        <v>80</v>
-      </c>
-      <c r="AN23">
-        <v>46</v>
-      </c>
-      <c r="AO23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP23">
-        <v>18.5</v>
-      </c>
-      <c r="AQ23">
-        <v>10</v>
-      </c>
-      <c r="AR23">
-        <v>10.5</v>
-      </c>
-      <c r="AS23">
-        <v>17.5</v>
-      </c>
-      <c r="AT23">
-        <v>17</v>
-      </c>
-      <c r="AU23">
-        <v>9.4</v>
-      </c>
-      <c r="AV23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW23">
-        <v>15</v>
-      </c>
-      <c r="AX23">
-        <v>34</v>
-      </c>
-      <c r="AY23">
+      <c r="BG23">
         <v>16.5</v>
       </c>
-      <c r="AZ23">
-        <v>16</v>
-      </c>
-      <c r="BA23">
-        <v>24</v>
-      </c>
-      <c r="BB23">
-        <v>46</v>
-      </c>
-      <c r="BC23">
-        <v>44</v>
-      </c>
-      <c r="BD23">
-        <v>44</v>
-      </c>
-      <c r="BE23">
-        <v>55</v>
-      </c>
-      <c r="BF23">
-        <v>34</v>
-      </c>
-      <c r="BG23">
-        <v>8</v>
-      </c>
       <c r="BH23">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6369,241 +6357,241 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>2.06</v>
+      </c>
+      <c r="H24">
+        <v>3.75</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24">
+        <v>3.9</v>
+      </c>
+      <c r="K24">
+        <v>4.2</v>
+      </c>
+      <c r="L24">
+        <v>1.33</v>
+      </c>
+      <c r="M24">
+        <v>1.05</v>
+      </c>
+      <c r="N24">
+        <v>4.8</v>
+      </c>
+      <c r="O24">
+        <v>1.24</v>
+      </c>
+      <c r="P24">
+        <v>2.28</v>
+      </c>
+      <c r="Q24">
+        <v>1.71</v>
+      </c>
+      <c r="R24">
+        <v>1.51</v>
+      </c>
+      <c r="S24">
+        <v>2.8</v>
+      </c>
+      <c r="T24">
+        <v>1.64</v>
+      </c>
+      <c r="U24">
+        <v>2.34</v>
+      </c>
+      <c r="V24">
+        <v>1.33</v>
+      </c>
+      <c r="W24">
+        <v>1.94</v>
+      </c>
+      <c r="X24">
+        <v>23</v>
+      </c>
+      <c r="Y24">
+        <v>23</v>
+      </c>
+      <c r="Z24">
+        <v>85</v>
+      </c>
+      <c r="AA24">
+        <v>170</v>
+      </c>
+      <c r="AB24">
+        <v>12</v>
+      </c>
+      <c r="AC24">
+        <v>9.4</v>
+      </c>
+      <c r="AD24">
+        <v>20</v>
+      </c>
+      <c r="AE24">
+        <v>48</v>
+      </c>
+      <c r="AF24">
+        <v>15</v>
+      </c>
+      <c r="AG24">
+        <v>11</v>
+      </c>
+      <c r="AH24">
+        <v>17</v>
+      </c>
+      <c r="AI24">
+        <v>50</v>
+      </c>
+      <c r="AJ24">
+        <v>29</v>
+      </c>
+      <c r="AK24">
+        <v>21</v>
+      </c>
+      <c r="AL24">
+        <v>42</v>
+      </c>
+      <c r="AM24">
+        <v>200</v>
+      </c>
+      <c r="AN24">
+        <v>12</v>
+      </c>
+      <c r="AO24">
+        <v>40</v>
+      </c>
+      <c r="AP24">
+        <v>17</v>
+      </c>
+      <c r="AQ24">
+        <v>14.5</v>
+      </c>
+      <c r="AR24">
+        <v>23</v>
+      </c>
+      <c r="AS24">
+        <v>50</v>
+      </c>
+      <c r="AT24">
+        <v>10</v>
+      </c>
+      <c r="AU24">
+        <v>8</v>
+      </c>
+      <c r="AV24">
+        <v>13.5</v>
+      </c>
+      <c r="AW24">
+        <v>27</v>
+      </c>
+      <c r="AX24">
+        <v>13</v>
+      </c>
+      <c r="AY24">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24">
+        <v>14</v>
+      </c>
+      <c r="BA24">
+        <v>30</v>
+      </c>
+      <c r="BB24">
+        <v>21</v>
+      </c>
+      <c r="BC24">
+        <v>17.5</v>
+      </c>
+      <c r="BD24">
+        <v>23</v>
+      </c>
+      <c r="BE24">
+        <v>55</v>
+      </c>
+      <c r="BF24">
+        <v>10</v>
+      </c>
+      <c r="BG24">
+        <v>21</v>
+      </c>
+      <c r="BH24">
+        <v>4.5</v>
+      </c>
+      <c r="BI24">
+        <v>3.25</v>
+      </c>
+      <c r="BJ24">
+        <v>10.5</v>
+      </c>
+      <c r="BK24">
+        <v>7</v>
+      </c>
+      <c r="BL24">
+        <v>110</v>
+      </c>
+      <c r="BM24">
+        <v>65</v>
+      </c>
+      <c r="BN24">
+        <v>5.7</v>
+      </c>
+      <c r="BO24">
+        <v>4</v>
+      </c>
+      <c r="BP24">
+        <v>15.5</v>
+      </c>
+      <c r="BQ24">
+        <v>10</v>
+      </c>
+      <c r="BR24">
+        <v>28</v>
+      </c>
+      <c r="BS24">
+        <v>18</v>
+      </c>
+      <c r="BT24">
+        <v>8.6</v>
+      </c>
+      <c r="BU24">
+        <v>5.8</v>
+      </c>
+      <c r="BV24">
+        <v>34</v>
+      </c>
+      <c r="BW24">
+        <v>21</v>
+      </c>
+      <c r="BX24">
+        <v>42</v>
+      </c>
+      <c r="BY24">
+        <v>26</v>
+      </c>
+      <c r="BZ24">
+        <v>21</v>
+      </c>
+      <c r="CA24">
+        <v>14</v>
+      </c>
+      <c r="CB24" t="s">
         <v>145</v>
-      </c>
-      <c r="F24">
-        <v>4.5</v>
-      </c>
-      <c r="G24">
-        <v>4.7</v>
-      </c>
-      <c r="H24">
-        <v>1.99</v>
-      </c>
-      <c r="I24">
-        <v>2.04</v>
-      </c>
-      <c r="J24">
-        <v>3.4</v>
-      </c>
-      <c r="K24">
-        <v>3.6</v>
-      </c>
-      <c r="L24">
-        <v>1.48</v>
-      </c>
-      <c r="M24">
-        <v>1.09</v>
-      </c>
-      <c r="N24">
-        <v>3.25</v>
-      </c>
-      <c r="O24">
-        <v>1.42</v>
-      </c>
-      <c r="P24">
-        <v>1.76</v>
-      </c>
-      <c r="Q24">
-        <v>2.26</v>
-      </c>
-      <c r="R24">
-        <v>1.27</v>
-      </c>
-      <c r="S24">
-        <v>4.3</v>
-      </c>
-      <c r="T24">
-        <v>2</v>
-      </c>
-      <c r="U24">
-        <v>1.91</v>
-      </c>
-      <c r="V24">
-        <v>1.96</v>
-      </c>
-      <c r="W24">
-        <v>1.27</v>
-      </c>
-      <c r="X24">
-        <v>11.5</v>
-      </c>
-      <c r="Y24">
-        <v>7.8</v>
-      </c>
-      <c r="Z24">
-        <v>11.5</v>
-      </c>
-      <c r="AA24">
-        <v>27</v>
-      </c>
-      <c r="AB24">
-        <v>14</v>
-      </c>
-      <c r="AC24">
-        <v>7.8</v>
-      </c>
-      <c r="AD24">
-        <v>11</v>
-      </c>
-      <c r="AE24">
-        <v>28</v>
-      </c>
-      <c r="AF24">
-        <v>38</v>
-      </c>
-      <c r="AG24">
-        <v>19.5</v>
-      </c>
-      <c r="AH24">
-        <v>25</v>
-      </c>
-      <c r="AI24">
-        <v>55</v>
-      </c>
-      <c r="AJ24">
-        <v>500</v>
-      </c>
-      <c r="AK24">
-        <v>170</v>
-      </c>
-      <c r="AL24">
-        <v>200</v>
-      </c>
-      <c r="AM24">
-        <v>580</v>
-      </c>
-      <c r="AN24">
-        <v>120</v>
-      </c>
-      <c r="AO24">
-        <v>20</v>
-      </c>
-      <c r="AP24">
-        <v>10</v>
-      </c>
-      <c r="AQ24">
-        <v>7</v>
-      </c>
-      <c r="AR24">
-        <v>10</v>
-      </c>
-      <c r="AS24">
-        <v>20</v>
-      </c>
-      <c r="AT24">
-        <v>12</v>
-      </c>
-      <c r="AU24">
-        <v>7</v>
-      </c>
-      <c r="AV24">
-        <v>9.6</v>
-      </c>
-      <c r="AW24">
-        <v>17.5</v>
-      </c>
-      <c r="AX24">
-        <v>27</v>
-      </c>
-      <c r="AY24">
-        <v>16</v>
-      </c>
-      <c r="AZ24">
-        <v>19</v>
-      </c>
-      <c r="BA24">
-        <v>32</v>
-      </c>
-      <c r="BB24">
-        <v>70</v>
-      </c>
-      <c r="BC24">
-        <v>46</v>
-      </c>
-      <c r="BD24">
-        <v>55</v>
-      </c>
-      <c r="BE24">
-        <v>34</v>
-      </c>
-      <c r="BF24">
-        <v>60</v>
-      </c>
-      <c r="BG24">
-        <v>16</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.01</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.01</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.01</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.01</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>1.01</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>1.01</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>1.01</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>1.01</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6611,241 +6599,241 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F25">
-        <v>1.99</v>
+        <v>1.28</v>
       </c>
       <c r="G25">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="H25">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M25">
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q25">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="R25">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T25">
-        <v>1.64</v>
+        <v>2.48</v>
       </c>
       <c r="U25">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="W25">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="X25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y25">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="Z25">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AA25">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
+        <v>7.6</v>
+      </c>
+      <c r="AC25">
+        <v>14</v>
+      </c>
+      <c r="AD25">
+        <v>65</v>
+      </c>
+      <c r="AE25">
+        <v>420</v>
+      </c>
+      <c r="AF25">
+        <v>7</v>
+      </c>
+      <c r="AG25">
+        <v>11.5</v>
+      </c>
+      <c r="AH25">
+        <v>46</v>
+      </c>
+      <c r="AI25">
+        <v>300</v>
+      </c>
+      <c r="AJ25">
+        <v>9</v>
+      </c>
+      <c r="AK25">
+        <v>16.5</v>
+      </c>
+      <c r="AL25">
+        <v>55</v>
+      </c>
+      <c r="AM25">
+        <v>350</v>
+      </c>
+      <c r="AN25">
+        <v>5.6</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>16.5</v>
+      </c>
+      <c r="AQ25">
+        <v>30</v>
+      </c>
+      <c r="AR25">
+        <v>34</v>
+      </c>
+      <c r="AS25">
+        <v>13</v>
+      </c>
+      <c r="AT25">
+        <v>6.6</v>
+      </c>
+      <c r="AU25">
         <v>12</v>
       </c>
-      <c r="AC25">
-        <v>9.4</v>
-      </c>
-      <c r="AD25">
-        <v>20</v>
-      </c>
-      <c r="AE25">
-        <v>48</v>
-      </c>
-      <c r="AF25">
-        <v>15</v>
-      </c>
-      <c r="AG25">
-        <v>11</v>
-      </c>
-      <c r="AH25">
-        <v>19</v>
-      </c>
-      <c r="AI25">
-        <v>50</v>
-      </c>
-      <c r="AJ25">
-        <v>29</v>
-      </c>
-      <c r="AK25">
-        <v>21</v>
-      </c>
-      <c r="AL25">
-        <v>42</v>
-      </c>
-      <c r="AM25">
-        <v>200</v>
-      </c>
-      <c r="AN25">
-        <v>12</v>
-      </c>
-      <c r="AO25">
-        <v>40</v>
-      </c>
-      <c r="AP25">
-        <v>17</v>
-      </c>
-      <c r="AQ25">
-        <v>14.5</v>
-      </c>
-      <c r="AR25">
-        <v>23</v>
-      </c>
-      <c r="AS25">
-        <v>50</v>
-      </c>
-      <c r="AT25">
+      <c r="AV25">
+        <v>25</v>
+      </c>
+      <c r="AW25">
+        <v>13</v>
+      </c>
+      <c r="AX25">
+        <v>6</v>
+      </c>
+      <c r="AY25">
         <v>10</v>
       </c>
-      <c r="AU25">
+      <c r="AZ25">
+        <v>16.5</v>
+      </c>
+      <c r="BA25">
+        <v>12.5</v>
+      </c>
+      <c r="BB25">
         <v>8</v>
       </c>
-      <c r="AV25">
-        <v>13.5</v>
-      </c>
-      <c r="AW25">
-        <v>27</v>
-      </c>
-      <c r="AX25">
-        <v>13</v>
-      </c>
-      <c r="AY25">
-        <v>9.4</v>
-      </c>
-      <c r="AZ25">
+      <c r="BC25">
         <v>14</v>
-      </c>
-      <c r="BA25">
-        <v>29</v>
-      </c>
-      <c r="BB25">
-        <v>21</v>
-      </c>
-      <c r="BC25">
-        <v>17.5</v>
       </c>
       <c r="BD25">
         <v>22</v>
       </c>
       <c r="BE25">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BF25">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BG25">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BH25">
         <v>4.5</v>
       </c>
       <c r="BI25">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ25">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BK25">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL25">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="BM25">
-        <v>65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="BO25">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="BP25">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BQ25">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BR25">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS25">
+        <v>7.4</v>
+      </c>
+      <c r="BT25">
         <v>18</v>
       </c>
-      <c r="BT25">
-        <v>8.6</v>
-      </c>
       <c r="BU25">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV25">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="BW25">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BX25">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="BY25">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="BZ25">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CA25">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="CB25" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6853,483 +6841,241 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F26">
-        <v>1.31</v>
+        <v>2.34</v>
       </c>
       <c r="G26">
-        <v>1.34</v>
+        <v>2.48</v>
       </c>
       <c r="H26">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="I26">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="J26">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="L26">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="O26">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="R26">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="T26">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="U26">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="V26">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="X26">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="Y26">
-        <v>120</v>
+        <v>12.5</v>
       </c>
       <c r="Z26">
+        <v>25</v>
+      </c>
+      <c r="AA26">
+        <v>75</v>
+      </c>
+      <c r="AB26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC26">
+        <v>7.8</v>
+      </c>
+      <c r="AD26">
+        <v>15.5</v>
+      </c>
+      <c r="AE26">
+        <v>50</v>
+      </c>
+      <c r="AF26">
+        <v>16</v>
+      </c>
+      <c r="AG26">
+        <v>12</v>
+      </c>
+      <c r="AH26">
+        <v>19.5</v>
+      </c>
+      <c r="AI26">
+        <v>65</v>
+      </c>
+      <c r="AJ26">
+        <v>40</v>
+      </c>
+      <c r="AK26">
+        <v>32</v>
+      </c>
+      <c r="AL26">
+        <v>50</v>
+      </c>
+      <c r="AM26">
         <v>130</v>
       </c>
-      <c r="AA26">
-        <v>610</v>
-      </c>
-      <c r="AB26">
-        <v>8.6</v>
-      </c>
-      <c r="AC26">
-        <v>14</v>
-      </c>
-      <c r="AD26">
-        <v>130</v>
-      </c>
-      <c r="AE26">
-        <v>250</v>
-      </c>
-      <c r="AF26">
-        <v>8</v>
-      </c>
-      <c r="AG26">
-        <v>11</v>
-      </c>
-      <c r="AH26">
-        <v>70</v>
-      </c>
-      <c r="AI26">
-        <v>190</v>
-      </c>
-      <c r="AJ26">
-        <v>10.5</v>
-      </c>
-      <c r="AK26">
-        <v>16.5</v>
-      </c>
-      <c r="AL26">
-        <v>100</v>
-      </c>
-      <c r="AM26">
-        <v>220</v>
-      </c>
       <c r="AN26">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="AO26">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="AP26">
         <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR26">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AS26">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="AT26">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AV26">
+        <v>12.5</v>
+      </c>
+      <c r="AW26">
+        <v>34</v>
+      </c>
+      <c r="AX26">
+        <v>12.5</v>
+      </c>
+      <c r="AY26">
+        <v>10</v>
+      </c>
+      <c r="AZ26">
+        <v>16</v>
+      </c>
+      <c r="BA26">
+        <v>38</v>
+      </c>
+      <c r="BB26">
+        <v>24</v>
+      </c>
+      <c r="BC26">
+        <v>21</v>
+      </c>
+      <c r="BD26">
+        <v>30</v>
+      </c>
+      <c r="BE26">
+        <v>80</v>
+      </c>
+      <c r="BF26">
+        <v>17</v>
+      </c>
+      <c r="BG26">
+        <v>36</v>
+      </c>
+      <c r="BH26">
+        <v>3.55</v>
+      </c>
+      <c r="BI26">
+        <v>2.64</v>
+      </c>
+      <c r="BJ26">
         <v>10.5</v>
       </c>
-      <c r="AW26">
-        <v>11.5</v>
-      </c>
-      <c r="AX26">
+      <c r="BK26">
+        <v>7.8</v>
+      </c>
+      <c r="BL26">
+        <v>160</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>5.4</v>
+      </c>
+      <c r="BO26">
+        <v>4.5</v>
+      </c>
+      <c r="BP26">
+        <v>19</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>36</v>
+      </c>
+      <c r="BS26">
+        <v>1.02</v>
+      </c>
+      <c r="BT26">
         <v>6.8</v>
       </c>
-      <c r="AY26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ26">
-        <v>10</v>
-      </c>
-      <c r="BA26">
-        <v>11.5</v>
-      </c>
-      <c r="BB26">
-        <v>9</v>
-      </c>
-      <c r="BC26">
-        <v>13.5</v>
-      </c>
-      <c r="BD26">
-        <v>10.5</v>
-      </c>
-      <c r="BE26">
-        <v>11.5</v>
-      </c>
-      <c r="BF26">
-        <v>4.7</v>
-      </c>
-      <c r="BG26">
-        <v>13</v>
-      </c>
-      <c r="BH26">
-        <v>4.7</v>
-      </c>
-      <c r="BI26">
-        <v>3.15</v>
-      </c>
-      <c r="BJ26">
-        <v>15</v>
-      </c>
-      <c r="BK26">
-        <v>4.4</v>
-      </c>
-      <c r="BL26">
-        <v>210</v>
-      </c>
-      <c r="BM26">
-        <v>6</v>
-      </c>
-      <c r="BN26">
-        <v>3.7</v>
-      </c>
-      <c r="BO26">
-        <v>3.35</v>
-      </c>
-      <c r="BP26">
-        <v>9</v>
-      </c>
-      <c r="BQ26">
-        <v>5.7</v>
-      </c>
-      <c r="BR26">
+      <c r="BU26">
+        <v>5.6</v>
+      </c>
+      <c r="BV26">
         <v>30</v>
       </c>
-      <c r="BS26">
-        <v>5.2</v>
-      </c>
-      <c r="BT26">
-        <v>17.5</v>
-      </c>
-      <c r="BU26">
-        <v>4.6</v>
-      </c>
-      <c r="BV26">
-        <v>130</v>
-      </c>
       <c r="BW26">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="BX26">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="BY26">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="CA26">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="CB26" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:80">
-      <c r="A27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27">
-        <v>2.36</v>
-      </c>
-      <c r="G27">
-        <v>2.46</v>
-      </c>
-      <c r="H27">
-        <v>3.3</v>
-      </c>
-      <c r="I27">
-        <v>3.5</v>
-      </c>
-      <c r="J27">
-        <v>3.35</v>
-      </c>
-      <c r="K27">
-        <v>3.5</v>
-      </c>
-      <c r="L27">
-        <v>1.45</v>
-      </c>
-      <c r="M27">
-        <v>1.08</v>
-      </c>
-      <c r="N27">
-        <v>3.35</v>
-      </c>
-      <c r="O27">
-        <v>1.38</v>
-      </c>
-      <c r="P27">
-        <v>1.79</v>
-      </c>
-      <c r="Q27">
-        <v>2.16</v>
-      </c>
-      <c r="R27">
-        <v>1.3</v>
-      </c>
-      <c r="S27">
-        <v>4</v>
-      </c>
-      <c r="T27">
-        <v>1.85</v>
-      </c>
-      <c r="U27">
-        <v>2.04</v>
-      </c>
-      <c r="V27">
-        <v>1.4</v>
-      </c>
-      <c r="W27">
-        <v>1.68</v>
-      </c>
-      <c r="X27">
-        <v>14</v>
-      </c>
-      <c r="Y27">
-        <v>12.5</v>
-      </c>
-      <c r="Z27">
-        <v>27</v>
-      </c>
-      <c r="AA27">
-        <v>75</v>
-      </c>
-      <c r="AB27">
-        <v>11</v>
-      </c>
-      <c r="AC27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD27">
-        <v>17</v>
-      </c>
-      <c r="AE27">
-        <v>50</v>
-      </c>
-      <c r="AF27">
-        <v>17</v>
-      </c>
-      <c r="AG27">
-        <v>13.5</v>
-      </c>
-      <c r="AH27">
-        <v>22</v>
-      </c>
-      <c r="AI27">
-        <v>65</v>
-      </c>
-      <c r="AJ27">
-        <v>38</v>
-      </c>
-      <c r="AK27">
-        <v>32</v>
-      </c>
-      <c r="AL27">
-        <v>50</v>
-      </c>
-      <c r="AM27">
-        <v>500</v>
-      </c>
-      <c r="AN27">
-        <v>26</v>
-      </c>
-      <c r="AO27">
-        <v>55</v>
-      </c>
-      <c r="AP27">
-        <v>10.5</v>
-      </c>
-      <c r="AQ27">
-        <v>10.5</v>
-      </c>
-      <c r="AR27">
-        <v>20</v>
-      </c>
-      <c r="AS27">
-        <v>5.1</v>
-      </c>
-      <c r="AT27">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU27">
-        <v>6.8</v>
-      </c>
-      <c r="AV27">
-        <v>12.5</v>
-      </c>
-      <c r="AW27">
-        <v>34</v>
-      </c>
-      <c r="AX27">
-        <v>12.5</v>
-      </c>
-      <c r="AY27">
-        <v>10</v>
-      </c>
-      <c r="AZ27">
-        <v>16</v>
-      </c>
-      <c r="BA27">
-        <v>5.1</v>
-      </c>
-      <c r="BB27">
-        <v>5.3</v>
-      </c>
-      <c r="BC27">
-        <v>5.6</v>
-      </c>
-      <c r="BD27">
-        <v>34</v>
-      </c>
-      <c r="BE27">
-        <v>5.3</v>
-      </c>
-      <c r="BF27">
-        <v>19</v>
-      </c>
-      <c r="BG27">
-        <v>5.6</v>
-      </c>
-      <c r="BH27">
-        <v>3.55</v>
-      </c>
-      <c r="BI27">
-        <v>2.64</v>
-      </c>
-      <c r="BJ27">
-        <v>11.5</v>
-      </c>
-      <c r="BK27">
-        <v>1.01</v>
-      </c>
-      <c r="BL27">
-        <v>160</v>
-      </c>
-      <c r="BM27">
-        <v>1.01</v>
-      </c>
-      <c r="BN27">
-        <v>5.9</v>
-      </c>
-      <c r="BO27">
-        <v>4.5</v>
-      </c>
-      <c r="BP27">
-        <v>21</v>
-      </c>
-      <c r="BQ27">
-        <v>1.01</v>
-      </c>
-      <c r="BR27">
-        <v>40</v>
-      </c>
-      <c r="BS27">
-        <v>1.02</v>
-      </c>
-      <c r="BT27">
-        <v>6.8</v>
-      </c>
-      <c r="BU27">
-        <v>5.1</v>
-      </c>
-      <c r="BV27">
-        <v>34</v>
-      </c>
-      <c r="BW27">
-        <v>1.02</v>
-      </c>
-      <c r="BX27">
-        <v>50</v>
-      </c>
-      <c r="BY27">
-        <v>1.01</v>
-      </c>
-      <c r="BZ27">
-        <v>36</v>
-      </c>
-      <c r="CA27">
-        <v>1.02</v>
-      </c>
-      <c r="CB27" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -319,12 +319,12 @@
     <t>Luxembourg</t>
   </si>
   <si>
+    <t>San Marino</t>
+  </si>
+  <si>
     <t>Spain</t>
   </si>
   <si>
-    <t>San Marino</t>
-  </si>
-  <si>
     <t>Czechia</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Iceland</t>
   </si>
   <si>
+    <t>Albania</t>
+  </si>
+  <si>
     <t>Croatia</t>
   </si>
   <si>
-    <t>Albania</t>
-  </si>
-  <si>
     <t>England</t>
   </si>
   <si>
@@ -451,7 +451,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 10:10:53</t>
+    <t>2026-09-29 12:22:20</t>
   </si>
 </sst>
 </file>
@@ -1045,40 +1045,40 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
         <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
         <v>1.27</v>
@@ -1087,184 +1087,184 @@
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>22</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP2">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2">
+        <v>10.5</v>
+      </c>
+      <c r="AR2">
+        <v>19.5</v>
+      </c>
+      <c r="AS2">
+        <v>50</v>
+      </c>
+      <c r="AT2">
+        <v>7.8</v>
+      </c>
+      <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
+        <v>42</v>
+      </c>
+      <c r="AX2">
+        <v>12</v>
+      </c>
+      <c r="AY2">
         <v>10</v>
       </c>
-      <c r="AQ2">
-        <v>9.4</v>
-      </c>
-      <c r="AR2">
-        <v>18</v>
-      </c>
-      <c r="AS2">
-        <v>44</v>
-      </c>
-      <c r="AT2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>11.5</v>
-      </c>
-      <c r="AW2">
-        <v>34</v>
-      </c>
-      <c r="AX2">
-        <v>13.5</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BD2">
         <v>38</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR2">
         <v>42</v>
       </c>
       <c r="BS2">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA2">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>145</v>
@@ -1287,172 +1287,172 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="G3">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P3">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AB3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>130</v>
       </c>
       <c r="AJ3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AR3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
         <v>27</v>
       </c>
       <c r="AW3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="BH3">
+        <v>3.4</v>
+      </c>
+      <c r="BI3">
         <v>3.2</v>
-      </c>
-      <c r="BI3">
-        <v>2.98</v>
       </c>
       <c r="BJ3">
         <v>12</v>
@@ -1461,52 +1461,52 @@
         <v>10.5</v>
       </c>
       <c r="BL3">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="BM3">
-        <v>150</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO3">
         <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BT3">
         <v>11</v>
       </c>
       <c r="BU3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV3">
+        <v>90</v>
+      </c>
+      <c r="BW3">
+        <v>13.5</v>
+      </c>
+      <c r="BX3">
         <v>95</v>
       </c>
-      <c r="BW3">
-        <v>12</v>
-      </c>
-      <c r="BX3">
-        <v>100</v>
-      </c>
       <c r="BY3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BZ3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,73 +1529,73 @@
         <v>122</v>
       </c>
       <c r="F4">
+        <v>3.3</v>
+      </c>
+      <c r="G4">
+        <v>3.35</v>
+      </c>
+      <c r="H4">
+        <v>2.74</v>
+      </c>
+      <c r="I4">
+        <v>2.76</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
         <v>3.05</v>
       </c>
-      <c r="G4">
-        <v>3.1</v>
-      </c>
-      <c r="H4">
-        <v>2.84</v>
-      </c>
-      <c r="I4">
-        <v>2.88</v>
-      </c>
-      <c r="J4">
-        <v>3.05</v>
-      </c>
-      <c r="K4">
-        <v>3.1</v>
-      </c>
       <c r="L4">
+        <v>1.68</v>
+      </c>
+      <c r="M4">
+        <v>1.15</v>
+      </c>
+      <c r="N4">
+        <v>2.5</v>
+      </c>
+      <c r="O4">
         <v>1.64</v>
       </c>
-      <c r="M4">
-        <v>1.13</v>
-      </c>
-      <c r="N4">
-        <v>2.7</v>
-      </c>
-      <c r="O4">
+      <c r="P4">
+        <v>1.48</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>1.17</v>
+      </c>
+      <c r="S4">
+        <v>6.6</v>
+      </c>
+      <c r="T4">
+        <v>2.3</v>
+      </c>
+      <c r="U4">
+        <v>1.73</v>
+      </c>
+      <c r="V4">
         <v>1.57</v>
       </c>
-      <c r="P4">
-        <v>1.54</v>
-      </c>
-      <c r="Q4">
-        <v>2.8</v>
-      </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
-      <c r="S4">
-        <v>5.8</v>
-      </c>
-      <c r="T4">
-        <v>2.16</v>
-      </c>
-      <c r="U4">
-        <v>1.84</v>
-      </c>
-      <c r="V4">
-        <v>1.53</v>
-      </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA4">
         <v>48</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
         <v>6.8</v>
@@ -1604,151 +1604,151 @@
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AK4">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO4">
         <v>55</v>
       </c>
       <c r="AP4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>14</v>
+      </c>
+      <c r="AS4">
+        <v>44</v>
+      </c>
+      <c r="AT4">
         <v>8</v>
-      </c>
-      <c r="AR4">
-        <v>15</v>
-      </c>
-      <c r="AS4">
-        <v>42</v>
-      </c>
-      <c r="AT4">
-        <v>8.4</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB4">
+        <v>60</v>
+      </c>
+      <c r="BC4">
         <v>50</v>
       </c>
-      <c r="BC4">
-        <v>42</v>
-      </c>
       <c r="BD4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BE4">
         <v>160</v>
       </c>
       <c r="BF4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BG4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH4">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="BI4">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="BM4">
         <v>200</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
+        <v>5.6</v>
+      </c>
+      <c r="BP4">
+        <v>40</v>
+      </c>
+      <c r="BQ4">
+        <v>18.5</v>
+      </c>
+      <c r="BR4">
+        <v>70</v>
+      </c>
+      <c r="BS4">
+        <v>13.5</v>
+      </c>
+      <c r="BT4">
         <v>5.3</v>
       </c>
-      <c r="BP4">
-        <v>34</v>
-      </c>
-      <c r="BQ4">
-        <v>10.5</v>
-      </c>
-      <c r="BR4">
-        <v>55</v>
-      </c>
-      <c r="BS4">
-        <v>11.5</v>
-      </c>
-      <c r="BT4">
-        <v>5.6</v>
-      </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
         <v>145</v>
@@ -1771,79 +1771,79 @@
         <v>123</v>
       </c>
       <c r="F5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G5">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H5">
         <v>8.6</v>
       </c>
       <c r="I5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y5">
         <v>38</v>
       </c>
       <c r="Z5">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA5">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5">
         <v>120</v>
@@ -1870,43 +1870,43 @@
         <v>30</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>790</v>
       </c>
       <c r="AN5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AO5">
         <v>180</v>
       </c>
       <c r="AP5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AS5">
         <v>15</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW5">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AX5">
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>20</v>
@@ -1915,7 +1915,7 @@
         <v>70</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC5">
         <v>12.5</v>
@@ -1924,19 +1924,19 @@
         <v>25</v>
       </c>
       <c r="BE5">
+        <v>75</v>
+      </c>
+      <c r="BF5">
+        <v>5</v>
+      </c>
+      <c r="BG5">
         <v>70</v>
       </c>
-      <c r="BF5">
-        <v>4.7</v>
-      </c>
-      <c r="BG5">
-        <v>16</v>
-      </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -1948,25 +1948,25 @@
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
         <v>8.4</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT5">
         <v>12.5</v>
@@ -1978,19 +1978,19 @@
         <v>65</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <v>60</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
         <v>145</v>
@@ -2013,16 +2013,16 @@
         <v>124</v>
       </c>
       <c r="F6">
+        <v>1.65</v>
+      </c>
+      <c r="G6">
         <v>1.67</v>
       </c>
-      <c r="G6">
-        <v>1.68</v>
-      </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>3.8</v>
@@ -2037,7 +2037,7 @@
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O6">
         <v>1.49</v>
@@ -2055,25 +2055,25 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>280</v>
@@ -2082,46 +2082,46 @@
         <v>6.2</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG6">
         <v>11</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK6">
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>290</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO6">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AP6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6">
         <v>15.5</v>
@@ -2136,28 +2136,28 @@
         <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AX6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BB6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
         <v>20</v>
@@ -2166,13 +2166,13 @@
         <v>50</v>
       </c>
       <c r="BE6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG6">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="BH6">
         <v>2.82</v>
@@ -2187,7 +2187,7 @@
         <v>11</v>
       </c>
       <c r="BL6">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="BM6">
         <v>75</v>
@@ -2196,13 +2196,13 @@
         <v>3.85</v>
       </c>
       <c r="BO6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR6">
         <v>38</v>
@@ -2211,28 +2211,28 @@
         <v>13</v>
       </c>
       <c r="BT6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BV6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BW6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BX6">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BY6">
         <v>16</v>
       </c>
       <c r="BZ6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="s">
         <v>145</v>
@@ -2255,25 +2255,25 @@
         <v>125</v>
       </c>
       <c r="F7">
+        <v>3.3</v>
+      </c>
+      <c r="G7">
+        <v>3.35</v>
+      </c>
+      <c r="H7">
+        <v>2.44</v>
+      </c>
+      <c r="I7">
+        <v>2.48</v>
+      </c>
+      <c r="J7">
         <v>3.4</v>
       </c>
-      <c r="G7">
+      <c r="K7">
         <v>3.45</v>
       </c>
-      <c r="H7">
-        <v>2.42</v>
-      </c>
-      <c r="I7">
-        <v>2.44</v>
-      </c>
-      <c r="J7">
-        <v>3.35</v>
-      </c>
-      <c r="K7">
-        <v>3.4</v>
-      </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2282,10 +2282,10 @@
         <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
         <v>2.3</v>
@@ -2297,25 +2297,25 @@
         <v>4.4</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U7">
         <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA7">
         <v>34</v>
@@ -2330,19 +2330,19 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF7">
         <v>22</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH7">
         <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
         <v>65</v>
@@ -2354,19 +2354,19 @@
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR7">
         <v>13</v>
@@ -2378,19 +2378,19 @@
         <v>10</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
         <v>18.5</v>
@@ -2402,7 +2402,7 @@
         <v>55</v>
       </c>
       <c r="BC7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BD7">
         <v>50</v>
@@ -2417,25 +2417,25 @@
         <v>25</v>
       </c>
       <c r="BH7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL7">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM7">
         <v>120</v>
       </c>
       <c r="BN7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO7">
         <v>5.7</v>
@@ -2444,31 +2444,31 @@
         <v>29</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU7">
         <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>42</v>
@@ -2497,226 +2497,226 @@
         <v>126</v>
       </c>
       <c r="F8">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>1.06</v>
+      </c>
+      <c r="I8">
+        <v>1.07</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
+        <v>23</v>
+      </c>
+      <c r="L8">
         <v>1.22</v>
       </c>
-      <c r="G8">
-        <v>1.23</v>
-      </c>
-      <c r="H8">
-        <v>16.5</v>
-      </c>
-      <c r="I8">
-        <v>17</v>
-      </c>
-      <c r="J8">
+      <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
         <v>8</v>
       </c>
-      <c r="K8">
+      <c r="O8">
+        <v>1.13</v>
+      </c>
+      <c r="P8">
+        <v>3.25</v>
+      </c>
+      <c r="Q8">
+        <v>1.42</v>
+      </c>
+      <c r="R8">
+        <v>1.87</v>
+      </c>
+      <c r="S8">
+        <v>2.1</v>
+      </c>
+      <c r="T8">
+        <v>4.7</v>
+      </c>
+      <c r="U8">
+        <v>1.26</v>
+      </c>
+      <c r="V8">
+        <v>15.5</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>55</v>
+      </c>
+      <c r="Y8">
+        <v>11</v>
+      </c>
+      <c r="Z8">
+        <v>6.2</v>
+      </c>
+      <c r="AA8">
+        <v>5.6</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>70</v>
+      </c>
+      <c r="AD8">
+        <v>25</v>
+      </c>
+      <c r="AE8">
+        <v>23</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>190</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>2.42</v>
+      </c>
+      <c r="AP8">
+        <v>44</v>
+      </c>
+      <c r="AQ8">
+        <v>10</v>
+      </c>
+      <c r="AR8">
+        <v>5.9</v>
+      </c>
+      <c r="AS8">
+        <v>5.4</v>
+      </c>
+      <c r="AT8">
+        <v>60</v>
+      </c>
+      <c r="AU8">
+        <v>50</v>
+      </c>
+      <c r="AV8">
+        <v>22</v>
+      </c>
+      <c r="AW8">
+        <v>21</v>
+      </c>
+      <c r="AX8">
+        <v>140</v>
+      </c>
+      <c r="AY8">
+        <v>90</v>
+      </c>
+      <c r="AZ8">
+        <v>26</v>
+      </c>
+      <c r="BA8">
+        <v>28</v>
+      </c>
+      <c r="BB8">
+        <v>600</v>
+      </c>
+      <c r="BC8">
+        <v>95</v>
+      </c>
+      <c r="BD8">
+        <v>95</v>
+      </c>
+      <c r="BE8">
+        <v>270</v>
+      </c>
+      <c r="BF8">
+        <v>38</v>
+      </c>
+      <c r="BG8">
+        <v>2.4</v>
+      </c>
+      <c r="BH8">
+        <v>6.4</v>
+      </c>
+      <c r="BI8">
+        <v>5</v>
+      </c>
+      <c r="BJ8">
+        <v>42</v>
+      </c>
+      <c r="BK8">
+        <v>7.8</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>350</v>
+      </c>
+      <c r="BN8">
+        <v>75</v>
+      </c>
+      <c r="BO8">
+        <v>8.4</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>9.6</v>
+      </c>
+      <c r="BR8">
+        <v>990</v>
+      </c>
+      <c r="BS8">
+        <v>9.4</v>
+      </c>
+      <c r="BT8">
+        <v>3.4</v>
+      </c>
+      <c r="BU8">
+        <v>3.1</v>
+      </c>
+      <c r="BV8">
+        <v>4.4</v>
+      </c>
+      <c r="BW8">
+        <v>4</v>
+      </c>
+      <c r="BX8">
+        <v>55</v>
+      </c>
+      <c r="BY8">
         <v>8.199999999999999</v>
       </c>
-      <c r="L8">
-        <v>1.27</v>
-      </c>
-      <c r="M8">
-        <v>1.03</v>
-      </c>
-      <c r="N8">
-        <v>7</v>
-      </c>
-      <c r="O8">
-        <v>1.16</v>
-      </c>
-      <c r="P8">
-        <v>3.05</v>
-      </c>
-      <c r="Q8">
-        <v>1.48</v>
-      </c>
-      <c r="R8">
-        <v>1.8</v>
-      </c>
-      <c r="S8">
-        <v>2.2</v>
-      </c>
-      <c r="T8">
-        <v>2.1</v>
-      </c>
-      <c r="U8">
-        <v>1.89</v>
-      </c>
-      <c r="V8">
-        <v>1.06</v>
-      </c>
-      <c r="W8">
-        <v>5.3</v>
-      </c>
-      <c r="X8">
-        <v>34</v>
-      </c>
-      <c r="Y8">
-        <v>60</v>
-      </c>
-      <c r="Z8">
-        <v>200</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>11.5</v>
-      </c>
-      <c r="AC8">
-        <v>17.5</v>
-      </c>
-      <c r="AD8">
-        <v>55</v>
-      </c>
-      <c r="AE8">
-        <v>310</v>
-      </c>
-      <c r="AF8">
-        <v>8.6</v>
-      </c>
-      <c r="AG8">
-        <v>12</v>
-      </c>
-      <c r="AH8">
-        <v>36</v>
-      </c>
-      <c r="AI8">
-        <v>170</v>
-      </c>
-      <c r="AJ8">
-        <v>9.4</v>
-      </c>
-      <c r="AK8">
-        <v>13</v>
-      </c>
-      <c r="AL8">
-        <v>36</v>
-      </c>
-      <c r="AM8">
-        <v>170</v>
-      </c>
-      <c r="AN8">
-        <v>3.5</v>
-      </c>
-      <c r="AO8">
-        <v>390</v>
-      </c>
-      <c r="AP8">
-        <v>30</v>
-      </c>
-      <c r="AQ8">
-        <v>48</v>
-      </c>
-      <c r="AR8">
-        <v>120</v>
-      </c>
-      <c r="AS8">
-        <v>26</v>
-      </c>
-      <c r="AT8">
-        <v>10.5</v>
-      </c>
-      <c r="AU8">
-        <v>16.5</v>
-      </c>
-      <c r="AV8">
-        <v>44</v>
-      </c>
-      <c r="AW8">
-        <v>22</v>
-      </c>
-      <c r="AX8">
-        <v>7.8</v>
-      </c>
-      <c r="AY8">
-        <v>11</v>
-      </c>
-      <c r="AZ8">
-        <v>32</v>
-      </c>
-      <c r="BA8">
-        <v>23</v>
-      </c>
-      <c r="BB8">
-        <v>9</v>
-      </c>
-      <c r="BC8">
-        <v>12</v>
-      </c>
-      <c r="BD8">
-        <v>30</v>
-      </c>
-      <c r="BE8">
-        <v>110</v>
-      </c>
-      <c r="BF8">
-        <v>3.35</v>
-      </c>
-      <c r="BG8">
-        <v>85</v>
-      </c>
-      <c r="BH8">
-        <v>4.8</v>
-      </c>
-      <c r="BI8">
-        <v>4.5</v>
-      </c>
-      <c r="BJ8">
-        <v>12.5</v>
-      </c>
-      <c r="BK8">
-        <v>11</v>
-      </c>
-      <c r="BL8">
-        <v>180</v>
-      </c>
-      <c r="BM8">
-        <v>19.5</v>
-      </c>
-      <c r="BN8">
-        <v>3.9</v>
-      </c>
-      <c r="BO8">
-        <v>3.65</v>
-      </c>
-      <c r="BP8">
-        <v>6.4</v>
-      </c>
-      <c r="BQ8">
-        <v>5.9</v>
-      </c>
-      <c r="BR8">
-        <v>21</v>
-      </c>
-      <c r="BS8">
-        <v>18</v>
-      </c>
-      <c r="BT8">
-        <v>16</v>
-      </c>
-      <c r="BU8">
-        <v>14</v>
-      </c>
-      <c r="BV8">
-        <v>130</v>
-      </c>
-      <c r="BW8">
-        <v>20</v>
-      </c>
-      <c r="BX8">
-        <v>110</v>
-      </c>
-      <c r="BY8">
-        <v>19.5</v>
-      </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="s">
         <v>145</v>
@@ -2739,226 +2739,226 @@
         <v>127</v>
       </c>
       <c r="F9">
+        <v>1.22</v>
+      </c>
+      <c r="G9">
+        <v>1.23</v>
+      </c>
+      <c r="H9">
+        <v>15.5</v>
+      </c>
+      <c r="I9">
+        <v>16</v>
+      </c>
+      <c r="J9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K9">
+        <v>8.4</v>
+      </c>
+      <c r="L9">
+        <v>1.25</v>
+      </c>
+      <c r="M9">
+        <v>1.03</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9">
+        <v>1.15</v>
+      </c>
+      <c r="P9">
+        <v>3.05</v>
+      </c>
+      <c r="Q9">
+        <v>1.47</v>
+      </c>
+      <c r="R9">
+        <v>1.82</v>
+      </c>
+      <c r="S9">
+        <v>2.2</v>
+      </c>
+      <c r="T9">
+        <v>2.06</v>
+      </c>
+      <c r="U9">
+        <v>1.91</v>
+      </c>
+      <c r="V9">
+        <v>1.06</v>
+      </c>
+      <c r="W9">
+        <v>5.3</v>
+      </c>
+      <c r="X9">
+        <v>34</v>
+      </c>
+      <c r="Y9">
         <v>55</v>
       </c>
-      <c r="G9">
-        <v>60</v>
-      </c>
-      <c r="H9">
-        <v>1.06</v>
-      </c>
-      <c r="I9">
-        <v>1.07</v>
-      </c>
-      <c r="J9">
+      <c r="Z9">
+        <v>160</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>11</v>
+      </c>
+      <c r="AC9">
+        <v>18.5</v>
+      </c>
+      <c r="AD9">
+        <v>50</v>
+      </c>
+      <c r="AE9">
+        <v>280</v>
+      </c>
+      <c r="AF9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG9">
+        <v>12</v>
+      </c>
+      <c r="AH9">
+        <v>34</v>
+      </c>
+      <c r="AI9">
+        <v>170</v>
+      </c>
+      <c r="AJ9">
+        <v>9.4</v>
+      </c>
+      <c r="AK9">
+        <v>13</v>
+      </c>
+      <c r="AL9">
+        <v>34</v>
+      </c>
+      <c r="AM9">
+        <v>150</v>
+      </c>
+      <c r="AN9">
+        <v>3.45</v>
+      </c>
+      <c r="AO9">
+        <v>390</v>
+      </c>
+      <c r="AP9">
+        <v>32</v>
+      </c>
+      <c r="AQ9">
+        <v>50</v>
+      </c>
+      <c r="AR9">
+        <v>120</v>
+      </c>
+      <c r="AS9">
+        <v>48</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>17.5</v>
+      </c>
+      <c r="AV9">
+        <v>44</v>
+      </c>
+      <c r="AW9">
+        <v>32</v>
+      </c>
+      <c r="AX9">
+        <v>8</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>32</v>
+      </c>
+      <c r="BA9">
+        <v>95</v>
+      </c>
+      <c r="BB9">
+        <v>9</v>
+      </c>
+      <c r="BC9">
+        <v>12</v>
+      </c>
+      <c r="BD9">
+        <v>32</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>3.35</v>
+      </c>
+      <c r="BG9">
+        <v>38</v>
+      </c>
+      <c r="BH9">
+        <v>4.9</v>
+      </c>
+      <c r="BI9">
+        <v>4.5</v>
+      </c>
+      <c r="BJ9">
+        <v>12.5</v>
+      </c>
+      <c r="BK9">
+        <v>11</v>
+      </c>
+      <c r="BL9">
+        <v>170</v>
+      </c>
+      <c r="BM9">
+        <v>17</v>
+      </c>
+      <c r="BN9">
+        <v>4</v>
+      </c>
+      <c r="BO9">
+        <v>3.65</v>
+      </c>
+      <c r="BP9">
+        <v>6.2</v>
+      </c>
+      <c r="BQ9">
+        <v>5.8</v>
+      </c>
+      <c r="BR9">
         <v>21</v>
       </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>1.23</v>
-      </c>
-      <c r="M9">
-        <v>1.02</v>
-      </c>
-      <c r="N9">
-        <v>7.6</v>
-      </c>
-      <c r="O9">
-        <v>1.14</v>
-      </c>
-      <c r="P9">
-        <v>3.15</v>
-      </c>
-      <c r="Q9">
-        <v>1.45</v>
-      </c>
-      <c r="R9">
-        <v>1.84</v>
-      </c>
-      <c r="S9">
-        <v>2.16</v>
-      </c>
-      <c r="T9">
-        <v>4.7</v>
-      </c>
-      <c r="U9">
-        <v>1.25</v>
-      </c>
-      <c r="V9">
-        <v>15</v>
-      </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>70</v>
-      </c>
-      <c r="Y9">
-        <v>11</v>
-      </c>
-      <c r="Z9">
-        <v>6.4</v>
-      </c>
-      <c r="AA9">
-        <v>5.5</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>60</v>
-      </c>
-      <c r="AD9">
-        <v>25</v>
-      </c>
-      <c r="AE9">
-        <v>24</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>330</v>
-      </c>
-      <c r="AI9">
-        <v>190</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>2.46</v>
-      </c>
-      <c r="AP9">
-        <v>42</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
-      </c>
-      <c r="AR9">
-        <v>6</v>
-      </c>
-      <c r="AS9">
-        <v>5.3</v>
-      </c>
-      <c r="AT9">
-        <v>29</v>
-      </c>
-      <c r="AU9">
-        <v>48</v>
-      </c>
-      <c r="AV9">
-        <v>22</v>
-      </c>
-      <c r="AW9">
-        <v>21</v>
-      </c>
-      <c r="AX9">
-        <v>140</v>
-      </c>
-      <c r="AY9">
-        <v>50</v>
-      </c>
-      <c r="AZ9">
-        <v>23</v>
-      </c>
-      <c r="BA9">
-        <v>27</v>
-      </c>
-      <c r="BB9">
-        <v>600</v>
-      </c>
-      <c r="BC9">
-        <v>90</v>
-      </c>
-      <c r="BD9">
-        <v>95</v>
-      </c>
-      <c r="BE9">
-        <v>270</v>
-      </c>
-      <c r="BF9">
-        <v>34</v>
-      </c>
-      <c r="BG9">
-        <v>2.42</v>
-      </c>
-      <c r="BH9">
-        <v>6.2</v>
-      </c>
-      <c r="BI9">
-        <v>4.8</v>
-      </c>
-      <c r="BJ9">
-        <v>36</v>
-      </c>
-      <c r="BK9">
-        <v>9</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>12</v>
-      </c>
-      <c r="BN9">
-        <v>60</v>
-      </c>
-      <c r="BO9">
-        <v>10</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>12</v>
-      </c>
-      <c r="BR9">
-        <v>920</v>
-      </c>
       <c r="BS9">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT9">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="BU9">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="BV9">
-        <v>4.6</v>
+        <v>130</v>
       </c>
       <c r="BW9">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="BY9">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="BZ9">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
         <v>145</v>
@@ -2981,64 +2981,64 @@
         <v>128</v>
       </c>
       <c r="F10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="I10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R10">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S10">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z10">
         <v>7.8</v>
@@ -3047,34 +3047,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AB10">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD10">
         <v>10.5</v>
       </c>
       <c r="AE10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF10">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AG10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH10">
         <v>28</v>
       </c>
       <c r="AI10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ10">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AL10">
         <v>140</v>
@@ -3083,16 +3083,16 @@
         <v>150</v>
       </c>
       <c r="AN10">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AO10">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AP10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AQ10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10">
         <v>7.6</v>
@@ -3101,31 +3101,31 @@
         <v>9.6</v>
       </c>
       <c r="AT10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV10">
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX10">
         <v>100</v>
       </c>
       <c r="AY10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AZ10">
         <v>27</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB10">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="BC10">
         <v>160</v>
@@ -3140,13 +3140,13 @@
         <v>240</v>
       </c>
       <c r="BG10">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BJ10">
         <v>12</v>
@@ -3155,13 +3155,13 @@
         <v>11</v>
       </c>
       <c r="BL10">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="BM10">
         <v>140</v>
       </c>
       <c r="BN10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BO10">
         <v>12.5</v>
@@ -3170,37 +3170,37 @@
         <v>110</v>
       </c>
       <c r="BQ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BR10">
         <v>95</v>
       </c>
       <c r="BS10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BU10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV10">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BW10">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX10">
         <v>26</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB10" t="s">
         <v>145</v>
@@ -3223,46 +3223,46 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G11">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I11">
         <v>16</v>
       </c>
       <c r="J11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R11">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T11">
         <v>2.48</v>
@@ -3274,25 +3274,25 @@
         <v>1.06</v>
       </c>
       <c r="W11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z11">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD11">
         <v>60</v>
@@ -3307,43 +3307,43 @@
         <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI11">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ11">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AK11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>300</v>
       </c>
       <c r="AN11">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AO11">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
         <v>34</v>
       </c>
       <c r="AR11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AS11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
         <v>13.5</v>
@@ -3352,7 +3352,7 @@
         <v>50</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AX11">
         <v>6.4</v>
@@ -3367,46 +3367,46 @@
         <v>38</v>
       </c>
       <c r="BB11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE11">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="BF11">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG11">
         <v>23</v>
       </c>
       <c r="BH11">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL11">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="BM11">
         <v>75</v>
       </c>
       <c r="BN11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BO11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP11">
         <v>7</v>
@@ -3415,34 +3415,34 @@
         <v>6.2</v>
       </c>
       <c r="BR11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS11">
         <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BU11">
         <v>14</v>
       </c>
       <c r="BV11">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BW11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BY11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CA11">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
         <v>145</v>
@@ -3465,28 +3465,28 @@
         <v>130</v>
       </c>
       <c r="F12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G12">
         <v>1.85</v>
       </c>
       <c r="H12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
+        <v>3.55</v>
+      </c>
+      <c r="K12">
         <v>3.6</v>
       </c>
-      <c r="K12">
-        <v>3.65</v>
-      </c>
       <c r="L12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -3495,10 +3495,10 @@
         <v>1.48</v>
       </c>
       <c r="P12">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
         <v>1.24</v>
@@ -3507,10 +3507,10 @@
         <v>4.9</v>
       </c>
       <c r="T12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V12">
         <v>1.21</v>
@@ -3522,7 +3522,7 @@
         <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z12">
         <v>38</v>
@@ -3555,7 +3555,7 @@
         <v>110</v>
       </c>
       <c r="AJ12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK12">
         <v>23</v>
@@ -3573,16 +3573,16 @@
         <v>150</v>
       </c>
       <c r="AP12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR12">
         <v>36</v>
       </c>
       <c r="AS12">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT12">
         <v>6.4</v>
@@ -3591,10 +3591,10 @@
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AX12">
         <v>9</v>
@@ -3606,7 +3606,7 @@
         <v>24</v>
       </c>
       <c r="BA12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB12">
         <v>18</v>
@@ -3627,16 +3627,16 @@
         <v>100</v>
       </c>
       <c r="BH12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI12">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK12">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BL12">
         <v>230</v>
@@ -3651,13 +3651,13 @@
         <v>3.8</v>
       </c>
       <c r="BP12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS12">
         <v>11</v>
@@ -3666,13 +3666,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV12">
         <v>70</v>
       </c>
       <c r="BW12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX12">
         <v>85</v>
@@ -3681,10 +3681,10 @@
         <v>13.5</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
         <v>145</v>
@@ -3707,25 +3707,25 @@
         <v>131</v>
       </c>
       <c r="F13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H13">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="I13">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M13">
         <v>1.09</v>
@@ -3734,31 +3734,31 @@
         <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
         <v>1.28</v>
       </c>
       <c r="S13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U13">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X13">
         <v>11.5</v>
@@ -3776,13 +3776,13 @@
         <v>13.5</v>
       </c>
       <c r="AC13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF13">
         <v>34</v>
@@ -3809,10 +3809,10 @@
         <v>140</v>
       </c>
       <c r="AN13">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP13">
         <v>10.5</v>
@@ -3830,13 +3830,13 @@
         <v>13</v>
       </c>
       <c r="AU13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV13">
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13">
         <v>30</v>
@@ -3845,10 +3845,10 @@
         <v>17.5</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB13">
         <v>100</v>
@@ -3863,16 +3863,16 @@
         <v>120</v>
       </c>
       <c r="BF13">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BG13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI13">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ13">
         <v>11.5</v>
@@ -3881,10 +3881,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL13">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM13">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="BN13">
         <v>8</v>
@@ -3893,19 +3893,19 @@
         <v>7.2</v>
       </c>
       <c r="BP13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR13">
         <v>75</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU13">
         <v>4</v>
@@ -3914,19 +3914,19 @@
         <v>14</v>
       </c>
       <c r="BW13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX13">
         <v>40</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13">
         <v>38</v>
       </c>
       <c r="CA13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="s">
         <v>145</v>
@@ -3949,7 +3949,7 @@
         <v>132</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G14">
         <v>5.2</v>
@@ -3961,10 +3961,10 @@
         <v>1.7</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L14">
         <v>1.32</v>
@@ -3982,19 +3982,19 @@
         <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R14">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V14">
         <v>2.42</v>
@@ -4003,7 +4003,7 @@
         <v>1.23</v>
       </c>
       <c r="X14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y14">
         <v>11</v>
@@ -4015,7 +4015,7 @@
         <v>17.5</v>
       </c>
       <c r="AB14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
@@ -4030,10 +4030,10 @@
         <v>48</v>
       </c>
       <c r="AG14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI14">
         <v>28</v>
@@ -4048,7 +4048,7 @@
         <v>60</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN14">
         <v>55</v>
@@ -4108,7 +4108,7 @@
         <v>42</v>
       </c>
       <c r="BG14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH14">
         <v>4.9</v>
@@ -4126,7 +4126,7 @@
         <v>120</v>
       </c>
       <c r="BM14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BN14">
         <v>9.199999999999999</v>
@@ -4138,25 +4138,25 @@
         <v>42</v>
       </c>
       <c r="BQ14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
         <v>55</v>
       </c>
       <c r="BS14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU14">
         <v>4.1</v>
       </c>
       <c r="BV14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW14">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX14">
         <v>23</v>
@@ -4191,28 +4191,28 @@
         <v>133</v>
       </c>
       <c r="F15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G15">
         <v>3.9</v>
       </c>
       <c r="H15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J15">
         <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.35</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
         <v>4.7</v>
@@ -4239,7 +4239,7 @@
         <v>2.38</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W15">
         <v>1.34</v>
@@ -4251,7 +4251,7 @@
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA15">
         <v>25</v>
@@ -4275,13 +4275,13 @@
         <v>16</v>
       </c>
       <c r="AH15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI15">
         <v>32</v>
       </c>
       <c r="AJ15">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AK15">
         <v>42</v>
@@ -4290,13 +4290,13 @@
         <v>46</v>
       </c>
       <c r="AM15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15">
         <v>36</v>
       </c>
       <c r="AO15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP15">
         <v>17.5</v>
@@ -4308,10 +4308,10 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU15">
         <v>8.800000000000001</v>
@@ -4326,16 +4326,16 @@
         <v>27</v>
       </c>
       <c r="AY15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ15">
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC15">
         <v>36</v>
@@ -4347,7 +4347,7 @@
         <v>65</v>
       </c>
       <c r="BF15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BG15">
         <v>10</v>
@@ -4356,37 +4356,37 @@
         <v>3.95</v>
       </c>
       <c r="BI15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL15">
         <v>110</v>
       </c>
       <c r="BM15">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN15">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BP15">
         <v>34</v>
       </c>
       <c r="BQ15">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR15">
         <v>42</v>
       </c>
       <c r="BS15">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15">
         <v>5</v>
@@ -4395,22 +4395,22 @@
         <v>4.4</v>
       </c>
       <c r="BV15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW15">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX15">
         <v>28</v>
       </c>
       <c r="BY15">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15">
         <v>22</v>
       </c>
       <c r="CA15">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB15" t="s">
         <v>145</v>
@@ -4433,10 +4433,10 @@
         <v>134</v>
       </c>
       <c r="F16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H16">
         <v>3.05</v>
@@ -4451,7 +4451,7 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
         <v>1.03</v>
@@ -4463,22 +4463,22 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
         <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V16">
         <v>1.45</v>
@@ -4493,22 +4493,22 @@
         <v>21</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA16">
         <v>65</v>
       </c>
       <c r="AB16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF16">
         <v>19.5</v>
@@ -4535,13 +4535,13 @@
         <v>65</v>
       </c>
       <c r="AN16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
         <v>18</v>
@@ -4553,7 +4553,7 @@
         <v>24</v>
       </c>
       <c r="AT16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4562,10 +4562,10 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY16">
         <v>10</v>
@@ -4574,7 +4574,7 @@
         <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB16">
         <v>25</v>
@@ -4589,7 +4589,7 @@
         <v>36</v>
       </c>
       <c r="BF16">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG16">
         <v>15.5</v>
@@ -4598,19 +4598,19 @@
         <v>5.4</v>
       </c>
       <c r="BI16">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL16">
         <v>85</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BN16">
         <v>6.8</v>
@@ -4622,13 +4622,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="BR16">
         <v>27</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BT16">
         <v>8.199999999999999</v>
@@ -4640,19 +4640,19 @@
         <v>26</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BX16">
         <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="CB16" t="s">
         <v>145</v>
@@ -4678,10 +4678,10 @@
         <v>1.93</v>
       </c>
       <c r="G17">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H17">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I17">
         <v>4.1</v>
@@ -4690,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.31</v>
@@ -4714,7 +4714,7 @@
         <v>1.58</v>
       </c>
       <c r="S17">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T17">
         <v>1.6</v>
@@ -4726,7 +4726,7 @@
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X17">
         <v>23</v>
@@ -4738,13 +4738,13 @@
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>13</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>17</v>
@@ -4777,7 +4777,7 @@
         <v>65</v>
       </c>
       <c r="AN17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO17">
         <v>32</v>
@@ -4786,13 +4786,13 @@
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS17">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -4804,19 +4804,19 @@
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX17">
         <v>13</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB17">
         <v>19.5</v>
@@ -4834,25 +4834,25 @@
         <v>8.6</v>
       </c>
       <c r="BG17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BH17">
         <v>4.2</v>
       </c>
       <c r="BI17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ17">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL17">
         <v>95</v>
       </c>
       <c r="BM17">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BN17">
         <v>5.1</v>
@@ -4864,37 +4864,37 @@
         <v>15</v>
       </c>
       <c r="BQ17">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BR17">
         <v>26</v>
       </c>
       <c r="BS17">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BT17">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU17">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV17">
         <v>32</v>
       </c>
       <c r="BW17">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
         <v>19</v>
       </c>
       <c r="CA17">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="s">
         <v>145</v>
@@ -4917,13 +4917,13 @@
         <v>136</v>
       </c>
       <c r="F18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G18">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I18">
         <v>3.5</v>
@@ -4932,46 +4932,46 @@
         <v>3.9</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P18">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R18">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S18">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U18">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="V18">
         <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y18">
         <v>17</v>
@@ -4983,10 +4983,10 @@
         <v>70</v>
       </c>
       <c r="AB18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC18">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD18">
         <v>15</v>
@@ -4995,7 +4995,7 @@
         <v>38</v>
       </c>
       <c r="AF18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
@@ -5004,7 +5004,7 @@
         <v>16.5</v>
       </c>
       <c r="AI18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ18">
         <v>29</v>
@@ -5013,25 +5013,25 @@
         <v>22</v>
       </c>
       <c r="AL18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM18">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO18">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS18">
         <v>32</v>
@@ -5040,7 +5040,7 @@
         <v>11</v>
       </c>
       <c r="AU18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
         <v>12.5</v>
@@ -5058,7 +5058,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB18">
         <v>21</v>
@@ -5067,34 +5067,34 @@
         <v>18</v>
       </c>
       <c r="BD18">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH18">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI18">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BJ18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK18">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL18">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM18">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5103,7 +5103,7 @@
         <v>4.7</v>
       </c>
       <c r="BP18">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BQ18">
         <v>9.199999999999999</v>
@@ -5112,31 +5112,31 @@
         <v>26</v>
       </c>
       <c r="BS18">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BT18">
         <v>7.2</v>
       </c>
       <c r="BU18">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV18">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BW18">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BX18">
         <v>34</v>
       </c>
       <c r="BY18">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BZ18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA18">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5159,25 +5159,25 @@
         <v>137</v>
       </c>
       <c r="F19">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G19">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="H19">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I19">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J19">
         <v>3.75</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
         <v>1.06</v>
@@ -5189,37 +5189,37 @@
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T19">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="X19">
         <v>19.5</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA19">
         <v>65</v>
@@ -5228,28 +5228,28 @@
         <v>12.5</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19">
+        <v>17</v>
+      </c>
+      <c r="AG19">
+        <v>12</v>
+      </c>
+      <c r="AH19">
         <v>16.5</v>
-      </c>
-      <c r="AG19">
-        <v>11.5</v>
-      </c>
-      <c r="AH19">
-        <v>17</v>
       </c>
       <c r="AI19">
         <v>48</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK19">
         <v>24</v>
@@ -5261,10 +5261,10 @@
         <v>90</v>
       </c>
       <c r="AN19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP19">
         <v>16</v>
@@ -5273,10 +5273,10 @@
         <v>13</v>
       </c>
       <c r="AR19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT19">
         <v>10.5</v>
@@ -5291,7 +5291,7 @@
         <v>27</v>
       </c>
       <c r="AX19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY19">
         <v>10</v>
@@ -5306,7 +5306,7 @@
         <v>25</v>
       </c>
       <c r="BC19">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD19">
         <v>27</v>
@@ -5315,10 +5315,10 @@
         <v>46</v>
       </c>
       <c r="BF19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BH19">
         <v>4.5</v>
@@ -5330,16 +5330,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL19">
         <v>110</v>
       </c>
       <c r="BM19">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN19">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO19">
         <v>4.8</v>
@@ -5348,7 +5348,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ19">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BR19">
         <v>32</v>
@@ -5357,19 +5357,19 @@
         <v>13.5</v>
       </c>
       <c r="BT19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BW19">
         <v>12</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY19">
         <v>16.5</v>
@@ -5401,13 +5401,13 @@
         <v>138</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G20">
         <v>1.84</v>
       </c>
       <c r="H20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I20">
         <v>4.7</v>
@@ -5419,58 +5419,58 @@
         <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
         <v>1.03</v>
       </c>
       <c r="N20">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q20">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
         <v>1.7</v>
       </c>
       <c r="S20">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T20">
         <v>1.56</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA20">
-        <v>170</v>
+        <v>310</v>
       </c>
       <c r="AB20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
         <v>19.5</v>
@@ -5497,22 +5497,22 @@
         <v>17.5</v>
       </c>
       <c r="AL20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO20">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR20">
         <v>30</v>
@@ -5536,10 +5536,10 @@
         <v>13</v>
       </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA20">
         <v>36</v>
@@ -5554,31 +5554,31 @@
         <v>21</v>
       </c>
       <c r="BE20">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BF20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH20">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI20">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BJ20">
         <v>10</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL20">
         <v>85</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN20">
         <v>5.7</v>
@@ -5590,37 +5590,37 @@
         <v>13</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR20">
         <v>23</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT20">
         <v>9.4</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW20">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="BX20">
         <v>38</v>
       </c>
       <c r="BY20">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BZ20">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5643,22 +5643,22 @@
         <v>139</v>
       </c>
       <c r="F21">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H21">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J21">
         <v>3.8</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.35</v>
@@ -5679,34 +5679,34 @@
         <v>1.74</v>
       </c>
       <c r="R21">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S21">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T21">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA21">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB21">
         <v>12</v>
@@ -5715,13 +5715,13 @@
         <v>9</v>
       </c>
       <c r="AD21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE21">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5730,28 +5730,28 @@
         <v>17.5</v>
       </c>
       <c r="AI21">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ21">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21">
         <v>36</v>
       </c>
       <c r="AM21">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO21">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21">
         <v>14</v>
@@ -5760,13 +5760,13 @@
         <v>22</v>
       </c>
       <c r="AS21">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AT21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
         <v>13</v>
@@ -5784,10 +5784,10 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21">
         <v>18</v>
@@ -5811,58 +5811,58 @@
         <v>3.45</v>
       </c>
       <c r="BJ21">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BL21">
         <v>110</v>
       </c>
       <c r="BM21">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BN21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO21">
         <v>4.6</v>
       </c>
       <c r="BP21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR21">
         <v>26</v>
       </c>
       <c r="BS21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT21">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU21">
         <v>6</v>
       </c>
       <c r="BV21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW21">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX21">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BZ21">
         <v>21</v>
       </c>
       <c r="CA21">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>
@@ -5885,16 +5885,16 @@
         <v>140</v>
       </c>
       <c r="F22">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="G22">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H22">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="I22">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="J22">
         <v>4.1</v>
@@ -5903,28 +5903,28 @@
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
         <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q22">
         <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S22">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T22">
         <v>1.5</v>
@@ -5933,19 +5933,19 @@
         <v>2.88</v>
       </c>
       <c r="V22">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X22">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z22">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA22">
         <v>44</v>
@@ -5957,13 +5957,13 @@
         <v>10.5</v>
       </c>
       <c r="AD22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
@@ -5972,7 +5972,7 @@
         <v>15</v>
       </c>
       <c r="AI22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
         <v>36</v>
@@ -5987,13 +5987,13 @@
         <v>50</v>
       </c>
       <c r="AN22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO22">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ22">
         <v>17.5</v>
@@ -6005,10 +6005,10 @@
         <v>38</v>
       </c>
       <c r="AT22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6017,10 +6017,10 @@
         <v>22</v>
       </c>
       <c r="AX22">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
         <v>13</v>
@@ -6029,13 +6029,13 @@
         <v>25</v>
       </c>
       <c r="BB22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE22">
         <v>42</v>
@@ -6044,67 +6044,67 @@
         <v>10</v>
       </c>
       <c r="BG22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI22">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BJ22">
         <v>9.4</v>
       </c>
       <c r="BK22">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="BL22">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BN22">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BO22">
         <v>5.2</v>
       </c>
       <c r="BP22">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR22">
         <v>25</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT22">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV22">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX22">
         <v>27</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB22" t="s">
         <v>145</v>
@@ -6127,226 +6127,226 @@
         <v>141</v>
       </c>
       <c r="F23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G23">
+        <v>4.4</v>
+      </c>
+      <c r="H23">
+        <v>1.97</v>
+      </c>
+      <c r="I23">
+        <v>1.99</v>
+      </c>
+      <c r="J23">
+        <v>3.8</v>
+      </c>
+      <c r="K23">
+        <v>3.9</v>
+      </c>
+      <c r="L23">
+        <v>1.37</v>
+      </c>
+      <c r="M23">
+        <v>1.06</v>
+      </c>
+      <c r="N23">
+        <v>4.4</v>
+      </c>
+      <c r="O23">
+        <v>1.28</v>
+      </c>
+      <c r="P23">
+        <v>2.16</v>
+      </c>
+      <c r="Q23">
+        <v>1.83</v>
+      </c>
+      <c r="R23">
+        <v>1.44</v>
+      </c>
+      <c r="S23">
+        <v>3.2</v>
+      </c>
+      <c r="T23">
+        <v>1.73</v>
+      </c>
+      <c r="U23">
+        <v>2.24</v>
+      </c>
+      <c r="V23">
+        <v>2</v>
+      </c>
+      <c r="W23">
+        <v>1.29</v>
+      </c>
+      <c r="X23">
+        <v>21</v>
+      </c>
+      <c r="Y23">
+        <v>10.5</v>
+      </c>
+      <c r="Z23">
+        <v>13</v>
+      </c>
+      <c r="AA23">
+        <v>22</v>
+      </c>
+      <c r="AB23">
+        <v>18.5</v>
+      </c>
+      <c r="AC23">
+        <v>8.6</v>
+      </c>
+      <c r="AD23">
+        <v>10.5</v>
+      </c>
+      <c r="AE23">
+        <v>21</v>
+      </c>
+      <c r="AF23">
+        <v>36</v>
+      </c>
+      <c r="AG23">
+        <v>16.5</v>
+      </c>
+      <c r="AH23">
+        <v>18.5</v>
+      </c>
+      <c r="AI23">
+        <v>38</v>
+      </c>
+      <c r="AJ23">
+        <v>95</v>
+      </c>
+      <c r="AK23">
+        <v>60</v>
+      </c>
+      <c r="AL23">
+        <v>60</v>
+      </c>
+      <c r="AM23">
+        <v>100</v>
+      </c>
+      <c r="AN23">
+        <v>55</v>
+      </c>
+      <c r="AO23">
+        <v>12.5</v>
+      </c>
+      <c r="AP23">
+        <v>15.5</v>
+      </c>
+      <c r="AQ23">
+        <v>9.6</v>
+      </c>
+      <c r="AR23">
+        <v>11.5</v>
+      </c>
+      <c r="AS23">
+        <v>19</v>
+      </c>
+      <c r="AT23">
+        <v>15</v>
+      </c>
+      <c r="AU23">
+        <v>8</v>
+      </c>
+      <c r="AV23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW23">
+        <v>17.5</v>
+      </c>
+      <c r="AX23">
+        <v>27</v>
+      </c>
+      <c r="AY23">
+        <v>15</v>
+      </c>
+      <c r="AZ23">
+        <v>15.5</v>
+      </c>
+      <c r="BA23">
+        <v>27</v>
+      </c>
+      <c r="BB23">
+        <v>55</v>
+      </c>
+      <c r="BC23">
+        <v>34</v>
+      </c>
+      <c r="BD23">
+        <v>38</v>
+      </c>
+      <c r="BE23">
+        <v>60</v>
+      </c>
+      <c r="BF23">
+        <v>29</v>
+      </c>
+      <c r="BG23">
+        <v>10.5</v>
+      </c>
+      <c r="BH23">
+        <v>4.1</v>
+      </c>
+      <c r="BI23">
+        <v>3.05</v>
+      </c>
+      <c r="BJ23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK23">
         <v>4.5</v>
       </c>
-      <c r="H23">
-        <v>2.04</v>
-      </c>
-      <c r="I23">
-        <v>2.08</v>
-      </c>
-      <c r="J23">
-        <v>3.4</v>
-      </c>
-      <c r="K23">
-        <v>3.55</v>
-      </c>
-      <c r="L23">
-        <v>1.48</v>
-      </c>
-      <c r="M23">
-        <v>1.09</v>
-      </c>
-      <c r="N23">
-        <v>3.3</v>
-      </c>
-      <c r="O23">
-        <v>1.41</v>
-      </c>
-      <c r="P23">
-        <v>1.76</v>
-      </c>
-      <c r="Q23">
-        <v>2.24</v>
-      </c>
-      <c r="R23">
-        <v>1.28</v>
-      </c>
-      <c r="S23">
-        <v>4.3</v>
-      </c>
-      <c r="T23">
-        <v>1.98</v>
-      </c>
-      <c r="U23">
-        <v>1.95</v>
-      </c>
-      <c r="V23">
-        <v>1.92</v>
-      </c>
-      <c r="W23">
-        <v>1.28</v>
-      </c>
-      <c r="X23">
-        <v>11.5</v>
-      </c>
-      <c r="Y23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z23">
-        <v>12</v>
-      </c>
-      <c r="AA23">
-        <v>28</v>
-      </c>
-      <c r="AB23">
+      <c r="BL23">
+        <v>120</v>
+      </c>
+      <c r="BM23">
+        <v>7.8</v>
+      </c>
+      <c r="BN23">
+        <v>8</v>
+      </c>
+      <c r="BO23">
+        <v>6</v>
+      </c>
+      <c r="BP23">
+        <v>34</v>
+      </c>
+      <c r="BQ23">
+        <v>6.8</v>
+      </c>
+      <c r="BR23">
+        <v>42</v>
+      </c>
+      <c r="BS23">
+        <v>7</v>
+      </c>
+      <c r="BT23">
+        <v>5</v>
+      </c>
+      <c r="BU23">
+        <v>3.85</v>
+      </c>
+      <c r="BV23">
         <v>14</v>
       </c>
-      <c r="AC23">
-        <v>7.8</v>
-      </c>
-      <c r="AD23">
-        <v>11</v>
-      </c>
-      <c r="AE23">
-        <v>32</v>
-      </c>
-      <c r="AF23">
-        <v>38</v>
-      </c>
-      <c r="AG23">
-        <v>18.5</v>
-      </c>
-      <c r="AH23">
-        <v>21</v>
-      </c>
-      <c r="AI23">
-        <v>55</v>
-      </c>
-      <c r="AJ23">
-        <v>120</v>
-      </c>
-      <c r="AK23">
-        <v>75</v>
-      </c>
-      <c r="AL23">
-        <v>90</v>
-      </c>
-      <c r="AM23">
-        <v>450</v>
-      </c>
-      <c r="AN23">
-        <v>95</v>
-      </c>
-      <c r="AO23">
-        <v>19</v>
-      </c>
-      <c r="AP23">
-        <v>10.5</v>
-      </c>
-      <c r="AQ23">
-        <v>7.4</v>
-      </c>
-      <c r="AR23">
-        <v>10</v>
-      </c>
-      <c r="AS23">
-        <v>18.5</v>
-      </c>
-      <c r="AT23">
-        <v>12</v>
-      </c>
-      <c r="AU23">
-        <v>7</v>
-      </c>
-      <c r="AV23">
-        <v>9.6</v>
-      </c>
-      <c r="AW23">
-        <v>20</v>
-      </c>
-      <c r="AX23">
-        <v>25</v>
-      </c>
-      <c r="AY23">
-        <v>16</v>
-      </c>
-      <c r="AZ23">
-        <v>19.5</v>
-      </c>
-      <c r="BA23">
-        <v>32</v>
-      </c>
-      <c r="BB23">
-        <v>60</v>
-      </c>
-      <c r="BC23">
-        <v>42</v>
-      </c>
-      <c r="BD23">
-        <v>50</v>
-      </c>
-      <c r="BE23">
-        <v>34</v>
-      </c>
-      <c r="BF23">
-        <v>55</v>
-      </c>
-      <c r="BG23">
-        <v>16.5</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.01</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.01</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.01</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.01</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.01</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB23" t="s">
         <v>145</v>
@@ -6375,10 +6375,10 @@
         <v>2.06</v>
       </c>
       <c r="H24">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J24">
         <v>3.9</v>
@@ -6405,7 +6405,7 @@
         <v>1.71</v>
       </c>
       <c r="R24">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S24">
         <v>2.8</v>
@@ -6441,7 +6441,7 @@
         <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE24">
         <v>48</v>
@@ -6453,7 +6453,7 @@
         <v>11</v>
       </c>
       <c r="AH24">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI24">
         <v>50</v>
@@ -6471,7 +6471,7 @@
         <v>200</v>
       </c>
       <c r="AN24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO24">
         <v>40</v>
@@ -6486,13 +6486,13 @@
         <v>23</v>
       </c>
       <c r="AS24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT24">
         <v>10</v>
       </c>
       <c r="AU24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24">
         <v>13.5</v>
@@ -6510,7 +6510,7 @@
         <v>14</v>
       </c>
       <c r="BA24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB24">
         <v>21</v>
@@ -6549,34 +6549,34 @@
         <v>65</v>
       </c>
       <c r="BN24">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO24">
         <v>4</v>
       </c>
       <c r="BP24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ24">
         <v>10</v>
       </c>
       <c r="BR24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS24">
         <v>18</v>
       </c>
       <c r="BT24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV24">
         <v>34</v>
       </c>
       <c r="BW24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BX24">
         <v>42</v>
@@ -6588,7 +6588,7 @@
         <v>21</v>
       </c>
       <c r="CA24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CB24" t="s">
         <v>145</v>
@@ -6611,52 +6611,52 @@
         <v>143</v>
       </c>
       <c r="F25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G25">
         <v>1.3</v>
       </c>
       <c r="H25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="I25">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M25">
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
         <v>1.27</v>
       </c>
       <c r="P25">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T25">
         <v>2.48</v>
       </c>
       <c r="U25">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V25">
         <v>1.06</v>
@@ -6665,94 +6665,94 @@
         <v>4.3</v>
       </c>
       <c r="X25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y25">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Z25">
         <v>170</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="AB25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD25">
         <v>65</v>
       </c>
       <c r="AE25">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG25">
         <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI25">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AJ25">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM25">
         <v>350</v>
       </c>
       <c r="AN25">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="AP25">
         <v>16.5</v>
       </c>
       <c r="AQ25">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AR25">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AS25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV25">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AW25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY25">
         <v>10</v>
       </c>
       <c r="AZ25">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="BA25">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB25">
         <v>8</v>
@@ -6761,76 +6761,76 @@
         <v>14</v>
       </c>
       <c r="BD25">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="BE25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG25">
+        <v>15</v>
+      </c>
+      <c r="BH25">
+        <v>3.9</v>
+      </c>
+      <c r="BI25">
+        <v>3.5</v>
+      </c>
+      <c r="BJ25">
+        <v>15.5</v>
+      </c>
+      <c r="BK25">
+        <v>7.8</v>
+      </c>
+      <c r="BL25">
+        <v>300</v>
+      </c>
+      <c r="BM25">
         <v>14.5</v>
-      </c>
-      <c r="BH25">
-        <v>4.5</v>
-      </c>
-      <c r="BI25">
-        <v>3.05</v>
-      </c>
-      <c r="BJ25">
-        <v>15</v>
-      </c>
-      <c r="BK25">
-        <v>5.8</v>
-      </c>
-      <c r="BL25">
-        <v>290</v>
-      </c>
-      <c r="BM25">
-        <v>9.199999999999999</v>
       </c>
       <c r="BN25">
         <v>3.45</v>
       </c>
       <c r="BO25">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP25">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ25">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BR25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS25">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BT25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BU25">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV25">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BW25">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BX25">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BY25">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BZ25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA25">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB25" t="s">
         <v>145</v>
@@ -6853,25 +6853,25 @@
         <v>144</v>
       </c>
       <c r="F26">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G26">
         <v>2.48</v>
       </c>
       <c r="H26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I26">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K26">
         <v>3.5</v>
       </c>
       <c r="L26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M26">
         <v>1.08</v>
@@ -6883,10 +6883,10 @@
         <v>1.39</v>
       </c>
       <c r="P26">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R26">
         <v>1.3</v>
@@ -6895,7 +6895,7 @@
         <v>4</v>
       </c>
       <c r="T26">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U26">
         <v>2.04</v>
@@ -6913,7 +6913,7 @@
         <v>12.5</v>
       </c>
       <c r="Z26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA26">
         <v>75</v>
@@ -6931,7 +6931,7 @@
         <v>50</v>
       </c>
       <c r="AF26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG26">
         <v>12</v>
@@ -6946,28 +6946,28 @@
         <v>40</v>
       </c>
       <c r="AK26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM26">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN26">
         <v>25</v>
       </c>
       <c r="AO26">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP26">
         <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR26">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS26">
         <v>44</v>
@@ -6982,7 +6982,7 @@
         <v>12.5</v>
       </c>
       <c r="AW26">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AX26">
         <v>12.5</v>
@@ -7000,7 +7000,7 @@
         <v>24</v>
       </c>
       <c r="BC26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD26">
         <v>30</v>
@@ -7009,22 +7009,22 @@
         <v>80</v>
       </c>
       <c r="BF26">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG26">
         <v>36</v>
       </c>
       <c r="BH26">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI26">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>160</v>
@@ -7033,43 +7033,43 @@
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO26">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP26">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU26">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV26">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BW26">
         <v>1.02</v>
       </c>
       <c r="BX26">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA26">
         <v>1.02</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-29.xlsx
@@ -451,7 +451,7 @@
     <t>Real Cartagena</t>
   </si>
   <si>
-    <t>2026-09-29 12:22:20</t>
+    <t>2026-09-29 14:34:15</t>
   </si>
 </sst>
 </file>
@@ -1045,226 +1045,226 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>1.53</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>2.44</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="P2">
+        <v>1.01</v>
+      </c>
+      <c r="Q2">
+        <v>65</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>230</v>
+      </c>
+      <c r="T2">
+        <v>16</v>
+      </c>
+      <c r="U2">
+        <v>1.05</v>
+      </c>
+      <c r="V2">
+        <v>1.17</v>
+      </c>
+      <c r="W2">
+        <v>1.27</v>
+      </c>
+      <c r="X2">
+        <v>1.78</v>
+      </c>
+      <c r="Y2">
+        <v>7.6</v>
+      </c>
+      <c r="Z2">
+        <v>85</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>5.7</v>
+      </c>
+      <c r="AC2">
+        <v>22</v>
+      </c>
+      <c r="AD2">
+        <v>990</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>42</v>
+      </c>
+      <c r="AG2">
+        <v>980</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>560</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
         <v>1.74</v>
       </c>
-      <c r="Q2">
-        <v>2.22</v>
-      </c>
-      <c r="R2">
-        <v>1.27</v>
-      </c>
-      <c r="S2">
-        <v>4.2</v>
-      </c>
-      <c r="T2">
-        <v>1.96</v>
-      </c>
-      <c r="U2">
-        <v>1.96</v>
-      </c>
-      <c r="V2">
-        <v>1.38</v>
-      </c>
-      <c r="W2">
-        <v>1.78</v>
-      </c>
-      <c r="X2">
-        <v>13.5</v>
-      </c>
-      <c r="Y2">
-        <v>11.5</v>
-      </c>
-      <c r="Z2">
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>50</v>
+      </c>
+      <c r="AS2">
+        <v>250</v>
+      </c>
+      <c r="AT2">
+        <v>5.2</v>
+      </c>
+      <c r="AU2">
+        <v>19</v>
+      </c>
+      <c r="AV2">
+        <v>120</v>
+      </c>
+      <c r="AW2">
+        <v>190</v>
+      </c>
+      <c r="AX2">
+        <v>30</v>
+      </c>
+      <c r="AY2">
+        <v>100</v>
+      </c>
+      <c r="AZ2">
+        <v>180</v>
+      </c>
+      <c r="BA2">
+        <v>210</v>
+      </c>
+      <c r="BB2">
+        <v>180</v>
+      </c>
+      <c r="BC2">
+        <v>170</v>
+      </c>
+      <c r="BD2">
         <v>24</v>
-      </c>
-      <c r="AA2">
-        <v>75</v>
-      </c>
-      <c r="AB2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>14.5</v>
-      </c>
-      <c r="AE2">
-        <v>55</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>22</v>
-      </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>28</v>
-      </c>
-      <c r="AL2">
-        <v>50</v>
-      </c>
-      <c r="AM2">
-        <v>140</v>
-      </c>
-      <c r="AN2">
-        <v>25</v>
-      </c>
-      <c r="AO2">
-        <v>60</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
-        <v>19.5</v>
-      </c>
-      <c r="AS2">
-        <v>50</v>
-      </c>
-      <c r="AT2">
-        <v>7.8</v>
-      </c>
-      <c r="AU2">
-        <v>7.2</v>
-      </c>
-      <c r="AV2">
-        <v>13</v>
-      </c>
-      <c r="AW2">
-        <v>42</v>
-      </c>
-      <c r="AX2">
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>48</v>
-      </c>
-      <c r="BB2">
-        <v>26</v>
-      </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
-      <c r="BD2">
-        <v>38</v>
       </c>
       <c r="BE2">
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>19.5</v>
+        <v>210</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>145</v>
@@ -1287,226 +1287,226 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
-        <v>1.53</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
+        <v>1.81</v>
+      </c>
+      <c r="K3">
+        <v>1.82</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.94</v>
+      </c>
+      <c r="N3">
+        <v>1.18</v>
+      </c>
+      <c r="O3">
+        <v>6.4</v>
+      </c>
+      <c r="P3">
+        <v>1.02</v>
+      </c>
+      <c r="Q3">
+        <v>36</v>
+      </c>
+      <c r="R3">
+        <v>1.01</v>
+      </c>
+      <c r="S3">
+        <v>170</v>
+      </c>
+      <c r="T3">
+        <v>12.5</v>
+      </c>
+      <c r="U3">
+        <v>1.07</v>
+      </c>
+      <c r="V3">
+        <v>1.16</v>
+      </c>
+      <c r="W3">
+        <v>1.46</v>
+      </c>
+      <c r="X3">
+        <v>2.04</v>
+      </c>
+      <c r="Y3">
+        <v>8.6</v>
+      </c>
+      <c r="Z3">
+        <v>90</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
         <v>4.5</v>
       </c>
-      <c r="K3">
-        <v>4.6</v>
-      </c>
-      <c r="L3">
-        <v>1.42</v>
-      </c>
-      <c r="M3">
-        <v>1.07</v>
-      </c>
-      <c r="N3">
-        <v>3.75</v>
-      </c>
-      <c r="O3">
-        <v>1.35</v>
-      </c>
-      <c r="P3">
-        <v>1.94</v>
-      </c>
-      <c r="Q3">
-        <v>2.04</v>
-      </c>
-      <c r="R3">
-        <v>1.34</v>
-      </c>
-      <c r="S3">
-        <v>3.75</v>
-      </c>
-      <c r="T3">
-        <v>2.22</v>
-      </c>
-      <c r="U3">
-        <v>1.79</v>
-      </c>
-      <c r="V3">
-        <v>1.13</v>
-      </c>
-      <c r="W3">
-        <v>2.9</v>
-      </c>
-      <c r="X3">
-        <v>14</v>
-      </c>
-      <c r="Y3">
-        <v>22</v>
-      </c>
-      <c r="Z3">
+      <c r="AC3">
+        <v>19.5</v>
+      </c>
+      <c r="AD3">
+        <v>220</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>100</v>
+      </c>
+      <c r="AG3">
+        <v>120</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>290</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>2</v>
+      </c>
+      <c r="AQ3">
+        <v>7.4</v>
+      </c>
+      <c r="AR3">
         <v>65</v>
       </c>
-      <c r="AA3">
-        <v>310</v>
-      </c>
-      <c r="AB3">
-        <v>7.2</v>
-      </c>
-      <c r="AC3">
-        <v>10.5</v>
-      </c>
-      <c r="AD3">
-        <v>29</v>
-      </c>
-      <c r="AE3">
-        <v>150</v>
-      </c>
-      <c r="AF3">
-        <v>7.8</v>
-      </c>
-      <c r="AG3">
-        <v>10</v>
-      </c>
-      <c r="AH3">
-        <v>26</v>
-      </c>
-      <c r="AI3">
+      <c r="AS3">
+        <v>85</v>
+      </c>
+      <c r="AT3">
+        <v>4.2</v>
+      </c>
+      <c r="AU3">
+        <v>17.5</v>
+      </c>
+      <c r="AV3">
         <v>130</v>
       </c>
-      <c r="AJ3">
-        <v>12</v>
-      </c>
-      <c r="AK3">
-        <v>17</v>
-      </c>
-      <c r="AL3">
-        <v>44</v>
-      </c>
-      <c r="AM3">
-        <v>180</v>
-      </c>
-      <c r="AN3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO3">
+      <c r="AW3">
+        <v>1000</v>
+      </c>
+      <c r="AX3">
+        <v>20</v>
+      </c>
+      <c r="AY3">
+        <v>75</v>
+      </c>
+      <c r="AZ3">
+        <v>290</v>
+      </c>
+      <c r="BA3">
+        <v>1000</v>
+      </c>
+      <c r="BB3">
+        <v>140</v>
+      </c>
+      <c r="BC3">
         <v>230</v>
       </c>
-      <c r="AP3">
-        <v>13.5</v>
-      </c>
-      <c r="AQ3">
-        <v>20</v>
-      </c>
-      <c r="AR3">
-        <v>55</v>
-      </c>
-      <c r="AS3">
-        <v>65</v>
-      </c>
-      <c r="AT3">
-        <v>6.8</v>
-      </c>
-      <c r="AU3">
-        <v>9.6</v>
-      </c>
-      <c r="AV3">
-        <v>27</v>
-      </c>
-      <c r="AW3">
-        <v>120</v>
-      </c>
-      <c r="AX3">
-        <v>7.6</v>
-      </c>
-      <c r="AY3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>25</v>
-      </c>
-      <c r="BA3">
-        <v>110</v>
-      </c>
-      <c r="BB3">
-        <v>11.5</v>
-      </c>
-      <c r="BC3">
-        <v>16.5</v>
-      </c>
       <c r="BD3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BE3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>170</v>
       </c>
       <c r="BG3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BH3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,226 +1529,226 @@
         <v>122</v>
       </c>
       <c r="F4">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>2.76</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="L4">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="X4">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>6.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
+        <v>46</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1000</v>
+      </c>
+      <c r="AQ4">
+        <v>1000</v>
+      </c>
+      <c r="AR4">
+        <v>1000</v>
+      </c>
+      <c r="AS4">
+        <v>1000</v>
+      </c>
+      <c r="AT4">
+        <v>1000</v>
+      </c>
+      <c r="AU4">
+        <v>1.71</v>
+      </c>
+      <c r="AV4">
+        <v>7</v>
+      </c>
+      <c r="AW4">
         <v>60</v>
       </c>
-      <c r="AL4">
-        <v>85</v>
-      </c>
-      <c r="AM4">
-        <v>200</v>
-      </c>
-      <c r="AN4">
-        <v>85</v>
-      </c>
-      <c r="AO4">
-        <v>55</v>
-      </c>
-      <c r="AP4">
-        <v>7.4</v>
-      </c>
-      <c r="AQ4">
-        <v>7</v>
-      </c>
-      <c r="AR4">
-        <v>14</v>
-      </c>
-      <c r="AS4">
-        <v>44</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>6.6</v>
-      </c>
-      <c r="AV4">
-        <v>13</v>
-      </c>
-      <c r="AW4">
-        <v>40</v>
-      </c>
       <c r="AX4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AY4">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="BB4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BD4">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BE4">
+        <v>170</v>
+      </c>
+      <c r="BF4">
+        <v>190</v>
+      </c>
+      <c r="BG4">
         <v>160</v>
       </c>
-      <c r="BF4">
-        <v>70</v>
-      </c>
-      <c r="BG4">
-        <v>48</v>
-      </c>
       <c r="BH4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>145</v>
@@ -1771,76 +1771,76 @@
         <v>123</v>
       </c>
       <c r="F5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H5">
         <v>8.6</v>
       </c>
       <c r="I5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K5">
         <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S5">
         <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X5">
         <v>25</v>
       </c>
       <c r="Y5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z5">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AA5">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB5">
         <v>11</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>32</v>
@@ -1852,13 +1852,13 @@
         <v>10</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
         <v>13</v>
@@ -1867,46 +1867,46 @@
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>790</v>
       </c>
       <c r="AN5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO5">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
         <v>29</v>
       </c>
       <c r="AR5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW5">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AX5">
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>20</v>
@@ -1915,22 +1915,22 @@
         <v>70</v>
       </c>
       <c r="BB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC5">
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5">
         <v>75</v>
       </c>
       <c r="BF5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG5">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
@@ -1939,58 +1939,58 @@
         <v>4.2</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL5">
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ5">
+        <v>6.4</v>
+      </c>
+      <c r="BR5">
+        <v>25</v>
+      </c>
+      <c r="BS5">
+        <v>6.6</v>
+      </c>
+      <c r="BT5">
+        <v>12</v>
+      </c>
+      <c r="BU5">
         <v>5.3</v>
       </c>
-      <c r="BR5">
-        <v>22</v>
-      </c>
-      <c r="BS5">
+      <c r="BV5">
+        <v>75</v>
+      </c>
+      <c r="BW5">
         <v>8</v>
       </c>
-      <c r="BT5">
-        <v>12.5</v>
-      </c>
-      <c r="BU5">
-        <v>6.2</v>
-      </c>
-      <c r="BV5">
-        <v>65</v>
-      </c>
-      <c r="BW5">
-        <v>10.5</v>
-      </c>
       <c r="BX5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>145</v>
@@ -2013,40 +2013,40 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="G6">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
         <v>1.23</v>
@@ -2055,85 +2055,85 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA6">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="AB6">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE6">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AF6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG6">
         <v>11</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI6">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AJ6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM6">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO6">
-        <v>330</v>
+        <v>440</v>
       </c>
       <c r="AP6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR6">
         <v>50</v>
       </c>
       <c r="AS6">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU6">
         <v>8.4</v>
@@ -2142,97 +2142,97 @@
         <v>28</v>
       </c>
       <c r="AW6">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AX6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA6">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE6">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="BF6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="BH6">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BI6">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BL6">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="BM6">
         <v>75</v>
       </c>
       <c r="BN6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO6">
         <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ6">
+        <v>10.5</v>
+      </c>
+      <c r="BR6">
+        <v>40</v>
+      </c>
+      <c r="BS6">
+        <v>21</v>
+      </c>
+      <c r="BT6">
+        <v>11</v>
+      </c>
+      <c r="BU6">
         <v>10</v>
       </c>
-      <c r="BR6">
-        <v>38</v>
-      </c>
-      <c r="BS6">
-        <v>13</v>
-      </c>
-      <c r="BT6">
-        <v>10.5</v>
-      </c>
-      <c r="BU6">
-        <v>9.6</v>
-      </c>
       <c r="BV6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BW6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BX6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BY6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BZ6">
         <v>36</v>
       </c>
       <c r="CA6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="CB6" t="s">
         <v>145</v>
@@ -2255,64 +2255,64 @@
         <v>125</v>
       </c>
       <c r="F7">
+        <v>3.25</v>
+      </c>
+      <c r="G7">
         <v>3.3</v>
       </c>
-      <c r="G7">
+      <c r="H7">
+        <v>2.48</v>
+      </c>
+      <c r="I7">
+        <v>2.5</v>
+      </c>
+      <c r="J7">
         <v>3.35</v>
       </c>
-      <c r="H7">
-        <v>2.44</v>
-      </c>
-      <c r="I7">
-        <v>2.48</v>
-      </c>
-      <c r="J7">
+      <c r="K7">
         <v>3.4</v>
-      </c>
-      <c r="K7">
-        <v>3.45</v>
       </c>
       <c r="L7">
         <v>1.49</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7">
         <v>11</v>
       </c>
       <c r="Y7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>14</v>
@@ -2324,67 +2324,67 @@
         <v>11</v>
       </c>
       <c r="AC7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD7">
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7">
         <v>14</v>
       </c>
       <c r="AH7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>120</v>
       </c>
       <c r="AN7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP7">
         <v>10</v>
       </c>
       <c r="AQ7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR7">
         <v>13</v>
       </c>
       <c r="AS7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT7">
         <v>10</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX7">
         <v>20</v>
@@ -2393,37 +2393,37 @@
         <v>13</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE7">
         <v>95</v>
       </c>
       <c r="BF7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BG7">
         <v>25</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK7">
         <v>8.800000000000001</v>
@@ -2438,43 +2438,43 @@
         <v>6.2</v>
       </c>
       <c r="BO7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ7">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT7">
         <v>5.2</v>
       </c>
       <c r="BU7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW7">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="BX7">
         <v>42</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7">
         <v>42</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
         <v>145</v>
@@ -2497,7 +2497,7 @@
         <v>126</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>60</v>
@@ -2515,34 +2515,34 @@
         <v>23</v>
       </c>
       <c r="L8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R8">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="T8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="U8">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V8">
         <v>15.5</v>
@@ -2551,40 +2551,40 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
+        <v>7</v>
+      </c>
+      <c r="AA8">
         <v>6.2</v>
       </c>
-      <c r="AA8">
-        <v>5.6</v>
-      </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AC8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF8">
         <v>1000</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AI8">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
         <v>1000</v>
@@ -2602,28 +2602,28 @@
         <v>1000</v>
       </c>
       <c r="AO8">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AP8">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AQ8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
+        <v>6.6</v>
+      </c>
+      <c r="AS8">
         <v>5.9</v>
       </c>
-      <c r="AS8">
-        <v>5.4</v>
-      </c>
       <c r="AT8">
+        <v>90</v>
+      </c>
+      <c r="AU8">
         <v>60</v>
       </c>
-      <c r="AU8">
-        <v>50</v>
-      </c>
       <c r="AV8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW8">
         <v>21</v>
@@ -2632,91 +2632,91 @@
         <v>140</v>
       </c>
       <c r="AY8">
+        <v>20</v>
+      </c>
+      <c r="AZ8">
+        <v>20</v>
+      </c>
+      <c r="BA8">
         <v>90</v>
       </c>
-      <c r="AZ8">
-        <v>26</v>
-      </c>
-      <c r="BA8">
-        <v>28</v>
-      </c>
       <c r="BB8">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="BC8">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="BD8">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BE8">
         <v>270</v>
       </c>
       <c r="BF8">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BG8">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BH8">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BI8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BJ8">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BK8">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="BM8">
         <v>350</v>
       </c>
       <c r="BN8">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BO8">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BR8">
-        <v>990</v>
+        <v>590</v>
       </c>
       <c r="BS8">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="BT8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BU8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BV8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BW8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY8">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BZ8">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="CA8">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="CB8" t="s">
         <v>145</v>
@@ -2739,16 +2739,16 @@
         <v>127</v>
       </c>
       <c r="F9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
         <v>15.5</v>
-      </c>
-      <c r="I9">
-        <v>16</v>
       </c>
       <c r="J9">
         <v>8.199999999999999</v>
@@ -2757,34 +2757,34 @@
         <v>8.4</v>
       </c>
       <c r="L9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O9">
         <v>1.15</v>
       </c>
       <c r="P9">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q9">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S9">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T9">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V9">
         <v>1.06</v>
@@ -2793,166 +2793,166 @@
         <v>5.3</v>
       </c>
       <c r="X9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z9">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
+        <v>19</v>
+      </c>
+      <c r="AD9">
+        <v>48</v>
+      </c>
+      <c r="AE9">
+        <v>260</v>
+      </c>
+      <c r="AF9">
+        <v>8.6</v>
+      </c>
+      <c r="AG9">
         <v>11</v>
-      </c>
-      <c r="AC9">
-        <v>18.5</v>
-      </c>
-      <c r="AD9">
-        <v>50</v>
-      </c>
-      <c r="AE9">
-        <v>280</v>
-      </c>
-      <c r="AF9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG9">
-        <v>12</v>
       </c>
       <c r="AH9">
         <v>34</v>
       </c>
       <c r="AI9">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ9">
         <v>9.4</v>
       </c>
       <c r="AK9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL9">
+        <v>32</v>
+      </c>
+      <c r="AM9">
+        <v>140</v>
+      </c>
+      <c r="AN9">
+        <v>3.55</v>
+      </c>
+      <c r="AO9">
+        <v>300</v>
+      </c>
+      <c r="AP9">
         <v>34</v>
-      </c>
-      <c r="AM9">
-        <v>150</v>
-      </c>
-      <c r="AN9">
-        <v>3.45</v>
-      </c>
-      <c r="AO9">
-        <v>390</v>
-      </c>
-      <c r="AP9">
-        <v>32</v>
       </c>
       <c r="AQ9">
         <v>50</v>
       </c>
       <c r="AR9">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AS9">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AV9">
         <v>44</v>
       </c>
       <c r="AW9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
         <v>32</v>
       </c>
       <c r="BA9">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="BB9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BH9">
         <v>4.9</v>
       </c>
       <c r="BI9">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
         <v>11</v>
       </c>
       <c r="BL9">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BN9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP9">
         <v>6.2</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BS9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BV9">
         <v>130</v>
       </c>
       <c r="BW9">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BX9">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="BY9">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>128</v>
       </c>
       <c r="F10">
+        <v>11.5</v>
+      </c>
+      <c r="G10">
         <v>12</v>
-      </c>
-      <c r="G10">
-        <v>12.5</v>
       </c>
       <c r="H10">
         <v>1.31</v>
@@ -2999,55 +2999,55 @@
         <v>6.4</v>
       </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="Q10">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R10">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="S10">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V10">
         <v>4.1</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>26</v>
       </c>
       <c r="Y10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AA10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC10">
         <v>14</v>
@@ -3056,49 +3056,49 @@
         <v>10.5</v>
       </c>
       <c r="AE10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AF10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AG10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AH10">
         <v>28</v>
       </c>
       <c r="AI10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK10">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AL10">
+        <v>120</v>
+      </c>
+      <c r="AM10">
         <v>140</v>
       </c>
-      <c r="AM10">
-        <v>150</v>
-      </c>
       <c r="AN10">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="AO10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AP10">
         <v>25</v>
       </c>
       <c r="AQ10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10">
         <v>38</v>
@@ -3110,97 +3110,97 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AY10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AZ10">
         <v>27</v>
       </c>
       <c r="BA10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB10">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="BC10">
         <v>160</v>
       </c>
       <c r="BD10">
+        <v>110</v>
+      </c>
+      <c r="BE10">
         <v>120</v>
       </c>
-      <c r="BE10">
-        <v>140</v>
-      </c>
       <c r="BF10">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="BG10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH10">
+        <v>4.4</v>
+      </c>
+      <c r="BI10">
         <v>4.3</v>
-      </c>
-      <c r="BI10">
-        <v>4</v>
       </c>
       <c r="BJ10">
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BL10">
         <v>150</v>
       </c>
       <c r="BM10">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="BN10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BO10">
         <v>12.5</v>
       </c>
       <c r="BP10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BQ10">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BR10">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BS10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BT10">
         <v>3.8</v>
       </c>
       <c r="BU10">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BV10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BW10">
         <v>6.4</v>
       </c>
       <c r="BX10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BY10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BZ10">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA10">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="s">
         <v>145</v>
@@ -3223,97 +3223,97 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="G11">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="H11">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="I11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J11">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="K11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="L11">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M11">
+        <v>1.04</v>
+      </c>
+      <c r="N11">
+        <v>5.3</v>
+      </c>
+      <c r="O11">
+        <v>1.22</v>
+      </c>
+      <c r="P11">
+        <v>2.4</v>
+      </c>
+      <c r="Q11">
+        <v>1.69</v>
+      </c>
+      <c r="R11">
+        <v>1.55</v>
+      </c>
+      <c r="S11">
+        <v>2.72</v>
+      </c>
+      <c r="T11">
+        <v>2.52</v>
+      </c>
+      <c r="U11">
+        <v>1.63</v>
+      </c>
+      <c r="V11">
         <v>1.05</v>
       </c>
-      <c r="N11">
-        <v>4.8</v>
-      </c>
-      <c r="O11">
-        <v>1.25</v>
-      </c>
-      <c r="P11">
-        <v>2.32</v>
-      </c>
-      <c r="Q11">
-        <v>1.74</v>
-      </c>
-      <c r="R11">
-        <v>1.5</v>
-      </c>
-      <c r="S11">
-        <v>2.92</v>
-      </c>
-      <c r="T11">
-        <v>2.48</v>
-      </c>
-      <c r="U11">
-        <v>1.64</v>
-      </c>
-      <c r="V11">
-        <v>1.06</v>
-      </c>
       <c r="W11">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="X11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y11">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z11">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AD11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AE11">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="AF11">
         <v>6.8</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI11">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="AJ11">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AK11">
         <v>15</v>
@@ -3322,79 +3322,79 @@
         <v>50</v>
       </c>
       <c r="AM11">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AN11">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AP11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
+        <v>42</v>
+      </c>
+      <c r="AR11">
+        <v>55</v>
+      </c>
+      <c r="AS11">
+        <v>60</v>
+      </c>
+      <c r="AT11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11">
+        <v>17</v>
+      </c>
+      <c r="AV11">
+        <v>55</v>
+      </c>
+      <c r="AW11">
+        <v>26</v>
+      </c>
+      <c r="AX11">
+        <v>6.6</v>
+      </c>
+      <c r="AY11">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11">
+        <v>46</v>
+      </c>
+      <c r="BA11">
         <v>34</v>
       </c>
-      <c r="AR11">
-        <v>100</v>
-      </c>
-      <c r="AS11">
-        <v>30</v>
-      </c>
-      <c r="AT11">
-        <v>7.8</v>
-      </c>
-      <c r="AU11">
+      <c r="BB11">
+        <v>7.2</v>
+      </c>
+      <c r="BC11">
         <v>13.5</v>
       </c>
-      <c r="AV11">
-        <v>50</v>
-      </c>
-      <c r="AW11">
-        <v>29</v>
-      </c>
-      <c r="AX11">
-        <v>6.4</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>40</v>
-      </c>
-      <c r="BA11">
-        <v>38</v>
-      </c>
-      <c r="BB11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC11">
-        <v>14</v>
-      </c>
       <c r="BD11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE11">
         <v>150</v>
       </c>
       <c r="BF11">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BG11">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BH11">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI11">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BJ11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BK11">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BL11">
         <v>240</v>
@@ -3406,43 +3406,43 @@
         <v>3.5</v>
       </c>
       <c r="BO11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BQ11">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS11">
         <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BU11">
         <v>14</v>
       </c>
       <c r="BV11">
+        <v>220</v>
+      </c>
+      <c r="BW11">
+        <v>16</v>
+      </c>
+      <c r="BX11">
         <v>170</v>
       </c>
-      <c r="BW11">
-        <v>14.5</v>
-      </c>
-      <c r="BX11">
-        <v>140</v>
-      </c>
       <c r="BY11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BZ11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="s">
         <v>145</v>
@@ -3465,16 +3465,16 @@
         <v>130</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G12">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>3.55</v>
@@ -3483,109 +3483,109 @@
         <v>3.6</v>
       </c>
       <c r="L12">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M12">
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O12">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P12">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q12">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T12">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U12">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="V12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X12">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y12">
         <v>14.5</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE12">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI12">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12">
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO12">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP12">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
         <v>13.5</v>
       </c>
       <c r="AR12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS12">
         <v>120</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU12">
         <v>7.8</v>
@@ -3597,13 +3597,13 @@
         <v>85</v>
       </c>
       <c r="AX12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA12">
         <v>90</v>
@@ -3612,34 +3612,34 @@
         <v>18</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE12">
         <v>120</v>
       </c>
       <c r="BF12">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BG12">
         <v>100</v>
       </c>
       <c r="BH12">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="BI12">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ12">
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL12">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="BM12">
         <v>140</v>
@@ -3648,43 +3648,43 @@
         <v>4.1</v>
       </c>
       <c r="BO12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP12">
         <v>14</v>
       </c>
       <c r="BQ12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR12">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BS12">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BT12">
         <v>8.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BW12">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY12">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="CB12" t="s">
         <v>145</v>
@@ -3713,19 +3713,19 @@
         <v>4.8</v>
       </c>
       <c r="H13">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I13">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J13">
+        <v>3.65</v>
+      </c>
+      <c r="K13">
         <v>3.7</v>
       </c>
-      <c r="K13">
-        <v>3.75</v>
-      </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M13">
         <v>1.09</v>
@@ -3737,7 +3737,7 @@
         <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
         <v>2.24</v>
@@ -3752,7 +3752,7 @@
         <v>2.06</v>
       </c>
       <c r="U13">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V13">
         <v>2.06</v>
@@ -3767,13 +3767,13 @@
         <v>7.4</v>
       </c>
       <c r="Z13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC13">
         <v>8.199999999999999</v>
@@ -3788,13 +3788,13 @@
         <v>34</v>
       </c>
       <c r="AG13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH13">
         <v>22</v>
       </c>
       <c r="AI13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ13">
         <v>120</v>
@@ -3803,13 +3803,13 @@
         <v>65</v>
       </c>
       <c r="AL13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM13">
         <v>140</v>
       </c>
       <c r="AN13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO13">
         <v>17</v>
@@ -3830,7 +3830,7 @@
         <v>13</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
         <v>10</v>
@@ -3842,10 +3842,10 @@
         <v>30</v>
       </c>
       <c r="AY13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA13">
         <v>40</v>
@@ -3857,25 +3857,25 @@
         <v>60</v>
       </c>
       <c r="BD13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE13">
         <v>120</v>
       </c>
       <c r="BF13">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BG13">
         <v>16</v>
       </c>
       <c r="BH13">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BI13">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK13">
         <v>9.800000000000001</v>
@@ -3887,7 +3887,7 @@
         <v>140</v>
       </c>
       <c r="BN13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO13">
         <v>7.2</v>
@@ -3896,13 +3896,13 @@
         <v>55</v>
       </c>
       <c r="BQ13">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BR13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BT13">
         <v>4.3</v>
@@ -3920,13 +3920,13 @@
         <v>40</v>
       </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13">
         <v>38</v>
       </c>
       <c r="CA13">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="CB13" t="s">
         <v>145</v>
@@ -3949,25 +3949,25 @@
         <v>132</v>
       </c>
       <c r="F14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>5.2</v>
       </c>
       <c r="H14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I14">
         <v>1.7</v>
       </c>
       <c r="J14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
         <v>4.8</v>
       </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -3976,22 +3976,22 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T14">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U14">
         <v>2.26</v>
@@ -4003,19 +4003,19 @@
         <v>1.23</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AB14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
@@ -4030,7 +4030,7 @@
         <v>48</v>
       </c>
       <c r="AG14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH14">
         <v>20</v>
@@ -4042,7 +4042,7 @@
         <v>900</v>
       </c>
       <c r="AK14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL14">
         <v>60</v>
@@ -4054,10 +4054,10 @@
         <v>55</v>
       </c>
       <c r="AO14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
         <v>10</v>
@@ -4072,7 +4072,7 @@
         <v>18.5</v>
       </c>
       <c r="AU14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14">
         <v>9</v>
@@ -4087,7 +4087,7 @@
         <v>17.5</v>
       </c>
       <c r="AZ14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA14">
         <v>25</v>
@@ -4099,25 +4099,25 @@
         <v>46</v>
       </c>
       <c r="BD14">
+        <v>50</v>
+      </c>
+      <c r="BE14">
+        <v>75</v>
+      </c>
+      <c r="BF14">
         <v>44</v>
       </c>
-      <c r="BE14">
-        <v>70</v>
-      </c>
-      <c r="BF14">
-        <v>42</v>
-      </c>
       <c r="BG14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH14">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BI14">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BJ14">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
         <v>7</v>
@@ -4129,7 +4129,7 @@
         <v>8</v>
       </c>
       <c r="BN14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO14">
         <v>6.4</v>
@@ -4138,16 +4138,16 @@
         <v>42</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU14">
         <v>4.1</v>
@@ -4156,7 +4156,7 @@
         <v>11</v>
       </c>
       <c r="BW14">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX14">
         <v>23</v>
@@ -4165,7 +4165,7 @@
         <v>11</v>
       </c>
       <c r="BZ14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CA14">
         <v>12</v>
@@ -4191,100 +4191,100 @@
         <v>133</v>
       </c>
       <c r="F15">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G15">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I15">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T15">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
         <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W15">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X15">
         <v>20</v>
       </c>
       <c r="Y15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA15">
         <v>25</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15">
         <v>10.5</v>
       </c>
       <c r="AE15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI15">
         <v>32</v>
       </c>
       <c r="AJ15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL15">
         <v>46</v>
@@ -4299,7 +4299,7 @@
         <v>11</v>
       </c>
       <c r="AP15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4311,10 +4311,10 @@
         <v>21</v>
       </c>
       <c r="AT15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15">
         <v>9.6</v>
@@ -4326,13 +4326,13 @@
         <v>27</v>
       </c>
       <c r="AY15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15">
         <v>65</v>
@@ -4344,49 +4344,49 @@
         <v>40</v>
       </c>
       <c r="BE15">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG15">
         <v>10</v>
       </c>
       <c r="BH15">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI15">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ15">
         <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM15">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN15">
         <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP15">
         <v>34</v>
       </c>
       <c r="BQ15">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT15">
         <v>5</v>
@@ -4395,22 +4395,22 @@
         <v>4.4</v>
       </c>
       <c r="BV15">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BW15">
         <v>10.5</v>
       </c>
       <c r="BX15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BY15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB15" t="s">
         <v>145</v>
@@ -4463,7 +4463,7 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q16">
         <v>1.54</v>
@@ -4475,13 +4475,13 @@
         <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W16">
         <v>1.76</v>
@@ -4493,7 +4493,7 @@
         <v>21</v>
       </c>
       <c r="Z16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA16">
         <v>65</v>
@@ -4502,7 +4502,7 @@
         <v>17.5</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
         <v>14</v>
@@ -4511,7 +4511,7 @@
         <v>32</v>
       </c>
       <c r="AF16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG16">
         <v>11.5</v>
@@ -4523,13 +4523,13 @@
         <v>36</v>
       </c>
       <c r="AJ16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK16">
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM16">
         <v>65</v>
@@ -4541,22 +4541,22 @@
         <v>19</v>
       </c>
       <c r="AP16">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16">
         <v>24</v>
       </c>
       <c r="AT16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU16">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV16">
         <v>12</v>
@@ -4583,7 +4583,7 @@
         <v>17.5</v>
       </c>
       <c r="BD16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE16">
         <v>36</v>
@@ -4592,10 +4592,10 @@
         <v>9.6</v>
       </c>
       <c r="BG16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH16">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI16">
         <v>4.1</v>
@@ -4610,28 +4610,28 @@
         <v>85</v>
       </c>
       <c r="BM16">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BN16">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP16">
         <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS16">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU16">
         <v>6</v>
@@ -4640,19 +4640,19 @@
         <v>26</v>
       </c>
       <c r="BW16">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="BX16">
         <v>32</v>
       </c>
       <c r="BY16">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BZ16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA16">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="CB16" t="s">
         <v>145</v>
@@ -4675,19 +4675,19 @@
         <v>135</v>
       </c>
       <c r="F17">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="G17">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I17">
+        <v>4.3</v>
+      </c>
+      <c r="J17">
         <v>4.1</v>
-      </c>
-      <c r="J17">
-        <v>4</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4696,46 +4696,46 @@
         <v>1.31</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
         <v>1.58</v>
       </c>
       <c r="S17">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T17">
         <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA17">
         <v>95</v>
@@ -4747,10 +4747,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE17">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF17">
         <v>14.5</v>
@@ -4762,22 +4762,22 @@
         <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM17">
         <v>65</v>
       </c>
       <c r="AN17">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO17">
         <v>32</v>
@@ -4786,55 +4786,55 @@
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AS17">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU17">
         <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE17">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BF17">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH17">
         <v>4.2</v>
@@ -4846,55 +4846,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL17">
         <v>95</v>
       </c>
       <c r="BM17">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR17">
         <v>26</v>
       </c>
       <c r="BS17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT17">
         <v>7.6</v>
       </c>
       <c r="BU17">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="s">
         <v>145</v>
@@ -4920,142 +4920,142 @@
         <v>2.16</v>
       </c>
       <c r="G18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M18">
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R18">
+        <v>1.6</v>
+      </c>
+      <c r="S18">
+        <v>2.6</v>
+      </c>
+      <c r="T18">
         <v>1.55</v>
       </c>
-      <c r="S18">
-        <v>2.68</v>
-      </c>
-      <c r="T18">
-        <v>1.59</v>
-      </c>
       <c r="U18">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W18">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
         <v>28</v>
       </c>
       <c r="AA18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD18">
         <v>15</v>
       </c>
       <c r="AE18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF18">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI18">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ18">
         <v>29</v>
       </c>
       <c r="AK18">
+        <v>21</v>
+      </c>
+      <c r="AL18">
+        <v>29</v>
+      </c>
+      <c r="AM18">
+        <v>75</v>
+      </c>
+      <c r="AN18">
+        <v>11.5</v>
+      </c>
+      <c r="AO18">
         <v>22</v>
       </c>
-      <c r="AL18">
-        <v>32</v>
-      </c>
-      <c r="AM18">
-        <v>200</v>
-      </c>
-      <c r="AN18">
-        <v>12</v>
-      </c>
-      <c r="AO18">
-        <v>26</v>
-      </c>
       <c r="AP18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR18">
         <v>22</v>
       </c>
       <c r="AS18">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AT18">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV18">
         <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AX18">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA18">
         <v>29</v>
@@ -5064,55 +5064,55 @@
         <v>21</v>
       </c>
       <c r="BC18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE18">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BF18">
         <v>10</v>
       </c>
       <c r="BG18">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI18">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ18">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL18">
         <v>95</v>
       </c>
       <c r="BM18">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BN18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP18">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BQ18">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BR18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS18">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BT18">
         <v>7.2</v>
@@ -5121,22 +5121,22 @@
         <v>6</v>
       </c>
       <c r="BV18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW18">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BX18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY18">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BZ18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA18">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5162,7 +5162,7 @@
         <v>2.3</v>
       </c>
       <c r="G19">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H19">
         <v>3.05</v>
@@ -5183,16 +5183,16 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R19">
         <v>1.47</v>
@@ -5201,25 +5201,25 @@
         <v>2.98</v>
       </c>
       <c r="T19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
         <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X19">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y19">
         <v>15.5</v>
       </c>
       <c r="Z19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA19">
         <v>65</v>
@@ -5246,7 +5246,7 @@
         <v>16.5</v>
       </c>
       <c r="AI19">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ19">
         <v>34</v>
@@ -5255,7 +5255,7 @@
         <v>24</v>
       </c>
       <c r="AL19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM19">
         <v>90</v>
@@ -5306,10 +5306,10 @@
         <v>25</v>
       </c>
       <c r="BC19">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE19">
         <v>46</v>
@@ -5330,55 +5330,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK19">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BL19">
         <v>110</v>
       </c>
       <c r="BM19">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN19">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO19">
         <v>4.8</v>
       </c>
       <c r="BP19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS19">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BT19">
         <v>6.8</v>
       </c>
       <c r="BU19">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BW19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BX19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY19">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA19">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB19" t="s">
         <v>145</v>
@@ -5401,22 +5401,22 @@
         <v>138</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G20">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I20">
         <v>4.7</v>
       </c>
       <c r="J20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>1.27</v>
@@ -5428,16 +5428,16 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S20">
         <v>2.34</v>
@@ -5446,13 +5446,13 @@
         <v>1.56</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V20">
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X20">
         <v>27</v>
@@ -5467,7 +5467,7 @@
         <v>310</v>
       </c>
       <c r="AB20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC20">
         <v>10.5</v>
@@ -5479,16 +5479,16 @@
         <v>50</v>
       </c>
       <c r="AF20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG20">
         <v>11</v>
       </c>
       <c r="AH20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI20">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ20">
         <v>21</v>
@@ -5503,19 +5503,19 @@
         <v>60</v>
       </c>
       <c r="AN20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO20">
         <v>34</v>
       </c>
       <c r="AP20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS20">
         <v>44</v>
@@ -5524,7 +5524,7 @@
         <v>12</v>
       </c>
       <c r="AU20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV20">
         <v>16.5</v>
@@ -5533,10 +5533,10 @@
         <v>34</v>
       </c>
       <c r="AX20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20">
         <v>13.5</v>
@@ -5563,25 +5563,25 @@
         <v>25</v>
       </c>
       <c r="BH20">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BI20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK20">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BL20">
         <v>85</v>
       </c>
       <c r="BM20">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BO20">
         <v>4.4</v>
@@ -5590,37 +5590,37 @@
         <v>13</v>
       </c>
       <c r="BQ20">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BR20">
         <v>23</v>
       </c>
       <c r="BS20">
+        <v>7.2</v>
+      </c>
+      <c r="BT20">
+        <v>8.4</v>
+      </c>
+      <c r="BU20">
         <v>4.9</v>
       </c>
-      <c r="BT20">
-        <v>9.4</v>
-      </c>
-      <c r="BU20">
-        <v>3.85</v>
-      </c>
       <c r="BV20">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BW20">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX20">
         <v>38</v>
       </c>
       <c r="BY20">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ20">
         <v>13.5</v>
       </c>
       <c r="CA20">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5646,16 +5646,16 @@
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H21">
         <v>3.35</v>
       </c>
       <c r="I21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
         <v>4</v>
@@ -5679,16 +5679,16 @@
         <v>1.74</v>
       </c>
       <c r="R21">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T21">
         <v>1.64</v>
       </c>
       <c r="U21">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
         <v>1.4</v>
@@ -5703,10 +5703,10 @@
         <v>16.5</v>
       </c>
       <c r="Z21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA21">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AB21">
         <v>12</v>
@@ -5727,16 +5727,16 @@
         <v>11</v>
       </c>
       <c r="AH21">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ21">
         <v>30</v>
       </c>
       <c r="AK21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21">
         <v>36</v>
@@ -5745,7 +5745,7 @@
         <v>85</v>
       </c>
       <c r="AN21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO21">
         <v>34</v>
@@ -5775,7 +5775,7 @@
         <v>30</v>
       </c>
       <c r="AX21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY21">
         <v>9.6</v>
@@ -5784,22 +5784,22 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BB21">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC21">
         <v>18</v>
       </c>
       <c r="BD21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE21">
         <v>46</v>
       </c>
       <c r="BF21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG21">
         <v>24</v>
@@ -5820,7 +5820,7 @@
         <v>110</v>
       </c>
       <c r="BM21">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN21">
         <v>5.9</v>
@@ -5832,37 +5832,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BS21">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT21">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BU21">
         <v>6</v>
       </c>
       <c r="BV21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BW21">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY21">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ21">
         <v>21</v>
       </c>
       <c r="CA21">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>
@@ -5885,22 +5885,22 @@
         <v>140</v>
       </c>
       <c r="F22">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G22">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H22">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I22">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>1.25</v>
@@ -5915,52 +5915,52 @@
         <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q22">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R22">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S22">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T22">
+        <v>1.48</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
         <v>1.5</v>
       </c>
-      <c r="U22">
-        <v>2.88</v>
-      </c>
-      <c r="V22">
-        <v>1.51</v>
-      </c>
       <c r="W22">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X22">
         <v>29</v>
       </c>
       <c r="Y22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z22">
         <v>26</v>
       </c>
       <c r="AA22">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB22">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF22">
         <v>21</v>
@@ -5969,13 +5969,13 @@
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK22">
         <v>23</v>
@@ -5984,37 +5984,37 @@
         <v>27</v>
       </c>
       <c r="AM22">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP22">
         <v>25</v>
       </c>
       <c r="AQ22">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS22">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU22">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX22">
         <v>18</v>
@@ -6026,10 +6026,10 @@
         <v>13</v>
       </c>
       <c r="BA22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC22">
         <v>19</v>
@@ -6038,73 +6038,73 @@
         <v>23</v>
       </c>
       <c r="BE22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF22">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH22">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BI22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22">
         <v>9.4</v>
       </c>
       <c r="BK22">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BL22">
         <v>70</v>
       </c>
       <c r="BM22">
+        <v>6</v>
+      </c>
+      <c r="BN22">
+        <v>6.4</v>
+      </c>
+      <c r="BO22">
+        <v>5.4</v>
+      </c>
+      <c r="BP22">
+        <v>17.5</v>
+      </c>
+      <c r="BQ22">
+        <v>4.7</v>
+      </c>
+      <c r="BR22">
+        <v>24</v>
+      </c>
+      <c r="BS22">
         <v>5.1</v>
-      </c>
-      <c r="BN22">
-        <v>7</v>
-      </c>
-      <c r="BO22">
-        <v>5.2</v>
-      </c>
-      <c r="BP22">
-        <v>18</v>
-      </c>
-      <c r="BQ22">
-        <v>4.2</v>
-      </c>
-      <c r="BR22">
-        <v>25</v>
-      </c>
-      <c r="BS22">
-        <v>4.5</v>
       </c>
       <c r="BT22">
         <v>7.6</v>
       </c>
       <c r="BU22">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW22">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BX22">
         <v>27</v>
       </c>
       <c r="BY22">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BZ22">
         <v>15</v>
       </c>
       <c r="CA22">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="s">
         <v>145</v>
@@ -6127,64 +6127,64 @@
         <v>141</v>
       </c>
       <c r="F23">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H23">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I23">
         <v>1.99</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R23">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>2</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y23">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z23">
         <v>13</v>
@@ -6196,16 +6196,16 @@
         <v>18.5</v>
       </c>
       <c r="AC23">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD23">
         <v>10.5</v>
       </c>
       <c r="AE23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG23">
         <v>16.5</v>
@@ -6214,40 +6214,40 @@
         <v>18.5</v>
       </c>
       <c r="AI23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL23">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR23">
         <v>11.5</v>
       </c>
       <c r="AS23">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU23">
         <v>8</v>
@@ -6259,10 +6259,10 @@
         <v>17.5</v>
       </c>
       <c r="AX23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY23">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ23">
         <v>15.5</v>
@@ -6277,76 +6277,76 @@
         <v>34</v>
       </c>
       <c r="BD23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE23">
         <v>60</v>
       </c>
       <c r="BF23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BG23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH23">
+        <v>4.4</v>
+      </c>
+      <c r="BI23">
+        <v>3.2</v>
+      </c>
+      <c r="BJ23">
         <v>10.5</v>
       </c>
-      <c r="BH23">
-        <v>4.1</v>
-      </c>
-      <c r="BI23">
-        <v>3.05</v>
-      </c>
-      <c r="BJ23">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK23">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BL23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM23">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BN23">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO23">
         <v>6</v>
       </c>
       <c r="BP23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ23">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BT23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BU23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW23">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY23">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BZ23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA23">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB23" t="s">
         <v>145</v>
@@ -6378,10 +6378,10 @@
         <v>3.7</v>
       </c>
       <c r="I24">
+        <v>3.9</v>
+      </c>
+      <c r="J24">
         <v>3.95</v>
-      </c>
-      <c r="J24">
-        <v>3.9</v>
       </c>
       <c r="K24">
         <v>4.2</v>
@@ -6393,7 +6393,7 @@
         <v>1.05</v>
       </c>
       <c r="N24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O24">
         <v>1.24</v>
@@ -6402,13 +6402,13 @@
         <v>2.28</v>
       </c>
       <c r="Q24">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R24">
         <v>1.5</v>
       </c>
       <c r="S24">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T24">
         <v>1.64</v>
@@ -6417,7 +6417,7 @@
         <v>2.34</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
         <v>1.94</v>
@@ -6432,7 +6432,7 @@
         <v>85</v>
       </c>
       <c r="AA24">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB24">
         <v>12</v>
@@ -6459,7 +6459,7 @@
         <v>50</v>
       </c>
       <c r="AJ24">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK24">
         <v>21</v>
@@ -6471,7 +6471,7 @@
         <v>200</v>
       </c>
       <c r="AN24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO24">
         <v>40</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="AX24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY24">
         <v>9.4</v>
@@ -6534,7 +6534,7 @@
         <v>4.5</v>
       </c>
       <c r="BI24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ24">
         <v>10.5</v>
@@ -6555,13 +6555,13 @@
         <v>4</v>
       </c>
       <c r="BP24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ24">
         <v>10</v>
       </c>
       <c r="BR24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS24">
         <v>18</v>
@@ -6570,25 +6570,25 @@
         <v>8.4</v>
       </c>
       <c r="BU24">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV24">
         <v>34</v>
       </c>
       <c r="BW24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BX24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY24">
         <v>26</v>
       </c>
       <c r="BZ24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB24" t="s">
         <v>145</v>
@@ -6614,7 +6614,7 @@
         <v>1.27</v>
       </c>
       <c r="G25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H25">
         <v>14.5</v>
@@ -6635,25 +6635,25 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
         <v>1.27</v>
       </c>
       <c r="P25">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q25">
         <v>1.82</v>
       </c>
       <c r="R25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S25">
         <v>3.1</v>
       </c>
       <c r="T25">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U25">
         <v>1.63</v>
@@ -6662,7 +6662,7 @@
         <v>1.06</v>
       </c>
       <c r="W25">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X25">
         <v>19</v>
@@ -6683,7 +6683,7 @@
         <v>14.5</v>
       </c>
       <c r="AD25">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE25">
         <v>370</v>
@@ -6701,16 +6701,16 @@
         <v>310</v>
       </c>
       <c r="AJ25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AK25">
         <v>16</v>
       </c>
       <c r="AL25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN25">
         <v>5.4</v>
@@ -6722,13 +6722,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ25">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AR25">
         <v>15.5</v>
       </c>
       <c r="AS25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT25">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>46</v>
       </c>
       <c r="AW25">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX25">
         <v>6.2</v>
@@ -6752,7 +6752,7 @@
         <v>36</v>
       </c>
       <c r="BA25">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BB25">
         <v>8</v>
@@ -6764,16 +6764,16 @@
         <v>44</v>
       </c>
       <c r="BE25">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG25">
         <v>15</v>
       </c>
       <c r="BH25">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI25">
         <v>3.5</v>
@@ -6782,13 +6782,13 @@
         <v>15.5</v>
       </c>
       <c r="BK25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL25">
         <v>300</v>
       </c>
       <c r="BM25">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN25">
         <v>3.45</v>
@@ -6800,37 +6800,37 @@
         <v>7</v>
       </c>
       <c r="BQ25">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT25">
         <v>18.5</v>
       </c>
       <c r="BU25">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV25">
         <v>200</v>
       </c>
       <c r="BW25">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX25">
         <v>170</v>
       </c>
       <c r="BY25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ25">
         <v>12.5</v>
       </c>
       <c r="CA25">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB25" t="s">
         <v>145</v>
@@ -6853,19 +6853,19 @@
         <v>144</v>
       </c>
       <c r="F26">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G26">
         <v>2.48</v>
       </c>
       <c r="H26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
         <v>3.5</v>
@@ -6886,13 +6886,13 @@
         <v>1.79</v>
       </c>
       <c r="Q26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R26">
         <v>1.3</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T26">
         <v>1.86</v>
@@ -6928,7 +6928,7 @@
         <v>15.5</v>
       </c>
       <c r="AE26">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>15.5</v>
@@ -6946,7 +6946,7 @@
         <v>40</v>
       </c>
       <c r="AK26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL26">
         <v>48</v>
@@ -6961,118 +6961,118 @@
         <v>48</v>
       </c>
       <c r="AP26">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AS26">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT26">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU26">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW26">
         <v>29</v>
       </c>
       <c r="AX26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26">
         <v>16</v>
       </c>
       <c r="BA26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB26">
         <v>24</v>
       </c>
       <c r="BC26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE26">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF26">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG26">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BH26">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
         <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>145</v>
